--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/tmp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F339F1DB6F1496FA3F0FA0F455E7AE3AF9DEE1D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_F325CED3A12F6FEA0D0EA0F455E7AE3A9952A318" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -536,13 +536,13 @@
     <t>継続時間</t>
   </si>
   <si>
-    <t>https://yaizu-smartcity.jp/yaizu-shizuoka-takashio-keizoku/{z}/{x}/{y}.png</t>
+    <t>https://yaizu-smartcity.jp/tiles/yaizu-shizuoka-takashio-keizoku/{z}/{x}/{y}.png</t>
   </si>
   <si>
     <t>浸水深</t>
   </si>
   <si>
-    <t>https://yaizu-smartcity.jp/yaizu-shizuoka-takashio-shinsuishin/{z}/{x}/{y}.png</t>
+    <t>https://yaizu-smartcity.jp/tiles/yaizu-shizuoka-takashio-shinsuishin/{z}/{x}/{y}.png</t>
   </si>
   <si>
     <t>家屋倒壊等氾濫想定区域（流体力）</t>
@@ -551,13 +551,13 @@
     <t>焼津市</t>
   </si>
   <si>
-    <t>https://yaizu-smartcity.jp/yaizu-kaoku-tokai-hanranryu/tiles.json</t>
+    <t>https://yaizu-smartcity.jp/tiles/yaizu-kaoku-tokai-hanranryu/tiles.json</t>
   </si>
   <si>
     <t>家屋倒壊等氾濫想定区域（越波）</t>
   </si>
   <si>
-    <t>https://yaizu-smartcity.jp/yaizu-kaoku-tokai-eppaha/tiles.json</t>
+    <t>https://yaizu-smartcity.jp/tiles/yaizu-kaoku-tokai-eppaha/tiles.json</t>
   </si>
   <si>
     <t>内水浸水想定区域(公共下水道区域内)</t>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/tmp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/naoppy/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F325CED3A12F6FEA0D0EA0F455E7AE3A9952A318" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68593DFF-3687-0B40-8CB2-FA3602D7227B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6540" yWindow="-20940" windowWidth="27920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="メニュー構造" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="630">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -530,1388 +530,1415 @@
     <t>https://yaizu-smartcity.jp/tiles/%E5%A4%A7%E6%B4%A5%E8%B0%B7%E5%B7%9D_%E5%AE%B6%E5%B1%8B%E5%80%92%E5%A3%8A%E7%AD%89%E6%B0%BE%E6%BF%AB%E6%83%B3%E5%AE%9A%EF%BC%88%E6%B2%B3%E5%B2%B8%E4%BE%B5%E9%A3%9F%EF%BC%89/tiles.json</t>
   </si>
   <si>
-    <t>高潮浸水想定区域</t>
-  </si>
-  <si>
-    <t>継続時間</t>
+    <t>家屋倒壊等氾濫想定区域（越波）</t>
+  </si>
+  <si>
+    <t>内水浸水想定区域(公共下水道区域内)</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%86%85%E6%B0%B4%E6%B5%B8%E6%B0%B4%E6%83%B3%E5%AE%9A%E5%8C%BA%E5%9F%9F(%E5%85%AC%E5%85%B1%E4%B8%8B%E6%B0%B4%E9%81%93%E5%8C%BA%E5%9F%9F%E5%86%85)/tiles.json</t>
+  </si>
+  <si>
+    <t>浸水履歴（平成9年～令和5年）</t>
+  </si>
+  <si>
+    <t>統合（平成9年～令和5年）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E7%B5%B1%E5%90%88/tiles.json</t>
+  </si>
+  <si>
+    <t>令和4年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E4%BB%A4%E5%92%8C4%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>令和元年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E4%BB%A4%E5%92%8C%E5%85%83%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成29年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9029%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成26年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9026%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成25年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9025%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成24年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9024%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成23年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9023%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成22年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9022%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成20年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9020%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成19年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9019%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成18年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9018%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成17年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9017%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成16年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9016%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成15年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9015%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成14年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9014%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成13年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9013%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成12年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9012%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成11年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9011%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成10年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9010%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>平成9年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%909%E5%B9%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>観光・イベント</t>
+  </si>
+  <si>
+    <t>お食事</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%81%8A%E9%A3%9F%E4%BA%8B/tiles.json</t>
+  </si>
+  <si>
+    <t>restaurant</t>
+  </si>
+  <si>
+    <t>海の幸グルメマップ</t>
+  </si>
+  <si>
+    <t>ミナミマグロ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E6%B5%B7%E3%81%AE%E5%B9%B8%E3%82%B0%E3%83%AB%E3%83%A1%E3%83%9E%E3%83%83%E3%83%97_%E3%83%9F%E3%83%8A%E3%83%9F%E3%83%9E%E3%82%B0%E3%83%AD/tiles.json</t>
+  </si>
+  <si>
+    <t>fish</t>
+  </si>
+  <si>
+    <t>カツオ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E6%B5%B7%E3%81%AE%E5%B9%B8%E3%82%B0%E3%83%AB%E3%83%A1%E3%83%9E%E3%83%83%E3%83%97_%E3%82%AB%E3%83%84%E3%82%AA/tiles.json</t>
+  </si>
+  <si>
+    <t>サバ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E6%B5%B7%E3%81%AE%E5%B9%B8%E3%82%B0%E3%83%AB%E3%83%A1%E3%83%9E%E3%83%83%E3%83%97_%E3%82%B5%E3%83%90/tiles.json</t>
+  </si>
+  <si>
+    <t>サクラエビ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E6%B5%B7%E3%81%AE%E5%B9%B8%E3%82%B0%E3%83%AB%E3%83%A1%E3%83%9E%E3%83%83%E3%83%97_%E3%82%B5%E3%82%AF%E3%83%A9%E3%82%A8%E3%83%93/tiles.json</t>
+  </si>
+  <si>
+    <t>シラス</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E6%B5%B7%E3%81%AE%E5%B9%B8%E3%82%B0%E3%83%AB%E3%83%A1%E3%83%9E%E3%83%83%E3%83%97_%E3%82%B7%E3%83%A9%E3%82%B9/tiles.json</t>
+  </si>
+  <si>
+    <t>お買い物</t>
+  </si>
+  <si>
+    <t>ショップ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%82%B7%E3%83%A7%E3%83%83%E3%83%97/tiles.json</t>
+  </si>
+  <si>
+    <t>shopping</t>
+  </si>
+  <si>
+    <t>工場併設直売所</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%B7%A5%E5%A0%B4%E4%BD%B5%E8%A8%AD%E7%9B%B4%E5%A3%B2%E6%89%80%E4%B8%80%E8%A6%A7/tiles.json</t>
+  </si>
+  <si>
+    <t>factory-shop</t>
+  </si>
+  <si>
+    <t>体験・見どころ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E4%BD%93%E9%A8%93%E3%83%BB%E8%A6%8B%E3%81%A9%E3%81%93%E3%82%8D/tiles.json</t>
+  </si>
+  <si>
+    <t>tourist-facility</t>
+  </si>
+  <si>
+    <t>日帰り温泉・足湯</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%97%A5%E5%B8%B0%E3%82%8A%E6%B8%A9%E6%B3%89%E3%83%BB%E8%B6%B3%E6%B9%AF/tiles.json</t>
+  </si>
+  <si>
+    <t>hotspring</t>
+  </si>
+  <si>
+    <t>宿泊</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%AE%BF%E6%B3%8A/tiles.json</t>
+  </si>
+  <si>
+    <t>hotel</t>
+  </si>
+  <si>
+    <t>移動・その他</t>
+  </si>
+  <si>
+    <t>レンタカー</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%AC%E3%83%B3%E3%82%BF%E3%82%AB%E3%83%BC/tiles.json</t>
+  </si>
+  <si>
+    <t>car-rental</t>
+  </si>
+  <si>
+    <t>その他</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%81%9D%E3%81%AE%E4%BB%96/tiles.json</t>
+  </si>
+  <si>
+    <t>#66cdaa</t>
+  </si>
+  <si>
+    <t>市営駐車場・駐輪場</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%B8%82%E5%96%B6%E9%A7%90%E8%BB%8A%E5%A0%B4%E3%83%BB%E9%A7%90%E8%BC%AA%E5%A0%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>parking</t>
+  </si>
+  <si>
+    <t>焼津観光マップ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E8%A6%B3%E5%85%89%E3%83%9E%E3%83%83%E3%83%97/tiles.json</t>
+  </si>
+  <si>
+    <t>#7385e5</t>
+  </si>
+  <si>
+    <t>高草山ハイキングマップ</t>
+  </si>
+  <si>
+    <t>高草山コース　1</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
+  </si>
+  <si>
+    <t>#009f45</t>
+  </si>
+  <si>
+    <t>高草山コース　2</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-2%E5%9D%82%E6%9C%AC_%E9%AB%98%E8%8D%89%E5%B1%B1%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
+  </si>
+  <si>
+    <t>#ef8da9</t>
+  </si>
+  <si>
+    <t>高草山コース　3</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-3%E7%84%BC%E6%B4%A5%E5%B8%82_%E9%96%A2%E6%96%B9_%E9%AB%98%E8%8D%89%E5%B1%B1%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
+  </si>
+  <si>
+    <t>#179fac</t>
+  </si>
+  <si>
+    <t>高草山コース　4</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-4%E8%97%A4%E6%9E%9D%E5%B8%82_%E4%B8%89%E8%BC%AA_%E9%AB%98%E8%8D%89%E5%B1%B1%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
+  </si>
+  <si>
+    <t>#7ac24c</t>
+  </si>
+  <si>
+    <t>満観峰コース</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_2%E7%84%BC%E6%B4%A5%E5%B8%82_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E6%BA%80%E8%A6%B3%E5%B3%B0%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
+  </si>
+  <si>
+    <t>#3d73ba</t>
+  </si>
+  <si>
+    <t>花沢山コース　1</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
+  </si>
+  <si>
+    <t>#b664a6</t>
+  </si>
+  <si>
+    <t>花沢山コース　2</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
+  </si>
+  <si>
+    <t>#dab06d</t>
+  </si>
+  <si>
+    <t>ハイキングスポット</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_%E5%9C%B0%E7%82%B9/tiles.json</t>
+  </si>
+  <si>
+    <t>brown-marker</t>
+  </si>
+  <si>
+    <t>トイレ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_%E5%9C%B0%E7%82%B9_%E3%83%88%E3%82%A4%E3%83%AC/tiles.json</t>
+  </si>
+  <si>
+    <t>public-toilets</t>
+  </si>
+  <si>
+    <t>駐車場・バス停</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_%E5%9C%B0%E7%82%B9_%E9%A7%90%E8%BB%8A%E5%A0%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>#ffffff</t>
+  </si>
+  <si>
+    <t>#2F2011</t>
+  </si>
+  <si>
+    <t>まちづくり</t>
+  </si>
+  <si>
+    <t>航空写真（令和5年度）</t>
+  </si>
+  <si>
+    <t>https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5</t>
+  </si>
+  <si>
+    <t>都市計画図</t>
+  </si>
+  <si>
+    <t>市街化区域界・市街化調整区域界</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/市街化区域界_市街化調整区域界/tiles.json</t>
+  </si>
+  <si>
+    <t>#cd853f</t>
+  </si>
+  <si>
+    <t>高度利用地区</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/高度利用地区/tiles.json</t>
+  </si>
+  <si>
+    <t>#ff6347</t>
+  </si>
+  <si>
+    <t>準防火地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/準防火地域/tiles.json</t>
+  </si>
+  <si>
+    <t>#ffb6c1</t>
+  </si>
+  <si>
+    <t>都市計画道路</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/都市計画道路/tiles.json</t>
+  </si>
+  <si>
+    <t>#ff0000</t>
+  </si>
+  <si>
+    <t>駐車場</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/駐車場/tiles.json</t>
+  </si>
+  <si>
+    <t>#000000</t>
+  </si>
+  <si>
+    <t>公園・緑地</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/公園_緑地/tiles.json</t>
+  </si>
+  <si>
+    <t>#228b22</t>
+  </si>
+  <si>
+    <t>ごみ焼却場</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%81%94%E3%81%BF%E7%84%BC%E5%8D%B4%E5%A0%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>#8b4513</t>
+  </si>
+  <si>
+    <t>し尿処理場</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/し尿処理場/tiles.json</t>
+  </si>
+  <si>
+    <t>#1e90ff</t>
+  </si>
+  <si>
+    <t>地区計画区域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/地区計画区域/tiles.json</t>
+  </si>
+  <si>
+    <t>#2f4f4f</t>
+  </si>
+  <si>
+    <t>土地区画整理事業区域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/土地区画整理事業区域/tiles.json</t>
+  </si>
+  <si>
+    <t>住まいるシティ拠点エリア（都市機能誘導区域）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/住まいるシティ拠点エリア_都市機能誘導区域/tiles.json</t>
+  </si>
+  <si>
+    <t>#00bfff</t>
+  </si>
+  <si>
+    <t>住まいるエリア（居住誘導区域）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/住まいるエリア_居住誘導区域/tiles.json</t>
+  </si>
+  <si>
+    <t>都市計画図（用途地域）</t>
+  </si>
+  <si>
+    <t>第一種低層住居専用地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E7%AC%AC%E4%B8%80%E7%A8%AE%E4%BD%8E%E5%B1%A4%E4%BD%8F%E5%B1%85%E5%B0%82%E7%94%A8%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>#A2D7D4</t>
+  </si>
+  <si>
+    <t>rgb(156,84,160)</t>
+  </si>
+  <si>
+    <t>第一種中高層住居専用地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E7%AC%AC%E4%B8%80%E7%A8%AE%E4%B8%AD%E9%AB%98%E5%B1%A4%E4%BD%8F%E5%B1%85%E5%B0%82%E7%94%A8%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>rgb(198,224,159)</t>
+  </si>
+  <si>
+    <t>第二種中高層住居専用地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E7%AC%AC%E4%BA%8C%E7%A8%AE%E4%B8%AD%E9%AB%98%E5%B1%A4%E4%BD%8F%E5%B1%85%E5%B0%82%E7%94%A8%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>rgb(234,243,220)</t>
+  </si>
+  <si>
+    <t>第一種住居地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E7%AC%AC%E4%B8%80%E7%A8%AE%E4%BD%8F%E5%B1%85%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>rgb(255,246,152)</t>
+  </si>
+  <si>
+    <t>第二種住居地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E7%AC%AC%E4%BA%8C%E7%A8%AE%E4%BD%8F%E5%B1%85%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>rgb(255,253,237)</t>
+  </si>
+  <si>
+    <t>準住居地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E6%BA%96%E4%BD%8F%E5%B1%85%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>rgb(251,194,144)</t>
+  </si>
+  <si>
+    <t>近隣商業地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E8%BF%91%E9%9A%A3%E5%95%86%E6%A5%AD%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>#F7C8DD</t>
+  </si>
+  <si>
+    <t>rgb(179,114,173)</t>
+  </si>
+  <si>
+    <t>商業地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E5%95%86%E6%A5%AD%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>#F29A75</t>
+  </si>
+  <si>
+    <t>準工業地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E6%BA%96%E5%B7%A5%E6%A5%AD%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>rgb(220,201,225)</t>
+  </si>
+  <si>
+    <t>工業地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E5%B7%A5%E6%A5%AD%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>rgb(217,235,248)</t>
+  </si>
+  <si>
+    <t>工業専用地域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E5%B7%A5%E6%A5%AD%E5%B0%82%E7%94%A8%E5%9C%B0%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>rgb(145,201,237)</t>
+  </si>
+  <si>
+    <t>敷地面積の最低限度指定区域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E6%95%B7%E5%9C%B0%E9%9D%A2%E7%A9%8D%E3%81%AE%E6%9C%80%E4%BD%8E%E9%99%90%E5%BA%A6%E6%8C%87%E5%AE%9A%E5%8C%BA%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>#E52187</t>
+  </si>
+  <si>
+    <t>区域図</t>
+  </si>
+  <si>
+    <t>令和6年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%8C%BA%E7%94%BB%E6%95%B4%E7%90%86%E5%9C%B0%E5%9B%B3/tiles.json</t>
+  </si>
+  <si>
+    <t>#93c9a3</t>
+  </si>
+  <si>
+    <t>大正9年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%98%94%E3%81%AE%E7%84%BC%E6%B4%A5%E3%81%A8%E6%AF%94%E3%81%B9%E3%81%A6%E3%81%BF%E3%82%88%E3%81%86/tiles.json</t>
+  </si>
+  <si>
+    <t>#6bbcb3</t>
+  </si>
+  <si>
+    <t>公衆トイレ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%85%AC%E8%A1%86%E3%83%88%E3%82%A4%E3%83%AC%E4%B8%80%E8%A6%A7/tiles.json</t>
+  </si>
+  <si>
+    <t>公園</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%85%AC%E5%9C%92%E4%B8%80%E8%A6%A7/tiles.json</t>
+  </si>
+  <si>
+    <t>park</t>
+  </si>
+  <si>
+    <t>さくら並木</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%81%95%E3%81%8F%E3%82%89%E4%B8%A6%E6%9C%A8%E7%AE%A1%E7%90%86%E8%AA%BF%E6%9B%B8/tiles.json</t>
+  </si>
+  <si>
+    <t>#eb3390</t>
+  </si>
+  <si>
+    <t>住まい</t>
+  </si>
+  <si>
+    <t>固定資産税・路線価図</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/固定資産税_路線価図/tiles.json</t>
+  </si>
+  <si>
+    <t>#1C1C1C</t>
+  </si>
+  <si>
+    <t>標準宅地</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%A8%99%E6%BA%96%E5%AE%85%E5%9C%B0/tiles.json</t>
+  </si>
+  <si>
+    <t>#262626</t>
+  </si>
+  <si>
+    <t>状況類似地区</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%8A%B6%E6%B3%81%E9%A1%9E%E4%BC%BC%E5%9C%B0%E5%8C%BA/tiles.json</t>
+  </si>
+  <si>
+    <t>#20202C</t>
+  </si>
+  <si>
+    <t>交通</t>
+  </si>
+  <si>
+    <t>交通安全施設整備</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%81%82%E3%82%93%E3%81%97%E3%82%93%E6%AD%A9%E8%A1%8C%E3%82%A8%E3%83%AA%E3%82%A2%E6%95%B4%E5%82%99%E5%8F%B0%E5%B8%B3/tiles.json</t>
+  </si>
+  <si>
+    <t>#00cc99</t>
+  </si>
+  <si>
+    <t>路線網図</t>
+  </si>
+  <si>
+    <t>国道・県道</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E8%B7%AF%E7%B7%9A%E7%B6%B2%E5%9B%B3_%E5%9B%BD%E9%81%93%E7%9C%8C%E9%81%93/tiles.json</t>
+  </si>
+  <si>
+    <t>#FDD15B</t>
+  </si>
+  <si>
+    <t>1/2500</t>
+  </si>
+  <si>
+    <t>市道1級</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E8%B7%AF%E7%B7%9A%E7%B6%B2%E5%9B%B3_%E5%B8%82%E9%81%93%E4%B8%80%E7%B4%9A%E3%83%AC%E3%82%A4%E3%83%A4%E3%83%BC/tiles.json</t>
+  </si>
+  <si>
+    <t>#5956FF</t>
+  </si>
+  <si>
+    <t>市道2級</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E8%B7%AF%E7%B7%9A%E7%B6%B2%E5%9B%B3_%E5%B8%82%E9%81%93%E4%BA%8C%E7%B4%9A%E3%83%AC%E3%82%A4%E3%83%A4%E3%83%BC/tiles.json</t>
+  </si>
+  <si>
+    <t>#28A00F</t>
+  </si>
+  <si>
+    <t>市道その他</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E8%B7%AF%E7%B7%9A%E7%B6%B2%E5%9B%B3_%E5%B8%82%E9%81%93%E3%81%9D%E3%81%AE%E4%BB%96%E3%83%AC%E3%82%A4%E3%83%A4%E3%83%BC/tiles.json</t>
+  </si>
+  <si>
+    <t>#F958FF</t>
+  </si>
+  <si>
+    <t>バス</t>
+  </si>
+  <si>
+    <t>バス停（自主運行）＆時刻表</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E5%B8%82%E8%87%AA%E4%B8%BB%E9%81%8B%E8%A1%8C%E3%83%90%E3%82%B9%E8%B7%AF%E7%B7%9A%E5%9B%B3_%E5%81%9C%E7%95%99%E6%89%80/tiles.json</t>
+  </si>
+  <si>
+    <t>bus-stop-pink</t>
+  </si>
+  <si>
+    <t>バス路線</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E5%B8%82%E8%87%AA%E4%B8%BB%E9%81%8B%E8%A1%8C%E3%83%90%E3%82%B9%E8%B7%AF%E7%B7%9A%E5%9B%B3_%E8%B7%AF%E7%B7%9A/tiles.json</t>
+  </si>
+  <si>
+    <t>デマンドタクシー</t>
+  </si>
+  <si>
+    <t>焼津インターチェンジ地区（乗降位置）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/焼津IC周辺地区_タクシー乗降位置/tiles.json</t>
+  </si>
+  <si>
+    <t>demand-taxi-lightbrown</t>
+  </si>
+  <si>
+    <t>焼津インターチェンジ地区（乗降区域）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/焼津IC周辺地区_タクシー乗降区域/tiles.json</t>
+  </si>
+  <si>
+    <t>#C79100</t>
+  </si>
+  <si>
+    <t>焼津インターチェンジ地区（指定施設）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5IC%E5%91%A8%E8%BE%BA%E5%9C%B0%E5%8C%BA_%E3%82%BF%E3%82%AF%E3%82%B7%E3%83%BC%E6%8C%87%E5%AE%9A%E6%96%BD%E8%A8%AD/tiles.json</t>
+  </si>
+  <si>
+    <t>大島・三和地区（乗降位置）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/大島・三和地区_タクシー乗降位置/tiles.json</t>
+  </si>
+  <si>
+    <t>demand-taxi-darkgray</t>
+  </si>
+  <si>
+    <t>大島・三和地区（指定施設）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%A4%A7%E5%B3%B6%E3%83%BB%E4%B8%89%E5%92%8C%E5%9C%B0%E5%8C%BA_%E3%82%BF%E3%82%AF%E3%82%B7%E3%83%BC%E6%8C%87%E5%AE%9A%E6%96%BD%E8%A8%AD/tiles.json</t>
+  </si>
+  <si>
+    <t>大井川地区（乗降位置）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/大井川地区_タクシー乗降位置/tiles.json</t>
+  </si>
+  <si>
+    <t>demand-taxi-lightblue</t>
+  </si>
+  <si>
+    <t>大井川地区（乗降区域）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/大井川地区_タクシー乗降区域/tiles.json</t>
+  </si>
+  <si>
+    <t>#83C3FF</t>
+  </si>
+  <si>
+    <t>交通事故分析情報</t>
+  </si>
+  <si>
+    <t>2022年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E4%BA%A4%E9%80%9A%E4%BA%8B%E6%95%85_2022/tiles.json</t>
+  </si>
+  <si>
+    <t>#1E6577</t>
+  </si>
+  <si>
+    <t>2021年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E4%BA%A4%E9%80%9A%E4%BA%8B%E6%95%85_2021/tiles.json</t>
+  </si>
+  <si>
+    <t>#2A899D</t>
+  </si>
+  <si>
+    <t>2020年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E4%BA%A4%E9%80%9A%E4%BA%8B%E6%95%85_2020/tiles.json</t>
+  </si>
+  <si>
+    <t>#68C6DA</t>
+  </si>
+  <si>
+    <t>2019年</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E4%BA%A4%E9%80%9A%E4%BA%8B%E6%95%85_2019/tiles.json</t>
+  </si>
+  <si>
+    <t>#ABE0EB</t>
+  </si>
+  <si>
+    <t>ドライブコンテスト</t>
+  </si>
+  <si>
+    <t>スマホ使用</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%B3%E3%83%B3%E3%83%86%E3%82%B9%E3%83%88_%E3%82%B9%E3%83%9E%E3%83%9B%E4%BD%BF%E7%94%A8/tiles.json</t>
+  </si>
+  <si>
+    <t>#A1A4FF</t>
+  </si>
+  <si>
+    <t>急ハンドル</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%B3%E3%83%B3%E3%83%86%E3%82%B9%E3%83%88_%E6%80%A5%E3%83%8F%E3%83%B3%E3%83%89%E3%83%AB/tiles.json</t>
+  </si>
+  <si>
+    <t>#FF8DFF</t>
+  </si>
+  <si>
+    <t>急ブレーキ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%B3%E3%83%B3%E3%83%86%E3%82%B9%E3%83%88_%E6%80%A5%E3%83%96%E3%83%AC%E3%83%BC%E3%82%AD/tiles.json</t>
+  </si>
+  <si>
+    <t>#FF6565</t>
+  </si>
+  <si>
+    <t>急加速</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%B3%E3%83%B3%E3%83%86%E3%82%B9%E3%83%88_%E6%80%A5%E5%8A%A0%E9%80%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>#3F4886</t>
+  </si>
+  <si>
+    <t>速度超過</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%B3%E3%83%B3%E3%83%86%E3%82%B9%E3%83%88_%E9%80%9F%E5%BA%A6%E8%B6%85%E9%81%8E/tiles.json</t>
+  </si>
+  <si>
+    <t>#3F994C</t>
+  </si>
+  <si>
+    <t>ごみ・リサイクル</t>
+  </si>
+  <si>
+    <t>リサイクル拠点</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%AA%E3%82%B5%E3%82%A4%E3%82%AF%E3%83%AB%E6%8B%A0%E7%82%B9/tiles.json</t>
+  </si>
+  <si>
+    <t>農業</t>
+  </si>
+  <si>
+    <t>農業地域振興計画</t>
+  </si>
+  <si>
+    <t>農用地区域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E8%BE%B2%E6%A5%AD%E5%9C%B0%E5%9F%9F%E6%8C%AF%E8%88%88%E8%A8%88%E7%94%BB_%E8%BE%B2%E7%94%A8%E5%9C%B0%E5%8C%BA%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>#FDFAC5</t>
+  </si>
+  <si>
+    <t>農業用施設用地</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E8%BE%B2%E6%A5%AD%E5%9C%B0%E5%9F%9F%E6%8C%AF%E8%88%88%E8%A8%88%E7%94%BB_%E8%BE%B2%E6%A5%AD%E7%94%A8%E6%96%BD%E8%A8%AD%E7%94%A8%E5%9C%B0/tiles.json</t>
+  </si>
+  <si>
+    <t>#F8E3B2</t>
+  </si>
+  <si>
+    <t>農業用施設図</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/農業用施設図/tiles.json</t>
+  </si>
+  <si>
+    <t>#518A04</t>
+  </si>
+  <si>
+    <t>高草山農道</t>
+  </si>
+  <si>
+    <t>農道</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/農道一般平面図_農道/tiles.json</t>
+  </si>
+  <si>
+    <t>#5A3224</t>
+  </si>
+  <si>
+    <t>林道</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/農道一般平面図_林道/tiles.json</t>
+  </si>
+  <si>
+    <t>ファミリー農園</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%95%E3%82%A1%E3%83%9F%E3%83%AA%E3%83%BC%E8%BE%B2%E5%9C%92/tiles.json</t>
+  </si>
+  <si>
+    <t>family-farm</t>
+  </si>
+  <si>
+    <t>こども・教育</t>
+  </si>
+  <si>
+    <t>小学校・学区</t>
+  </si>
+  <si>
+    <t>小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>preschool-red</t>
+  </si>
+  <si>
+    <t>小学校区</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%B0%8F%E5%AD%A6%E6%A0%A1%E5%8C%BA/tiles.json</t>
+  </si>
+  <si>
+    <t>中学校・学区</t>
+  </si>
+  <si>
+    <t>中学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E4%B8%AD%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>preschool</t>
+  </si>
+  <si>
+    <t>中学校区</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E4%B8%AD%E5%AD%A6%E6%A0%A1%E5%8C%BA/tiles.json</t>
+  </si>
+  <si>
+    <t>#006AB6</t>
+  </si>
+  <si>
+    <t>通学路</t>
+  </si>
+  <si>
+    <t>和田小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%92%8C%E7%94%B0%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#E74C3C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大井川南小学校 </t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%A4%A7%E4%BA%95%E5%B7%9D%E5%8D%97%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#F39C12</t>
+  </si>
+  <si>
+    <t>大井川東小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%A4%A7%E4%BA%95%E5%B7%9D%E6%9D%B1%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#F1C40F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大井川西小学校 </t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%A4%A7%E4%BA%95%E5%B7%9D%E8%A5%BF%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#27AE60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大富小学校 </t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%A4%A7%E5%AF%8C%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#2ECC71</t>
+  </si>
+  <si>
+    <t>小川小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%B0%8F%E5%B7%9D%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#1ABC9C</t>
+  </si>
+  <si>
+    <t>東益津小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E6%9D%B1%E7%9B%8A%E6%B4%A5%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#3498DB</t>
+  </si>
+  <si>
+    <t>港小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E6%B8%AF%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#9B59B6</t>
+  </si>
+  <si>
+    <t>焼津南小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E7%84%BC%E6%B4%A5%E5%8D%97%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#34495E</t>
+  </si>
+  <si>
+    <t>焼津東小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E7%84%BC%E6%B4%A5%E6%9D%B1%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#D35400</t>
+  </si>
+  <si>
+    <t>焼津西小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E7%84%BC%E6%B4%A5%E8%A5%BF%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#8E44AD</t>
+  </si>
+  <si>
+    <t>豊田小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E8%B1%8A%E7%94%B0%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#16A085</t>
+  </si>
+  <si>
+    <t>黒石小学校</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E9%BB%92%E7%9F%B3%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#2C3E50</t>
+  </si>
+  <si>
+    <t>その他教育</t>
+  </si>
+  <si>
+    <t>放課後等デイサービス</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%94%BE%E8%AA%B2%E5%BE%8C%E7%AD%89%E3%83%87%E3%82%A4%E3%82%B5%E3%83%BC%E3%83%93%E3%82%B9%E4%B8%80%E8%A6%A7/tiles.json</t>
+  </si>
+  <si>
+    <t>#0179c4</t>
+  </si>
+  <si>
+    <t>子育て</t>
+  </si>
+  <si>
+    <t>幼稚園・保育所</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%AD%90%E8%82%B2%E3%81%A6%E6%96%BD%E8%A8%AD%E4%B8%80%E8%A6%A7/tiles.json</t>
+  </si>
+  <si>
+    <t>#ef8307</t>
+  </si>
+  <si>
+    <t>子育て支援施設</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%AD%90%E8%82%B2%E3%81%A6%E6%94%AF%E6%8F%B4%E6%96%BD%E8%A8%AD/tiles.json</t>
+  </si>
+  <si>
+    <t>#be68c9</t>
+  </si>
+  <si>
+    <t>あかちゃんえき</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%81%82%E3%81%8B%E3%81%A1%E3%82%83%E3%82%93%E3%81%88%E3%81%8D%E4%B8%80%E8%A6%A7/tiles.json</t>
+  </si>
+  <si>
+    <t>baby</t>
+  </si>
+  <si>
+    <t>地域・コミュニティ</t>
+  </si>
+  <si>
+    <t>地域交流センター</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%9C%B0%E5%9F%9F%E4%BA%A4%E6%B5%81%E3%82%BB%E3%83%B3%E3%82%BF%E3%83%BC/tiles.json</t>
+  </si>
+  <si>
+    <t>daycare</t>
+  </si>
+  <si>
+    <t>自治会区域</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E8%87%AA%E6%B2%BB%E4%BC%9A%E5%8C%BA%E5%9F%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>#564340</t>
+  </si>
+  <si>
+    <t>文化・スポーツ</t>
+  </si>
+  <si>
+    <t>小泉八雲ゆかりの地</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%B0%8F%E6%B3%89%E5%85%AB%E9%9B%B2%E3%83%9E%E3%83%83%E3%83%97/tiles.json</t>
+  </si>
+  <si>
+    <t>historical-folk-facilities</t>
+  </si>
+  <si>
+    <t>浜通り（八雲通り）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%B0%8F%E6%B3%89%E5%85%AB%E9%9B%B2%E3%83%9E%E3%83%83%E3%83%97_%E6%B5%9C%E9%80%9A%E3%82%8A/tiles.json</t>
+  </si>
+  <si>
+    <t>文化会館・資料館</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%96%87%E5%8C%96%E4%BC%9A%E9%A4%A8%E3%83%BB%E8%B3%87%E6%96%99%E9%A4%A8/tiles.json</t>
+  </si>
+  <si>
+    <t>museums</t>
+  </si>
+  <si>
+    <t>図書館</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%9B%B3%E6%9B%B8%E9%A4%A8/tiles.json</t>
+  </si>
+  <si>
+    <t>library</t>
+  </si>
+  <si>
+    <t>スポーツ施設</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%82%B9%E3%83%9D%E3%83%BC%E3%83%84%E6%96%BD%E8%A8%AD/tiles.json</t>
+  </si>
+  <si>
+    <t>sports</t>
+  </si>
+  <si>
+    <t>文化財マップ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%96%87%E5%8C%96%E8%B2%A1%E3%83%9E%E3%83%83%E3%83%97/tiles.json</t>
+  </si>
+  <si>
+    <t>bunkazai</t>
+  </si>
+  <si>
+    <t>埋蔵文化財</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%9F%8B%E8%94%B5%E6%96%87%E5%8C%96%E8%B2%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>#ff0302</t>
+  </si>
+  <si>
+    <t>健康・福祉</t>
+  </si>
+  <si>
+    <t>ベジチェック設置場所</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%99%E3%82%B8%E3%83%81%E3%82%A7%E3%83%83%E3%82%AF%E8%A8%AD%E7%BD%AE%E5%A0%B4%E6%89%80/tiles.json</t>
+  </si>
+  <si>
+    <t>agricultural-experience-facility</t>
+  </si>
+  <si>
+    <t>まちなか涼みどころ</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%81%BE%E3%81%A1%E3%81%AA%E3%81%8B%E6%B6%BC%E3%81%BF%E3%81%A9%E3%81%93%E3%82%8D/tiles.json</t>
+  </si>
+  <si>
+    <t>reservoir</t>
+  </si>
+  <si>
+    <t>福祉会館</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%A6%8F%E7%A5%89%E4%BC%9A%E9%A4%A8/tiles.json</t>
+  </si>
+  <si>
+    <t>welfare-center</t>
+  </si>
+  <si>
+    <t>AED設置場所</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/AED%E8%A8%AD%E7%BD%AE%E7%AE%87%E6%89%80%E4%B8%80%E8%A6%A7/tiles.json</t>
+  </si>
+  <si>
+    <t>aed</t>
+  </si>
+  <si>
+    <t>市の窓口</t>
+  </si>
+  <si>
+    <t>市役所など</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%B8%82%E5%BD%B9%E6%89%80%E3%83%BB%E3%82%BB%E3%83%B3%E3%82%BF%E3%83%BC/tiles.json</t>
+  </si>
+  <si>
+    <t>public-facility-navy</t>
+  </si>
+  <si>
+    <t>Free Wi-Fiスポット</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%85%AC%E8%A1%86%E7%84%A1%E7%B7%9ALAN%E4%B8%80%E8%A6%A7/tiles.json</t>
+  </si>
+  <si>
+    <t>wifi-access-point</t>
+  </si>
+  <si>
+    <t>焼津駅前を歩こう！</t>
+  </si>
+  <si>
+    <t>有料駐車場（焼津駅周辺）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%AD%9A%E3%83%95%E3%82%A7%E3%82%B9%E5%91%A8%E8%BE%BA%E3%82%B9%E3%83%9D%E3%83%83%E3%83%88_%E6%9C%89%E6%96%99%E9%A7%90%E8%BB%8A%E5%A0%B4/tiles.json</t>
+  </si>
+  <si>
+    <t>歴史・史跡</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%AD%9A%E3%83%95%E3%82%A7%E3%82%B9%E5%91%A8%E8%BE%BA%E3%82%B9%E3%83%9D%E3%83%83%E3%83%88_%E5%8F%B2%E8%B7%A1/tiles.json</t>
+  </si>
+  <si>
+    <t>便利なスポット</t>
+  </si>
+  <si>
+    <t>休憩場所（ベンチ）</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%AD%9A%E3%83%95%E3%82%A7%E3%82%B9%E5%91%A8%E8%BE%BA%E3%82%B9%E3%83%9D%E3%83%83%E3%83%88_%E4%BC%91%E6%86%A9%E5%A0%B4%E6%89%80/tiles.json</t>
+  </si>
+  <si>
+    <t>自動販売機</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%AD%9A%E3%83%95%E3%82%A7%E3%82%B9%E5%91%A8%E8%BE%BA%E3%82%B9%E3%83%9D%E3%83%83%E3%83%88_%E8%87%AA%E5%8B%95%E8%B2%A9%E5%A3%B2%E6%A9%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>vending-machine</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E9%AD%9A%E3%83%95%E3%82%A7%E3%82%B9%E5%91%A8%E8%BE%BA%E3%82%B9%E3%83%9D%E3%83%83%E3%83%88_%E3%81%9D%E3%81%AE%E4%BB%96/tiles.json</t>
+  </si>
+  <si>
+    <t>marker-ultramarine</t>
+  </si>
+  <si>
+    <t>防災</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>#FF0000</t>
+  </si>
+  <si>
+    <t>#00E700</t>
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/yaizu-shizuoka-takashio-keizoku/{z}/{x}/{y}.png</t>
-  </si>
-  <si>
-    <t>浸水深</t>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/yaizu-shizuoka-takashio-shinsuishin/{z}/{x}/{y}.png</t>
-  </si>
-  <si>
-    <t>家屋倒壊等氾濫想定区域（流体力）</t>
-  </si>
-  <si>
-    <t>焼津市</t>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/yaizu-kaoku-tokai-hanranryu/tiles.json</t>
-  </si>
-  <si>
-    <t>家屋倒壊等氾濫想定区域（越波）</t>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/yaizu-kaoku-tokai-eppaha/tiles.json</t>
-  </si>
-  <si>
-    <t>内水浸水想定区域(公共下水道区域内)</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%86%85%E6%B0%B4%E6%B5%B8%E6%B0%B4%E6%83%B3%E5%AE%9A%E5%8C%BA%E5%9F%9F(%E5%85%AC%E5%85%B1%E4%B8%8B%E6%B0%B4%E9%81%93%E5%8C%BA%E5%9F%9F%E5%86%85)/tiles.json</t>
-  </si>
-  <si>
-    <t>浸水履歴（平成9年～令和5年）</t>
-  </si>
-  <si>
-    <t>統合（平成9年～令和5年）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E7%B5%B1%E5%90%88/tiles.json</t>
-  </si>
-  <si>
-    <t>令和4年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E4%BB%A4%E5%92%8C4%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>令和元年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E4%BB%A4%E5%92%8C%E5%85%83%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成29年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9029%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成26年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9026%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成25年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9025%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成24年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9024%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成23年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9023%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成22年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9022%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成20年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9020%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成19年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9019%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成18年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9018%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成17年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9017%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成16年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9016%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成15年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9015%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成14年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9014%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成13年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9013%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成12年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9012%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成11年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9011%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成10年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%9010%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>平成9年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%909%E5%B9%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>観光・イベント</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>高潮浸水想定区域（浸水継続時間）</t>
+    <rPh sb="9" eb="15">
+      <t xml:space="preserve">シンスイケイゾクジカン </t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>お食事</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%81%8A%E9%A3%9F%E4%BA%8B/tiles.json</t>
-  </si>
-  <si>
-    <t>restaurant</t>
-  </si>
-  <si>
-    <t>海の幸グルメマップ</t>
-  </si>
-  <si>
-    <t>ミナミマグロ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E6%B5%B7%E3%81%AE%E5%B9%B8%E3%82%B0%E3%83%AB%E3%83%A1%E3%83%9E%E3%83%83%E3%83%97_%E3%83%9F%E3%83%8A%E3%83%9F%E3%83%9E%E3%82%B0%E3%83%AD/tiles.json</t>
-  </si>
-  <si>
-    <t>fish</t>
-  </si>
-  <si>
-    <t>カツオ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E6%B5%B7%E3%81%AE%E5%B9%B8%E3%82%B0%E3%83%AB%E3%83%A1%E3%83%9E%E3%83%83%E3%83%97_%E3%82%AB%E3%83%84%E3%82%AA/tiles.json</t>
-  </si>
-  <si>
-    <t>サバ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E6%B5%B7%E3%81%AE%E5%B9%B8%E3%82%B0%E3%83%AB%E3%83%A1%E3%83%9E%E3%83%83%E3%83%97_%E3%82%B5%E3%83%90/tiles.json</t>
-  </si>
-  <si>
-    <t>サクラエビ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E6%B5%B7%E3%81%AE%E5%B9%B8%E3%82%B0%E3%83%AB%E3%83%A1%E3%83%9E%E3%83%83%E3%83%97_%E3%82%B5%E3%82%AF%E3%83%A9%E3%82%A8%E3%83%93/tiles.json</t>
-  </si>
-  <si>
-    <t>シラス</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E6%B5%B7%E3%81%AE%E5%B9%B8%E3%82%B0%E3%83%AB%E3%83%A1%E3%83%9E%E3%83%83%E3%83%97_%E3%82%B7%E3%83%A9%E3%82%B9/tiles.json</t>
-  </si>
-  <si>
-    <t>お買い物</t>
-  </si>
-  <si>
-    <t>ショップ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%82%B7%E3%83%A7%E3%83%83%E3%83%97/tiles.json</t>
-  </si>
-  <si>
-    <t>shopping</t>
-  </si>
-  <si>
-    <t>工場併設直売所</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%B7%A5%E5%A0%B4%E4%BD%B5%E8%A8%AD%E7%9B%B4%E5%A3%B2%E6%89%80%E4%B8%80%E8%A6%A7/tiles.json</t>
-  </si>
-  <si>
-    <t>factory-shop</t>
-  </si>
-  <si>
-    <t>体験・見どころ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E4%BD%93%E9%A8%93%E3%83%BB%E8%A6%8B%E3%81%A9%E3%81%93%E3%82%8D/tiles.json</t>
-  </si>
-  <si>
-    <t>tourist-facility</t>
-  </si>
-  <si>
-    <t>日帰り温泉・足湯</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%97%A5%E5%B8%B0%E3%82%8A%E6%B8%A9%E6%B3%89%E3%83%BB%E8%B6%B3%E6%B9%AF/tiles.json</t>
-  </si>
-  <si>
-    <t>hotspring</t>
-  </si>
-  <si>
-    <t>宿泊</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%AE%BF%E6%B3%8A/tiles.json</t>
-  </si>
-  <si>
-    <t>hotel</t>
-  </si>
-  <si>
-    <t>移動・その他</t>
-  </si>
-  <si>
-    <t>レンタカー</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%AC%E3%83%B3%E3%82%BF%E3%82%AB%E3%83%BC/tiles.json</t>
-  </si>
-  <si>
-    <t>car-rental</t>
-  </si>
-  <si>
-    <t>その他</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%81%9D%E3%81%AE%E4%BB%96/tiles.json</t>
-  </si>
-  <si>
-    <t>#66cdaa</t>
-  </si>
-  <si>
-    <t>市営駐車場・駐輪場</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%B8%82%E5%96%B6%E9%A7%90%E8%BB%8A%E5%A0%B4%E3%83%BB%E9%A7%90%E8%BC%AA%E5%A0%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>parking</t>
-  </si>
-  <si>
-    <t>焼津観光マップ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E8%A6%B3%E5%85%89%E3%83%9E%E3%83%83%E3%83%97/tiles.json</t>
-  </si>
-  <si>
-    <t>#7385e5</t>
-  </si>
-  <si>
-    <t>高草山ハイキングマップ</t>
-  </si>
-  <si>
-    <t>高草山コース　1</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
-  </si>
-  <si>
-    <t>#009f45</t>
-  </si>
-  <si>
-    <t>高草山コース　2</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-2%E5%9D%82%E6%9C%AC_%E9%AB%98%E8%8D%89%E5%B1%B1%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
-  </si>
-  <si>
-    <t>#ef8da9</t>
-  </si>
-  <si>
-    <t>高草山コース　3</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-3%E7%84%BC%E6%B4%A5%E5%B8%82_%E9%96%A2%E6%96%B9_%E9%AB%98%E8%8D%89%E5%B1%B1%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
-  </si>
-  <si>
-    <t>#179fac</t>
-  </si>
-  <si>
-    <t>高草山コース　4</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-4%E8%97%A4%E6%9E%9D%E5%B8%82_%E4%B8%89%E8%BC%AA_%E9%AB%98%E8%8D%89%E5%B1%B1%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
-  </si>
-  <si>
-    <t>#7ac24c</t>
-  </si>
-  <si>
-    <t>満観峰コース</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_2%E7%84%BC%E6%B4%A5%E5%B8%82_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E6%BA%80%E8%A6%B3%E5%B3%B0%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
-  </si>
-  <si>
-    <t>#3d73ba</t>
-  </si>
-  <si>
-    <t>花沢山コース　1</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
-  </si>
-  <si>
-    <t>#b664a6</t>
-  </si>
-  <si>
-    <t>花沢山コース　2</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json</t>
-  </si>
-  <si>
-    <t>#dab06d</t>
-  </si>
-  <si>
-    <t>ハイキングスポット</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_%E5%9C%B0%E7%82%B9/tiles.json</t>
-  </si>
-  <si>
-    <t>brown-marker</t>
-  </si>
-  <si>
-    <t>トイレ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_%E5%9C%B0%E7%82%B9_%E3%83%88%E3%82%A4%E3%83%AC/tiles.json</t>
-  </si>
-  <si>
-    <t>public-toilets</t>
-  </si>
-  <si>
-    <t>駐車場・バス停</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_%E5%9C%B0%E7%82%B9_%E9%A7%90%E8%BB%8A%E5%A0%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>#ffffff</t>
-  </si>
-  <si>
-    <t>#2F2011</t>
-  </si>
-  <si>
-    <t>まちづくり</t>
-  </si>
-  <si>
-    <t>航空写真（令和5年度）</t>
-  </si>
-  <si>
-    <t>https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5</t>
-  </si>
-  <si>
-    <t>都市計画図</t>
-  </si>
-  <si>
-    <t>市街化区域界・市街化調整区域界</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/市街化区域界_市街化調整区域界/tiles.json</t>
-  </si>
-  <si>
-    <t>#cd853f</t>
-  </si>
-  <si>
-    <t>高度利用地区</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/高度利用地区/tiles.json</t>
-  </si>
-  <si>
-    <t>#ff6347</t>
-  </si>
-  <si>
-    <t>準防火地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/準防火地域/tiles.json</t>
-  </si>
-  <si>
-    <t>#ffb6c1</t>
-  </si>
-  <si>
-    <t>都市計画道路</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/都市計画道路/tiles.json</t>
-  </si>
-  <si>
-    <t>#ff0000</t>
-  </si>
-  <si>
-    <t>駐車場</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/駐車場/tiles.json</t>
-  </si>
-  <si>
-    <t>#000000</t>
-  </si>
-  <si>
-    <t>公園・緑地</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/公園_緑地/tiles.json</t>
-  </si>
-  <si>
-    <t>#228b22</t>
-  </si>
-  <si>
-    <t>ごみ焼却場</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%81%94%E3%81%BF%E7%84%BC%E5%8D%B4%E5%A0%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>#8b4513</t>
-  </si>
-  <si>
-    <t>し尿処理場</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/し尿処理場/tiles.json</t>
-  </si>
-  <si>
-    <t>#1e90ff</t>
-  </si>
-  <si>
-    <t>地区計画区域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/地区計画区域/tiles.json</t>
-  </si>
-  <si>
-    <t>#2f4f4f</t>
-  </si>
-  <si>
-    <t>土地区画整理事業区域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/土地区画整理事業区域/tiles.json</t>
-  </si>
-  <si>
-    <t>住まいるシティ拠点エリア（都市機能誘導区域）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/住まいるシティ拠点エリア_都市機能誘導区域/tiles.json</t>
-  </si>
-  <si>
-    <t>#00bfff</t>
-  </si>
-  <si>
-    <t>住まいるエリア（居住誘導区域）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/住まいるエリア_居住誘導区域/tiles.json</t>
-  </si>
-  <si>
-    <t>都市計画図（用途地域）</t>
-  </si>
-  <si>
-    <t>第一種低層住居専用地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E7%AC%AC%E4%B8%80%E7%A8%AE%E4%BD%8E%E5%B1%A4%E4%BD%8F%E5%B1%85%E5%B0%82%E7%94%A8%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>#A2D7D4</t>
-  </si>
-  <si>
-    <t>rgb(156,84,160)</t>
-  </si>
-  <si>
-    <t>第一種中高層住居専用地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E7%AC%AC%E4%B8%80%E7%A8%AE%E4%B8%AD%E9%AB%98%E5%B1%A4%E4%BD%8F%E5%B1%85%E5%B0%82%E7%94%A8%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>rgb(198,224,159)</t>
-  </si>
-  <si>
-    <t>第二種中高層住居専用地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E7%AC%AC%E4%BA%8C%E7%A8%AE%E4%B8%AD%E9%AB%98%E5%B1%A4%E4%BD%8F%E5%B1%85%E5%B0%82%E7%94%A8%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>rgb(234,243,220)</t>
-  </si>
-  <si>
-    <t>第一種住居地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E7%AC%AC%E4%B8%80%E7%A8%AE%E4%BD%8F%E5%B1%85%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>rgb(255,246,152)</t>
-  </si>
-  <si>
-    <t>第二種住居地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E7%AC%AC%E4%BA%8C%E7%A8%AE%E4%BD%8F%E5%B1%85%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>rgb(255,253,237)</t>
-  </si>
-  <si>
-    <t>準住居地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E6%BA%96%E4%BD%8F%E5%B1%85%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>rgb(251,194,144)</t>
-  </si>
-  <si>
-    <t>近隣商業地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E8%BF%91%E9%9A%A3%E5%95%86%E6%A5%AD%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>#F7C8DD</t>
-  </si>
-  <si>
-    <t>rgb(179,114,173)</t>
-  </si>
-  <si>
-    <t>商業地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E5%95%86%E6%A5%AD%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>#F29A75</t>
-  </si>
-  <si>
-    <t>準工業地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E6%BA%96%E5%B7%A5%E6%A5%AD%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>rgb(220,201,225)</t>
-  </si>
-  <si>
-    <t>工業地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E5%B7%A5%E6%A5%AD%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>rgb(217,235,248)</t>
-  </si>
-  <si>
-    <t>工業専用地域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E5%B7%A5%E6%A5%AD%E5%B0%82%E7%94%A8%E5%9C%B0%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>rgb(145,201,237)</t>
-  </si>
-  <si>
-    <t>敷地面積の最低限度指定区域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%83%BD%E5%B8%82%E8%A8%88%E7%94%BB%E5%9B%B3_%E6%95%B7%E5%9C%B0%E9%9D%A2%E7%A9%8D%E3%81%AE%E6%9C%80%E4%BD%8E%E9%99%90%E5%BA%A6%E6%8C%87%E5%AE%9A%E5%8C%BA%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>#E52187</t>
-  </si>
-  <si>
-    <t>区域図</t>
-  </si>
-  <si>
-    <t>令和6年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%8C%BA%E7%94%BB%E6%95%B4%E7%90%86%E5%9C%B0%E5%9B%B3/tiles.json</t>
-  </si>
-  <si>
-    <t>#93c9a3</t>
-  </si>
-  <si>
-    <t>大正9年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%98%94%E3%81%AE%E7%84%BC%E6%B4%A5%E3%81%A8%E6%AF%94%E3%81%B9%E3%81%A6%E3%81%BF%E3%82%88%E3%81%86/tiles.json</t>
-  </si>
-  <si>
-    <t>#6bbcb3</t>
-  </si>
-  <si>
-    <t>公衆トイレ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%85%AC%E8%A1%86%E3%83%88%E3%82%A4%E3%83%AC%E4%B8%80%E8%A6%A7/tiles.json</t>
-  </si>
-  <si>
-    <t>公園</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%85%AC%E5%9C%92%E4%B8%80%E8%A6%A7/tiles.json</t>
-  </si>
-  <si>
-    <t>park</t>
-  </si>
-  <si>
-    <t>さくら並木</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%81%95%E3%81%8F%E3%82%89%E4%B8%A6%E6%9C%A8%E7%AE%A1%E7%90%86%E8%AA%BF%E6%9B%B8/tiles.json</t>
-  </si>
-  <si>
-    <t>#eb3390</t>
-  </si>
-  <si>
-    <t>住まい</t>
-  </si>
-  <si>
-    <t>固定資産税・路線価図</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/固定資産税_路線価図/tiles.json</t>
-  </si>
-  <si>
-    <t>#1C1C1C</t>
-  </si>
-  <si>
-    <t>標準宅地</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%A8%99%E6%BA%96%E5%AE%85%E5%9C%B0/tiles.json</t>
-  </si>
-  <si>
-    <t>#262626</t>
-  </si>
-  <si>
-    <t>状況類似地区</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%8A%B6%E6%B3%81%E9%A1%9E%E4%BC%BC%E5%9C%B0%E5%8C%BA/tiles.json</t>
-  </si>
-  <si>
-    <t>#20202C</t>
-  </si>
-  <si>
-    <t>交通</t>
-  </si>
-  <si>
-    <t>交通安全施設整備</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%81%82%E3%82%93%E3%81%97%E3%82%93%E6%AD%A9%E8%A1%8C%E3%82%A8%E3%83%AA%E3%82%A2%E6%95%B4%E5%82%99%E5%8F%B0%E5%B8%B3/tiles.json</t>
-  </si>
-  <si>
-    <t>#00cc99</t>
-  </si>
-  <si>
-    <t>路線網図</t>
-  </si>
-  <si>
-    <t>国道・県道</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E8%B7%AF%E7%B7%9A%E7%B6%B2%E5%9B%B3_%E5%9B%BD%E9%81%93%E7%9C%8C%E9%81%93/tiles.json</t>
-  </si>
-  <si>
-    <t>#FDD15B</t>
-  </si>
-  <si>
-    <t>1/2500</t>
-  </si>
-  <si>
-    <t>市道1級</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E8%B7%AF%E7%B7%9A%E7%B6%B2%E5%9B%B3_%E5%B8%82%E9%81%93%E4%B8%80%E7%B4%9A%E3%83%AC%E3%82%A4%E3%83%A4%E3%83%BC/tiles.json</t>
-  </si>
-  <si>
-    <t>#5956FF</t>
-  </si>
-  <si>
-    <t>市道2級</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E8%B7%AF%E7%B7%9A%E7%B6%B2%E5%9B%B3_%E5%B8%82%E9%81%93%E4%BA%8C%E7%B4%9A%E3%83%AC%E3%82%A4%E3%83%A4%E3%83%BC/tiles.json</t>
-  </si>
-  <si>
-    <t>#28A00F</t>
-  </si>
-  <si>
-    <t>市道その他</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E8%B7%AF%E7%B7%9A%E7%B6%B2%E5%9B%B3_%E5%B8%82%E9%81%93%E3%81%9D%E3%81%AE%E4%BB%96%E3%83%AC%E3%82%A4%E3%83%A4%E3%83%BC/tiles.json</t>
-  </si>
-  <si>
-    <t>#F958FF</t>
-  </si>
-  <si>
-    <t>バス</t>
-  </si>
-  <si>
-    <t>バス停（自主運行）＆時刻表</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E5%B8%82%E8%87%AA%E4%B8%BB%E9%81%8B%E8%A1%8C%E3%83%90%E3%82%B9%E8%B7%AF%E7%B7%9A%E5%9B%B3_%E5%81%9C%E7%95%99%E6%89%80/tiles.json</t>
-  </si>
-  <si>
-    <t>bus-stop-pink</t>
-  </si>
-  <si>
-    <t>バス路線</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E5%B8%82%E8%87%AA%E4%B8%BB%E9%81%8B%E8%A1%8C%E3%83%90%E3%82%B9%E8%B7%AF%E7%B7%9A%E5%9B%B3_%E8%B7%AF%E7%B7%9A/tiles.json</t>
-  </si>
-  <si>
-    <t>デマンドタクシー</t>
-  </si>
-  <si>
-    <t>焼津インターチェンジ地区（乗降位置）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/焼津IC周辺地区_タクシー乗降位置/tiles.json</t>
-  </si>
-  <si>
-    <t>demand-taxi-lightbrown</t>
-  </si>
-  <si>
-    <t>焼津インターチェンジ地区（乗降区域）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/焼津IC周辺地区_タクシー乗降区域/tiles.json</t>
-  </si>
-  <si>
-    <t>#C79100</t>
-  </si>
-  <si>
-    <t>焼津インターチェンジ地区（指定施設）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5IC%E5%91%A8%E8%BE%BA%E5%9C%B0%E5%8C%BA_%E3%82%BF%E3%82%AF%E3%82%B7%E3%83%BC%E6%8C%87%E5%AE%9A%E6%96%BD%E8%A8%AD/tiles.json</t>
-  </si>
-  <si>
-    <t>大島・三和地区（乗降位置）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/大島・三和地区_タクシー乗降位置/tiles.json</t>
-  </si>
-  <si>
-    <t>demand-taxi-darkgray</t>
-  </si>
-  <si>
-    <t>大島・三和地区（指定施設）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%A4%A7%E5%B3%B6%E3%83%BB%E4%B8%89%E5%92%8C%E5%9C%B0%E5%8C%BA_%E3%82%BF%E3%82%AF%E3%82%B7%E3%83%BC%E6%8C%87%E5%AE%9A%E6%96%BD%E8%A8%AD/tiles.json</t>
-  </si>
-  <si>
-    <t>大井川地区（乗降位置）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/大井川地区_タクシー乗降位置/tiles.json</t>
-  </si>
-  <si>
-    <t>demand-taxi-lightblue</t>
-  </si>
-  <si>
-    <t>大井川地区（乗降区域）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/大井川地区_タクシー乗降区域/tiles.json</t>
-  </si>
-  <si>
-    <t>#83C3FF</t>
-  </si>
-  <si>
-    <t>交通事故分析情報</t>
-  </si>
-  <si>
-    <t>2022年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E4%BA%A4%E9%80%9A%E4%BA%8B%E6%95%85_2022/tiles.json</t>
-  </si>
-  <si>
-    <t>#1E6577</t>
-  </si>
-  <si>
-    <t>2021年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E4%BA%A4%E9%80%9A%E4%BA%8B%E6%95%85_2021/tiles.json</t>
-  </si>
-  <si>
-    <t>#2A899D</t>
-  </si>
-  <si>
-    <t>2020年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E4%BA%A4%E9%80%9A%E4%BA%8B%E6%95%85_2020/tiles.json</t>
-  </si>
-  <si>
-    <t>#68C6DA</t>
-  </si>
-  <si>
-    <t>2019年</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E4%BA%A4%E9%80%9A%E4%BA%8B%E6%95%85_2019/tiles.json</t>
-  </si>
-  <si>
-    <t>#ABE0EB</t>
-  </si>
-  <si>
-    <t>ドライブコンテスト</t>
-  </si>
-  <si>
-    <t>スマホ使用</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%B3%E3%83%B3%E3%83%86%E3%82%B9%E3%83%88_%E3%82%B9%E3%83%9E%E3%83%9B%E4%BD%BF%E7%94%A8/tiles.json</t>
-  </si>
-  <si>
-    <t>#A1A4FF</t>
-  </si>
-  <si>
-    <t>急ハンドル</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%B3%E3%83%B3%E3%83%86%E3%82%B9%E3%83%88_%E6%80%A5%E3%83%8F%E3%83%B3%E3%83%89%E3%83%AB/tiles.json</t>
-  </si>
-  <si>
-    <t>#FF8DFF</t>
-  </si>
-  <si>
-    <t>急ブレーキ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%B3%E3%83%B3%E3%83%86%E3%82%B9%E3%83%88_%E6%80%A5%E3%83%96%E3%83%AC%E3%83%BC%E3%82%AD/tiles.json</t>
-  </si>
-  <si>
-    <t>#FF6565</t>
-  </si>
-  <si>
-    <t>急加速</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%B3%E3%83%B3%E3%83%86%E3%82%B9%E3%83%88_%E6%80%A5%E5%8A%A0%E9%80%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>#3F4886</t>
-  </si>
-  <si>
-    <t>速度超過</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%89%E3%83%A9%E3%82%A4%E3%83%96%E3%82%B3%E3%83%B3%E3%83%86%E3%82%B9%E3%83%88_%E9%80%9F%E5%BA%A6%E8%B6%85%E9%81%8E/tiles.json</t>
-  </si>
-  <si>
-    <t>#3F994C</t>
-  </si>
-  <si>
-    <t>ごみ・リサイクル</t>
-  </si>
-  <si>
-    <t>リサイクル拠点</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%AA%E3%82%B5%E3%82%A4%E3%82%AF%E3%83%AB%E6%8B%A0%E7%82%B9/tiles.json</t>
-  </si>
-  <si>
-    <t>農業</t>
-  </si>
-  <si>
-    <t>農業地域振興計画</t>
-  </si>
-  <si>
-    <t>農用地区域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E8%BE%B2%E6%A5%AD%E5%9C%B0%E5%9F%9F%E6%8C%AF%E8%88%88%E8%A8%88%E7%94%BB_%E8%BE%B2%E7%94%A8%E5%9C%B0%E5%8C%BA%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>#FDFAC5</t>
-  </si>
-  <si>
-    <t>農業用施設用地</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E8%BE%B2%E6%A5%AD%E5%9C%B0%E5%9F%9F%E6%8C%AF%E8%88%88%E8%A8%88%E7%94%BB_%E8%BE%B2%E6%A5%AD%E7%94%A8%E6%96%BD%E8%A8%AD%E7%94%A8%E5%9C%B0/tiles.json</t>
-  </si>
-  <si>
-    <t>#F8E3B2</t>
-  </si>
-  <si>
-    <t>農業用施設図</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/農業用施設図/tiles.json</t>
-  </si>
-  <si>
-    <t>#518A04</t>
-  </si>
-  <si>
-    <t>高草山農道</t>
-  </si>
-  <si>
-    <t>農道</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/農道一般平面図_農道/tiles.json</t>
-  </si>
-  <si>
-    <t>#5A3224</t>
-  </si>
-  <si>
-    <t>林道</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/農道一般平面図_林道/tiles.json</t>
-  </si>
-  <si>
-    <t>ファミリー農園</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%95%E3%82%A1%E3%83%9F%E3%83%AA%E3%83%BC%E8%BE%B2%E5%9C%92/tiles.json</t>
-  </si>
-  <si>
-    <t>family-farm</t>
-  </si>
-  <si>
-    <t>こども・教育</t>
-  </si>
-  <si>
-    <t>小学校・学区</t>
-  </si>
-  <si>
-    <t>小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>preschool-red</t>
-  </si>
-  <si>
-    <t>小学校区</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%B0%8F%E5%AD%A6%E6%A0%A1%E5%8C%BA/tiles.json</t>
-  </si>
-  <si>
-    <t>中学校・学区</t>
-  </si>
-  <si>
-    <t>中学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E4%B8%AD%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>preschool</t>
-  </si>
-  <si>
-    <t>中学校区</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E4%B8%AD%E5%AD%A6%E6%A0%A1%E5%8C%BA/tiles.json</t>
-  </si>
-  <si>
-    <t>#006AB6</t>
-  </si>
-  <si>
-    <t>通学路</t>
-  </si>
-  <si>
-    <t>和田小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%92%8C%E7%94%B0%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#E74C3C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大井川南小学校 </t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%A4%A7%E4%BA%95%E5%B7%9D%E5%8D%97%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#F39C12</t>
-  </si>
-  <si>
-    <t>大井川東小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%A4%A7%E4%BA%95%E5%B7%9D%E6%9D%B1%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#F1C40F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大井川西小学校 </t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%A4%A7%E4%BA%95%E5%B7%9D%E8%A5%BF%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#27AE60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大富小学校 </t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%A4%A7%E5%AF%8C%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#2ECC71</t>
-  </si>
-  <si>
-    <t>小川小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E5%B0%8F%E5%B7%9D%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#1ABC9C</t>
-  </si>
-  <si>
-    <t>東益津小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E6%9D%B1%E7%9B%8A%E6%B4%A5%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#3498DB</t>
-  </si>
-  <si>
-    <t>港小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E6%B8%AF%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#9B59B6</t>
-  </si>
-  <si>
-    <t>焼津南小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E7%84%BC%E6%B4%A5%E5%8D%97%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#34495E</t>
-  </si>
-  <si>
-    <t>焼津東小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E7%84%BC%E6%B4%A5%E6%9D%B1%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#D35400</t>
-  </si>
-  <si>
-    <t>焼津西小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E7%84%BC%E6%B4%A5%E8%A5%BF%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#8E44AD</t>
-  </si>
-  <si>
-    <t>豊田小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E8%B1%8A%E7%94%B0%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#16A085</t>
-  </si>
-  <si>
-    <t>黒石小学校</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%80%9A%E5%AD%A6%E8%B7%AF_%E9%BB%92%E7%9F%B3%E5%B0%8F%E5%AD%A6%E6%A0%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#2C3E50</t>
-  </si>
-  <si>
-    <t>その他教育</t>
-  </si>
-  <si>
-    <t>放課後等デイサービス</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%94%BE%E8%AA%B2%E5%BE%8C%E7%AD%89%E3%83%87%E3%82%A4%E3%82%B5%E3%83%BC%E3%83%93%E3%82%B9%E4%B8%80%E8%A6%A7/tiles.json</t>
-  </si>
-  <si>
-    <t>#0179c4</t>
-  </si>
-  <si>
-    <t>子育て</t>
-  </si>
-  <si>
-    <t>幼稚園・保育所</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%AD%90%E8%82%B2%E3%81%A6%E6%96%BD%E8%A8%AD%E4%B8%80%E8%A6%A7/tiles.json</t>
-  </si>
-  <si>
-    <t>#ef8307</t>
-  </si>
-  <si>
-    <t>子育て支援施設</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%AD%90%E8%82%B2%E3%81%A6%E6%94%AF%E6%8F%B4%E6%96%BD%E8%A8%AD/tiles.json</t>
-  </si>
-  <si>
-    <t>#be68c9</t>
-  </si>
-  <si>
-    <t>あかちゃんえき</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%81%82%E3%81%8B%E3%81%A1%E3%82%83%E3%82%93%E3%81%88%E3%81%8D%E4%B8%80%E8%A6%A7/tiles.json</t>
-  </si>
-  <si>
-    <t>baby</t>
-  </si>
-  <si>
-    <t>地域・コミュニティ</t>
-  </si>
-  <si>
-    <t>地域交流センター</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%9C%B0%E5%9F%9F%E4%BA%A4%E6%B5%81%E3%82%BB%E3%83%B3%E3%82%BF%E3%83%BC/tiles.json</t>
-  </si>
-  <si>
-    <t>daycare</t>
-  </si>
-  <si>
-    <t>自治会区域</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E8%87%AA%E6%B2%BB%E4%BC%9A%E5%8C%BA%E5%9F%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>#564340</t>
-  </si>
-  <si>
-    <t>文化・スポーツ</t>
-  </si>
-  <si>
-    <t>小泉八雲ゆかりの地</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%B0%8F%E6%B3%89%E5%85%AB%E9%9B%B2%E3%83%9E%E3%83%83%E3%83%97/tiles.json</t>
-  </si>
-  <si>
-    <t>historical-folk-facilities</t>
-  </si>
-  <si>
-    <t>浜通り（八雲通り）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%B0%8F%E6%B3%89%E5%85%AB%E9%9B%B2%E3%83%9E%E3%83%83%E3%83%97_%E6%B5%9C%E9%80%9A%E3%82%8A/tiles.json</t>
-  </si>
-  <si>
-    <t>文化会館・資料館</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%96%87%E5%8C%96%E4%BC%9A%E9%A4%A8%E3%83%BB%E8%B3%87%E6%96%99%E9%A4%A8/tiles.json</t>
-  </si>
-  <si>
-    <t>museums</t>
-  </si>
-  <si>
-    <t>図書館</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%9B%B3%E6%9B%B8%E9%A4%A8/tiles.json</t>
-  </si>
-  <si>
-    <t>library</t>
-  </si>
-  <si>
-    <t>スポーツ施設</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%82%B9%E3%83%9D%E3%83%BC%E3%83%84%E6%96%BD%E8%A8%AD/tiles.json</t>
-  </si>
-  <si>
-    <t>sports</t>
-  </si>
-  <si>
-    <t>文化財マップ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E6%96%87%E5%8C%96%E8%B2%A1%E3%83%9E%E3%83%83%E3%83%97/tiles.json</t>
-  </si>
-  <si>
-    <t>bunkazai</t>
-  </si>
-  <si>
-    <t>埋蔵文化財</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%9F%8B%E8%94%B5%E6%96%87%E5%8C%96%E8%B2%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>#ff0302</t>
-  </si>
-  <si>
-    <t>健康・福祉</t>
-  </si>
-  <si>
-    <t>ベジチェック設置場所</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%83%99%E3%82%B8%E3%83%81%E3%82%A7%E3%83%83%E3%82%AF%E8%A8%AD%E7%BD%AE%E5%A0%B4%E6%89%80/tiles.json</t>
-  </si>
-  <si>
-    <t>agricultural-experience-facility</t>
-  </si>
-  <si>
-    <t>まちなか涼みどころ</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E3%81%BE%E3%81%A1%E3%81%AA%E3%81%8B%E6%B6%BC%E3%81%BF%E3%81%A9%E3%81%93%E3%82%8D/tiles.json</t>
-  </si>
-  <si>
-    <t>reservoir</t>
-  </si>
-  <si>
-    <t>福祉会館</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E7%A6%8F%E7%A5%89%E4%BC%9A%E9%A4%A8/tiles.json</t>
-  </si>
-  <si>
-    <t>welfare-center</t>
-  </si>
-  <si>
-    <t>AED設置場所</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/AED%E8%A8%AD%E7%BD%AE%E7%AE%87%E6%89%80%E4%B8%80%E8%A6%A7/tiles.json</t>
-  </si>
-  <si>
-    <t>aed</t>
-  </si>
-  <si>
-    <t>市の窓口</t>
-  </si>
-  <si>
-    <t>市役所など</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%B8%82%E5%BD%B9%E6%89%80%E3%83%BB%E3%82%BB%E3%83%B3%E3%82%BF%E3%83%BC/tiles.json</t>
-  </si>
-  <si>
-    <t>public-facility-navy</t>
-  </si>
-  <si>
-    <t>Free Wi-Fiスポット</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E5%85%AC%E8%A1%86%E7%84%A1%E7%B7%9ALAN%E4%B8%80%E8%A6%A7/tiles.json</t>
-  </si>
-  <si>
-    <t>wifi-access-point</t>
-  </si>
-  <si>
-    <t>焼津駅前を歩こう！</t>
-  </si>
-  <si>
-    <t>有料駐車場（焼津駅周辺）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%AD%9A%E3%83%95%E3%82%A7%E3%82%B9%E5%91%A8%E8%BE%BA%E3%82%B9%E3%83%9D%E3%83%83%E3%83%88_%E6%9C%89%E6%96%99%E9%A7%90%E8%BB%8A%E5%A0%B4/tiles.json</t>
-  </si>
-  <si>
-    <t>歴史・史跡</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%AD%9A%E3%83%95%E3%82%A7%E3%82%B9%E5%91%A8%E8%BE%BA%E3%82%B9%E3%83%9D%E3%83%83%E3%83%88_%E5%8F%B2%E8%B7%A1/tiles.json</t>
-  </si>
-  <si>
-    <t>便利なスポット</t>
-  </si>
-  <si>
-    <t>休憩場所（ベンチ）</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%AD%9A%E3%83%95%E3%82%A7%E3%82%B9%E5%91%A8%E8%BE%BA%E3%82%B9%E3%83%9D%E3%83%83%E3%83%88_%E4%BC%91%E6%86%A9%E5%A0%B4%E6%89%80/tiles.json</t>
-  </si>
-  <si>
-    <t>自動販売機</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%AD%9A%E3%83%95%E3%82%A7%E3%82%B9%E5%91%A8%E8%BE%BA%E3%82%B9%E3%83%9D%E3%83%83%E3%83%88_%E8%87%AA%E5%8B%95%E8%B2%A9%E5%A3%B2%E6%A9%9F/tiles.json</t>
-  </si>
-  <si>
-    <t>vending-machine</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/%E9%AD%9A%E3%83%95%E3%82%A7%E3%82%B9%E5%91%A8%E8%BE%BA%E3%82%B9%E3%83%9D%E3%83%83%E3%83%88_%E3%81%9D%E3%81%AE%E4%BB%96/tiles.json</t>
-  </si>
-  <si>
-    <t>marker-ultramarine</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>高潮浸水想定区域（想定最大時間）</t>
+    <rPh sb="8" eb="9">
+      <t>（</t>
+    </rPh>
+    <rPh sb="9" eb="15">
+      <t xml:space="preserve">ソウテイサイダイジカン </t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>家屋倒壊等氾濫想定区域（氾濫流）</t>
+    <rPh sb="12" eb="15">
+      <t xml:space="preserve">ハンランリュウ </t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2034,6 +2061,20 @@
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="MS Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2189,7 +2230,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2288,6 +2329,13 @@
     <xf numFmtId="49" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5190,91 +5238,183 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A72" t="s">
+    <row r="72" spans="1:26" ht="13.5" customHeight="1">
+      <c r="A72" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B72" t="s">
-        <v>169</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="B72" s="5"/>
+      <c r="C72" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="13" t="s">
         <v>171</v>
       </c>
+      <c r="E72" s="5"/>
+      <c r="F72" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="3"/>
     </row>
     <row r="73" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A73" t="s">
+      <c r="A73" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B73" t="s">
-        <v>169</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="B73" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D73" t="s">
+      <c r="C73" s="6" t="s">
         <v>173</v>
       </c>
+      <c r="D73" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+      <c r="S73" s="3"/>
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73" s="3"/>
+      <c r="W73" s="3"/>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="3"/>
+      <c r="Z73" s="3"/>
     </row>
     <row r="74" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A74" t="s">
+      <c r="A74" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B74" t="s">
-        <v>174</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="B74" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="E74" t="s">
-        <v>157</v>
-      </c>
-      <c r="H74" t="s">
-        <v>157</v>
-      </c>
+      <c r="E74" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="3"/>
     </row>
     <row r="75" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A75" t="s">
+      <c r="A75" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="D75" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="E75" t="s">
-        <v>157</v>
-      </c>
-      <c r="H75" t="s">
-        <v>157</v>
-      </c>
+      <c r="E75" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+      <c r="S75" s="3"/>
+      <c r="T75" s="3"/>
+      <c r="U75" s="3"/>
+      <c r="V75" s="3"/>
+      <c r="W75" s="3"/>
+      <c r="X75" s="3"/>
+      <c r="Y75" s="3"/>
+      <c r="Z75" s="3"/>
     </row>
     <row r="76" spans="1:26" ht="13.5" customHeight="1">
       <c r="A76" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B76" s="5"/>
+      <c r="B76" s="6" t="s">
+        <v>172</v>
+      </c>
       <c r="C76" s="6" t="s">
         <v>179</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="E76" s="5"/>
-      <c r="F76" s="6" t="s">
-        <v>76</v>
-      </c>
+      <c r="E76" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="5"/>
       <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
+      <c r="H76" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
@@ -5299,13 +5439,13 @@
         <v>16</v>
       </c>
       <c r="B77" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C77" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="D77" s="13" t="s">
         <v>182</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>183</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>15</v>
@@ -5339,27 +5479,27 @@
         <v>16</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C78" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D78" s="13" t="s">
         <v>184</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>185</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
       <c r="H78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I78" s="5"/>
-      <c r="J78" s="5"/>
-      <c r="K78" s="5"/>
-      <c r="L78" s="5"/>
-      <c r="M78" s="6"/>
+      <c r="I78" s="16"/>
+      <c r="J78" s="16"/>
+      <c r="K78" s="16"/>
+      <c r="L78" s="16"/>
+      <c r="M78" s="17"/>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
@@ -5379,13 +5519,13 @@
         <v>16</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C79" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D79" s="13" t="s">
         <v>186</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>187</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>15</v>
@@ -5419,13 +5559,13 @@
         <v>16</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C80" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D80" s="13" t="s">
         <v>188</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>189</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>15</v>
@@ -5459,13 +5599,13 @@
         <v>16</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C81" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D81" s="13" t="s">
         <v>190</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>191</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>15</v>
@@ -5499,27 +5639,27 @@
         <v>16</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C82" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D82" s="13" t="s">
         <v>192</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>193</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F82" s="16"/>
-      <c r="G82" s="16"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
       <c r="H82" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I82" s="16"/>
-      <c r="J82" s="16"/>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="17"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="6"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
@@ -5539,13 +5679,13 @@
         <v>16</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C83" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D83" s="13" t="s">
         <v>194</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>195</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>15</v>
@@ -5579,13 +5719,13 @@
         <v>16</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C84" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D84" s="13" t="s">
         <v>196</v>
-      </c>
-      <c r="D84" s="13" t="s">
-        <v>197</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>15</v>
@@ -5619,13 +5759,13 @@
         <v>16</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C85" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D85" s="13" t="s">
         <v>198</v>
-      </c>
-      <c r="D85" s="13" t="s">
-        <v>199</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>15</v>
@@ -5659,13 +5799,13 @@
         <v>16</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C86" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D86" s="13" t="s">
         <v>200</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>201</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>15</v>
@@ -5699,13 +5839,13 @@
         <v>16</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C87" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D87" s="13" t="s">
         <v>202</v>
-      </c>
-      <c r="D87" s="13" t="s">
-        <v>203</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>15</v>
@@ -5739,13 +5879,13 @@
         <v>16</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C88" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D88" s="13" t="s">
         <v>204</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>205</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>15</v>
@@ -5779,13 +5919,13 @@
         <v>16</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C89" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D89" s="13" t="s">
         <v>206</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>207</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>15</v>
@@ -5819,27 +5959,27 @@
         <v>16</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C90" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D90" s="13" t="s">
         <v>208</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>209</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="16"/>
       <c r="H90" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I90" s="5"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="5"/>
-      <c r="M90" s="6"/>
+      <c r="I90" s="16"/>
+      <c r="J90" s="16"/>
+      <c r="K90" s="16"/>
+      <c r="L90" s="16"/>
+      <c r="M90" s="17"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
@@ -5859,13 +5999,13 @@
         <v>16</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C91" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D91" s="13" t="s">
         <v>210</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>211</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>15</v>
@@ -5899,27 +6039,27 @@
         <v>16</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C92" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D92" s="13" t="s">
         <v>212</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>213</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="16"/>
       <c r="H92" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="5"/>
-      <c r="M92" s="6"/>
+      <c r="K92" s="16"/>
+      <c r="L92" s="16"/>
+      <c r="M92" s="17"/>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
@@ -5939,13 +6079,13 @@
         <v>16</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C93" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D93" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>215</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>15</v>
@@ -5975,182 +6115,114 @@
       <c r="Z93" s="3"/>
     </row>
     <row r="94" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B94" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" s="16"/>
-      <c r="G94" s="16"/>
-      <c r="H94" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" s="16"/>
-      <c r="J94" s="16"/>
-      <c r="K94" s="16"/>
-      <c r="L94" s="16"/>
-      <c r="M94" s="17"/>
-      <c r="N94" s="3"/>
-      <c r="O94" s="3"/>
-      <c r="P94" s="3"/>
-      <c r="Q94" s="3"/>
-      <c r="R94" s="3"/>
-      <c r="S94" s="3"/>
-      <c r="T94" s="3"/>
-      <c r="U94" s="3"/>
-      <c r="V94" s="3"/>
-      <c r="W94" s="3"/>
-      <c r="X94" s="3"/>
-      <c r="Y94" s="3"/>
-      <c r="Z94" s="3"/>
-    </row>
-    <row r="95" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A95" s="8" t="s">
+      <c r="B94" s="44"/>
+      <c r="C94" s="44" t="s">
+        <v>628</v>
+      </c>
+      <c r="D94" s="46" t="s">
+        <v>623</v>
+      </c>
+      <c r="E94" s="43"/>
+      <c r="F94" s="43"/>
+      <c r="G94" s="43"/>
+      <c r="H94" s="43"/>
+      <c r="I94" s="43"/>
+      <c r="J94" s="43"/>
+      <c r="K94" s="43"/>
+      <c r="L94" s="43"/>
+      <c r="M94" s="43"/>
+    </row>
+    <row r="95" spans="1:26" ht="15" customHeight="1">
+      <c r="A95" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B95" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I95" s="5"/>
-      <c r="J95" s="5"/>
-      <c r="K95" s="5"/>
-      <c r="L95" s="5"/>
-      <c r="M95" s="6"/>
-      <c r="N95" s="3"/>
-      <c r="O95" s="3"/>
-      <c r="P95" s="3"/>
-      <c r="Q95" s="3"/>
-      <c r="R95" s="3"/>
-      <c r="S95" s="3"/>
-      <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
-      <c r="X95" s="3"/>
-      <c r="Y95" s="3"/>
-      <c r="Z95" s="3"/>
+      <c r="B95" s="44"/>
+      <c r="C95" s="44" t="s">
+        <v>626</v>
+      </c>
+      <c r="D95" s="46" t="s">
+        <v>622</v>
+      </c>
+      <c r="E95" s="43"/>
+      <c r="F95" s="43"/>
+      <c r="G95" s="43"/>
+      <c r="H95" s="43"/>
+      <c r="I95" s="43"/>
+      <c r="J95" s="43"/>
+      <c r="K95" s="43"/>
+      <c r="L95" s="43"/>
+      <c r="M95" s="43"/>
     </row>
     <row r="96" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="44" t="s">
+        <v>619</v>
+      </c>
+      <c r="B96" s="43"/>
+      <c r="C96" s="44" t="s">
+        <v>629</v>
+      </c>
+      <c r="D96" s="46" t="s">
+        <v>624</v>
+      </c>
+      <c r="E96" s="45" t="s">
+        <v>621</v>
+      </c>
+      <c r="F96" s="43"/>
+      <c r="G96" s="43"/>
+      <c r="H96" s="45" t="s">
+        <v>621</v>
+      </c>
+      <c r="I96" s="43"/>
+      <c r="J96" s="43"/>
+      <c r="K96" s="43"/>
+      <c r="L96" s="43"/>
+      <c r="M96" s="43"/>
+    </row>
+    <row r="97" spans="1:26" ht="13.5" customHeight="1">
+      <c r="A97" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B96" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F96" s="16"/>
-      <c r="G96" s="16"/>
-      <c r="H96" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I96" s="5"/>
-      <c r="J96" s="5"/>
-      <c r="K96" s="16"/>
-      <c r="L96" s="16"/>
-      <c r="M96" s="17"/>
-      <c r="N96" s="3"/>
-      <c r="O96" s="3"/>
-      <c r="P96" s="3"/>
-      <c r="Q96" s="3"/>
-      <c r="R96" s="3"/>
-      <c r="S96" s="3"/>
-      <c r="T96" s="3"/>
-      <c r="U96" s="3"/>
-      <c r="V96" s="3"/>
-      <c r="W96" s="3"/>
-      <c r="X96" s="3"/>
-      <c r="Y96" s="3"/>
-      <c r="Z96" s="3"/>
-    </row>
-    <row r="97" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A97" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D97" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I97" s="5"/>
-      <c r="J97" s="5"/>
-      <c r="K97" s="5"/>
-      <c r="L97" s="5"/>
-      <c r="M97" s="6"/>
-      <c r="N97" s="3"/>
-      <c r="O97" s="3"/>
-      <c r="P97" s="3"/>
-      <c r="Q97" s="3"/>
-      <c r="R97" s="3"/>
-      <c r="S97" s="3"/>
-      <c r="T97" s="3"/>
-      <c r="U97" s="3"/>
-      <c r="V97" s="3"/>
-      <c r="W97" s="3"/>
-      <c r="X97" s="3"/>
-      <c r="Y97" s="3"/>
-      <c r="Z97" s="3"/>
+      <c r="B97" s="43"/>
+      <c r="C97" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="D97" s="46" t="s">
+        <v>625</v>
+      </c>
+      <c r="E97" s="45" t="s">
+        <v>620</v>
+      </c>
+      <c r="F97" s="43"/>
+      <c r="G97" s="43"/>
+      <c r="H97" s="45" t="s">
+        <v>620</v>
+      </c>
+      <c r="I97" s="43"/>
+      <c r="J97" s="43"/>
+      <c r="K97" s="43"/>
+      <c r="L97" s="43"/>
+      <c r="M97" s="43"/>
     </row>
     <row r="98" spans="1:26" ht="13.5" customHeight="1">
       <c r="A98" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B98" s="5"/>
-      <c r="C98" s="6" t="s">
-        <v>225</v>
+      <c r="C98" s="47" t="s">
+        <v>627</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
       <c r="H98" s="4"/>
       <c r="I98" s="6" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="J98" s="5"/>
       <c r="K98" s="5"/>
@@ -6172,23 +6244,23 @@
     </row>
     <row r="99" spans="1:26" ht="13.5" customHeight="1">
       <c r="A99" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B99" s="33" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
       <c r="H99" s="4"/>
       <c r="I99" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J99" s="5"/>
       <c r="K99" s="5"/>
@@ -6210,23 +6282,23 @@
     </row>
     <row r="100" spans="1:26" ht="13.5" customHeight="1">
       <c r="A100" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B100" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="C100" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="D100" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="B100" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="C100" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>233</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="16"/>
       <c r="G100" s="16"/>
       <c r="H100" s="4"/>
       <c r="I100" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J100" s="5"/>
       <c r="K100" s="5"/>
@@ -6248,23 +6320,23 @@
     </row>
     <row r="101" spans="1:26" ht="13.5" customHeight="1">
       <c r="A101" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B101" s="33" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="16"/>
       <c r="G101" s="16"/>
       <c r="H101" s="4"/>
       <c r="I101" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
@@ -6286,23 +6358,23 @@
     </row>
     <row r="102" spans="1:26" ht="13.5" customHeight="1">
       <c r="A102" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B102" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="C102" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="D102" s="40" t="s">
         <v>228</v>
-      </c>
-      <c r="C102" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="D102" s="40" t="s">
-        <v>237</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="16"/>
       <c r="G102" s="16"/>
       <c r="H102" s="4"/>
       <c r="I102" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J102" s="5"/>
       <c r="K102" s="5"/>
@@ -6324,23 +6396,23 @@
     </row>
     <row r="103" spans="1:26" ht="13.5" customHeight="1">
       <c r="A103" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B103" s="33" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C103" s="26" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="16"/>
       <c r="G103" s="16"/>
       <c r="H103" s="4"/>
       <c r="I103" s="6" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J103" s="5"/>
       <c r="K103" s="5"/>
@@ -6362,23 +6434,23 @@
     </row>
     <row r="104" spans="1:26" ht="13.5" customHeight="1">
       <c r="A104" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="16"/>
       <c r="G104" s="16"/>
       <c r="H104" s="4"/>
       <c r="I104" s="6" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
@@ -6400,23 +6472,23 @@
     </row>
     <row r="105" spans="1:26" ht="13.5" customHeight="1">
       <c r="A105" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="5"/>
       <c r="G105" s="16"/>
       <c r="H105" s="4"/>
       <c r="I105" s="6" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
@@ -6438,21 +6510,21 @@
     </row>
     <row r="106" spans="1:26" ht="15" customHeight="1">
       <c r="A106" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="16"/>
       <c r="G106" s="16"/>
       <c r="H106" s="4"/>
       <c r="I106" s="6" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="J106" s="5"/>
       <c r="K106" s="5"/>
@@ -6474,21 +6546,21 @@
     </row>
     <row r="107" spans="1:26" ht="13.5" customHeight="1">
       <c r="A107" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="16"/>
       <c r="G107" s="16"/>
       <c r="H107" s="4"/>
       <c r="I107" s="6" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="J107" s="5"/>
       <c r="K107" s="5"/>
@@ -6510,21 +6582,21 @@
     </row>
     <row r="108" spans="1:26" ht="13.5" customHeight="1">
       <c r="A108" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="16"/>
       <c r="G108" s="16"/>
       <c r="H108" s="4"/>
       <c r="I108" s="6" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="J108" s="5"/>
       <c r="K108" s="5"/>
@@ -6546,23 +6618,23 @@
     </row>
     <row r="109" spans="1:26" ht="12.75" customHeight="1">
       <c r="A109" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="16"/>
       <c r="G109" s="16"/>
       <c r="H109" s="4"/>
       <c r="I109" s="8" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
@@ -6584,22 +6656,22 @@
     </row>
     <row r="110" spans="1:26" ht="12.75" customHeight="1">
       <c r="A110" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="5"/>
       <c r="G110" s="5"/>
       <c r="H110" s="8" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
@@ -6622,21 +6694,21 @@
     </row>
     <row r="111" spans="1:26" ht="12.75" customHeight="1">
       <c r="A111" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B111" s="5"/>
       <c r="C111" s="8" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E111" s="4"/>
       <c r="F111" s="16"/>
       <c r="G111" s="16"/>
       <c r="H111" s="4"/>
       <c r="I111" s="6" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="J111" s="5"/>
       <c r="K111" s="5"/>
@@ -6658,20 +6730,20 @@
     </row>
     <row r="112" spans="1:26" ht="12.75" customHeight="1">
       <c r="A112" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B112" s="5"/>
       <c r="C112" s="8" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="5"/>
       <c r="G112" s="5"/>
       <c r="H112" s="4" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
@@ -6694,20 +6766,20 @@
     </row>
     <row r="113" spans="1:26" ht="12.75" customHeight="1">
       <c r="A113" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E113" s="5"/>
       <c r="F113" s="6" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
@@ -6732,20 +6804,20 @@
     </row>
     <row r="114" spans="1:26" ht="12.75" customHeight="1">
       <c r="A114" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="E114" s="5"/>
       <c r="F114" s="6" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -6770,20 +6842,20 @@
     </row>
     <row r="115" spans="1:26" ht="12.75" customHeight="1">
       <c r="A115" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E115" s="5"/>
       <c r="F115" s="6" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
@@ -6808,20 +6880,20 @@
     </row>
     <row r="116" spans="1:26" ht="13.5" customHeight="1">
       <c r="A116" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E116" s="5"/>
       <c r="F116" s="6" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
@@ -6846,20 +6918,20 @@
     </row>
     <row r="117" spans="1:26" ht="13.5" customHeight="1">
       <c r="A117" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E117" s="5"/>
       <c r="F117" s="6" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
@@ -6884,20 +6956,20 @@
     </row>
     <row r="118" spans="1:26" ht="13.5" customHeight="1">
       <c r="A118" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E118" s="5"/>
       <c r="F118" s="6" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -6922,20 +6994,20 @@
     </row>
     <row r="119" spans="1:26" ht="13.5" customHeight="1">
       <c r="A119" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="6" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
@@ -6960,23 +7032,23 @@
     </row>
     <row r="120" spans="1:26" ht="13.5" customHeight="1">
       <c r="A120" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
       <c r="I120" s="6" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="J120" s="16"/>
       <c r="K120" s="5"/>
@@ -6998,23 +7070,23 @@
     </row>
     <row r="121" spans="1:26" ht="13.5" customHeight="1">
       <c r="A121" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
       <c r="H121" s="5"/>
       <c r="I121" s="6" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="J121" s="16"/>
       <c r="K121" s="5"/>
@@ -7036,24 +7108,24 @@
     </row>
     <row r="122" spans="1:26" ht="13.5" customHeight="1">
       <c r="A122" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E122" s="5"/>
       <c r="F122" s="17" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="G122" s="5"/>
       <c r="H122" s="17" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
@@ -7076,14 +7148,14 @@
     </row>
     <row r="123" spans="1:26" ht="13.5" customHeight="1">
       <c r="A123" s="6" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="6" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
@@ -7110,19 +7182,19 @@
     </row>
     <row r="124" spans="1:26" ht="13.5" customHeight="1">
       <c r="A124" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
@@ -7148,19 +7220,19 @@
     </row>
     <row r="125" spans="1:26" ht="13.5" customHeight="1">
       <c r="A125" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="E125" s="8" t="s">
         <v>301</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>310</v>
       </c>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
@@ -7186,19 +7258,19 @@
     </row>
     <row r="126" spans="1:26" ht="13.5" customHeight="1">
       <c r="A126" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B126" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="E126" s="8" t="s">
         <v>304</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D126" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>313</v>
       </c>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
@@ -7224,19 +7296,19 @@
     </row>
     <row r="127" spans="1:26" ht="13.5" customHeight="1">
       <c r="A127" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
@@ -7262,19 +7334,19 @@
     </row>
     <row r="128" spans="1:26" ht="13.5" customHeight="1">
       <c r="A128" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="F128" s="5"/>
       <c r="G128" s="5"/>
@@ -7300,19 +7372,19 @@
     </row>
     <row r="129" spans="1:26" ht="13.5" customHeight="1">
       <c r="A129" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="F129" s="5"/>
       <c r="G129" s="5"/>
@@ -7338,19 +7410,19 @@
     </row>
     <row r="130" spans="1:26" ht="13.5" customHeight="1">
       <c r="A130" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="F130" s="5"/>
       <c r="G130" s="5"/>
@@ -7376,19 +7448,19 @@
     </row>
     <row r="131" spans="1:26" ht="13.5" customHeight="1">
       <c r="A131" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
@@ -7414,19 +7486,19 @@
     </row>
     <row r="132" spans="1:26" ht="13.5" customHeight="1">
       <c r="A132" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="F132" s="5"/>
       <c r="G132" s="5"/>
@@ -7452,19 +7524,19 @@
     </row>
     <row r="133" spans="1:26" ht="13.5" customHeight="1">
       <c r="A133" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
@@ -7490,19 +7562,19 @@
     </row>
     <row r="134" spans="1:26" ht="13.5" customHeight="1">
       <c r="A134" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
@@ -7528,19 +7600,19 @@
     </row>
     <row r="135" spans="1:26" ht="13.5" customHeight="1">
       <c r="A135" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
@@ -7566,22 +7638,22 @@
     </row>
     <row r="136" spans="1:26" ht="13.5" customHeight="1">
       <c r="A136" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
@@ -7606,22 +7678,22 @@
     </row>
     <row r="137" spans="1:26" ht="13.5" customHeight="1">
       <c r="A137" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
@@ -7646,22 +7718,22 @@
     </row>
     <row r="138" spans="1:26" ht="13.5" customHeight="1">
       <c r="A138" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B138" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D138" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>348</v>
-      </c>
       <c r="E138" s="6" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -7686,22 +7758,22 @@
     </row>
     <row r="139" spans="1:26" ht="13.5" customHeight="1">
       <c r="A139" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -7726,22 +7798,22 @@
     </row>
     <row r="140" spans="1:26" ht="13.5" customHeight="1">
       <c r="A140" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -7766,22 +7838,22 @@
     </row>
     <row r="141" spans="1:26" ht="13.5" customHeight="1">
       <c r="A141" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -7806,22 +7878,22 @@
     </row>
     <row r="142" spans="1:26" ht="13.5" customHeight="1">
       <c r="A142" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -7846,22 +7918,22 @@
     </row>
     <row r="143" spans="1:26" ht="13.5" customHeight="1">
       <c r="A143" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="4"/>
@@ -7886,22 +7958,22 @@
     </row>
     <row r="144" spans="1:26" ht="13.5" customHeight="1">
       <c r="A144" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -7926,22 +7998,22 @@
     </row>
     <row r="145" spans="1:26" ht="13.5" customHeight="1">
       <c r="A145" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
@@ -7966,22 +8038,22 @@
     </row>
     <row r="146" spans="1:26" ht="13.5" customHeight="1">
       <c r="A146" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
@@ -8006,22 +8078,22 @@
     </row>
     <row r="147" spans="1:26" ht="13.5" customHeight="1">
       <c r="A147" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
@@ -8046,22 +8118,22 @@
     </row>
     <row r="148" spans="1:26" ht="13.5" customHeight="1">
       <c r="A148" s="6" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D148" s="13" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
@@ -8086,22 +8158,22 @@
     </row>
     <row r="149" spans="1:26" ht="13.5" customHeight="1">
       <c r="A149" s="6" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
@@ -8126,21 +8198,21 @@
     </row>
     <row r="150" spans="1:26" ht="13.5" customHeight="1">
       <c r="A150" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B150" s="5"/>
       <c r="C150" s="6" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="E150" s="5"/>
       <c r="F150" s="16"/>
       <c r="G150" s="16"/>
       <c r="H150" s="5"/>
       <c r="I150" s="17" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="J150" s="16"/>
       <c r="K150" s="5"/>
@@ -8162,21 +8234,21 @@
     </row>
     <row r="151" spans="1:26" ht="13.5" customHeight="1">
       <c r="A151" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="6" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="E151" s="5"/>
       <c r="F151" s="16"/>
       <c r="G151" s="16"/>
       <c r="H151" s="5"/>
       <c r="I151" s="17" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="J151" s="16"/>
       <c r="K151" s="5"/>
@@ -8198,22 +8270,22 @@
     </row>
     <row r="152" spans="1:26" ht="13.5" customHeight="1">
       <c r="A152" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B152" s="5"/>
       <c r="C152" s="6" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F152" s="5"/>
       <c r="G152" s="5"/>
       <c r="H152" s="6" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
@@ -8236,22 +8308,22 @@
     </row>
     <row r="153" spans="1:26" ht="13.5" customHeight="1">
       <c r="A153" s="6" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="6" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="F153" s="5"/>
       <c r="G153" s="5"/>
       <c r="H153" s="6" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
@@ -8274,22 +8346,22 @@
     </row>
     <row r="154" spans="1:26" ht="13.5" customHeight="1">
       <c r="A154" s="6" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B154" s="5"/>
       <c r="C154" s="6" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="F154" s="5"/>
       <c r="G154" s="5"/>
       <c r="H154" s="6" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
@@ -8312,20 +8384,20 @@
     </row>
     <row r="155" spans="1:26" ht="13.5" customHeight="1">
       <c r="A155" s="6" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="6" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>76</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
@@ -8350,17 +8422,17 @@
     </row>
     <row r="156" spans="1:26" ht="13.5" customHeight="1">
       <c r="A156" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B156" s="6"/>
       <c r="C156" s="6" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F156" s="5"/>
       <c r="G156" s="5"/>
@@ -8386,22 +8458,22 @@
     </row>
     <row r="157" spans="1:26" ht="15" customHeight="1">
       <c r="A157" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
@@ -8410,7 +8482,7 @@
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
       <c r="M157" s="6" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="N157" s="3"/>
       <c r="O157" s="3"/>
@@ -8428,33 +8500,33 @@
     </row>
     <row r="158" spans="1:26" ht="13.5" customHeight="1">
       <c r="A158" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C158" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="B158" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>412</v>
-      </c>
       <c r="D158" s="11" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="G158" s="5"/>
       <c r="H158" s="6" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
       <c r="M158" s="6" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="N158" s="3"/>
       <c r="O158" s="3"/>
@@ -8472,33 +8544,33 @@
     </row>
     <row r="159" spans="1:26" ht="13.5" customHeight="1">
       <c r="A159" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B159" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="D159" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="C159" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="D159" s="11" t="s">
-        <v>416</v>
-      </c>
       <c r="E159" s="6" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="6" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
       <c r="M159" s="6" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="N159" s="3"/>
       <c r="O159" s="3"/>
@@ -8516,33 +8588,33 @@
     </row>
     <row r="160" spans="1:26" ht="13.5" customHeight="1">
       <c r="A160" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="G160" s="5"/>
       <c r="H160" s="6" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
       <c r="K160" s="5"/>
       <c r="L160" s="5"/>
       <c r="M160" s="6" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="N160" s="3"/>
       <c r="O160" s="3"/>
@@ -8560,23 +8632,23 @@
     </row>
     <row r="161" spans="1:26" ht="13.5" customHeight="1">
       <c r="A161" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
       <c r="I161" s="6" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="J161" s="5"/>
       <c r="K161" s="5"/>
@@ -8598,16 +8670,16 @@
     </row>
     <row r="162" spans="1:26" ht="13.5" customHeight="1">
       <c r="A162" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="E162" s="5"/>
       <c r="F162" s="5"/>
@@ -8634,23 +8706,23 @@
     </row>
     <row r="163" spans="1:26" ht="13.5" customHeight="1">
       <c r="A163" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="E163" s="5"/>
       <c r="F163" s="5"/>
       <c r="G163" s="5"/>
       <c r="H163" s="5"/>
       <c r="I163" s="6" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="J163" s="5"/>
       <c r="K163" s="5"/>
@@ -8672,26 +8744,26 @@
     </row>
     <row r="164" spans="1:26" ht="13.5" customHeight="1">
       <c r="A164" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="6" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
@@ -8714,23 +8786,23 @@
     </row>
     <row r="165" spans="1:26" ht="13.5" customHeight="1">
       <c r="A165" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E165" s="5"/>
       <c r="F165" s="5"/>
       <c r="G165" s="5"/>
       <c r="H165" s="5"/>
       <c r="I165" s="6" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="J165" s="5"/>
       <c r="K165" s="5"/>
@@ -8752,23 +8824,23 @@
     </row>
     <row r="166" spans="1:26" ht="13.5" customHeight="1">
       <c r="A166" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B166" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="C166" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="C166" s="6" t="s">
-        <v>436</v>
-      </c>
       <c r="D166" s="11" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="E166" s="5"/>
       <c r="F166" s="5"/>
       <c r="G166" s="5"/>
       <c r="H166" s="5"/>
       <c r="I166" s="8" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="J166" s="5"/>
       <c r="K166" s="5"/>
@@ -8790,23 +8862,23 @@
     </row>
     <row r="167" spans="1:26" ht="13.5" customHeight="1">
       <c r="A167" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E167" s="5"/>
       <c r="F167" s="5"/>
       <c r="G167" s="5"/>
       <c r="H167" s="5"/>
       <c r="I167" s="8" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="J167" s="5"/>
       <c r="K167" s="5"/>
@@ -8828,23 +8900,23 @@
     </row>
     <row r="168" spans="1:26" ht="13.5" customHeight="1">
       <c r="A168" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E168" s="5"/>
       <c r="F168" s="5"/>
       <c r="G168" s="5"/>
       <c r="H168" s="5"/>
       <c r="I168" s="8" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J168" s="5"/>
       <c r="K168" s="5"/>
@@ -8866,26 +8938,26 @@
     </row>
     <row r="169" spans="1:26" ht="13.5" customHeight="1">
       <c r="A169" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="G169" s="5"/>
       <c r="H169" s="6" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
@@ -8908,24 +8980,24 @@
     </row>
     <row r="170" spans="1:26" ht="13.5" customHeight="1">
       <c r="A170" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D170" s="13" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="F170" s="5"/>
       <c r="G170" s="5"/>
       <c r="H170" s="6" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
@@ -8948,24 +9020,24 @@
     </row>
     <row r="171" spans="1:26" ht="13.5" customHeight="1">
       <c r="A171" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="D171" s="13" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F171" s="5"/>
       <c r="G171" s="5"/>
       <c r="H171" s="6" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
@@ -8988,24 +9060,24 @@
     </row>
     <row r="172" spans="1:26" ht="13.5" customHeight="1">
       <c r="A172" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B172" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="E172" s="6" t="s">
         <v>447</v>
-      </c>
-      <c r="C172" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="D172" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="E172" s="6" t="s">
-        <v>456</v>
       </c>
       <c r="F172" s="5"/>
       <c r="G172" s="5"/>
       <c r="H172" s="6" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
@@ -9028,24 +9100,24 @@
     </row>
     <row r="173" spans="1:26" ht="13.5" customHeight="1">
       <c r="A173" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D173" s="13" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="F173" s="5"/>
       <c r="G173" s="5"/>
       <c r="H173" s="6" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
@@ -9068,22 +9140,22 @@
     </row>
     <row r="174" spans="1:26" ht="13.5" customHeight="1">
       <c r="A174" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B174" s="26" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C174" s="26" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D174" s="29" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="E174" s="6"/>
       <c r="F174" s="5"/>
       <c r="G174" s="5"/>
       <c r="H174" s="6" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
@@ -9106,22 +9178,22 @@
     </row>
     <row r="175" spans="1:26" ht="13.5" customHeight="1">
       <c r="A175" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B175" s="26" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C175" s="26" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="D175" s="29" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E175" s="6"/>
       <c r="F175" s="5"/>
       <c r="G175" s="5"/>
       <c r="H175" s="6" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
@@ -9144,22 +9216,22 @@
     </row>
     <row r="176" spans="1:26" ht="13.5" customHeight="1">
       <c r="A176" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B176" s="26" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C176" s="26" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="D176" s="28" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E176" s="6"/>
       <c r="F176" s="5"/>
       <c r="G176" s="5"/>
       <c r="H176" s="6" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="I176" s="5"/>
       <c r="J176" s="5"/>
@@ -9182,22 +9254,22 @@
     </row>
     <row r="177" spans="1:26" ht="13.5" customHeight="1">
       <c r="A177" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B177" s="26" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C177" s="26" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D177" s="29" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="E177" s="6"/>
       <c r="F177" s="5"/>
       <c r="G177" s="5"/>
       <c r="H177" s="6" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="I177" s="5"/>
       <c r="J177" s="5"/>
@@ -9220,22 +9292,22 @@
     </row>
     <row r="178" spans="1:26" ht="13.5" customHeight="1">
       <c r="A178" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B178" s="26" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C178" s="26" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="D178" s="29" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="E178" s="6"/>
       <c r="F178" s="5"/>
       <c r="G178" s="5"/>
       <c r="H178" s="6" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="I178" s="5"/>
       <c r="J178" s="5"/>
@@ -9258,22 +9330,22 @@
     </row>
     <row r="179" spans="1:26" ht="13.5" customHeight="1">
       <c r="A179" s="6" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="B179" s="5"/>
       <c r="C179" s="6" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F179" s="5"/>
       <c r="G179" s="5"/>
       <c r="H179" s="6" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="I179" s="5"/>
       <c r="J179" s="5"/>
@@ -9296,22 +9368,22 @@
     </row>
     <row r="180" spans="1:26" ht="13.5" customHeight="1">
       <c r="A180" s="8" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G180" s="5"/>
       <c r="H180" s="5"/>
@@ -9336,22 +9408,22 @@
     </row>
     <row r="181" spans="1:26" ht="13.5" customHeight="1">
       <c r="A181" s="8" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G181" s="5"/>
       <c r="H181" s="5"/>
@@ -9376,24 +9448,24 @@
     </row>
     <row r="182" spans="1:26" ht="13.5" customHeight="1">
       <c r="A182" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="D182" s="11" t="s">
         <v>479</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="C182" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="D182" s="11" t="s">
-        <v>488</v>
       </c>
       <c r="E182" s="5"/>
       <c r="F182" s="6" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="G182" s="5"/>
       <c r="H182" s="6" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="I182" s="5"/>
       <c r="J182" s="5"/>
@@ -9416,26 +9488,26 @@
     </row>
     <row r="183" spans="1:26" ht="13.5" customHeight="1">
       <c r="A183" s="8" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="G183" s="5"/>
       <c r="H183" s="6" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="I183" s="5"/>
       <c r="J183" s="5"/>
@@ -9458,16 +9530,16 @@
     </row>
     <row r="184" spans="1:26" ht="13.5" customHeight="1">
       <c r="A184" s="8" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>23</v>
@@ -9500,21 +9572,21 @@
     </row>
     <row r="185" spans="1:26" ht="13.5" customHeight="1">
       <c r="A185" s="8" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B185" s="5"/>
       <c r="C185" s="6" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="E185" s="5"/>
       <c r="F185" s="5"/>
       <c r="G185" s="5"/>
       <c r="H185" s="5"/>
       <c r="I185" s="6" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="J185" s="5"/>
       <c r="K185" s="5"/>
@@ -9536,23 +9608,23 @@
     </row>
     <row r="186" spans="1:26" ht="13.5" customHeight="1">
       <c r="A186" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="E186" s="5"/>
       <c r="F186" s="5"/>
       <c r="G186" s="5"/>
       <c r="H186" s="5"/>
       <c r="I186" s="8" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="J186" s="5"/>
       <c r="K186" s="5"/>
@@ -9574,24 +9646,24 @@
     </row>
     <row r="187" spans="1:26" ht="13.5" customHeight="1">
       <c r="A187" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F187" s="5"/>
       <c r="G187" s="5"/>
       <c r="H187" s="6" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="I187" s="5"/>
       <c r="J187" s="5"/>
@@ -9614,23 +9686,23 @@
     </row>
     <row r="188" spans="1:26" ht="13.5" customHeight="1">
       <c r="A188" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="D188" s="18" t="s">
         <v>499</v>
-      </c>
-      <c r="B188" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="C188" s="8" t="s">
-        <v>507</v>
-      </c>
-      <c r="D188" s="18" t="s">
-        <v>508</v>
       </c>
       <c r="E188" s="19"/>
       <c r="F188" s="19"/>
       <c r="G188" s="19"/>
       <c r="H188" s="20"/>
       <c r="I188" s="8" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="J188" s="5"/>
       <c r="K188" s="5"/>
@@ -9652,24 +9724,24 @@
     </row>
     <row r="189" spans="1:26" ht="13.5" customHeight="1">
       <c r="A189" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="F189" s="5"/>
       <c r="G189" s="5"/>
       <c r="H189" s="6" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I189" s="5"/>
       <c r="J189" s="5"/>
@@ -9692,20 +9764,20 @@
     </row>
     <row r="190" spans="1:26" ht="13.5" customHeight="1">
       <c r="A190" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="E190" s="5"/>
       <c r="F190" s="6" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="G190" s="5"/>
       <c r="H190" s="5"/>
@@ -9730,20 +9802,20 @@
     </row>
     <row r="191" spans="1:26" ht="13.5" customHeight="1">
       <c r="A191" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="E191" s="5"/>
       <c r="F191" s="6" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="G191" s="5"/>
       <c r="H191" s="5"/>
@@ -9768,20 +9840,20 @@
     </row>
     <row r="192" spans="1:26" ht="13.5" customHeight="1">
       <c r="A192" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="E192" s="5"/>
       <c r="F192" s="6" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="G192" s="5"/>
       <c r="H192" s="5"/>
@@ -9806,20 +9878,20 @@
     </row>
     <row r="193" spans="1:26" ht="13.5" customHeight="1">
       <c r="A193" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E193" s="5"/>
       <c r="F193" s="6" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="G193" s="5"/>
       <c r="H193" s="5"/>
@@ -9844,20 +9916,20 @@
     </row>
     <row r="194" spans="1:26" ht="13.5" customHeight="1">
       <c r="A194" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="E194" s="5"/>
       <c r="F194" s="6" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="G194" s="5"/>
       <c r="H194" s="5"/>
@@ -9882,20 +9954,20 @@
     </row>
     <row r="195" spans="1:26" ht="13.5" customHeight="1">
       <c r="A195" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="E195" s="5"/>
       <c r="F195" s="6" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="G195" s="5"/>
       <c r="H195" s="5"/>
@@ -9920,20 +9992,20 @@
     </row>
     <row r="196" spans="1:26" ht="13.5" customHeight="1">
       <c r="A196" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="E196" s="5"/>
       <c r="F196" s="6" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="G196" s="5"/>
       <c r="H196" s="5"/>
@@ -9958,20 +10030,20 @@
     </row>
     <row r="197" spans="1:26" ht="13.5" customHeight="1">
       <c r="A197" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="E197" s="5"/>
       <c r="F197" s="6" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="G197" s="5"/>
       <c r="H197" s="5"/>
@@ -9996,20 +10068,20 @@
     </row>
     <row r="198" spans="1:26" ht="13.5" customHeight="1">
       <c r="A198" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="E198" s="5"/>
       <c r="F198" s="6" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="G198" s="5"/>
       <c r="H198" s="5"/>
@@ -10034,20 +10106,20 @@
     </row>
     <row r="199" spans="1:26" ht="13.5" customHeight="1">
       <c r="A199" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="D199" s="11" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="E199" s="5"/>
       <c r="F199" s="6" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="G199" s="5"/>
       <c r="H199" s="5"/>
@@ -10072,20 +10144,20 @@
     </row>
     <row r="200" spans="1:26" ht="13.5" customHeight="1">
       <c r="A200" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="E200" s="5"/>
       <c r="F200" s="6" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="G200" s="5"/>
       <c r="H200" s="5"/>
@@ -10110,20 +10182,20 @@
     </row>
     <row r="201" spans="1:26" ht="13.5" customHeight="1">
       <c r="A201" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="E201" s="5"/>
       <c r="F201" s="6" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="G201" s="5"/>
       <c r="H201" s="5"/>
@@ -10148,20 +10220,20 @@
     </row>
     <row r="202" spans="1:26" ht="13.5" customHeight="1">
       <c r="A202" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="E202" s="5"/>
       <c r="F202" s="6" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="G202" s="5"/>
       <c r="H202" s="5"/>
@@ -10186,22 +10258,22 @@
     </row>
     <row r="203" spans="1:26" ht="13.5" customHeight="1">
       <c r="A203" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="E203" s="5"/>
       <c r="F203" s="5"/>
       <c r="G203" s="5"/>
       <c r="H203" s="5" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="I203" s="5"/>
       <c r="J203" s="5"/>
@@ -10224,22 +10296,22 @@
     </row>
     <row r="204" spans="1:26" ht="13.5" customHeight="1">
       <c r="A204" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="D204" s="11" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="E204" s="5"/>
       <c r="F204" s="5"/>
       <c r="G204" s="5"/>
       <c r="H204" s="5" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="I204" s="5"/>
       <c r="J204" s="5"/>
@@ -10262,22 +10334,22 @@
     </row>
     <row r="205" spans="1:26" ht="13.5" customHeight="1">
       <c r="A205" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="E205" s="5"/>
       <c r="F205" s="5"/>
       <c r="G205" s="5"/>
       <c r="H205" s="5" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="I205" s="5"/>
       <c r="J205" s="5"/>
@@ -10300,23 +10372,23 @@
     </row>
     <row r="206" spans="1:26" ht="13.5" customHeight="1">
       <c r="A206" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D206" s="11" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="E206" s="5"/>
       <c r="F206" s="5"/>
       <c r="G206" s="5"/>
       <c r="H206" s="5"/>
       <c r="I206" s="6" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="J206" s="5"/>
       <c r="K206" s="5"/>
@@ -10338,21 +10410,21 @@
     </row>
     <row r="207" spans="1:26" ht="13.5" customHeight="1">
       <c r="A207" s="8" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="B207" s="5"/>
       <c r="C207" s="8" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="E207" s="5"/>
       <c r="F207" s="5"/>
       <c r="G207" s="5"/>
       <c r="H207" s="5"/>
       <c r="I207" s="6" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="J207" s="5"/>
       <c r="K207" s="5"/>
@@ -10374,20 +10446,20 @@
     </row>
     <row r="208" spans="1:26" ht="13.5" customHeight="1">
       <c r="A208" s="8" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="B208" s="5"/>
       <c r="C208" s="8" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="D208" s="11" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="G208" s="5"/>
       <c r="H208" s="5"/>
@@ -10412,23 +10484,23 @@
     </row>
     <row r="209" spans="1:26" ht="13.5" customHeight="1">
       <c r="A209" s="6" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B209" s="33" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="C209" s="41" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="D209" s="27" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="E209" s="5"/>
       <c r="F209" s="5"/>
       <c r="G209" s="5"/>
       <c r="H209" s="5"/>
       <c r="I209" s="5" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
@@ -10450,22 +10522,22 @@
     </row>
     <row r="210" spans="1:26" ht="13.5" customHeight="1">
       <c r="A210" s="6" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B210" s="33" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="C210" s="41" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="D210" s="42" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="G210" s="5"/>
       <c r="H210" s="5"/>
@@ -10490,21 +10562,21 @@
     </row>
     <row r="211" spans="1:26" ht="13.5" customHeight="1">
       <c r="A211" s="6" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B211" s="5"/>
       <c r="C211" s="6" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="D211" s="11" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="E211" s="5"/>
       <c r="F211" s="5"/>
       <c r="G211" s="5"/>
       <c r="H211" s="5"/>
       <c r="I211" s="6" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="J211" s="5"/>
       <c r="K211" s="5"/>
@@ -10526,21 +10598,21 @@
     </row>
     <row r="212" spans="1:26" ht="13.5" customHeight="1">
       <c r="A212" s="6" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B212" s="5"/>
       <c r="C212" s="8" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="E212" s="5"/>
       <c r="F212" s="5"/>
       <c r="G212" s="5"/>
       <c r="H212" s="5"/>
       <c r="I212" s="8" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="J212" s="5"/>
       <c r="K212" s="5"/>
@@ -10562,21 +10634,21 @@
     </row>
     <row r="213" spans="1:26" ht="13.5" customHeight="1">
       <c r="A213" s="6" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B213" s="5"/>
       <c r="C213" s="8" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E213" s="5"/>
       <c r="F213" s="5"/>
       <c r="G213" s="5"/>
       <c r="H213" s="5"/>
       <c r="I213" s="6" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="J213" s="5"/>
       <c r="K213" s="5"/>
@@ -10598,21 +10670,21 @@
     </row>
     <row r="214" spans="1:26" ht="13.5" customHeight="1">
       <c r="A214" s="6" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B214" s="5"/>
       <c r="C214" s="6" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="E214" s="5"/>
       <c r="F214" s="5"/>
       <c r="G214" s="5"/>
       <c r="H214" s="5"/>
       <c r="I214" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="J214" s="5"/>
       <c r="K214" s="5"/>
@@ -10634,17 +10706,17 @@
     </row>
     <row r="215" spans="1:26" ht="13.5" customHeight="1">
       <c r="A215" s="6" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B215" s="5"/>
       <c r="C215" s="6" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="E215" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="F215" s="5"/>
       <c r="G215" s="5"/>
@@ -10670,21 +10742,21 @@
     </row>
     <row r="216" spans="1:26" ht="13.5" customHeight="1">
       <c r="A216" s="8" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B216" s="5"/>
       <c r="C216" s="26" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="D216" s="27" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="E216" s="6"/>
       <c r="F216" s="5"/>
       <c r="G216" s="5"/>
       <c r="H216" s="5"/>
       <c r="I216" s="5" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="J216" s="5"/>
       <c r="K216" s="5"/>
@@ -10706,21 +10778,21 @@
     </row>
     <row r="217" spans="1:26" ht="13.5" customHeight="1">
       <c r="A217" s="8" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B217" s="4"/>
       <c r="C217" s="21" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="D217" s="22" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="5"/>
       <c r="G217" s="5"/>
       <c r="H217" s="4"/>
       <c r="I217" s="6" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="J217" s="5"/>
       <c r="K217" s="5"/>
@@ -10742,21 +10814,21 @@
     </row>
     <row r="218" spans="1:26" ht="13.5" customHeight="1">
       <c r="A218" s="8" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B218" s="4"/>
       <c r="C218" s="8" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="5"/>
       <c r="G218" s="5"/>
       <c r="H218" s="4"/>
       <c r="I218" s="6" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="J218" s="5"/>
       <c r="K218" s="5"/>
@@ -10778,21 +10850,21 @@
     </row>
     <row r="219" spans="1:26" ht="13.5" customHeight="1">
       <c r="A219" s="8" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="8" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="5"/>
       <c r="G219" s="5"/>
       <c r="H219" s="4"/>
       <c r="I219" s="6" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="J219" s="5"/>
       <c r="K219" s="5"/>
@@ -10814,21 +10886,21 @@
     </row>
     <row r="220" spans="1:26" ht="13.5" customHeight="1">
       <c r="A220" s="8" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="B220" s="5"/>
       <c r="C220" s="6" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="E220" s="5"/>
       <c r="F220" s="5"/>
       <c r="G220" s="5"/>
       <c r="H220" s="5"/>
       <c r="I220" s="6" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="J220" s="5"/>
       <c r="K220" s="5"/>
@@ -10850,21 +10922,21 @@
     </row>
     <row r="221" spans="1:26" ht="13.5" customHeight="1">
       <c r="A221" s="8" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="B221" s="5"/>
       <c r="C221" s="6" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="D221" s="32" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="E221" s="5"/>
       <c r="F221" s="5"/>
       <c r="G221" s="5"/>
       <c r="H221" s="5"/>
       <c r="I221" s="6" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="J221" s="5"/>
       <c r="K221" s="5"/>
@@ -10886,21 +10958,21 @@
     </row>
     <row r="222" spans="1:26" ht="13.5" customHeight="1">
       <c r="A222" s="23" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B222" s="30"/>
       <c r="C222" s="36" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="D222" s="37" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="E222" s="31"/>
       <c r="F222" s="5"/>
       <c r="G222" s="5"/>
       <c r="H222" s="5"/>
       <c r="I222" s="6" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="J222" s="5"/>
       <c r="K222" s="5"/>
@@ -10922,21 +10994,21 @@
     </row>
     <row r="223" spans="1:26" ht="13.5" customHeight="1">
       <c r="A223" s="23" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B223" s="33"/>
       <c r="C223" s="38" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="E223" s="4"/>
       <c r="F223" s="16"/>
       <c r="G223" s="16"/>
       <c r="H223" s="4"/>
       <c r="I223" s="6" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="J223" s="5"/>
       <c r="K223" s="5"/>
@@ -10958,21 +11030,21 @@
     </row>
     <row r="224" spans="1:26" ht="13.5" customHeight="1">
       <c r="A224" s="23" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B224" s="33"/>
       <c r="C224" s="25" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="D224" s="24" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="E224" s="5"/>
       <c r="F224" s="5"/>
       <c r="G224" s="5"/>
       <c r="H224" s="5"/>
       <c r="I224" s="5" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="J224" s="5"/>
       <c r="K224" s="5"/>
@@ -10994,21 +11066,21 @@
     </row>
     <row r="225" spans="1:26" ht="13.5" customHeight="1">
       <c r="A225" s="23" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B225" s="30"/>
       <c r="C225" s="34" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D225" s="35" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="16"/>
       <c r="G225" s="16"/>
       <c r="H225" s="4"/>
       <c r="I225" s="6" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="J225" s="5"/>
       <c r="K225" s="5"/>
@@ -11030,21 +11102,21 @@
     </row>
     <row r="226" spans="1:26" ht="13.5" customHeight="1">
       <c r="A226" s="23" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B226" s="30"/>
       <c r="C226" s="6" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E226" s="4"/>
       <c r="F226" s="16"/>
       <c r="G226" s="16"/>
       <c r="H226" s="4"/>
       <c r="I226" s="6" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="J226" s="5"/>
       <c r="K226" s="5"/>
@@ -11066,23 +11138,23 @@
     </row>
     <row r="227" spans="1:26" ht="13.5" customHeight="1">
       <c r="A227" s="23" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B227" s="30" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="C227" s="25" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="D227" s="24" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E227" s="5"/>
       <c r="F227" s="5"/>
       <c r="G227" s="5"/>
       <c r="H227" s="5"/>
       <c r="I227" s="5" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="J227" s="5"/>
       <c r="K227" s="5"/>
@@ -11104,23 +11176,23 @@
     </row>
     <row r="228" spans="1:26" ht="13.5" customHeight="1">
       <c r="A228" s="23" t="s">
+        <v>606</v>
+      </c>
+      <c r="B228" s="30" t="s">
+        <v>611</v>
+      </c>
+      <c r="C228" s="25" t="s">
+        <v>614</v>
+      </c>
+      <c r="D228" s="24" t="s">
         <v>615</v>
-      </c>
-      <c r="B228" s="30" t="s">
-        <v>620</v>
-      </c>
-      <c r="C228" s="25" t="s">
-        <v>623</v>
-      </c>
-      <c r="D228" s="24" t="s">
-        <v>624</v>
       </c>
       <c r="E228" s="5"/>
       <c r="F228" s="5"/>
       <c r="G228" s="5"/>
       <c r="H228" s="5"/>
       <c r="I228" s="5" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="J228" s="5"/>
       <c r="K228" s="5"/>
@@ -11142,23 +11214,23 @@
     </row>
     <row r="229" spans="1:26" ht="13.5" customHeight="1">
       <c r="A229" s="23" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="B229" s="30" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="C229" s="25" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="D229" s="24" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="E229" s="5"/>
       <c r="F229" s="5"/>
       <c r="G229" s="5"/>
       <c r="H229" s="5"/>
       <c r="I229" s="5" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="J229" s="5"/>
       <c r="K229" s="5"/>
@@ -17079,145 +17151,146 @@
     <hyperlink ref="D69" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
     <hyperlink ref="D70" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
     <hyperlink ref="D71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D72" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="D73" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D74" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="D75" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D76" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D77" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D78" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D79" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D80" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D81" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D82" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D83" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D84" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D85" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D86" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D87" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D88" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D89" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D90" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D94" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D100" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D101" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D102" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D103" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D104" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D105" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="D106" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D107" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D108" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D109" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="D110" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="D111" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="D112" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="D113" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="D114" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="D115" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="D116" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="D117" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="D118" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D119" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="D120" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="D121" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="D122" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D123" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="D124" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="D125" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="D126" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="D127" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="D128" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D129" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="D130" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="D131" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="D132" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="D133" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="D134" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="D135" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="D136" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="D137" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="D138" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="D139" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="D140" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="D141" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="D142" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="D143" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="D144" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="D145" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="D146" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="D147" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="D148" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="D149" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="D150" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="D151" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="D157" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="D158" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="D159" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="D160" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="D161" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="D162" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="D163" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="D164" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="D165" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="D166" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="D167" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="D168" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="D169" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="D170" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="D171" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="D173" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="D174" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D175" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="D176" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D177" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="D178" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D179" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D180" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D181" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="D182" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D183" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="D184" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D185" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="D186" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D187" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D188" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D189" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D190" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D191" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="D192" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D193" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="D194" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D195" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="D196" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D197" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="D198" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D199" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D200" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D201" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D202" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D203" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D204" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D205" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D207" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D208" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D209" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D210" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D211" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D212" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="D213" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D214" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="D215" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D216" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="D217" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D219" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="D221" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D222" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="D95" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="D96" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D97" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="D72" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D73" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D74" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D75" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D76" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D77" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D78" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D79" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D80" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D81" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D82" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D83" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D84" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D85" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D86" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D87" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D88" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D89" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D90" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D100" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D101" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D102" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D103" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D104" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="D105" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="D106" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="D107" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D108" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="D109" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="D110" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="D111" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="D112" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="D113" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="D114" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="D115" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="D116" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="D117" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="D118" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="D119" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="D120" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="D121" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="D122" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="D123" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="D124" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="D125" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="D126" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="D127" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="D128" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="D129" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="D130" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="D131" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="D132" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="D133" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="D134" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="D135" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="D136" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="D137" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="D138" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="D139" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="D140" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="D141" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="D142" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="D143" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="D144" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="D145" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="D146" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="D147" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="D148" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="D149" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="D150" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="D151" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="D157" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="D158" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="D159" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="D160" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="D161" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="D162" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="D163" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="D164" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="D165" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="D166" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="D167" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="D168" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="D169" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="D170" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="D171" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="D173" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="D174" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="D175" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="D176" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="D177" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="D178" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="D179" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="D180" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="D181" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="D182" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="D183" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="D184" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="D185" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="D186" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="D187" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="D188" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="D189" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="D190" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="D191" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="D192" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="D193" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="D194" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="D195" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="D196" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="D197" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="D198" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="D199" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D200" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D201" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D202" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D203" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D204" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D205" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D207" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D208" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D209" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D210" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D211" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D212" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="D213" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="D214" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="D215" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="D216" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="D217" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="D219" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="D221" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="D222" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="D94" r:id="rId206" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <headerFooter>
     <oddFooter>&amp;C000000&amp;P</oddFooter>
   </headerFooter>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/naoppy/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68593DFF-3687-0B40-8CB2-FA3602D7227B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EB5213-5622-C542-9493-07EB03DAC7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6540" yWindow="-20940" windowWidth="27920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="631">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -1930,6 +1930,13 @@
     <t>家屋倒壊等氾濫想定区域（氾濫流）</t>
     <rPh sb="12" eb="15">
       <t xml:space="preserve">ハンランリュウ </t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>全域</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ゼンイキ </t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -4879,66 +4886,53 @@
       <c r="Z62" s="3"/>
     </row>
     <row r="63" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A63" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-      <c r="Q63" s="3"/>
-      <c r="R63" s="3"/>
-      <c r="S63" s="3"/>
-      <c r="T63" s="3"/>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
-      <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
+      <c r="A63" s="44" t="s">
+        <v>619</v>
+      </c>
+      <c r="B63" s="44" t="s">
+        <v>629</v>
+      </c>
+      <c r="C63" s="44" t="s">
+        <v>630</v>
+      </c>
+      <c r="D63" s="46" t="s">
+        <v>624</v>
+      </c>
+      <c r="E63" s="45" t="s">
+        <v>621</v>
+      </c>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="45" t="s">
+        <v>621</v>
+      </c>
+      <c r="I63" s="43"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="43"/>
+      <c r="L63" s="43"/>
+      <c r="M63" s="43"/>
     </row>
     <row r="64" spans="1:26" ht="13.5" customHeight="1">
       <c r="A64" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>161</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="F64" s="5"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
+      <c r="H64" s="6" t="s">
+        <v>157</v>
+      </c>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
@@ -4966,10 +4960,10 @@
         <v>158</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>160</v>
@@ -5006,10 +5000,10 @@
         <v>158</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>160</v>
@@ -5046,10 +5040,10 @@
         <v>158</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>160</v>
@@ -5086,10 +5080,10 @@
         <v>158</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>160</v>
@@ -5126,10 +5120,10 @@
         <v>158</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>160</v>
@@ -5166,10 +5160,10 @@
         <v>158</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>160</v>
@@ -5206,10 +5200,10 @@
         <v>158</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>160</v>
@@ -5242,16 +5236,20 @@
       <c r="A72" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B72" s="5"/>
+      <c r="B72" s="6" t="s">
+        <v>158</v>
+      </c>
       <c r="C72" s="6" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="E72" s="5"/>
+        <v>168</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>160</v>
+      </c>
       <c r="F72" s="6" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -5278,23 +5276,19 @@
       <c r="A73" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B73" s="6" t="s">
-        <v>172</v>
-      </c>
+      <c r="B73" s="5"/>
       <c r="C73" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" s="5"/>
+        <v>171</v>
+      </c>
+      <c r="E73" s="5"/>
+      <c r="F73" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="G73" s="5"/>
-      <c r="H73" s="8" t="s">
-        <v>15</v>
-      </c>
+      <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
@@ -5322,10 +5316,10 @@
         <v>172</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>15</v>
@@ -5362,10 +5356,10 @@
         <v>172</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>15</v>
@@ -5402,10 +5396,10 @@
         <v>172</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>15</v>
@@ -5442,10 +5436,10 @@
         <v>172</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>15</v>
@@ -5482,24 +5476,24 @@
         <v>172</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
       <c r="H78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I78" s="16"/>
-      <c r="J78" s="16"/>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="17"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="6"/>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
@@ -5522,24 +5516,24 @@
         <v>172</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
       <c r="H79" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I79" s="5"/>
-      <c r="J79" s="5"/>
-      <c r="K79" s="5"/>
-      <c r="L79" s="5"/>
-      <c r="M79" s="6"/>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="16"/>
+      <c r="M79" s="17"/>
       <c r="N79" s="3"/>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
@@ -5562,10 +5556,10 @@
         <v>172</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>15</v>
@@ -5602,10 +5596,10 @@
         <v>172</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>15</v>
@@ -5642,10 +5636,10 @@
         <v>172</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>15</v>
@@ -5682,10 +5676,10 @@
         <v>172</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>15</v>
@@ -5722,10 +5716,10 @@
         <v>172</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>15</v>
@@ -5762,10 +5756,10 @@
         <v>172</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>15</v>
@@ -5802,10 +5796,10 @@
         <v>172</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>15</v>
@@ -5842,10 +5836,10 @@
         <v>172</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>15</v>
@@ -5882,10 +5876,10 @@
         <v>172</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>15</v>
@@ -5922,10 +5916,10 @@
         <v>172</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>15</v>
@@ -5962,24 +5956,24 @@
         <v>172</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F90" s="16"/>
-      <c r="G90" s="16"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
       <c r="H90" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I90" s="16"/>
-      <c r="J90" s="16"/>
-      <c r="K90" s="16"/>
-      <c r="L90" s="16"/>
-      <c r="M90" s="17"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="5"/>
+      <c r="M90" s="6"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
@@ -6002,24 +5996,24 @@
         <v>172</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="16"/>
       <c r="H91" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="5"/>
-      <c r="M91" s="6"/>
+      <c r="I91" s="16"/>
+      <c r="J91" s="16"/>
+      <c r="K91" s="16"/>
+      <c r="L91" s="16"/>
+      <c r="M91" s="17"/>
       <c r="N91" s="3"/>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
@@ -6042,24 +6036,24 @@
         <v>172</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F92" s="16"/>
-      <c r="G92" s="16"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
       <c r="H92" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
-      <c r="K92" s="16"/>
-      <c r="L92" s="16"/>
-      <c r="M92" s="17"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="6"/>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
@@ -6082,24 +6076,24 @@
         <v>172</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="16"/>
       <c r="H93" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
-      <c r="K93" s="5"/>
-      <c r="L93" s="5"/>
-      <c r="M93" s="6"/>
+      <c r="K93" s="16"/>
+      <c r="L93" s="16"/>
+      <c r="M93" s="17"/>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
@@ -6115,36 +6109,55 @@
       <c r="Z93" s="3"/>
     </row>
     <row r="94" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A94" s="43" t="s">
+      <c r="A94" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B94" s="44"/>
-      <c r="C94" s="44" t="s">
-        <v>628</v>
-      </c>
-      <c r="D94" s="46" t="s">
-        <v>623</v>
-      </c>
-      <c r="E94" s="43"/>
-      <c r="F94" s="43"/>
-      <c r="G94" s="43"/>
-      <c r="H94" s="43"/>
-      <c r="I94" s="43"/>
-      <c r="J94" s="43"/>
-      <c r="K94" s="43"/>
-      <c r="L94" s="43"/>
-      <c r="M94" s="43"/>
-    </row>
-    <row r="95" spans="1:26" ht="15" customHeight="1">
+      <c r="B94" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3"/>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3"/>
+      <c r="S94" s="3"/>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
+      <c r="Z94" s="3"/>
+    </row>
+    <row r="95" spans="1:26" ht="13.5" customHeight="1">
       <c r="A95" s="43" t="s">
         <v>16</v>
       </c>
       <c r="B95" s="44"/>
       <c r="C95" s="44" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D95" s="46" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E95" s="43"/>
       <c r="F95" s="43"/>
@@ -6156,25 +6169,21 @@
       <c r="L95" s="43"/>
       <c r="M95" s="43"/>
     </row>
-    <row r="96" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A96" s="44" t="s">
-        <v>619</v>
-      </c>
-      <c r="B96" s="43"/>
+    <row r="96" spans="1:26" ht="15" customHeight="1">
+      <c r="A96" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B96" s="44"/>
       <c r="C96" s="44" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D96" s="46" t="s">
-        <v>624</v>
-      </c>
-      <c r="E96" s="45" t="s">
-        <v>621</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="E96" s="43"/>
       <c r="F96" s="43"/>
       <c r="G96" s="43"/>
-      <c r="H96" s="45" t="s">
-        <v>621</v>
-      </c>
+      <c r="H96" s="43"/>
       <c r="I96" s="43"/>
       <c r="J96" s="43"/>
       <c r="K96" s="43"/>
@@ -17142,37 +17151,37 @@
     <hyperlink ref="D60" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
     <hyperlink ref="D61" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
     <hyperlink ref="D62" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="D63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D64" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="D65" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D66" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="D67" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D68" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="D69" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D70" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="D71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D95" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="D96" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D64" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="D65" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="D66" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D67" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="D68" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="D69" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="D70" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="D71" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="D72" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="D96" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="D63" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
     <hyperlink ref="D97" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D72" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D73" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D74" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D75" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D76" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D77" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D78" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D79" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D80" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D81" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D82" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D83" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D84" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D85" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D86" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D87" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D88" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D89" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D90" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D73" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D74" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D75" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D76" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D77" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D78" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D79" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D80" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D81" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D82" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D83" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D84" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D85" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D86" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D87" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D88" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D89" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D90" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D91" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
     <hyperlink ref="D100" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
     <hyperlink ref="D101" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
     <hyperlink ref="D102" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
@@ -17287,7 +17296,7 @@
     <hyperlink ref="D219" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
     <hyperlink ref="D221" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
     <hyperlink ref="D222" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="D94" r:id="rId206" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="D95" r:id="rId206" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/naoppy/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/naoppy/geolonia/yaizu-city/app/メニュー/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EB5213-5622-C542-9493-07EB03DAC7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC051919-2595-E84A-846E-9BE963E19EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="-20940" windowWidth="27920" windowHeight="20780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="メニュー構造" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="630">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -1928,16 +1928,6 @@
   </si>
   <si>
     <t>家屋倒壊等氾濫想定区域（氾濫流）</t>
-    <rPh sb="12" eb="15">
-      <t xml:space="preserve">ハンランリュウ </t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>全域</t>
-    <rPh sb="0" eb="1">
-      <t xml:space="preserve">ゼンイキ </t>
-    </rPh>
     <phoneticPr fontId="13"/>
   </si>
 </sst>
@@ -4886,53 +4876,66 @@
       <c r="Z62" s="3"/>
     </row>
     <row r="63" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A63" s="44" t="s">
-        <v>619</v>
-      </c>
-      <c r="B63" s="44" t="s">
-        <v>629</v>
-      </c>
-      <c r="C63" s="44" t="s">
-        <v>630</v>
-      </c>
-      <c r="D63" s="46" t="s">
-        <v>624</v>
-      </c>
-      <c r="E63" s="45" t="s">
-        <v>621</v>
-      </c>
-      <c r="F63" s="43"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="45" t="s">
-        <v>621</v>
-      </c>
-      <c r="I63" s="43"/>
-      <c r="J63" s="43"/>
-      <c r="K63" s="43"/>
-      <c r="L63" s="43"/>
-      <c r="M63" s="43"/>
+      <c r="A63" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63" s="3"/>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="3"/>
     </row>
     <row r="64" spans="1:26" ht="13.5" customHeight="1">
       <c r="A64" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F64" s="5"/>
+        <v>160</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>161</v>
+      </c>
       <c r="G64" s="5"/>
-      <c r="H64" s="6" t="s">
-        <v>157</v>
-      </c>
+      <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
@@ -4960,10 +4963,10 @@
         <v>158</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>160</v>
@@ -5000,10 +5003,10 @@
         <v>158</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>160</v>
@@ -5040,10 +5043,10 @@
         <v>158</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>160</v>
@@ -5080,10 +5083,10 @@
         <v>158</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>160</v>
@@ -5120,10 +5123,10 @@
         <v>158</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>160</v>
@@ -5160,10 +5163,10 @@
         <v>158</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>160</v>
@@ -5200,10 +5203,10 @@
         <v>158</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>160</v>
@@ -5236,20 +5239,16 @@
       <c r="A72" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B72" s="6" t="s">
-        <v>158</v>
-      </c>
+      <c r="B72" s="5"/>
       <c r="C72" s="6" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>160</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="E72" s="5"/>
       <c r="F72" s="6" t="s">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -5276,19 +5275,23 @@
       <c r="A73" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B73" s="5"/>
+      <c r="B73" s="6" t="s">
+        <v>172</v>
+      </c>
       <c r="C73" s="6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="E73" s="5"/>
-      <c r="F73" s="6" t="s">
-        <v>76</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="5"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
+      <c r="H73" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
@@ -5316,10 +5319,10 @@
         <v>172</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>15</v>
@@ -5356,10 +5359,10 @@
         <v>172</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>15</v>
@@ -5396,10 +5399,10 @@
         <v>172</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>15</v>
@@ -5436,10 +5439,10 @@
         <v>172</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>15</v>
@@ -5476,24 +5479,24 @@
         <v>172</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
       <c r="H78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I78" s="5"/>
-      <c r="J78" s="5"/>
-      <c r="K78" s="5"/>
-      <c r="L78" s="5"/>
-      <c r="M78" s="6"/>
+      <c r="I78" s="16"/>
+      <c r="J78" s="16"/>
+      <c r="K78" s="16"/>
+      <c r="L78" s="16"/>
+      <c r="M78" s="17"/>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
@@ -5516,24 +5519,24 @@
         <v>172</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
       <c r="H79" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I79" s="16"/>
-      <c r="J79" s="16"/>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="17"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="6"/>
       <c r="N79" s="3"/>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
@@ -5556,10 +5559,10 @@
         <v>172</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>15</v>
@@ -5596,10 +5599,10 @@
         <v>172</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>15</v>
@@ -5636,10 +5639,10 @@
         <v>172</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>15</v>
@@ -5676,10 +5679,10 @@
         <v>172</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>15</v>
@@ -5716,10 +5719,10 @@
         <v>172</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>15</v>
@@ -5756,10 +5759,10 @@
         <v>172</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>15</v>
@@ -5796,10 +5799,10 @@
         <v>172</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>15</v>
@@ -5836,10 +5839,10 @@
         <v>172</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>15</v>
@@ -5876,10 +5879,10 @@
         <v>172</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>15</v>
@@ -5916,10 +5919,10 @@
         <v>172</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>15</v>
@@ -5956,24 +5959,24 @@
         <v>172</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
+      <c r="F90" s="16"/>
+      <c r="G90" s="16"/>
       <c r="H90" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I90" s="5"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="5"/>
-      <c r="M90" s="6"/>
+      <c r="I90" s="16"/>
+      <c r="J90" s="16"/>
+      <c r="K90" s="16"/>
+      <c r="L90" s="16"/>
+      <c r="M90" s="17"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
@@ -5996,24 +5999,24 @@
         <v>172</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F91" s="16"/>
-      <c r="G91" s="16"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
       <c r="H91" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I91" s="16"/>
-      <c r="J91" s="16"/>
-      <c r="K91" s="16"/>
-      <c r="L91" s="16"/>
-      <c r="M91" s="17"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="6"/>
       <c r="N91" s="3"/>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
@@ -6036,24 +6039,24 @@
         <v>172</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="16"/>
       <c r="H92" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="5"/>
-      <c r="M92" s="6"/>
+      <c r="K92" s="16"/>
+      <c r="L92" s="16"/>
+      <c r="M92" s="17"/>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
@@ -6076,24 +6079,24 @@
         <v>172</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F93" s="16"/>
-      <c r="G93" s="16"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
       <c r="H93" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
-      <c r="K93" s="16"/>
-      <c r="L93" s="16"/>
-      <c r="M93" s="17"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="6"/>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
@@ -6109,55 +6112,36 @@
       <c r="Z93" s="3"/>
     </row>
     <row r="94" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B94" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
-      <c r="H94" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" s="5"/>
-      <c r="J94" s="5"/>
-      <c r="K94" s="5"/>
-      <c r="L94" s="5"/>
-      <c r="M94" s="6"/>
-      <c r="N94" s="3"/>
-      <c r="O94" s="3"/>
-      <c r="P94" s="3"/>
-      <c r="Q94" s="3"/>
-      <c r="R94" s="3"/>
-      <c r="S94" s="3"/>
-      <c r="T94" s="3"/>
-      <c r="U94" s="3"/>
-      <c r="V94" s="3"/>
-      <c r="W94" s="3"/>
-      <c r="X94" s="3"/>
-      <c r="Y94" s="3"/>
-      <c r="Z94" s="3"/>
-    </row>
-    <row r="95" spans="1:26" ht="13.5" customHeight="1">
+      <c r="B94" s="44"/>
+      <c r="C94" s="44" t="s">
+        <v>628</v>
+      </c>
+      <c r="D94" s="46" t="s">
+        <v>623</v>
+      </c>
+      <c r="E94" s="43"/>
+      <c r="F94" s="43"/>
+      <c r="G94" s="43"/>
+      <c r="H94" s="43"/>
+      <c r="I94" s="43"/>
+      <c r="J94" s="43"/>
+      <c r="K94" s="43"/>
+      <c r="L94" s="43"/>
+      <c r="M94" s="43"/>
+    </row>
+    <row r="95" spans="1:26" ht="15" customHeight="1">
       <c r="A95" s="43" t="s">
         <v>16</v>
       </c>
       <c r="B95" s="44"/>
       <c r="C95" s="44" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D95" s="46" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E95" s="43"/>
       <c r="F95" s="43"/>
@@ -6169,21 +6153,25 @@
       <c r="L95" s="43"/>
       <c r="M95" s="43"/>
     </row>
-    <row r="96" spans="1:26" ht="15" customHeight="1">
-      <c r="A96" s="43" t="s">
-        <v>16</v>
+    <row r="96" spans="1:26" ht="13.5" customHeight="1">
+      <c r="A96" s="44" t="s">
+        <v>619</v>
       </c>
       <c r="B96" s="44"/>
       <c r="C96" s="44" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D96" s="46" t="s">
-        <v>622</v>
-      </c>
-      <c r="E96" s="43"/>
+        <v>624</v>
+      </c>
+      <c r="E96" s="45" t="s">
+        <v>621</v>
+      </c>
       <c r="F96" s="43"/>
       <c r="G96" s="43"/>
-      <c r="H96" s="43"/>
+      <c r="H96" s="45" t="s">
+        <v>621</v>
+      </c>
       <c r="I96" s="43"/>
       <c r="J96" s="43"/>
       <c r="K96" s="43"/>
@@ -17151,152 +17139,152 @@
     <hyperlink ref="D60" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
     <hyperlink ref="D61" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
     <hyperlink ref="D62" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="D64" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D65" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="D66" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D67" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="D68" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D69" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="D70" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D71" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="D72" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D96" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="D63" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="D97" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D73" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D74" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D75" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D76" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D77" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D78" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D79" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D80" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D81" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D82" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D83" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D84" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D85" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D86" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D87" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D88" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D89" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D90" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D91" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D100" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D101" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D102" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D103" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D104" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D105" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="D106" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D107" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D108" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D109" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="D110" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="D111" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="D112" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="D113" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="D114" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="D115" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="D116" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="D117" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="D118" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D119" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="D120" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="D121" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="D122" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D123" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="D124" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="D125" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="D126" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="D127" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="D128" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D129" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="D130" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="D131" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="D132" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="D133" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="D134" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="D135" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="D136" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="D137" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="D138" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="D139" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="D140" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="D141" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="D142" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="D143" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="D144" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="D145" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="D146" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="D147" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="D148" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="D149" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="D150" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="D151" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="D157" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="D158" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="D159" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="D160" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="D161" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="D162" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="D163" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="D164" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="D165" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="D166" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="D167" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="D168" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="D169" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="D170" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="D171" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="D173" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="D174" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D175" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="D176" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D177" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="D178" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D179" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D180" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D181" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="D182" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D183" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="D184" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D185" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="D186" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D187" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D188" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D189" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D190" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D191" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="D192" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D193" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="D194" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D195" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="D196" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D197" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="D198" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D199" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D200" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D201" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D202" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D203" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D204" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D205" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D207" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D208" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D209" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D210" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D211" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D212" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="D213" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D214" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="D215" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D216" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="D217" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D219" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="D221" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D222" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="D95" r:id="rId206" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="D63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="D64" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="D65" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D66" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="D67" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="D68" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="D69" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="D70" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="D71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="D96" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D97" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="D72" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D73" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D74" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D75" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D76" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D77" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D78" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D79" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D80" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D81" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D82" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D83" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D84" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D85" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D86" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D87" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D88" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D89" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D90" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D100" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D101" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D102" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D103" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D104" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="D105" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="D106" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="D107" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D108" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="D109" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="D110" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="D111" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="D112" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="D113" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="D114" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="D115" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="D116" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="D117" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="D118" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="D119" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="D120" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="D121" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="D122" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="D123" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="D124" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="D125" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="D126" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="D127" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="D128" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="D129" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="D130" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="D131" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="D132" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="D133" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="D134" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="D135" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="D136" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="D137" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="D138" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="D139" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="D140" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="D141" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="D142" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="D143" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="D144" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="D145" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="D146" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="D147" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="D148" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="D149" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="D150" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="D151" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="D157" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="D158" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="D159" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="D160" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="D161" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="D162" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="D163" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="D164" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="D165" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="D166" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="D167" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="D168" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="D169" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="D170" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="D171" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="D173" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="D174" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="D175" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="D176" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="D177" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="D178" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="D179" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="D180" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="D181" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="D182" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="D183" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="D184" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="D185" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="D186" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="D187" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="D188" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="D189" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="D190" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="D191" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="D192" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="D193" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="D194" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="D195" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="D196" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="D197" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="D198" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="D199" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D200" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D201" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D202" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D203" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D204" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D205" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D207" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D208" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D209" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D210" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D211" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D212" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="D213" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="D214" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="D215" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="D216" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="D217" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="D219" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="D221" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="D222" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="D94" r:id="rId205" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="D95" r:id="rId206" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/naoppy/geolonia/yaizu-city/app/メニュー/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC051919-2595-E84A-846E-9BE963E19EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C6F2E8-AA50-3C4C-BF12-5711D10C4F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="630">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -1927,7 +1927,10 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>家屋倒壊等氾濫想定区域（氾濫流）</t>
+    <t>全域</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ゼンイキ </t>
+    </rPh>
     <phoneticPr fontId="13"/>
   </si>
 </sst>
@@ -4876,66 +4879,53 @@
       <c r="Z62" s="3"/>
     </row>
     <row r="63" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A63" s="8" t="s">
-        <v>16</v>
+      <c r="A63" s="44" t="s">
+        <v>619</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-      <c r="Q63" s="3"/>
-      <c r="R63" s="3"/>
-      <c r="S63" s="3"/>
-      <c r="T63" s="3"/>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
-      <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
+      <c r="C63" s="44" t="s">
+        <v>629</v>
+      </c>
+      <c r="D63" s="46" t="s">
+        <v>624</v>
+      </c>
+      <c r="E63" s="45" t="s">
+        <v>621</v>
+      </c>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="45" t="s">
+        <v>621</v>
+      </c>
+      <c r="I63" s="43"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="43"/>
+      <c r="L63" s="43"/>
+      <c r="M63" s="43"/>
     </row>
     <row r="64" spans="1:26" ht="13.5" customHeight="1">
       <c r="A64" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>105</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>161</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="F64" s="5"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
+      <c r="H64" s="6" t="s">
+        <v>157</v>
+      </c>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
@@ -4963,10 +4953,10 @@
         <v>158</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>160</v>
@@ -5003,10 +4993,10 @@
         <v>158</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>160</v>
@@ -5043,10 +5033,10 @@
         <v>158</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>160</v>
@@ -5083,10 +5073,10 @@
         <v>158</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>160</v>
@@ -5123,10 +5113,10 @@
         <v>158</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>160</v>
@@ -5163,10 +5153,10 @@
         <v>158</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>160</v>
@@ -5203,10 +5193,10 @@
         <v>158</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>160</v>
@@ -5239,16 +5229,20 @@
       <c r="A72" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B72" s="5"/>
+      <c r="B72" s="6" t="s">
+        <v>158</v>
+      </c>
       <c r="C72" s="6" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="E72" s="5"/>
+        <v>168</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>160</v>
+      </c>
       <c r="F72" s="6" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -5275,23 +5269,19 @@
       <c r="A73" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B73" s="6" t="s">
-        <v>172</v>
-      </c>
+      <c r="B73" s="5"/>
       <c r="C73" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" s="5"/>
+        <v>171</v>
+      </c>
+      <c r="E73" s="5"/>
+      <c r="F73" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="G73" s="5"/>
-      <c r="H73" s="8" t="s">
-        <v>15</v>
-      </c>
+      <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
@@ -5319,10 +5309,10 @@
         <v>172</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>15</v>
@@ -5359,10 +5349,10 @@
         <v>172</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>15</v>
@@ -5399,10 +5389,10 @@
         <v>172</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>15</v>
@@ -5439,10 +5429,10 @@
         <v>172</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>15</v>
@@ -5479,24 +5469,24 @@
         <v>172</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
       <c r="H78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I78" s="16"/>
-      <c r="J78" s="16"/>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="17"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="6"/>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
@@ -5519,24 +5509,24 @@
         <v>172</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
       <c r="H79" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I79" s="5"/>
-      <c r="J79" s="5"/>
-      <c r="K79" s="5"/>
-      <c r="L79" s="5"/>
-      <c r="M79" s="6"/>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="16"/>
+      <c r="M79" s="17"/>
       <c r="N79" s="3"/>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
@@ -5559,10 +5549,10 @@
         <v>172</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>15</v>
@@ -5599,10 +5589,10 @@
         <v>172</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>15</v>
@@ -5639,10 +5629,10 @@
         <v>172</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>15</v>
@@ -5679,10 +5669,10 @@
         <v>172</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>15</v>
@@ -5719,10 +5709,10 @@
         <v>172</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>15</v>
@@ -5759,10 +5749,10 @@
         <v>172</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>15</v>
@@ -5799,10 +5789,10 @@
         <v>172</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>15</v>
@@ -5839,10 +5829,10 @@
         <v>172</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>15</v>
@@ -5879,10 +5869,10 @@
         <v>172</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>15</v>
@@ -5919,10 +5909,10 @@
         <v>172</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>15</v>
@@ -5959,24 +5949,24 @@
         <v>172</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F90" s="16"/>
-      <c r="G90" s="16"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
       <c r="H90" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I90" s="16"/>
-      <c r="J90" s="16"/>
-      <c r="K90" s="16"/>
-      <c r="L90" s="16"/>
-      <c r="M90" s="17"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="5"/>
+      <c r="M90" s="6"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
@@ -5999,24 +5989,24 @@
         <v>172</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="16"/>
       <c r="H91" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="5"/>
-      <c r="M91" s="6"/>
+      <c r="I91" s="16"/>
+      <c r="J91" s="16"/>
+      <c r="K91" s="16"/>
+      <c r="L91" s="16"/>
+      <c r="M91" s="17"/>
       <c r="N91" s="3"/>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
@@ -6039,24 +6029,24 @@
         <v>172</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F92" s="16"/>
-      <c r="G92" s="16"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
       <c r="H92" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
-      <c r="K92" s="16"/>
-      <c r="L92" s="16"/>
-      <c r="M92" s="17"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="6"/>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
@@ -6079,24 +6069,24 @@
         <v>172</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="16"/>
       <c r="H93" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
-      <c r="K93" s="5"/>
-      <c r="L93" s="5"/>
-      <c r="M93" s="6"/>
+      <c r="K93" s="16"/>
+      <c r="L93" s="16"/>
+      <c r="M93" s="17"/>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
@@ -6112,36 +6102,55 @@
       <c r="Z93" s="3"/>
     </row>
     <row r="94" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A94" s="43" t="s">
+      <c r="A94" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B94" s="44"/>
-      <c r="C94" s="44" t="s">
-        <v>628</v>
-      </c>
-      <c r="D94" s="46" t="s">
-        <v>623</v>
-      </c>
-      <c r="E94" s="43"/>
-      <c r="F94" s="43"/>
-      <c r="G94" s="43"/>
-      <c r="H94" s="43"/>
-      <c r="I94" s="43"/>
-      <c r="J94" s="43"/>
-      <c r="K94" s="43"/>
-      <c r="L94" s="43"/>
-      <c r="M94" s="43"/>
-    </row>
-    <row r="95" spans="1:26" ht="15" customHeight="1">
+      <c r="B94" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3"/>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3"/>
+      <c r="S94" s="3"/>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
+      <c r="Z94" s="3"/>
+    </row>
+    <row r="95" spans="1:26" ht="13.5" customHeight="1">
       <c r="A95" s="43" t="s">
         <v>16</v>
       </c>
       <c r="B95" s="44"/>
       <c r="C95" s="44" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D95" s="46" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E95" s="43"/>
       <c r="F95" s="43"/>
@@ -6153,25 +6162,21 @@
       <c r="L95" s="43"/>
       <c r="M95" s="43"/>
     </row>
-    <row r="96" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A96" s="44" t="s">
-        <v>619</v>
+    <row r="96" spans="1:26" ht="15" customHeight="1">
+      <c r="A96" s="43" t="s">
+        <v>16</v>
       </c>
       <c r="B96" s="44"/>
       <c r="C96" s="44" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D96" s="46" t="s">
-        <v>624</v>
-      </c>
-      <c r="E96" s="45" t="s">
-        <v>621</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="E96" s="43"/>
       <c r="F96" s="43"/>
       <c r="G96" s="43"/>
-      <c r="H96" s="45" t="s">
-        <v>621</v>
-      </c>
+      <c r="H96" s="43"/>
       <c r="I96" s="43"/>
       <c r="J96" s="43"/>
       <c r="K96" s="43"/>
@@ -17139,36 +17144,36 @@
     <hyperlink ref="D60" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
     <hyperlink ref="D61" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
     <hyperlink ref="D62" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="D63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D64" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="D65" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D66" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="D67" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D68" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="D69" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D70" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="D71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D96" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D64" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="D65" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="D66" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D67" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="D68" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="D69" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="D70" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="D71" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="D72" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="D63" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
     <hyperlink ref="D97" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D72" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D73" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D74" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D75" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D76" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D77" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D78" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D79" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D80" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D81" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D82" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D83" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D84" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D85" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D86" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D87" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D88" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D89" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D90" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
     <hyperlink ref="D100" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
     <hyperlink ref="D101" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
     <hyperlink ref="D102" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
@@ -17283,8 +17288,8 @@
     <hyperlink ref="D219" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
     <hyperlink ref="D221" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
     <hyperlink ref="D222" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="D94" r:id="rId205" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D95" r:id="rId206" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="D95" r:id="rId205" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="D96" r:id="rId206" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\vm22flo01\DownloadFiles\DX推進課\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFECE15-F4D3-46B5-9182-8C125FE15E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C833C6B1-82E7-43B3-8F39-7C8609AD59DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="632">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -3213,9 +3213,6 @@
     </r>
   </si>
   <si>
-    <t>#0179c4</t>
-  </si>
-  <si>
     <t>子育て</t>
   </si>
   <si>
@@ -3234,9 +3231,6 @@
     </r>
   </si>
   <si>
-    <t>#ef8307</t>
-  </si>
-  <si>
     <t>子育て支援施設</t>
   </si>
   <si>
@@ -3250,9 +3244,6 @@
       </rPr>
       <t>https://yaizu-smartcity.jp/tiles/%E5%AD%90%E8%82%B2%E3%81%A6%E6%94%AF%E6%8F%B4%E6%96%BD%E8%A8%AD/tiles.json</t>
     </r>
-  </si>
-  <si>
-    <t>#be68c9</t>
   </si>
   <si>
     <t>あかちゃんえき</t>
@@ -3802,6 +3793,69 @@
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/%E5%B0%8F%E6%B3%89%E5%85%AB%E9%9B%B2%E3%83%9E%E3%83%83%E3%83%97_%E6%B5%9C%E9%80%9A%E3%82%8A/tiles.json</t>
+  </si>
+  <si>
+    <t>【生活応援商品券】使えるお店</t>
+    <rPh sb="1" eb="8">
+      <t>セイカツオウエンショウヒンケン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ミセ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>小売り店</t>
+    <rPh sb="0" eb="2">
+      <t>コウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>飲食店</t>
+    <rPh sb="0" eb="2">
+      <t>インショク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%94%9F%E6%B4%BB%E5%BF%9C%E6%8F%B4%E5%95%86%E5%93%81%E5%88%B8_%E9%A3%B2%E9%A3%9F/tiles.json</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%94%9F%E6%B4%BB%E5%BF%9C%E6%8F%B4%E5%95%86%E5%93%81%E5%88%B8_%E5%B0%8F%E5%A3%B2%E3%82%8A/tiles.json</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%94%9F%E6%B4%BB%E5%BF%9C%E6%8F%B4%E5%95%86%E5%93%81%E5%88%B8_%E3%81%9D%E3%81%AE%E4%BB%96/tiles.json</t>
+  </si>
+  <si>
+    <t>cart</t>
+  </si>
+  <si>
+    <t>bench</t>
+  </si>
+  <si>
+    <t>preshool_blue</t>
+  </si>
+  <si>
+    <t>public-facility-small-green</t>
+  </si>
+  <si>
+    <t>preshool_green</t>
+  </si>
+  <si>
+    <t>recycle-center</t>
+  </si>
+  <si>
+    <t>marker-orange</t>
   </si>
 </sst>
 </file>
@@ -4405,7 +4459,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z1009"/>
+  <dimension ref="A1:Z1012"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.88671875" customWidth="1"/>
@@ -4433,10 +4487,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -4667,16 +4721,16 @@
         <v>15</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="5"/>
@@ -7967,18 +8021,20 @@
       <c r="A94" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="5"/>
-      <c r="C94" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="E94" s="4"/>
-      <c r="F94" s="16"/>
-      <c r="G94" s="16"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="6" t="s">
+      <c r="B94" s="26" t="s">
+        <v>619</v>
+      </c>
+      <c r="C94" s="26" t="s">
+        <v>621</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>622</v>
+      </c>
+      <c r="E94" s="8"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="5" t="s">
         <v>212</v>
       </c>
       <c r="J94" s="5"/>
@@ -8003,21 +8059,21 @@
       <c r="A95" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B95" s="33" t="s">
-        <v>613</v>
+      <c r="B95" s="26" t="s">
+        <v>619</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>602</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="E95" s="4"/>
-      <c r="F95" s="16"/>
-      <c r="G95" s="16"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="6" t="s">
-        <v>607</v>
+        <v>620</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>623</v>
+      </c>
+      <c r="E95" s="8"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="5" t="s">
+        <v>625</v>
       </c>
       <c r="J95" s="5"/>
       <c r="K95" s="5"/>
@@ -8041,21 +8097,21 @@
       <c r="A96" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B96" s="33" t="s">
-        <v>613</v>
+      <c r="B96" s="26" t="s">
+        <v>619</v>
       </c>
       <c r="C96" s="26" t="s">
-        <v>606</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="E96" s="4"/>
-      <c r="F96" s="16"/>
-      <c r="G96" s="16"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="6" t="s">
-        <v>607</v>
+        <v>586</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>624</v>
+      </c>
+      <c r="E96" s="8"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="5" t="s">
+        <v>631</v>
       </c>
       <c r="J96" s="5"/>
       <c r="K96" s="5"/>
@@ -8079,21 +8135,19 @@
       <c r="A97" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B97" s="33" t="s">
-        <v>613</v>
-      </c>
-      <c r="C97" s="26" t="s">
-        <v>605</v>
+      <c r="B97" s="5"/>
+      <c r="C97" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>609</v>
+        <v>211</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
       <c r="H97" s="4"/>
       <c r="I97" s="6" t="s">
-        <v>607</v>
+        <v>212</v>
       </c>
       <c r="J97" s="5"/>
       <c r="K97" s="5"/>
@@ -8118,20 +8172,20 @@
         <v>209</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C98" s="26" t="s">
-        <v>603</v>
-      </c>
-      <c r="D98" s="40" t="s">
-        <v>614</v>
+        <v>599</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>608</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
       <c r="H98" s="4"/>
       <c r="I98" s="6" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="J98" s="5"/>
       <c r="K98" s="5"/>
@@ -8156,20 +8210,20 @@
         <v>209</v>
       </c>
       <c r="B99" s="33" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
       <c r="H99" s="4"/>
       <c r="I99" s="6" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="J99" s="5"/>
       <c r="K99" s="5"/>
@@ -8193,21 +8247,21 @@
       <c r="A100" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B100" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>214</v>
+      <c r="B100" s="33" t="s">
+        <v>610</v>
+      </c>
+      <c r="C100" s="26" t="s">
+        <v>602</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>215</v>
+        <v>606</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="16"/>
       <c r="G100" s="16"/>
       <c r="H100" s="4"/>
       <c r="I100" s="6" t="s">
-        <v>216</v>
+        <v>604</v>
       </c>
       <c r="J100" s="5"/>
       <c r="K100" s="5"/>
@@ -8231,21 +8285,21 @@
       <c r="A101" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B101" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>218</v>
+      <c r="B101" s="33" t="s">
+        <v>610</v>
+      </c>
+      <c r="C101" s="26" t="s">
+        <v>600</v>
+      </c>
+      <c r="D101" s="40" t="s">
+        <v>611</v>
       </c>
       <c r="E101" s="4"/>
-      <c r="F101" s="5"/>
+      <c r="F101" s="16"/>
       <c r="G101" s="16"/>
       <c r="H101" s="4"/>
       <c r="I101" s="6" t="s">
-        <v>219</v>
+        <v>604</v>
       </c>
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
@@ -8269,19 +8323,21 @@
       <c r="A102" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B102" s="4"/>
-      <c r="C102" s="8" t="s">
-        <v>220</v>
+      <c r="B102" s="33" t="s">
+        <v>610</v>
+      </c>
+      <c r="C102" s="26" t="s">
+        <v>601</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>221</v>
+        <v>607</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="16"/>
       <c r="G102" s="16"/>
       <c r="H102" s="4"/>
       <c r="I102" s="6" t="s">
-        <v>222</v>
+        <v>604</v>
       </c>
       <c r="J102" s="5"/>
       <c r="K102" s="5"/>
@@ -8305,19 +8361,21 @@
       <c r="A103" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B103" s="4"/>
+      <c r="B103" s="6" t="s">
+        <v>213</v>
+      </c>
       <c r="C103" s="8" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="16"/>
       <c r="G103" s="16"/>
       <c r="H103" s="4"/>
       <c r="I103" s="6" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="J103" s="5"/>
       <c r="K103" s="5"/>
@@ -8341,19 +8399,21 @@
       <c r="A104" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B104" s="4"/>
+      <c r="B104" s="6" t="s">
+        <v>213</v>
+      </c>
       <c r="C104" s="8" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E104" s="4"/>
-      <c r="F104" s="16"/>
+      <c r="F104" s="5"/>
       <c r="G104" s="16"/>
       <c r="H104" s="4"/>
       <c r="I104" s="6" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
@@ -8377,21 +8437,19 @@
       <c r="A105" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B105" s="6" t="s">
-        <v>229</v>
-      </c>
+      <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="16"/>
       <c r="G105" s="16"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="8" t="s">
-        <v>232</v>
+      <c r="I105" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
@@ -8411,26 +8469,24 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" spans="1:26" ht="15" customHeight="1">
+    <row r="106" spans="1:26" ht="13.5" customHeight="1">
       <c r="A106" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B106" s="6" t="s">
-        <v>229</v>
-      </c>
+      <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E106" s="4"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="I106" s="5"/>
+      <c r="F106" s="16"/>
+      <c r="G106" s="16"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="6" t="s">
+        <v>225</v>
+      </c>
       <c r="J106" s="5"/>
       <c r="K106" s="5"/>
       <c r="L106" s="5"/>
@@ -8453,19 +8509,19 @@
       <c r="A107" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B107" s="5"/>
+      <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="16"/>
       <c r="G107" s="16"/>
       <c r="H107" s="4"/>
       <c r="I107" s="6" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="J107" s="5"/>
       <c r="K107" s="5"/>
@@ -8489,20 +8545,22 @@
       <c r="A108" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B108" s="5"/>
+      <c r="B108" s="6" t="s">
+        <v>229</v>
+      </c>
       <c r="C108" s="8" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E108" s="4"/>
-      <c r="F108" s="5"/>
-      <c r="G108" s="5"/>
-      <c r="H108" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I108" s="5"/>
+      <c r="F108" s="16"/>
+      <c r="G108" s="16"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="8" t="s">
+        <v>232</v>
+      </c>
       <c r="J108" s="5"/>
       <c r="K108" s="5"/>
       <c r="L108" s="5"/>
@@ -8521,25 +8579,25 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" spans="1:26" ht="12.75" customHeight="1">
+    <row r="109" spans="1:26" ht="15" customHeight="1">
       <c r="A109" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B109" s="8" t="s">
-        <v>242</v>
+      <c r="B109" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D109" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="E109" s="5"/>
-      <c r="F109" s="6" t="s">
-        <v>245</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E109" s="4"/>
+      <c r="F109" s="5"/>
       <c r="G109" s="5"/>
-      <c r="H109" s="5"/>
+      <c r="H109" s="8" t="s">
+        <v>235</v>
+      </c>
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
@@ -8559,26 +8617,24 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" spans="1:26" ht="12.75" customHeight="1">
+    <row r="110" spans="1:26" ht="13.5" customHeight="1">
       <c r="A110" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B110" s="8" t="s">
-        <v>242</v>
-      </c>
+      <c r="B110" s="5"/>
       <c r="C110" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="D110" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="E110" s="5"/>
-      <c r="F110" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="G110" s="5"/>
-      <c r="H110" s="5"/>
-      <c r="I110" s="5"/>
+        <v>236</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E110" s="4"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="16"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="6" t="s">
+        <v>238</v>
+      </c>
       <c r="J110" s="5"/>
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
@@ -8597,25 +8653,23 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" spans="1:26" ht="12.75" customHeight="1">
+    <row r="111" spans="1:26" ht="13.5" customHeight="1">
       <c r="A111" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B111" s="8" t="s">
-        <v>242</v>
-      </c>
+      <c r="B111" s="5"/>
       <c r="C111" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="E111" s="5"/>
-      <c r="F111" s="6" t="s">
-        <v>251</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E111" s="4"/>
+      <c r="F111" s="5"/>
       <c r="G111" s="5"/>
-      <c r="H111" s="5"/>
+      <c r="H111" s="4" t="s">
+        <v>241</v>
+      </c>
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
       <c r="K111" s="5"/>
@@ -8643,14 +8697,14 @@
         <v>242</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E112" s="5"/>
       <c r="F112" s="6" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
@@ -8681,14 +8735,14 @@
         <v>242</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E113" s="5"/>
       <c r="F113" s="6" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
@@ -8719,14 +8773,14 @@
         <v>242</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="E114" s="5"/>
       <c r="F114" s="6" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -8757,14 +8811,14 @@
         <v>242</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="E115" s="5"/>
       <c r="F115" s="6" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
@@ -8787,7 +8841,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:26" ht="13.5" customHeight="1">
+    <row r="116" spans="1:26" ht="12.75" customHeight="1">
       <c r="A116" s="8" t="s">
         <v>209</v>
       </c>
@@ -8795,19 +8849,19 @@
         <v>242</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
+      <c r="F116" s="6" t="s">
+        <v>257</v>
+      </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
-      <c r="I116" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="J116" s="16"/>
+      <c r="I116" s="5"/>
+      <c r="J116" s="5"/>
       <c r="K116" s="5"/>
       <c r="L116" s="5"/>
       <c r="M116" s="6"/>
@@ -8825,7 +8879,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" spans="1:26" ht="13.5" customHeight="1">
+    <row r="117" spans="1:26" ht="12.75" customHeight="1">
       <c r="A117" s="8" t="s">
         <v>209</v>
       </c>
@@ -8833,19 +8887,19 @@
         <v>242</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>268</v>
+        <v>258</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>259</v>
       </c>
       <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
+      <c r="F117" s="6" t="s">
+        <v>260</v>
+      </c>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
-      <c r="I117" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="J117" s="16"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="5"/>
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="6"/>
@@ -8863,27 +8917,25 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" spans="1:26" ht="13.5" customHeight="1">
+    <row r="118" spans="1:26" ht="12.75" customHeight="1">
       <c r="A118" s="8" t="s">
         <v>209</v>
       </c>
       <c r="B118" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>271</v>
+      <c r="C118" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>262</v>
       </c>
       <c r="E118" s="5"/>
-      <c r="F118" s="17" t="s">
-        <v>272</v>
+      <c r="F118" s="6" t="s">
+        <v>263</v>
       </c>
       <c r="G118" s="5"/>
-      <c r="H118" s="17" t="s">
-        <v>273</v>
-      </c>
+      <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="5"/>
@@ -8904,22 +8956,26 @@
       <c r="Z118" s="3"/>
     </row>
     <row r="119" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A119" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B119" s="5"/>
-      <c r="C119" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>276</v>
+      <c r="A119" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>265</v>
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
-      <c r="I119" s="5"/>
-      <c r="J119" s="5"/>
+      <c r="I119" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="J119" s="16"/>
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="6"/>
@@ -8939,25 +8995,25 @@
     </row>
     <row r="120" spans="1:26" ht="13.5" customHeight="1">
       <c r="A120" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>278</v>
+        <v>209</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>267</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>280</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="E120" s="5"/>
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
-      <c r="H120" s="4"/>
-      <c r="I120" s="5"/>
-      <c r="J120" s="5"/>
+      <c r="H120" s="5"/>
+      <c r="I120" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J120" s="16"/>
       <c r="K120" s="5"/>
       <c r="L120" s="5"/>
       <c r="M120" s="6"/>
@@ -8977,23 +9033,25 @@
     </row>
     <row r="121" spans="1:26" ht="13.5" customHeight="1">
       <c r="A121" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>277</v>
+        <v>209</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>242</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="F121" s="5"/>
+        <v>271</v>
+      </c>
+      <c r="E121" s="5"/>
+      <c r="F121" s="17" t="s">
+        <v>272</v>
+      </c>
       <c r="G121" s="5"/>
-      <c r="H121" s="4"/>
+      <c r="H121" s="17" t="s">
+        <v>273</v>
+      </c>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
       <c r="K121" s="5"/>
@@ -9014,24 +9072,20 @@
       <c r="Z121" s="3"/>
     </row>
     <row r="122" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A122" s="8" t="s">
+      <c r="A122" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B122" s="6" t="s">
-        <v>277</v>
-      </c>
+      <c r="B122" s="5"/>
       <c r="C122" s="6" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>286</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E122" s="5"/>
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
-      <c r="H122" s="4"/>
+      <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
       <c r="K122" s="5"/>
@@ -9059,13 +9113,13 @@
         <v>277</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
@@ -9097,17 +9151,17 @@
         <v>277</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="E124" s="6" t="s">
-        <v>292</v>
+        <v>282</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>283</v>
       </c>
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
-      <c r="H124" s="5"/>
+      <c r="H124" s="4"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
       <c r="K124" s="5"/>
@@ -9135,13 +9189,13 @@
         <v>277</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="D125" s="13" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
@@ -9173,13 +9227,13 @@
         <v>277</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
@@ -9211,17 +9265,17 @@
         <v>277</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D127" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>301</v>
+        <v>291</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
-      <c r="H127" s="4"/>
+      <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="5"/>
@@ -9249,17 +9303,17 @@
         <v>277</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>304</v>
+        <v>294</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>295</v>
       </c>
       <c r="F128" s="5"/>
       <c r="G128" s="5"/>
-      <c r="H128" s="5"/>
+      <c r="H128" s="4"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="5"/>
@@ -9287,17 +9341,17 @@
         <v>277</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="E129" s="6" t="s">
-        <v>304</v>
+        <v>297</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>298</v>
       </c>
       <c r="F129" s="5"/>
       <c r="G129" s="5"/>
-      <c r="H129" s="5"/>
+      <c r="H129" s="4"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="5"/>
@@ -9325,17 +9379,17 @@
         <v>277</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>309</v>
+        <v>300</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>301</v>
       </c>
       <c r="F130" s="5"/>
       <c r="G130" s="5"/>
-      <c r="H130" s="5"/>
+      <c r="H130" s="4"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5"/>
@@ -9363,13 +9417,13 @@
         <v>277</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
@@ -9398,20 +9452,18 @@
         <v>274</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>316</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="F132" s="5"/>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
@@ -9438,20 +9490,18 @@
         <v>274</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>316</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="F133" s="5"/>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
@@ -9478,20 +9528,18 @@
         <v>274</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>316</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="F134" s="5"/>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
@@ -9521,13 +9569,13 @@
         <v>312</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D135" s="13" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>316</v>
@@ -9561,13 +9609,13 @@
         <v>312</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>316</v>
@@ -9601,13 +9649,13 @@
         <v>312</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>316</v>
@@ -9641,16 +9689,16 @@
         <v>312</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
@@ -9681,19 +9729,19 @@
         <v>312</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="E139" s="8" t="s">
-        <v>338</v>
+        <v>327</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>328</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="G139" s="5"/>
-      <c r="H139" s="4"/>
+      <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5"/>
@@ -9721,16 +9769,16 @@
         <v>312</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -9761,13 +9809,13 @@
         <v>312</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="F141" s="6" t="s">
         <v>335</v>
@@ -9801,19 +9849,19 @@
         <v>312</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="E142" s="6" t="s">
-        <v>347</v>
+        <v>337</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>335</v>
       </c>
       <c r="G142" s="5"/>
-      <c r="H142" s="5"/>
+      <c r="H142" s="4"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
       <c r="K142" s="5"/>
@@ -9837,17 +9885,17 @@
       <c r="A143" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B143" s="8" t="s">
+      <c r="B143" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="C143" s="8" t="s">
-        <v>348</v>
+      <c r="C143" s="6" t="s">
+        <v>339</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="F143" s="6" t="s">
         <v>335</v>
@@ -9855,7 +9903,7 @@
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
-      <c r="J143" s="6"/>
+      <c r="J143" s="5"/>
       <c r="K143" s="5"/>
       <c r="L143" s="5"/>
       <c r="M143" s="6"/>
@@ -9874,23 +9922,23 @@
       <c r="Z143" s="3"/>
     </row>
     <row r="144" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A144" s="6" t="s">
+      <c r="A144" s="8" t="s">
         <v>274</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>354</v>
+        <v>343</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>335</v>
       </c>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
@@ -9914,23 +9962,23 @@
       <c r="Z144" s="3"/>
     </row>
     <row r="145" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A145" s="6" t="s">
+      <c r="A145" s="8" t="s">
         <v>274</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>357</v>
+        <v>346</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>335</v>
       </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
@@ -9957,21 +10005,25 @@
       <c r="A146" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B146" s="5"/>
-      <c r="C146" s="6" t="s">
-        <v>358</v>
+      <c r="B146" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="E146" s="5"/>
-      <c r="F146" s="16"/>
-      <c r="G146" s="16"/>
+        <v>349</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G146" s="5"/>
       <c r="H146" s="5"/>
-      <c r="I146" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="J146" s="16"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="6"/>
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
       <c r="M146" s="6"/>
@@ -9990,24 +10042,28 @@
       <c r="Z146" s="3"/>
     </row>
     <row r="147" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A147" s="8" t="s">
+      <c r="A147" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B147" s="5"/>
+      <c r="B147" s="6" t="s">
+        <v>351</v>
+      </c>
       <c r="C147" s="6" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="E147" s="5"/>
-      <c r="F147" s="16"/>
-      <c r="G147" s="16"/>
+        <v>353</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="G147" s="5"/>
       <c r="H147" s="5"/>
-      <c r="I147" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="J147" s="16"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5"/>
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="6"/>
@@ -10026,24 +10082,26 @@
       <c r="Z147" s="3"/>
     </row>
     <row r="148" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A148" s="8" t="s">
+      <c r="A148" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B148" s="5"/>
+      <c r="B148" s="6" t="s">
+        <v>351</v>
+      </c>
       <c r="C148" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="D148" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="F148" s="5"/>
+        <v>355</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>357</v>
+      </c>
       <c r="G148" s="5"/>
-      <c r="H148" s="6" t="s">
-        <v>365</v>
-      </c>
+      <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
@@ -10064,26 +10122,24 @@
       <c r="Z148" s="3"/>
     </row>
     <row r="149" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A149" s="6" t="s">
-        <v>366</v>
+      <c r="A149" s="8" t="s">
+        <v>274</v>
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="D149" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="F149" s="5"/>
-      <c r="G149" s="5"/>
-      <c r="H149" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="I149" s="5"/>
-      <c r="J149" s="5"/>
+        <v>358</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="E149" s="5"/>
+      <c r="F149" s="16"/>
+      <c r="G149" s="16"/>
+      <c r="H149" s="5"/>
+      <c r="I149" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="J149" s="16"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="6"/>
@@ -10102,26 +10158,24 @@
       <c r="Z149" s="3"/>
     </row>
     <row r="150" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A150" s="6" t="s">
-        <v>366</v>
+      <c r="A150" s="8" t="s">
+        <v>274</v>
       </c>
       <c r="B150" s="5"/>
       <c r="C150" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="D150" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="F150" s="5"/>
-      <c r="G150" s="5"/>
-      <c r="H150" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="I150" s="5"/>
-      <c r="J150" s="5"/>
+        <v>360</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="E150" s="5"/>
+      <c r="F150" s="16"/>
+      <c r="G150" s="16"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="J150" s="16"/>
       <c r="K150" s="5"/>
       <c r="L150" s="5"/>
       <c r="M150" s="6"/>
@@ -10140,24 +10194,24 @@
       <c r="Z150" s="3"/>
     </row>
     <row r="151" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A151" s="6" t="s">
-        <v>366</v>
+      <c r="A151" s="8" t="s">
+        <v>274</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="6" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>375</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="F151" s="5"/>
       <c r="G151" s="5"/>
-      <c r="H151" s="5"/>
+      <c r="H151" s="6" t="s">
+        <v>365</v>
+      </c>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
@@ -10179,21 +10233,23 @@
     </row>
     <row r="152" spans="1:26" ht="13.5" customHeight="1">
       <c r="A152" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="B152" s="6"/>
+        <v>366</v>
+      </c>
+      <c r="B152" s="5"/>
       <c r="C152" s="6" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="F152" s="5"/>
       <c r="G152" s="5"/>
-      <c r="H152" s="5"/>
+      <c r="H152" s="6" t="s">
+        <v>369</v>
+      </c>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
@@ -10215,32 +10271,28 @@
     </row>
     <row r="153" spans="1:26" ht="13.5" customHeight="1">
       <c r="A153" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>380</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="B153" s="5"/>
       <c r="C153" s="6" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="F153" s="6" t="s">
-        <v>383</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="F153" s="5"/>
       <c r="G153" s="5"/>
-      <c r="H153" s="5"/>
+      <c r="H153" s="6" t="s">
+        <v>372</v>
+      </c>
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
       <c r="L153" s="5"/>
-      <c r="M153" s="6" t="s">
-        <v>384</v>
-      </c>
+      <c r="M153" s="6"/>
       <c r="N153" s="3"/>
       <c r="O153" s="3"/>
       <c r="P153" s="3"/>
@@ -10257,34 +10309,28 @@
     </row>
     <row r="154" spans="1:26" ht="13.5" customHeight="1">
       <c r="A154" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>380</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="B154" s="5"/>
       <c r="C154" s="6" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>387</v>
+        <v>71</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="G154" s="5"/>
-      <c r="H154" s="6" t="s">
-        <v>387</v>
-      </c>
+      <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
-      <c r="M154" s="6" t="s">
-        <v>384</v>
-      </c>
+      <c r="M154" s="6"/>
       <c r="N154" s="3"/>
       <c r="O154" s="3"/>
       <c r="P154" s="3"/>
@@ -10303,32 +10349,24 @@
       <c r="A155" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="B155" s="6" t="s">
-        <v>380</v>
-      </c>
+      <c r="B155" s="6"/>
       <c r="C155" s="6" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="F155" s="6" t="s">
-        <v>390</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="F155" s="5"/>
       <c r="G155" s="5"/>
-      <c r="H155" s="6" t="s">
-        <v>390</v>
-      </c>
+      <c r="H155" s="5"/>
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
-      <c r="M155" s="6" t="s">
-        <v>384</v>
-      </c>
+      <c r="M155" s="6"/>
       <c r="N155" s="3"/>
       <c r="O155" s="3"/>
       <c r="P155" s="3"/>
@@ -10351,21 +10389,19 @@
         <v>380</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="G156" s="5"/>
-      <c r="H156" s="6" t="s">
-        <v>393</v>
-      </c>
+      <c r="H156" s="5"/>
       <c r="I156" s="5"/>
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
@@ -10387,30 +10423,36 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" spans="1:26" ht="15" customHeight="1">
+    <row r="157" spans="1:26" ht="13.5" customHeight="1">
       <c r="A157" s="6" t="s">
         <v>376</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>396</v>
-      </c>
-      <c r="E157" s="5"/>
-      <c r="F157" s="5"/>
+        <v>386</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>387</v>
+      </c>
       <c r="G157" s="5"/>
-      <c r="H157" s="5"/>
-      <c r="I157" s="6" t="s">
-        <v>397</v>
-      </c>
+      <c r="H157" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
-      <c r="M157" s="6"/>
+      <c r="M157" s="6" t="s">
+        <v>384</v>
+      </c>
       <c r="N157" s="3"/>
       <c r="O157" s="3"/>
       <c r="P157" s="3"/>
@@ -10430,23 +10472,31 @@
         <v>376</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D158" s="11" t="s">
-        <v>399</v>
-      </c>
-      <c r="E158" s="5"/>
-      <c r="F158" s="5"/>
+        <v>389</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>390</v>
+      </c>
       <c r="G158" s="5"/>
-      <c r="H158" s="5"/>
+      <c r="H158" s="6" t="s">
+        <v>390</v>
+      </c>
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
-      <c r="M158" s="6"/>
+      <c r="M158" s="6" t="s">
+        <v>384</v>
+      </c>
       <c r="N158" s="3"/>
       <c r="O158" s="3"/>
       <c r="P158" s="3"/>
@@ -10465,26 +10515,32 @@
       <c r="A159" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="B159" s="8" t="s">
-        <v>400</v>
+      <c r="B159" s="6" t="s">
+        <v>380</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="E159" s="5"/>
-      <c r="F159" s="5"/>
+        <v>392</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>393</v>
+      </c>
       <c r="G159" s="5"/>
-      <c r="H159" s="5"/>
-      <c r="I159" s="6" t="s">
-        <v>403</v>
-      </c>
+      <c r="H159" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="I159" s="5"/>
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
-      <c r="M159" s="6"/>
+      <c r="M159" s="6" t="s">
+        <v>384</v>
+      </c>
       <c r="N159" s="3"/>
       <c r="O159" s="3"/>
       <c r="P159" s="3"/>
@@ -10499,30 +10555,26 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" spans="1:26" ht="13.5" customHeight="1">
+    <row r="160" spans="1:26" ht="15" customHeight="1">
       <c r="A160" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="B160" s="8" t="s">
-        <v>400</v>
+      <c r="B160" s="6" t="s">
+        <v>394</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>406</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="E160" s="5"/>
+      <c r="F160" s="5"/>
       <c r="G160" s="5"/>
-      <c r="H160" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="I160" s="5"/>
+      <c r="H160" s="5"/>
+      <c r="I160" s="6" t="s">
+        <v>397</v>
+      </c>
       <c r="J160" s="5"/>
       <c r="K160" s="5"/>
       <c r="L160" s="5"/>
@@ -10545,22 +10597,20 @@
       <c r="A161" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="B161" s="8" t="s">
-        <v>400</v>
+      <c r="B161" s="6" t="s">
+        <v>394</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
-      <c r="I161" s="6" t="s">
-        <v>403</v>
-      </c>
+      <c r="I161" s="5"/>
       <c r="J161" s="5"/>
       <c r="K161" s="5"/>
       <c r="L161" s="5"/>
@@ -10587,17 +10637,17 @@
         <v>400</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E162" s="5"/>
       <c r="F162" s="5"/>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
-      <c r="I162" s="8" t="s">
-        <v>411</v>
+      <c r="I162" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="J162" s="5"/>
       <c r="K162" s="5"/>
@@ -10625,18 +10675,22 @@
         <v>400</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="E163" s="5"/>
-      <c r="F163" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>406</v>
+      </c>
       <c r="G163" s="5"/>
-      <c r="H163" s="5"/>
-      <c r="I163" s="8" t="s">
-        <v>411</v>
-      </c>
+      <c r="H163" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="I163" s="5"/>
       <c r="J163" s="5"/>
       <c r="K163" s="5"/>
       <c r="L163" s="5"/>
@@ -10663,17 +10717,17 @@
         <v>400</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
       <c r="G164" s="5"/>
       <c r="H164" s="5"/>
-      <c r="I164" s="8" t="s">
-        <v>416</v>
+      <c r="I164" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="J164" s="5"/>
       <c r="K164" s="5"/>
@@ -10701,22 +10755,18 @@
         <v>400</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>418</v>
-      </c>
-      <c r="E165" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="F165" s="6" t="s">
-        <v>419</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="E165" s="5"/>
+      <c r="F165" s="5"/>
       <c r="G165" s="5"/>
-      <c r="H165" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="I165" s="5"/>
+      <c r="H165" s="5"/>
+      <c r="I165" s="8" t="s">
+        <v>411</v>
+      </c>
       <c r="J165" s="5"/>
       <c r="K165" s="5"/>
       <c r="L165" s="5"/>
@@ -10739,24 +10789,22 @@
       <c r="A166" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="B166" s="6" t="s">
-        <v>420</v>
+      <c r="B166" s="8" t="s">
+        <v>400</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="D166" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="E166" s="6" t="s">
-        <v>423</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="E166" s="5"/>
       <c r="F166" s="5"/>
       <c r="G166" s="5"/>
-      <c r="H166" s="6" t="s">
-        <v>423</v>
-      </c>
-      <c r="I166" s="5"/>
+      <c r="H166" s="5"/>
+      <c r="I166" s="8" t="s">
+        <v>411</v>
+      </c>
       <c r="J166" s="5"/>
       <c r="K166" s="5"/>
       <c r="L166" s="5"/>
@@ -10779,24 +10827,22 @@
       <c r="A167" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="B167" s="6" t="s">
-        <v>420</v>
+      <c r="B167" s="8" t="s">
+        <v>400</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="D167" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="E167" s="6" t="s">
-        <v>426</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="E167" s="5"/>
       <c r="F167" s="5"/>
       <c r="G167" s="5"/>
-      <c r="H167" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="I167" s="5"/>
+      <c r="H167" s="5"/>
+      <c r="I167" s="8" t="s">
+        <v>416</v>
+      </c>
       <c r="J167" s="5"/>
       <c r="K167" s="5"/>
       <c r="L167" s="5"/>
@@ -10819,22 +10865,24 @@
       <c r="A168" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="B168" s="6" t="s">
-        <v>420</v>
+      <c r="B168" s="8" t="s">
+        <v>400</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="D168" s="13" t="s">
-        <v>428</v>
+        <v>417</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>418</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="F168" s="5"/>
+        <v>419</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>419</v>
+      </c>
       <c r="G168" s="5"/>
       <c r="H168" s="6" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
@@ -10863,18 +10911,18 @@
         <v>420</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="D169" s="13" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="F169" s="5"/>
       <c r="G169" s="5"/>
       <c r="H169" s="6" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
@@ -10899,20 +10947,22 @@
       <c r="A170" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="B170" s="26" t="s">
-        <v>567</v>
-      </c>
-      <c r="C170" s="26" t="s">
-        <v>568</v>
-      </c>
-      <c r="D170" s="29" t="s">
-        <v>573</v>
-      </c>
-      <c r="E170" s="6"/>
+      <c r="B170" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D170" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>426</v>
+      </c>
       <c r="F170" s="5"/>
       <c r="G170" s="5"/>
       <c r="H170" s="6" t="s">
-        <v>578</v>
+        <v>426</v>
       </c>
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
@@ -10937,20 +10987,22 @@
       <c r="A171" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="B171" s="26" t="s">
-        <v>567</v>
-      </c>
-      <c r="C171" s="26" t="s">
-        <v>569</v>
-      </c>
-      <c r="D171" s="29" t="s">
-        <v>574</v>
-      </c>
-      <c r="E171" s="6"/>
+      <c r="B171" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>429</v>
+      </c>
       <c r="F171" s="5"/>
       <c r="G171" s="5"/>
       <c r="H171" s="6" t="s">
-        <v>579</v>
+        <v>429</v>
       </c>
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
@@ -10975,20 +11027,22 @@
       <c r="A172" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="B172" s="26" t="s">
-        <v>567</v>
-      </c>
-      <c r="C172" s="26" t="s">
-        <v>570</v>
-      </c>
-      <c r="D172" s="28" t="s">
-        <v>575</v>
-      </c>
-      <c r="E172" s="6"/>
+      <c r="B172" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>432</v>
+      </c>
       <c r="F172" s="5"/>
       <c r="G172" s="5"/>
       <c r="H172" s="6" t="s">
-        <v>580</v>
+        <v>432</v>
       </c>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
@@ -11014,19 +11068,19 @@
         <v>376</v>
       </c>
       <c r="B173" s="26" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C173" s="26" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="D173" s="29" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="E173" s="6"/>
       <c r="F173" s="5"/>
       <c r="G173" s="5"/>
       <c r="H173" s="6" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
@@ -11052,19 +11106,19 @@
         <v>376</v>
       </c>
       <c r="B174" s="26" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C174" s="26" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D174" s="29" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="E174" s="6"/>
       <c r="F174" s="5"/>
       <c r="G174" s="5"/>
       <c r="H174" s="6" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
@@ -11087,22 +11141,22 @@
     </row>
     <row r="175" spans="1:26" ht="13.5" customHeight="1">
       <c r="A175" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="B175" s="5"/>
-      <c r="C175" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="D175" s="11" t="s">
-        <v>435</v>
-      </c>
-      <c r="E175" s="6" t="s">
-        <v>289</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="B175" s="26" t="s">
+        <v>564</v>
+      </c>
+      <c r="C175" s="26" t="s">
+        <v>567</v>
+      </c>
+      <c r="D175" s="28" t="s">
+        <v>572</v>
+      </c>
+      <c r="E175" s="6"/>
       <c r="F175" s="5"/>
       <c r="G175" s="5"/>
       <c r="H175" s="6" t="s">
-        <v>289</v>
+        <v>577</v>
       </c>
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
@@ -11124,26 +11178,24 @@
       <c r="Z175" s="3"/>
     </row>
     <row r="176" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A176" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="C176" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="D176" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="E176" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="F176" s="6" t="s">
-        <v>292</v>
-      </c>
+      <c r="A176" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B176" s="26" t="s">
+        <v>564</v>
+      </c>
+      <c r="C176" s="26" t="s">
+        <v>568</v>
+      </c>
+      <c r="D176" s="29" t="s">
+        <v>573</v>
+      </c>
+      <c r="E176" s="6"/>
+      <c r="F176" s="5"/>
       <c r="G176" s="5"/>
-      <c r="H176" s="5"/>
+      <c r="H176" s="6" t="s">
+        <v>578</v>
+      </c>
       <c r="I176" s="5"/>
       <c r="J176" s="5"/>
       <c r="K176" s="5"/>
@@ -11164,26 +11216,24 @@
       <c r="Z176" s="3"/>
     </row>
     <row r="177" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A177" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="B177" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="C177" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="D177" s="11" t="s">
-        <v>442</v>
-      </c>
-      <c r="E177" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="F177" s="6" t="s">
-        <v>292</v>
-      </c>
+      <c r="A177" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B177" s="26" t="s">
+        <v>564</v>
+      </c>
+      <c r="C177" s="26" t="s">
+        <v>569</v>
+      </c>
+      <c r="D177" s="29" t="s">
+        <v>574</v>
+      </c>
+      <c r="E177" s="6"/>
+      <c r="F177" s="5"/>
       <c r="G177" s="5"/>
-      <c r="H177" s="5"/>
+      <c r="H177" s="6" t="s">
+        <v>579</v>
+      </c>
       <c r="I177" s="5"/>
       <c r="J177" s="5"/>
       <c r="K177" s="5"/>
@@ -11204,27 +11254,25 @@
       <c r="Z177" s="3"/>
     </row>
     <row r="178" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A178" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>444</v>
-      </c>
+      <c r="A178" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B178" s="5"/>
       <c r="C178" s="6" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="E178" s="5"/>
-      <c r="F178" s="6" t="s">
-        <v>446</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="F178" s="5"/>
       <c r="G178" s="5"/>
-      <c r="H178" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="I178" s="5"/>
+      <c r="H178" s="6"/>
+      <c r="I178" s="5" t="s">
+        <v>630</v>
+      </c>
       <c r="J178" s="5"/>
       <c r="K178" s="5"/>
       <c r="L178" s="5"/>
@@ -11248,24 +11296,22 @@
         <v>436</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>450</v>
+        <v>292</v>
       </c>
       <c r="G179" s="5"/>
-      <c r="H179" s="6" t="s">
-        <v>450</v>
-      </c>
+      <c r="H179" s="5"/>
       <c r="I179" s="5"/>
       <c r="J179" s="5"/>
       <c r="K179" s="5"/>
@@ -11290,24 +11336,22 @@
         <v>436</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>21</v>
+        <v>443</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="G180" s="5"/>
-      <c r="H180" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="H180" s="5"/>
       <c r="I180" s="5"/>
       <c r="J180" s="5"/>
       <c r="K180" s="5"/>
@@ -11331,20 +11375,24 @@
       <c r="A181" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="B181" s="5"/>
+      <c r="B181" s="6" t="s">
+        <v>444</v>
+      </c>
       <c r="C181" s="6" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="E181" s="5"/>
-      <c r="F181" s="5"/>
+      <c r="F181" s="6" t="s">
+        <v>446</v>
+      </c>
       <c r="G181" s="5"/>
-      <c r="H181" s="5"/>
-      <c r="I181" s="6" t="s">
-        <v>455</v>
-      </c>
+      <c r="H181" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="I181" s="5"/>
       <c r="J181" s="5"/>
       <c r="K181" s="5"/>
       <c r="L181" s="5"/>
@@ -11365,24 +11413,28 @@
     </row>
     <row r="182" spans="1:26" ht="13.5" customHeight="1">
       <c r="A182" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="B182" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="C182" s="8" t="s">
-        <v>458</v>
+        <v>436</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>448</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="E182" s="5"/>
-      <c r="F182" s="5"/>
+        <v>449</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>450</v>
+      </c>
       <c r="G182" s="5"/>
-      <c r="H182" s="5"/>
-      <c r="I182" s="8" t="s">
-        <v>460</v>
-      </c>
+      <c r="H182" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="I182" s="5"/>
       <c r="J182" s="5"/>
       <c r="K182" s="5"/>
       <c r="L182" s="5"/>
@@ -11403,24 +11455,26 @@
     </row>
     <row r="183" spans="1:26" ht="13.5" customHeight="1">
       <c r="A183" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="B183" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="C183" s="8" t="s">
-        <v>461</v>
+        <v>436</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>451</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="F183" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="G183" s="5"/>
       <c r="H183" s="6" t="s">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="I183" s="5"/>
       <c r="J183" s="5"/>
@@ -11443,23 +11497,21 @@
     </row>
     <row r="184" spans="1:26" ht="13.5" customHeight="1">
       <c r="A184" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="B184" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="C184" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="D184" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="E184" s="19"/>
-      <c r="F184" s="19"/>
-      <c r="G184" s="19"/>
-      <c r="H184" s="20"/>
-      <c r="I184" s="8" t="s">
-        <v>466</v>
+        <v>436</v>
+      </c>
+      <c r="B184" s="5"/>
+      <c r="C184" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="E184" s="5"/>
+      <c r="F184" s="5"/>
+      <c r="G184" s="5"/>
+      <c r="H184" s="5"/>
+      <c r="I184" s="6" t="s">
+        <v>455</v>
       </c>
       <c r="J184" s="5"/>
       <c r="K184" s="5"/>
@@ -11484,23 +11536,21 @@
         <v>456</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="E185" s="6" t="s">
-        <v>469</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="E185" s="5"/>
       <c r="F185" s="5"/>
       <c r="G185" s="5"/>
-      <c r="H185" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="I185" s="5"/>
+      <c r="H185" s="5"/>
+      <c r="I185" s="8" t="s">
+        <v>460</v>
+      </c>
       <c r="J185" s="5"/>
       <c r="K185" s="5"/>
       <c r="L185" s="5"/>
@@ -11524,20 +11574,22 @@
         <v>456</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>472</v>
-      </c>
-      <c r="E186" s="5"/>
-      <c r="F186" s="6" t="s">
-        <v>473</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="F186" s="5"/>
       <c r="G186" s="5"/>
-      <c r="H186" s="5"/>
+      <c r="H186" s="6" t="s">
+        <v>289</v>
+      </c>
       <c r="I186" s="5"/>
       <c r="J186" s="5"/>
       <c r="K186" s="5"/>
@@ -11562,21 +11614,21 @@
         <v>456</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="D187" s="11" t="s">
-        <v>475</v>
-      </c>
-      <c r="E187" s="5"/>
-      <c r="F187" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G187" s="5"/>
-      <c r="H187" s="5"/>
-      <c r="I187" s="5"/>
+        <v>464</v>
+      </c>
+      <c r="D187" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="E187" s="19"/>
+      <c r="F187" s="19"/>
+      <c r="G187" s="19"/>
+      <c r="H187" s="20"/>
+      <c r="I187" s="8" t="s">
+        <v>466</v>
+      </c>
       <c r="J187" s="5"/>
       <c r="K187" s="5"/>
       <c r="L187" s="5"/>
@@ -11600,20 +11652,22 @@
         <v>456</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="E188" s="5"/>
-      <c r="F188" s="6" t="s">
-        <v>479</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="F188" s="5"/>
       <c r="G188" s="5"/>
-      <c r="H188" s="5"/>
+      <c r="H188" s="6" t="s">
+        <v>469</v>
+      </c>
       <c r="I188" s="5"/>
       <c r="J188" s="5"/>
       <c r="K188" s="5"/>
@@ -11641,14 +11695,14 @@
         <v>470</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="E189" s="5"/>
       <c r="F189" s="6" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="G189" s="5"/>
       <c r="H189" s="5"/>
@@ -11679,14 +11733,14 @@
         <v>470</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E190" s="5"/>
       <c r="F190" s="6" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="G190" s="5"/>
       <c r="H190" s="5"/>
@@ -11717,14 +11771,14 @@
         <v>470</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="E191" s="5"/>
       <c r="F191" s="6" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="G191" s="5"/>
       <c r="H191" s="5"/>
@@ -11755,14 +11809,14 @@
         <v>470</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="E192" s="5"/>
       <c r="F192" s="6" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="G192" s="5"/>
       <c r="H192" s="5"/>
@@ -11793,14 +11847,14 @@
         <v>470</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="E193" s="5"/>
       <c r="F193" s="6" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="G193" s="5"/>
       <c r="H193" s="5"/>
@@ -11831,14 +11885,14 @@
         <v>470</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="E194" s="5"/>
       <c r="F194" s="6" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="G194" s="5"/>
       <c r="H194" s="5"/>
@@ -11869,14 +11923,14 @@
         <v>470</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="E195" s="5"/>
       <c r="F195" s="6" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="G195" s="5"/>
       <c r="H195" s="5"/>
@@ -11907,14 +11961,14 @@
         <v>470</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="E196" s="5"/>
       <c r="F196" s="6" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="G196" s="5"/>
       <c r="H196" s="5"/>
@@ -11945,14 +11999,14 @@
         <v>470</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="E197" s="5"/>
       <c r="F197" s="6" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="G197" s="5"/>
       <c r="H197" s="5"/>
@@ -11983,14 +12037,14 @@
         <v>470</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="E198" s="5"/>
       <c r="F198" s="6" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="G198" s="5"/>
       <c r="H198" s="5"/>
@@ -12018,20 +12072,20 @@
         <v>456</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D199" s="11" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="E199" s="5"/>
-      <c r="F199" s="5"/>
+      <c r="F199" s="6" t="s">
+        <v>503</v>
+      </c>
       <c r="G199" s="5"/>
-      <c r="H199" s="5" t="s">
-        <v>513</v>
-      </c>
+      <c r="H199" s="5"/>
       <c r="I199" s="5"/>
       <c r="J199" s="5"/>
       <c r="K199" s="5"/>
@@ -12056,20 +12110,20 @@
         <v>456</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>514</v>
+        <v>470</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="E200" s="5"/>
-      <c r="F200" s="5"/>
+      <c r="F200" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="G200" s="5"/>
-      <c r="H200" s="5" t="s">
-        <v>517</v>
-      </c>
+      <c r="H200" s="5"/>
       <c r="I200" s="5"/>
       <c r="J200" s="5"/>
       <c r="K200" s="5"/>
@@ -12094,20 +12148,20 @@
         <v>456</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>514</v>
+        <v>470</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="E201" s="5"/>
-      <c r="F201" s="5"/>
+      <c r="F201" s="6" t="s">
+        <v>509</v>
+      </c>
       <c r="G201" s="5"/>
-      <c r="H201" s="5" t="s">
-        <v>520</v>
-      </c>
+      <c r="H201" s="5"/>
       <c r="I201" s="5"/>
       <c r="J201" s="5"/>
       <c r="K201" s="5"/>
@@ -12132,20 +12186,20 @@
         <v>456</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="E202" s="5"/>
       <c r="F202" s="5"/>
       <c r="G202" s="5"/>
       <c r="H202" s="5"/>
-      <c r="I202" s="6" t="s">
-        <v>523</v>
+      <c r="I202" s="5" t="s">
+        <v>524</v>
       </c>
       <c r="J202" s="5"/>
       <c r="K202" s="5"/>
@@ -12167,21 +12221,23 @@
     </row>
     <row r="203" spans="1:26" ht="13.5" customHeight="1">
       <c r="A203" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="B203" s="5"/>
+        <v>456</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>513</v>
+      </c>
       <c r="C203" s="8" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="E203" s="5"/>
       <c r="F203" s="5"/>
       <c r="G203" s="5"/>
       <c r="H203" s="5"/>
-      <c r="I203" s="6" t="s">
-        <v>527</v>
+      <c r="I203" s="5" t="s">
+        <v>627</v>
       </c>
       <c r="J203" s="5"/>
       <c r="K203" s="5"/>
@@ -12203,24 +12259,24 @@
     </row>
     <row r="204" spans="1:26" ht="13.5" customHeight="1">
       <c r="A204" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="B204" s="5"/>
+        <v>456</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>513</v>
+      </c>
       <c r="C204" s="8" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="D204" s="11" t="s">
-        <v>529</v>
-      </c>
-      <c r="E204" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="F204" s="5" t="s">
-        <v>530</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="E204" s="5"/>
+      <c r="F204" s="5"/>
       <c r="G204" s="5"/>
       <c r="H204" s="5"/>
-      <c r="I204" s="5"/>
+      <c r="I204" s="5" t="s">
+        <v>629</v>
+      </c>
       <c r="J204" s="5"/>
       <c r="K204" s="5"/>
       <c r="L204" s="5"/>
@@ -12240,24 +12296,24 @@
       <c r="Z204" s="3"/>
     </row>
     <row r="205" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A205" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="B205" s="33" t="s">
-        <v>617</v>
-      </c>
-      <c r="C205" s="41" t="s">
-        <v>618</v>
-      </c>
-      <c r="D205" s="27" t="s">
-        <v>619</v>
+      <c r="A205" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C205" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="D205" s="11" t="s">
+        <v>519</v>
       </c>
       <c r="E205" s="5"/>
       <c r="F205" s="5"/>
       <c r="G205" s="5"/>
       <c r="H205" s="5"/>
-      <c r="I205" s="5" t="s">
-        <v>595</v>
+      <c r="I205" s="6" t="s">
+        <v>520</v>
       </c>
       <c r="J205" s="5"/>
       <c r="K205" s="5"/>
@@ -12278,27 +12334,23 @@
       <c r="Z205" s="3"/>
     </row>
     <row r="206" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A206" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="B206" s="33" t="s">
-        <v>617</v>
-      </c>
-      <c r="C206" s="41" t="s">
-        <v>620</v>
-      </c>
-      <c r="D206" s="42" t="s">
-        <v>621</v>
-      </c>
-      <c r="E206" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="F206" s="5" t="s">
-        <v>235</v>
-      </c>
+      <c r="A206" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="B206" s="5"/>
+      <c r="C206" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="D206" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="E206" s="5"/>
+      <c r="F206" s="5"/>
       <c r="G206" s="5"/>
       <c r="H206" s="5"/>
-      <c r="I206" s="5"/>
+      <c r="I206" s="6" t="s">
+        <v>628</v>
+      </c>
       <c r="J206" s="5"/>
       <c r="K206" s="5"/>
       <c r="L206" s="5"/>
@@ -12318,23 +12370,25 @@
       <c r="Z206" s="3"/>
     </row>
     <row r="207" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A207" s="6" t="s">
-        <v>531</v>
+      <c r="A207" s="8" t="s">
+        <v>521</v>
       </c>
       <c r="B207" s="5"/>
-      <c r="C207" s="6" t="s">
-        <v>532</v>
+      <c r="C207" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>533</v>
-      </c>
-      <c r="E207" s="5"/>
-      <c r="F207" s="5"/>
+        <v>526</v>
+      </c>
+      <c r="E207" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>527</v>
+      </c>
       <c r="G207" s="5"/>
       <c r="H207" s="5"/>
-      <c r="I207" s="6" t="s">
-        <v>534</v>
-      </c>
+      <c r="I207" s="5"/>
       <c r="J207" s="5"/>
       <c r="K207" s="5"/>
       <c r="L207" s="5"/>
@@ -12355,21 +12409,23 @@
     </row>
     <row r="208" spans="1:26" ht="13.5" customHeight="1">
       <c r="A208" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="B208" s="5"/>
-      <c r="C208" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="D208" s="11" t="s">
-        <v>536</v>
+        <v>528</v>
+      </c>
+      <c r="B208" s="33" t="s">
+        <v>614</v>
+      </c>
+      <c r="C208" s="41" t="s">
+        <v>615</v>
+      </c>
+      <c r="D208" s="27" t="s">
+        <v>616</v>
       </c>
       <c r="E208" s="5"/>
       <c r="F208" s="5"/>
       <c r="G208" s="5"/>
       <c r="H208" s="5"/>
-      <c r="I208" s="8" t="s">
-        <v>537</v>
+      <c r="I208" s="5" t="s">
+        <v>592</v>
       </c>
       <c r="J208" s="5"/>
       <c r="K208" s="5"/>
@@ -12391,22 +12447,26 @@
     </row>
     <row r="209" spans="1:26" ht="13.5" customHeight="1">
       <c r="A209" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="B209" s="5"/>
-      <c r="C209" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="D209" s="11" t="s">
-        <v>539</v>
-      </c>
-      <c r="E209" s="5"/>
-      <c r="F209" s="5"/>
+        <v>528</v>
+      </c>
+      <c r="B209" s="33" t="s">
+        <v>614</v>
+      </c>
+      <c r="C209" s="41" t="s">
+        <v>617</v>
+      </c>
+      <c r="D209" s="42" t="s">
+        <v>618</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>235</v>
+      </c>
       <c r="G209" s="5"/>
       <c r="H209" s="5"/>
-      <c r="I209" s="6" t="s">
-        <v>540</v>
-      </c>
+      <c r="I209" s="5"/>
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
       <c r="L209" s="5"/>
@@ -12427,21 +12487,21 @@
     </row>
     <row r="210" spans="1:26" ht="13.5" customHeight="1">
       <c r="A210" s="6" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B210" s="5"/>
       <c r="C210" s="6" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="E210" s="5"/>
       <c r="F210" s="5"/>
       <c r="G210" s="5"/>
       <c r="H210" s="5"/>
       <c r="I210" s="6" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="J210" s="5"/>
       <c r="K210" s="5"/>
@@ -12463,22 +12523,22 @@
     </row>
     <row r="211" spans="1:26" ht="13.5" customHeight="1">
       <c r="A211" s="6" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B211" s="5"/>
-      <c r="C211" s="6" t="s">
-        <v>544</v>
+      <c r="C211" s="8" t="s">
+        <v>532</v>
       </c>
       <c r="D211" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="E211" s="6" t="s">
-        <v>546</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="E211" s="5"/>
       <c r="F211" s="5"/>
       <c r="G211" s="5"/>
       <c r="H211" s="5"/>
-      <c r="I211" s="5"/>
+      <c r="I211" s="8" t="s">
+        <v>534</v>
+      </c>
       <c r="J211" s="5"/>
       <c r="K211" s="5"/>
       <c r="L211" s="5"/>
@@ -12498,22 +12558,22 @@
       <c r="Z211" s="3"/>
     </row>
     <row r="212" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A212" s="8" t="s">
-        <v>547</v>
+      <c r="A212" s="6" t="s">
+        <v>528</v>
       </c>
       <c r="B212" s="5"/>
-      <c r="C212" s="26" t="s">
-        <v>564</v>
-      </c>
-      <c r="D212" s="27" t="s">
-        <v>566</v>
-      </c>
-      <c r="E212" s="6"/>
+      <c r="C212" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="D212" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="E212" s="5"/>
       <c r="F212" s="5"/>
       <c r="G212" s="5"/>
       <c r="H212" s="5"/>
-      <c r="I212" s="5" t="s">
-        <v>565</v>
+      <c r="I212" s="6" t="s">
+        <v>537</v>
       </c>
       <c r="J212" s="5"/>
       <c r="K212" s="5"/>
@@ -12534,22 +12594,22 @@
       <c r="Z212" s="3"/>
     </row>
     <row r="213" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A213" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="B213" s="4"/>
-      <c r="C213" s="21" t="s">
-        <v>548</v>
-      </c>
-      <c r="D213" s="22" t="s">
-        <v>549</v>
-      </c>
-      <c r="E213" s="4"/>
+      <c r="A213" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="B213" s="5"/>
+      <c r="C213" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="D213" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="E213" s="5"/>
       <c r="F213" s="5"/>
       <c r="G213" s="5"/>
-      <c r="H213" s="4"/>
+      <c r="H213" s="5"/>
       <c r="I213" s="6" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="J213" s="5"/>
       <c r="K213" s="5"/>
@@ -12570,23 +12630,23 @@
       <c r="Z213" s="3"/>
     </row>
     <row r="214" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A214" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="B214" s="4"/>
-      <c r="C214" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="D214" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="E214" s="4"/>
+      <c r="A214" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="B214" s="5"/>
+      <c r="C214" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="D214" s="11" t="s">
+        <v>542</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>543</v>
+      </c>
       <c r="F214" s="5"/>
       <c r="G214" s="5"/>
-      <c r="H214" s="4"/>
-      <c r="I214" s="6" t="s">
-        <v>553</v>
-      </c>
+      <c r="H214" s="5"/>
+      <c r="I214" s="5"/>
       <c r="J214" s="5"/>
       <c r="K214" s="5"/>
       <c r="L214" s="5"/>
@@ -12607,21 +12667,21 @@
     </row>
     <row r="215" spans="1:26" ht="13.5" customHeight="1">
       <c r="A215" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="B215" s="4"/>
-      <c r="C215" s="8" t="s">
-        <v>554</v>
-      </c>
-      <c r="D215" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="E215" s="4"/>
+        <v>544</v>
+      </c>
+      <c r="B215" s="5"/>
+      <c r="C215" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="D215" s="27" t="s">
+        <v>563</v>
+      </c>
+      <c r="E215" s="6"/>
       <c r="F215" s="5"/>
       <c r="G215" s="5"/>
-      <c r="H215" s="4"/>
-      <c r="I215" s="6" t="s">
-        <v>556</v>
+      <c r="H215" s="5"/>
+      <c r="I215" s="5" t="s">
+        <v>562</v>
       </c>
       <c r="J215" s="5"/>
       <c r="K215" s="5"/>
@@ -12643,21 +12703,21 @@
     </row>
     <row r="216" spans="1:26" ht="13.5" customHeight="1">
       <c r="A216" s="8" t="s">
-        <v>557</v>
-      </c>
-      <c r="B216" s="5"/>
-      <c r="C216" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="D216" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="E216" s="5"/>
+        <v>544</v>
+      </c>
+      <c r="B216" s="4"/>
+      <c r="C216" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="D216" s="22" t="s">
+        <v>546</v>
+      </c>
+      <c r="E216" s="4"/>
       <c r="F216" s="5"/>
       <c r="G216" s="5"/>
-      <c r="H216" s="5"/>
+      <c r="H216" s="4"/>
       <c r="I216" s="6" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="J216" s="5"/>
       <c r="K216" s="5"/>
@@ -12679,21 +12739,21 @@
     </row>
     <row r="217" spans="1:26" ht="13.5" customHeight="1">
       <c r="A217" s="8" t="s">
-        <v>557</v>
-      </c>
-      <c r="B217" s="5"/>
-      <c r="C217" s="6" t="s">
-        <v>561</v>
-      </c>
-      <c r="D217" s="32" t="s">
-        <v>562</v>
-      </c>
-      <c r="E217" s="5"/>
+        <v>544</v>
+      </c>
+      <c r="B217" s="4"/>
+      <c r="C217" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="D217" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="E217" s="4"/>
       <c r="F217" s="5"/>
       <c r="G217" s="5"/>
-      <c r="H217" s="5"/>
+      <c r="H217" s="4"/>
       <c r="I217" s="6" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="J217" s="5"/>
       <c r="K217" s="5"/>
@@ -12714,22 +12774,22 @@
       <c r="Z217" s="3"/>
     </row>
     <row r="218" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A218" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="B218" s="30"/>
-      <c r="C218" s="36" t="s">
-        <v>587</v>
-      </c>
-      <c r="D218" s="37" t="s">
-        <v>590</v>
-      </c>
-      <c r="E218" s="31"/>
+      <c r="A218" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="B218" s="4"/>
+      <c r="C218" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="D218" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="E218" s="4"/>
       <c r="F218" s="5"/>
       <c r="G218" s="5"/>
-      <c r="H218" s="5"/>
+      <c r="H218" s="4"/>
       <c r="I218" s="6" t="s">
-        <v>583</v>
+        <v>553</v>
       </c>
       <c r="J218" s="5"/>
       <c r="K218" s="5"/>
@@ -12750,22 +12810,22 @@
       <c r="Z218" s="3"/>
     </row>
     <row r="219" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A219" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="B219" s="33"/>
-      <c r="C219" s="38" t="s">
-        <v>597</v>
-      </c>
-      <c r="D219" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="E219" s="4"/>
-      <c r="F219" s="16"/>
-      <c r="G219" s="16"/>
-      <c r="H219" s="4"/>
+      <c r="A219" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="B219" s="5"/>
+      <c r="C219" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="D219" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="E219" s="5"/>
+      <c r="F219" s="5"/>
+      <c r="G219" s="5"/>
+      <c r="H219" s="5"/>
       <c r="I219" s="6" t="s">
-        <v>225</v>
+        <v>557</v>
       </c>
       <c r="J219" s="5"/>
       <c r="K219" s="5"/>
@@ -12786,22 +12846,22 @@
       <c r="Z219" s="3"/>
     </row>
     <row r="220" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A220" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="B220" s="33"/>
-      <c r="C220" s="25" t="s">
-        <v>584</v>
-      </c>
-      <c r="D220" s="24" t="s">
-        <v>593</v>
+      <c r="A220" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="B220" s="5"/>
+      <c r="C220" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="D220" s="32" t="s">
+        <v>559</v>
       </c>
       <c r="E220" s="5"/>
       <c r="F220" s="5"/>
       <c r="G220" s="5"/>
       <c r="H220" s="5"/>
-      <c r="I220" s="5" t="s">
-        <v>595</v>
+      <c r="I220" s="6" t="s">
+        <v>560</v>
       </c>
       <c r="J220" s="5"/>
       <c r="K220" s="5"/>
@@ -12823,21 +12883,21 @@
     </row>
     <row r="221" spans="1:26" ht="13.5" customHeight="1">
       <c r="A221" s="23" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B221" s="30"/>
-      <c r="C221" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="D221" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="E221" s="4"/>
-      <c r="F221" s="16"/>
-      <c r="G221" s="16"/>
-      <c r="H221" s="4"/>
+      <c r="C221" s="36" t="s">
+        <v>584</v>
+      </c>
+      <c r="D221" s="37" t="s">
+        <v>587</v>
+      </c>
+      <c r="E221" s="31"/>
+      <c r="F221" s="5"/>
+      <c r="G221" s="5"/>
+      <c r="H221" s="5"/>
       <c r="I221" s="6" t="s">
-        <v>212</v>
+        <v>580</v>
       </c>
       <c r="J221" s="5"/>
       <c r="K221" s="5"/>
@@ -12859,21 +12919,21 @@
     </row>
     <row r="222" spans="1:26" ht="13.5" customHeight="1">
       <c r="A222" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="B222" s="30"/>
-      <c r="C222" s="6" t="s">
-        <v>213</v>
+        <v>593</v>
+      </c>
+      <c r="B222" s="33"/>
+      <c r="C222" s="38" t="s">
+        <v>594</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="16"/>
       <c r="G222" s="16"/>
       <c r="H222" s="4"/>
       <c r="I222" s="6" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="J222" s="5"/>
       <c r="K222" s="5"/>
@@ -12895,23 +12955,21 @@
     </row>
     <row r="223" spans="1:26" ht="13.5" customHeight="1">
       <c r="A223" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="B223" s="30" t="s">
-        <v>588</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="B223" s="33"/>
       <c r="C223" s="25" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D223" s="24" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E223" s="5"/>
       <c r="F223" s="5"/>
       <c r="G223" s="5"/>
       <c r="H223" s="5"/>
       <c r="I223" s="5" t="s">
-        <v>266</v>
+        <v>592</v>
       </c>
       <c r="J223" s="5"/>
       <c r="K223" s="5"/>
@@ -12933,23 +12991,21 @@
     </row>
     <row r="224" spans="1:26" ht="13.5" customHeight="1">
       <c r="A224" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="B224" s="30" t="s">
-        <v>588</v>
-      </c>
-      <c r="C224" s="25" t="s">
-        <v>586</v>
-      </c>
-      <c r="D224" s="24" t="s">
-        <v>594</v>
-      </c>
-      <c r="E224" s="5"/>
-      <c r="F224" s="5"/>
-      <c r="G224" s="5"/>
-      <c r="H224" s="5"/>
-      <c r="I224" s="5" t="s">
-        <v>615</v>
+        <v>593</v>
+      </c>
+      <c r="B224" s="30"/>
+      <c r="C224" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="D224" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="E224" s="4"/>
+      <c r="F224" s="16"/>
+      <c r="G224" s="16"/>
+      <c r="H224" s="4"/>
+      <c r="I224" s="6" t="s">
+        <v>212</v>
       </c>
       <c r="J224" s="5"/>
       <c r="K224" s="5"/>
@@ -12971,23 +13027,21 @@
     </row>
     <row r="225" spans="1:26" ht="13.5" customHeight="1">
       <c r="A225" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="B225" s="30" t="s">
-        <v>588</v>
-      </c>
-      <c r="C225" s="25" t="s">
-        <v>589</v>
-      </c>
-      <c r="D225" s="24" t="s">
-        <v>591</v>
-      </c>
-      <c r="E225" s="5"/>
-      <c r="F225" s="5"/>
-      <c r="G225" s="5"/>
-      <c r="H225" s="5"/>
-      <c r="I225" s="5" t="s">
-        <v>616</v>
+        <v>593</v>
+      </c>
+      <c r="B225" s="30"/>
+      <c r="C225" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E225" s="4"/>
+      <c r="F225" s="16"/>
+      <c r="G225" s="16"/>
+      <c r="H225" s="4"/>
+      <c r="I225" s="6" t="s">
+        <v>216</v>
       </c>
       <c r="J225" s="5"/>
       <c r="K225" s="5"/>
@@ -13008,15 +13062,25 @@
       <c r="Z225" s="3"/>
     </row>
     <row r="226" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A226" s="5"/>
-      <c r="B226" s="5"/>
-      <c r="C226" s="5"/>
-      <c r="D226" s="5"/>
+      <c r="A226" s="23" t="s">
+        <v>593</v>
+      </c>
+      <c r="B226" s="30" t="s">
+        <v>585</v>
+      </c>
+      <c r="C226" s="25" t="s">
+        <v>582</v>
+      </c>
+      <c r="D226" s="24" t="s">
+        <v>589</v>
+      </c>
       <c r="E226" s="5"/>
       <c r="F226" s="5"/>
       <c r="G226" s="5"/>
       <c r="H226" s="5"/>
-      <c r="I226" s="5"/>
+      <c r="I226" s="5" t="s">
+        <v>626</v>
+      </c>
       <c r="J226" s="5"/>
       <c r="K226" s="5"/>
       <c r="L226" s="5"/>
@@ -13036,15 +13100,25 @@
       <c r="Z226" s="3"/>
     </row>
     <row r="227" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A227" s="5"/>
-      <c r="B227" s="5"/>
-      <c r="C227" s="5"/>
-      <c r="D227" s="5"/>
+      <c r="A227" s="23" t="s">
+        <v>593</v>
+      </c>
+      <c r="B227" s="30" t="s">
+        <v>585</v>
+      </c>
+      <c r="C227" s="25" t="s">
+        <v>583</v>
+      </c>
+      <c r="D227" s="24" t="s">
+        <v>591</v>
+      </c>
       <c r="E227" s="5"/>
       <c r="F227" s="5"/>
       <c r="G227" s="5"/>
       <c r="H227" s="5"/>
-      <c r="I227" s="5"/>
+      <c r="I227" s="5" t="s">
+        <v>612</v>
+      </c>
       <c r="J227" s="5"/>
       <c r="K227" s="5"/>
       <c r="L227" s="5"/>
@@ -13064,15 +13138,25 @@
       <c r="Z227" s="3"/>
     </row>
     <row r="228" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A228" s="5"/>
-      <c r="B228" s="5"/>
-      <c r="C228" s="5"/>
-      <c r="D228" s="5"/>
+      <c r="A228" s="23" t="s">
+        <v>593</v>
+      </c>
+      <c r="B228" s="30" t="s">
+        <v>585</v>
+      </c>
+      <c r="C228" s="25" t="s">
+        <v>586</v>
+      </c>
+      <c r="D228" s="24" t="s">
+        <v>588</v>
+      </c>
       <c r="E228" s="5"/>
       <c r="F228" s="5"/>
       <c r="G228" s="5"/>
       <c r="H228" s="5"/>
-      <c r="I228" s="5"/>
+      <c r="I228" s="5" t="s">
+        <v>613</v>
+      </c>
       <c r="J228" s="5"/>
       <c r="K228" s="5"/>
       <c r="L228" s="5"/>
@@ -18243,9 +18327,90 @@
       <c r="Y412" s="3"/>
       <c r="Z412" s="3"/>
     </row>
-    <row r="413" spans="1:26" ht="15.75" customHeight="1"/>
-    <row r="414" spans="1:26" ht="15.75" customHeight="1"/>
-    <row r="415" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="413" spans="1:26" ht="13.5" customHeight="1">
+      <c r="A413" s="5"/>
+      <c r="B413" s="5"/>
+      <c r="C413" s="5"/>
+      <c r="D413" s="5"/>
+      <c r="E413" s="5"/>
+      <c r="F413" s="5"/>
+      <c r="G413" s="5"/>
+      <c r="H413" s="5"/>
+      <c r="I413" s="5"/>
+      <c r="J413" s="5"/>
+      <c r="K413" s="5"/>
+      <c r="L413" s="5"/>
+      <c r="M413" s="6"/>
+      <c r="N413" s="3"/>
+      <c r="O413" s="3"/>
+      <c r="P413" s="3"/>
+      <c r="Q413" s="3"/>
+      <c r="R413" s="3"/>
+      <c r="S413" s="3"/>
+      <c r="T413" s="3"/>
+      <c r="U413" s="3"/>
+      <c r="V413" s="3"/>
+      <c r="W413" s="3"/>
+      <c r="X413" s="3"/>
+      <c r="Y413" s="3"/>
+      <c r="Z413" s="3"/>
+    </row>
+    <row r="414" spans="1:26" ht="13.5" customHeight="1">
+      <c r="A414" s="5"/>
+      <c r="B414" s="5"/>
+      <c r="C414" s="5"/>
+      <c r="D414" s="5"/>
+      <c r="E414" s="5"/>
+      <c r="F414" s="5"/>
+      <c r="G414" s="5"/>
+      <c r="H414" s="5"/>
+      <c r="I414" s="5"/>
+      <c r="J414" s="5"/>
+      <c r="K414" s="5"/>
+      <c r="L414" s="5"/>
+      <c r="M414" s="6"/>
+      <c r="N414" s="3"/>
+      <c r="O414" s="3"/>
+      <c r="P414" s="3"/>
+      <c r="Q414" s="3"/>
+      <c r="R414" s="3"/>
+      <c r="S414" s="3"/>
+      <c r="T414" s="3"/>
+      <c r="U414" s="3"/>
+      <c r="V414" s="3"/>
+      <c r="W414" s="3"/>
+      <c r="X414" s="3"/>
+      <c r="Y414" s="3"/>
+      <c r="Z414" s="3"/>
+    </row>
+    <row r="415" spans="1:26" ht="13.5" customHeight="1">
+      <c r="A415" s="5"/>
+      <c r="B415" s="5"/>
+      <c r="C415" s="5"/>
+      <c r="D415" s="5"/>
+      <c r="E415" s="5"/>
+      <c r="F415" s="5"/>
+      <c r="G415" s="5"/>
+      <c r="H415" s="5"/>
+      <c r="I415" s="5"/>
+      <c r="J415" s="5"/>
+      <c r="K415" s="5"/>
+      <c r="L415" s="5"/>
+      <c r="M415" s="6"/>
+      <c r="N415" s="3"/>
+      <c r="O415" s="3"/>
+      <c r="P415" s="3"/>
+      <c r="Q415" s="3"/>
+      <c r="R415" s="3"/>
+      <c r="S415" s="3"/>
+      <c r="T415" s="3"/>
+      <c r="U415" s="3"/>
+      <c r="V415" s="3"/>
+      <c r="W415" s="3"/>
+      <c r="X415" s="3"/>
+      <c r="Y415" s="3"/>
+      <c r="Z415" s="3"/>
+    </row>
     <row r="416" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="417" ht="15.75" customHeight="1"/>
     <row r="418" ht="15.75" customHeight="1"/>
@@ -18840,6 +19005,9 @@
     <row r="1007" ht="15.75" customHeight="1"/>
     <row r="1008" ht="15.75" customHeight="1"/>
     <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="13"/>
   <hyperlinks>
@@ -18934,121 +19102,121 @@
     <hyperlink ref="D91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
     <hyperlink ref="D92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
     <hyperlink ref="D93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D94" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D100" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D101" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D102" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D103" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D104" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D105" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="D106" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D107" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D108" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D109" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="D110" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="D111" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="D112" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="D113" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="D114" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="D115" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="D116" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="D117" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="D118" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D119" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="D120" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="D121" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="D122" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D123" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="D124" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="D125" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="D126" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="D127" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="D128" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D129" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="D130" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="D131" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="D132" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="D133" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="D134" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="D135" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="D136" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="D137" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="D138" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="D139" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="D140" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="D141" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="D142" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="D143" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="D144" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="D145" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="D146" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="D147" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="D148" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="D149" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="D150" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="D151" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="D157" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="D158" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="D159" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="D160" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="D161" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="D162" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="D163" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="D164" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="D165" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="D166" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="D167" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="D168" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="D169" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="D175" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="D176" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="D177" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="D178" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D179" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="D180" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D181" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="D182" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D183" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D184" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D185" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="D186" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D187" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="D188" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D189" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="D190" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D191" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D192" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D193" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D194" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D195" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="D196" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D197" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="D198" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D199" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="D200" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D201" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="D202" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D203" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D204" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D207" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D208" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D209" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D210" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D211" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D213" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D214" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D215" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D216" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D217" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D212" r:id="rId198" xr:uid="{FB5BD734-C92C-4DCB-AC83-E67BDA12DFF4}"/>
-    <hyperlink ref="D170" r:id="rId199" xr:uid="{E6F63535-7CB0-4B0A-8A9B-2FF45193FA31}"/>
-    <hyperlink ref="D171" r:id="rId200" xr:uid="{23618A7F-70F1-429D-A989-04E42D5219C5}"/>
-    <hyperlink ref="D173" r:id="rId201" xr:uid="{A61CFECD-5D13-489A-855F-076420E34CFD}"/>
-    <hyperlink ref="D174" r:id="rId202" xr:uid="{6EDE7FBD-C182-4315-93DC-5FE3983DF025}"/>
-    <hyperlink ref="D219" r:id="rId203" xr:uid="{511CA28D-F4D7-4764-8143-3595BDCD915C}"/>
-    <hyperlink ref="D222" r:id="rId204" xr:uid="{F41BCF05-CC73-422D-8893-0B9A8DAAA427}"/>
-    <hyperlink ref="D221" r:id="rId205" xr:uid="{F8CC161C-3698-4455-AE50-3DBD3D45797B}"/>
-    <hyperlink ref="D205" r:id="rId206" xr:uid="{A0788907-6004-4492-830F-55A09B035597}"/>
+    <hyperlink ref="D97" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D103" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D104" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D105" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D106" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D107" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="D108" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="D109" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="D110" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D111" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="D112" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="D113" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="D114" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="D115" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="D116" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="D117" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="D118" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="D119" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="D120" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="D121" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="D122" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="D123" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="D124" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="D125" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="D126" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="D127" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="D128" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="D129" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="D130" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="D131" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="D132" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="D133" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="D134" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="D135" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="D136" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="D137" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="D138" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="D139" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="D140" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="D141" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="D142" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="D143" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="D144" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="D145" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="D146" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="D147" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="D148" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="D149" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="D150" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="D151" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="D152" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="D153" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="D154" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="D160" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="D161" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="D162" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="D163" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="D164" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="D165" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="D166" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="D167" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="D168" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="D169" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="D170" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="D171" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="D172" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="D178" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="D179" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="D180" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="D181" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="D182" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="D183" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="D184" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="D185" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="D186" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="D187" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="D188" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="D189" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="D190" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="D191" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="D192" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="D193" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="D194" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="D195" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="D196" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="D197" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="D198" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="D199" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="D200" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="D201" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="D202" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="D203" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="D204" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="D205" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="D206" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D207" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D210" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D211" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D212" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D213" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D214" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D216" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D217" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D218" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D219" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D220" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D215" r:id="rId198" xr:uid="{FB5BD734-C92C-4DCB-AC83-E67BDA12DFF4}"/>
+    <hyperlink ref="D173" r:id="rId199" xr:uid="{E6F63535-7CB0-4B0A-8A9B-2FF45193FA31}"/>
+    <hyperlink ref="D174" r:id="rId200" xr:uid="{23618A7F-70F1-429D-A989-04E42D5219C5}"/>
+    <hyperlink ref="D176" r:id="rId201" xr:uid="{A61CFECD-5D13-489A-855F-076420E34CFD}"/>
+    <hyperlink ref="D177" r:id="rId202" xr:uid="{6EDE7FBD-C182-4315-93DC-5FE3983DF025}"/>
+    <hyperlink ref="D222" r:id="rId203" xr:uid="{511CA28D-F4D7-4764-8143-3595BDCD915C}"/>
+    <hyperlink ref="D225" r:id="rId204" xr:uid="{F41BCF05-CC73-422D-8893-0B9A8DAAA427}"/>
+    <hyperlink ref="D224" r:id="rId205" xr:uid="{F8CC161C-3698-4455-AE50-3DBD3D45797B}"/>
+    <hyperlink ref="D208" r:id="rId206" xr:uid="{A0788907-6004-4492-830F-55A09B035597}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <headerFooter>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z1009"/>
+  <dimension ref="A1:M229"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2039,11 +2039,8 @@
       <c r="A97" t="str">
         <v>防災</v>
       </c>
-      <c r="B97" t="str">
+      <c r="C97" t="str">
         <v>家屋倒壊等氾濫想定区域（氾濫流・高潮）</v>
-      </c>
-      <c r="C97" t="str">
-        <v>全域</v>
       </c>
       <c r="D97" t="str">
         <v>https://yaizu-smartcity.jp/tiles/yaizu-kaoku-tokai-hanranryu/tiles.json</v>
@@ -4343,7 +4340,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z1009"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M229"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\vm22flo01\DownloadFiles\DX推進課\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C833C6B1-82E7-43B3-8F39-7C8609AD59DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3914772D-068F-45DA-8B4B-B944FA533546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3855,7 +3855,8 @@
     <t>recycle-center</t>
   </si>
   <si>
-    <t>marker-orange</t>
+    <t>marker-green</t>
+    <phoneticPr fontId="13"/>
   </si>
 </sst>
 </file>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dx-user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD99CD1A-38DC-4493-B2FE-D26E6C746316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4D8AA7-EB2B-4DEB-B67A-45FEA262815D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="メニュー構造" sheetId="1" r:id="rId1"/>
@@ -3294,9 +3294,6 @@
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>#ffff00</t>
-  </si>
-  <si>
     <t>#db7093</t>
   </si>
   <si>
@@ -3304,10 +3301,6 @@
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>star</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
     <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%82%AD%E3%83%83%E3%82%BA%E3%83%80%E3%83%B3%E3%82%B9%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
     <phoneticPr fontId="14"/>
   </si>
@@ -3353,6 +3346,13 @@
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E7%AB%8B%E5%85%A5%E7%A6%81%E6%AD%A2%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>#ffa500</t>
+  </si>
+  <si>
+    <t>balloon</t>
     <phoneticPr fontId="14"/>
   </si>
 </sst>
@@ -6521,15 +6521,15 @@
         <v>640</v>
       </c>
       <c r="D101" s="52" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E101" s="45" t="s">
-        <v>15</v>
+        <v>344</v>
       </c>
       <c r="F101" s="46"/>
       <c r="G101" s="46"/>
       <c r="H101" s="45" t="s">
-        <v>15</v>
+        <v>344</v>
       </c>
       <c r="I101" s="47"/>
       <c r="J101" s="46"/>
@@ -6548,14 +6548,14 @@
         <v>644</v>
       </c>
       <c r="D102" s="51" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
       <c r="H102" s="7"/>
       <c r="I102" s="23" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
@@ -6573,15 +6573,15 @@
         <v>642</v>
       </c>
       <c r="D103" s="51" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E103" s="45" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
       <c r="H103" s="45" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="I103" s="23"/>
       <c r="J103" s="4"/>
@@ -6600,7 +6600,7 @@
         <v>641</v>
       </c>
       <c r="D104" s="45" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E104" s="48" t="s">
         <v>655</v>
@@ -6627,7 +6627,7 @@
         <v>646</v>
       </c>
       <c r="D105" s="51" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="4"/>
@@ -6652,7 +6652,7 @@
         <v>643</v>
       </c>
       <c r="D106" s="51" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="4"/>
@@ -6677,7 +6677,7 @@
         <v>650</v>
       </c>
       <c r="D107" s="51" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="4"/>
@@ -6702,7 +6702,7 @@
         <v>648</v>
       </c>
       <c r="D108" s="51" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>321</v>
@@ -6729,15 +6729,15 @@
         <v>647</v>
       </c>
       <c r="D109" s="51" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="4"/>
       <c r="H109" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I109" s="23"/>
       <c r="J109" s="4"/>
@@ -6756,7 +6756,7 @@
         <v>645</v>
       </c>
       <c r="D110" s="51" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E110" s="45" t="s">
         <v>658</v>
@@ -6783,7 +6783,7 @@
         <v>649</v>
       </c>
       <c r="D111" s="51" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E111" s="45" t="s">
         <v>654</v>
@@ -6810,7 +6810,7 @@
         <v>651</v>
       </c>
       <c r="D112" s="51" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E112" s="45" t="s">
         <v>652</v>
@@ -6818,7 +6818,7 @@
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
       <c r="H112" s="45" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I112" s="23"/>
       <c r="J112" s="4"/>
@@ -13769,24 +13769,24 @@
     <hyperlink ref="E112" r:id="rId208" tooltip="dimgray  #696969" display="https://www.colordic.org/colorsample/1001" xr:uid="{230614D3-EFCC-4782-B7F6-D1C1F8CE862A}"/>
     <hyperlink ref="H111" r:id="rId209" tooltip="khaki  #f0e68c" display="https://www.colordic.org/colorsample/1090" xr:uid="{FBAD9EF9-90D3-4E9F-9AAB-9D9CF309EDE3}"/>
     <hyperlink ref="E111" r:id="rId210" tooltip="khaki  #f0e68c" display="https://www.colordic.org/colorsample/1090" xr:uid="{37BB103E-8F35-4A8A-919F-4D852F82FC05}"/>
-    <hyperlink ref="E101" r:id="rId211" tooltip="royalblue  #4169e1" display="https://www.colordic.org/colorsample/1035" xr:uid="{20A05952-E781-4438-8F66-95B16F4DAEE2}"/>
-    <hyperlink ref="H101" r:id="rId212" tooltip="royalblue  #4169e1" display="https://www.colordic.org/colorsample/1035" xr:uid="{A4A36F19-4339-4C7E-9C1E-D72D307ABE0F}"/>
-    <hyperlink ref="H103" r:id="rId213" tooltip="yellow  #ffff00" display="https://www.colordic.org/colorsample/1091" xr:uid="{2D96B419-058A-4C1D-9C9D-BD8B0C35B88A}"/>
-    <hyperlink ref="E103" r:id="rId214" tooltip="yellow  #ffff00" display="https://www.colordic.org/colorsample/1091" xr:uid="{B1CB4729-A89D-4EB3-B373-203E160B7944}"/>
-    <hyperlink ref="H110" r:id="rId215" tooltip="darkorange  #ff8c00" display="https://www.colordic.org/colorsample/1095" xr:uid="{0914380F-8A58-45FD-B9A4-FA9B66AAAA41}"/>
-    <hyperlink ref="E110" r:id="rId216" tooltip="darkorange  #ff8c00" display="https://www.colordic.org/colorsample/1095" xr:uid="{66B0B074-4103-4FC0-9CE0-6C0F3E2CA302}"/>
-    <hyperlink ref="D104" r:id="rId217" xr:uid="{FF3BD575-FE73-48FB-A29B-75817D1BC817}"/>
-    <hyperlink ref="D103" r:id="rId218" xr:uid="{740A7353-663C-40DD-BEC5-D34D2A3DE0B4}"/>
-    <hyperlink ref="D106" r:id="rId219" xr:uid="{A990E518-E683-4550-8AD6-50967E0D7E69}"/>
-    <hyperlink ref="D102" r:id="rId220" xr:uid="{30DD64BF-50A1-416D-B51B-F1EDACD91BA0}"/>
-    <hyperlink ref="D110" r:id="rId221" xr:uid="{3F16F6D6-B4A2-42CF-A13F-17BF09553EAB}"/>
-    <hyperlink ref="D105" r:id="rId222" xr:uid="{5089A3CB-0C3C-4CBE-BEE5-DB2E7E8733F4}"/>
-    <hyperlink ref="D101" r:id="rId223" xr:uid="{2D986A3F-DA2B-4AB0-A387-B05C4587954B}"/>
-    <hyperlink ref="D109" r:id="rId224" xr:uid="{605583FE-206F-474B-AFDE-865FCAFE9308}"/>
-    <hyperlink ref="D108" r:id="rId225" xr:uid="{DD857A5B-11B3-4160-9040-8D1AB025F551}"/>
-    <hyperlink ref="D111" r:id="rId226" xr:uid="{11835446-AC0F-42B4-9B6B-880180A02441}"/>
-    <hyperlink ref="D107" r:id="rId227" xr:uid="{157E47C1-4242-454F-BC61-6571BD7D509F}"/>
-    <hyperlink ref="D112" r:id="rId228" xr:uid="{F40B81F1-F9E3-4149-8568-5E7758BDF06A}"/>
+    <hyperlink ref="H110" r:id="rId211" tooltip="darkorange  #ff8c00" display="https://www.colordic.org/colorsample/1095" xr:uid="{0914380F-8A58-45FD-B9A4-FA9B66AAAA41}"/>
+    <hyperlink ref="E110" r:id="rId212" tooltip="darkorange  #ff8c00" display="https://www.colordic.org/colorsample/1095" xr:uid="{66B0B074-4103-4FC0-9CE0-6C0F3E2CA302}"/>
+    <hyperlink ref="D104" r:id="rId213" xr:uid="{FF3BD575-FE73-48FB-A29B-75817D1BC817}"/>
+    <hyperlink ref="D103" r:id="rId214" xr:uid="{740A7353-663C-40DD-BEC5-D34D2A3DE0B4}"/>
+    <hyperlink ref="D106" r:id="rId215" xr:uid="{A990E518-E683-4550-8AD6-50967E0D7E69}"/>
+    <hyperlink ref="D102" r:id="rId216" xr:uid="{30DD64BF-50A1-416D-B51B-F1EDACD91BA0}"/>
+    <hyperlink ref="D110" r:id="rId217" xr:uid="{3F16F6D6-B4A2-42CF-A13F-17BF09553EAB}"/>
+    <hyperlink ref="D105" r:id="rId218" xr:uid="{5089A3CB-0C3C-4CBE-BEE5-DB2E7E8733F4}"/>
+    <hyperlink ref="D101" r:id="rId219" xr:uid="{2D986A3F-DA2B-4AB0-A387-B05C4587954B}"/>
+    <hyperlink ref="D109" r:id="rId220" xr:uid="{605583FE-206F-474B-AFDE-865FCAFE9308}"/>
+    <hyperlink ref="D108" r:id="rId221" xr:uid="{DD857A5B-11B3-4160-9040-8D1AB025F551}"/>
+    <hyperlink ref="D111" r:id="rId222" xr:uid="{11835446-AC0F-42B4-9B6B-880180A02441}"/>
+    <hyperlink ref="D107" r:id="rId223" xr:uid="{157E47C1-4242-454F-BC61-6571BD7D509F}"/>
+    <hyperlink ref="D112" r:id="rId224" xr:uid="{F40B81F1-F9E3-4149-8568-5E7758BDF06A}"/>
+    <hyperlink ref="H103" r:id="rId225" tooltip="orange  #ffa500" display="https://www.colordic.org/colorsample/1093" xr:uid="{0E50748A-5511-4F08-B700-DECF8CD6293E}"/>
+    <hyperlink ref="E103" r:id="rId226" tooltip="orange  #ffa500" display="https://www.colordic.org/colorsample/1093" xr:uid="{661BF55A-54A8-40C6-B910-46B8500694F4}"/>
+    <hyperlink ref="H101" r:id="rId227" tooltip="deepskyblue  #00bfff" display="https://www.colordic.org/colorsample/1043" xr:uid="{38FC15DB-1677-4C70-B9CE-25256B391F19}"/>
+    <hyperlink ref="E101" r:id="rId228" tooltip="deepskyblue  #00bfff" display="https://www.colordic.org/colorsample/1043" xr:uid="{E285B9B4-6649-417B-BACA-C000D239641A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dx-user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4D8AA7-EB2B-4DEB-B67A-45FEA262815D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176955B8-70C8-43D7-BE9A-B0AF4C6ECB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="683">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -3354,6 +3354,30 @@
   <si>
     <t>balloon</t>
     <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%83%8F%E3%83%BC%E3%83%88%E3%83%95%E3%83%AB%E3%83%BB%E6%9C%AA%E5%B0%B1%E5%AD%A6%E5%85%90%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>ハートフル・未就学児エリア</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%83%8F%E3%83%BC%E3%83%88%E3%83%95%E3%83%AB%E3%82%A8%E3%83%AA%E3%82%A2%E5%88%A9%E7%94%A8%E8%80%85%E5%B0%82%E7%94%A8%E9%A7%90%E8%BB%8A%E5%A0%B4/tiles.json</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>ハートフルエリア利用者専用駐車場</t>
+  </si>
+  <si>
+    <t>#ff8c00</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>#C3D941</t>
+  </si>
+  <si>
+    <t>#65C294</t>
   </si>
 </sst>
 </file>
@@ -3994,7 +4018,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M1028"/>
+  <dimension ref="A1:M1030"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -6764,7 +6788,7 @@
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
       <c r="H110" s="45" t="s">
-        <v>658</v>
+        <v>680</v>
       </c>
       <c r="I110" s="23"/>
       <c r="J110" s="4"/>
@@ -6780,18 +6804,16 @@
         <v>638</v>
       </c>
       <c r="C111" s="22" t="s">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="D111" s="51" t="s">
-        <v>671</v>
-      </c>
-      <c r="E111" s="45" t="s">
-        <v>654</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="E111" s="45"/>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
       <c r="H111" s="45" t="s">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="I111" s="23"/>
       <c r="J111" s="4"/>
@@ -6807,18 +6829,16 @@
         <v>638</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>651</v>
+        <v>679</v>
       </c>
       <c r="D112" s="51" t="s">
-        <v>673</v>
-      </c>
-      <c r="E112" s="45" t="s">
-        <v>652</v>
-      </c>
+        <v>678</v>
+      </c>
+      <c r="E112" s="45"/>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
       <c r="H112" s="45" t="s">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="I112" s="23"/>
       <c r="J112" s="4"/>
@@ -6830,20 +6850,24 @@
       <c r="A113" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B113" s="4"/>
-      <c r="C113" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="E113" s="3"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="8" t="s">
-        <v>228</v>
-      </c>
+      <c r="B113" s="22" t="s">
+        <v>638</v>
+      </c>
+      <c r="C113" s="22" t="s">
+        <v>649</v>
+      </c>
+      <c r="D113" s="51" t="s">
+        <v>671</v>
+      </c>
+      <c r="E113" s="45" t="s">
+        <v>654</v>
+      </c>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="45" t="s">
+        <v>654</v>
+      </c>
+      <c r="I113" s="23"/>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4"/>
@@ -6853,22 +6877,24 @@
       <c r="A114" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B114" s="24" t="s">
-        <v>237</v>
+      <c r="B114" s="22" t="s">
+        <v>638</v>
       </c>
       <c r="C114" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="E114" s="3"/>
-      <c r="F114" s="20"/>
-      <c r="G114" s="20"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="8" t="s">
-        <v>240</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="D114" s="51" t="s">
+        <v>673</v>
+      </c>
+      <c r="E114" s="45" t="s">
+        <v>652</v>
+      </c>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="45" t="s">
+        <v>661</v>
+      </c>
+      <c r="I114" s="23"/>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4"/>
@@ -6878,21 +6904,19 @@
       <c r="A115" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B115" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="C115" s="22" t="s">
-        <v>241</v>
+      <c r="B115" s="4"/>
+      <c r="C115" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="20"/>
       <c r="G115" s="20"/>
       <c r="H115" s="3"/>
       <c r="I115" s="8" t="s">
-        <v>653</v>
+        <v>228</v>
       </c>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
@@ -6907,10 +6931,10 @@
         <v>237</v>
       </c>
       <c r="C116" s="22" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="20"/>
@@ -6932,17 +6956,17 @@
         <v>237</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="D117" s="25" t="s">
-        <v>246</v>
+        <v>241</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>242</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="20"/>
       <c r="G117" s="20"/>
       <c r="H117" s="3"/>
       <c r="I117" s="8" t="s">
-        <v>240</v>
+        <v>653</v>
       </c>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
@@ -6957,10 +6981,10 @@
         <v>237</v>
       </c>
       <c r="C118" s="22" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="20"/>
@@ -6978,21 +7002,21 @@
       <c r="A119" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B119" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D119" s="9" t="s">
-        <v>251</v>
+      <c r="B119" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="C119" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="D119" s="25" t="s">
+        <v>246</v>
       </c>
       <c r="E119" s="3"/>
       <c r="F119" s="20"/>
       <c r="G119" s="20"/>
       <c r="H119" s="3"/>
       <c r="I119" s="8" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
@@ -7003,21 +7027,21 @@
       <c r="A120" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B120" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>253</v>
+      <c r="B120" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="C120" s="22" t="s">
+        <v>247</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E120" s="3"/>
-      <c r="F120" s="4"/>
+      <c r="F120" s="20"/>
       <c r="G120" s="20"/>
       <c r="H120" s="3"/>
       <c r="I120" s="8" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
@@ -7028,19 +7052,21 @@
       <c r="A121" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B121" s="3"/>
+      <c r="B121" s="5" t="s">
+        <v>249</v>
+      </c>
       <c r="C121" s="7" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="20"/>
       <c r="G121" s="20"/>
       <c r="H121" s="3"/>
       <c r="I121" s="8" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
@@ -7051,19 +7077,21 @@
       <c r="A122" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B122" s="3"/>
+      <c r="B122" s="5" t="s">
+        <v>249</v>
+      </c>
       <c r="C122" s="7" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E122" s="3"/>
-      <c r="F122" s="20"/>
+      <c r="F122" s="4"/>
       <c r="G122" s="20"/>
       <c r="H122" s="3"/>
       <c r="I122" s="8" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="J122" s="4"/>
       <c r="K122" s="4"/>
@@ -7076,17 +7104,17 @@
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="7" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="20"/>
       <c r="G123" s="20"/>
       <c r="H123" s="3"/>
       <c r="I123" s="8" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="J123" s="4"/>
       <c r="K123" s="4"/>
@@ -7097,47 +7125,43 @@
       <c r="A124" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B124" s="5" t="s">
-        <v>265</v>
-      </c>
+      <c r="B124" s="3"/>
       <c r="C124" s="7" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E124" s="3"/>
       <c r="F124" s="20"/>
       <c r="G124" s="20"/>
       <c r="H124" s="3"/>
-      <c r="I124" s="10" t="s">
-        <v>268</v>
+      <c r="I124" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
       <c r="L124" s="4"/>
       <c r="M124" s="5"/>
     </row>
-    <row r="125" spans="1:13" ht="15" customHeight="1">
+    <row r="125" spans="1:13" ht="13.5" customHeight="1">
       <c r="A125" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B125" s="5" t="s">
-        <v>265</v>
-      </c>
+      <c r="B125" s="3"/>
       <c r="C125" s="7" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="E125" s="3"/>
-      <c r="F125" s="4"/>
-      <c r="G125" s="4"/>
-      <c r="H125" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="I125" s="4"/>
+      <c r="F125" s="20"/>
+      <c r="G125" s="20"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="8" t="s">
+        <v>264</v>
+      </c>
       <c r="J125" s="4"/>
       <c r="K125" s="4"/>
       <c r="L125" s="4"/>
@@ -7147,41 +7171,45 @@
       <c r="A126" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B126" s="4"/>
+      <c r="B126" s="5" t="s">
+        <v>265</v>
+      </c>
       <c r="C126" s="7" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="20"/>
       <c r="G126" s="20"/>
       <c r="H126" s="3"/>
-      <c r="I126" s="8" t="s">
-        <v>273</v>
+      <c r="I126" s="10" t="s">
+        <v>268</v>
       </c>
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
       <c r="L126" s="4"/>
       <c r="M126" s="5"/>
     </row>
-    <row r="127" spans="1:13" ht="13.5" customHeight="1">
+    <row r="127" spans="1:13" ht="15" customHeight="1">
       <c r="A127" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B127" s="4"/>
+      <c r="B127" s="5" t="s">
+        <v>265</v>
+      </c>
       <c r="C127" s="7" t="s">
-        <v>274</v>
+        <v>232</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4"/>
-      <c r="H127" s="14" t="s">
-        <v>276</v>
+      <c r="H127" s="10" t="s">
+        <v>270</v>
       </c>
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
@@ -7189,50 +7217,46 @@
       <c r="L127" s="4"/>
       <c r="M127" s="5"/>
     </row>
-    <row r="128" spans="1:13" ht="12.75" customHeight="1">
+    <row r="128" spans="1:13" ht="13.5" customHeight="1">
       <c r="A128" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B128" s="7" t="s">
-        <v>277</v>
-      </c>
+      <c r="B128" s="4"/>
       <c r="C128" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="D128" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E128" s="4"/>
-      <c r="F128" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
-      <c r="I128" s="4"/>
+        <v>271</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E128" s="3"/>
+      <c r="F128" s="20"/>
+      <c r="G128" s="20"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="8" t="s">
+        <v>273</v>
+      </c>
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
       <c r="L128" s="4"/>
       <c r="M128" s="5"/>
     </row>
-    <row r="129" spans="1:13" ht="12.75" customHeight="1">
+    <row r="129" spans="1:13" ht="13.5" customHeight="1">
       <c r="A129" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B129" s="7" t="s">
-        <v>277</v>
-      </c>
+      <c r="B129" s="4"/>
       <c r="C129" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="D129" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="E129" s="4"/>
-      <c r="F129" s="8" t="s">
-        <v>283</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E129" s="3"/>
+      <c r="F129" s="4"/>
       <c r="G129" s="4"/>
-      <c r="H129" s="4"/>
+      <c r="H129" s="14" t="s">
+        <v>276</v>
+      </c>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
@@ -7247,14 +7271,14 @@
         <v>277</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="8" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
@@ -7272,14 +7296,14 @@
         <v>277</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D131" s="15" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="8" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
@@ -7297,14 +7321,14 @@
         <v>277</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D132" s="15" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="8" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
@@ -7322,14 +7346,14 @@
         <v>277</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="8" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
@@ -7347,14 +7371,14 @@
         <v>277</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="8" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
@@ -7364,7 +7388,7 @@
       <c r="L134" s="4"/>
       <c r="M134" s="5"/>
     </row>
-    <row r="135" spans="1:13" ht="13.5" customHeight="1">
+    <row r="135" spans="1:13" ht="12.75" customHeight="1">
       <c r="A135" s="7" t="s">
         <v>224</v>
       </c>
@@ -7372,24 +7396,24 @@
         <v>277</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E135" s="4"/>
-      <c r="F135" s="4"/>
+      <c r="F135" s="8" t="s">
+        <v>295</v>
+      </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4"/>
-      <c r="I135" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="J135" s="20"/>
+      <c r="I135" s="4"/>
+      <c r="J135" s="4"/>
       <c r="K135" s="4"/>
       <c r="L135" s="4"/>
       <c r="M135" s="5"/>
     </row>
-    <row r="136" spans="1:13" ht="13.5" customHeight="1">
+    <row r="136" spans="1:13" ht="12.75" customHeight="1">
       <c r="A136" s="7" t="s">
         <v>224</v>
       </c>
@@ -7397,19 +7421,19 @@
         <v>277</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="D136" s="17" t="s">
-        <v>303</v>
+        <v>296</v>
+      </c>
+      <c r="D136" s="15" t="s">
+        <v>297</v>
       </c>
       <c r="E136" s="4"/>
-      <c r="F136" s="4"/>
+      <c r="F136" s="8" t="s">
+        <v>298</v>
+      </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
-      <c r="I136" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="J136" s="20"/>
+      <c r="I136" s="4"/>
+      <c r="J136" s="4"/>
       <c r="K136" s="4"/>
       <c r="L136" s="4"/>
       <c r="M136" s="5"/>
@@ -7421,66 +7445,70 @@
       <c r="B137" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="D137" s="17" t="s">
-        <v>306</v>
+      <c r="C137" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D137" s="15" t="s">
+        <v>300</v>
       </c>
       <c r="E137" s="4"/>
-      <c r="F137" s="26" t="s">
-        <v>307</v>
-      </c>
+      <c r="F137" s="4"/>
       <c r="G137" s="4"/>
-      <c r="H137" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
+      <c r="H137" s="4"/>
+      <c r="I137" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="J137" s="20"/>
       <c r="K137" s="4"/>
       <c r="L137" s="4"/>
       <c r="M137" s="5"/>
     </row>
     <row r="138" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A138" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B138" s="4"/>
-      <c r="C138" s="5" t="s">
-        <v>310</v>
+      <c r="A138" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>302</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
+      <c r="I138" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="J138" s="20"/>
       <c r="K138" s="4"/>
       <c r="L138" s="4"/>
       <c r="M138" s="5"/>
     </row>
     <row r="139" spans="1:13" ht="13.5" customHeight="1">
       <c r="A139" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>312</v>
+        <v>224</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>277</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="E139" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="F139" s="4"/>
+        <v>306</v>
+      </c>
+      <c r="E139" s="4"/>
+      <c r="F139" s="26" t="s">
+        <v>307</v>
+      </c>
       <c r="G139" s="4"/>
-      <c r="H139" s="3"/>
+      <c r="H139" s="26" t="s">
+        <v>308</v>
+      </c>
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
@@ -7488,24 +7516,20 @@
       <c r="M139" s="5"/>
     </row>
     <row r="140" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A140" s="7" t="s">
+      <c r="A140" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B140" s="5" t="s">
-        <v>312</v>
-      </c>
+      <c r="B140" s="4"/>
       <c r="C140" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="E140" s="10" t="s">
-        <v>318</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="E140" s="4"/>
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
-      <c r="H140" s="3"/>
+      <c r="H140" s="4"/>
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
@@ -7520,13 +7544,13 @@
         <v>312</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F141" s="4"/>
       <c r="G141" s="4"/>
@@ -7545,13 +7569,13 @@
         <v>312</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E142" s="10" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F142" s="4"/>
       <c r="G142" s="4"/>
@@ -7570,17 +7594,17 @@
         <v>312</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="E143" s="8" t="s">
-        <v>327</v>
+        <v>320</v>
+      </c>
+      <c r="E143" s="10" t="s">
+        <v>321</v>
       </c>
       <c r="F143" s="4"/>
       <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
+      <c r="H143" s="3"/>
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
       <c r="K143" s="4"/>
@@ -7595,13 +7619,13 @@
         <v>312</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E144" s="10" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F144" s="4"/>
       <c r="G144" s="4"/>
@@ -7620,17 +7644,17 @@
         <v>312</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="E145" s="10" t="s">
-        <v>333</v>
+        <v>326</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>327</v>
       </c>
       <c r="F145" s="4"/>
       <c r="G145" s="4"/>
-      <c r="H145" s="3"/>
+      <c r="H145" s="4"/>
       <c r="I145" s="4"/>
       <c r="J145" s="4"/>
       <c r="K145" s="4"/>
@@ -7645,13 +7669,13 @@
         <v>312</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="E146" s="10" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
@@ -7670,17 +7694,17 @@
         <v>312</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>338</v>
-      </c>
-      <c r="E147" s="8" t="s">
-        <v>339</v>
+        <v>332</v>
+      </c>
+      <c r="E147" s="10" t="s">
+        <v>333</v>
       </c>
       <c r="F147" s="4"/>
       <c r="G147" s="4"/>
-      <c r="H147" s="4"/>
+      <c r="H147" s="3"/>
       <c r="I147" s="4"/>
       <c r="J147" s="4"/>
       <c r="K147" s="4"/>
@@ -7695,17 +7719,17 @@
         <v>312</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>339</v>
+        <v>335</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>336</v>
       </c>
       <c r="F148" s="4"/>
       <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
+      <c r="H148" s="3"/>
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
@@ -7720,13 +7744,13 @@
         <v>312</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F149" s="4"/>
       <c r="G149" s="4"/>
@@ -7745,13 +7769,13 @@
         <v>312</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F150" s="4"/>
       <c r="G150" s="4"/>
@@ -7767,20 +7791,18 @@
         <v>309</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="F151" s="8" t="s">
-        <v>351</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="F151" s="4"/>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
@@ -7794,20 +7816,18 @@
         <v>309</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="F152" s="8" t="s">
-        <v>351</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="F152" s="4"/>
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
@@ -7824,13 +7844,13 @@
         <v>347</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D153" s="17" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>351</v>
@@ -7851,13 +7871,13 @@
         <v>347</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>351</v>
@@ -7878,13 +7898,13 @@
         <v>347</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>351</v>
@@ -7905,13 +7925,13 @@
         <v>347</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D156" s="17" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>351</v>
@@ -7932,16 +7952,16 @@
         <v>347</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
@@ -7959,19 +7979,19 @@
         <v>347</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>373</v>
+        <v>365</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>366</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="G158" s="4"/>
-      <c r="H158" s="3"/>
+      <c r="H158" s="4"/>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
       <c r="K158" s="4"/>
@@ -7986,13 +8006,13 @@
         <v>347</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="D159" s="17" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>370</v>
@@ -8013,19 +8033,19 @@
         <v>347</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D160" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="E160" s="8" t="s">
-        <v>379</v>
+        <v>372</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>373</v>
       </c>
       <c r="F160" s="8" t="s">
         <v>370</v>
       </c>
       <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
+      <c r="H160" s="3"/>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
@@ -8040,13 +8060,13 @@
         <v>347</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D161" s="17" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F161" s="8" t="s">
         <v>370</v>
@@ -8063,17 +8083,17 @@
       <c r="A162" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="B162" s="7" t="s">
+      <c r="B162" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="C162" s="7" t="s">
-        <v>383</v>
+      <c r="C162" s="5" t="s">
+        <v>377</v>
       </c>
       <c r="D162" s="17" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>370</v>
@@ -8081,29 +8101,29 @@
       <c r="G162" s="4"/>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
-      <c r="J162" s="5"/>
+      <c r="J162" s="4"/>
       <c r="K162" s="4"/>
       <c r="L162" s="4"/>
       <c r="M162" s="5"/>
     </row>
     <row r="163" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A163" s="5" t="s">
+      <c r="A163" s="7" t="s">
         <v>309</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>386</v>
+        <v>347</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D163" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="E163" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="F163" s="23" t="s">
-        <v>389</v>
+        <v>381</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>370</v>
       </c>
       <c r="G163" s="4"/>
       <c r="H163" s="4"/>
@@ -8114,74 +8134,82 @@
       <c r="M163" s="5"/>
     </row>
     <row r="164" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A164" s="5" t="s">
+      <c r="A164" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="B164" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>390</v>
+      <c r="B164" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>383</v>
       </c>
       <c r="D164" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="E164" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="F164" s="23" t="s">
-        <v>392</v>
+        <v>384</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>370</v>
       </c>
       <c r="G164" s="4"/>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
-      <c r="J164" s="4"/>
+      <c r="J164" s="5"/>
       <c r="K164" s="4"/>
       <c r="L164" s="4"/>
       <c r="M164" s="5"/>
     </row>
     <row r="165" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A165" s="7" t="s">
+      <c r="A165" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B165" s="4"/>
+      <c r="B165" s="5" t="s">
+        <v>386</v>
+      </c>
       <c r="C165" s="5" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D165" s="17" t="s">
-        <v>394</v>
-      </c>
-      <c r="E165" s="4"/>
-      <c r="F165" s="20"/>
-      <c r="G165" s="20"/>
+        <v>388</v>
+      </c>
+      <c r="E165" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F165" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="G165" s="4"/>
       <c r="H165" s="4"/>
-      <c r="I165" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="J165" s="20"/>
+      <c r="I165" s="4"/>
+      <c r="J165" s="4"/>
       <c r="K165" s="4"/>
       <c r="L165" s="4"/>
       <c r="M165" s="5"/>
     </row>
     <row r="166" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A166" s="7" t="s">
+      <c r="A166" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B166" s="4"/>
+      <c r="B166" s="5" t="s">
+        <v>386</v>
+      </c>
       <c r="C166" s="5" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D166" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="E166" s="4"/>
-      <c r="F166" s="20"/>
-      <c r="G166" s="20"/>
+        <v>391</v>
+      </c>
+      <c r="E166" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="F166" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="G166" s="4"/>
       <c r="H166" s="4"/>
-      <c r="I166" s="26" t="s">
-        <v>397</v>
-      </c>
-      <c r="J166" s="20"/>
+      <c r="I166" s="4"/>
+      <c r="J166" s="4"/>
       <c r="K166" s="4"/>
       <c r="L166" s="4"/>
       <c r="M166" s="5"/>
@@ -8192,68 +8220,64 @@
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="D167" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="F167" s="4"/>
-      <c r="G167" s="4"/>
-      <c r="H167" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="I167" s="4"/>
-      <c r="J167" s="4"/>
+        <v>393</v>
+      </c>
+      <c r="D167" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="E167" s="4"/>
+      <c r="F167" s="20"/>
+      <c r="G167" s="20"/>
+      <c r="H167" s="4"/>
+      <c r="I167" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="J167" s="20"/>
       <c r="K167" s="4"/>
       <c r="L167" s="4"/>
       <c r="M167" s="5"/>
     </row>
     <row r="168" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A168" s="5" t="s">
-        <v>401</v>
+      <c r="A168" s="7" t="s">
+        <v>309</v>
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="D168" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="E168" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="F168" s="4"/>
-      <c r="G168" s="4"/>
-      <c r="H168" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="I168" s="4"/>
-      <c r="J168" s="4"/>
+        <v>395</v>
+      </c>
+      <c r="D168" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="E168" s="4"/>
+      <c r="F168" s="20"/>
+      <c r="G168" s="20"/>
+      <c r="H168" s="4"/>
+      <c r="I168" s="26" t="s">
+        <v>397</v>
+      </c>
+      <c r="J168" s="20"/>
       <c r="K168" s="4"/>
       <c r="L168" s="4"/>
       <c r="M168" s="5"/>
     </row>
     <row r="169" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A169" s="5" t="s">
-        <v>401</v>
+      <c r="A169" s="7" t="s">
+        <v>309</v>
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="5" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E169" s="8" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
       <c r="H169" s="8" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="I169" s="4"/>
       <c r="J169" s="4"/>
@@ -8267,19 +8291,19 @@
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="5" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F170" s="8" t="s">
-        <v>410</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="F170" s="4"/>
       <c r="G170" s="4"/>
-      <c r="H170" s="4"/>
+      <c r="H170" s="8" t="s">
+        <v>404</v>
+      </c>
       <c r="I170" s="4"/>
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
@@ -8288,21 +8312,23 @@
     </row>
     <row r="171" spans="1:13" ht="13.5" customHeight="1">
       <c r="A171" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B171" s="5"/>
+        <v>401</v>
+      </c>
+      <c r="B171" s="4"/>
       <c r="C171" s="5" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="F171" s="4"/>
       <c r="G171" s="4"/>
-      <c r="H171" s="4"/>
+      <c r="H171" s="8" t="s">
+        <v>407</v>
+      </c>
       <c r="I171" s="4"/>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
@@ -8311,22 +8337,20 @@
     </row>
     <row r="172" spans="1:13" ht="13.5" customHeight="1">
       <c r="A172" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>415</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="B172" s="4"/>
       <c r="C172" s="5" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E172" s="8" t="s">
-        <v>418</v>
+        <v>76</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
@@ -8334,40 +8358,30 @@
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
       <c r="L172" s="4"/>
-      <c r="M172" s="8" t="s">
-        <v>419</v>
-      </c>
+      <c r="M172" s="5"/>
     </row>
     <row r="173" spans="1:13" ht="13.5" customHeight="1">
       <c r="A173" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B173" s="5" t="s">
-        <v>415</v>
-      </c>
+      <c r="B173" s="5"/>
       <c r="C173" s="5" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="F173" s="8" t="s">
-        <v>422</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="F173" s="4"/>
       <c r="G173" s="4"/>
-      <c r="H173" s="8" t="s">
-        <v>422</v>
-      </c>
+      <c r="H173" s="4"/>
       <c r="I173" s="4"/>
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
       <c r="L173" s="4"/>
-      <c r="M173" s="8" t="s">
-        <v>419</v>
-      </c>
+      <c r="M173" s="5"/>
     </row>
     <row r="174" spans="1:13" ht="13.5" customHeight="1">
       <c r="A174" s="5" t="s">
@@ -8377,21 +8391,19 @@
         <v>415</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G174" s="4"/>
-      <c r="H174" s="8" t="s">
-        <v>425</v>
-      </c>
+      <c r="H174" s="4"/>
       <c r="I174" s="4"/>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
@@ -8408,20 +8420,20 @@
         <v>415</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="F175" s="8" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="G175" s="4"/>
       <c r="H175" s="8" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
@@ -8431,73 +8443,87 @@
         <v>419</v>
       </c>
     </row>
-    <row r="176" spans="1:13" ht="15" customHeight="1">
+    <row r="176" spans="1:13" ht="13.5" customHeight="1">
       <c r="A176" s="5" t="s">
         <v>411</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="E176" s="4"/>
-      <c r="F176" s="4"/>
+        <v>424</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>425</v>
+      </c>
       <c r="G176" s="4"/>
-      <c r="H176" s="4"/>
-      <c r="I176" s="8" t="s">
-        <v>432</v>
-      </c>
+      <c r="H176" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="I176" s="4"/>
       <c r="J176" s="4"/>
       <c r="K176" s="4"/>
       <c r="L176" s="4"/>
-      <c r="M176" s="5"/>
+      <c r="M176" s="8" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="177" spans="1:13" ht="13.5" customHeight="1">
       <c r="A177" s="5" t="s">
         <v>411</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="E177" s="4"/>
-      <c r="F177" s="4"/>
+        <v>427</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>428</v>
+      </c>
       <c r="G177" s="4"/>
-      <c r="H177" s="4"/>
+      <c r="H177" s="8" t="s">
+        <v>428</v>
+      </c>
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
       <c r="L177" s="4"/>
-      <c r="M177" s="5"/>
-    </row>
-    <row r="178" spans="1:13" ht="13.5" customHeight="1">
+      <c r="M177" s="8" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" ht="15" customHeight="1">
       <c r="A178" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B178" s="7" t="s">
-        <v>435</v>
+      <c r="B178" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
       <c r="H178" s="4"/>
       <c r="I178" s="8" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
@@ -8508,25 +8534,19 @@
       <c r="A179" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B179" s="7" t="s">
-        <v>435</v>
+      <c r="B179" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="E179" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="F179" s="8" t="s">
-        <v>441</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="E179" s="4"/>
+      <c r="F179" s="4"/>
       <c r="G179" s="4"/>
-      <c r="H179" s="8" t="s">
-        <v>441</v>
-      </c>
+      <c r="H179" s="4"/>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
@@ -8541,10 +8561,10 @@
         <v>435</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
@@ -8566,18 +8586,22 @@
         <v>435</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D181" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="E181" s="4"/>
-      <c r="F181" s="4"/>
+        <v>440</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>441</v>
+      </c>
       <c r="G181" s="4"/>
-      <c r="H181" s="4"/>
-      <c r="I181" s="10" t="s">
-        <v>446</v>
-      </c>
+      <c r="H181" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="I181" s="4"/>
       <c r="J181" s="4"/>
       <c r="K181" s="4"/>
       <c r="L181" s="4"/>
@@ -8591,17 +8615,17 @@
         <v>435</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D182" s="15" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
       <c r="H182" s="4"/>
-      <c r="I182" s="10" t="s">
-        <v>446</v>
+      <c r="I182" s="8" t="s">
+        <v>438</v>
       </c>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
@@ -8616,17 +8640,17 @@
         <v>435</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D183" s="15" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
       <c r="H183" s="4"/>
       <c r="I183" s="10" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
@@ -8641,22 +8665,18 @@
         <v>435</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="E184" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="F184" s="8" t="s">
-        <v>454</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="E184" s="4"/>
+      <c r="F184" s="4"/>
       <c r="G184" s="4"/>
-      <c r="H184" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="I184" s="4"/>
+      <c r="H184" s="4"/>
+      <c r="I184" s="10" t="s">
+        <v>446</v>
+      </c>
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
       <c r="L184" s="4"/>
@@ -8666,24 +8686,22 @@
       <c r="A185" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B185" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C185" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="D185" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="E185" s="8" t="s">
-        <v>458</v>
-      </c>
+      <c r="B185" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D185" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
-      <c r="H185" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="I185" s="4"/>
+      <c r="H185" s="4"/>
+      <c r="I185" s="10" t="s">
+        <v>451</v>
+      </c>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
       <c r="L185" s="4"/>
@@ -8693,22 +8711,24 @@
       <c r="A186" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B186" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C186" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="D186" s="17" t="s">
-        <v>460</v>
+      <c r="B186" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D186" s="15" t="s">
+        <v>453</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="F186" s="4"/>
+        <v>454</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>454</v>
+      </c>
       <c r="G186" s="4"/>
       <c r="H186" s="8" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
@@ -8724,18 +8744,18 @@
         <v>455</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D187" s="17" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="F187" s="4"/>
       <c r="G187" s="4"/>
       <c r="H187" s="8" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
@@ -8751,18 +8771,18 @@
         <v>455</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D188" s="17" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="F188" s="4"/>
       <c r="G188" s="4"/>
       <c r="H188" s="8" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
@@ -8774,20 +8794,22 @@
       <c r="A189" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B189" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="C189" s="22" t="s">
-        <v>469</v>
-      </c>
-      <c r="D189" s="27" t="s">
-        <v>470</v>
-      </c>
-      <c r="E189" s="5"/>
+      <c r="B189" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="D189" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>464</v>
+      </c>
       <c r="F189" s="4"/>
       <c r="G189" s="4"/>
       <c r="H189" s="8" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
@@ -8799,20 +8821,22 @@
       <c r="A190" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B190" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="C190" s="22" t="s">
-        <v>472</v>
-      </c>
-      <c r="D190" s="27" t="s">
-        <v>473</v>
-      </c>
-      <c r="E190" s="5"/>
+      <c r="B190" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="D190" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>467</v>
+      </c>
       <c r="F190" s="4"/>
       <c r="G190" s="4"/>
       <c r="H190" s="8" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
@@ -8828,16 +8852,16 @@
         <v>468</v>
       </c>
       <c r="C191" s="22" t="s">
-        <v>475</v>
-      </c>
-      <c r="D191" s="28" t="s">
-        <v>476</v>
+        <v>469</v>
+      </c>
+      <c r="D191" s="27" t="s">
+        <v>470</v>
       </c>
       <c r="E191" s="5"/>
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
       <c r="H191" s="8" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
@@ -8853,16 +8877,16 @@
         <v>468</v>
       </c>
       <c r="C192" s="22" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="D192" s="27" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="E192" s="5"/>
       <c r="F192" s="4"/>
       <c r="G192" s="4"/>
       <c r="H192" s="8" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="I192" s="4"/>
       <c r="J192" s="4"/>
@@ -8878,16 +8902,16 @@
         <v>468</v>
       </c>
       <c r="C193" s="22" t="s">
-        <v>481</v>
-      </c>
-      <c r="D193" s="27" t="s">
-        <v>482</v>
+        <v>475</v>
+      </c>
+      <c r="D193" s="28" t="s">
+        <v>476</v>
       </c>
       <c r="E193" s="5"/>
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
       <c r="H193" s="8" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
@@ -8897,50 +8921,48 @@
     </row>
     <row r="194" spans="1:13" ht="13.5" customHeight="1">
       <c r="A194" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="B194" s="4"/>
-      <c r="C194" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="D194" s="15" t="s">
-        <v>486</v>
-      </c>
-      <c r="E194" s="8" t="s">
-        <v>324</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="B194" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="C194" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="D194" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="E194" s="5"/>
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
-      <c r="H194" s="5"/>
-      <c r="I194" s="23" t="s">
-        <v>487</v>
-      </c>
+      <c r="H194" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="I194" s="4"/>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
       <c r="L194" s="4"/>
       <c r="M194" s="5"/>
     </row>
     <row r="195" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A195" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="B195" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="D195" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="E195" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="F195" s="8" t="s">
-        <v>327</v>
-      </c>
+      <c r="A195" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="B195" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="C195" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="D195" s="27" t="s">
+        <v>482</v>
+      </c>
+      <c r="E195" s="5"/>
+      <c r="F195" s="4"/>
       <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
+      <c r="H195" s="8" t="s">
+        <v>483</v>
+      </c>
       <c r="I195" s="4"/>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
@@ -8948,27 +8970,25 @@
       <c r="M195" s="5"/>
     </row>
     <row r="196" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A196" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="B196" s="5" t="s">
-        <v>489</v>
-      </c>
+      <c r="A196" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="B196" s="4"/>
       <c r="C196" s="5" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="F196" s="8" t="s">
-        <v>327</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="F196" s="4"/>
       <c r="G196" s="4"/>
-      <c r="H196" s="4"/>
-      <c r="I196" s="4"/>
+      <c r="H196" s="5"/>
+      <c r="I196" s="23" t="s">
+        <v>487</v>
+      </c>
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
       <c r="L196" s="4"/>
@@ -8979,22 +8999,22 @@
         <v>488</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>497</v>
-      </c>
-      <c r="E197" s="4"/>
+        <v>491</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>492</v>
+      </c>
       <c r="F197" s="8" t="s">
-        <v>498</v>
+        <v>327</v>
       </c>
       <c r="G197" s="4"/>
-      <c r="H197" s="8" t="s">
-        <v>498</v>
-      </c>
+      <c r="H197" s="4"/>
       <c r="I197" s="4"/>
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
@@ -9006,24 +9026,22 @@
         <v>488</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="E198" s="8" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>502</v>
+        <v>327</v>
       </c>
       <c r="G198" s="4"/>
-      <c r="H198" s="8" t="s">
-        <v>502</v>
-      </c>
+      <c r="H198" s="4"/>
       <c r="I198" s="4"/>
       <c r="J198" s="4"/>
       <c r="K198" s="4"/>
@@ -9035,23 +9053,21 @@
         <v>488</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>504</v>
-      </c>
-      <c r="E199" s="8" t="s">
-        <v>23</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="E199" s="4"/>
       <c r="F199" s="8" t="s">
-        <v>23</v>
+        <v>498</v>
       </c>
       <c r="G199" s="4"/>
       <c r="H199" s="8" t="s">
-        <v>23</v>
+        <v>498</v>
       </c>
       <c r="I199" s="4"/>
       <c r="J199" s="4"/>
@@ -9063,20 +9079,26 @@
       <c r="A200" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="B200" s="4"/>
+      <c r="B200" s="5" t="s">
+        <v>499</v>
+      </c>
       <c r="C200" s="5" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="E200" s="4"/>
-      <c r="F200" s="4"/>
+        <v>501</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>502</v>
+      </c>
       <c r="G200" s="4"/>
-      <c r="H200" s="4"/>
-      <c r="I200" s="8" t="s">
-        <v>507</v>
-      </c>
+      <c r="H200" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="I200" s="4"/>
       <c r="J200" s="4"/>
       <c r="K200" s="4"/>
       <c r="L200" s="4"/>
@@ -9084,24 +9106,28 @@
     </row>
     <row r="201" spans="1:13" ht="13.5" customHeight="1">
       <c r="A201" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B201" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="C201" s="7" t="s">
-        <v>510</v>
+        <v>488</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>503</v>
       </c>
       <c r="D201" s="15" t="s">
-        <v>511</v>
-      </c>
-      <c r="E201" s="4"/>
-      <c r="F201" s="4"/>
+        <v>504</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="G201" s="4"/>
-      <c r="H201" s="4"/>
-      <c r="I201" s="10" t="s">
-        <v>512</v>
-      </c>
+      <c r="H201" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I201" s="4"/>
       <c r="J201" s="4"/>
       <c r="K201" s="4"/>
       <c r="L201" s="4"/>
@@ -9109,26 +9135,22 @@
     </row>
     <row r="202" spans="1:13" ht="13.5" customHeight="1">
       <c r="A202" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B202" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="C202" s="7" t="s">
-        <v>513</v>
+        <v>488</v>
+      </c>
+      <c r="B202" s="4"/>
+      <c r="C202" s="5" t="s">
+        <v>505</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>514</v>
-      </c>
-      <c r="E202" s="8" t="s">
-        <v>324</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="E202" s="4"/>
       <c r="F202" s="4"/>
       <c r="G202" s="4"/>
-      <c r="H202" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="I202" s="4"/>
+      <c r="H202" s="4"/>
+      <c r="I202" s="8" t="s">
+        <v>507</v>
+      </c>
       <c r="J202" s="4"/>
       <c r="K202" s="4"/>
       <c r="L202" s="4"/>
@@ -9139,20 +9161,20 @@
         <v>508</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="D203" s="29" t="s">
-        <v>517</v>
-      </c>
-      <c r="E203" s="30"/>
-      <c r="F203" s="30"/>
-      <c r="G203" s="30"/>
-      <c r="H203" s="31"/>
+        <v>510</v>
+      </c>
+      <c r="D203" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="E203" s="4"/>
+      <c r="F203" s="4"/>
+      <c r="G203" s="4"/>
+      <c r="H203" s="4"/>
       <c r="I203" s="10" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="J203" s="4"/>
       <c r="K203" s="4"/>
@@ -9164,21 +9186,21 @@
         <v>508</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E204" s="8" t="s">
-        <v>521</v>
+        <v>324</v>
       </c>
       <c r="F204" s="4"/>
       <c r="G204" s="4"/>
       <c r="H204" s="8" t="s">
-        <v>521</v>
+        <v>324</v>
       </c>
       <c r="I204" s="4"/>
       <c r="J204" s="4"/>
@@ -9191,21 +9213,21 @@
         <v>508</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="D205" s="15" t="s">
-        <v>524</v>
-      </c>
-      <c r="E205" s="4"/>
-      <c r="F205" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="G205" s="4"/>
-      <c r="H205" s="4"/>
-      <c r="I205" s="4"/>
+        <v>516</v>
+      </c>
+      <c r="D205" s="29" t="s">
+        <v>517</v>
+      </c>
+      <c r="E205" s="30"/>
+      <c r="F205" s="30"/>
+      <c r="G205" s="30"/>
+      <c r="H205" s="31"/>
+      <c r="I205" s="10" t="s">
+        <v>518</v>
+      </c>
       <c r="J205" s="4"/>
       <c r="K205" s="4"/>
       <c r="L205" s="4"/>
@@ -9216,20 +9238,22 @@
         <v>508</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>527</v>
-      </c>
-      <c r="E206" s="4"/>
-      <c r="F206" s="8" t="s">
-        <v>528</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="E206" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="F206" s="4"/>
       <c r="G206" s="4"/>
-      <c r="H206" s="4"/>
+      <c r="H206" s="8" t="s">
+        <v>521</v>
+      </c>
       <c r="I206" s="4"/>
       <c r="J206" s="4"/>
       <c r="K206" s="4"/>
@@ -9244,14 +9268,14 @@
         <v>522</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="8" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
@@ -9269,14 +9293,14 @@
         <v>522</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="8" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
@@ -9294,14 +9318,14 @@
         <v>522</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="8" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
@@ -9319,14 +9343,14 @@
         <v>522</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D210" s="15" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="8" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
@@ -9344,14 +9368,14 @@
         <v>522</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="8" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
@@ -9369,14 +9393,14 @@
         <v>522</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="8" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
@@ -9394,14 +9418,14 @@
         <v>522</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="8" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
@@ -9419,14 +9443,14 @@
         <v>522</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="8" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
@@ -9444,14 +9468,14 @@
         <v>522</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="8" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
@@ -9469,14 +9493,14 @@
         <v>522</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D216" s="15" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="8" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
@@ -9494,14 +9518,14 @@
         <v>522</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="8" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
@@ -9516,21 +9540,21 @@
         <v>508</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>562</v>
+        <v>522</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="E218" s="4"/>
-      <c r="F218" s="4"/>
+      <c r="F218" s="8" t="s">
+        <v>558</v>
+      </c>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
-      <c r="I218" s="23" t="s">
-        <v>565</v>
-      </c>
+      <c r="I218" s="4"/>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
       <c r="L218" s="4"/>
@@ -9541,21 +9565,21 @@
         <v>508</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>566</v>
+        <v>522</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="E219" s="4"/>
-      <c r="F219" s="4"/>
+      <c r="F219" s="8" t="s">
+        <v>561</v>
+      </c>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
-      <c r="I219" s="23" t="s">
-        <v>569</v>
-      </c>
+      <c r="I219" s="4"/>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
       <c r="L219" s="4"/>
@@ -9566,20 +9590,20 @@
         <v>508</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="D220" s="15" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
       <c r="I220" s="23" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
@@ -9594,17 +9618,17 @@
         <v>566</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D221" s="15" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
-      <c r="I221" s="8" t="s">
-        <v>575</v>
+      <c r="I221" s="23" t="s">
+        <v>569</v>
       </c>
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
@@ -9613,21 +9637,23 @@
     </row>
     <row r="222" spans="1:13" ht="13.5" customHeight="1">
       <c r="A222" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="B222" s="4"/>
+        <v>508</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>566</v>
+      </c>
       <c r="C222" s="7" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="D222" s="15" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
       <c r="H222" s="4"/>
-      <c r="I222" s="8" t="s">
-        <v>579</v>
+      <c r="I222" s="23" t="s">
+        <v>572</v>
       </c>
       <c r="J222" s="4"/>
       <c r="K222" s="4"/>
@@ -9636,48 +9662,46 @@
     </row>
     <row r="223" spans="1:13" ht="13.5" customHeight="1">
       <c r="A223" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="B223" s="4"/>
+        <v>508</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>566</v>
+      </c>
       <c r="C223" s="7" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="D223" s="15" t="s">
-        <v>581</v>
-      </c>
-      <c r="E223" s="23" t="s">
-        <v>582</v>
-      </c>
-      <c r="F223" s="23" t="s">
-        <v>582</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="E223" s="4"/>
+      <c r="F223" s="4"/>
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
-      <c r="I223" s="4"/>
+      <c r="I223" s="8" t="s">
+        <v>575</v>
+      </c>
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
       <c r="L223" s="4"/>
       <c r="M223" s="5"/>
     </row>
     <row r="224" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A224" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="B224" s="24" t="s">
-        <v>584</v>
-      </c>
-      <c r="C224" s="32" t="s">
-        <v>584</v>
-      </c>
-      <c r="D224" s="33" t="s">
-        <v>585</v>
+      <c r="A224" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="B224" s="4"/>
+      <c r="C224" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D224" s="15" t="s">
+        <v>578</v>
       </c>
       <c r="E224" s="4"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
-      <c r="I224" s="23" t="s">
-        <v>586</v>
+      <c r="I224" s="8" t="s">
+        <v>579</v>
       </c>
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
@@ -9685,23 +9709,21 @@
       <c r="M224" s="5"/>
     </row>
     <row r="225" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A225" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="B225" s="24" t="s">
-        <v>584</v>
-      </c>
-      <c r="C225" s="32" t="s">
-        <v>587</v>
+      <c r="A225" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="B225" s="4"/>
+      <c r="C225" s="7" t="s">
+        <v>580</v>
       </c>
       <c r="D225" s="15" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="E225" s="23" t="s">
-        <v>270</v>
+        <v>582</v>
       </c>
       <c r="F225" s="23" t="s">
-        <v>270</v>
+        <v>582</v>
       </c>
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
@@ -9715,19 +9737,21 @@
       <c r="A226" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="B226" s="4"/>
-      <c r="C226" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="D226" s="15" t="s">
-        <v>590</v>
+      <c r="B226" s="24" t="s">
+        <v>584</v>
+      </c>
+      <c r="C226" s="32" t="s">
+        <v>584</v>
+      </c>
+      <c r="D226" s="33" t="s">
+        <v>585</v>
       </c>
       <c r="E226" s="4"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
       <c r="H226" s="4"/>
-      <c r="I226" s="8" t="s">
-        <v>591</v>
+      <c r="I226" s="23" t="s">
+        <v>586</v>
       </c>
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
@@ -9738,20 +9762,24 @@
       <c r="A227" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="B227" s="4"/>
-      <c r="C227" s="7" t="s">
-        <v>592</v>
+      <c r="B227" s="24" t="s">
+        <v>584</v>
+      </c>
+      <c r="C227" s="32" t="s">
+        <v>587</v>
       </c>
       <c r="D227" s="15" t="s">
-        <v>593</v>
-      </c>
-      <c r="E227" s="4"/>
-      <c r="F227" s="4"/>
+        <v>588</v>
+      </c>
+      <c r="E227" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="F227" s="23" t="s">
+        <v>270</v>
+      </c>
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
-      <c r="I227" s="10" t="s">
-        <v>594</v>
-      </c>
+      <c r="I227" s="4"/>
       <c r="J227" s="4"/>
       <c r="K227" s="4"/>
       <c r="L227" s="4"/>
@@ -9762,18 +9790,18 @@
         <v>583</v>
       </c>
       <c r="B228" s="4"/>
-      <c r="C228" s="7" t="s">
-        <v>595</v>
+      <c r="C228" s="5" t="s">
+        <v>589</v>
       </c>
       <c r="D228" s="15" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
       <c r="G228" s="4"/>
       <c r="H228" s="4"/>
       <c r="I228" s="8" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="J228" s="4"/>
       <c r="K228" s="4"/>
@@ -9785,18 +9813,18 @@
         <v>583</v>
       </c>
       <c r="B229" s="4"/>
-      <c r="C229" s="5" t="s">
-        <v>598</v>
+      <c r="C229" s="7" t="s">
+        <v>592</v>
       </c>
       <c r="D229" s="15" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="E229" s="4"/>
       <c r="F229" s="4"/>
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
-      <c r="I229" s="8" t="s">
-        <v>600</v>
+      <c r="I229" s="10" t="s">
+        <v>594</v>
       </c>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
@@ -9808,41 +9836,41 @@
         <v>583</v>
       </c>
       <c r="B230" s="4"/>
-      <c r="C230" s="5" t="s">
-        <v>601</v>
+      <c r="C230" s="7" t="s">
+        <v>595</v>
       </c>
       <c r="D230" s="15" t="s">
-        <v>602</v>
-      </c>
-      <c r="E230" s="8" t="s">
-        <v>603</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="E230" s="4"/>
       <c r="F230" s="4"/>
       <c r="G230" s="4"/>
       <c r="H230" s="4"/>
-      <c r="I230" s="4"/>
+      <c r="I230" s="8" t="s">
+        <v>597</v>
+      </c>
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
       <c r="L230" s="4"/>
       <c r="M230" s="5"/>
     </row>
     <row r="231" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A231" s="7" t="s">
-        <v>604</v>
+      <c r="A231" s="5" t="s">
+        <v>583</v>
       </c>
       <c r="B231" s="4"/>
-      <c r="C231" s="22" t="s">
-        <v>605</v>
-      </c>
-      <c r="D231" s="33" t="s">
-        <v>606</v>
-      </c>
-      <c r="E231" s="5"/>
+      <c r="C231" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="D231" s="15" t="s">
+        <v>599</v>
+      </c>
+      <c r="E231" s="4"/>
       <c r="F231" s="4"/>
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
-      <c r="I231" s="23" t="s">
-        <v>607</v>
+      <c r="I231" s="8" t="s">
+        <v>600</v>
       </c>
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
@@ -9850,23 +9878,23 @@
       <c r="M231" s="5"/>
     </row>
     <row r="232" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A232" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="B232" s="3"/>
-      <c r="C232" s="34" t="s">
-        <v>608</v>
-      </c>
-      <c r="D232" s="35" t="s">
-        <v>609</v>
-      </c>
-      <c r="E232" s="3"/>
+      <c r="A232" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="B232" s="4"/>
+      <c r="C232" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="D232" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="E232" s="8" t="s">
+        <v>603</v>
+      </c>
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
-      <c r="H232" s="3"/>
-      <c r="I232" s="8" t="s">
-        <v>610</v>
-      </c>
+      <c r="H232" s="4"/>
+      <c r="I232" s="4"/>
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
       <c r="L232" s="4"/>
@@ -9876,19 +9904,19 @@
       <c r="A233" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="B233" s="3"/>
-      <c r="C233" s="7" t="s">
-        <v>611</v>
-      </c>
-      <c r="D233" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="E233" s="3"/>
+      <c r="B233" s="4"/>
+      <c r="C233" s="22" t="s">
+        <v>605</v>
+      </c>
+      <c r="D233" s="33" t="s">
+        <v>606</v>
+      </c>
+      <c r="E233" s="5"/>
       <c r="F233" s="4"/>
       <c r="G233" s="4"/>
-      <c r="H233" s="3"/>
-      <c r="I233" s="8" t="s">
-        <v>613</v>
+      <c r="H233" s="4"/>
+      <c r="I233" s="23" t="s">
+        <v>607</v>
       </c>
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
@@ -9900,18 +9928,18 @@
         <v>604</v>
       </c>
       <c r="B234" s="3"/>
-      <c r="C234" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="D234" s="9" t="s">
-        <v>615</v>
+      <c r="C234" s="34" t="s">
+        <v>608</v>
+      </c>
+      <c r="D234" s="35" t="s">
+        <v>609</v>
       </c>
       <c r="E234" s="3"/>
       <c r="F234" s="4"/>
       <c r="G234" s="4"/>
       <c r="H234" s="3"/>
       <c r="I234" s="8" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
@@ -9920,21 +9948,21 @@
     </row>
     <row r="235" spans="1:13" ht="13.5" customHeight="1">
       <c r="A235" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="B235" s="4"/>
-      <c r="C235" s="5" t="s">
-        <v>618</v>
-      </c>
-      <c r="D235" s="15" t="s">
-        <v>619</v>
-      </c>
-      <c r="E235" s="4"/>
+        <v>604</v>
+      </c>
+      <c r="B235" s="3"/>
+      <c r="C235" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="D235" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="E235" s="3"/>
       <c r="F235" s="4"/>
       <c r="G235" s="4"/>
-      <c r="H235" s="4"/>
+      <c r="H235" s="3"/>
       <c r="I235" s="8" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="J235" s="4"/>
       <c r="K235" s="4"/>
@@ -9943,21 +9971,21 @@
     </row>
     <row r="236" spans="1:13" ht="13.5" customHeight="1">
       <c r="A236" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="B236" s="4"/>
-      <c r="C236" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="D236" s="36" t="s">
-        <v>622</v>
-      </c>
-      <c r="E236" s="4"/>
+        <v>604</v>
+      </c>
+      <c r="B236" s="3"/>
+      <c r="C236" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="D236" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="E236" s="3"/>
       <c r="F236" s="4"/>
       <c r="G236" s="4"/>
-      <c r="H236" s="4"/>
+      <c r="H236" s="3"/>
       <c r="I236" s="8" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="J236" s="4"/>
       <c r="K236" s="4"/>
@@ -9965,22 +9993,22 @@
       <c r="M236" s="5"/>
     </row>
     <row r="237" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A237" s="37" t="s">
-        <v>624</v>
-      </c>
-      <c r="B237" s="38"/>
-      <c r="C237" s="39" t="s">
-        <v>625</v>
-      </c>
-      <c r="D237" s="40" t="s">
-        <v>626</v>
-      </c>
-      <c r="E237" s="41"/>
+      <c r="A237" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B237" s="4"/>
+      <c r="C237" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="D237" s="15" t="s">
+        <v>619</v>
+      </c>
+      <c r="E237" s="4"/>
       <c r="F237" s="4"/>
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
       <c r="I237" s="8" t="s">
-        <v>273</v>
+        <v>620</v>
       </c>
       <c r="J237" s="4"/>
       <c r="K237" s="4"/>
@@ -9988,22 +10016,22 @@
       <c r="M237" s="5"/>
     </row>
     <row r="238" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A238" s="37" t="s">
-        <v>624</v>
-      </c>
-      <c r="B238" s="24"/>
-      <c r="C238" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="D238" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="E238" s="3"/>
-      <c r="F238" s="20"/>
-      <c r="G238" s="20"/>
-      <c r="H238" s="3"/>
+      <c r="A238" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B238" s="4"/>
+      <c r="C238" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="D238" s="36" t="s">
+        <v>622</v>
+      </c>
+      <c r="E238" s="4"/>
+      <c r="F238" s="4"/>
+      <c r="G238" s="4"/>
+      <c r="H238" s="4"/>
       <c r="I238" s="8" t="s">
-        <v>261</v>
+        <v>623</v>
       </c>
       <c r="J238" s="4"/>
       <c r="K238" s="4"/>
@@ -10014,19 +10042,19 @@
       <c r="A239" s="37" t="s">
         <v>624</v>
       </c>
-      <c r="B239" s="24"/>
+      <c r="B239" s="38"/>
       <c r="C239" s="39" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D239" s="40" t="s">
-        <v>628</v>
-      </c>
-      <c r="E239" s="4"/>
+        <v>626</v>
+      </c>
+      <c r="E239" s="41"/>
       <c r="F239" s="4"/>
       <c r="G239" s="4"/>
       <c r="H239" s="4"/>
-      <c r="I239" s="23" t="s">
-        <v>586</v>
+      <c r="I239" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="J239" s="4"/>
       <c r="K239" s="4"/>
@@ -10037,19 +10065,19 @@
       <c r="A240" s="37" t="s">
         <v>624</v>
       </c>
-      <c r="B240" s="38"/>
-      <c r="C240" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="D240" s="44" t="s">
-        <v>236</v>
+      <c r="B240" s="24"/>
+      <c r="C240" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="D240" s="9" t="s">
+        <v>260</v>
       </c>
       <c r="E240" s="3"/>
       <c r="F240" s="20"/>
       <c r="G240" s="20"/>
       <c r="H240" s="3"/>
       <c r="I240" s="8" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
       <c r="J240" s="4"/>
       <c r="K240" s="4"/>
@@ -10060,19 +10088,19 @@
       <c r="A241" s="37" t="s">
         <v>624</v>
       </c>
-      <c r="B241" s="38"/>
-      <c r="C241" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D241" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E241" s="3"/>
-      <c r="F241" s="20"/>
-      <c r="G241" s="20"/>
-      <c r="H241" s="3"/>
-      <c r="I241" s="8" t="s">
-        <v>252</v>
+      <c r="B241" s="24"/>
+      <c r="C241" s="39" t="s">
+        <v>627</v>
+      </c>
+      <c r="D241" s="40" t="s">
+        <v>628</v>
+      </c>
+      <c r="E241" s="4"/>
+      <c r="F241" s="4"/>
+      <c r="G241" s="4"/>
+      <c r="H241" s="4"/>
+      <c r="I241" s="23" t="s">
+        <v>586</v>
       </c>
       <c r="J241" s="4"/>
       <c r="K241" s="4"/>
@@ -10083,21 +10111,19 @@
       <c r="A242" s="37" t="s">
         <v>624</v>
       </c>
-      <c r="B242" s="38" t="s">
-        <v>629</v>
-      </c>
-      <c r="C242" s="39" t="s">
-        <v>630</v>
-      </c>
-      <c r="D242" s="40" t="s">
-        <v>631</v>
-      </c>
-      <c r="E242" s="4"/>
-      <c r="F242" s="4"/>
-      <c r="G242" s="4"/>
-      <c r="H242" s="4"/>
-      <c r="I242" s="23" t="s">
-        <v>632</v>
+      <c r="B242" s="38"/>
+      <c r="C242" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="D242" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="E242" s="3"/>
+      <c r="F242" s="20"/>
+      <c r="G242" s="20"/>
+      <c r="H242" s="3"/>
+      <c r="I242" s="8" t="s">
+        <v>228</v>
       </c>
       <c r="J242" s="4"/>
       <c r="K242" s="4"/>
@@ -10108,21 +10134,19 @@
       <c r="A243" s="37" t="s">
         <v>624</v>
       </c>
-      <c r="B243" s="38" t="s">
-        <v>629</v>
-      </c>
-      <c r="C243" s="39" t="s">
-        <v>633</v>
-      </c>
-      <c r="D243" s="40" t="s">
-        <v>634</v>
-      </c>
-      <c r="E243" s="4"/>
-      <c r="F243" s="4"/>
-      <c r="G243" s="4"/>
-      <c r="H243" s="4"/>
-      <c r="I243" s="23" t="s">
-        <v>635</v>
+      <c r="B243" s="38"/>
+      <c r="C243" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D243" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E243" s="3"/>
+      <c r="F243" s="20"/>
+      <c r="G243" s="20"/>
+      <c r="H243" s="3"/>
+      <c r="I243" s="8" t="s">
+        <v>252</v>
       </c>
       <c r="J243" s="4"/>
       <c r="K243" s="4"/>
@@ -10137,17 +10161,17 @@
         <v>629</v>
       </c>
       <c r="C244" s="39" t="s">
-        <v>232</v>
+        <v>630</v>
       </c>
       <c r="D244" s="40" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="E244" s="4"/>
       <c r="F244" s="4"/>
       <c r="G244" s="4"/>
       <c r="H244" s="4"/>
       <c r="I244" s="23" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="J244" s="4"/>
       <c r="K244" s="4"/>
@@ -10155,30 +10179,50 @@
       <c r="M244" s="5"/>
     </row>
     <row r="245" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A245" s="4"/>
-      <c r="B245" s="4"/>
-      <c r="C245" s="4"/>
-      <c r="D245" s="4"/>
+      <c r="A245" s="37" t="s">
+        <v>624</v>
+      </c>
+      <c r="B245" s="38" t="s">
+        <v>629</v>
+      </c>
+      <c r="C245" s="39" t="s">
+        <v>633</v>
+      </c>
+      <c r="D245" s="40" t="s">
+        <v>634</v>
+      </c>
       <c r="E245" s="4"/>
       <c r="F245" s="4"/>
       <c r="G245" s="4"/>
       <c r="H245" s="4"/>
-      <c r="I245" s="4"/>
+      <c r="I245" s="23" t="s">
+        <v>635</v>
+      </c>
       <c r="J245" s="4"/>
       <c r="K245" s="4"/>
       <c r="L245" s="4"/>
       <c r="M245" s="5"/>
     </row>
     <row r="246" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A246" s="4"/>
-      <c r="B246" s="4"/>
-      <c r="C246" s="4"/>
-      <c r="D246" s="4"/>
+      <c r="A246" s="37" t="s">
+        <v>624</v>
+      </c>
+      <c r="B246" s="38" t="s">
+        <v>629</v>
+      </c>
+      <c r="C246" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="D246" s="40" t="s">
+        <v>636</v>
+      </c>
       <c r="E246" s="4"/>
       <c r="F246" s="4"/>
       <c r="G246" s="4"/>
       <c r="H246" s="4"/>
-      <c r="I246" s="4"/>
+      <c r="I246" s="23" t="s">
+        <v>637</v>
+      </c>
       <c r="J246" s="4"/>
       <c r="K246" s="4"/>
       <c r="L246" s="4"/>
@@ -12959,23 +13003,51 @@
       <c r="L431" s="4"/>
       <c r="M431" s="5"/>
     </row>
-    <row r="432" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="432" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A432" s="4"/>
+      <c r="B432" s="4"/>
+      <c r="C432" s="4"/>
+      <c r="D432" s="4"/>
+      <c r="E432" s="4"/>
+      <c r="F432" s="4"/>
+      <c r="G432" s="4"/>
+      <c r="H432" s="4"/>
+      <c r="I432" s="4"/>
+      <c r="J432" s="4"/>
+      <c r="K432" s="4"/>
+      <c r="L432" s="4"/>
+      <c r="M432" s="5"/>
+    </row>
+    <row r="433" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A433" s="4"/>
+      <c r="B433" s="4"/>
+      <c r="C433" s="4"/>
+      <c r="D433" s="4"/>
+      <c r="E433" s="4"/>
+      <c r="F433" s="4"/>
+      <c r="G433" s="4"/>
+      <c r="H433" s="4"/>
+      <c r="I433" s="4"/>
+      <c r="J433" s="4"/>
+      <c r="K433" s="4"/>
+      <c r="L433" s="4"/>
+      <c r="M433" s="5"/>
+    </row>
+    <row r="434" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="435" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="436" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="437" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="438" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="439" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="440" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="441" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="442" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="443" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="444" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="445" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="446" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="447" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="448" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="449" ht="15.75" customHeight="1"/>
     <row r="450" ht="15.75" customHeight="1"/>
     <row r="451" ht="15.75" customHeight="1"/>
@@ -13556,6 +13628,8 @@
     <row r="1026" ht="15.75" customHeight="1"/>
     <row r="1027" ht="15.75" customHeight="1"/>
     <row r="1028" ht="15.75" customHeight="1"/>
+    <row r="1029" ht="15.75" customHeight="1"/>
+    <row r="1030" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="14"/>
   <hyperlinks>
@@ -13650,125 +13724,125 @@
     <hyperlink ref="D91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
     <hyperlink ref="D92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
     <hyperlink ref="D93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D113" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D119" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D120" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D121" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D122" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D123" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D124" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="D125" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D126" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D127" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D128" r:id="rId102" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="D129" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="D130" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="D131" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="D132" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="D133" r:id="rId107" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="D134" r:id="rId108" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="D135" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="D136" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="D137" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D138" r:id="rId112" display="https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="D139" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="D140" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="D141" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D142" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="D143" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="D144" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="D145" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="D146" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="D147" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D148" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="D149" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="D150" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="D151" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="D152" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="D153" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="D154" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="D155" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="D156" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="D157" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="D158" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="D159" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="D160" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="D161" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="D162" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="D163" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="D164" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="D165" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="D166" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="D167" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="D168" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="D169" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="D170" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="D176" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="D177" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="D178" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="D179" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="D180" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="D181" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="D182" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="D183" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="D184" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="D185" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="D186" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="D187" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="D188" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="D189" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="D190" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="D192" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="D193" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D194" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="D195" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D196" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="D197" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D198" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D199" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D200" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="D201" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D202" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="D203" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D204" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="D205" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D206" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D207" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D208" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D209" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D210" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="D211" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D212" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="D213" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D214" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="D215" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D216" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="D217" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D218" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D219" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D220" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D221" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D222" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D223" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D224" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D226" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D227" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D228" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D229" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D230" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D231" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="D232" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D233" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="D234" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D235" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="D236" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D238" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="D240" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D241" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="H112" r:id="rId207" tooltip="dimgray  #696969" display="https://www.colordic.org/colorsample/1001" xr:uid="{97FCABF6-F58B-4F9A-834E-9678B6A306CC}"/>
-    <hyperlink ref="E112" r:id="rId208" tooltip="dimgray  #696969" display="https://www.colordic.org/colorsample/1001" xr:uid="{230614D3-EFCC-4782-B7F6-D1C1F8CE862A}"/>
-    <hyperlink ref="H111" r:id="rId209" tooltip="khaki  #f0e68c" display="https://www.colordic.org/colorsample/1090" xr:uid="{FBAD9EF9-90D3-4E9F-9AAB-9D9CF309EDE3}"/>
-    <hyperlink ref="E111" r:id="rId210" tooltip="khaki  #f0e68c" display="https://www.colordic.org/colorsample/1090" xr:uid="{37BB103E-8F35-4A8A-919F-4D852F82FC05}"/>
+    <hyperlink ref="D115" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D121" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D122" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D123" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D124" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D125" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="D126" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="D127" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="D128" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D129" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="D130" r:id="rId102" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="D131" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="D132" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="D133" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="D134" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="D135" r:id="rId107" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="D136" r:id="rId108" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="D137" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="D138" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="D139" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="D140" r:id="rId112" display="https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="D141" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="D142" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="D143" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="D144" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="D145" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="D146" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="D147" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="D148" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="D149" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="D150" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="D151" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="D152" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="D153" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="D154" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="D155" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="D156" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="D157" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="D158" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="D159" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="D160" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="D161" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="D162" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="D163" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="D164" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="D165" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="D166" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="D167" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="D168" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="D169" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="D170" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="D171" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="D172" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="D178" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="D179" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="D180" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="D181" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="D182" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="D183" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="D184" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="D185" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="D186" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="D187" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="D188" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="D189" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="D190" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="D191" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="D192" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="D194" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="D195" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="D196" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="D197" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="D198" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="D199" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="D200" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="D201" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="D202" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="D203" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="D204" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="D205" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="D206" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="D207" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="D208" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="D209" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="D210" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="D211" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="D212" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="D213" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="D214" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="D215" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="D216" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="D217" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="D218" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="D219" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="D220" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D221" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D222" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D223" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D224" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D225" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D226" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D228" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D229" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D230" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D231" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D232" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D233" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="D234" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="D235" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="D236" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="D237" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="D238" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="D240" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="D242" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="D243" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="H114" r:id="rId207" tooltip="dimgray  #696969" display="https://www.colordic.org/colorsample/1001" xr:uid="{97FCABF6-F58B-4F9A-834E-9678B6A306CC}"/>
+    <hyperlink ref="E114" r:id="rId208" tooltip="dimgray  #696969" display="https://www.colordic.org/colorsample/1001" xr:uid="{230614D3-EFCC-4782-B7F6-D1C1F8CE862A}"/>
+    <hyperlink ref="H113" r:id="rId209" tooltip="khaki  #f0e68c" display="https://www.colordic.org/colorsample/1090" xr:uid="{FBAD9EF9-90D3-4E9F-9AAB-9D9CF309EDE3}"/>
+    <hyperlink ref="E113" r:id="rId210" tooltip="khaki  #f0e68c" display="https://www.colordic.org/colorsample/1090" xr:uid="{37BB103E-8F35-4A8A-919F-4D852F82FC05}"/>
     <hyperlink ref="H110" r:id="rId211" tooltip="darkorange  #ff8c00" display="https://www.colordic.org/colorsample/1095" xr:uid="{0914380F-8A58-45FD-B9A4-FA9B66AAAA41}"/>
     <hyperlink ref="E110" r:id="rId212" tooltip="darkorange  #ff8c00" display="https://www.colordic.org/colorsample/1095" xr:uid="{66B0B074-4103-4FC0-9CE0-6C0F3E2CA302}"/>
     <hyperlink ref="D104" r:id="rId213" xr:uid="{FF3BD575-FE73-48FB-A29B-75817D1BC817}"/>
@@ -13780,13 +13854,15 @@
     <hyperlink ref="D101" r:id="rId219" xr:uid="{2D986A3F-DA2B-4AB0-A387-B05C4587954B}"/>
     <hyperlink ref="D109" r:id="rId220" xr:uid="{605583FE-206F-474B-AFDE-865FCAFE9308}"/>
     <hyperlink ref="D108" r:id="rId221" xr:uid="{DD857A5B-11B3-4160-9040-8D1AB025F551}"/>
-    <hyperlink ref="D111" r:id="rId222" xr:uid="{11835446-AC0F-42B4-9B6B-880180A02441}"/>
+    <hyperlink ref="D113" r:id="rId222" xr:uid="{11835446-AC0F-42B4-9B6B-880180A02441}"/>
     <hyperlink ref="D107" r:id="rId223" xr:uid="{157E47C1-4242-454F-BC61-6571BD7D509F}"/>
-    <hyperlink ref="D112" r:id="rId224" xr:uid="{F40B81F1-F9E3-4149-8568-5E7758BDF06A}"/>
+    <hyperlink ref="D114" r:id="rId224" xr:uid="{F40B81F1-F9E3-4149-8568-5E7758BDF06A}"/>
     <hyperlink ref="H103" r:id="rId225" tooltip="orange  #ffa500" display="https://www.colordic.org/colorsample/1093" xr:uid="{0E50748A-5511-4F08-B700-DECF8CD6293E}"/>
     <hyperlink ref="E103" r:id="rId226" tooltip="orange  #ffa500" display="https://www.colordic.org/colorsample/1093" xr:uid="{661BF55A-54A8-40C6-B910-46B8500694F4}"/>
     <hyperlink ref="H101" r:id="rId227" tooltip="deepskyblue  #00bfff" display="https://www.colordic.org/colorsample/1043" xr:uid="{38FC15DB-1677-4C70-B9CE-25256B391F19}"/>
     <hyperlink ref="E101" r:id="rId228" tooltip="deepskyblue  #00bfff" display="https://www.colordic.org/colorsample/1043" xr:uid="{E285B9B4-6649-417B-BACA-C000D239641A}"/>
+    <hyperlink ref="D111" r:id="rId229" xr:uid="{532AD0A0-A331-4708-93CE-A31170BD661C}"/>
+    <hyperlink ref="D112" r:id="rId230" xr:uid="{9495A3C4-6D47-42AF-9398-148988A0C189}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dx-user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176955B8-70C8-43D7-BE9A-B0AF4C6ECB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621D0C2E-847A-41E9-86DC-53C1212CC409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="644">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -1515,9 +1515,6 @@
     <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E5%B9%B3%E6%88%909%E5%B9%B4/tiles.json</t>
   </si>
   <si>
-    <t>高潮浸水想定区域（浸水区域及び浸水深）</t>
-  </si>
-  <si>
     <t>https://yaizu-smartcity.jp/tiles/yaizu-shizuoka-takashio-shinsuishin/{z}/{x}/{y}.png</t>
   </si>
   <si>
@@ -3160,224 +3157,50 @@
     <t>marker-ultramarine</t>
   </si>
   <si>
-    <t>【市政75周年】みなとまつりスペシャルパレード</t>
-  </si>
-  <si>
-    <t>【市政75周年】みなとまつりスペシャルパレード</t>
+    <t>fish</t>
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>みなとまつり会場</t>
-    <rPh sb="6" eb="8">
-      <t>カイジョウ</t>
+    <t>https://yaizu-smartcity.jp/tiles/%E8%A6%81%E9%85%8D%E6%85%AE%E8%80%85%E5%88%A9%E7%94%A8%E6%96%BD%E8%A8%AD/tiles.json</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>避難施設</t>
+    <rPh sb="0" eb="4">
+      <t>ヒナンシセツ</t>
     </rPh>
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>キッズダンスエリア</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>ダッフィーバス展示</t>
-    <rPh sb="7" eb="9">
-      <t>テンジ</t>
+    <t>要配慮者利用施設</t>
+    <rPh sb="0" eb="1">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ハイリョ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シセツ</t>
     </rPh>
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>トイレ</t>
+    <t>防災</t>
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>パレードスタート・ゴール</t>
+    <t>elderly-welfare-facility</t>
     <phoneticPr fontId="14"/>
   </si>
   <si>
-    <t>パレード出演者観覧エリア</t>
-    <rPh sb="4" eb="7">
-      <t>シュツエンシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カンラン</t>
-    </rPh>
+    <t>高潮浸水想定区域（浸水区域及び浸水深）</t>
     <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>ベビーカー置き場・授乳室</t>
-    <rPh sb="5" eb="6">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>ジュニュウシツ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>一般座り観覧エリア</t>
-    <rPh sb="0" eb="2">
-      <t>イッパン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>スワ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カンラン</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>一般観覧エリア</t>
-    <rPh sb="0" eb="2">
-      <t>イッパン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カンラン</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>報道エリア</t>
-    <rPh sb="0" eb="2">
-      <t>ホウドウ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>案内所・運営本部</t>
-    <rPh sb="0" eb="3">
-      <t>アンナイジョ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ウンエイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ホンブ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>立入禁止エリア</t>
-    <rPh sb="0" eb="4">
-      <t>タチイリキンシ</t>
-    </rPh>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>#696969</t>
-  </si>
-  <si>
-    <t>fish</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>#f0e68c</t>
-  </si>
-  <si>
-    <t>#ff69b4</t>
-  </si>
-  <si>
-    <t>baby</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>outdoor</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>#ff8c00</t>
-  </si>
-  <si>
-    <t>public-toilets</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>#db7093</t>
-  </si>
-  <si>
-    <t>#696969</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%82%AD%E3%83%83%E3%82%BA%E3%83%80%E3%83%B3%E3%82%B9%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%83%80%E3%83%83%E3%83%95%E3%82%A3%E3%83%BC%E3%83%90%E3%82%B9%E5%B1%95%E7%A4%BA%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%83%88%E3%82%A4%E3%83%AC/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89%E3%82%B9%E3%82%BF%E3%83%BC%E3%83%88%E3%83%BB%E3%82%B4%E3%83%BC%E3%83%AB%E5%9C%B0%E7%82%B9/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89%E5%87%BA%E6%BC%94%E8%80%85%E8%A6%B3%E8%A6%A7%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%83%99%E3%83%93%E3%83%BC%E3%82%AB%E3%83%BC%E7%BD%AE%E3%81%8D%E5%A0%B4%E3%83%BB%E6%8E%88%E4%B9%B3%E5%AE%A4/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%81%BF%E3%81%AA%E3%81%A8%E3%81%BE%E3%81%A4%E3%82%8A%E4%BC%9A%E5%A0%B4/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E4%B8%80%E8%88%AC%E5%BA%A7%E3%82%8A%E8%A6%B3%E8%A6%A7%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E4%B8%80%E8%88%AC%E8%A6%B3%E8%A6%A7%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E5%A0%B1%E9%81%93%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E6%A1%88%E5%86%85%E6%89%80%E3%83%BB%E9%81%8B%E5%96%B6%E6%9C%AC%E9%83%A8/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E7%AB%8B%E5%85%A5%E7%A6%81%E6%AD%A2%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>#ffa500</t>
-  </si>
-  <si>
-    <t>balloon</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%83%8F%E3%83%BC%E3%83%88%E3%83%95%E3%83%AB%E3%83%BB%E6%9C%AA%E5%B0%B1%E5%AD%A6%E5%85%90%E3%82%A8%E3%83%AA%E3%82%A2/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>ハートフル・未就学児エリア</t>
-  </si>
-  <si>
-    <t>https://yaizu-smartcity.jp/tiles/75%E5%91%A8%E5%B9%B4%E3%83%91%E3%83%AC%E3%83%BC%E3%83%89_%E3%83%8F%E3%83%BC%E3%83%88%E3%83%95%E3%83%AB%E3%82%A8%E3%83%AA%E3%82%A2%E5%88%A9%E7%94%A8%E8%80%85%E5%B0%82%E7%94%A8%E9%A7%90%E8%BB%8A%E5%A0%B4/tiles.json</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>ハートフルエリア利用者専用駐車場</t>
-  </si>
-  <si>
-    <t>#ff8c00</t>
-    <phoneticPr fontId="14"/>
-  </si>
-  <si>
-    <t>#C3D941</t>
-  </si>
-  <si>
-    <t>#65C294</t>
   </si>
 </sst>
 </file>
@@ -3633,7 +3456,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3737,22 +3560,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -4018,7 +3826,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M1030"/>
+  <dimension ref="A1:M1017"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -4099,7 +3907,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>17</v>
+        <v>639</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>18</v>
@@ -4124,7 +3932,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>17</v>
+        <v>639</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>21</v>
@@ -4149,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>17</v>
+        <v>639</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>24</v>
@@ -4421,24 +4229,24 @@
     </row>
     <row r="16" spans="1:13" ht="13.5" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>16</v>
+        <v>641</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>638</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="12" t="s">
+        <v>642</v>
+      </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -4452,14 +4260,14 @@
         <v>57</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -4477,14 +4285,14 @@
         <v>57</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -4499,21 +4307,21 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="F19" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
-      <c r="I19" s="8" t="s">
-        <v>70</v>
-      </c>
+      <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -4527,17 +4335,17 @@
         <v>67</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -4548,24 +4356,22 @@
       <c r="A21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="C21" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>77</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -4575,19 +4381,23 @@
       <c r="A22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>79</v>
+      <c r="B22" s="3"/>
+      <c r="C22" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="G22" s="4"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
@@ -4602,10 +4412,10 @@
         <v>78</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="4"/>
@@ -4621,19 +4431,19 @@
       <c r="A24" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="4"/>
+      <c r="B24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="3"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="H24" s="3"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
@@ -4645,22 +4455,18 @@
         <v>16</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>87</v>
+        <v>83</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>89</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="8" t="s">
-        <v>89</v>
-      </c>
+      <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -4675,18 +4481,18 @@
         <v>86</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -4702,18 +4508,18 @@
         <v>86</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -4729,18 +4535,18 @@
         <v>86</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -4756,18 +4562,18 @@
         <v>86</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
@@ -4780,18 +4586,22 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>103</v>
+        <v>86</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>99</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>101</v>
+      </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="H30" s="8" t="s">
+        <v>101</v>
+      </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
@@ -4806,10 +4616,10 @@
         <v>102</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -4829,10 +4639,10 @@
         <v>102</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
@@ -4852,10 +4662,10 @@
         <v>102</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -4875,10 +4685,10 @@
         <v>102</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -4898,10 +4708,10 @@
         <v>102</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -4921,10 +4731,10 @@
         <v>102</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -4944,10 +4754,10 @@
         <v>102</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -4967,10 +4777,10 @@
         <v>102</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -4990,10 +4800,10 @@
         <v>102</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -5013,10 +4823,10 @@
         <v>102</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -5036,10 +4846,10 @@
         <v>102</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -5059,10 +4869,10 @@
         <v>102</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -5082,10 +4892,10 @@
         <v>102</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -5105,10 +4915,10 @@
         <v>102</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -5128,10 +4938,10 @@
         <v>102</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -5151,10 +4961,10 @@
         <v>102</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>136</v>
+        <v>133</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>134</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -5171,13 +4981,13 @@
         <v>16</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>138</v>
+        <v>135</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>136</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -5197,10 +5007,10 @@
         <v>137</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -5220,10 +5030,10 @@
         <v>137</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -5243,10 +5053,10 @@
         <v>137</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
@@ -5266,10 +5076,10 @@
         <v>137</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
@@ -5289,10 +5099,10 @@
         <v>137</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
@@ -5312,10 +5122,10 @@
         <v>137</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
@@ -5332,13 +5142,13 @@
         <v>16</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
@@ -5358,10 +5168,10 @@
         <v>145</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
@@ -5381,10 +5191,10 @@
         <v>145</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
@@ -5404,10 +5214,10 @@
         <v>145</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
@@ -5427,10 +5237,10 @@
         <v>145</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
@@ -5450,10 +5260,10 @@
         <v>145</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
@@ -5473,10 +5283,10 @@
         <v>145</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
@@ -5496,10 +5306,10 @@
         <v>145</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
@@ -5519,10 +5329,10 @@
         <v>145</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
@@ -5539,22 +5349,18 @@
         <v>16</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>157</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
-      <c r="H63" s="8" t="s">
-        <v>157</v>
-      </c>
+      <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
@@ -5566,22 +5372,22 @@
         <v>16</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>161</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="F64" s="4"/>
       <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
+      <c r="H64" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
@@ -5596,10 +5402,10 @@
         <v>158</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>160</v>
@@ -5623,10 +5429,10 @@
         <v>158</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>160</v>
@@ -5650,10 +5456,10 @@
         <v>158</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>160</v>
@@ -5677,10 +5483,10 @@
         <v>158</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>160</v>
@@ -5704,10 +5510,10 @@
         <v>158</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>160</v>
@@ -5731,10 +5537,10 @@
         <v>158</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>160</v>
@@ -5758,10 +5564,10 @@
         <v>158</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>160</v>
@@ -5777,20 +5583,24 @@
       <c r="L71" s="4"/>
       <c r="M71" s="5"/>
     </row>
-    <row r="72" spans="1:13" ht="14.25" customHeight="1">
+    <row r="72" spans="1:13" ht="13.5" customHeight="1">
       <c r="A72" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B72" s="4"/>
+      <c r="B72" s="5" t="s">
+        <v>158</v>
+      </c>
       <c r="C72" s="5" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="E72" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>160</v>
+      </c>
       <c r="F72" s="8" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
@@ -5800,27 +5610,23 @@
       <c r="L72" s="4"/>
       <c r="M72" s="5"/>
     </row>
-    <row r="73" spans="1:13" ht="13.5" customHeight="1">
+    <row r="73" spans="1:13" ht="14.25" customHeight="1">
       <c r="A73" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>171</v>
-      </c>
+      <c r="B73" s="4"/>
       <c r="C73" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" s="4"/>
+        <v>170</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="G73" s="4"/>
-      <c r="H73" s="10" t="s">
-        <v>15</v>
-      </c>
+      <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
@@ -5835,10 +5641,10 @@
         <v>171</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>15</v>
@@ -5862,10 +5668,10 @@
         <v>171</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>15</v>
@@ -5889,10 +5695,10 @@
         <v>171</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>15</v>
@@ -5916,10 +5722,10 @@
         <v>171</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>15</v>
@@ -5943,24 +5749,24 @@
         <v>171</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
       <c r="H78" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I78" s="20"/>
-      <c r="J78" s="20"/>
-      <c r="K78" s="20"/>
-      <c r="L78" s="20"/>
-      <c r="M78" s="21"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="5"/>
     </row>
     <row r="79" spans="1:13" ht="13.5" customHeight="1">
       <c r="A79" s="7" t="s">
@@ -5970,24 +5776,24 @@
         <v>171</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
       <c r="H79" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="5"/>
+      <c r="I79" s="20"/>
+      <c r="J79" s="20"/>
+      <c r="K79" s="20"/>
+      <c r="L79" s="20"/>
+      <c r="M79" s="21"/>
     </row>
     <row r="80" spans="1:13" ht="13.5" customHeight="1">
       <c r="A80" s="7" t="s">
@@ -5997,10 +5803,10 @@
         <v>171</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>15</v>
@@ -6024,10 +5830,10 @@
         <v>171</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>15</v>
@@ -6051,10 +5857,10 @@
         <v>171</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>15</v>
@@ -6078,10 +5884,10 @@
         <v>171</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>15</v>
@@ -6105,10 +5911,10 @@
         <v>171</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>15</v>
@@ -6132,10 +5938,10 @@
         <v>171</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>15</v>
@@ -6159,10 +5965,10 @@
         <v>171</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>15</v>
@@ -6186,10 +5992,10 @@
         <v>171</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>15</v>
@@ -6213,10 +6019,10 @@
         <v>171</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>15</v>
@@ -6240,10 +6046,10 @@
         <v>171</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>15</v>
@@ -6267,24 +6073,24 @@
         <v>171</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F90" s="20"/>
-      <c r="G90" s="20"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
       <c r="H90" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I90" s="20"/>
-      <c r="J90" s="20"/>
-      <c r="K90" s="20"/>
-      <c r="L90" s="20"/>
-      <c r="M90" s="21"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="5"/>
     </row>
     <row r="91" spans="1:13" ht="13.5" customHeight="1">
       <c r="A91" s="7" t="s">
@@ -6294,24 +6100,24 @@
         <v>171</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
+      <c r="F91" s="20"/>
+      <c r="G91" s="20"/>
       <c r="H91" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="5"/>
+      <c r="I91" s="20"/>
+      <c r="J91" s="20"/>
+      <c r="K91" s="20"/>
+      <c r="L91" s="20"/>
+      <c r="M91" s="21"/>
     </row>
     <row r="92" spans="1:13" ht="13.5" customHeight="1">
       <c r="A92" s="7" t="s">
@@ -6321,24 +6127,24 @@
         <v>171</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F92" s="20"/>
-      <c r="G92" s="20"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
       <c r="H92" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="4"/>
       <c r="J92" s="4"/>
-      <c r="K92" s="20"/>
-      <c r="L92" s="20"/>
-      <c r="M92" s="21"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="5"/>
     </row>
     <row r="93" spans="1:13" ht="13.5" customHeight="1">
       <c r="A93" s="7" t="s">
@@ -6348,40 +6154,46 @@
         <v>171</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
+      <c r="F93" s="20"/>
+      <c r="G93" s="20"/>
       <c r="H93" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="5"/>
+      <c r="K93" s="20"/>
+      <c r="L93" s="20"/>
+      <c r="M93" s="21"/>
     </row>
     <row r="94" spans="1:13" ht="13.5" customHeight="1">
       <c r="A94" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B94" s="5"/>
+      <c r="B94" s="5" t="s">
+        <v>171</v>
+      </c>
       <c r="C94" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="E94" s="7"/>
+        <v>213</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
-      <c r="H94" s="7"/>
+      <c r="H94" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
@@ -6394,10 +6206,10 @@
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="5" t="s">
-        <v>216</v>
+        <v>643</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="4"/>
@@ -6415,19 +6227,15 @@
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>220</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="E96" s="7"/>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
-      <c r="H96" s="10" t="s">
-        <v>220</v>
-      </c>
+      <c r="H96" s="7"/>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
@@ -6440,18 +6248,18 @@
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
       <c r="H97" s="10" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
@@ -6461,24 +6269,24 @@
     </row>
     <row r="98" spans="1:13" ht="13.5" customHeight="1">
       <c r="A98" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B98" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="C98" s="22" t="s">
-        <v>226</v>
+        <v>16</v>
+      </c>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="E98" s="7"/>
+        <v>221</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>222</v>
+      </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
-      <c r="H98" s="7"/>
-      <c r="I98" s="23" t="s">
-        <v>228</v>
-      </c>
+      <c r="H98" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="I98" s="4"/>
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
@@ -6486,23 +6294,23 @@
     </row>
     <row r="99" spans="1:13" ht="13.5" customHeight="1">
       <c r="A99" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B99" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="B99" s="22" t="s">
+      <c r="C99" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="C99" s="22" t="s">
-        <v>229</v>
-      </c>
       <c r="D99" s="17" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
       <c r="H99" s="7"/>
       <c r="I99" s="23" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
@@ -6511,23 +6319,23 @@
     </row>
     <row r="100" spans="1:13" ht="13.5" customHeight="1">
       <c r="A100" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B100" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="B100" s="22" t="s">
-        <v>225</v>
-      </c>
       <c r="C100" s="22" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E100" s="7"/>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
       <c r="H100" s="7"/>
       <c r="I100" s="23" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
@@ -6536,50 +6344,46 @@
     </row>
     <row r="101" spans="1:13" ht="13.5" customHeight="1">
       <c r="A101" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="B101" s="22" t="s">
-        <v>639</v>
-      </c>
       <c r="C101" s="22" t="s">
-        <v>640</v>
-      </c>
-      <c r="D101" s="52" t="s">
-        <v>668</v>
-      </c>
-      <c r="E101" s="45" t="s">
-        <v>344</v>
-      </c>
-      <c r="F101" s="46"/>
-      <c r="G101" s="46"/>
-      <c r="H101" s="45" t="s">
-        <v>344</v>
-      </c>
-      <c r="I101" s="47"/>
-      <c r="J101" s="46"/>
+        <v>231</v>
+      </c>
+      <c r="D101" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="E101" s="7"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="J101" s="4"/>
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
       <c r="M101" s="5"/>
     </row>
     <row r="102" spans="1:13" ht="13.5" customHeight="1">
       <c r="A102" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B102" s="22" t="s">
-        <v>638</v>
-      </c>
-      <c r="C102" s="22" t="s">
-        <v>644</v>
-      </c>
-      <c r="D102" s="51" t="s">
-        <v>665</v>
-      </c>
-      <c r="E102" s="7"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="7"/>
-      <c r="I102" s="23" t="s">
-        <v>675</v>
+        <v>223</v>
+      </c>
+      <c r="B102" s="4"/>
+      <c r="C102" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E102" s="3"/>
+      <c r="F102" s="20"/>
+      <c r="G102" s="20"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="8" t="s">
+        <v>227</v>
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
@@ -6588,26 +6392,24 @@
     </row>
     <row r="103" spans="1:13" ht="13.5" customHeight="1">
       <c r="A103" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B103" s="22" t="s">
-        <v>638</v>
+        <v>223</v>
+      </c>
+      <c r="B103" s="24" t="s">
+        <v>236</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>642</v>
-      </c>
-      <c r="D103" s="51" t="s">
-        <v>663</v>
-      </c>
-      <c r="E103" s="45" t="s">
-        <v>674</v>
-      </c>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="45" t="s">
-        <v>674</v>
-      </c>
-      <c r="I103" s="23"/>
+        <v>237</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="E103" s="3"/>
+      <c r="F103" s="20"/>
+      <c r="G103" s="20"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
@@ -6615,50 +6417,48 @@
     </row>
     <row r="104" spans="1:13" ht="13.5" customHeight="1">
       <c r="A104" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B104" s="22" t="s">
-        <v>639</v>
+        <v>223</v>
+      </c>
+      <c r="B104" s="24" t="s">
+        <v>236</v>
       </c>
       <c r="C104" s="22" t="s">
-        <v>641</v>
-      </c>
-      <c r="D104" s="45" t="s">
-        <v>662</v>
-      </c>
-      <c r="E104" s="48" t="s">
-        <v>655</v>
-      </c>
-      <c r="F104" s="49"/>
-      <c r="G104" s="49"/>
-      <c r="H104" s="48" t="s">
-        <v>655</v>
-      </c>
-      <c r="I104" s="50"/>
-      <c r="J104" s="49"/>
+        <v>240</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E104" s="3"/>
+      <c r="F104" s="20"/>
+      <c r="G104" s="20"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="J104" s="4"/>
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
       <c r="M104" s="5"/>
     </row>
     <row r="105" spans="1:13" ht="13.5" customHeight="1">
       <c r="A105" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B105" s="22" t="s">
-        <v>638</v>
+        <v>223</v>
+      </c>
+      <c r="B105" s="24" t="s">
+        <v>236</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>646</v>
-      </c>
-      <c r="D105" s="51" t="s">
-        <v>667</v>
-      </c>
-      <c r="E105" s="7"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="7"/>
-      <c r="I105" s="23" t="s">
-        <v>656</v>
+        <v>242</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E105" s="3"/>
+      <c r="F105" s="20"/>
+      <c r="G105" s="20"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="8" t="s">
+        <v>239</v>
       </c>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
@@ -6667,23 +6467,23 @@
     </row>
     <row r="106" spans="1:13" ht="13.5" customHeight="1">
       <c r="A106" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B106" s="22" t="s">
-        <v>638</v>
+        <v>223</v>
+      </c>
+      <c r="B106" s="24" t="s">
+        <v>236</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>643</v>
-      </c>
-      <c r="D106" s="51" t="s">
-        <v>664</v>
-      </c>
-      <c r="E106" s="7"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="7"/>
-      <c r="I106" s="23" t="s">
-        <v>659</v>
+        <v>244</v>
+      </c>
+      <c r="D106" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="E106" s="3"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="20"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="8" t="s">
+        <v>239</v>
       </c>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
@@ -6692,23 +6492,23 @@
     </row>
     <row r="107" spans="1:13" ht="13.5" customHeight="1">
       <c r="A107" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B107" s="22" t="s">
-        <v>638</v>
+        <v>223</v>
+      </c>
+      <c r="B107" s="24" t="s">
+        <v>236</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>650</v>
-      </c>
-      <c r="D107" s="51" t="s">
-        <v>672</v>
-      </c>
-      <c r="E107" s="7"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="23" t="s">
-        <v>657</v>
+        <v>246</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E107" s="3"/>
+      <c r="F107" s="20"/>
+      <c r="G107" s="20"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="8" t="s">
+        <v>239</v>
       </c>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
@@ -6717,26 +6517,24 @@
     </row>
     <row r="108" spans="1:13" ht="13.5" customHeight="1">
       <c r="A108" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B108" s="22" t="s">
-        <v>638</v>
-      </c>
-      <c r="C108" s="22" t="s">
-        <v>648</v>
-      </c>
-      <c r="D108" s="51" t="s">
-        <v>670</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="I108" s="7"/>
+        <v>223</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E108" s="3"/>
+      <c r="F108" s="20"/>
+      <c r="G108" s="20"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="8" t="s">
+        <v>251</v>
+      </c>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
@@ -6744,26 +6542,24 @@
     </row>
     <row r="109" spans="1:13" ht="13.5" customHeight="1">
       <c r="A109" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B109" s="22" t="s">
-        <v>638</v>
-      </c>
-      <c r="C109" s="22" t="s">
-        <v>647</v>
-      </c>
-      <c r="D109" s="51" t="s">
-        <v>669</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>660</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E109" s="3"/>
       <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="7" t="s">
-        <v>660</v>
-      </c>
-      <c r="I109" s="23"/>
+      <c r="G109" s="20"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="8" t="s">
+        <v>254</v>
+      </c>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
@@ -6771,26 +6567,22 @@
     </row>
     <row r="110" spans="1:13" ht="13.5" customHeight="1">
       <c r="A110" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B110" s="22" t="s">
-        <v>638</v>
-      </c>
-      <c r="C110" s="22" t="s">
-        <v>645</v>
-      </c>
-      <c r="D110" s="51" t="s">
-        <v>666</v>
-      </c>
-      <c r="E110" s="45" t="s">
-        <v>658</v>
-      </c>
-      <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
-      <c r="H110" s="45" t="s">
-        <v>680</v>
-      </c>
-      <c r="I110" s="23"/>
+        <v>223</v>
+      </c>
+      <c r="B110" s="3"/>
+      <c r="C110" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E110" s="3"/>
+      <c r="F110" s="20"/>
+      <c r="G110" s="20"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="8" t="s">
+        <v>257</v>
+      </c>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
@@ -6798,24 +6590,22 @@
     </row>
     <row r="111" spans="1:13" ht="13.5" customHeight="1">
       <c r="A111" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B111" s="22" t="s">
-        <v>638</v>
-      </c>
-      <c r="C111" s="22" t="s">
-        <v>677</v>
-      </c>
-      <c r="D111" s="51" t="s">
-        <v>676</v>
-      </c>
-      <c r="E111" s="45"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
-      <c r="H111" s="45" t="s">
-        <v>682</v>
-      </c>
-      <c r="I111" s="23"/>
+        <v>223</v>
+      </c>
+      <c r="B111" s="3"/>
+      <c r="C111" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="E111" s="3"/>
+      <c r="F111" s="20"/>
+      <c r="G111" s="20"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
@@ -6823,24 +6613,22 @@
     </row>
     <row r="112" spans="1:13" ht="13.5" customHeight="1">
       <c r="A112" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B112" s="22" t="s">
-        <v>638</v>
-      </c>
-      <c r="C112" s="22" t="s">
-        <v>679</v>
-      </c>
-      <c r="D112" s="51" t="s">
-        <v>678</v>
-      </c>
-      <c r="E112" s="45"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
-      <c r="H112" s="45" t="s">
-        <v>681</v>
-      </c>
-      <c r="I112" s="23"/>
+        <v>223</v>
+      </c>
+      <c r="B112" s="3"/>
+      <c r="C112" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E112" s="3"/>
+      <c r="F112" s="20"/>
+      <c r="G112" s="20"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="8" t="s">
+        <v>263</v>
+      </c>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4"/>
@@ -6848,53 +6636,49 @@
     </row>
     <row r="113" spans="1:13" ht="13.5" customHeight="1">
       <c r="A113" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B113" s="22" t="s">
-        <v>638</v>
-      </c>
-      <c r="C113" s="22" t="s">
-        <v>649</v>
-      </c>
-      <c r="D113" s="51" t="s">
-        <v>671</v>
-      </c>
-      <c r="E113" s="45" t="s">
-        <v>654</v>
-      </c>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="45" t="s">
-        <v>654</v>
-      </c>
-      <c r="I113" s="23"/>
+        <v>223</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E113" s="3"/>
+      <c r="F113" s="20"/>
+      <c r="G113" s="20"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="10" t="s">
+        <v>267</v>
+      </c>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4"/>
       <c r="M113" s="5"/>
     </row>
-    <row r="114" spans="1:13" ht="13.5" customHeight="1">
+    <row r="114" spans="1:13" ht="15" customHeight="1">
       <c r="A114" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B114" s="22" t="s">
-        <v>638</v>
-      </c>
-      <c r="C114" s="22" t="s">
-        <v>651</v>
-      </c>
-      <c r="D114" s="51" t="s">
-        <v>673</v>
-      </c>
-      <c r="E114" s="45" t="s">
-        <v>652</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E114" s="3"/>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
-      <c r="H114" s="45" t="s">
-        <v>661</v>
-      </c>
-      <c r="I114" s="23"/>
+      <c r="H114" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="I114" s="4"/>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4"/>
@@ -6902,21 +6686,21 @@
     </row>
     <row r="115" spans="1:13" ht="13.5" customHeight="1">
       <c r="A115" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B115" s="4"/>
-      <c r="C115" s="5" t="s">
-        <v>235</v>
+      <c r="C115" s="7" t="s">
+        <v>270</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="20"/>
       <c r="G115" s="20"/>
       <c r="H115" s="3"/>
       <c r="I115" s="8" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
@@ -6925,197 +6709,197 @@
     </row>
     <row r="116" spans="1:13" ht="13.5" customHeight="1">
       <c r="A116" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B116" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="C116" s="22" t="s">
-        <v>238</v>
+        <v>223</v>
+      </c>
+      <c r="B116" s="4"/>
+      <c r="C116" s="7" t="s">
+        <v>273</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="E116" s="3"/>
-      <c r="F116" s="20"/>
-      <c r="G116" s="20"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="I116" s="4"/>
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
     </row>
-    <row r="117" spans="1:13" ht="13.5" customHeight="1">
+    <row r="117" spans="1:13" ht="12.75" customHeight="1">
       <c r="A117" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B117" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="C117" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="E117" s="3"/>
-      <c r="F117" s="20"/>
-      <c r="G117" s="20"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="8" t="s">
-        <v>653</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D117" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="E117" s="4"/>
+      <c r="F117" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
       <c r="M117" s="5"/>
     </row>
-    <row r="118" spans="1:13" ht="13.5" customHeight="1">
+    <row r="118" spans="1:13" ht="12.75" customHeight="1">
       <c r="A118" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B118" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="C118" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="E118" s="3"/>
-      <c r="F118" s="20"/>
-      <c r="G118" s="20"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="8" t="s">
-        <v>240</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="E118" s="4"/>
+      <c r="F118" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
       <c r="L118" s="4"/>
       <c r="M118" s="5"/>
     </row>
-    <row r="119" spans="1:13" ht="13.5" customHeight="1">
+    <row r="119" spans="1:13" ht="12.75" customHeight="1">
       <c r="A119" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B119" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="C119" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="D119" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="E119" s="3"/>
-      <c r="F119" s="20"/>
-      <c r="G119" s="20"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="8" t="s">
-        <v>240</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="E119" s="4"/>
+      <c r="F119" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
       <c r="L119" s="4"/>
       <c r="M119" s="5"/>
     </row>
-    <row r="120" spans="1:13" ht="13.5" customHeight="1">
+    <row r="120" spans="1:13" ht="12.75" customHeight="1">
       <c r="A120" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B120" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="C120" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="D120" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="E120" s="3"/>
-      <c r="F120" s="20"/>
-      <c r="G120" s="20"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="8" t="s">
-        <v>240</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="E120" s="4"/>
+      <c r="F120" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4"/>
+      <c r="I120" s="4"/>
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
       <c r="L120" s="4"/>
       <c r="M120" s="5"/>
     </row>
-    <row r="121" spans="1:13" ht="13.5" customHeight="1">
+    <row r="121" spans="1:13" ht="12.75" customHeight="1">
       <c r="A121" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>249</v>
+        <v>223</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>276</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E121" s="3"/>
-      <c r="F121" s="20"/>
-      <c r="G121" s="20"/>
-      <c r="H121" s="3"/>
-      <c r="I121" s="8" t="s">
-        <v>252</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="D121" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="E121" s="4"/>
+      <c r="F121" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
       <c r="L121" s="4"/>
       <c r="M121" s="5"/>
     </row>
-    <row r="122" spans="1:13" ht="13.5" customHeight="1">
+    <row r="122" spans="1:13" ht="12.75" customHeight="1">
       <c r="A122" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>249</v>
+        <v>223</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>276</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="D122" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="E122" s="3"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="20"/>
-      <c r="H122" s="3"/>
-      <c r="I122" s="8" t="s">
-        <v>255</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="D122" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="E122" s="4"/>
+      <c r="F122" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="G122" s="4"/>
+      <c r="H122" s="4"/>
+      <c r="I122" s="4"/>
       <c r="J122" s="4"/>
       <c r="K122" s="4"/>
       <c r="L122" s="4"/>
       <c r="M122" s="5"/>
     </row>
-    <row r="123" spans="1:13" ht="13.5" customHeight="1">
+    <row r="123" spans="1:13" ht="12.75" customHeight="1">
       <c r="A123" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B123" s="3"/>
+        <v>223</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>276</v>
+      </c>
       <c r="C123" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="D123" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E123" s="3"/>
-      <c r="F123" s="20"/>
-      <c r="G123" s="20"/>
-      <c r="H123" s="3"/>
-      <c r="I123" s="8" t="s">
-        <v>258</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="D123" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="E123" s="4"/>
+      <c r="F123" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
+      <c r="I123" s="4"/>
       <c r="J123" s="4"/>
       <c r="K123" s="4"/>
       <c r="L123" s="4"/>
@@ -7123,94 +6907,96 @@
     </row>
     <row r="124" spans="1:13" ht="13.5" customHeight="1">
       <c r="A124" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B124" s="3"/>
+        <v>223</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>276</v>
+      </c>
       <c r="C124" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D124" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="E124" s="3"/>
-      <c r="F124" s="20"/>
-      <c r="G124" s="20"/>
-      <c r="H124" s="3"/>
+        <v>298</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="4"/>
+      <c r="H124" s="4"/>
       <c r="I124" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="J124" s="4"/>
+        <v>300</v>
+      </c>
+      <c r="J124" s="20"/>
       <c r="K124" s="4"/>
       <c r="L124" s="4"/>
       <c r="M124" s="5"/>
     </row>
     <row r="125" spans="1:13" ht="13.5" customHeight="1">
       <c r="A125" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B125" s="3"/>
+        <v>223</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>276</v>
+      </c>
       <c r="C125" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="D125" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="E125" s="3"/>
-      <c r="F125" s="20"/>
-      <c r="G125" s="20"/>
-      <c r="H125" s="3"/>
+        <v>301</v>
+      </c>
+      <c r="D125" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
+      <c r="G125" s="4"/>
+      <c r="H125" s="4"/>
       <c r="I125" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="J125" s="4"/>
+        <v>303</v>
+      </c>
+      <c r="J125" s="20"/>
       <c r="K125" s="4"/>
       <c r="L125" s="4"/>
       <c r="M125" s="5"/>
     </row>
     <row r="126" spans="1:13" ht="13.5" customHeight="1">
       <c r="A126" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="D126" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="E126" s="3"/>
-      <c r="F126" s="20"/>
-      <c r="G126" s="20"/>
-      <c r="H126" s="3"/>
-      <c r="I126" s="10" t="s">
-        <v>268</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D126" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E126" s="4"/>
+      <c r="F126" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="G126" s="4"/>
+      <c r="H126" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="I126" s="4"/>
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
       <c r="L126" s="4"/>
       <c r="M126" s="5"/>
     </row>
-    <row r="127" spans="1:13" ht="15" customHeight="1">
-      <c r="A127" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D127" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="E127" s="3"/>
+    <row r="127" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A127" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B127" s="4"/>
+      <c r="C127" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D127" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4"/>
-      <c r="H127" s="10" t="s">
-        <v>270</v>
-      </c>
+      <c r="H127" s="4"/>
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
@@ -7219,22 +7005,24 @@
     </row>
     <row r="128" spans="1:13" ht="13.5" customHeight="1">
       <c r="A128" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B128" s="4"/>
-      <c r="C128" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="D128" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="E128" s="3"/>
-      <c r="F128" s="20"/>
-      <c r="G128" s="20"/>
+        <v>308</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D128" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F128" s="4"/>
+      <c r="G128" s="4"/>
       <c r="H128" s="3"/>
-      <c r="I128" s="8" t="s">
-        <v>273</v>
-      </c>
+      <c r="I128" s="4"/>
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
       <c r="L128" s="4"/>
@@ -7242,94 +7030,96 @@
     </row>
     <row r="129" spans="1:13" ht="13.5" customHeight="1">
       <c r="A129" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B129" s="4"/>
-      <c r="C129" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="D129" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="E129" s="3"/>
+        <v>308</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D129" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>317</v>
+      </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
-      <c r="H129" s="14" t="s">
-        <v>276</v>
-      </c>
+      <c r="H129" s="3"/>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
       <c r="L129" s="4"/>
       <c r="M129" s="5"/>
     </row>
-    <row r="130" spans="1:13" ht="12.75" customHeight="1">
+    <row r="130" spans="1:13" ht="13.5" customHeight="1">
       <c r="A130" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="D130" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E130" s="4"/>
-      <c r="F130" s="8" t="s">
-        <v>280</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D130" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="F130" s="4"/>
       <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
+      <c r="H130" s="3"/>
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
       <c r="L130" s="4"/>
       <c r="M130" s="5"/>
     </row>
-    <row r="131" spans="1:13" ht="12.75" customHeight="1">
+    <row r="131" spans="1:13" ht="13.5" customHeight="1">
       <c r="A131" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="D131" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="E131" s="4"/>
-      <c r="F131" s="8" t="s">
-        <v>283</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D131" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="F131" s="4"/>
       <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
+      <c r="H131" s="3"/>
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
       <c r="K131" s="4"/>
       <c r="L131" s="4"/>
       <c r="M131" s="5"/>
     </row>
-    <row r="132" spans="1:13" ht="12.75" customHeight="1">
+    <row r="132" spans="1:13" ht="13.5" customHeight="1">
       <c r="A132" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D132" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="E132" s="4"/>
-      <c r="F132" s="8" t="s">
-        <v>286</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="D132" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F132" s="4"/>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
@@ -7338,98 +7128,98 @@
       <c r="L132" s="4"/>
       <c r="M132" s="5"/>
     </row>
-    <row r="133" spans="1:13" ht="12.75" customHeight="1">
+    <row r="133" spans="1:13" ht="13.5" customHeight="1">
       <c r="A133" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D133" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="E133" s="4"/>
-      <c r="F133" s="8" t="s">
-        <v>289</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="D133" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="E133" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="F133" s="4"/>
       <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
+      <c r="H133" s="3"/>
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
       <c r="L133" s="4"/>
       <c r="M133" s="5"/>
     </row>
-    <row r="134" spans="1:13" ht="12.75" customHeight="1">
+    <row r="134" spans="1:13" ht="13.5" customHeight="1">
       <c r="A134" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D134" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="E134" s="4"/>
-      <c r="F134" s="8" t="s">
-        <v>292</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="D134" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="F134" s="4"/>
       <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
+      <c r="H134" s="3"/>
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
       <c r="L134" s="4"/>
       <c r="M134" s="5"/>
     </row>
-    <row r="135" spans="1:13" ht="12.75" customHeight="1">
+    <row r="135" spans="1:13" ht="13.5" customHeight="1">
       <c r="A135" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D135" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="E135" s="4"/>
-      <c r="F135" s="8" t="s">
-        <v>295</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D135" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F135" s="4"/>
       <c r="G135" s="4"/>
-      <c r="H135" s="4"/>
+      <c r="H135" s="3"/>
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
       <c r="L135" s="4"/>
       <c r="M135" s="5"/>
     </row>
-    <row r="136" spans="1:13" ht="12.75" customHeight="1">
+    <row r="136" spans="1:13" ht="13.5" customHeight="1">
       <c r="A136" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="D136" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="E136" s="4"/>
-      <c r="F136" s="8" t="s">
-        <v>298</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D136" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="F136" s="4"/>
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
@@ -7440,75 +7230,73 @@
     </row>
     <row r="137" spans="1:13" ht="13.5" customHeight="1">
       <c r="A137" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="D137" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="E137" s="4"/>
+        <v>308</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D137" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>338</v>
+      </c>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
-      <c r="I137" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="J137" s="20"/>
+      <c r="I137" s="4"/>
+      <c r="J137" s="4"/>
       <c r="K137" s="4"/>
       <c r="L137" s="4"/>
       <c r="M137" s="5"/>
     </row>
     <row r="138" spans="1:13" ht="13.5" customHeight="1">
       <c r="A138" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>302</v>
+        <v>308</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>341</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="E138" s="4"/>
+        <v>342</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>343</v>
+      </c>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
-      <c r="I138" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="J138" s="20"/>
+      <c r="I138" s="4"/>
+      <c r="J138" s="4"/>
       <c r="K138" s="4"/>
       <c r="L138" s="4"/>
       <c r="M138" s="5"/>
     </row>
     <row r="139" spans="1:13" ht="13.5" customHeight="1">
       <c r="A139" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>277</v>
+        <v>308</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>311</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="E139" s="4"/>
-      <c r="F139" s="26" t="s">
-        <v>307</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F139" s="4"/>
       <c r="G139" s="4"/>
-      <c r="H139" s="26" t="s">
-        <v>308</v>
-      </c>
+      <c r="H139" s="4"/>
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
@@ -7516,18 +7304,24 @@
       <c r="M139" s="5"/>
     </row>
     <row r="140" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A140" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B140" s="4"/>
+      <c r="A140" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>346</v>
+      </c>
       <c r="C140" s="5" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="E140" s="4"/>
-      <c r="F140" s="4"/>
+        <v>348</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>350</v>
+      </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
@@ -7538,23 +7332,25 @@
     </row>
     <row r="141" spans="1:13" ht="13.5" customHeight="1">
       <c r="A141" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="E141" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="F141" s="4"/>
+        <v>352</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>350</v>
+      </c>
       <c r="G141" s="4"/>
-      <c r="H141" s="3"/>
+      <c r="H141" s="4"/>
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
@@ -7563,23 +7359,25 @@
     </row>
     <row r="142" spans="1:13" ht="13.5" customHeight="1">
       <c r="A142" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="E142" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="F142" s="4"/>
+        <v>355</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>350</v>
+      </c>
       <c r="G142" s="4"/>
-      <c r="H142" s="3"/>
+      <c r="H142" s="4"/>
       <c r="I142" s="4"/>
       <c r="J142" s="4"/>
       <c r="K142" s="4"/>
@@ -7588,23 +7386,25 @@
     </row>
     <row r="143" spans="1:13" ht="13.5" customHeight="1">
       <c r="A143" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="E143" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="F143" s="4"/>
+        <v>358</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>350</v>
+      </c>
       <c r="G143" s="4"/>
-      <c r="H143" s="3"/>
+      <c r="H143" s="4"/>
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
       <c r="K143" s="4"/>
@@ -7613,23 +7413,25 @@
     </row>
     <row r="144" spans="1:13" ht="13.5" customHeight="1">
       <c r="A144" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="E144" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="F144" s="4"/>
+        <v>361</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>350</v>
+      </c>
       <c r="G144" s="4"/>
-      <c r="H144" s="3"/>
+      <c r="H144" s="4"/>
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
@@ -7638,21 +7440,23 @@
     </row>
     <row r="145" spans="1:13" ht="13.5" customHeight="1">
       <c r="A145" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F145" s="4"/>
+        <v>365</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>350</v>
+      </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
@@ -7663,23 +7467,25 @@
     </row>
     <row r="146" spans="1:13" ht="13.5" customHeight="1">
       <c r="A146" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="E146" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="F146" s="4"/>
+        <v>367</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>369</v>
+      </c>
       <c r="G146" s="4"/>
-      <c r="H146" s="3"/>
+      <c r="H146" s="4"/>
       <c r="I146" s="4"/>
       <c r="J146" s="4"/>
       <c r="K146" s="4"/>
@@ -7688,21 +7494,23 @@
     </row>
     <row r="147" spans="1:13" ht="13.5" customHeight="1">
       <c r="A147" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="F147" s="4"/>
+        <v>372</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>369</v>
+      </c>
       <c r="G147" s="4"/>
       <c r="H147" s="3"/>
       <c r="I147" s="4"/>
@@ -7713,23 +7521,25 @@
     </row>
     <row r="148" spans="1:13" ht="13.5" customHeight="1">
       <c r="A148" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="E148" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="F148" s="4"/>
+        <v>374</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>369</v>
+      </c>
       <c r="G148" s="4"/>
-      <c r="H148" s="3"/>
+      <c r="H148" s="4"/>
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
@@ -7738,21 +7548,23 @@
     </row>
     <row r="149" spans="1:13" ht="13.5" customHeight="1">
       <c r="A149" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>338</v>
+        <v>377</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="F149" s="4"/>
+        <v>378</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>369</v>
+      </c>
       <c r="G149" s="4"/>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
@@ -7763,21 +7575,23 @@
     </row>
     <row r="150" spans="1:13" ht="13.5" customHeight="1">
       <c r="A150" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>341</v>
+        <v>380</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="F150" s="4"/>
+        <v>381</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>369</v>
+      </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
       <c r="I150" s="4"/>
@@ -7788,46 +7602,50 @@
     </row>
     <row r="151" spans="1:13" ht="13.5" customHeight="1">
       <c r="A151" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>342</v>
+        <v>308</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>343</v>
+        <v>383</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="F151" s="4"/>
+        <v>384</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>369</v>
+      </c>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
-      <c r="J151" s="4"/>
+      <c r="J151" s="5"/>
       <c r="K151" s="4"/>
       <c r="L151" s="4"/>
       <c r="M151" s="5"/>
     </row>
     <row r="152" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A152" s="7" t="s">
-        <v>309</v>
+      <c r="A152" s="5" t="s">
+        <v>308</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>312</v>
+        <v>385</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="E152" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="F152" s="4"/>
+        <v>387</v>
+      </c>
+      <c r="E152" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="F152" s="23" t="s">
+        <v>388</v>
+      </c>
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
@@ -7837,23 +7655,23 @@
       <c r="M152" s="5"/>
     </row>
     <row r="153" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A153" s="7" t="s">
-        <v>309</v>
+      <c r="A153" s="5" t="s">
+        <v>308</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>348</v>
+        <v>389</v>
       </c>
       <c r="D153" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="E153" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="F153" s="8" t="s">
-        <v>351</v>
+        <v>390</v>
+      </c>
+      <c r="E153" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="F153" s="23" t="s">
+        <v>391</v>
       </c>
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
@@ -7865,79 +7683,69 @@
     </row>
     <row r="154" spans="1:13" ht="13.5" customHeight="1">
       <c r="A154" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>347</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B154" s="4"/>
       <c r="C154" s="5" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="E154" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="G154" s="4"/>
+        <v>393</v>
+      </c>
+      <c r="E154" s="4"/>
+      <c r="F154" s="20"/>
+      <c r="G154" s="20"/>
       <c r="H154" s="4"/>
-      <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
+      <c r="I154" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="J154" s="20"/>
       <c r="K154" s="4"/>
       <c r="L154" s="4"/>
       <c r="M154" s="5"/>
     </row>
     <row r="155" spans="1:13" ht="13.5" customHeight="1">
       <c r="A155" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>347</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B155" s="4"/>
       <c r="C155" s="5" t="s">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="E155" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F155" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="G155" s="4"/>
+        <v>395</v>
+      </c>
+      <c r="E155" s="4"/>
+      <c r="F155" s="20"/>
+      <c r="G155" s="20"/>
       <c r="H155" s="4"/>
-      <c r="I155" s="4"/>
-      <c r="J155" s="4"/>
+      <c r="I155" s="26" t="s">
+        <v>396</v>
+      </c>
+      <c r="J155" s="20"/>
       <c r="K155" s="4"/>
       <c r="L155" s="4"/>
       <c r="M155" s="5"/>
     </row>
     <row r="156" spans="1:13" ht="13.5" customHeight="1">
       <c r="A156" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>347</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="B156" s="4"/>
       <c r="C156" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D156" s="17" t="s">
-        <v>359</v>
+        <v>397</v>
+      </c>
+      <c r="D156" s="15" t="s">
+        <v>398</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>351</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="F156" s="4"/>
       <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
+      <c r="H156" s="8" t="s">
+        <v>399</v>
+      </c>
       <c r="I156" s="4"/>
       <c r="J156" s="4"/>
       <c r="K156" s="4"/>
@@ -7945,26 +7753,24 @@
       <c r="M156" s="5"/>
     </row>
     <row r="157" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A157" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>347</v>
-      </c>
+      <c r="A157" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B157" s="4"/>
       <c r="C157" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="D157" s="17" t="s">
-        <v>362</v>
+        <v>401</v>
+      </c>
+      <c r="D157" s="15" t="s">
+        <v>402</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="F157" s="8" t="s">
-        <v>351</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="F157" s="4"/>
       <c r="G157" s="4"/>
-      <c r="H157" s="4"/>
+      <c r="H157" s="8" t="s">
+        <v>403</v>
+      </c>
       <c r="I157" s="4"/>
       <c r="J157" s="4"/>
       <c r="K157" s="4"/>
@@ -7972,26 +7778,24 @@
       <c r="M157" s="5"/>
     </row>
     <row r="158" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A158" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>347</v>
-      </c>
+      <c r="A158" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B158" s="4"/>
       <c r="C158" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="D158" s="17" t="s">
-        <v>365</v>
+        <v>404</v>
+      </c>
+      <c r="D158" s="15" t="s">
+        <v>405</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="F158" s="8" t="s">
-        <v>351</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="F158" s="4"/>
       <c r="G158" s="4"/>
-      <c r="H158" s="4"/>
+      <c r="H158" s="8" t="s">
+        <v>406</v>
+      </c>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
       <c r="K158" s="4"/>
@@ -7999,23 +7803,21 @@
       <c r="M158" s="5"/>
     </row>
     <row r="159" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A159" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>347</v>
-      </c>
+      <c r="A159" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B159" s="4"/>
       <c r="C159" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="D159" s="17" t="s">
-        <v>368</v>
+        <v>407</v>
+      </c>
+      <c r="D159" s="15" t="s">
+        <v>408</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>369</v>
+        <v>76</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>370</v>
+        <v>409</v>
       </c>
       <c r="G159" s="4"/>
       <c r="H159" s="4"/>
@@ -8026,26 +7828,22 @@
       <c r="M159" s="5"/>
     </row>
     <row r="160" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A160" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>347</v>
-      </c>
+      <c r="A160" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B160" s="5"/>
       <c r="C160" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="D160" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="E160" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="F160" s="8" t="s">
-        <v>370</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="D160" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="F160" s="4"/>
       <c r="G160" s="4"/>
-      <c r="H160" s="3"/>
+      <c r="H160" s="4"/>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
@@ -8053,23 +7851,23 @@
       <c r="M160" s="5"/>
     </row>
     <row r="161" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A161" s="7" t="s">
-        <v>309</v>
+      <c r="A161" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>347</v>
+        <v>414</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="D161" s="17" t="s">
-        <v>375</v>
+        <v>415</v>
+      </c>
+      <c r="D161" s="15" t="s">
+        <v>416</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>376</v>
+        <v>417</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>370</v>
+        <v>417</v>
       </c>
       <c r="G161" s="4"/>
       <c r="H161" s="4"/>
@@ -8077,111 +7875,123 @@
       <c r="J161" s="4"/>
       <c r="K161" s="4"/>
       <c r="L161" s="4"/>
-      <c r="M161" s="5"/>
+      <c r="M161" s="8" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="162" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A162" s="7" t="s">
-        <v>309</v>
+      <c r="A162" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>347</v>
+        <v>414</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="D162" s="17" t="s">
-        <v>378</v>
+        <v>419</v>
+      </c>
+      <c r="D162" s="15" t="s">
+        <v>420</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>379</v>
+        <v>421</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>370</v>
+        <v>421</v>
       </c>
       <c r="G162" s="4"/>
-      <c r="H162" s="4"/>
+      <c r="H162" s="8" t="s">
+        <v>421</v>
+      </c>
       <c r="I162" s="4"/>
       <c r="J162" s="4"/>
       <c r="K162" s="4"/>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
+      <c r="M162" s="8" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="163" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A163" s="7" t="s">
-        <v>309</v>
+      <c r="A163" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>347</v>
+        <v>414</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="D163" s="17" t="s">
-        <v>381</v>
+        <v>422</v>
+      </c>
+      <c r="D163" s="15" t="s">
+        <v>423</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>382</v>
+        <v>424</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>370</v>
+        <v>424</v>
       </c>
       <c r="G163" s="4"/>
-      <c r="H163" s="4"/>
+      <c r="H163" s="8" t="s">
+        <v>424</v>
+      </c>
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
       <c r="K163" s="4"/>
       <c r="L163" s="4"/>
-      <c r="M163" s="5"/>
+      <c r="M163" s="8" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="164" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A164" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="C164" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="D164" s="17" t="s">
-        <v>384</v>
+      <c r="A164" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="D164" s="15" t="s">
+        <v>426</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F164" s="8" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="G164" s="4"/>
-      <c r="H164" s="4"/>
+      <c r="H164" s="8" t="s">
+        <v>427</v>
+      </c>
       <c r="I164" s="4"/>
-      <c r="J164" s="5"/>
+      <c r="J164" s="4"/>
       <c r="K164" s="4"/>
       <c r="L164" s="4"/>
-      <c r="M164" s="5"/>
-    </row>
-    <row r="165" spans="1:13" ht="13.5" customHeight="1">
+      <c r="M164" s="8" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="15" customHeight="1">
       <c r="A165" s="5" t="s">
-        <v>309</v>
+        <v>410</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="D165" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="E165" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="F165" s="23" t="s">
-        <v>389</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="D165" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4"/>
       <c r="G165" s="4"/>
       <c r="H165" s="4"/>
-      <c r="I165" s="4"/>
+      <c r="I165" s="8" t="s">
+        <v>431</v>
+      </c>
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
       <c r="L165" s="4"/>
@@ -8189,23 +7999,19 @@
     </row>
     <row r="166" spans="1:13" ht="13.5" customHeight="1">
       <c r="A166" s="5" t="s">
-        <v>309</v>
+        <v>410</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="D166" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="E166" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="F166" s="23" t="s">
-        <v>392</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="D166" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4"/>
       <c r="G166" s="4"/>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
@@ -8215,71 +8021,79 @@
       <c r="M166" s="5"/>
     </row>
     <row r="167" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A167" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B167" s="4"/>
+      <c r="A167" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="C167" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="D167" s="17" t="s">
-        <v>394</v>
+        <v>435</v>
+      </c>
+      <c r="D167" s="15" t="s">
+        <v>436</v>
       </c>
       <c r="E167" s="4"/>
-      <c r="F167" s="20"/>
-      <c r="G167" s="20"/>
+      <c r="F167" s="4"/>
+      <c r="G167" s="4"/>
       <c r="H167" s="4"/>
-      <c r="I167" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="J167" s="20"/>
+      <c r="I167" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="J167" s="4"/>
       <c r="K167" s="4"/>
       <c r="L167" s="4"/>
       <c r="M167" s="5"/>
     </row>
     <row r="168" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A168" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B168" s="4"/>
+      <c r="A168" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="C168" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="D168" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="E168" s="4"/>
-      <c r="F168" s="20"/>
-      <c r="G168" s="20"/>
-      <c r="H168" s="4"/>
-      <c r="I168" s="26" t="s">
-        <v>397</v>
-      </c>
-      <c r="J168" s="20"/>
+        <v>438</v>
+      </c>
+      <c r="D168" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="G168" s="4"/>
+      <c r="H168" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="I168" s="4"/>
+      <c r="J168" s="4"/>
       <c r="K168" s="4"/>
       <c r="L168" s="4"/>
       <c r="M168" s="5"/>
     </row>
     <row r="169" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A169" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B169" s="4"/>
+      <c r="A169" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="C169" s="5" t="s">
-        <v>398</v>
+        <v>441</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="E169" s="8" t="s">
-        <v>400</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
-      <c r="H169" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="I169" s="4"/>
+      <c r="H169" s="4"/>
+      <c r="I169" s="8" t="s">
+        <v>437</v>
+      </c>
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
       <c r="L169" s="4"/>
@@ -8287,24 +8101,24 @@
     </row>
     <row r="170" spans="1:13" ht="13.5" customHeight="1">
       <c r="A170" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="B170" s="4"/>
+        <v>410</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="C170" s="5" t="s">
-        <v>402</v>
+        <v>443</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="E170" s="8" t="s">
-        <v>404</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="E170" s="4"/>
       <c r="F170" s="4"/>
       <c r="G170" s="4"/>
-      <c r="H170" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="I170" s="4"/>
+      <c r="H170" s="4"/>
+      <c r="I170" s="10" t="s">
+        <v>445</v>
+      </c>
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
       <c r="L170" s="4"/>
@@ -8312,24 +8126,24 @@
     </row>
     <row r="171" spans="1:13" ht="13.5" customHeight="1">
       <c r="A171" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="B171" s="4"/>
+        <v>410</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="C171" s="5" t="s">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>407</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="E171" s="4"/>
       <c r="F171" s="4"/>
       <c r="G171" s="4"/>
-      <c r="H171" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="I171" s="4"/>
+      <c r="H171" s="4"/>
+      <c r="I171" s="10" t="s">
+        <v>445</v>
+      </c>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
       <c r="L171" s="4"/>
@@ -8337,24 +8151,24 @@
     </row>
     <row r="172" spans="1:13" ht="13.5" customHeight="1">
       <c r="A172" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="B172" s="4"/>
+        <v>410</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="C172" s="5" t="s">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="E172" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F172" s="8" t="s">
-        <v>410</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="E172" s="4"/>
+      <c r="F172" s="4"/>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
-      <c r="I172" s="4"/>
+      <c r="I172" s="10" t="s">
+        <v>450</v>
+      </c>
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
       <c r="L172" s="4"/>
@@ -8362,21 +8176,27 @@
     </row>
     <row r="173" spans="1:13" ht="13.5" customHeight="1">
       <c r="A173" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B173" s="5"/>
+        <v>410</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>434</v>
+      </c>
       <c r="C173" s="5" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>413</v>
+        <v>452</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="F173" s="4"/>
+        <v>453</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>453</v>
+      </c>
       <c r="G173" s="4"/>
-      <c r="H173" s="4"/>
+      <c r="H173" s="8" t="s">
+        <v>453</v>
+      </c>
       <c r="I173" s="4"/>
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
@@ -8385,146 +8205,132 @@
     </row>
     <row r="174" spans="1:13" ht="13.5" customHeight="1">
       <c r="A174" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D174" s="15" t="s">
-        <v>417</v>
+        <v>454</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="D174" s="17" t="s">
+        <v>456</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="F174" s="8" t="s">
-        <v>418</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="F174" s="4"/>
       <c r="G174" s="4"/>
-      <c r="H174" s="4"/>
+      <c r="H174" s="8" t="s">
+        <v>457</v>
+      </c>
       <c r="I174" s="4"/>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
       <c r="L174" s="4"/>
-      <c r="M174" s="8" t="s">
-        <v>419</v>
-      </c>
+      <c r="M174" s="5"/>
     </row>
     <row r="175" spans="1:13" ht="13.5" customHeight="1">
       <c r="A175" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="D175" s="15" t="s">
-        <v>421</v>
+        <v>454</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="D175" s="17" t="s">
+        <v>459</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="F175" s="8" t="s">
-        <v>422</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="F175" s="4"/>
       <c r="G175" s="4"/>
       <c r="H175" s="8" t="s">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
       <c r="K175" s="4"/>
       <c r="L175" s="4"/>
-      <c r="M175" s="8" t="s">
-        <v>419</v>
-      </c>
+      <c r="M175" s="5"/>
     </row>
     <row r="176" spans="1:13" ht="13.5" customHeight="1">
       <c r="A176" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="D176" s="15" t="s">
-        <v>424</v>
+        <v>454</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="D176" s="17" t="s">
+        <v>462</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="F176" s="8" t="s">
-        <v>425</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="F176" s="4"/>
       <c r="G176" s="4"/>
       <c r="H176" s="8" t="s">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
       <c r="K176" s="4"/>
       <c r="L176" s="4"/>
-      <c r="M176" s="8" t="s">
-        <v>419</v>
-      </c>
+      <c r="M176" s="5"/>
     </row>
     <row r="177" spans="1:13" ht="13.5" customHeight="1">
       <c r="A177" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D177" s="15" t="s">
-        <v>427</v>
+        <v>454</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="D177" s="17" t="s">
+        <v>465</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="F177" s="8" t="s">
-        <v>428</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="F177" s="4"/>
       <c r="G177" s="4"/>
       <c r="H177" s="8" t="s">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
       <c r="L177" s="4"/>
-      <c r="M177" s="8" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="178" spans="1:13" ht="15" customHeight="1">
+      <c r="M177" s="5"/>
+    </row>
+    <row r="178" spans="1:13" ht="13.5" customHeight="1">
       <c r="A178" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="D178" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="E178" s="4"/>
+        <v>410</v>
+      </c>
+      <c r="B178" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="C178" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="D178" s="27" t="s">
+        <v>469</v>
+      </c>
+      <c r="E178" s="5"/>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
-      <c r="H178" s="4"/>
-      <c r="I178" s="8" t="s">
-        <v>432</v>
-      </c>
+      <c r="H178" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="I178" s="4"/>
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
       <c r="L178" s="4"/>
@@ -8532,21 +8338,23 @@
     </row>
     <row r="179" spans="1:13" ht="13.5" customHeight="1">
       <c r="A179" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="D179" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="E179" s="4"/>
+        <v>410</v>
+      </c>
+      <c r="B179" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="C179" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="D179" s="27" t="s">
+        <v>472</v>
+      </c>
+      <c r="E179" s="5"/>
       <c r="F179" s="4"/>
       <c r="G179" s="4"/>
-      <c r="H179" s="4"/>
+      <c r="H179" s="8" t="s">
+        <v>473</v>
+      </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
@@ -8555,24 +8363,24 @@
     </row>
     <row r="180" spans="1:13" ht="13.5" customHeight="1">
       <c r="A180" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B180" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="D180" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="E180" s="4"/>
+        <v>410</v>
+      </c>
+      <c r="B180" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="C180" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="D180" s="28" t="s">
+        <v>475</v>
+      </c>
+      <c r="E180" s="5"/>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
-      <c r="H180" s="4"/>
-      <c r="I180" s="8" t="s">
-        <v>438</v>
-      </c>
+      <c r="H180" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="I180" s="4"/>
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
       <c r="L180" s="4"/>
@@ -8580,26 +8388,22 @@
     </row>
     <row r="181" spans="1:13" ht="13.5" customHeight="1">
       <c r="A181" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B181" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="D181" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="E181" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="F181" s="8" t="s">
-        <v>441</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="B181" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="C181" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="D181" s="27" t="s">
+        <v>478</v>
+      </c>
+      <c r="E181" s="5"/>
+      <c r="F181" s="4"/>
       <c r="G181" s="4"/>
       <c r="H181" s="8" t="s">
-        <v>441</v>
+        <v>479</v>
       </c>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
@@ -8609,24 +8413,24 @@
     </row>
     <row r="182" spans="1:13" ht="13.5" customHeight="1">
       <c r="A182" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="D182" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="E182" s="4"/>
+        <v>410</v>
+      </c>
+      <c r="B182" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="C182" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="D182" s="27" t="s">
+        <v>481</v>
+      </c>
+      <c r="E182" s="5"/>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
-      <c r="H182" s="4"/>
-      <c r="I182" s="8" t="s">
-        <v>438</v>
-      </c>
+      <c r="H182" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="I182" s="4"/>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
       <c r="L182" s="4"/>
@@ -8634,23 +8438,23 @@
     </row>
     <row r="183" spans="1:13" ht="13.5" customHeight="1">
       <c r="A183" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B183" s="7" t="s">
-        <v>435</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="B183" s="4"/>
       <c r="C183" s="5" t="s">
-        <v>444</v>
+        <v>484</v>
       </c>
       <c r="D183" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="E183" s="4"/>
+        <v>485</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>323</v>
+      </c>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
-      <c r="H183" s="4"/>
-      <c r="I183" s="10" t="s">
-        <v>446</v>
+      <c r="H183" s="5"/>
+      <c r="I183" s="23" t="s">
+        <v>486</v>
       </c>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
@@ -8658,77 +8462,79 @@
       <c r="M183" s="5"/>
     </row>
     <row r="184" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A184" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>435</v>
+      <c r="A184" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>488</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>447</v>
+        <v>489</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="E184" s="4"/>
-      <c r="F184" s="4"/>
+        <v>490</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>326</v>
+      </c>
       <c r="G184" s="4"/>
       <c r="H184" s="4"/>
-      <c r="I184" s="10" t="s">
-        <v>446</v>
-      </c>
+      <c r="I184" s="4"/>
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
       <c r="L184" s="4"/>
       <c r="M184" s="5"/>
     </row>
     <row r="185" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A185" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B185" s="7" t="s">
-        <v>435</v>
+      <c r="A185" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>488</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>449</v>
+        <v>492</v>
       </c>
       <c r="D185" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="E185" s="4"/>
-      <c r="F185" s="4"/>
+        <v>493</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>326</v>
+      </c>
       <c r="G185" s="4"/>
       <c r="H185" s="4"/>
-      <c r="I185" s="10" t="s">
-        <v>451</v>
-      </c>
+      <c r="I185" s="4"/>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
       <c r="L185" s="4"/>
       <c r="M185" s="5"/>
     </row>
     <row r="186" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A186" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>435</v>
+      <c r="A186" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>495</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>452</v>
+        <v>495</v>
       </c>
       <c r="D186" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="E186" s="8" t="s">
-        <v>454</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="E186" s="4"/>
       <c r="F186" s="8" t="s">
-        <v>454</v>
+        <v>497</v>
       </c>
       <c r="G186" s="4"/>
       <c r="H186" s="8" t="s">
-        <v>454</v>
+        <v>497</v>
       </c>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
@@ -8737,25 +8543,27 @@
       <c r="M186" s="5"/>
     </row>
     <row r="187" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A187" s="5" t="s">
-        <v>411</v>
+      <c r="A187" s="7" t="s">
+        <v>487</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C187" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="D187" s="17" t="s">
-        <v>457</v>
+        <v>498</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="D187" s="15" t="s">
+        <v>500</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="F187" s="4"/>
+        <v>501</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>501</v>
+      </c>
       <c r="G187" s="4"/>
       <c r="H187" s="8" t="s">
-        <v>458</v>
+        <v>501</v>
       </c>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
@@ -8764,25 +8572,27 @@
       <c r="M187" s="5"/>
     </row>
     <row r="188" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A188" s="5" t="s">
-        <v>411</v>
+      <c r="A188" s="7" t="s">
+        <v>487</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C188" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="D188" s="17" t="s">
-        <v>460</v>
+        <v>498</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="D188" s="15" t="s">
+        <v>503</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="F188" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="G188" s="4"/>
       <c r="H188" s="8" t="s">
-        <v>461</v>
+        <v>23</v>
       </c>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
@@ -8791,77 +8601,73 @@
       <c r="M188" s="5"/>
     </row>
     <row r="189" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A189" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C189" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="D189" s="17" t="s">
-        <v>463</v>
-      </c>
-      <c r="E189" s="8" t="s">
-        <v>464</v>
-      </c>
+      <c r="A189" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="B189" s="4"/>
+      <c r="C189" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D189" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="E189" s="4"/>
       <c r="F189" s="4"/>
       <c r="G189" s="4"/>
-      <c r="H189" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="I189" s="4"/>
+      <c r="H189" s="4"/>
+      <c r="I189" s="8" t="s">
+        <v>506</v>
+      </c>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
       <c r="L189" s="4"/>
       <c r="M189" s="5"/>
     </row>
     <row r="190" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A190" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C190" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="D190" s="17" t="s">
-        <v>466</v>
-      </c>
-      <c r="E190" s="8" t="s">
-        <v>467</v>
-      </c>
+      <c r="A190" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="D190" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="E190" s="4"/>
       <c r="F190" s="4"/>
       <c r="G190" s="4"/>
-      <c r="H190" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="I190" s="4"/>
+      <c r="H190" s="4"/>
+      <c r="I190" s="10" t="s">
+        <v>511</v>
+      </c>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
       <c r="L190" s="4"/>
       <c r="M190" s="5"/>
     </row>
     <row r="191" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A191" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B191" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="C191" s="22" t="s">
-        <v>469</v>
-      </c>
-      <c r="D191" s="27" t="s">
-        <v>470</v>
-      </c>
-      <c r="E191" s="5"/>
+      <c r="A191" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="D191" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>323</v>
+      </c>
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
       <c r="H191" s="8" t="s">
-        <v>471</v>
+        <v>323</v>
       </c>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
@@ -8870,48 +8676,50 @@
       <c r="M191" s="5"/>
     </row>
     <row r="192" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A192" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B192" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="C192" s="22" t="s">
-        <v>472</v>
-      </c>
-      <c r="D192" s="27" t="s">
-        <v>473</v>
-      </c>
-      <c r="E192" s="5"/>
-      <c r="F192" s="4"/>
-      <c r="G192" s="4"/>
-      <c r="H192" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="I192" s="4"/>
+      <c r="A192" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D192" s="29" t="s">
+        <v>516</v>
+      </c>
+      <c r="E192" s="30"/>
+      <c r="F192" s="30"/>
+      <c r="G192" s="30"/>
+      <c r="H192" s="31"/>
+      <c r="I192" s="10" t="s">
+        <v>517</v>
+      </c>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
       <c r="L192" s="4"/>
       <c r="M192" s="5"/>
     </row>
     <row r="193" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A193" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B193" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="C193" s="22" t="s">
-        <v>475</v>
-      </c>
-      <c r="D193" s="28" t="s">
-        <v>476</v>
-      </c>
-      <c r="E193" s="5"/>
+      <c r="A193" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="D193" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>520</v>
+      </c>
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
       <c r="H193" s="8" t="s">
-        <v>477</v>
+        <v>520</v>
       </c>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
@@ -8920,24 +8728,24 @@
       <c r="M193" s="5"/>
     </row>
     <row r="194" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A194" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B194" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="C194" s="22" t="s">
-        <v>478</v>
-      </c>
-      <c r="D194" s="27" t="s">
-        <v>479</v>
-      </c>
-      <c r="E194" s="5"/>
-      <c r="F194" s="4"/>
+      <c r="A194" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="D194" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="E194" s="4"/>
+      <c r="F194" s="8" t="s">
+        <v>524</v>
+      </c>
       <c r="G194" s="4"/>
-      <c r="H194" s="8" t="s">
-        <v>480</v>
-      </c>
+      <c r="H194" s="4"/>
       <c r="I194" s="4"/>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
@@ -8945,24 +8753,24 @@
       <c r="M194" s="5"/>
     </row>
     <row r="195" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A195" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B195" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="C195" s="22" t="s">
-        <v>481</v>
-      </c>
-      <c r="D195" s="27" t="s">
-        <v>482</v>
-      </c>
-      <c r="E195" s="5"/>
-      <c r="F195" s="4"/>
+      <c r="A195" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D195" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="E195" s="4"/>
+      <c r="F195" s="8" t="s">
+        <v>527</v>
+      </c>
       <c r="G195" s="4"/>
-      <c r="H195" s="8" t="s">
-        <v>483</v>
-      </c>
+      <c r="H195" s="4"/>
       <c r="I195" s="4"/>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
@@ -8970,25 +8778,25 @@
       <c r="M195" s="5"/>
     </row>
     <row r="196" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A196" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="B196" s="4"/>
-      <c r="C196" s="5" t="s">
-        <v>485</v>
+      <c r="A196" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>528</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>486</v>
-      </c>
-      <c r="E196" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="F196" s="4"/>
+        <v>529</v>
+      </c>
+      <c r="E196" s="4"/>
+      <c r="F196" s="8" t="s">
+        <v>530</v>
+      </c>
       <c r="G196" s="4"/>
-      <c r="H196" s="5"/>
-      <c r="I196" s="23" t="s">
-        <v>487</v>
-      </c>
+      <c r="H196" s="4"/>
+      <c r="I196" s="4"/>
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
       <c r="L196" s="4"/>
@@ -8996,22 +8804,20 @@
     </row>
     <row r="197" spans="1:13" ht="13.5" customHeight="1">
       <c r="A197" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>490</v>
+        <v>507</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>531</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="E197" s="8" t="s">
-        <v>492</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="E197" s="4"/>
       <c r="F197" s="8" t="s">
-        <v>327</v>
+        <v>533</v>
       </c>
       <c r="G197" s="4"/>
       <c r="H197" s="4"/>
@@ -9023,22 +8829,20 @@
     </row>
     <row r="198" spans="1:13" ht="13.5" customHeight="1">
       <c r="A198" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>493</v>
+        <v>507</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>534</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>494</v>
-      </c>
-      <c r="E198" s="8" t="s">
-        <v>495</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="E198" s="4"/>
       <c r="F198" s="8" t="s">
-        <v>327</v>
+        <v>536</v>
       </c>
       <c r="G198" s="4"/>
       <c r="H198" s="4"/>
@@ -9050,25 +8854,23 @@
     </row>
     <row r="199" spans="1:13" ht="13.5" customHeight="1">
       <c r="A199" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>496</v>
+        <v>507</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>537</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="8" t="s">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="G199" s="4"/>
-      <c r="H199" s="8" t="s">
-        <v>498</v>
-      </c>
+      <c r="H199" s="4"/>
       <c r="I199" s="4"/>
       <c r="J199" s="4"/>
       <c r="K199" s="4"/>
@@ -9077,27 +8879,23 @@
     </row>
     <row r="200" spans="1:13" ht="13.5" customHeight="1">
       <c r="A200" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>500</v>
+        <v>507</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>540</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>501</v>
-      </c>
-      <c r="E200" s="8" t="s">
-        <v>502</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="E200" s="4"/>
       <c r="F200" s="8" t="s">
-        <v>502</v>
+        <v>542</v>
       </c>
       <c r="G200" s="4"/>
-      <c r="H200" s="8" t="s">
-        <v>502</v>
-      </c>
+      <c r="H200" s="4"/>
       <c r="I200" s="4"/>
       <c r="J200" s="4"/>
       <c r="K200" s="4"/>
@@ -9106,27 +8904,23 @@
     </row>
     <row r="201" spans="1:13" ht="13.5" customHeight="1">
       <c r="A201" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>503</v>
+        <v>507</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>543</v>
       </c>
       <c r="D201" s="15" t="s">
-        <v>504</v>
-      </c>
-      <c r="E201" s="8" t="s">
-        <v>23</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="E201" s="4"/>
       <c r="F201" s="8" t="s">
-        <v>23</v>
+        <v>545</v>
       </c>
       <c r="G201" s="4"/>
-      <c r="H201" s="8" t="s">
-        <v>23</v>
-      </c>
+      <c r="H201" s="4"/>
       <c r="I201" s="4"/>
       <c r="J201" s="4"/>
       <c r="K201" s="4"/>
@@ -9135,22 +8929,24 @@
     </row>
     <row r="202" spans="1:13" ht="13.5" customHeight="1">
       <c r="A202" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="B202" s="4"/>
-      <c r="C202" s="5" t="s">
-        <v>505</v>
+        <v>507</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>546</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
       <c r="E202" s="4"/>
-      <c r="F202" s="4"/>
+      <c r="F202" s="8" t="s">
+        <v>548</v>
+      </c>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
-      <c r="I202" s="8" t="s">
-        <v>507</v>
-      </c>
+      <c r="I202" s="4"/>
       <c r="J202" s="4"/>
       <c r="K202" s="4"/>
       <c r="L202" s="4"/>
@@ -9158,24 +8954,24 @@
     </row>
     <row r="203" spans="1:13" ht="13.5" customHeight="1">
       <c r="A203" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>510</v>
+        <v>549</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>511</v>
+        <v>550</v>
       </c>
       <c r="E203" s="4"/>
-      <c r="F203" s="4"/>
+      <c r="F203" s="8" t="s">
+        <v>551</v>
+      </c>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
-      <c r="I203" s="10" t="s">
-        <v>512</v>
-      </c>
+      <c r="I203" s="4"/>
       <c r="J203" s="4"/>
       <c r="K203" s="4"/>
       <c r="L203" s="4"/>
@@ -9183,25 +8979,23 @@
     </row>
     <row r="204" spans="1:13" ht="13.5" customHeight="1">
       <c r="A204" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>514</v>
-      </c>
-      <c r="E204" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="F204" s="4"/>
+        <v>553</v>
+      </c>
+      <c r="E204" s="4"/>
+      <c r="F204" s="8" t="s">
+        <v>554</v>
+      </c>
       <c r="G204" s="4"/>
-      <c r="H204" s="8" t="s">
-        <v>324</v>
-      </c>
+      <c r="H204" s="4"/>
       <c r="I204" s="4"/>
       <c r="J204" s="4"/>
       <c r="K204" s="4"/>
@@ -9210,24 +9004,24 @@
     </row>
     <row r="205" spans="1:13" ht="13.5" customHeight="1">
       <c r="A205" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="D205" s="29" t="s">
-        <v>517</v>
-      </c>
-      <c r="E205" s="30"/>
-      <c r="F205" s="30"/>
-      <c r="G205" s="30"/>
-      <c r="H205" s="31"/>
-      <c r="I205" s="10" t="s">
-        <v>518</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="D205" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="E205" s="4"/>
+      <c r="F205" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="G205" s="4"/>
+      <c r="H205" s="4"/>
+      <c r="I205" s="4"/>
       <c r="J205" s="4"/>
       <c r="K205" s="4"/>
       <c r="L205" s="4"/>
@@ -9235,25 +9029,23 @@
     </row>
     <row r="206" spans="1:13" ht="13.5" customHeight="1">
       <c r="A206" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>519</v>
+        <v>558</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="E206" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="F206" s="4"/>
+        <v>559</v>
+      </c>
+      <c r="E206" s="4"/>
+      <c r="F206" s="8" t="s">
+        <v>560</v>
+      </c>
       <c r="G206" s="4"/>
-      <c r="H206" s="8" t="s">
-        <v>521</v>
-      </c>
+      <c r="H206" s="4"/>
       <c r="I206" s="4"/>
       <c r="J206" s="4"/>
       <c r="K206" s="4"/>
@@ -9262,24 +9054,24 @@
     </row>
     <row r="207" spans="1:13" ht="13.5" customHeight="1">
       <c r="A207" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>523</v>
+        <v>562</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>524</v>
+        <v>563</v>
       </c>
       <c r="E207" s="4"/>
-      <c r="F207" s="8" t="s">
-        <v>525</v>
-      </c>
+      <c r="F207" s="4"/>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
-      <c r="I207" s="4"/>
+      <c r="I207" s="23" t="s">
+        <v>564</v>
+      </c>
       <c r="J207" s="4"/>
       <c r="K207" s="4"/>
       <c r="L207" s="4"/>
@@ -9287,24 +9079,24 @@
     </row>
     <row r="208" spans="1:13" ht="13.5" customHeight="1">
       <c r="A208" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>522</v>
+        <v>565</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>526</v>
+        <v>566</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>527</v>
+        <v>567</v>
       </c>
       <c r="E208" s="4"/>
-      <c r="F208" s="8" t="s">
-        <v>528</v>
-      </c>
+      <c r="F208" s="4"/>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
-      <c r="I208" s="4"/>
+      <c r="I208" s="23" t="s">
+        <v>568</v>
+      </c>
       <c r="J208" s="4"/>
       <c r="K208" s="4"/>
       <c r="L208" s="4"/>
@@ -9312,24 +9104,24 @@
     </row>
     <row r="209" spans="1:13" ht="13.5" customHeight="1">
       <c r="A209" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>522</v>
+        <v>565</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>529</v>
+        <v>569</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>530</v>
+        <v>570</v>
       </c>
       <c r="E209" s="4"/>
-      <c r="F209" s="8" t="s">
-        <v>531</v>
-      </c>
+      <c r="F209" s="4"/>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
-      <c r="I209" s="4"/>
+      <c r="I209" s="23" t="s">
+        <v>571</v>
+      </c>
       <c r="J209" s="4"/>
       <c r="K209" s="4"/>
       <c r="L209" s="4"/>
@@ -9337,24 +9129,24 @@
     </row>
     <row r="210" spans="1:13" ht="13.5" customHeight="1">
       <c r="A210" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>522</v>
+        <v>565</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>532</v>
+        <v>572</v>
       </c>
       <c r="D210" s="15" t="s">
-        <v>533</v>
+        <v>573</v>
       </c>
       <c r="E210" s="4"/>
-      <c r="F210" s="8" t="s">
-        <v>534</v>
-      </c>
+      <c r="F210" s="4"/>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
-      <c r="I210" s="4"/>
+      <c r="I210" s="8" t="s">
+        <v>574</v>
+      </c>
       <c r="J210" s="4"/>
       <c r="K210" s="4"/>
       <c r="L210" s="4"/>
@@ -9362,24 +9154,22 @@
     </row>
     <row r="211" spans="1:13" ht="13.5" customHeight="1">
       <c r="A211" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B211" s="7" t="s">
-        <v>522</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="B211" s="4"/>
       <c r="C211" s="7" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="E211" s="4"/>
-      <c r="F211" s="8" t="s">
-        <v>537</v>
-      </c>
+      <c r="F211" s="4"/>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
-      <c r="I211" s="4"/>
+      <c r="I211" s="8" t="s">
+        <v>578</v>
+      </c>
       <c r="J211" s="4"/>
       <c r="K211" s="4"/>
       <c r="L211" s="4"/>
@@ -9387,20 +9177,20 @@
     </row>
     <row r="212" spans="1:13" ht="13.5" customHeight="1">
       <c r="A212" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B212" s="7" t="s">
-        <v>522</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="B212" s="4"/>
       <c r="C212" s="7" t="s">
-        <v>538</v>
+        <v>579</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>539</v>
-      </c>
-      <c r="E212" s="4"/>
-      <c r="F212" s="8" t="s">
-        <v>540</v>
+        <v>580</v>
+      </c>
+      <c r="E212" s="23" t="s">
+        <v>581</v>
+      </c>
+      <c r="F212" s="23" t="s">
+        <v>581</v>
       </c>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
@@ -9411,46 +9201,48 @@
       <c r="M212" s="5"/>
     </row>
     <row r="213" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A213" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B213" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="C213" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="D213" s="15" t="s">
-        <v>542</v>
+      <c r="A213" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B213" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="C213" s="32" t="s">
+        <v>583</v>
+      </c>
+      <c r="D213" s="33" t="s">
+        <v>584</v>
       </c>
       <c r="E213" s="4"/>
-      <c r="F213" s="8" t="s">
-        <v>543</v>
-      </c>
+      <c r="F213" s="4"/>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
-      <c r="I213" s="4"/>
+      <c r="I213" s="23" t="s">
+        <v>585</v>
+      </c>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
       <c r="L213" s="4"/>
       <c r="M213" s="5"/>
     </row>
     <row r="214" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A214" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B214" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="C214" s="7" t="s">
-        <v>544</v>
+      <c r="A214" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B214" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="C214" s="32" t="s">
+        <v>586</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>545</v>
-      </c>
-      <c r="E214" s="4"/>
-      <c r="F214" s="8" t="s">
-        <v>546</v>
+        <v>587</v>
+      </c>
+      <c r="E214" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="F214" s="23" t="s">
+        <v>269</v>
       </c>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
@@ -9461,122 +9253,112 @@
       <c r="M214" s="5"/>
     </row>
     <row r="215" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A215" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B215" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="C215" s="7" t="s">
-        <v>547</v>
+      <c r="A215" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B215" s="4"/>
+      <c r="C215" s="5" t="s">
+        <v>588</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>548</v>
+        <v>589</v>
       </c>
       <c r="E215" s="4"/>
-      <c r="F215" s="8" t="s">
-        <v>549</v>
-      </c>
+      <c r="F215" s="4"/>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
-      <c r="I215" s="4"/>
+      <c r="I215" s="8" t="s">
+        <v>590</v>
+      </c>
       <c r="J215" s="4"/>
       <c r="K215" s="4"/>
       <c r="L215" s="4"/>
       <c r="M215" s="5"/>
     </row>
     <row r="216" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A216" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B216" s="7" t="s">
-        <v>522</v>
-      </c>
+      <c r="A216" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B216" s="4"/>
       <c r="C216" s="7" t="s">
-        <v>550</v>
+        <v>591</v>
       </c>
       <c r="D216" s="15" t="s">
-        <v>551</v>
+        <v>592</v>
       </c>
       <c r="E216" s="4"/>
-      <c r="F216" s="8" t="s">
-        <v>552</v>
-      </c>
+      <c r="F216" s="4"/>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
-      <c r="I216" s="4"/>
+      <c r="I216" s="10" t="s">
+        <v>593</v>
+      </c>
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
       <c r="L216" s="4"/>
       <c r="M216" s="5"/>
     </row>
     <row r="217" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A217" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B217" s="7" t="s">
-        <v>522</v>
-      </c>
+      <c r="A217" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B217" s="4"/>
       <c r="C217" s="7" t="s">
-        <v>553</v>
+        <v>594</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>554</v>
+        <v>595</v>
       </c>
       <c r="E217" s="4"/>
-      <c r="F217" s="8" t="s">
-        <v>555</v>
-      </c>
+      <c r="F217" s="4"/>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
-      <c r="I217" s="4"/>
+      <c r="I217" s="8" t="s">
+        <v>596</v>
+      </c>
       <c r="J217" s="4"/>
       <c r="K217" s="4"/>
       <c r="L217" s="4"/>
       <c r="M217" s="5"/>
     </row>
     <row r="218" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A218" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B218" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="C218" s="7" t="s">
-        <v>556</v>
+      <c r="A218" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B218" s="4"/>
+      <c r="C218" s="5" t="s">
+        <v>597</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>557</v>
+        <v>598</v>
       </c>
       <c r="E218" s="4"/>
-      <c r="F218" s="8" t="s">
-        <v>558</v>
-      </c>
+      <c r="F218" s="4"/>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
-      <c r="I218" s="4"/>
+      <c r="I218" s="8" t="s">
+        <v>599</v>
+      </c>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
       <c r="L218" s="4"/>
       <c r="M218" s="5"/>
     </row>
     <row r="219" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A219" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B219" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="C219" s="7" t="s">
-        <v>559</v>
+      <c r="A219" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B219" s="4"/>
+      <c r="C219" s="5" t="s">
+        <v>600</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>560</v>
-      </c>
-      <c r="E219" s="4"/>
-      <c r="F219" s="8" t="s">
-        <v>561</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="E219" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="F219" s="4"/>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
@@ -9587,23 +9369,21 @@
     </row>
     <row r="220" spans="1:13" ht="13.5" customHeight="1">
       <c r="A220" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B220" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="C220" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="D220" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="E220" s="4"/>
+        <v>603</v>
+      </c>
+      <c r="B220" s="4"/>
+      <c r="C220" s="22" t="s">
+        <v>604</v>
+      </c>
+      <c r="D220" s="33" t="s">
+        <v>605</v>
+      </c>
+      <c r="E220" s="5"/>
       <c r="F220" s="4"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
       <c r="I220" s="23" t="s">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
@@ -9612,23 +9392,21 @@
     </row>
     <row r="221" spans="1:13" ht="13.5" customHeight="1">
       <c r="A221" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B221" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="C221" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="D221" s="15" t="s">
-        <v>568</v>
-      </c>
-      <c r="E221" s="4"/>
+        <v>603</v>
+      </c>
+      <c r="B221" s="3"/>
+      <c r="C221" s="34" t="s">
+        <v>607</v>
+      </c>
+      <c r="D221" s="35" t="s">
+        <v>608</v>
+      </c>
+      <c r="E221" s="3"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
-      <c r="H221" s="4"/>
-      <c r="I221" s="23" t="s">
-        <v>569</v>
+      <c r="H221" s="3"/>
+      <c r="I221" s="8" t="s">
+        <v>609</v>
       </c>
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
@@ -9637,23 +9415,21 @@
     </row>
     <row r="222" spans="1:13" ht="13.5" customHeight="1">
       <c r="A222" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B222" s="7" t="s">
-        <v>566</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="B222" s="3"/>
       <c r="C222" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="D222" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="E222" s="4"/>
+        <v>610</v>
+      </c>
+      <c r="D222" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="E222" s="3"/>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
-      <c r="H222" s="4"/>
-      <c r="I222" s="23" t="s">
-        <v>572</v>
+      <c r="H222" s="3"/>
+      <c r="I222" s="8" t="s">
+        <v>612</v>
       </c>
       <c r="J222" s="4"/>
       <c r="K222" s="4"/>
@@ -9662,23 +9438,21 @@
     </row>
     <row r="223" spans="1:13" ht="13.5" customHeight="1">
       <c r="A223" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B223" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="C223" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="D223" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="E223" s="4"/>
+        <v>603</v>
+      </c>
+      <c r="B223" s="3"/>
+      <c r="C223" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="E223" s="3"/>
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
-      <c r="H223" s="4"/>
+      <c r="H223" s="3"/>
       <c r="I223" s="8" t="s">
-        <v>575</v>
+        <v>615</v>
       </c>
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
@@ -9687,21 +9461,21 @@
     </row>
     <row r="224" spans="1:13" ht="13.5" customHeight="1">
       <c r="A224" s="7" t="s">
-        <v>576</v>
+        <v>616</v>
       </c>
       <c r="B224" s="4"/>
-      <c r="C224" s="7" t="s">
-        <v>577</v>
+      <c r="C224" s="5" t="s">
+        <v>617</v>
       </c>
       <c r="D224" s="15" t="s">
-        <v>578</v>
+        <v>618</v>
       </c>
       <c r="E224" s="4"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
       <c r="I224" s="8" t="s">
-        <v>579</v>
+        <v>619</v>
       </c>
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
@@ -9710,48 +9484,44 @@
     </row>
     <row r="225" spans="1:13" ht="13.5" customHeight="1">
       <c r="A225" s="7" t="s">
-        <v>576</v>
+        <v>616</v>
       </c>
       <c r="B225" s="4"/>
-      <c r="C225" s="7" t="s">
-        <v>580</v>
-      </c>
-      <c r="D225" s="15" t="s">
-        <v>581</v>
-      </c>
-      <c r="E225" s="23" t="s">
-        <v>582</v>
-      </c>
-      <c r="F225" s="23" t="s">
-        <v>582</v>
-      </c>
+      <c r="C225" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="D225" s="36" t="s">
+        <v>621</v>
+      </c>
+      <c r="E225" s="4"/>
+      <c r="F225" s="4"/>
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
-      <c r="I225" s="4"/>
+      <c r="I225" s="8" t="s">
+        <v>622</v>
+      </c>
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
       <c r="L225" s="4"/>
       <c r="M225" s="5"/>
     </row>
     <row r="226" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A226" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="B226" s="24" t="s">
-        <v>584</v>
-      </c>
-      <c r="C226" s="32" t="s">
-        <v>584</v>
-      </c>
-      <c r="D226" s="33" t="s">
-        <v>585</v>
-      </c>
-      <c r="E226" s="4"/>
+      <c r="A226" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="B226" s="38"/>
+      <c r="C226" s="39" t="s">
+        <v>624</v>
+      </c>
+      <c r="D226" s="40" t="s">
+        <v>625</v>
+      </c>
+      <c r="E226" s="41"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
       <c r="H226" s="4"/>
-      <c r="I226" s="23" t="s">
-        <v>586</v>
+      <c r="I226" s="8" t="s">
+        <v>272</v>
       </c>
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
@@ -9759,49 +9529,45 @@
       <c r="M226" s="5"/>
     </row>
     <row r="227" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A227" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="B227" s="24" t="s">
-        <v>584</v>
-      </c>
-      <c r="C227" s="32" t="s">
-        <v>587</v>
-      </c>
-      <c r="D227" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="E227" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="F227" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="G227" s="4"/>
-      <c r="H227" s="4"/>
-      <c r="I227" s="4"/>
+      <c r="A227" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="B227" s="24"/>
+      <c r="C227" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="E227" s="3"/>
+      <c r="F227" s="20"/>
+      <c r="G227" s="20"/>
+      <c r="H227" s="3"/>
+      <c r="I227" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="J227" s="4"/>
       <c r="K227" s="4"/>
       <c r="L227" s="4"/>
       <c r="M227" s="5"/>
     </row>
     <row r="228" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A228" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="B228" s="4"/>
-      <c r="C228" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="D228" s="15" t="s">
-        <v>590</v>
+      <c r="A228" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="B228" s="24"/>
+      <c r="C228" s="39" t="s">
+        <v>626</v>
+      </c>
+      <c r="D228" s="40" t="s">
+        <v>627</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
       <c r="G228" s="4"/>
       <c r="H228" s="4"/>
-      <c r="I228" s="8" t="s">
-        <v>591</v>
+      <c r="I228" s="23" t="s">
+        <v>585</v>
       </c>
       <c r="J228" s="4"/>
       <c r="K228" s="4"/>
@@ -9809,22 +9575,22 @@
       <c r="M228" s="5"/>
     </row>
     <row r="229" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A229" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="B229" s="4"/>
-      <c r="C229" s="7" t="s">
-        <v>592</v>
-      </c>
-      <c r="D229" s="15" t="s">
-        <v>593</v>
-      </c>
-      <c r="E229" s="4"/>
-      <c r="F229" s="4"/>
-      <c r="G229" s="4"/>
-      <c r="H229" s="4"/>
-      <c r="I229" s="10" t="s">
-        <v>594</v>
+      <c r="A229" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="B229" s="38"/>
+      <c r="C229" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="D229" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="E229" s="3"/>
+      <c r="F229" s="20"/>
+      <c r="G229" s="20"/>
+      <c r="H229" s="3"/>
+      <c r="I229" s="8" t="s">
+        <v>227</v>
       </c>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
@@ -9832,22 +9598,22 @@
       <c r="M229" s="5"/>
     </row>
     <row r="230" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A230" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="B230" s="4"/>
-      <c r="C230" s="7" t="s">
-        <v>595</v>
-      </c>
-      <c r="D230" s="15" t="s">
-        <v>596</v>
-      </c>
-      <c r="E230" s="4"/>
-      <c r="F230" s="4"/>
-      <c r="G230" s="4"/>
-      <c r="H230" s="4"/>
+      <c r="A230" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="B230" s="38"/>
+      <c r="C230" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D230" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E230" s="3"/>
+      <c r="F230" s="20"/>
+      <c r="G230" s="20"/>
+      <c r="H230" s="3"/>
       <c r="I230" s="8" t="s">
-        <v>597</v>
+        <v>251</v>
       </c>
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
@@ -9855,22 +9621,24 @@
       <c r="M230" s="5"/>
     </row>
     <row r="231" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A231" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="B231" s="4"/>
-      <c r="C231" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="D231" s="15" t="s">
-        <v>599</v>
+      <c r="A231" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="B231" s="38" t="s">
+        <v>628</v>
+      </c>
+      <c r="C231" s="39" t="s">
+        <v>629</v>
+      </c>
+      <c r="D231" s="40" t="s">
+        <v>630</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="4"/>
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
-      <c r="I231" s="8" t="s">
-        <v>600</v>
+      <c r="I231" s="23" t="s">
+        <v>631</v>
       </c>
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
@@ -9878,45 +9646,49 @@
       <c r="M231" s="5"/>
     </row>
     <row r="232" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A232" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="B232" s="4"/>
-      <c r="C232" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="D232" s="15" t="s">
-        <v>602</v>
-      </c>
-      <c r="E232" s="8" t="s">
-        <v>603</v>
-      </c>
+      <c r="A232" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="B232" s="38" t="s">
+        <v>628</v>
+      </c>
+      <c r="C232" s="39" t="s">
+        <v>632</v>
+      </c>
+      <c r="D232" s="40" t="s">
+        <v>633</v>
+      </c>
+      <c r="E232" s="4"/>
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
       <c r="H232" s="4"/>
-      <c r="I232" s="4"/>
+      <c r="I232" s="23" t="s">
+        <v>634</v>
+      </c>
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
       <c r="L232" s="4"/>
       <c r="M232" s="5"/>
     </row>
     <row r="233" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A233" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="B233" s="4"/>
-      <c r="C233" s="22" t="s">
-        <v>605</v>
-      </c>
-      <c r="D233" s="33" t="s">
-        <v>606</v>
-      </c>
-      <c r="E233" s="5"/>
+      <c r="A233" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="B233" s="38" t="s">
+        <v>628</v>
+      </c>
+      <c r="C233" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="D233" s="40" t="s">
+        <v>635</v>
+      </c>
+      <c r="E233" s="4"/>
       <c r="F233" s="4"/>
       <c r="G233" s="4"/>
       <c r="H233" s="4"/>
       <c r="I233" s="23" t="s">
-        <v>607</v>
+        <v>636</v>
       </c>
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
@@ -9924,305 +9696,195 @@
       <c r="M233" s="5"/>
     </row>
     <row r="234" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A234" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="B234" s="3"/>
-      <c r="C234" s="34" t="s">
-        <v>608</v>
-      </c>
-      <c r="D234" s="35" t="s">
-        <v>609</v>
-      </c>
-      <c r="E234" s="3"/>
+      <c r="A234" s="4"/>
+      <c r="B234" s="4"/>
+      <c r="C234" s="4"/>
+      <c r="D234" s="4"/>
+      <c r="E234" s="4"/>
       <c r="F234" s="4"/>
       <c r="G234" s="4"/>
-      <c r="H234" s="3"/>
-      <c r="I234" s="8" t="s">
-        <v>610</v>
-      </c>
+      <c r="H234" s="4"/>
+      <c r="I234" s="4"/>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
       <c r="L234" s="4"/>
       <c r="M234" s="5"/>
     </row>
     <row r="235" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A235" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="B235" s="3"/>
-      <c r="C235" s="7" t="s">
-        <v>611</v>
-      </c>
-      <c r="D235" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="E235" s="3"/>
+      <c r="A235" s="4"/>
+      <c r="B235" s="4"/>
+      <c r="C235" s="4"/>
+      <c r="D235" s="4"/>
+      <c r="E235" s="4"/>
       <c r="F235" s="4"/>
       <c r="G235" s="4"/>
-      <c r="H235" s="3"/>
-      <c r="I235" s="8" t="s">
-        <v>613</v>
-      </c>
+      <c r="H235" s="4"/>
+      <c r="I235" s="4"/>
       <c r="J235" s="4"/>
       <c r="K235" s="4"/>
       <c r="L235" s="4"/>
       <c r="M235" s="5"/>
     </row>
     <row r="236" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A236" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="B236" s="3"/>
-      <c r="C236" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="D236" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="E236" s="3"/>
+      <c r="A236" s="4"/>
+      <c r="B236" s="4"/>
+      <c r="C236" s="4"/>
+      <c r="D236" s="4"/>
+      <c r="E236" s="4"/>
       <c r="F236" s="4"/>
       <c r="G236" s="4"/>
-      <c r="H236" s="3"/>
-      <c r="I236" s="8" t="s">
-        <v>616</v>
-      </c>
+      <c r="H236" s="4"/>
+      <c r="I236" s="4"/>
       <c r="J236" s="4"/>
       <c r="K236" s="4"/>
       <c r="L236" s="4"/>
       <c r="M236" s="5"/>
     </row>
     <row r="237" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A237" s="7" t="s">
-        <v>617</v>
-      </c>
+      <c r="A237" s="4"/>
       <c r="B237" s="4"/>
-      <c r="C237" s="5" t="s">
-        <v>618</v>
-      </c>
-      <c r="D237" s="15" t="s">
-        <v>619</v>
-      </c>
+      <c r="C237" s="4"/>
+      <c r="D237" s="4"/>
       <c r="E237" s="4"/>
       <c r="F237" s="4"/>
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
-      <c r="I237" s="8" t="s">
-        <v>620</v>
-      </c>
+      <c r="I237" s="4"/>
       <c r="J237" s="4"/>
       <c r="K237" s="4"/>
       <c r="L237" s="4"/>
       <c r="M237" s="5"/>
     </row>
     <row r="238" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A238" s="7" t="s">
-        <v>617</v>
-      </c>
+      <c r="A238" s="4"/>
       <c r="B238" s="4"/>
-      <c r="C238" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="D238" s="36" t="s">
-        <v>622</v>
-      </c>
+      <c r="C238" s="4"/>
+      <c r="D238" s="4"/>
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
-      <c r="I238" s="8" t="s">
-        <v>623</v>
-      </c>
+      <c r="I238" s="4"/>
       <c r="J238" s="4"/>
       <c r="K238" s="4"/>
       <c r="L238" s="4"/>
       <c r="M238" s="5"/>
     </row>
     <row r="239" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A239" s="37" t="s">
-        <v>624</v>
-      </c>
-      <c r="B239" s="38"/>
-      <c r="C239" s="39" t="s">
-        <v>625</v>
-      </c>
-      <c r="D239" s="40" t="s">
-        <v>626</v>
-      </c>
-      <c r="E239" s="41"/>
+      <c r="A239" s="4"/>
+      <c r="B239" s="4"/>
+      <c r="C239" s="4"/>
+      <c r="D239" s="4"/>
+      <c r="E239" s="4"/>
       <c r="F239" s="4"/>
       <c r="G239" s="4"/>
       <c r="H239" s="4"/>
-      <c r="I239" s="8" t="s">
-        <v>273</v>
-      </c>
+      <c r="I239" s="4"/>
       <c r="J239" s="4"/>
       <c r="K239" s="4"/>
       <c r="L239" s="4"/>
       <c r="M239" s="5"/>
     </row>
     <row r="240" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A240" s="37" t="s">
-        <v>624</v>
-      </c>
-      <c r="B240" s="24"/>
-      <c r="C240" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="D240" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="E240" s="3"/>
-      <c r="F240" s="20"/>
-      <c r="G240" s="20"/>
-      <c r="H240" s="3"/>
-      <c r="I240" s="8" t="s">
-        <v>261</v>
-      </c>
+      <c r="A240" s="4"/>
+      <c r="B240" s="4"/>
+      <c r="C240" s="4"/>
+      <c r="D240" s="4"/>
+      <c r="E240" s="4"/>
+      <c r="F240" s="4"/>
+      <c r="G240" s="4"/>
+      <c r="H240" s="4"/>
+      <c r="I240" s="4"/>
       <c r="J240" s="4"/>
       <c r="K240" s="4"/>
       <c r="L240" s="4"/>
       <c r="M240" s="5"/>
     </row>
     <row r="241" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A241" s="37" t="s">
-        <v>624</v>
-      </c>
-      <c r="B241" s="24"/>
-      <c r="C241" s="39" t="s">
-        <v>627</v>
-      </c>
-      <c r="D241" s="40" t="s">
-        <v>628</v>
-      </c>
+      <c r="A241" s="4"/>
+      <c r="B241" s="4"/>
+      <c r="C241" s="4"/>
+      <c r="D241" s="4"/>
       <c r="E241" s="4"/>
       <c r="F241" s="4"/>
       <c r="G241" s="4"/>
       <c r="H241" s="4"/>
-      <c r="I241" s="23" t="s">
-        <v>586</v>
-      </c>
+      <c r="I241" s="4"/>
       <c r="J241" s="4"/>
       <c r="K241" s="4"/>
       <c r="L241" s="4"/>
       <c r="M241" s="5"/>
     </row>
     <row r="242" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A242" s="37" t="s">
-        <v>624</v>
-      </c>
-      <c r="B242" s="38"/>
-      <c r="C242" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="D242" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="E242" s="3"/>
-      <c r="F242" s="20"/>
-      <c r="G242" s="20"/>
-      <c r="H242" s="3"/>
-      <c r="I242" s="8" t="s">
-        <v>228</v>
-      </c>
+      <c r="A242" s="4"/>
+      <c r="B242" s="4"/>
+      <c r="C242" s="4"/>
+      <c r="D242" s="4"/>
+      <c r="E242" s="4"/>
+      <c r="F242" s="4"/>
+      <c r="G242" s="4"/>
+      <c r="H242" s="4"/>
+      <c r="I242" s="4"/>
       <c r="J242" s="4"/>
       <c r="K242" s="4"/>
       <c r="L242" s="4"/>
       <c r="M242" s="5"/>
     </row>
     <row r="243" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A243" s="37" t="s">
-        <v>624</v>
-      </c>
-      <c r="B243" s="38"/>
-      <c r="C243" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D243" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E243" s="3"/>
-      <c r="F243" s="20"/>
-      <c r="G243" s="20"/>
-      <c r="H243" s="3"/>
-      <c r="I243" s="8" t="s">
-        <v>252</v>
-      </c>
+      <c r="A243" s="4"/>
+      <c r="B243" s="4"/>
+      <c r="C243" s="4"/>
+      <c r="D243" s="4"/>
+      <c r="E243" s="4"/>
+      <c r="F243" s="4"/>
+      <c r="G243" s="4"/>
+      <c r="H243" s="4"/>
+      <c r="I243" s="4"/>
       <c r="J243" s="4"/>
       <c r="K243" s="4"/>
       <c r="L243" s="4"/>
       <c r="M243" s="5"/>
     </row>
     <row r="244" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A244" s="37" t="s">
-        <v>624</v>
-      </c>
-      <c r="B244" s="38" t="s">
-        <v>629</v>
-      </c>
-      <c r="C244" s="39" t="s">
-        <v>630</v>
-      </c>
-      <c r="D244" s="40" t="s">
-        <v>631</v>
-      </c>
+      <c r="A244" s="4"/>
+      <c r="B244" s="4"/>
+      <c r="C244" s="4"/>
+      <c r="D244" s="4"/>
       <c r="E244" s="4"/>
       <c r="F244" s="4"/>
       <c r="G244" s="4"/>
       <c r="H244" s="4"/>
-      <c r="I244" s="23" t="s">
-        <v>632</v>
-      </c>
+      <c r="I244" s="4"/>
       <c r="J244" s="4"/>
       <c r="K244" s="4"/>
       <c r="L244" s="4"/>
       <c r="M244" s="5"/>
     </row>
     <row r="245" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A245" s="37" t="s">
-        <v>624</v>
-      </c>
-      <c r="B245" s="38" t="s">
-        <v>629</v>
-      </c>
-      <c r="C245" s="39" t="s">
-        <v>633</v>
-      </c>
-      <c r="D245" s="40" t="s">
-        <v>634</v>
-      </c>
+      <c r="A245" s="4"/>
+      <c r="B245" s="4"/>
+      <c r="C245" s="4"/>
+      <c r="D245" s="4"/>
       <c r="E245" s="4"/>
       <c r="F245" s="4"/>
       <c r="G245" s="4"/>
       <c r="H245" s="4"/>
-      <c r="I245" s="23" t="s">
-        <v>635</v>
-      </c>
+      <c r="I245" s="4"/>
       <c r="J245" s="4"/>
       <c r="K245" s="4"/>
       <c r="L245" s="4"/>
       <c r="M245" s="5"/>
     </row>
     <row r="246" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A246" s="37" t="s">
-        <v>624</v>
-      </c>
-      <c r="B246" s="38" t="s">
-        <v>629</v>
-      </c>
-      <c r="C246" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="D246" s="40" t="s">
-        <v>636</v>
-      </c>
+      <c r="A246" s="4"/>
+      <c r="B246" s="4"/>
+      <c r="C246" s="4"/>
+      <c r="D246" s="4"/>
       <c r="E246" s="4"/>
       <c r="F246" s="4"/>
       <c r="G246" s="4"/>
       <c r="H246" s="4"/>
-      <c r="I246" s="23" t="s">
-        <v>637</v>
-      </c>
+      <c r="I246" s="4"/>
       <c r="J246" s="4"/>
       <c r="K246" s="4"/>
       <c r="L246" s="4"/>
@@ -12838,216 +12500,34 @@
       <c r="L420" s="4"/>
       <c r="M420" s="5"/>
     </row>
-    <row r="421" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A421" s="4"/>
-      <c r="B421" s="4"/>
-      <c r="C421" s="4"/>
-      <c r="D421" s="4"/>
-      <c r="E421" s="4"/>
-      <c r="F421" s="4"/>
-      <c r="G421" s="4"/>
-      <c r="H421" s="4"/>
-      <c r="I421" s="4"/>
-      <c r="J421" s="4"/>
-      <c r="K421" s="4"/>
-      <c r="L421" s="4"/>
-      <c r="M421" s="5"/>
-    </row>
-    <row r="422" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A422" s="4"/>
-      <c r="B422" s="4"/>
-      <c r="C422" s="4"/>
-      <c r="D422" s="4"/>
-      <c r="E422" s="4"/>
-      <c r="F422" s="4"/>
-      <c r="G422" s="4"/>
-      <c r="H422" s="4"/>
-      <c r="I422" s="4"/>
-      <c r="J422" s="4"/>
-      <c r="K422" s="4"/>
-      <c r="L422" s="4"/>
-      <c r="M422" s="5"/>
-    </row>
-    <row r="423" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A423" s="4"/>
-      <c r="B423" s="4"/>
-      <c r="C423" s="4"/>
-      <c r="D423" s="4"/>
-      <c r="E423" s="4"/>
-      <c r="F423" s="4"/>
-      <c r="G423" s="4"/>
-      <c r="H423" s="4"/>
-      <c r="I423" s="4"/>
-      <c r="J423" s="4"/>
-      <c r="K423" s="4"/>
-      <c r="L423" s="4"/>
-      <c r="M423" s="5"/>
-    </row>
-    <row r="424" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A424" s="4"/>
-      <c r="B424" s="4"/>
-      <c r="C424" s="4"/>
-      <c r="D424" s="4"/>
-      <c r="E424" s="4"/>
-      <c r="F424" s="4"/>
-      <c r="G424" s="4"/>
-      <c r="H424" s="4"/>
-      <c r="I424" s="4"/>
-      <c r="J424" s="4"/>
-      <c r="K424" s="4"/>
-      <c r="L424" s="4"/>
-      <c r="M424" s="5"/>
-    </row>
-    <row r="425" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A425" s="4"/>
-      <c r="B425" s="4"/>
-      <c r="C425" s="4"/>
-      <c r="D425" s="4"/>
-      <c r="E425" s="4"/>
-      <c r="F425" s="4"/>
-      <c r="G425" s="4"/>
-      <c r="H425" s="4"/>
-      <c r="I425" s="4"/>
-      <c r="J425" s="4"/>
-      <c r="K425" s="4"/>
-      <c r="L425" s="4"/>
-      <c r="M425" s="5"/>
-    </row>
-    <row r="426" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A426" s="4"/>
-      <c r="B426" s="4"/>
-      <c r="C426" s="4"/>
-      <c r="D426" s="4"/>
-      <c r="E426" s="4"/>
-      <c r="F426" s="4"/>
-      <c r="G426" s="4"/>
-      <c r="H426" s="4"/>
-      <c r="I426" s="4"/>
-      <c r="J426" s="4"/>
-      <c r="K426" s="4"/>
-      <c r="L426" s="4"/>
-      <c r="M426" s="5"/>
-    </row>
-    <row r="427" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A427" s="4"/>
-      <c r="B427" s="4"/>
-      <c r="C427" s="4"/>
-      <c r="D427" s="4"/>
-      <c r="E427" s="4"/>
-      <c r="F427" s="4"/>
-      <c r="G427" s="4"/>
-      <c r="H427" s="4"/>
-      <c r="I427" s="4"/>
-      <c r="J427" s="4"/>
-      <c r="K427" s="4"/>
-      <c r="L427" s="4"/>
-      <c r="M427" s="5"/>
-    </row>
-    <row r="428" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A428" s="4"/>
-      <c r="B428" s="4"/>
-      <c r="C428" s="4"/>
-      <c r="D428" s="4"/>
-      <c r="E428" s="4"/>
-      <c r="F428" s="4"/>
-      <c r="G428" s="4"/>
-      <c r="H428" s="4"/>
-      <c r="I428" s="4"/>
-      <c r="J428" s="4"/>
-      <c r="K428" s="4"/>
-      <c r="L428" s="4"/>
-      <c r="M428" s="5"/>
-    </row>
-    <row r="429" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A429" s="4"/>
-      <c r="B429" s="4"/>
-      <c r="C429" s="4"/>
-      <c r="D429" s="4"/>
-      <c r="E429" s="4"/>
-      <c r="F429" s="4"/>
-      <c r="G429" s="4"/>
-      <c r="H429" s="4"/>
-      <c r="I429" s="4"/>
-      <c r="J429" s="4"/>
-      <c r="K429" s="4"/>
-      <c r="L429" s="4"/>
-      <c r="M429" s="5"/>
-    </row>
-    <row r="430" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A430" s="4"/>
-      <c r="B430" s="4"/>
-      <c r="C430" s="4"/>
-      <c r="D430" s="4"/>
-      <c r="E430" s="4"/>
-      <c r="F430" s="4"/>
-      <c r="G430" s="4"/>
-      <c r="H430" s="4"/>
-      <c r="I430" s="4"/>
-      <c r="J430" s="4"/>
-      <c r="K430" s="4"/>
-      <c r="L430" s="4"/>
-      <c r="M430" s="5"/>
-    </row>
-    <row r="431" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A431" s="4"/>
-      <c r="B431" s="4"/>
-      <c r="C431" s="4"/>
-      <c r="D431" s="4"/>
-      <c r="E431" s="4"/>
-      <c r="F431" s="4"/>
-      <c r="G431" s="4"/>
-      <c r="H431" s="4"/>
-      <c r="I431" s="4"/>
-      <c r="J431" s="4"/>
-      <c r="K431" s="4"/>
-      <c r="L431" s="4"/>
-      <c r="M431" s="5"/>
-    </row>
-    <row r="432" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A432" s="4"/>
-      <c r="B432" s="4"/>
-      <c r="C432" s="4"/>
-      <c r="D432" s="4"/>
-      <c r="E432" s="4"/>
-      <c r="F432" s="4"/>
-      <c r="G432" s="4"/>
-      <c r="H432" s="4"/>
-      <c r="I432" s="4"/>
-      <c r="J432" s="4"/>
-      <c r="K432" s="4"/>
-      <c r="L432" s="4"/>
-      <c r="M432" s="5"/>
-    </row>
-    <row r="433" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A433" s="4"/>
-      <c r="B433" s="4"/>
-      <c r="C433" s="4"/>
-      <c r="D433" s="4"/>
-      <c r="E433" s="4"/>
-      <c r="F433" s="4"/>
-      <c r="G433" s="4"/>
-      <c r="H433" s="4"/>
-      <c r="I433" s="4"/>
-      <c r="J433" s="4"/>
-      <c r="K433" s="4"/>
-      <c r="L433" s="4"/>
-      <c r="M433" s="5"/>
-    </row>
-    <row r="434" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="435" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="436" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="437" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="438" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="439" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="440" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="441" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="442" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="443" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="444" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="445" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="446" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="447" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="448" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="421" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="422" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="423" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="424" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="425" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="426" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="427" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="428" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="429" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="430" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="431" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="432" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
     <row r="449" ht="15.75" customHeight="1"/>
     <row r="450" ht="15.75" customHeight="1"/>
     <row r="451" ht="15.75" customHeight="1"/>
@@ -13617,19 +13097,6 @@
     <row r="1015" ht="15.75" customHeight="1"/>
     <row r="1016" ht="15.75" customHeight="1"/>
     <row r="1017" ht="15.75" customHeight="1"/>
-    <row r="1018" ht="15.75" customHeight="1"/>
-    <row r="1019" ht="15.75" customHeight="1"/>
-    <row r="1020" ht="15.75" customHeight="1"/>
-    <row r="1021" ht="15.75" customHeight="1"/>
-    <row r="1022" ht="15.75" customHeight="1"/>
-    <row r="1023" ht="15.75" customHeight="1"/>
-    <row r="1024" ht="15.75" customHeight="1"/>
-    <row r="1025" ht="15.75" customHeight="1"/>
-    <row r="1026" ht="15.75" customHeight="1"/>
-    <row r="1027" ht="15.75" customHeight="1"/>
-    <row r="1028" ht="15.75" customHeight="1"/>
-    <row r="1029" ht="15.75" customHeight="1"/>
-    <row r="1030" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="14"/>
   <hyperlinks>
@@ -13646,223 +13113,200 @@
     <hyperlink ref="D13" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
     <hyperlink ref="D14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="D15" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D16" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="D17" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="D18" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="D19" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="D20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D21" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="D22" r:id="rId20" display="https://tileserver.geolonia.com/yaizu-smartmap-shindobunpu/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpbmRvYnVucHV8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zaGluZG9idW5wdS0wMUpGWTlGRzE1VDdCSlhRUTJQU1k4TlYzTiP8BmltEvFgZ7AbtdKg7djJVPCvEaVsVGPshOWpe6gKgg&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D23" r:id="rId21" display="https://tileserver.geolonia.com/yaizu-smartmap-ekijyouka/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtZWtpanlvdWthfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtZWtpanlvdWthLTAxSkcwNTZOWFhRQk1UTkpGQUhUOFhNWkVaI3kGu2YpRPXXVDMk0_MykR8ek8rKaS9gxzJwC5M4jj0c&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="D24" r:id="rId22" display="https://tileserver.geolonia.com/yaizu-smartmap-4th-tsunami-shinsui/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtNHRoLXRzdW5hbWktc2hpbnN1aXxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLTR0aC10c3VuYW1pLXNoaW5zdWktMDFKRzFRRjFTQ1hLNUhaRzJZWkRGSk1XM1gjLfrbRh2tvRwxB46BnVq1eJAP4L5jhCAiR9miZwWJ3hk&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="D25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="D26" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="D27" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="D28" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="D29" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D30" r:id="rId28" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWFsbF9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNNDZIR1hZR0swUUpNTjNZUDRLNlkjPCK5r3Br4iBJ6gs43vYJ3CP6pHMrS3prdRz8lVj3KiE&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="D31" r:id="rId29" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1vb2lnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU05U0dKUVZQNjBTTVE5MzBBNVBTUyN4ZFSCYWcG-VtbFmW8f7esVIHQGyyB-N_-8c-5sjW6lQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="D32" r:id="rId30" display="https://tileserver.geolonia.com/yaizu-smartmap-takakusagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdGFrYWt1c2FnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXRha2FrdXNhZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQUJIQTdUVjRYWEE5QTkzR0FHWkgjimM1TsDVEkqLCSi4wpFK8q5JcfTnTIY6i3i6r57CX0A&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D33" r:id="rId31" display="https://tileserver.geolonia.com/yaizu-smartmap-ishiwakigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaXNoaXdha2lnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWlzaGl3YWtpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOTkyRkZLRFoxV0ZZMDVXOUg1RTUjdD9kb3q6n-edazGHScn5Z_BB2dOtDwwBL0WYUslrNz0&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="D34" r:id="rId32" display="https://tileserver.geolonia.com/yaizu-smartmap-asahinagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTkyN0VEWVA2RzZHWlFENkZHWFdCI5apEATwxiJ5O-u8vrCa_Aq8i588yYu99pyHCD-6cnJD&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="D35" r:id="rId33" display="https://tileserver.geolonia.com/yaizu-smartmap-hanashigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTk1UFdES1ZZUUdFNjg1RkRFWDA5IzJO1Gu9VFWg7akAUXsx62QIvoMMD3bV0B99FamjVRWH&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="D36" r:id="rId34" display="https://tileserver.geolonia.com/yaizu-smartmap-umedagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdW1lZGFnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXVtZWRhZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQU4wNUFFQ0c1Q0dXNFE3VE5GVFkjVEgHYpNTdDz0-WFNj93-ZwFbTyu6Z0d2wk2iM9R5u7Q&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="D37" r:id="rId35" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TUE0RDdKMFZIS0o4Sk1WOTJOTTVBIxuMCm_quVhuckWPNF1obvQO2eCdJtGYUMEVHn3gRKKK&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="D38" r:id="rId36" display="https://tileserver.geolonia.com/yaizu-smartmap-uchisetotanigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdWNoaXNldG90YW5pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC11Y2hpc2V0b3RhbmlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BSjVRSDkwVEg4OUtHV1NDWUQ1WSMydwZLx6k83TZLytgIgc_DPtLeFNHJTqwf9gZAhWFbfA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="D39" r:id="rId37" display="https://tileserver.geolonia.com/yaizu-smartmap-koishigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta29pc2hpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1rb2lzaGlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU05RjdYWU1ZNkpQM0dKTjg5NkhXNiNYOsA7y7e0r_Iu0xpEQOEsj_X5p1-ruM4dQIoVYOSRVw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="D40" r:id="rId38" display="https://tileserver.geolonia.com/yaizu-smartmap-kuroishigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta3Vyb2lzaGlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWt1cm9pc2hpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOU5GNjA3OEs0WUFHQkhXNUhQRFYjLsEzoWos3xapWiBFua2VXJUD5vbReBaMpvfpr_TB3Ng&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="D41" r:id="rId39" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTlKNTROUjlCUVM4QlBWWVc3SzEwI3r7R2_FhpUp13cFLSg7diJ2jHwWVzgQWzKSk7nqnxoQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="D42" r:id="rId40" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC10b2NoaXlhbWFnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BRTlCVDNEWFAxQkdCSjBLNlI2UCOyAh242YqHr6vhWYEoYxNDPOkyFsQGJOX99vXLPs9jvQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="D43" r:id="rId41" display="https://tileserver.geolonia.com/yaizu-smartmap-seanjigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2VhbmppZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zZWFuamlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BMUM5TVJaS0hSVFpTTUJNRU5ITSOLbk41LqC3NJjdsDptQg3a5dUe1-jYrf9Ci_w7me138w&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="D44" r:id="rId42" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXNoaWRhdGFuYWthZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQTg5NjExWUs0M0pKWFhKMzNEQ0sjjXDhElx_Bq-DmgbAZv1rkLWFAJz_mYHzTJ1uT5fEXXE&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="D45" r:id="rId43" display="https://tileserver.geolonia.com/yaizu-smartmap-izumigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaXp1bWlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWl6dW1pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOUMyNEM3NDIzWlA4M0U5MTFaOTIjiZDvCV2809c0N38igMrrlYkjUOlioRRIzO2VhSPcBEU&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="D46" r:id="rId44" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLW90c3V0YW5pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOVhUMUJDMEU1OVMwRUhRQzRRRU4juXpVh3i0MnT59rsmSRi1Y-5Yv9Q2ka273F77i7qhk6M&amp;key=bb4125ebc1ba442da48d3556f1fe13f5_x000a_" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="D47" r:id="rId45" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1hbGxfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVRETjFRNVk2S1E3WTYwV0JSWkVXRiMvFbymz4lH_fdrJRy-jvgwTVw2D13DlzjxNICrb7qY1A&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="D48" r:id="rId46" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyLTAxSko1VERWUkdYNjBLNlFBQTFLM1I5UU5SI3K6_rl11h-EuwrNQ4AE7yQiOLb8PCKqFDOJ4FDRsG-g&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D49" r:id="rId47" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXNldG9nYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjItMDFKSjVURTFZNVRWRTBIVzFWOUFLMzBLRFcji6G-BXNCHGZShICjglWb3w_mWK_NKrvuXH_tI_9nlgQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="D50" r:id="rId48" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWtveWFnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjItMDFKSjVURFJXSldXSkVXUFdESEMzV0sxNTgjf-2T3_0XdWSFLtX6dSNEbLxxCj2IDXBYnWuWoALGMxI&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="D51" r:id="rId49" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyLTAxSko1VEU4NktENUZWU1RGVjE4RDNRVFBUI0UGkE67qVTbtRvaLl2OvOsiZu9Hnd-9AT1ia-ckrXPG&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="D52" r:id="rId50" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zaGlkYXRhbmFrYWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVRFNTUyV0dRWUVTWVdWVkFHNURDUiM6XrMaFpsN_nu69zOxecuTueNyhch7DBXrxCJmaCBV8w&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="D53" r:id="rId51" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1vdHN1dGFuaWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVREWkFYQVcyMktRNEdWVkhOTTQ4USPJeHao4Q6wyWn0IEPkPECr5W-lDwzRh1n7dcRP_rd19Q&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="D54" r:id="rId52" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-duration/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLWR1cmF0aW9ufGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLWR1cmF0aW9uLTAxSkZDMjM2TkNFOEE4WlY1RlpXUTFUNjdQI72n4lnDlqr_qS3dvbGif0AlepOAnvK3E1Vx_MjVLXsc&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="D55" r:id="rId53" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZHxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLW9vaWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWQtMDFKRkMyM0tRRTBOOE02RlJaWlBYWTdNVEsjb6TUQ42ra-hBJK2eSP06FX90ArT2yTi5_X9jzEWntEw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="D56" r:id="rId54" display="https://tileserver.geolonia.com/yaizu-smartmap-asahinagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1hc2FoaW5hZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzQUtEQkFQUkpXMkNKSE45Q0pWNCOv1qiFcrLRZll0zMjGPpeTcM-NM60iPJiH7OxfIPrruw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D57" r:id="rId55" display="https://tileserver.geolonia.com/yaizu-smartmap-hanashigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1oYW5hc2hpZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzRFJBTVYzWFRDUlY0WVJCUUVIUyOyqbE2vnFeS_9BZw94HXS20jBUsE7o_rmOXEyGSp0CYA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="D58" r:id="rId56" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zZXRvZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzVDFETjRKNDZSSENUNkc3VlBGMSM4etkawiLQc6u4jK6mqi1X2xklmi7fEC1D6aIWymyDbA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D59" r:id="rId57" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1rb3lhZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzR1ZZWEFDQzg4MUg3QjlLV1lFOCOfdwjLULNhmI_ow4g0dWNl2dx8qQUUG8aFUeQo_0hXDQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="D60" r:id="rId58" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZHxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXRvY2hpeWFtYWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWQtMDFKRkMyM1pWWVE3MEowUzdaNTZHWkNKRFojC5eX3JK7qasK2odfocPvh5KVdzgW8GfTWFIWWxO0-OY&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="D61" r:id="rId59" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkLTAxSkZDMjNYNFlBNDZLMlQxTVdGMVFWODJaI8I_8TmmNT2ZBas2uO_iuv708Hw-rSmd9df6Iy_TRMzO&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D62" r:id="rId60" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkLTAxSkZDMjNRNENHRURIR1FLNEtGU1lLMzZBI7KZF6uvKMllQBtCXF86Bop_8GzzniSe6NN1Rp0RaowV&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="D63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D64" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="D65" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D66" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="D67" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D68" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="D69" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D70" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="D71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D72" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="D73" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D74" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="D75" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D76" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D77" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D78" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D79" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D80" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D81" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D82" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D83" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D84" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D85" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D86" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D87" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D88" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D89" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D90" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D115" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D121" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D122" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D123" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D124" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D125" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D126" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="D127" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D128" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D129" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D130" r:id="rId102" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="D131" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="D132" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="D133" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="D134" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="D135" r:id="rId107" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="D136" r:id="rId108" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="D137" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="D138" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="D139" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D140" r:id="rId112" display="https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="D141" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="D142" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="D143" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D144" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="D145" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="D146" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="D147" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="D148" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="D149" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D150" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="D151" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="D152" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="D153" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="D154" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="D155" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="D156" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="D157" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="D158" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="D159" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="D160" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="D161" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="D162" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="D163" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="D164" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="D165" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="D166" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="D167" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="D168" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="D169" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="D170" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="D171" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="D172" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="D178" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="D179" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="D180" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="D181" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="D182" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="D183" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="D184" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="D185" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="D186" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="D187" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="D188" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="D189" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="D190" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="D191" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="D192" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="D194" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="D195" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D196" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="D197" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D198" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="D199" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D200" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D201" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D202" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="D203" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D204" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="D205" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D206" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="D207" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D208" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D209" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D210" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D211" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D212" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="D213" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D214" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="D215" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D216" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="D217" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D218" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="D219" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D220" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D221" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D222" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D223" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D224" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D225" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D226" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D228" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D229" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D230" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D231" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D232" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D233" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="D234" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D235" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="D236" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D237" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="D238" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D240" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="D242" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D243" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="H114" r:id="rId207" tooltip="dimgray  #696969" display="https://www.colordic.org/colorsample/1001" xr:uid="{97FCABF6-F58B-4F9A-834E-9678B6A306CC}"/>
-    <hyperlink ref="E114" r:id="rId208" tooltip="dimgray  #696969" display="https://www.colordic.org/colorsample/1001" xr:uid="{230614D3-EFCC-4782-B7F6-D1C1F8CE862A}"/>
-    <hyperlink ref="H113" r:id="rId209" tooltip="khaki  #f0e68c" display="https://www.colordic.org/colorsample/1090" xr:uid="{FBAD9EF9-90D3-4E9F-9AAB-9D9CF309EDE3}"/>
-    <hyperlink ref="E113" r:id="rId210" tooltip="khaki  #f0e68c" display="https://www.colordic.org/colorsample/1090" xr:uid="{37BB103E-8F35-4A8A-919F-4D852F82FC05}"/>
-    <hyperlink ref="H110" r:id="rId211" tooltip="darkorange  #ff8c00" display="https://www.colordic.org/colorsample/1095" xr:uid="{0914380F-8A58-45FD-B9A4-FA9B66AAAA41}"/>
-    <hyperlink ref="E110" r:id="rId212" tooltip="darkorange  #ff8c00" display="https://www.colordic.org/colorsample/1095" xr:uid="{66B0B074-4103-4FC0-9CE0-6C0F3E2CA302}"/>
-    <hyperlink ref="D104" r:id="rId213" xr:uid="{FF3BD575-FE73-48FB-A29B-75817D1BC817}"/>
-    <hyperlink ref="D103" r:id="rId214" xr:uid="{740A7353-663C-40DD-BEC5-D34D2A3DE0B4}"/>
-    <hyperlink ref="D106" r:id="rId215" xr:uid="{A990E518-E683-4550-8AD6-50967E0D7E69}"/>
-    <hyperlink ref="D102" r:id="rId216" xr:uid="{30DD64BF-50A1-416D-B51B-F1EDACD91BA0}"/>
-    <hyperlink ref="D110" r:id="rId217" xr:uid="{3F16F6D6-B4A2-42CF-A13F-17BF09553EAB}"/>
-    <hyperlink ref="D105" r:id="rId218" xr:uid="{5089A3CB-0C3C-4CBE-BEE5-DB2E7E8733F4}"/>
-    <hyperlink ref="D101" r:id="rId219" xr:uid="{2D986A3F-DA2B-4AB0-A387-B05C4587954B}"/>
-    <hyperlink ref="D109" r:id="rId220" xr:uid="{605583FE-206F-474B-AFDE-865FCAFE9308}"/>
-    <hyperlink ref="D108" r:id="rId221" xr:uid="{DD857A5B-11B3-4160-9040-8D1AB025F551}"/>
-    <hyperlink ref="D113" r:id="rId222" xr:uid="{11835446-AC0F-42B4-9B6B-880180A02441}"/>
-    <hyperlink ref="D107" r:id="rId223" xr:uid="{157E47C1-4242-454F-BC61-6571BD7D509F}"/>
-    <hyperlink ref="D114" r:id="rId224" xr:uid="{F40B81F1-F9E3-4149-8568-5E7758BDF06A}"/>
-    <hyperlink ref="H103" r:id="rId225" tooltip="orange  #ffa500" display="https://www.colordic.org/colorsample/1093" xr:uid="{0E50748A-5511-4F08-B700-DECF8CD6293E}"/>
-    <hyperlink ref="E103" r:id="rId226" tooltip="orange  #ffa500" display="https://www.colordic.org/colorsample/1093" xr:uid="{661BF55A-54A8-40C6-B910-46B8500694F4}"/>
-    <hyperlink ref="H101" r:id="rId227" tooltip="deepskyblue  #00bfff" display="https://www.colordic.org/colorsample/1043" xr:uid="{38FC15DB-1677-4C70-B9CE-25256B391F19}"/>
-    <hyperlink ref="E101" r:id="rId228" tooltip="deepskyblue  #00bfff" display="https://www.colordic.org/colorsample/1043" xr:uid="{E285B9B4-6649-417B-BACA-C000D239641A}"/>
-    <hyperlink ref="D111" r:id="rId229" xr:uid="{532AD0A0-A331-4708-93CE-A31170BD661C}"/>
-    <hyperlink ref="D112" r:id="rId230" xr:uid="{9495A3C4-6D47-42AF-9398-148988A0C189}"/>
+    <hyperlink ref="D17" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="D18" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="D19" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="D20" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="D21" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="D22" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="D23" r:id="rId20" display="https://tileserver.geolonia.com/yaizu-smartmap-shindobunpu/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpbmRvYnVucHV8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zaGluZG9idW5wdS0wMUpGWTlGRzE1VDdCSlhRUTJQU1k4TlYzTiP8BmltEvFgZ7AbtdKg7djJVPCvEaVsVGPshOWpe6gKgg&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D24" r:id="rId21" display="https://tileserver.geolonia.com/yaizu-smartmap-ekijyouka/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtZWtpanlvdWthfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtZWtpanlvdWthLTAxSkcwNTZOWFhRQk1UTkpGQUhUOFhNWkVaI3kGu2YpRPXXVDMk0_MykR8ek8rKaS9gxzJwC5M4jj0c&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="D25" r:id="rId22" display="https://tileserver.geolonia.com/yaizu-smartmap-4th-tsunami-shinsui/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtNHRoLXRzdW5hbWktc2hpbnN1aXxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLTR0aC10c3VuYW1pLXNoaW5zdWktMDFKRzFRRjFTQ1hLNUhaRzJZWkRGSk1XM1gjLfrbRh2tvRwxB46BnVq1eJAP4L5jhCAiR9miZwWJ3hk&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="D26" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="D27" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="D28" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="D29" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="D30" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D31" r:id="rId28" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWFsbF9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNNDZIR1hZR0swUUpNTjNZUDRLNlkjPCK5r3Br4iBJ6gs43vYJ3CP6pHMrS3prdRz8lVj3KiE&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="D32" r:id="rId29" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1vb2lnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU05U0dKUVZQNjBTTVE5MzBBNVBTUyN4ZFSCYWcG-VtbFmW8f7esVIHQGyyB-N_-8c-5sjW6lQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="D33" r:id="rId30" display="https://tileserver.geolonia.com/yaizu-smartmap-takakusagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdGFrYWt1c2FnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXRha2FrdXNhZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQUJIQTdUVjRYWEE5QTkzR0FHWkgjimM1TsDVEkqLCSi4wpFK8q5JcfTnTIY6i3i6r57CX0A&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D34" r:id="rId31" display="https://tileserver.geolonia.com/yaizu-smartmap-ishiwakigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaXNoaXdha2lnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWlzaGl3YWtpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOTkyRkZLRFoxV0ZZMDVXOUg1RTUjdD9kb3q6n-edazGHScn5Z_BB2dOtDwwBL0WYUslrNz0&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="D35" r:id="rId32" display="https://tileserver.geolonia.com/yaizu-smartmap-asahinagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTkyN0VEWVA2RzZHWlFENkZHWFdCI5apEATwxiJ5O-u8vrCa_Aq8i588yYu99pyHCD-6cnJD&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="D36" r:id="rId33" display="https://tileserver.geolonia.com/yaizu-smartmap-hanashigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTk1UFdES1ZZUUdFNjg1RkRFWDA5IzJO1Gu9VFWg7akAUXsx62QIvoMMD3bV0B99FamjVRWH&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="D37" r:id="rId34" display="https://tileserver.geolonia.com/yaizu-smartmap-umedagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdW1lZGFnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXVtZWRhZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQU4wNUFFQ0c1Q0dXNFE3VE5GVFkjVEgHYpNTdDz0-WFNj93-ZwFbTyu6Z0d2wk2iM9R5u7Q&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="D38" r:id="rId35" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TUE0RDdKMFZIS0o4Sk1WOTJOTTVBIxuMCm_quVhuckWPNF1obvQO2eCdJtGYUMEVHn3gRKKK&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="D39" r:id="rId36" display="https://tileserver.geolonia.com/yaizu-smartmap-uchisetotanigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdWNoaXNldG90YW5pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC11Y2hpc2V0b3RhbmlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BSjVRSDkwVEg4OUtHV1NDWUQ1WSMydwZLx6k83TZLytgIgc_DPtLeFNHJTqwf9gZAhWFbfA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="D40" r:id="rId37" display="https://tileserver.geolonia.com/yaizu-smartmap-koishigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta29pc2hpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1rb2lzaGlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU05RjdYWU1ZNkpQM0dKTjg5NkhXNiNYOsA7y7e0r_Iu0xpEQOEsj_X5p1-ruM4dQIoVYOSRVw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="D41" r:id="rId38" display="https://tileserver.geolonia.com/yaizu-smartmap-kuroishigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta3Vyb2lzaGlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWt1cm9pc2hpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOU5GNjA3OEs0WUFHQkhXNUhQRFYjLsEzoWos3xapWiBFua2VXJUD5vbReBaMpvfpr_TB3Ng&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="D42" r:id="rId39" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTlKNTROUjlCUVM4QlBWWVc3SzEwI3r7R2_FhpUp13cFLSg7diJ2jHwWVzgQWzKSk7nqnxoQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="D43" r:id="rId40" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC10b2NoaXlhbWFnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BRTlCVDNEWFAxQkdCSjBLNlI2UCOyAh242YqHr6vhWYEoYxNDPOkyFsQGJOX99vXLPs9jvQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="D44" r:id="rId41" display="https://tileserver.geolonia.com/yaizu-smartmap-seanjigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2VhbmppZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zZWFuamlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BMUM5TVJaS0hSVFpTTUJNRU5ITSOLbk41LqC3NJjdsDptQg3a5dUe1-jYrf9Ci_w7me138w&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="D45" r:id="rId42" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXNoaWRhdGFuYWthZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQTg5NjExWUs0M0pKWFhKMzNEQ0sjjXDhElx_Bq-DmgbAZv1rkLWFAJz_mYHzTJ1uT5fEXXE&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="D46" r:id="rId43" display="https://tileserver.geolonia.com/yaizu-smartmap-izumigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaXp1bWlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWl6dW1pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOUMyNEM3NDIzWlA4M0U5MTFaOTIjiZDvCV2809c0N38igMrrlYkjUOlioRRIzO2VhSPcBEU&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="D47" r:id="rId44" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLW90c3V0YW5pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOVhUMUJDMEU1OVMwRUhRQzRRRU4juXpVh3i0MnT59rsmSRi1Y-5Yv9Q2ka273F77i7qhk6M&amp;key=bb4125ebc1ba442da48d3556f1fe13f5_x000a_" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="D48" r:id="rId45" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1hbGxfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVRETjFRNVk2S1E3WTYwV0JSWkVXRiMvFbymz4lH_fdrJRy-jvgwTVw2D13DlzjxNICrb7qY1A&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="D49" r:id="rId46" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyLTAxSko1VERWUkdYNjBLNlFBQTFLM1I5UU5SI3K6_rl11h-EuwrNQ4AE7yQiOLb8PCKqFDOJ4FDRsG-g&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D50" r:id="rId47" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXNldG9nYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjItMDFKSjVURTFZNVRWRTBIVzFWOUFLMzBLRFcji6G-BXNCHGZShICjglWb3w_mWK_NKrvuXH_tI_9nlgQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="D51" r:id="rId48" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWtveWFnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjItMDFKSjVURFJXSldXSkVXUFdESEMzV0sxNTgjf-2T3_0XdWSFLtX6dSNEbLxxCj2IDXBYnWuWoALGMxI&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="D52" r:id="rId49" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyLTAxSko1VEU4NktENUZWU1RGVjE4RDNRVFBUI0UGkE67qVTbtRvaLl2OvOsiZu9Hnd-9AT1ia-ckrXPG&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="D53" r:id="rId50" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zaGlkYXRhbmFrYWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVRFNTUyV0dRWUVTWVdWVkFHNURDUiM6XrMaFpsN_nu69zOxecuTueNyhch7DBXrxCJmaCBV8w&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="D54" r:id="rId51" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1vdHN1dGFuaWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVREWkFYQVcyMktRNEdWVkhOTTQ4USPJeHao4Q6wyWn0IEPkPECr5W-lDwzRh1n7dcRP_rd19Q&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="D55" r:id="rId52" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-duration/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLWR1cmF0aW9ufGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLWR1cmF0aW9uLTAxSkZDMjM2TkNFOEE4WlY1RlpXUTFUNjdQI72n4lnDlqr_qS3dvbGif0AlepOAnvK3E1Vx_MjVLXsc&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="D56" r:id="rId53" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZHxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLW9vaWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWQtMDFKRkMyM0tRRTBOOE02RlJaWlBYWTdNVEsjb6TUQ42ra-hBJK2eSP06FX90ArT2yTi5_X9jzEWntEw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="D57" r:id="rId54" display="https://tileserver.geolonia.com/yaizu-smartmap-asahinagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1hc2FoaW5hZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzQUtEQkFQUkpXMkNKSE45Q0pWNCOv1qiFcrLRZll0zMjGPpeTcM-NM60iPJiH7OxfIPrruw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D58" r:id="rId55" display="https://tileserver.geolonia.com/yaizu-smartmap-hanashigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1oYW5hc2hpZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzRFJBTVYzWFRDUlY0WVJCUUVIUyOyqbE2vnFeS_9BZw94HXS20jBUsE7o_rmOXEyGSp0CYA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="D59" r:id="rId56" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zZXRvZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzVDFETjRKNDZSSENUNkc3VlBGMSM4etkawiLQc6u4jK6mqi1X2xklmi7fEC1D6aIWymyDbA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D60" r:id="rId57" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1rb3lhZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzR1ZZWEFDQzg4MUg3QjlLV1lFOCOfdwjLULNhmI_ow4g0dWNl2dx8qQUUG8aFUeQo_0hXDQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="D61" r:id="rId58" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZHxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXRvY2hpeWFtYWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWQtMDFKRkMyM1pWWVE3MEowUzdaNTZHWkNKRFojC5eX3JK7qasK2odfocPvh5KVdzgW8GfTWFIWWxO0-OY&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="D62" r:id="rId59" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkLTAxSkZDMjNYNFlBNDZLMlQxTVdGMVFWODJaI8I_8TmmNT2ZBas2uO_iuv708Hw-rSmd9df6Iy_TRMzO&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D63" r:id="rId60" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkLTAxSkZDMjNRNENHRURIR1FLNEtGU1lLMzZBI7KZF6uvKMllQBtCXF86Bop_8GzzniSe6NN1Rp0RaowV&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="D64" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="D65" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="D66" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D67" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="D68" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="D69" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="D70" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="D71" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="D72" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="D73" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="D74" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="D75" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D76" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="D77" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D78" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D79" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D80" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D81" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D82" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D83" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D84" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D85" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D86" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D87" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D88" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D89" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D90" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D91" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D92" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D93" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D94" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D102" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D108" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D109" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D110" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D111" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D112" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="D113" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="D114" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="D115" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D116" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="D117" r:id="rId102" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="D118" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="D119" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="D120" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="D121" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="D122" r:id="rId107" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="D123" r:id="rId108" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="D124" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="D125" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="D126" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="D127" r:id="rId112" display="https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="D128" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="D129" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="D130" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="D131" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="D132" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="D133" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="D134" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="D135" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="D136" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="D137" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="D138" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="D139" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="D140" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="D141" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="D142" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="D143" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="D144" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="D145" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="D146" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="D147" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="D148" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="D149" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="D150" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="D151" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="D152" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="D153" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="D154" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="D155" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="D156" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="D157" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="D158" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="D159" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="D165" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="D166" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="D167" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="D168" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="D169" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="D170" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="D171" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="D172" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="D173" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="D174" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="D175" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="D176" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="D177" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="D178" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="D179" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="D181" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="D182" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="D183" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="D184" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="D185" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="D186" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="D187" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="D188" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="D189" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="D190" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="D191" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="D192" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="D193" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="D194" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="D195" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="D196" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="D197" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="D198" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="D199" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="D200" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="D201" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="D202" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="D203" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="D204" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="D205" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="D206" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="D207" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D208" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D209" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D210" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D211" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D212" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D213" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D215" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D216" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D217" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D218" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D219" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D220" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="D221" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="D222" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="D223" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="D224" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="D225" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="D227" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="D229" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="D230" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="D16" r:id="rId207" xr:uid="{101A33D7-B7BA-422E-B2FC-342D5148D1EA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dx-user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621D0C2E-847A-41E9-86DC-53C1212CC409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAC6FEA-A2EA-48AB-A828-A864C0D55A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="647">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -3201,6 +3201,26 @@
   <si>
     <t>高潮浸水想定区域（浸水区域及び浸水深）</t>
     <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>子どもを守る家</t>
+    <rPh sb="0" eb="1">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マモ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>イエ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E5%AD%90%E3%81%A9%E3%82%82%E3%82%92%E5%AE%88%E3%82%8B%E5%AE%B6/tiles.json</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>randoseru</t>
   </si>
 </sst>
 </file>
@@ -3826,7 +3846,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M1017"/>
+  <dimension ref="A1:M1018"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -9056,21 +9076,19 @@
       <c r="A207" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="B207" s="7" t="s">
-        <v>561</v>
-      </c>
+      <c r="B207" s="7"/>
       <c r="C207" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="D207" s="15" t="s">
-        <v>563</v>
+        <v>644</v>
+      </c>
+      <c r="D207" s="45" t="s">
+        <v>645</v>
       </c>
       <c r="E207" s="4"/>
-      <c r="F207" s="4"/>
+      <c r="F207" s="8"/>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
-      <c r="I207" s="23" t="s">
-        <v>564</v>
+      <c r="I207" s="4" t="s">
+        <v>646</v>
       </c>
       <c r="J207" s="4"/>
       <c r="K207" s="4"/>
@@ -9082,20 +9100,20 @@
         <v>507</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="4"/>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
       <c r="I208" s="23" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="J208" s="4"/>
       <c r="K208" s="4"/>
@@ -9110,17 +9128,17 @@
         <v>565</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="4"/>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
       <c r="I209" s="23" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="J209" s="4"/>
       <c r="K209" s="4"/>
@@ -9135,17 +9153,17 @@
         <v>565</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D210" s="15" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="4"/>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
-      <c r="I210" s="8" t="s">
-        <v>574</v>
+      <c r="I210" s="23" t="s">
+        <v>571</v>
       </c>
       <c r="J210" s="4"/>
       <c r="K210" s="4"/>
@@ -9154,21 +9172,23 @@
     </row>
     <row r="211" spans="1:13" ht="13.5" customHeight="1">
       <c r="A211" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="B211" s="4"/>
+        <v>507</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>565</v>
+      </c>
       <c r="C211" s="7" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
       <c r="I211" s="8" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="J211" s="4"/>
       <c r="K211" s="4"/>
@@ -9181,45 +9201,43 @@
       </c>
       <c r="B212" s="4"/>
       <c r="C212" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>580</v>
-      </c>
-      <c r="E212" s="23" t="s">
-        <v>581</v>
-      </c>
-      <c r="F212" s="23" t="s">
-        <v>581</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="E212" s="4"/>
+      <c r="F212" s="4"/>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
-      <c r="I212" s="4"/>
+      <c r="I212" s="8" t="s">
+        <v>578</v>
+      </c>
       <c r="J212" s="4"/>
       <c r="K212" s="4"/>
       <c r="L212" s="4"/>
       <c r="M212" s="5"/>
     </row>
     <row r="213" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A213" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="B213" s="24" t="s">
-        <v>583</v>
-      </c>
-      <c r="C213" s="32" t="s">
-        <v>583</v>
-      </c>
-      <c r="D213" s="33" t="s">
-        <v>584</v>
-      </c>
-      <c r="E213" s="4"/>
-      <c r="F213" s="4"/>
+      <c r="A213" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="B213" s="4"/>
+      <c r="C213" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="D213" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="E213" s="23" t="s">
+        <v>581</v>
+      </c>
+      <c r="F213" s="23" t="s">
+        <v>581</v>
+      </c>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
-      <c r="I213" s="23" t="s">
-        <v>585</v>
-      </c>
+      <c r="I213" s="4"/>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
       <c r="L213" s="4"/>
@@ -9233,20 +9251,18 @@
         <v>583</v>
       </c>
       <c r="C214" s="32" t="s">
-        <v>586</v>
-      </c>
-      <c r="D214" s="15" t="s">
-        <v>587</v>
-      </c>
-      <c r="E214" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="F214" s="23" t="s">
-        <v>269</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="D214" s="33" t="s">
+        <v>584</v>
+      </c>
+      <c r="E214" s="4"/>
+      <c r="F214" s="4"/>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
-      <c r="I214" s="4"/>
+      <c r="I214" s="23" t="s">
+        <v>585</v>
+      </c>
       <c r="J214" s="4"/>
       <c r="K214" s="4"/>
       <c r="L214" s="4"/>
@@ -9256,20 +9272,24 @@
       <c r="A215" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="B215" s="4"/>
-      <c r="C215" s="5" t="s">
-        <v>588</v>
+      <c r="B215" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="C215" s="32" t="s">
+        <v>586</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="E215" s="4"/>
-      <c r="F215" s="4"/>
+        <v>587</v>
+      </c>
+      <c r="E215" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="F215" s="23" t="s">
+        <v>269</v>
+      </c>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
-      <c r="I215" s="8" t="s">
-        <v>590</v>
-      </c>
+      <c r="I215" s="4"/>
       <c r="J215" s="4"/>
       <c r="K215" s="4"/>
       <c r="L215" s="4"/>
@@ -9280,18 +9300,18 @@
         <v>582</v>
       </c>
       <c r="B216" s="4"/>
-      <c r="C216" s="7" t="s">
-        <v>591</v>
+      <c r="C216" s="5" t="s">
+        <v>588</v>
       </c>
       <c r="D216" s="15" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
-      <c r="I216" s="10" t="s">
-        <v>593</v>
+      <c r="I216" s="8" t="s">
+        <v>590</v>
       </c>
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
@@ -9304,17 +9324,17 @@
       </c>
       <c r="B217" s="4"/>
       <c r="C217" s="7" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
-      <c r="I217" s="8" t="s">
-        <v>596</v>
+      <c r="I217" s="10" t="s">
+        <v>593</v>
       </c>
       <c r="J217" s="4"/>
       <c r="K217" s="4"/>
@@ -9326,18 +9346,18 @@
         <v>582</v>
       </c>
       <c r="B218" s="4"/>
-      <c r="C218" s="5" t="s">
-        <v>597</v>
+      <c r="C218" s="7" t="s">
+        <v>594</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
       <c r="I218" s="8" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
@@ -9350,41 +9370,41 @@
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="5" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>601</v>
-      </c>
-      <c r="E219" s="8" t="s">
-        <v>602</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="E219" s="4"/>
       <c r="F219" s="4"/>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
-      <c r="I219" s="4"/>
+      <c r="I219" s="8" t="s">
+        <v>599</v>
+      </c>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
       <c r="L219" s="4"/>
       <c r="M219" s="5"/>
     </row>
     <row r="220" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A220" s="7" t="s">
-        <v>603</v>
+      <c r="A220" s="5" t="s">
+        <v>582</v>
       </c>
       <c r="B220" s="4"/>
-      <c r="C220" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D220" s="33" t="s">
-        <v>605</v>
-      </c>
-      <c r="E220" s="5"/>
+      <c r="C220" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="D220" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="E220" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="F220" s="4"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
-      <c r="I220" s="23" t="s">
-        <v>606</v>
-      </c>
+      <c r="I220" s="4"/>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
       <c r="L220" s="4"/>
@@ -9394,19 +9414,19 @@
       <c r="A221" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="B221" s="3"/>
-      <c r="C221" s="34" t="s">
-        <v>607</v>
-      </c>
-      <c r="D221" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="E221" s="3"/>
+      <c r="B221" s="4"/>
+      <c r="C221" s="22" t="s">
+        <v>604</v>
+      </c>
+      <c r="D221" s="33" t="s">
+        <v>605</v>
+      </c>
+      <c r="E221" s="5"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
-      <c r="H221" s="3"/>
-      <c r="I221" s="8" t="s">
-        <v>609</v>
+      <c r="H221" s="4"/>
+      <c r="I221" s="23" t="s">
+        <v>606</v>
       </c>
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
@@ -9418,18 +9438,18 @@
         <v>603</v>
       </c>
       <c r="B222" s="3"/>
-      <c r="C222" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="D222" s="9" t="s">
-        <v>611</v>
+      <c r="C222" s="34" t="s">
+        <v>607</v>
+      </c>
+      <c r="D222" s="35" t="s">
+        <v>608</v>
       </c>
       <c r="E222" s="3"/>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
       <c r="H222" s="3"/>
       <c r="I222" s="8" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J222" s="4"/>
       <c r="K222" s="4"/>
@@ -9441,18 +9461,18 @@
         <v>603</v>
       </c>
       <c r="B223" s="3"/>
-      <c r="C223" s="10" t="s">
-        <v>613</v>
+      <c r="C223" s="7" t="s">
+        <v>610</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E223" s="3"/>
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
       <c r="H223" s="3"/>
       <c r="I223" s="8" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
@@ -9461,21 +9481,21 @@
     </row>
     <row r="224" spans="1:13" ht="13.5" customHeight="1">
       <c r="A224" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="B224" s="4"/>
-      <c r="C224" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="D224" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="E224" s="4"/>
+        <v>603</v>
+      </c>
+      <c r="B224" s="3"/>
+      <c r="C224" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="D224" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="E224" s="3"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
-      <c r="H224" s="4"/>
+      <c r="H224" s="3"/>
       <c r="I224" s="8" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
@@ -9487,18 +9507,18 @@
         <v>616</v>
       </c>
       <c r="B225" s="4"/>
-      <c r="C225" s="8" t="s">
-        <v>620</v>
-      </c>
-      <c r="D225" s="36" t="s">
-        <v>621</v>
+      <c r="C225" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="D225" s="15" t="s">
+        <v>618</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="4"/>
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
       <c r="I225" s="8" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
@@ -9506,22 +9526,22 @@
       <c r="M225" s="5"/>
     </row>
     <row r="226" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A226" s="37" t="s">
-        <v>623</v>
-      </c>
-      <c r="B226" s="38"/>
-      <c r="C226" s="39" t="s">
-        <v>624</v>
-      </c>
-      <c r="D226" s="40" t="s">
-        <v>625</v>
-      </c>
-      <c r="E226" s="41"/>
+      <c r="A226" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="B226" s="4"/>
+      <c r="C226" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="D226" s="36" t="s">
+        <v>621</v>
+      </c>
+      <c r="E226" s="4"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
       <c r="H226" s="4"/>
       <c r="I226" s="8" t="s">
-        <v>272</v>
+        <v>622</v>
       </c>
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
@@ -9532,19 +9552,19 @@
       <c r="A227" s="37" t="s">
         <v>623</v>
       </c>
-      <c r="B227" s="24"/>
-      <c r="C227" s="42" t="s">
-        <v>258</v>
-      </c>
-      <c r="D227" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="E227" s="3"/>
-      <c r="F227" s="20"/>
-      <c r="G227" s="20"/>
-      <c r="H227" s="3"/>
+      <c r="B227" s="38"/>
+      <c r="C227" s="39" t="s">
+        <v>624</v>
+      </c>
+      <c r="D227" s="40" t="s">
+        <v>625</v>
+      </c>
+      <c r="E227" s="41"/>
+      <c r="F227" s="4"/>
+      <c r="G227" s="4"/>
+      <c r="H227" s="4"/>
       <c r="I227" s="8" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="J227" s="4"/>
       <c r="K227" s="4"/>
@@ -9556,18 +9576,18 @@
         <v>623</v>
       </c>
       <c r="B228" s="24"/>
-      <c r="C228" s="39" t="s">
-        <v>626</v>
-      </c>
-      <c r="D228" s="40" t="s">
-        <v>627</v>
-      </c>
-      <c r="E228" s="4"/>
-      <c r="F228" s="4"/>
-      <c r="G228" s="4"/>
-      <c r="H228" s="4"/>
-      <c r="I228" s="23" t="s">
-        <v>585</v>
+      <c r="C228" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D228" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="E228" s="3"/>
+      <c r="F228" s="20"/>
+      <c r="G228" s="20"/>
+      <c r="H228" s="3"/>
+      <c r="I228" s="8" t="s">
+        <v>260</v>
       </c>
       <c r="J228" s="4"/>
       <c r="K228" s="4"/>
@@ -9578,19 +9598,19 @@
       <c r="A229" s="37" t="s">
         <v>623</v>
       </c>
-      <c r="B229" s="38"/>
-      <c r="C229" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="D229" s="44" t="s">
-        <v>235</v>
-      </c>
-      <c r="E229" s="3"/>
-      <c r="F229" s="20"/>
-      <c r="G229" s="20"/>
-      <c r="H229" s="3"/>
-      <c r="I229" s="8" t="s">
-        <v>227</v>
+      <c r="B229" s="24"/>
+      <c r="C229" s="39" t="s">
+        <v>626</v>
+      </c>
+      <c r="D229" s="40" t="s">
+        <v>627</v>
+      </c>
+      <c r="E229" s="4"/>
+      <c r="F229" s="4"/>
+      <c r="G229" s="4"/>
+      <c r="H229" s="4"/>
+      <c r="I229" s="23" t="s">
+        <v>585</v>
       </c>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
@@ -9602,18 +9622,18 @@
         <v>623</v>
       </c>
       <c r="B230" s="38"/>
-      <c r="C230" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D230" s="9" t="s">
-        <v>250</v>
+      <c r="C230" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="D230" s="44" t="s">
+        <v>235</v>
       </c>
       <c r="E230" s="3"/>
       <c r="F230" s="20"/>
       <c r="G230" s="20"/>
       <c r="H230" s="3"/>
       <c r="I230" s="8" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
@@ -9624,21 +9644,19 @@
       <c r="A231" s="37" t="s">
         <v>623</v>
       </c>
-      <c r="B231" s="38" t="s">
-        <v>628</v>
-      </c>
-      <c r="C231" s="39" t="s">
-        <v>629</v>
-      </c>
-      <c r="D231" s="40" t="s">
-        <v>630</v>
-      </c>
-      <c r="E231" s="4"/>
-      <c r="F231" s="4"/>
-      <c r="G231" s="4"/>
-      <c r="H231" s="4"/>
-      <c r="I231" s="23" t="s">
-        <v>631</v>
+      <c r="B231" s="38"/>
+      <c r="C231" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D231" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E231" s="3"/>
+      <c r="F231" s="20"/>
+      <c r="G231" s="20"/>
+      <c r="H231" s="3"/>
+      <c r="I231" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
@@ -9653,17 +9671,17 @@
         <v>628</v>
       </c>
       <c r="C232" s="39" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D232" s="40" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E232" s="4"/>
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
       <c r="H232" s="4"/>
       <c r="I232" s="23" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
@@ -9678,17 +9696,17 @@
         <v>628</v>
       </c>
       <c r="C233" s="39" t="s">
-        <v>231</v>
+        <v>632</v>
       </c>
       <c r="D233" s="40" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E233" s="4"/>
       <c r="F233" s="4"/>
       <c r="G233" s="4"/>
       <c r="H233" s="4"/>
       <c r="I233" s="23" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
@@ -9696,15 +9714,25 @@
       <c r="M233" s="5"/>
     </row>
     <row r="234" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A234" s="4"/>
-      <c r="B234" s="4"/>
-      <c r="C234" s="4"/>
-      <c r="D234" s="4"/>
+      <c r="A234" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="B234" s="38" t="s">
+        <v>628</v>
+      </c>
+      <c r="C234" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="D234" s="40" t="s">
+        <v>635</v>
+      </c>
       <c r="E234" s="4"/>
       <c r="F234" s="4"/>
       <c r="G234" s="4"/>
       <c r="H234" s="4"/>
-      <c r="I234" s="4"/>
+      <c r="I234" s="23" t="s">
+        <v>636</v>
+      </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
       <c r="L234" s="4"/>
@@ -12500,7 +12528,21 @@
       <c r="L420" s="4"/>
       <c r="M420" s="5"/>
     </row>
-    <row r="421" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="421" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A421" s="4"/>
+      <c r="B421" s="4"/>
+      <c r="C421" s="4"/>
+      <c r="D421" s="4"/>
+      <c r="E421" s="4"/>
+      <c r="F421" s="4"/>
+      <c r="G421" s="4"/>
+      <c r="H421" s="4"/>
+      <c r="I421" s="4"/>
+      <c r="J421" s="4"/>
+      <c r="K421" s="4"/>
+      <c r="L421" s="4"/>
+      <c r="M421" s="5"/>
+    </row>
     <row r="422" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="423" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="424" spans="1:13" ht="15.75" customHeight="1"/>
@@ -13097,6 +13139,7 @@
     <row r="1015" ht="15.75" customHeight="1"/>
     <row r="1016" ht="15.75" customHeight="1"/>
     <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="14"/>
   <hyperlinks>
@@ -13285,28 +13328,29 @@
     <hyperlink ref="D204" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
     <hyperlink ref="D205" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
     <hyperlink ref="D206" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D207" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D208" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D209" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D210" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D211" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D212" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D213" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D215" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D216" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D217" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D218" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D219" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D220" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="D221" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D222" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="D223" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D224" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="D225" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D227" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="D229" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D230" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="D208" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D209" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D210" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D211" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D212" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D213" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D214" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D216" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D217" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D218" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D219" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D220" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D221" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="D222" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="D223" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="D224" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="D225" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="D226" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="D228" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="D230" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="D231" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
     <hyperlink ref="D16" r:id="rId207" xr:uid="{101A33D7-B7BA-422E-B2FC-342D5148D1EA}"/>
+    <hyperlink ref="D207" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dx-user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\vm22flo01\DownloadFiles\スマートシティ課\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAC6FEA-A2EA-48AB-A828-A864C0D55A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C386E1D-0B89-44A2-AC61-E0DFAA35871F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="メニュー構造" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="651">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -789,91 +789,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>統合（平成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>年～令和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>年）</t>
-    </r>
-  </si>
-  <si>
     <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E7%B5%B1%E5%90%88/tiles.json</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>令和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>年</t>
-    </r>
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E4%BB%A4%E5%92%8C4%E5%B9%B4/tiles.json</t>
@@ -3221,6 +3137,74 @@
   </si>
   <si>
     <t>randoseru</t>
+  </si>
+  <si>
+    <t>令和7年</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>令和6年</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <r>
+      <t>統合（平成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年～令和7年）</t>
+    </r>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E4%BB%A4%E5%92%8C6%E5%B9%B4/tiles.json</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E4%BB%A4%E5%92%8C7%E5%B9%B4/tiles.json</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <r>
+      <t>令和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <phoneticPr fontId="14"/>
   </si>
 </sst>
 </file>
@@ -3846,7 +3830,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M1018"/>
+  <dimension ref="A1:M1020"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -3927,7 +3911,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>18</v>
@@ -3952,7 +3936,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>21</v>
@@ -3977,7 +3961,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>24</v>
@@ -4249,23 +4233,23 @@
     </row>
     <row r="16" spans="1:13" ht="13.5" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D16" s="45" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="12" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -5661,10 +5645,10 @@
         <v>171</v>
       </c>
       <c r="C74" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="D74" s="17" t="s">
         <v>172</v>
-      </c>
-      <c r="D74" s="17" t="s">
-        <v>173</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>15</v>
@@ -5688,10 +5672,10 @@
         <v>171</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D75" s="17" t="s">
-        <v>175</v>
+        <v>645</v>
+      </c>
+      <c r="D75" s="45" t="s">
+        <v>649</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>15</v>
@@ -5715,10 +5699,10 @@
         <v>171</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D76" s="17" t="s">
-        <v>177</v>
+        <v>646</v>
+      </c>
+      <c r="D76" s="45" t="s">
+        <v>648</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>15</v>
@@ -5742,10 +5726,10 @@
         <v>171</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>178</v>
+        <v>650</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>15</v>
@@ -5769,10 +5753,10 @@
         <v>171</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>15</v>
@@ -5796,24 +5780,24 @@
         <v>171</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
       <c r="H79" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I79" s="20"/>
-      <c r="J79" s="20"/>
-      <c r="K79" s="20"/>
-      <c r="L79" s="20"/>
-      <c r="M79" s="21"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="5"/>
     </row>
     <row r="80" spans="1:13" ht="13.5" customHeight="1">
       <c r="A80" s="7" t="s">
@@ -5823,10 +5807,10 @@
         <v>171</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>15</v>
@@ -5850,24 +5834,24 @@
         <v>171</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
       <c r="H81" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4"/>
-      <c r="M81" s="5"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
+      <c r="K81" s="20"/>
+      <c r="L81" s="20"/>
+      <c r="M81" s="21"/>
     </row>
     <row r="82" spans="1:13" ht="13.5" customHeight="1">
       <c r="A82" s="7" t="s">
@@ -5877,10 +5861,10 @@
         <v>171</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>15</v>
@@ -5904,10 +5888,10 @@
         <v>171</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>15</v>
@@ -5931,10 +5915,10 @@
         <v>171</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>15</v>
@@ -5958,10 +5942,10 @@
         <v>171</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>15</v>
@@ -5985,10 +5969,10 @@
         <v>171</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>15</v>
@@ -6012,10 +5996,10 @@
         <v>171</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>15</v>
@@ -6039,10 +6023,10 @@
         <v>171</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>15</v>
@@ -6066,10 +6050,10 @@
         <v>171</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>15</v>
@@ -6093,10 +6077,10 @@
         <v>171</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>15</v>
@@ -6120,24 +6104,24 @@
         <v>171</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F91" s="20"/>
-      <c r="G91" s="20"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
       <c r="H91" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I91" s="20"/>
-      <c r="J91" s="20"/>
-      <c r="K91" s="20"/>
-      <c r="L91" s="20"/>
-      <c r="M91" s="21"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="5"/>
     </row>
     <row r="92" spans="1:13" ht="13.5" customHeight="1">
       <c r="A92" s="7" t="s">
@@ -6147,10 +6131,10 @@
         <v>171</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>15</v>
@@ -6174,10 +6158,10 @@
         <v>171</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>15</v>
@@ -6187,8 +6171,8 @@
       <c r="H93" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
+      <c r="I93" s="20"/>
+      <c r="J93" s="20"/>
       <c r="K93" s="20"/>
       <c r="L93" s="20"/>
       <c r="M93" s="21"/>
@@ -6201,10 +6185,10 @@
         <v>171</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>15</v>
@@ -6224,38 +6208,50 @@
       <c r="A95" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B95" s="5"/>
+      <c r="B95" s="5" t="s">
+        <v>171</v>
+      </c>
       <c r="C95" s="5" t="s">
-        <v>643</v>
+        <v>208</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="E95" s="7"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="7"/>
+        <v>209</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" s="20"/>
+      <c r="G95" s="20"/>
+      <c r="H95" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="5"/>
+      <c r="K95" s="20"/>
+      <c r="L95" s="20"/>
+      <c r="M95" s="21"/>
     </row>
     <row r="96" spans="1:13" ht="13.5" customHeight="1">
       <c r="A96" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B96" s="5"/>
+      <c r="B96" s="5" t="s">
+        <v>171</v>
+      </c>
       <c r="C96" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="E96" s="7"/>
+        <v>211</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
-      <c r="H96" s="7"/>
+      <c r="H96" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
@@ -6268,19 +6264,15 @@
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5" t="s">
-        <v>217</v>
+        <v>641</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>219</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="E97" s="7"/>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
-      <c r="H97" s="10" t="s">
-        <v>219</v>
-      </c>
+      <c r="H97" s="7"/>
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
@@ -6293,19 +6285,15 @@
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>222</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="E98" s="7"/>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
-      <c r="H98" s="10" t="s">
-        <v>222</v>
-      </c>
+      <c r="H98" s="7"/>
       <c r="I98" s="4"/>
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
@@ -6314,24 +6302,24 @@
     </row>
     <row r="99" spans="1:13" ht="13.5" customHeight="1">
       <c r="A99" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B99" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="C99" s="22" t="s">
-        <v>225</v>
+        <v>16</v>
+      </c>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="E99" s="7"/>
+        <v>216</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>217</v>
+      </c>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
-      <c r="H99" s="7"/>
-      <c r="I99" s="23" t="s">
-        <v>227</v>
-      </c>
+      <c r="H99" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="I99" s="4"/>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
       <c r="L99" s="4"/>
@@ -6339,24 +6327,24 @@
     </row>
     <row r="100" spans="1:13" ht="13.5" customHeight="1">
       <c r="A100" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B100" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="C100" s="22" t="s">
-        <v>228</v>
+        <v>16</v>
+      </c>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="E100" s="7"/>
+        <v>219</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>220</v>
+      </c>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
-      <c r="H100" s="7"/>
-      <c r="I100" s="23" t="s">
-        <v>230</v>
-      </c>
+      <c r="H100" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I100" s="4"/>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
@@ -6364,23 +6352,23 @@
     </row>
     <row r="101" spans="1:13" ht="13.5" customHeight="1">
       <c r="A101" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B101" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C101" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="B101" s="22" t="s">
+      <c r="D101" s="17" t="s">
         <v>224</v>
-      </c>
-      <c r="C101" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="D101" s="17" t="s">
-        <v>232</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
       <c r="H101" s="7"/>
       <c r="I101" s="23" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
@@ -6389,21 +6377,23 @@
     </row>
     <row r="102" spans="1:13" ht="13.5" customHeight="1">
       <c r="A102" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B102" s="4"/>
-      <c r="C102" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="E102" s="3"/>
-      <c r="F102" s="20"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B102" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C102" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="D102" s="17" t="s">
         <v>227</v>
+      </c>
+      <c r="E102" s="7"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="23" t="s">
+        <v>228</v>
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
@@ -6412,23 +6402,23 @@
     </row>
     <row r="103" spans="1:13" ht="13.5" customHeight="1">
       <c r="A103" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B103" s="24" t="s">
-        <v>236</v>
+        <v>221</v>
+      </c>
+      <c r="B103" s="22" t="s">
+        <v>222</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="E103" s="3"/>
-      <c r="F103" s="20"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="8" t="s">
-        <v>239</v>
+        <v>229</v>
+      </c>
+      <c r="D103" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="E103" s="7"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="23" t="s">
+        <v>231</v>
       </c>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
@@ -6437,23 +6427,21 @@
     </row>
     <row r="104" spans="1:13" ht="13.5" customHeight="1">
       <c r="A104" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B104" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="C104" s="22" t="s">
-        <v>240</v>
+        <v>221</v>
+      </c>
+      <c r="B104" s="4"/>
+      <c r="C104" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="20"/>
       <c r="G104" s="20"/>
       <c r="H104" s="3"/>
       <c r="I104" s="8" t="s">
-        <v>637</v>
+        <v>225</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
@@ -6462,23 +6450,23 @@
     </row>
     <row r="105" spans="1:13" ht="13.5" customHeight="1">
       <c r="A105" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B105" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="C105" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="D105" s="9" t="s">
         <v>236</v>
-      </c>
-      <c r="C105" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>243</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="20"/>
       <c r="G105" s="20"/>
       <c r="H105" s="3"/>
       <c r="I105" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
@@ -6487,23 +6475,23 @@
     </row>
     <row r="106" spans="1:13" ht="13.5" customHeight="1">
       <c r="A106" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B106" s="24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="D106" s="25" t="s">
-        <v>245</v>
+        <v>238</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>239</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="20"/>
       <c r="G106" s="20"/>
       <c r="H106" s="3"/>
       <c r="I106" s="8" t="s">
-        <v>239</v>
+        <v>635</v>
       </c>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
@@ -6512,23 +6500,23 @@
     </row>
     <row r="107" spans="1:13" ht="13.5" customHeight="1">
       <c r="A107" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B107" s="24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="20"/>
       <c r="G107" s="20"/>
       <c r="H107" s="3"/>
       <c r="I107" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
@@ -6537,23 +6525,23 @@
     </row>
     <row r="108" spans="1:13" ht="13.5" customHeight="1">
       <c r="A108" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>250</v>
+        <v>221</v>
+      </c>
+      <c r="B108" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="C108" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="D108" s="25" t="s">
+        <v>243</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="20"/>
       <c r="G108" s="20"/>
       <c r="H108" s="3"/>
       <c r="I108" s="8" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
@@ -6562,23 +6550,23 @@
     </row>
     <row r="109" spans="1:13" ht="13.5" customHeight="1">
       <c r="A109" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="B109" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="C109" s="22" t="s">
+        <v>244</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E109" s="3"/>
-      <c r="F109" s="4"/>
+      <c r="F109" s="20"/>
       <c r="G109" s="20"/>
       <c r="H109" s="3"/>
       <c r="I109" s="8" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
@@ -6587,21 +6575,23 @@
     </row>
     <row r="110" spans="1:13" ht="13.5" customHeight="1">
       <c r="A110" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B110" s="3"/>
+        <v>221</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>246</v>
+      </c>
       <c r="C110" s="7" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="20"/>
       <c r="G110" s="20"/>
       <c r="H110" s="3"/>
       <c r="I110" s="8" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
@@ -6610,21 +6600,23 @@
     </row>
     <row r="111" spans="1:13" ht="13.5" customHeight="1">
       <c r="A111" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B111" s="3"/>
+        <v>221</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>246</v>
+      </c>
       <c r="C111" s="7" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E111" s="3"/>
-      <c r="F111" s="20"/>
+      <c r="F111" s="4"/>
       <c r="G111" s="20"/>
       <c r="H111" s="3"/>
       <c r="I111" s="8" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
@@ -6633,21 +6625,21 @@
     </row>
     <row r="112" spans="1:13" ht="13.5" customHeight="1">
       <c r="A112" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="7" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="20"/>
       <c r="G112" s="20"/>
       <c r="H112" s="3"/>
       <c r="I112" s="8" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
@@ -6656,49 +6648,45 @@
     </row>
     <row r="113" spans="1:13" ht="13.5" customHeight="1">
       <c r="A113" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>264</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="B113" s="3"/>
       <c r="C113" s="7" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="20"/>
       <c r="G113" s="20"/>
       <c r="H113" s="3"/>
-      <c r="I113" s="10" t="s">
-        <v>267</v>
+      <c r="I113" s="8" t="s">
+        <v>258</v>
       </c>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4"/>
       <c r="M113" s="5"/>
     </row>
-    <row r="114" spans="1:13" ht="15" customHeight="1">
+    <row r="114" spans="1:13" ht="13.5" customHeight="1">
       <c r="A114" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>264</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="B114" s="3"/>
       <c r="C114" s="7" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E114" s="3"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
-      <c r="H114" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="I114" s="4"/>
+      <c r="F114" s="20"/>
+      <c r="G114" s="20"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="8" t="s">
+        <v>261</v>
+      </c>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4"/>
@@ -6706,43 +6694,47 @@
     </row>
     <row r="115" spans="1:13" ht="13.5" customHeight="1">
       <c r="A115" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B115" s="4"/>
+        <v>221</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>262</v>
+      </c>
       <c r="C115" s="7" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="20"/>
       <c r="G115" s="20"/>
       <c r="H115" s="3"/>
-      <c r="I115" s="8" t="s">
-        <v>272</v>
+      <c r="I115" s="10" t="s">
+        <v>265</v>
       </c>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
       <c r="L115" s="4"/>
       <c r="M115" s="5"/>
     </row>
-    <row r="116" spans="1:13" ht="13.5" customHeight="1">
+    <row r="116" spans="1:13" ht="15" customHeight="1">
       <c r="A116" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B116" s="4"/>
+        <v>221</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>262</v>
+      </c>
       <c r="C116" s="7" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="4"/>
       <c r="G116" s="4"/>
-      <c r="H116" s="14" t="s">
-        <v>275</v>
+      <c r="H116" s="10" t="s">
+        <v>267</v>
       </c>
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
@@ -6750,50 +6742,46 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
     </row>
-    <row r="117" spans="1:13" ht="12.75" customHeight="1">
+    <row r="117" spans="1:13" ht="13.5" customHeight="1">
       <c r="A117" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>276</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="B117" s="4"/>
       <c r="C117" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="D117" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="E117" s="4"/>
-      <c r="F117" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4"/>
-      <c r="I117" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E117" s="3"/>
+      <c r="F117" s="20"/>
+      <c r="G117" s="20"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
       <c r="M117" s="5"/>
     </row>
-    <row r="118" spans="1:13" ht="12.75" customHeight="1">
+    <row r="118" spans="1:13" ht="13.5" customHeight="1">
       <c r="A118" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>276</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="B118" s="4"/>
       <c r="C118" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="D118" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="E118" s="4"/>
-      <c r="F118" s="8" t="s">
-        <v>282</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E118" s="3"/>
+      <c r="F118" s="4"/>
       <c r="G118" s="4"/>
-      <c r="H118" s="4"/>
+      <c r="H118" s="14" t="s">
+        <v>273</v>
+      </c>
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
@@ -6802,20 +6790,20 @@
     </row>
     <row r="119" spans="1:13" ht="12.75" customHeight="1">
       <c r="A119" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B119" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D119" s="15" t="s">
         <v>276</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="D119" s="15" t="s">
-        <v>284</v>
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="8" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
@@ -6827,20 +6815,20 @@
     </row>
     <row r="120" spans="1:13" ht="12.75" customHeight="1">
       <c r="A120" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="8" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
@@ -6852,20 +6840,20 @@
     </row>
     <row r="121" spans="1:13" ht="12.75" customHeight="1">
       <c r="A121" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E121" s="4"/>
       <c r="F121" s="8" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
@@ -6877,20 +6865,20 @@
     </row>
     <row r="122" spans="1:13" ht="12.75" customHeight="1">
       <c r="A122" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="8" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
@@ -6902,20 +6890,20 @@
     </row>
     <row r="123" spans="1:13" ht="12.75" customHeight="1">
       <c r="A123" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="8" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
@@ -6925,123 +6913,127 @@
       <c r="L123" s="4"/>
       <c r="M123" s="5"/>
     </row>
-    <row r="124" spans="1:13" ht="13.5" customHeight="1">
+    <row r="124" spans="1:13" ht="12.75" customHeight="1">
       <c r="A124" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="E124" s="4"/>
-      <c r="F124" s="4"/>
+      <c r="F124" s="8" t="s">
+        <v>292</v>
+      </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
-      <c r="I124" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="J124" s="20"/>
+      <c r="I124" s="4"/>
+      <c r="J124" s="4"/>
       <c r="K124" s="4"/>
       <c r="L124" s="4"/>
       <c r="M124" s="5"/>
     </row>
-    <row r="125" spans="1:13" ht="13.5" customHeight="1">
+    <row r="125" spans="1:13" ht="12.75" customHeight="1">
       <c r="A125" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="D125" s="17" t="s">
-        <v>302</v>
+        <v>293</v>
+      </c>
+      <c r="D125" s="15" t="s">
+        <v>294</v>
       </c>
       <c r="E125" s="4"/>
-      <c r="F125" s="4"/>
+      <c r="F125" s="8" t="s">
+        <v>295</v>
+      </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
-      <c r="I125" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="J125" s="20"/>
+      <c r="I125" s="4"/>
+      <c r="J125" s="4"/>
       <c r="K125" s="4"/>
       <c r="L125" s="4"/>
       <c r="M125" s="5"/>
     </row>
     <row r="126" spans="1:13" ht="13.5" customHeight="1">
       <c r="A126" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="D126" s="17" t="s">
-        <v>305</v>
+        <v>274</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>297</v>
       </c>
       <c r="E126" s="4"/>
-      <c r="F126" s="26" t="s">
-        <v>306</v>
-      </c>
+      <c r="F126" s="4"/>
       <c r="G126" s="4"/>
-      <c r="H126" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="I126" s="4"/>
-      <c r="J126" s="4"/>
+      <c r="H126" s="4"/>
+      <c r="I126" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="J126" s="20"/>
       <c r="K126" s="4"/>
       <c r="L126" s="4"/>
       <c r="M126" s="5"/>
     </row>
     <row r="127" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A127" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B127" s="4"/>
-      <c r="C127" s="5" t="s">
-        <v>309</v>
+      <c r="A127" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-      <c r="J127" s="4"/>
+      <c r="I127" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="J127" s="20"/>
       <c r="K127" s="4"/>
       <c r="L127" s="4"/>
       <c r="M127" s="5"/>
     </row>
     <row r="128" spans="1:13" ht="13.5" customHeight="1">
       <c r="A128" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>311</v>
+        <v>221</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>274</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F128" s="4"/>
+        <v>303</v>
+      </c>
+      <c r="E128" s="4"/>
+      <c r="F128" s="26" t="s">
+        <v>304</v>
+      </c>
       <c r="G128" s="4"/>
-      <c r="H128" s="3"/>
+      <c r="H128" s="26" t="s">
+        <v>305</v>
+      </c>
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
@@ -7049,24 +7041,20 @@
       <c r="M128" s="5"/>
     </row>
     <row r="129" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A129" s="7" t="s">
+      <c r="A129" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B129" s="4"/>
+      <c r="C129" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D129" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="B129" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="D129" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>317</v>
-      </c>
+      <c r="E129" s="4"/>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
-      <c r="H129" s="3"/>
+      <c r="H129" s="4"/>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
@@ -7075,19 +7063,19 @@
     </row>
     <row r="130" spans="1:13" ht="13.5" customHeight="1">
       <c r="A130" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B130" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D130" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="C130" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="D130" s="17" t="s">
-        <v>319</v>
-      </c>
       <c r="E130" s="10" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
@@ -7100,19 +7088,19 @@
     </row>
     <row r="131" spans="1:13" ht="13.5" customHeight="1">
       <c r="A131" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
@@ -7125,23 +7113,23 @@
     </row>
     <row r="132" spans="1:13" ht="13.5" customHeight="1">
       <c r="A132" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>326</v>
+        <v>317</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>318</v>
       </c>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
+      <c r="H132" s="3"/>
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
@@ -7150,19 +7138,19 @@
     </row>
     <row r="133" spans="1:13" ht="13.5" customHeight="1">
       <c r="A133" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
@@ -7175,23 +7163,23 @@
     </row>
     <row r="134" spans="1:13" ht="13.5" customHeight="1">
       <c r="A134" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="E134" s="10" t="s">
-        <v>332</v>
+        <v>323</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>324</v>
       </c>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
-      <c r="H134" s="3"/>
+      <c r="H134" s="4"/>
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
@@ -7200,19 +7188,19 @@
     </row>
     <row r="135" spans="1:13" ht="13.5" customHeight="1">
       <c r="A135" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
@@ -7225,23 +7213,23 @@
     </row>
     <row r="136" spans="1:13" ht="13.5" customHeight="1">
       <c r="A136" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="E136" s="8" t="s">
-        <v>338</v>
+        <v>329</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>330</v>
       </c>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
+      <c r="H136" s="3"/>
       <c r="I136" s="4"/>
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
@@ -7250,23 +7238,23 @@
     </row>
     <row r="137" spans="1:13" ht="13.5" customHeight="1">
       <c r="A137" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="E137" s="8" t="s">
-        <v>338</v>
+        <v>332</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>333</v>
       </c>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
+      <c r="H137" s="3"/>
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
@@ -7275,19 +7263,19 @@
     </row>
     <row r="138" spans="1:13" ht="13.5" customHeight="1">
       <c r="A138" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
@@ -7300,19 +7288,19 @@
     </row>
     <row r="139" spans="1:13" ht="13.5" customHeight="1">
       <c r="A139" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F139" s="4"/>
       <c r="G139" s="4"/>
@@ -7325,23 +7313,21 @@
     </row>
     <row r="140" spans="1:13" ht="13.5" customHeight="1">
       <c r="A140" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>346</v>
+        <v>309</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>350</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="F140" s="4"/>
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
@@ -7352,23 +7338,21 @@
     </row>
     <row r="141" spans="1:13" ht="13.5" customHeight="1">
       <c r="A141" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>346</v>
+        <v>309</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="F141" s="8" t="s">
-        <v>350</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="F141" s="4"/>
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
@@ -7379,22 +7363,22 @@
     </row>
     <row r="142" spans="1:13" ht="13.5" customHeight="1">
       <c r="A142" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B142" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="D142" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="C142" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="D142" s="17" t="s">
-        <v>355</v>
-      </c>
       <c r="E142" s="8" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
@@ -7406,22 +7390,22 @@
     </row>
     <row r="143" spans="1:13" ht="13.5" customHeight="1">
       <c r="A143" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
@@ -7433,22 +7417,22 @@
     </row>
     <row r="144" spans="1:13" ht="13.5" customHeight="1">
       <c r="A144" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
@@ -7460,22 +7444,22 @@
     </row>
     <row r="145" spans="1:13" ht="13.5" customHeight="1">
       <c r="A145" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
@@ -7487,22 +7471,22 @@
     </row>
     <row r="146" spans="1:13" ht="13.5" customHeight="1">
       <c r="A146" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
@@ -7514,25 +7498,25 @@
     </row>
     <row r="147" spans="1:13" ht="13.5" customHeight="1">
       <c r="A147" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>372</v>
+        <v>362</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>363</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="G147" s="4"/>
-      <c r="H147" s="3"/>
+      <c r="H147" s="4"/>
       <c r="I147" s="4"/>
       <c r="J147" s="4"/>
       <c r="K147" s="4"/>
@@ -7541,22 +7525,22 @@
     </row>
     <row r="148" spans="1:13" ht="13.5" customHeight="1">
       <c r="A148" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4"/>
@@ -7568,25 +7552,25 @@
     </row>
     <row r="149" spans="1:13" ht="13.5" customHeight="1">
       <c r="A149" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="E149" s="8" t="s">
-        <v>378</v>
+        <v>369</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>370</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G149" s="4"/>
-      <c r="H149" s="4"/>
+      <c r="H149" s="3"/>
       <c r="I149" s="4"/>
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
@@ -7595,22 +7579,22 @@
     </row>
     <row r="150" spans="1:13" ht="13.5" customHeight="1">
       <c r="A150" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
@@ -7622,49 +7606,49 @@
     </row>
     <row r="151" spans="1:13" ht="13.5" customHeight="1">
       <c r="A151" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>382</v>
+        <v>306</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>374</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
-      <c r="J151" s="5"/>
+      <c r="J151" s="4"/>
       <c r="K151" s="4"/>
       <c r="L151" s="4"/>
       <c r="M151" s="5"/>
     </row>
     <row r="152" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A152" s="5" t="s">
-        <v>308</v>
+      <c r="A152" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>387</v>
-      </c>
-      <c r="E152" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="F152" s="23" t="s">
-        <v>388</v>
+        <v>378</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>367</v>
       </c>
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
@@ -7675,146 +7659,150 @@
       <c r="M152" s="5"/>
     </row>
     <row r="153" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A153" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>389</v>
+      <c r="A153" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>380</v>
       </c>
       <c r="D153" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="E153" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F153" s="23" t="s">
-        <v>391</v>
+        <v>381</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>367</v>
       </c>
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
-      <c r="J153" s="4"/>
+      <c r="J153" s="5"/>
       <c r="K153" s="4"/>
       <c r="L153" s="4"/>
       <c r="M153" s="5"/>
     </row>
     <row r="154" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A154" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B154" s="4"/>
+      <c r="A154" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="C154" s="5" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>393</v>
-      </c>
-      <c r="E154" s="4"/>
-      <c r="F154" s="20"/>
-      <c r="G154" s="20"/>
+        <v>385</v>
+      </c>
+      <c r="E154" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="F154" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="G154" s="4"/>
       <c r="H154" s="4"/>
-      <c r="I154" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="J154" s="20"/>
+      <c r="I154" s="4"/>
+      <c r="J154" s="4"/>
       <c r="K154" s="4"/>
       <c r="L154" s="4"/>
       <c r="M154" s="5"/>
     </row>
     <row r="155" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A155" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B155" s="4"/>
+      <c r="A155" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>383</v>
+      </c>
       <c r="C155" s="5" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>395</v>
-      </c>
-      <c r="E155" s="4"/>
-      <c r="F155" s="20"/>
-      <c r="G155" s="20"/>
+        <v>388</v>
+      </c>
+      <c r="E155" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="F155" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="G155" s="4"/>
       <c r="H155" s="4"/>
-      <c r="I155" s="26" t="s">
-        <v>396</v>
-      </c>
-      <c r="J155" s="20"/>
+      <c r="I155" s="4"/>
+      <c r="J155" s="4"/>
       <c r="K155" s="4"/>
       <c r="L155" s="4"/>
       <c r="M155" s="5"/>
     </row>
     <row r="156" spans="1:13" ht="13.5" customHeight="1">
       <c r="A156" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="D156" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="E156" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="F156" s="4"/>
-      <c r="G156" s="4"/>
-      <c r="H156" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="I156" s="4"/>
-      <c r="J156" s="4"/>
+        <v>390</v>
+      </c>
+      <c r="D156" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="E156" s="4"/>
+      <c r="F156" s="20"/>
+      <c r="G156" s="20"/>
+      <c r="H156" s="4"/>
+      <c r="I156" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="J156" s="20"/>
       <c r="K156" s="4"/>
       <c r="L156" s="4"/>
       <c r="M156" s="5"/>
     </row>
     <row r="157" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A157" s="5" t="s">
-        <v>400</v>
+      <c r="A157" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="D157" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="E157" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="F157" s="4"/>
-      <c r="G157" s="4"/>
-      <c r="H157" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
+        <v>392</v>
+      </c>
+      <c r="D157" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="E157" s="4"/>
+      <c r="F157" s="20"/>
+      <c r="G157" s="20"/>
+      <c r="H157" s="4"/>
+      <c r="I157" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="J157" s="20"/>
       <c r="K157" s="4"/>
       <c r="L157" s="4"/>
       <c r="M157" s="5"/>
     </row>
     <row r="158" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A158" s="5" t="s">
-        <v>400</v>
+      <c r="A158" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="5" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F158" s="4"/>
       <c r="G158" s="4"/>
       <c r="H158" s="8" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
@@ -7824,23 +7812,23 @@
     </row>
     <row r="159" spans="1:13" ht="13.5" customHeight="1">
       <c r="A159" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="5" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F159" s="8" t="s">
-        <v>409</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="F159" s="4"/>
       <c r="G159" s="4"/>
-      <c r="H159" s="4"/>
+      <c r="H159" s="8" t="s">
+        <v>401</v>
+      </c>
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
       <c r="K159" s="4"/>
@@ -7849,21 +7837,23 @@
     </row>
     <row r="160" spans="1:13" ht="13.5" customHeight="1">
       <c r="A160" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="B160" s="5"/>
+        <v>398</v>
+      </c>
+      <c r="B160" s="4"/>
       <c r="C160" s="5" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="F160" s="4"/>
       <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
+      <c r="H160" s="8" t="s">
+        <v>404</v>
+      </c>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
@@ -7872,22 +7862,20 @@
     </row>
     <row r="161" spans="1:13" ht="13.5" customHeight="1">
       <c r="A161" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>414</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="B161" s="4"/>
       <c r="C161" s="5" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>417</v>
+        <v>76</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="G161" s="4"/>
       <c r="H161" s="4"/>
@@ -7895,170 +7883,172 @@
       <c r="J161" s="4"/>
       <c r="K161" s="4"/>
       <c r="L161" s="4"/>
-      <c r="M161" s="8" t="s">
-        <v>418</v>
-      </c>
+      <c r="M161" s="5"/>
     </row>
     <row r="162" spans="1:13" ht="13.5" customHeight="1">
       <c r="A162" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B162" s="5"/>
+      <c r="C162" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="D162" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="B162" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="D162" s="15" t="s">
-        <v>420</v>
-      </c>
       <c r="E162" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="F162" s="8" t="s">
-        <v>421</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="F162" s="4"/>
       <c r="G162" s="4"/>
-      <c r="H162" s="8" t="s">
-        <v>421</v>
-      </c>
+      <c r="H162" s="4"/>
       <c r="I162" s="4"/>
       <c r="J162" s="4"/>
       <c r="K162" s="4"/>
       <c r="L162" s="4"/>
-      <c r="M162" s="8" t="s">
-        <v>418</v>
-      </c>
+      <c r="M162" s="5"/>
     </row>
     <row r="163" spans="1:13" ht="13.5" customHeight="1">
       <c r="A163" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B163" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="D163" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="C163" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="D163" s="15" t="s">
-        <v>423</v>
-      </c>
       <c r="E163" s="8" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="G163" s="4"/>
-      <c r="H163" s="8" t="s">
-        <v>424</v>
-      </c>
+      <c r="H163" s="4"/>
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
       <c r="K163" s="4"/>
       <c r="L163" s="4"/>
       <c r="M163" s="8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="13.5" customHeight="1">
       <c r="A164" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="F164" s="8" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="G164" s="4"/>
       <c r="H164" s="8" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
       <c r="K164" s="4"/>
       <c r="L164" s="4"/>
       <c r="M164" s="8" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" ht="15" customHeight="1">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="13.5" customHeight="1">
       <c r="A165" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="E165" s="4"/>
-      <c r="F165" s="4"/>
+        <v>421</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>422</v>
+      </c>
       <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
-      <c r="I165" s="8" t="s">
-        <v>431</v>
-      </c>
+      <c r="H165" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="I165" s="4"/>
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
+      <c r="M165" s="8" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="166" spans="1:13" ht="13.5" customHeight="1">
       <c r="A166" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="E166" s="4"/>
-      <c r="F166" s="4"/>
+        <v>424</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>425</v>
+      </c>
       <c r="G166" s="4"/>
-      <c r="H166" s="4"/>
+      <c r="H166" s="8" t="s">
+        <v>425</v>
+      </c>
       <c r="I166" s="4"/>
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
       <c r="L166" s="4"/>
-      <c r="M166" s="5"/>
-    </row>
-    <row r="167" spans="1:13" ht="13.5" customHeight="1">
+      <c r="M166" s="8" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" ht="15" customHeight="1">
       <c r="A167" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>434</v>
+        <v>408</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>426</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
       <c r="H167" s="4"/>
       <c r="I167" s="8" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="J167" s="4"/>
       <c r="K167" s="4"/>
@@ -8067,27 +8057,21 @@
     </row>
     <row r="168" spans="1:13" ht="13.5" customHeight="1">
       <c r="A168" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>434</v>
+        <v>408</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>426</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="E168" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="F168" s="8" t="s">
-        <v>440</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4"/>
       <c r="G168" s="4"/>
-      <c r="H168" s="8" t="s">
-        <v>440</v>
-      </c>
+      <c r="H168" s="4"/>
       <c r="I168" s="4"/>
       <c r="J168" s="4"/>
       <c r="K168" s="4"/>
@@ -8096,23 +8080,23 @@
     </row>
     <row r="169" spans="1:13" ht="13.5" customHeight="1">
       <c r="A169" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B169" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="D169" s="15" t="s">
         <v>434</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="D169" s="15" t="s">
-        <v>442</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
       <c r="H169" s="4"/>
       <c r="I169" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
@@ -8121,24 +8105,28 @@
     </row>
     <row r="170" spans="1:13" ht="13.5" customHeight="1">
       <c r="A170" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="E170" s="4"/>
-      <c r="F170" s="4"/>
+        <v>437</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>438</v>
+      </c>
       <c r="G170" s="4"/>
-      <c r="H170" s="4"/>
-      <c r="I170" s="10" t="s">
-        <v>445</v>
-      </c>
+      <c r="H170" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="I170" s="4"/>
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
       <c r="L170" s="4"/>
@@ -8146,23 +8134,23 @@
     </row>
     <row r="171" spans="1:13" ht="13.5" customHeight="1">
       <c r="A171" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
       <c r="G171" s="4"/>
       <c r="H171" s="4"/>
-      <c r="I171" s="10" t="s">
-        <v>445</v>
+      <c r="I171" s="8" t="s">
+        <v>435</v>
       </c>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
@@ -8171,23 +8159,23 @@
     </row>
     <row r="172" spans="1:13" ht="13.5" customHeight="1">
       <c r="A172" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
       <c r="I172" s="10" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
@@ -8196,28 +8184,24 @@
     </row>
     <row r="173" spans="1:13" ht="13.5" customHeight="1">
       <c r="A173" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="E173" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="F173" s="8" t="s">
-        <v>453</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4"/>
       <c r="G173" s="4"/>
-      <c r="H173" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="I173" s="4"/>
+      <c r="H173" s="4"/>
+      <c r="I173" s="10" t="s">
+        <v>443</v>
+      </c>
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
       <c r="L173" s="4"/>
@@ -8225,26 +8209,24 @@
     </row>
     <row r="174" spans="1:13" ht="13.5" customHeight="1">
       <c r="A174" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="D174" s="17" t="s">
-        <v>456</v>
-      </c>
-      <c r="E174" s="8" t="s">
-        <v>457</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D174" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="E174" s="4"/>
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
-      <c r="H174" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="I174" s="4"/>
+      <c r="H174" s="4"/>
+      <c r="I174" s="10" t="s">
+        <v>448</v>
+      </c>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
       <c r="L174" s="4"/>
@@ -8252,24 +8234,26 @@
     </row>
     <row r="175" spans="1:13" ht="13.5" customHeight="1">
       <c r="A175" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="D175" s="17" t="s">
-        <v>459</v>
+        <v>408</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D175" s="15" t="s">
+        <v>450</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="F175" s="4"/>
+        <v>451</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>451</v>
+      </c>
       <c r="G175" s="4"/>
       <c r="H175" s="8" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
@@ -8279,24 +8263,24 @@
     </row>
     <row r="176" spans="1:13" ht="13.5" customHeight="1">
       <c r="A176" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B176" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D176" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="C176" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="D176" s="17" t="s">
-        <v>462</v>
-      </c>
       <c r="E176" s="8" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
       <c r="H176" s="8" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
@@ -8306,24 +8290,24 @@
     </row>
     <row r="177" spans="1:13" ht="13.5" customHeight="1">
       <c r="A177" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="D177" s="17" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
       <c r="H177" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
@@ -8333,22 +8317,24 @@
     </row>
     <row r="178" spans="1:13" ht="13.5" customHeight="1">
       <c r="A178" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="B178" s="22" t="s">
-        <v>467</v>
-      </c>
-      <c r="C178" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="D178" s="27" t="s">
-        <v>469</v>
-      </c>
-      <c r="E178" s="5"/>
+        <v>408</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="D178" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>461</v>
+      </c>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
       <c r="H178" s="8" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
@@ -8358,22 +8344,24 @@
     </row>
     <row r="179" spans="1:13" ht="13.5" customHeight="1">
       <c r="A179" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="B179" s="22" t="s">
-        <v>467</v>
-      </c>
-      <c r="C179" s="22" t="s">
-        <v>471</v>
-      </c>
-      <c r="D179" s="27" t="s">
-        <v>472</v>
-      </c>
-      <c r="E179" s="5"/>
+        <v>408</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="D179" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>464</v>
+      </c>
       <c r="F179" s="4"/>
       <c r="G179" s="4"/>
       <c r="H179" s="8" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
@@ -8383,22 +8371,22 @@
     </row>
     <row r="180" spans="1:13" ht="13.5" customHeight="1">
       <c r="A180" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B180" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="C180" s="22" t="s">
+        <v>466</v>
+      </c>
+      <c r="D180" s="27" t="s">
         <v>467</v>
-      </c>
-      <c r="C180" s="22" t="s">
-        <v>474</v>
-      </c>
-      <c r="D180" s="28" t="s">
-        <v>475</v>
       </c>
       <c r="E180" s="5"/>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
       <c r="H180" s="8" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
@@ -8408,22 +8396,22 @@
     </row>
     <row r="181" spans="1:13" ht="13.5" customHeight="1">
       <c r="A181" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C181" s="22" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="D181" s="27" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="E181" s="5"/>
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
       <c r="H181" s="8" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
@@ -8433,22 +8421,22 @@
     </row>
     <row r="182" spans="1:13" ht="13.5" customHeight="1">
       <c r="A182" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B182" s="22" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C182" s="22" t="s">
-        <v>480</v>
-      </c>
-      <c r="D182" s="27" t="s">
-        <v>481</v>
+        <v>472</v>
+      </c>
+      <c r="D182" s="28" t="s">
+        <v>473</v>
       </c>
       <c r="E182" s="5"/>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
       <c r="H182" s="8" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
@@ -8458,50 +8446,48 @@
     </row>
     <row r="183" spans="1:13" ht="13.5" customHeight="1">
       <c r="A183" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B183" s="4"/>
-      <c r="C183" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="D183" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="E183" s="8" t="s">
-        <v>323</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="B183" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="C183" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="D183" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="E183" s="5"/>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
-      <c r="H183" s="5"/>
-      <c r="I183" s="23" t="s">
-        <v>486</v>
-      </c>
+      <c r="H183" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="I183" s="4"/>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
       <c r="L183" s="4"/>
       <c r="M183" s="5"/>
     </row>
     <row r="184" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A184" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="D184" s="15" t="s">
-        <v>490</v>
-      </c>
-      <c r="E184" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="F184" s="8" t="s">
-        <v>326</v>
-      </c>
+      <c r="A184" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B184" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="C184" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="D184" s="27" t="s">
+        <v>479</v>
+      </c>
+      <c r="E184" s="5"/>
+      <c r="F184" s="4"/>
       <c r="G184" s="4"/>
-      <c r="H184" s="4"/>
+      <c r="H184" s="8" t="s">
+        <v>480</v>
+      </c>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
@@ -8509,27 +8495,25 @@
       <c r="M184" s="5"/>
     </row>
     <row r="185" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A185" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>488</v>
-      </c>
+      <c r="A185" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B185" s="4"/>
       <c r="C185" s="5" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="D185" s="15" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="F185" s="8" t="s">
-        <v>326</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="F185" s="4"/>
       <c r="G185" s="4"/>
-      <c r="H185" s="4"/>
-      <c r="I185" s="4"/>
+      <c r="H185" s="5"/>
+      <c r="I185" s="23" t="s">
+        <v>484</v>
+      </c>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
       <c r="L185" s="4"/>
@@ -8537,25 +8521,25 @@
     </row>
     <row r="186" spans="1:13" ht="13.5" customHeight="1">
       <c r="A186" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C186" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="B186" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>495</v>
-      </c>
       <c r="D186" s="15" t="s">
-        <v>496</v>
-      </c>
-      <c r="E186" s="4"/>
+        <v>488</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>489</v>
+      </c>
       <c r="F186" s="8" t="s">
-        <v>497</v>
+        <v>324</v>
       </c>
       <c r="G186" s="4"/>
-      <c r="H186" s="8" t="s">
-        <v>497</v>
-      </c>
+      <c r="H186" s="4"/>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
@@ -8564,27 +8548,25 @@
     </row>
     <row r="187" spans="1:13" ht="13.5" customHeight="1">
       <c r="A187" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="D187" s="15" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="F187" s="8" t="s">
-        <v>501</v>
+        <v>324</v>
       </c>
       <c r="G187" s="4"/>
-      <c r="H187" s="8" t="s">
-        <v>501</v>
-      </c>
+      <c r="H187" s="4"/>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
@@ -8593,26 +8575,24 @@
     </row>
     <row r="188" spans="1:13" ht="13.5" customHeight="1">
       <c r="A188" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="D188" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="E188" s="8" t="s">
-        <v>23</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="E188" s="4"/>
       <c r="F188" s="8" t="s">
-        <v>23</v>
+        <v>495</v>
       </c>
       <c r="G188" s="4"/>
       <c r="H188" s="8" t="s">
-        <v>23</v>
+        <v>495</v>
       </c>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
@@ -8622,22 +8602,28 @@
     </row>
     <row r="189" spans="1:13" ht="13.5" customHeight="1">
       <c r="A189" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="B189" s="4"/>
+        <v>485</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>496</v>
+      </c>
       <c r="C189" s="5" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>505</v>
-      </c>
-      <c r="E189" s="4"/>
-      <c r="F189" s="4"/>
+        <v>498</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>499</v>
+      </c>
       <c r="G189" s="4"/>
-      <c r="H189" s="4"/>
-      <c r="I189" s="8" t="s">
-        <v>506</v>
-      </c>
+      <c r="H189" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="I189" s="4"/>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
       <c r="L189" s="4"/>
@@ -8645,24 +8631,28 @@
     </row>
     <row r="190" spans="1:13" ht="13.5" customHeight="1">
       <c r="A190" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>509</v>
+        <v>485</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>500</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="E190" s="4"/>
-      <c r="F190" s="4"/>
+        <v>501</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="G190" s="4"/>
-      <c r="H190" s="4"/>
-      <c r="I190" s="10" t="s">
-        <v>511</v>
-      </c>
+      <c r="H190" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I190" s="4"/>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
       <c r="L190" s="4"/>
@@ -8670,26 +8660,22 @@
     </row>
     <row r="191" spans="1:13" ht="13.5" customHeight="1">
       <c r="A191" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="B191" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="C191" s="7" t="s">
-        <v>512</v>
+        <v>485</v>
+      </c>
+      <c r="B191" s="4"/>
+      <c r="C191" s="5" t="s">
+        <v>502</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="E191" s="8" t="s">
-        <v>323</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="E191" s="4"/>
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
-      <c r="H191" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="I191" s="4"/>
+      <c r="H191" s="4"/>
+      <c r="I191" s="8" t="s">
+        <v>504</v>
+      </c>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
       <c r="L191" s="4"/>
@@ -8697,23 +8683,23 @@
     </row>
     <row r="192" spans="1:13" ht="13.5" customHeight="1">
       <c r="A192" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C192" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="B192" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="C192" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="D192" s="29" t="s">
-        <v>516</v>
-      </c>
-      <c r="E192" s="30"/>
-      <c r="F192" s="30"/>
-      <c r="G192" s="30"/>
-      <c r="H192" s="31"/>
+      <c r="D192" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4"/>
+      <c r="G192" s="4"/>
+      <c r="H192" s="4"/>
       <c r="I192" s="10" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
@@ -8722,24 +8708,24 @@
     </row>
     <row r="193" spans="1:13" ht="13.5" customHeight="1">
       <c r="A193" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="D193" s="15" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>520</v>
+        <v>321</v>
       </c>
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
       <c r="H193" s="8" t="s">
-        <v>520</v>
+        <v>321</v>
       </c>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
@@ -8749,24 +8735,24 @@
     </row>
     <row r="194" spans="1:13" ht="13.5" customHeight="1">
       <c r="A194" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="D194" s="15" t="s">
-        <v>523</v>
-      </c>
-      <c r="E194" s="4"/>
-      <c r="F194" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="G194" s="4"/>
-      <c r="H194" s="4"/>
-      <c r="I194" s="4"/>
+        <v>513</v>
+      </c>
+      <c r="D194" s="29" t="s">
+        <v>514</v>
+      </c>
+      <c r="E194" s="30"/>
+      <c r="F194" s="30"/>
+      <c r="G194" s="30"/>
+      <c r="H194" s="31"/>
+      <c r="I194" s="10" t="s">
+        <v>515</v>
+      </c>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
       <c r="L194" s="4"/>
@@ -8774,23 +8760,25 @@
     </row>
     <row r="195" spans="1:13" ht="13.5" customHeight="1">
       <c r="A195" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="D195" s="15" t="s">
-        <v>526</v>
-      </c>
-      <c r="E195" s="4"/>
-      <c r="F195" s="8" t="s">
-        <v>527</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="F195" s="4"/>
       <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
+      <c r="H195" s="8" t="s">
+        <v>518</v>
+      </c>
       <c r="I195" s="4"/>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
@@ -8799,20 +8787,20 @@
     </row>
     <row r="196" spans="1:13" ht="13.5" customHeight="1">
       <c r="A196" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B196" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="D196" s="15" t="s">
         <v>521</v>
-      </c>
-      <c r="C196" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="D196" s="15" t="s">
-        <v>529</v>
       </c>
       <c r="E196" s="4"/>
       <c r="F196" s="8" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="G196" s="4"/>
       <c r="H196" s="4"/>
@@ -8824,20 +8812,20 @@
     </row>
     <row r="197" spans="1:13" ht="13.5" customHeight="1">
       <c r="A197" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="8" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="G197" s="4"/>
       <c r="H197" s="4"/>
@@ -8849,20 +8837,20 @@
     </row>
     <row r="198" spans="1:13" ht="13.5" customHeight="1">
       <c r="A198" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="8" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="G198" s="4"/>
       <c r="H198" s="4"/>
@@ -8874,20 +8862,20 @@
     </row>
     <row r="199" spans="1:13" ht="13.5" customHeight="1">
       <c r="A199" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="8" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="G199" s="4"/>
       <c r="H199" s="4"/>
@@ -8899,20 +8887,20 @@
     </row>
     <row r="200" spans="1:13" ht="13.5" customHeight="1">
       <c r="A200" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="8" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
@@ -8924,20 +8912,20 @@
     </row>
     <row r="201" spans="1:13" ht="13.5" customHeight="1">
       <c r="A201" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="D201" s="15" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="E201" s="4"/>
       <c r="F201" s="8" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
@@ -8949,20 +8937,20 @@
     </row>
     <row r="202" spans="1:13" ht="13.5" customHeight="1">
       <c r="A202" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="E202" s="4"/>
       <c r="F202" s="8" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
@@ -8974,20 +8962,20 @@
     </row>
     <row r="203" spans="1:13" ht="13.5" customHeight="1">
       <c r="A203" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="8" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
@@ -8999,20 +8987,20 @@
     </row>
     <row r="204" spans="1:13" ht="13.5" customHeight="1">
       <c r="A204" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="8" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="G204" s="4"/>
       <c r="H204" s="4"/>
@@ -9024,20 +9012,20 @@
     </row>
     <row r="205" spans="1:13" ht="13.5" customHeight="1">
       <c r="A205" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="D205" s="15" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="8" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
@@ -9049,20 +9037,20 @@
     </row>
     <row r="206" spans="1:13" ht="13.5" customHeight="1">
       <c r="A206" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="8" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
@@ -9074,22 +9062,24 @@
     </row>
     <row r="207" spans="1:13" ht="13.5" customHeight="1">
       <c r="A207" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="B207" s="7"/>
+        <v>505</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>519</v>
+      </c>
       <c r="C207" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="D207" s="45" t="s">
-        <v>645</v>
+        <v>553</v>
+      </c>
+      <c r="D207" s="15" t="s">
+        <v>554</v>
       </c>
       <c r="E207" s="4"/>
-      <c r="F207" s="8"/>
+      <c r="F207" s="8" t="s">
+        <v>555</v>
+      </c>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
-      <c r="I207" s="4" t="s">
-        <v>646</v>
-      </c>
+      <c r="I207" s="4"/>
       <c r="J207" s="4"/>
       <c r="K207" s="4"/>
       <c r="L207" s="4"/>
@@ -9097,24 +9087,24 @@
     </row>
     <row r="208" spans="1:13" ht="13.5" customHeight="1">
       <c r="A208" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>561</v>
+        <v>519</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E208" s="4"/>
-      <c r="F208" s="4"/>
+      <c r="F208" s="8" t="s">
+        <v>558</v>
+      </c>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
-      <c r="I208" s="23" t="s">
-        <v>564</v>
-      </c>
+      <c r="I208" s="4"/>
       <c r="J208" s="4"/>
       <c r="K208" s="4"/>
       <c r="L208" s="4"/>
@@ -9122,23 +9112,21 @@
     </row>
     <row r="209" spans="1:13" ht="13.5" customHeight="1">
       <c r="A209" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="B209" s="7" t="s">
-        <v>565</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="B209" s="7"/>
       <c r="C209" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="D209" s="15" t="s">
-        <v>567</v>
+        <v>642</v>
+      </c>
+      <c r="D209" s="45" t="s">
+        <v>643</v>
       </c>
       <c r="E209" s="4"/>
-      <c r="F209" s="4"/>
+      <c r="F209" s="8"/>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
-      <c r="I209" s="23" t="s">
-        <v>568</v>
+      <c r="I209" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="J209" s="4"/>
       <c r="K209" s="4"/>
@@ -9147,23 +9135,23 @@
     </row>
     <row r="210" spans="1:13" ht="13.5" customHeight="1">
       <c r="A210" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="D210" s="15" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="4"/>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
       <c r="I210" s="23" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="J210" s="4"/>
       <c r="K210" s="4"/>
@@ -9172,23 +9160,23 @@
     </row>
     <row r="211" spans="1:13" ht="13.5" customHeight="1">
       <c r="A211" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B211" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="D211" s="15" t="s">
         <v>565</v>
-      </c>
-      <c r="C211" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="D211" s="15" t="s">
-        <v>573</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
-      <c r="I211" s="8" t="s">
-        <v>574</v>
+      <c r="I211" s="23" t="s">
+        <v>566</v>
       </c>
       <c r="J211" s="4"/>
       <c r="K211" s="4"/>
@@ -9197,21 +9185,23 @@
     </row>
     <row r="212" spans="1:13" ht="13.5" customHeight="1">
       <c r="A212" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="B212" s="4"/>
+        <v>505</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>563</v>
+      </c>
       <c r="C212" s="7" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="4"/>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
-      <c r="I212" s="8" t="s">
-        <v>578</v>
+      <c r="I212" s="23" t="s">
+        <v>569</v>
       </c>
       <c r="J212" s="4"/>
       <c r="K212" s="4"/>
@@ -9220,48 +9210,46 @@
     </row>
     <row r="213" spans="1:13" ht="13.5" customHeight="1">
       <c r="A213" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="B213" s="4"/>
+        <v>505</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>563</v>
+      </c>
       <c r="C213" s="7" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>580</v>
-      </c>
-      <c r="E213" s="23" t="s">
-        <v>581</v>
-      </c>
-      <c r="F213" s="23" t="s">
-        <v>581</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="E213" s="4"/>
+      <c r="F213" s="4"/>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
-      <c r="I213" s="4"/>
+      <c r="I213" s="8" t="s">
+        <v>572</v>
+      </c>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
       <c r="L213" s="4"/>
       <c r="M213" s="5"/>
     </row>
     <row r="214" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A214" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="B214" s="24" t="s">
-        <v>583</v>
-      </c>
-      <c r="C214" s="32" t="s">
-        <v>583</v>
-      </c>
-      <c r="D214" s="33" t="s">
-        <v>584</v>
+      <c r="A214" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="B214" s="4"/>
+      <c r="C214" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="D214" s="15" t="s">
+        <v>575</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
-      <c r="I214" s="23" t="s">
-        <v>585</v>
+      <c r="I214" s="8" t="s">
+        <v>576</v>
       </c>
       <c r="J214" s="4"/>
       <c r="K214" s="4"/>
@@ -9269,23 +9257,21 @@
       <c r="M214" s="5"/>
     </row>
     <row r="215" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A215" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="B215" s="24" t="s">
-        <v>583</v>
-      </c>
-      <c r="C215" s="32" t="s">
-        <v>586</v>
+      <c r="A215" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="B215" s="4"/>
+      <c r="C215" s="7" t="s">
+        <v>577</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E215" s="23" t="s">
-        <v>269</v>
+        <v>579</v>
       </c>
       <c r="F215" s="23" t="s">
-        <v>269</v>
+        <v>579</v>
       </c>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
@@ -9297,21 +9283,23 @@
     </row>
     <row r="216" spans="1:13" ht="13.5" customHeight="1">
       <c r="A216" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B216" s="24" t="s">
+        <v>581</v>
+      </c>
+      <c r="C216" s="32" t="s">
+        <v>581</v>
+      </c>
+      <c r="D216" s="33" t="s">
         <v>582</v>
-      </c>
-      <c r="B216" s="4"/>
-      <c r="C216" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="D216" s="15" t="s">
-        <v>589</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
-      <c r="I216" s="8" t="s">
-        <v>590</v>
+      <c r="I216" s="23" t="s">
+        <v>583</v>
       </c>
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
@@ -9320,22 +9308,26 @@
     </row>
     <row r="217" spans="1:13" ht="13.5" customHeight="1">
       <c r="A217" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="B217" s="4"/>
-      <c r="C217" s="7" t="s">
-        <v>591</v>
+        <v>580</v>
+      </c>
+      <c r="B217" s="24" t="s">
+        <v>581</v>
+      </c>
+      <c r="C217" s="32" t="s">
+        <v>584</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>592</v>
-      </c>
-      <c r="E217" s="4"/>
-      <c r="F217" s="4"/>
+        <v>585</v>
+      </c>
+      <c r="E217" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="F217" s="23" t="s">
+        <v>267</v>
+      </c>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
-      <c r="I217" s="10" t="s">
-        <v>593</v>
-      </c>
+      <c r="I217" s="4"/>
       <c r="J217" s="4"/>
       <c r="K217" s="4"/>
       <c r="L217" s="4"/>
@@ -9343,21 +9335,21 @@
     </row>
     <row r="218" spans="1:13" ht="13.5" customHeight="1">
       <c r="A218" s="5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B218" s="4"/>
-      <c r="C218" s="7" t="s">
-        <v>594</v>
+      <c r="C218" s="5" t="s">
+        <v>586</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
       <c r="I218" s="8" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
@@ -9366,21 +9358,21 @@
     </row>
     <row r="219" spans="1:13" ht="13.5" customHeight="1">
       <c r="A219" s="5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B219" s="4"/>
-      <c r="C219" s="5" t="s">
-        <v>597</v>
+      <c r="C219" s="7" t="s">
+        <v>589</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
-      <c r="I219" s="8" t="s">
-        <v>599</v>
+      <c r="I219" s="10" t="s">
+        <v>591</v>
       </c>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
@@ -9389,44 +9381,44 @@
     </row>
     <row r="220" spans="1:13" ht="13.5" customHeight="1">
       <c r="A220" s="5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B220" s="4"/>
-      <c r="C220" s="5" t="s">
-        <v>600</v>
+      <c r="C220" s="7" t="s">
+        <v>592</v>
       </c>
       <c r="D220" s="15" t="s">
-        <v>601</v>
-      </c>
-      <c r="E220" s="8" t="s">
-        <v>602</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="E220" s="4"/>
       <c r="F220" s="4"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
-      <c r="I220" s="4"/>
+      <c r="I220" s="8" t="s">
+        <v>594</v>
+      </c>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
       <c r="L220" s="4"/>
       <c r="M220" s="5"/>
     </row>
     <row r="221" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A221" s="7" t="s">
-        <v>603</v>
+      <c r="A221" s="5" t="s">
+        <v>580</v>
       </c>
       <c r="B221" s="4"/>
-      <c r="C221" s="22" t="s">
-        <v>604</v>
-      </c>
-      <c r="D221" s="33" t="s">
-        <v>605</v>
-      </c>
-      <c r="E221" s="5"/>
+      <c r="C221" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="D221" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="E221" s="4"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
-      <c r="I221" s="23" t="s">
-        <v>606</v>
+      <c r="I221" s="8" t="s">
+        <v>597</v>
       </c>
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
@@ -9434,23 +9426,23 @@
       <c r="M221" s="5"/>
     </row>
     <row r="222" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A222" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="B222" s="3"/>
-      <c r="C222" s="34" t="s">
-        <v>607</v>
-      </c>
-      <c r="D222" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="E222" s="3"/>
+      <c r="A222" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B222" s="4"/>
+      <c r="C222" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="D222" s="15" t="s">
+        <v>599</v>
+      </c>
+      <c r="E222" s="8" t="s">
+        <v>600</v>
+      </c>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
-      <c r="H222" s="3"/>
-      <c r="I222" s="8" t="s">
-        <v>609</v>
-      </c>
+      <c r="H222" s="4"/>
+      <c r="I222" s="4"/>
       <c r="J222" s="4"/>
       <c r="K222" s="4"/>
       <c r="L222" s="4"/>
@@ -9458,21 +9450,21 @@
     </row>
     <row r="223" spans="1:13" ht="13.5" customHeight="1">
       <c r="A223" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="B223" s="4"/>
+      <c r="C223" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="D223" s="33" t="s">
         <v>603</v>
       </c>
-      <c r="B223" s="3"/>
-      <c r="C223" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="D223" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="E223" s="3"/>
+      <c r="E223" s="5"/>
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
-      <c r="H223" s="3"/>
-      <c r="I223" s="8" t="s">
-        <v>612</v>
+      <c r="H223" s="4"/>
+      <c r="I223" s="23" t="s">
+        <v>604</v>
       </c>
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
@@ -9481,21 +9473,21 @@
     </row>
     <row r="224" spans="1:13" ht="13.5" customHeight="1">
       <c r="A224" s="7" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B224" s="3"/>
-      <c r="C224" s="10" t="s">
-        <v>613</v>
-      </c>
-      <c r="D224" s="9" t="s">
-        <v>614</v>
+      <c r="C224" s="34" t="s">
+        <v>605</v>
+      </c>
+      <c r="D224" s="35" t="s">
+        <v>606</v>
       </c>
       <c r="E224" s="3"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
       <c r="H224" s="3"/>
       <c r="I224" s="8" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
@@ -9504,21 +9496,21 @@
     </row>
     <row r="225" spans="1:13" ht="13.5" customHeight="1">
       <c r="A225" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="B225" s="4"/>
-      <c r="C225" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="D225" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="E225" s="4"/>
+        <v>601</v>
+      </c>
+      <c r="B225" s="3"/>
+      <c r="C225" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="E225" s="3"/>
       <c r="F225" s="4"/>
       <c r="G225" s="4"/>
-      <c r="H225" s="4"/>
+      <c r="H225" s="3"/>
       <c r="I225" s="8" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
@@ -9527,21 +9519,21 @@
     </row>
     <row r="226" spans="1:13" ht="13.5" customHeight="1">
       <c r="A226" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="B226" s="4"/>
-      <c r="C226" s="8" t="s">
-        <v>620</v>
-      </c>
-      <c r="D226" s="36" t="s">
-        <v>621</v>
-      </c>
-      <c r="E226" s="4"/>
+        <v>601</v>
+      </c>
+      <c r="B226" s="3"/>
+      <c r="C226" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="D226" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="E226" s="3"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
-      <c r="H226" s="4"/>
+      <c r="H226" s="3"/>
       <c r="I226" s="8" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
@@ -9549,22 +9541,22 @@
       <c r="M226" s="5"/>
     </row>
     <row r="227" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A227" s="37" t="s">
-        <v>623</v>
-      </c>
-      <c r="B227" s="38"/>
-      <c r="C227" s="39" t="s">
-        <v>624</v>
-      </c>
-      <c r="D227" s="40" t="s">
-        <v>625</v>
-      </c>
-      <c r="E227" s="41"/>
+      <c r="A227" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="B227" s="4"/>
+      <c r="C227" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="D227" s="15" t="s">
+        <v>616</v>
+      </c>
+      <c r="E227" s="4"/>
       <c r="F227" s="4"/>
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
       <c r="I227" s="8" t="s">
-        <v>272</v>
+        <v>617</v>
       </c>
       <c r="J227" s="4"/>
       <c r="K227" s="4"/>
@@ -9572,22 +9564,22 @@
       <c r="M227" s="5"/>
     </row>
     <row r="228" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A228" s="37" t="s">
-        <v>623</v>
-      </c>
-      <c r="B228" s="24"/>
-      <c r="C228" s="42" t="s">
-        <v>258</v>
-      </c>
-      <c r="D228" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="E228" s="3"/>
-      <c r="F228" s="20"/>
-      <c r="G228" s="20"/>
-      <c r="H228" s="3"/>
+      <c r="A228" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="B228" s="4"/>
+      <c r="C228" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="D228" s="36" t="s">
+        <v>619</v>
+      </c>
+      <c r="E228" s="4"/>
+      <c r="F228" s="4"/>
+      <c r="G228" s="4"/>
+      <c r="H228" s="4"/>
       <c r="I228" s="8" t="s">
-        <v>260</v>
+        <v>620</v>
       </c>
       <c r="J228" s="4"/>
       <c r="K228" s="4"/>
@@ -9596,21 +9588,21 @@
     </row>
     <row r="229" spans="1:13" ht="13.5" customHeight="1">
       <c r="A229" s="37" t="s">
+        <v>621</v>
+      </c>
+      <c r="B229" s="38"/>
+      <c r="C229" s="39" t="s">
+        <v>622</v>
+      </c>
+      <c r="D229" s="40" t="s">
         <v>623</v>
       </c>
-      <c r="B229" s="24"/>
-      <c r="C229" s="39" t="s">
-        <v>626</v>
-      </c>
-      <c r="D229" s="40" t="s">
-        <v>627</v>
-      </c>
-      <c r="E229" s="4"/>
+      <c r="E229" s="41"/>
       <c r="F229" s="4"/>
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
-      <c r="I229" s="23" t="s">
-        <v>585</v>
+      <c r="I229" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
@@ -9619,21 +9611,21 @@
     </row>
     <row r="230" spans="1:13" ht="13.5" customHeight="1">
       <c r="A230" s="37" t="s">
-        <v>623</v>
-      </c>
-      <c r="B230" s="38"/>
-      <c r="C230" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="D230" s="44" t="s">
-        <v>235</v>
+        <v>621</v>
+      </c>
+      <c r="B230" s="24"/>
+      <c r="C230" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="D230" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="E230" s="3"/>
       <c r="F230" s="20"/>
       <c r="G230" s="20"/>
       <c r="H230" s="3"/>
       <c r="I230" s="8" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
@@ -9642,21 +9634,21 @@
     </row>
     <row r="231" spans="1:13" ht="13.5" customHeight="1">
       <c r="A231" s="37" t="s">
-        <v>623</v>
-      </c>
-      <c r="B231" s="38"/>
-      <c r="C231" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D231" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="E231" s="3"/>
-      <c r="F231" s="20"/>
-      <c r="G231" s="20"/>
-      <c r="H231" s="3"/>
-      <c r="I231" s="8" t="s">
-        <v>251</v>
+        <v>621</v>
+      </c>
+      <c r="B231" s="24"/>
+      <c r="C231" s="39" t="s">
+        <v>624</v>
+      </c>
+      <c r="D231" s="40" t="s">
+        <v>625</v>
+      </c>
+      <c r="E231" s="4"/>
+      <c r="F231" s="4"/>
+      <c r="G231" s="4"/>
+      <c r="H231" s="4"/>
+      <c r="I231" s="23" t="s">
+        <v>583</v>
       </c>
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
@@ -9665,23 +9657,21 @@
     </row>
     <row r="232" spans="1:13" ht="13.5" customHeight="1">
       <c r="A232" s="37" t="s">
-        <v>623</v>
-      </c>
-      <c r="B232" s="38" t="s">
-        <v>628</v>
-      </c>
-      <c r="C232" s="39" t="s">
-        <v>629</v>
-      </c>
-      <c r="D232" s="40" t="s">
-        <v>630</v>
-      </c>
-      <c r="E232" s="4"/>
-      <c r="F232" s="4"/>
-      <c r="G232" s="4"/>
-      <c r="H232" s="4"/>
-      <c r="I232" s="23" t="s">
-        <v>631</v>
+        <v>621</v>
+      </c>
+      <c r="B232" s="38"/>
+      <c r="C232" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="D232" s="44" t="s">
+        <v>233</v>
+      </c>
+      <c r="E232" s="3"/>
+      <c r="F232" s="20"/>
+      <c r="G232" s="20"/>
+      <c r="H232" s="3"/>
+      <c r="I232" s="8" t="s">
+        <v>225</v>
       </c>
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
@@ -9690,23 +9680,21 @@
     </row>
     <row r="233" spans="1:13" ht="13.5" customHeight="1">
       <c r="A233" s="37" t="s">
-        <v>623</v>
-      </c>
-      <c r="B233" s="38" t="s">
-        <v>628</v>
-      </c>
-      <c r="C233" s="39" t="s">
-        <v>632</v>
-      </c>
-      <c r="D233" s="40" t="s">
-        <v>633</v>
-      </c>
-      <c r="E233" s="4"/>
-      <c r="F233" s="4"/>
-      <c r="G233" s="4"/>
-      <c r="H233" s="4"/>
-      <c r="I233" s="23" t="s">
-        <v>634</v>
+        <v>621</v>
+      </c>
+      <c r="B233" s="38"/>
+      <c r="C233" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E233" s="3"/>
+      <c r="F233" s="20"/>
+      <c r="G233" s="20"/>
+      <c r="H233" s="3"/>
+      <c r="I233" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
@@ -9715,23 +9703,23 @@
     </row>
     <row r="234" spans="1:13" ht="13.5" customHeight="1">
       <c r="A234" s="37" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B234" s="38" t="s">
+        <v>626</v>
+      </c>
+      <c r="C234" s="39" t="s">
+        <v>627</v>
+      </c>
+      <c r="D234" s="40" t="s">
         <v>628</v>
-      </c>
-      <c r="C234" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="D234" s="40" t="s">
-        <v>635</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="4"/>
       <c r="G234" s="4"/>
       <c r="H234" s="4"/>
       <c r="I234" s="23" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
@@ -9739,30 +9727,50 @@
       <c r="M234" s="5"/>
     </row>
     <row r="235" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A235" s="4"/>
-      <c r="B235" s="4"/>
-      <c r="C235" s="4"/>
-      <c r="D235" s="4"/>
+      <c r="A235" s="37" t="s">
+        <v>621</v>
+      </c>
+      <c r="B235" s="38" t="s">
+        <v>626</v>
+      </c>
+      <c r="C235" s="39" t="s">
+        <v>630</v>
+      </c>
+      <c r="D235" s="40" t="s">
+        <v>631</v>
+      </c>
       <c r="E235" s="4"/>
       <c r="F235" s="4"/>
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
-      <c r="I235" s="4"/>
+      <c r="I235" s="23" t="s">
+        <v>632</v>
+      </c>
       <c r="J235" s="4"/>
       <c r="K235" s="4"/>
       <c r="L235" s="4"/>
       <c r="M235" s="5"/>
     </row>
     <row r="236" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A236" s="4"/>
-      <c r="B236" s="4"/>
-      <c r="C236" s="4"/>
-      <c r="D236" s="4"/>
+      <c r="A236" s="37" t="s">
+        <v>621</v>
+      </c>
+      <c r="B236" s="38" t="s">
+        <v>626</v>
+      </c>
+      <c r="C236" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="D236" s="40" t="s">
+        <v>633</v>
+      </c>
       <c r="E236" s="4"/>
       <c r="F236" s="4"/>
       <c r="G236" s="4"/>
       <c r="H236" s="4"/>
-      <c r="I236" s="4"/>
+      <c r="I236" s="23" t="s">
+        <v>634</v>
+      </c>
       <c r="J236" s="4"/>
       <c r="K236" s="4"/>
       <c r="L236" s="4"/>
@@ -12543,8 +12551,36 @@
       <c r="L421" s="4"/>
       <c r="M421" s="5"/>
     </row>
-    <row r="422" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="423" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="422" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A422" s="4"/>
+      <c r="B422" s="4"/>
+      <c r="C422" s="4"/>
+      <c r="D422" s="4"/>
+      <c r="E422" s="4"/>
+      <c r="F422" s="4"/>
+      <c r="G422" s="4"/>
+      <c r="H422" s="4"/>
+      <c r="I422" s="4"/>
+      <c r="J422" s="4"/>
+      <c r="K422" s="4"/>
+      <c r="L422" s="4"/>
+      <c r="M422" s="5"/>
+    </row>
+    <row r="423" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A423" s="4"/>
+      <c r="B423" s="4"/>
+      <c r="C423" s="4"/>
+      <c r="D423" s="4"/>
+      <c r="E423" s="4"/>
+      <c r="F423" s="4"/>
+      <c r="G423" s="4"/>
+      <c r="H423" s="4"/>
+      <c r="I423" s="4"/>
+      <c r="J423" s="4"/>
+      <c r="K423" s="4"/>
+      <c r="L423" s="4"/>
+      <c r="M423" s="5"/>
+    </row>
     <row r="424" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="425" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="426" spans="1:13" ht="15.75" customHeight="1"/>
@@ -13140,6 +13176,8 @@
     <row r="1016" ht="15.75" customHeight="1"/>
     <row r="1017" ht="15.75" customHeight="1"/>
     <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
+    <row r="1020" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="14"/>
   <hyperlinks>
@@ -13214,143 +13252,145 @@
     <hyperlink ref="D72" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
     <hyperlink ref="D73" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
     <hyperlink ref="D74" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D75" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="D76" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D77" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D78" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D79" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D80" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D81" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D82" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D83" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D84" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D85" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D86" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D87" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D88" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D89" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D90" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D91" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D92" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D93" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D94" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D102" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D108" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D109" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D110" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D111" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D112" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D113" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="D114" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D115" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D116" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D117" r:id="rId102" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="D118" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="D119" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="D120" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="D121" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="D122" r:id="rId107" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="D123" r:id="rId108" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="D124" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="D125" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="D126" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D127" r:id="rId112" display="https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="D128" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="D129" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="D130" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D131" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="D132" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="D133" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="D134" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="D135" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="D136" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D137" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="D138" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="D139" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="D140" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="D141" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="D142" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="D143" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="D144" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="D145" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="D146" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="D147" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="D148" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="D149" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="D150" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="D151" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="D152" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="D153" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="D154" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="D155" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="D156" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="D157" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="D158" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="D159" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="D165" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="D166" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="D167" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="D168" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="D169" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="D170" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="D171" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="D172" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="D173" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="D174" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="D175" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="D176" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="D177" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="D178" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="D179" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="D181" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="D182" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D183" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="D184" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D185" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="D186" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D187" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D188" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D189" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="D190" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D191" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="D192" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D193" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="D194" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D195" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D196" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D197" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D198" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D199" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="D200" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D201" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="D202" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D203" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="D204" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D205" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="D206" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D208" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D209" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D210" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D211" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D212" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D213" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D214" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D216" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D217" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D218" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D219" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D220" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D221" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="D222" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D223" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="D224" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D225" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="D226" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D228" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="D230" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D231" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="D77" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D78" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="D79" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D80" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D81" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D82" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D83" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D84" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D85" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D86" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D87" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D88" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D89" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D90" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D91" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D92" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D93" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D94" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D95" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D96" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D104" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D110" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D111" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D112" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D113" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D114" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="D115" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="D116" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="D117" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D118" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="D119" r:id="rId102" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="D120" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="D121" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="D122" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="D123" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="D124" r:id="rId107" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="D125" r:id="rId108" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="D126" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="D127" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="D128" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="D129" r:id="rId112" display="https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="D130" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="D131" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="D132" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="D133" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="D134" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="D135" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="D136" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="D137" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="D138" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="D139" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="D140" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="D141" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="D142" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="D143" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="D144" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="D145" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="D146" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="D147" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="D148" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="D149" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="D150" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="D151" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="D152" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="D153" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="D154" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="D155" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="D156" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="D157" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="D158" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="D159" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="D160" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="D161" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="D167" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="D168" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="D169" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="D170" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="D171" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="D172" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="D173" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="D174" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="D175" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="D176" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="D177" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="D178" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="D179" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="D180" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="D181" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="D183" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="D184" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="D185" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="D186" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="D187" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="D188" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="D189" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="D190" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="D191" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="D192" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="D193" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="D194" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="D195" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="D196" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="D197" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="D198" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="D199" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="D200" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="D201" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="D202" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="D203" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="D204" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="D205" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="D206" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="D207" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="D208" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="D210" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D211" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D212" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D213" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D214" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D215" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D216" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D218" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D219" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D220" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D221" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D222" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D223" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="D224" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="D225" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="D226" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="D227" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="D228" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="D230" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="D232" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="D233" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
     <hyperlink ref="D16" r:id="rId207" xr:uid="{101A33D7-B7BA-422E-B2FC-342D5148D1EA}"/>
-    <hyperlink ref="D207" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
+    <hyperlink ref="D209" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
+    <hyperlink ref="D76" r:id="rId209" xr:uid="{15E62A8C-2F55-4EC5-B29A-D16518F2E4D9}"/>
+    <hyperlink ref="D75" r:id="rId210" xr:uid="{FC2D964E-B283-4703-AAB9-28EC36520D76}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\vm22flo01\DownloadFiles\スマートシティ課\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C386E1D-0B89-44A2-AC61-E0DFAA35871F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900785F1-3AFA-4EC2-A333-B03E27B74E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="652">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -737,58 +737,6 @@
     <t>https://yaizu-smartcity.jp/tiles/%E5%86%85%E6%B0%B4%E6%B5%B8%E6%B0%B4%E6%83%B3%E5%AE%9A%E5%8C%BA%E5%9F%9F(%E5%85%AC%E5%85%B1%E4%B8%8B%E6%B0%B4%E9%81%93%E5%8C%BA%E5%9F%9F%E5%86%85)/tiles.json</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>浸水履歴（平成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>年～令和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>年）</t>
-    </r>
-  </si>
-  <si>
     <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E7%B5%B1%E5%90%88/tiles.json</t>
   </si>
   <si>
@@ -3074,18 +3022,18 @@
   </si>
   <si>
     <t>fish</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/%E8%A6%81%E9%85%8D%E6%85%AE%E8%80%85%E5%88%A9%E7%94%A8%E6%96%BD%E8%A8%AD/tiles.json</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>避難施設</t>
     <rPh sb="0" eb="4">
       <t>ヒナンシセツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>要配慮者利用施設</t>
@@ -3104,19 +3052,19 @@
     <rPh sb="6" eb="8">
       <t>シセツ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>防災</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>elderly-welfare-facility</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>高潮浸水想定区域（浸水区域及び浸水深）</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>子どもを守る家</t>
@@ -3129,22 +3077,22 @@
     <rPh sb="6" eb="7">
       <t>イエ</t>
     </rPh>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/%E5%AD%90%E3%81%A9%E3%82%82%E3%82%92%E5%AE%88%E3%82%8B%E5%AE%B6/tiles.json</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>randoseru</t>
   </si>
   <si>
     <t>令和7年</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>令和6年</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <r>
@@ -3170,15 +3118,15 @@
       </rPr>
       <t>年～令和7年）</t>
     </r>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E4%BB%A4%E5%92%8C6%E5%B9%B4/tiles.json</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <t>https://yaizu-smartcity.jp/tiles/%E6%B5%B8%E6%B0%B4%E5%B1%A5%E6%AD%B4_%E4%BB%A4%E5%92%8C7%E5%B9%B4/tiles.json</t>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
   </si>
   <si>
     <r>
@@ -3204,20 +3152,90 @@
       </rPr>
       <t>年</t>
     </r>
-    <phoneticPr fontId="14"/>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <r>
+      <t>浸水履歴（平成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年～令和7年）</t>
+    </r>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <r>
+      <t>浸水履歴（平成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年～令和7年）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3458,14 +3476,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3475,96 +3493,96 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -3834,7 +3852,7 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.21875" customWidth="1"/>
     <col min="3" max="3" width="23.44140625" customWidth="1"/>
     <col min="4" max="4" width="153.109375" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" customWidth="1"/>
@@ -3911,7 +3929,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>18</v>
@@ -3936,7 +3954,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>21</v>
@@ -3961,7 +3979,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>24</v>
@@ -4233,23 +4251,23 @@
     </row>
     <row r="16" spans="1:13" ht="13.5" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D16" s="45" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="12" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -5642,13 +5660,13 @@
         <v>16</v>
       </c>
       <c r="B74" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="D74" s="17" t="s">
         <v>171</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>647</v>
-      </c>
-      <c r="D74" s="17" t="s">
-        <v>172</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>15</v>
@@ -5669,13 +5687,13 @@
         <v>16</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>171</v>
+        <v>650</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D75" s="45" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>15</v>
@@ -5696,13 +5714,13 @@
         <v>16</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D76" s="45" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>15</v>
@@ -5723,13 +5741,13 @@
         <v>16</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>15</v>
@@ -5750,13 +5768,13 @@
         <v>16</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C78" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D78" s="17" t="s">
         <v>174</v>
-      </c>
-      <c r="D78" s="17" t="s">
-        <v>175</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>15</v>
@@ -5777,13 +5795,13 @@
         <v>16</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C79" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D79" s="17" t="s">
         <v>176</v>
-      </c>
-      <c r="D79" s="17" t="s">
-        <v>177</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>15</v>
@@ -5804,13 +5822,13 @@
         <v>16</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C80" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D80" s="17" t="s">
         <v>178</v>
-      </c>
-      <c r="D80" s="17" t="s">
-        <v>179</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>15</v>
@@ -5831,13 +5849,13 @@
         <v>16</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C81" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D81" s="17" t="s">
         <v>180</v>
-      </c>
-      <c r="D81" s="17" t="s">
-        <v>181</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>15</v>
@@ -5858,13 +5876,13 @@
         <v>16</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C82" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D82" s="17" t="s">
         <v>182</v>
-      </c>
-      <c r="D82" s="17" t="s">
-        <v>183</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>15</v>
@@ -5885,13 +5903,13 @@
         <v>16</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C83" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D83" s="17" t="s">
         <v>184</v>
-      </c>
-      <c r="D83" s="17" t="s">
-        <v>185</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>15</v>
@@ -5912,13 +5930,13 @@
         <v>16</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C84" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D84" s="17" t="s">
         <v>186</v>
-      </c>
-      <c r="D84" s="17" t="s">
-        <v>187</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>15</v>
@@ -5939,13 +5957,13 @@
         <v>16</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C85" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D85" s="17" t="s">
         <v>188</v>
-      </c>
-      <c r="D85" s="17" t="s">
-        <v>189</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>15</v>
@@ -5966,13 +5984,13 @@
         <v>16</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C86" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D86" s="17" t="s">
         <v>190</v>
-      </c>
-      <c r="D86" s="17" t="s">
-        <v>191</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>15</v>
@@ -5993,13 +6011,13 @@
         <v>16</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C87" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D87" s="17" t="s">
         <v>192</v>
-      </c>
-      <c r="D87" s="17" t="s">
-        <v>193</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>15</v>
@@ -6020,13 +6038,13 @@
         <v>16</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C88" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D88" s="17" t="s">
         <v>194</v>
-      </c>
-      <c r="D88" s="17" t="s">
-        <v>195</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>15</v>
@@ -6047,13 +6065,13 @@
         <v>16</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C89" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D89" s="17" t="s">
         <v>196</v>
-      </c>
-      <c r="D89" s="17" t="s">
-        <v>197</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>15</v>
@@ -6074,13 +6092,13 @@
         <v>16</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C90" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D90" s="17" t="s">
         <v>198</v>
-      </c>
-      <c r="D90" s="17" t="s">
-        <v>199</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>15</v>
@@ -6101,13 +6119,13 @@
         <v>16</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C91" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D91" s="17" t="s">
         <v>200</v>
-      </c>
-      <c r="D91" s="17" t="s">
-        <v>201</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>15</v>
@@ -6128,13 +6146,13 @@
         <v>16</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C92" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D92" s="17" t="s">
         <v>202</v>
-      </c>
-      <c r="D92" s="17" t="s">
-        <v>203</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>15</v>
@@ -6155,13 +6173,13 @@
         <v>16</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C93" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D93" s="17" t="s">
         <v>204</v>
-      </c>
-      <c r="D93" s="17" t="s">
-        <v>205</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>15</v>
@@ -6182,13 +6200,13 @@
         <v>16</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C94" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D94" s="17" t="s">
         <v>206</v>
-      </c>
-      <c r="D94" s="17" t="s">
-        <v>207</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>15</v>
@@ -6209,13 +6227,13 @@
         <v>16</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C95" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D95" s="17" t="s">
         <v>208</v>
-      </c>
-      <c r="D95" s="17" t="s">
-        <v>209</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>15</v>
@@ -6236,13 +6254,13 @@
         <v>16</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>171</v>
+        <v>651</v>
       </c>
       <c r="C96" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D96" s="17" t="s">
         <v>210</v>
-      </c>
-      <c r="D96" s="17" t="s">
-        <v>211</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>15</v>
@@ -6264,10 +6282,10 @@
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="4"/>
@@ -6285,10 +6303,10 @@
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D98" s="17" t="s">
         <v>213</v>
-      </c>
-      <c r="D98" s="17" t="s">
-        <v>214</v>
       </c>
       <c r="E98" s="7"/>
       <c r="F98" s="4"/>
@@ -6306,18 +6324,18 @@
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D99" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="D99" s="17" t="s">
+      <c r="E99" s="10" t="s">
         <v>216</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>217</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
       <c r="H99" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
@@ -6331,18 +6349,18 @@
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D100" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="D100" s="17" t="s">
+      <c r="E100" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
       <c r="H100" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
@@ -6352,23 +6370,23 @@
     </row>
     <row r="101" spans="1:13" ht="13.5" customHeight="1">
       <c r="A101" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B101" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="B101" s="22" t="s">
+      <c r="C101" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="C101" s="22" t="s">
+      <c r="D101" s="17" t="s">
         <v>223</v>
-      </c>
-      <c r="D101" s="17" t="s">
-        <v>224</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
       <c r="H101" s="7"/>
       <c r="I101" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
@@ -6377,23 +6395,23 @@
     </row>
     <row r="102" spans="1:13" ht="13.5" customHeight="1">
       <c r="A102" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B102" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="B102" s="22" t="s">
-        <v>222</v>
-      </c>
       <c r="C102" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="D102" s="17" t="s">
         <v>226</v>
-      </c>
-      <c r="D102" s="17" t="s">
-        <v>227</v>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
       <c r="H102" s="7"/>
       <c r="I102" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
@@ -6402,23 +6420,23 @@
     </row>
     <row r="103" spans="1:13" ht="13.5" customHeight="1">
       <c r="A103" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B103" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="B103" s="22" t="s">
-        <v>222</v>
-      </c>
       <c r="C103" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D103" s="17" t="s">
         <v>229</v>
-      </c>
-      <c r="D103" s="17" t="s">
-        <v>230</v>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
       <c r="H103" s="7"/>
       <c r="I103" s="23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
@@ -6427,21 +6445,21 @@
     </row>
     <row r="104" spans="1:13" ht="13.5" customHeight="1">
       <c r="A104" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>233</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="20"/>
       <c r="G104" s="20"/>
       <c r="H104" s="3"/>
       <c r="I104" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
@@ -6450,23 +6468,23 @@
     </row>
     <row r="105" spans="1:13" ht="13.5" customHeight="1">
       <c r="A105" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B105" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="C105" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="C105" s="22" t="s">
+      <c r="D105" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="20"/>
       <c r="G105" s="20"/>
       <c r="H105" s="3"/>
       <c r="I105" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
@@ -6475,23 +6493,23 @@
     </row>
     <row r="106" spans="1:13" ht="13.5" customHeight="1">
       <c r="A106" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B106" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C106" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="D106" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="20"/>
       <c r="G106" s="20"/>
       <c r="H106" s="3"/>
       <c r="I106" s="8" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
@@ -6500,23 +6518,23 @@
     </row>
     <row r="107" spans="1:13" ht="13.5" customHeight="1">
       <c r="A107" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B107" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C107" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="D107" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="20"/>
       <c r="G107" s="20"/>
       <c r="H107" s="3"/>
       <c r="I107" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
@@ -6525,23 +6543,23 @@
     </row>
     <row r="108" spans="1:13" ht="13.5" customHeight="1">
       <c r="A108" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B108" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C108" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="D108" s="25" t="s">
         <v>242</v>
-      </c>
-      <c r="D108" s="25" t="s">
-        <v>243</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="20"/>
       <c r="G108" s="20"/>
       <c r="H108" s="3"/>
       <c r="I108" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
@@ -6550,23 +6568,23 @@
     </row>
     <row r="109" spans="1:13" ht="13.5" customHeight="1">
       <c r="A109" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B109" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C109" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="D109" s="9" t="s">
         <v>244</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>245</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="20"/>
       <c r="G109" s="20"/>
       <c r="H109" s="3"/>
       <c r="I109" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
@@ -6575,23 +6593,23 @@
     </row>
     <row r="110" spans="1:13" ht="13.5" customHeight="1">
       <c r="A110" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B110" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C110" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="D110" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="D110" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="20"/>
       <c r="G110" s="20"/>
       <c r="H110" s="3"/>
       <c r="I110" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
@@ -6600,23 +6618,23 @@
     </row>
     <row r="111" spans="1:13" ht="13.5" customHeight="1">
       <c r="A111" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C111" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D111" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>251</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="4"/>
       <c r="G111" s="20"/>
       <c r="H111" s="3"/>
       <c r="I111" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
@@ -6625,21 +6643,21 @@
     </row>
     <row r="112" spans="1:13" ht="13.5" customHeight="1">
       <c r="A112" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D112" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>254</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="20"/>
       <c r="G112" s="20"/>
       <c r="H112" s="3"/>
       <c r="I112" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
@@ -6648,21 +6666,21 @@
     </row>
     <row r="113" spans="1:13" ht="13.5" customHeight="1">
       <c r="A113" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D113" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="20"/>
       <c r="G113" s="20"/>
       <c r="H113" s="3"/>
       <c r="I113" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
@@ -6671,21 +6689,21 @@
     </row>
     <row r="114" spans="1:13" ht="13.5" customHeight="1">
       <c r="A114" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D114" s="9" t="s">
         <v>259</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>260</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="20"/>
       <c r="G114" s="20"/>
       <c r="H114" s="3"/>
       <c r="I114" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
@@ -6694,23 +6712,23 @@
     </row>
     <row r="115" spans="1:13" ht="13.5" customHeight="1">
       <c r="A115" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B115" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C115" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="D115" s="9" t="s">
         <v>263</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>264</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="20"/>
       <c r="G115" s="20"/>
       <c r="H115" s="3"/>
       <c r="I115" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
@@ -6719,22 +6737,22 @@
     </row>
     <row r="116" spans="1:13" ht="15" customHeight="1">
       <c r="A116" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="4"/>
       <c r="G116" s="4"/>
       <c r="H116" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
@@ -6744,21 +6762,21 @@
     </row>
     <row r="117" spans="1:13" ht="13.5" customHeight="1">
       <c r="A117" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D117" s="9" t="s">
         <v>268</v>
-      </c>
-      <c r="D117" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="20"/>
       <c r="G117" s="20"/>
       <c r="H117" s="3"/>
       <c r="I117" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
@@ -6767,20 +6785,20 @@
     </row>
     <row r="118" spans="1:13" ht="13.5" customHeight="1">
       <c r="A118" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D118" s="9" t="s">
         <v>271</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>272</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="4"/>
       <c r="G118" s="4"/>
       <c r="H118" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
@@ -6790,20 +6808,20 @@
     </row>
     <row r="119" spans="1:13" ht="12.75" customHeight="1">
       <c r="A119" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B119" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C119" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="C119" s="7" t="s">
+      <c r="D119" s="15" t="s">
         <v>275</v>
-      </c>
-      <c r="D119" s="15" t="s">
-        <v>276</v>
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
@@ -6815,20 +6833,20 @@
     </row>
     <row r="120" spans="1:13" ht="12.75" customHeight="1">
       <c r="A120" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C120" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D120" s="15" t="s">
         <v>278</v>
-      </c>
-      <c r="D120" s="15" t="s">
-        <v>279</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
@@ -6840,20 +6858,20 @@
     </row>
     <row r="121" spans="1:13" ht="12.75" customHeight="1">
       <c r="A121" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C121" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D121" s="15" t="s">
         <v>281</v>
-      </c>
-      <c r="D121" s="15" t="s">
-        <v>282</v>
       </c>
       <c r="E121" s="4"/>
       <c r="F121" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
@@ -6865,20 +6883,20 @@
     </row>
     <row r="122" spans="1:13" ht="12.75" customHeight="1">
       <c r="A122" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C122" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D122" s="15" t="s">
         <v>284</v>
-      </c>
-      <c r="D122" s="15" t="s">
-        <v>285</v>
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
@@ -6890,20 +6908,20 @@
     </row>
     <row r="123" spans="1:13" ht="12.75" customHeight="1">
       <c r="A123" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C123" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D123" s="15" t="s">
         <v>287</v>
-      </c>
-      <c r="D123" s="15" t="s">
-        <v>288</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
@@ -6915,20 +6933,20 @@
     </row>
     <row r="124" spans="1:13" ht="12.75" customHeight="1">
       <c r="A124" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C124" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D124" s="15" t="s">
         <v>290</v>
-      </c>
-      <c r="D124" s="15" t="s">
-        <v>291</v>
       </c>
       <c r="E124" s="4"/>
       <c r="F124" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
@@ -6940,20 +6958,20 @@
     </row>
     <row r="125" spans="1:13" ht="12.75" customHeight="1">
       <c r="A125" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C125" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D125" s="15" t="s">
         <v>293</v>
-      </c>
-      <c r="D125" s="15" t="s">
-        <v>294</v>
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
@@ -6965,23 +6983,23 @@
     </row>
     <row r="126" spans="1:13" ht="13.5" customHeight="1">
       <c r="A126" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C126" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D126" s="15" t="s">
         <v>296</v>
-      </c>
-      <c r="D126" s="15" t="s">
-        <v>297</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
       <c r="I126" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J126" s="20"/>
       <c r="K126" s="4"/>
@@ -6990,23 +7008,23 @@
     </row>
     <row r="127" spans="1:13" ht="13.5" customHeight="1">
       <c r="A127" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C127" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D127" s="17" t="s">
         <v>299</v>
-      </c>
-      <c r="D127" s="17" t="s">
-        <v>300</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
       <c r="I127" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J127" s="20"/>
       <c r="K127" s="4"/>
@@ -7015,24 +7033,24 @@
     </row>
     <row r="128" spans="1:13" ht="13.5" customHeight="1">
       <c r="A128" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C128" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D128" s="17" t="s">
         <v>302</v>
-      </c>
-      <c r="D128" s="17" t="s">
-        <v>303</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
@@ -7042,14 +7060,14 @@
     </row>
     <row r="129" spans="1:13" ht="13.5" customHeight="1">
       <c r="A129" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D129" s="17" t="s">
         <v>307</v>
-      </c>
-      <c r="D129" s="17" t="s">
-        <v>308</v>
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
@@ -7063,19 +7081,19 @@
     </row>
     <row r="130" spans="1:13" ht="13.5" customHeight="1">
       <c r="A130" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B130" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C130" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="D130" s="17" t="s">
         <v>310</v>
       </c>
-      <c r="D130" s="17" t="s">
+      <c r="E130" s="10" t="s">
         <v>311</v>
-      </c>
-      <c r="E130" s="10" t="s">
-        <v>312</v>
       </c>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
@@ -7088,19 +7106,19 @@
     </row>
     <row r="131" spans="1:13" ht="13.5" customHeight="1">
       <c r="A131" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C131" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D131" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="D131" s="17" t="s">
+      <c r="E131" s="10" t="s">
         <v>314</v>
-      </c>
-      <c r="E131" s="10" t="s">
-        <v>315</v>
       </c>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
@@ -7113,19 +7131,19 @@
     </row>
     <row r="132" spans="1:13" ht="13.5" customHeight="1">
       <c r="A132" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C132" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D132" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="D132" s="17" t="s">
+      <c r="E132" s="10" t="s">
         <v>317</v>
-      </c>
-      <c r="E132" s="10" t="s">
-        <v>318</v>
       </c>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
@@ -7138,19 +7156,19 @@
     </row>
     <row r="133" spans="1:13" ht="13.5" customHeight="1">
       <c r="A133" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C133" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D133" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="D133" s="17" t="s">
+      <c r="E133" s="10" t="s">
         <v>320</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>321</v>
       </c>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
@@ -7163,19 +7181,19 @@
     </row>
     <row r="134" spans="1:13" ht="13.5" customHeight="1">
       <c r="A134" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C134" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D134" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="D134" s="17" t="s">
+      <c r="E134" s="8" t="s">
         <v>323</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>324</v>
       </c>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
@@ -7188,19 +7206,19 @@
     </row>
     <row r="135" spans="1:13" ht="13.5" customHeight="1">
       <c r="A135" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C135" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="D135" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="D135" s="17" t="s">
+      <c r="E135" s="10" t="s">
         <v>326</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>327</v>
       </c>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
@@ -7213,19 +7231,19 @@
     </row>
     <row r="136" spans="1:13" ht="13.5" customHeight="1">
       <c r="A136" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C136" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="D136" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="D136" s="17" t="s">
+      <c r="E136" s="10" t="s">
         <v>329</v>
-      </c>
-      <c r="E136" s="10" t="s">
-        <v>330</v>
       </c>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
@@ -7238,19 +7256,19 @@
     </row>
     <row r="137" spans="1:13" ht="13.5" customHeight="1">
       <c r="A137" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C137" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="D137" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="D137" s="17" t="s">
+      <c r="E137" s="10" t="s">
         <v>332</v>
-      </c>
-      <c r="E137" s="10" t="s">
-        <v>333</v>
       </c>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
@@ -7263,19 +7281,19 @@
     </row>
     <row r="138" spans="1:13" ht="13.5" customHeight="1">
       <c r="A138" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C138" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D138" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="D138" s="17" t="s">
+      <c r="E138" s="8" t="s">
         <v>335</v>
-      </c>
-      <c r="E138" s="8" t="s">
-        <v>336</v>
       </c>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
@@ -7288,19 +7306,19 @@
     </row>
     <row r="139" spans="1:13" ht="13.5" customHeight="1">
       <c r="A139" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C139" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D139" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="D139" s="17" t="s">
-        <v>338</v>
-      </c>
       <c r="E139" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F139" s="4"/>
       <c r="G139" s="4"/>
@@ -7313,19 +7331,19 @@
     </row>
     <row r="140" spans="1:13" ht="13.5" customHeight="1">
       <c r="A140" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C140" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D140" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="D140" s="17" t="s">
+      <c r="E140" s="8" t="s">
         <v>340</v>
-      </c>
-      <c r="E140" s="8" t="s">
-        <v>341</v>
       </c>
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
@@ -7338,19 +7356,19 @@
     </row>
     <row r="141" spans="1:13" ht="13.5" customHeight="1">
       <c r="A141" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C141" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="D141" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="D141" s="17" t="s">
-        <v>343</v>
-      </c>
       <c r="E141" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F141" s="4"/>
       <c r="G141" s="4"/>
@@ -7363,22 +7381,22 @@
     </row>
     <row r="142" spans="1:13" ht="13.5" customHeight="1">
       <c r="A142" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B142" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C142" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="D142" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="D142" s="17" t="s">
+      <c r="E142" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="E142" s="8" t="s">
+      <c r="F142" s="8" t="s">
         <v>347</v>
-      </c>
-      <c r="F142" s="8" t="s">
-        <v>348</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
@@ -7390,22 +7408,22 @@
     </row>
     <row r="143" spans="1:13" ht="13.5" customHeight="1">
       <c r="A143" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C143" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D143" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="D143" s="17" t="s">
+      <c r="E143" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="E143" s="8" t="s">
-        <v>351</v>
-      </c>
       <c r="F143" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
@@ -7417,22 +7435,22 @@
     </row>
     <row r="144" spans="1:13" ht="13.5" customHeight="1">
       <c r="A144" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C144" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D144" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="D144" s="17" t="s">
+      <c r="E144" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="E144" s="8" t="s">
-        <v>354</v>
-      </c>
       <c r="F144" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
@@ -7444,22 +7462,22 @@
     </row>
     <row r="145" spans="1:13" ht="13.5" customHeight="1">
       <c r="A145" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C145" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D145" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="D145" s="17" t="s">
+      <c r="E145" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="E145" s="8" t="s">
-        <v>357</v>
-      </c>
       <c r="F145" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
@@ -7471,22 +7489,22 @@
     </row>
     <row r="146" spans="1:13" ht="13.5" customHeight="1">
       <c r="A146" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C146" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D146" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="D146" s="17" t="s">
+      <c r="E146" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="E146" s="8" t="s">
-        <v>360</v>
-      </c>
       <c r="F146" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
@@ -7498,22 +7516,22 @@
     </row>
     <row r="147" spans="1:13" ht="13.5" customHeight="1">
       <c r="A147" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C147" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D147" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="D147" s="17" t="s">
+      <c r="E147" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="E147" s="8" t="s">
-        <v>363</v>
-      </c>
       <c r="F147" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
@@ -7525,22 +7543,22 @@
     </row>
     <row r="148" spans="1:13" ht="13.5" customHeight="1">
       <c r="A148" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C148" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D148" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="D148" s="17" t="s">
+      <c r="E148" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E148" s="8" t="s">
+      <c r="F148" s="8" t="s">
         <v>366</v>
-      </c>
-      <c r="F148" s="8" t="s">
-        <v>367</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4"/>
@@ -7552,22 +7570,22 @@
     </row>
     <row r="149" spans="1:13" ht="13.5" customHeight="1">
       <c r="A149" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C149" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D149" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="D149" s="17" t="s">
+      <c r="E149" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="E149" s="10" t="s">
-        <v>370</v>
-      </c>
       <c r="F149" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G149" s="4"/>
       <c r="H149" s="3"/>
@@ -7579,22 +7597,22 @@
     </row>
     <row r="150" spans="1:13" ht="13.5" customHeight="1">
       <c r="A150" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C150" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D150" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="D150" s="17" t="s">
+      <c r="E150" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="E150" s="8" t="s">
-        <v>373</v>
-      </c>
       <c r="F150" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
@@ -7606,22 +7624,22 @@
     </row>
     <row r="151" spans="1:13" ht="13.5" customHeight="1">
       <c r="A151" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C151" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="D151" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="D151" s="17" t="s">
+      <c r="E151" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="E151" s="8" t="s">
-        <v>376</v>
-      </c>
       <c r="F151" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
@@ -7633,22 +7651,22 @@
     </row>
     <row r="152" spans="1:13" ht="13.5" customHeight="1">
       <c r="A152" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C152" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D152" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="D152" s="17" t="s">
+      <c r="E152" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="E152" s="8" t="s">
-        <v>379</v>
-      </c>
       <c r="F152" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
@@ -7660,22 +7678,22 @@
     </row>
     <row r="153" spans="1:13" ht="13.5" customHeight="1">
       <c r="A153" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C153" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D153" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="D153" s="17" t="s">
+      <c r="E153" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="E153" s="8" t="s">
-        <v>382</v>
-      </c>
       <c r="F153" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
@@ -7687,22 +7705,22 @@
     </row>
     <row r="154" spans="1:13" ht="13.5" customHeight="1">
       <c r="A154" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B154" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C154" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="C154" s="5" t="s">
+      <c r="D154" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="D154" s="17" t="s">
+      <c r="E154" s="23" t="s">
         <v>385</v>
       </c>
-      <c r="E154" s="23" t="s">
-        <v>386</v>
-      </c>
       <c r="F154" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
@@ -7714,22 +7732,22 @@
     </row>
     <row r="155" spans="1:13" ht="13.5" customHeight="1">
       <c r="A155" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C155" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D155" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="D155" s="17" t="s">
+      <c r="E155" s="23" t="s">
         <v>388</v>
       </c>
-      <c r="E155" s="23" t="s">
-        <v>389</v>
-      </c>
       <c r="F155" s="23" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
@@ -7741,21 +7759,21 @@
     </row>
     <row r="156" spans="1:13" ht="13.5" customHeight="1">
       <c r="A156" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D156" s="17" t="s">
         <v>390</v>
-      </c>
-      <c r="D156" s="17" t="s">
-        <v>391</v>
       </c>
       <c r="E156" s="4"/>
       <c r="F156" s="20"/>
       <c r="G156" s="20"/>
       <c r="H156" s="4"/>
       <c r="I156" s="26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J156" s="20"/>
       <c r="K156" s="4"/>
@@ -7764,21 +7782,21 @@
     </row>
     <row r="157" spans="1:13" ht="13.5" customHeight="1">
       <c r="A157" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="D157" s="17" t="s">
         <v>392</v>
-      </c>
-      <c r="D157" s="17" t="s">
-        <v>393</v>
       </c>
       <c r="E157" s="4"/>
       <c r="F157" s="20"/>
       <c r="G157" s="20"/>
       <c r="H157" s="4"/>
       <c r="I157" s="26" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J157" s="20"/>
       <c r="K157" s="4"/>
@@ -7787,22 +7805,22 @@
     </row>
     <row r="158" spans="1:13" ht="13.5" customHeight="1">
       <c r="A158" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D158" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="D158" s="15" t="s">
+      <c r="E158" s="8" t="s">
         <v>396</v>
-      </c>
-      <c r="E158" s="8" t="s">
-        <v>397</v>
       </c>
       <c r="F158" s="4"/>
       <c r="G158" s="4"/>
       <c r="H158" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
@@ -7812,22 +7830,22 @@
     </row>
     <row r="159" spans="1:13" ht="13.5" customHeight="1">
       <c r="A159" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D159" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="D159" s="15" t="s">
+      <c r="E159" s="8" t="s">
         <v>400</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>401</v>
       </c>
       <c r="F159" s="4"/>
       <c r="G159" s="4"/>
       <c r="H159" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
@@ -7837,22 +7855,22 @@
     </row>
     <row r="160" spans="1:13" ht="13.5" customHeight="1">
       <c r="A160" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="D160" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="D160" s="15" t="s">
+      <c r="E160" s="8" t="s">
         <v>403</v>
-      </c>
-      <c r="E160" s="8" t="s">
-        <v>404</v>
       </c>
       <c r="F160" s="4"/>
       <c r="G160" s="4"/>
       <c r="H160" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
@@ -7862,20 +7880,20 @@
     </row>
     <row r="161" spans="1:13" ht="13.5" customHeight="1">
       <c r="A161" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="D161" s="15" t="s">
         <v>405</v>
-      </c>
-      <c r="D161" s="15" t="s">
-        <v>406</v>
       </c>
       <c r="E161" s="8" t="s">
         <v>76</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G161" s="4"/>
       <c r="H161" s="4"/>
@@ -7887,17 +7905,17 @@
     </row>
     <row r="162" spans="1:13" ht="13.5" customHeight="1">
       <c r="A162" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B162" s="5"/>
       <c r="C162" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D162" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="D162" s="15" t="s">
+      <c r="E162" s="8" t="s">
         <v>410</v>
-      </c>
-      <c r="E162" s="8" t="s">
-        <v>411</v>
       </c>
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
@@ -7910,22 +7928,22 @@
     </row>
     <row r="163" spans="1:13" ht="13.5" customHeight="1">
       <c r="A163" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B163" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C163" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="C163" s="5" t="s">
+      <c r="D163" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="D163" s="15" t="s">
+      <c r="E163" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="E163" s="8" t="s">
-        <v>415</v>
-      </c>
       <c r="F163" s="8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G163" s="4"/>
       <c r="H163" s="4"/>
@@ -7934,121 +7952,121 @@
       <c r="K163" s="4"/>
       <c r="L163" s="4"/>
       <c r="M163" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="13.5" customHeight="1">
       <c r="A164" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C164" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D164" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="D164" s="15" t="s">
+      <c r="E164" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="E164" s="8" t="s">
-        <v>419</v>
-      </c>
       <c r="F164" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G164" s="4"/>
       <c r="H164" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
       <c r="K164" s="4"/>
       <c r="L164" s="4"/>
       <c r="M164" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="13.5" customHeight="1">
       <c r="A165" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C165" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D165" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="D165" s="15" t="s">
+      <c r="E165" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="E165" s="8" t="s">
-        <v>422</v>
-      </c>
       <c r="F165" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G165" s="4"/>
       <c r="H165" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
       <c r="L165" s="4"/>
       <c r="M165" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="13.5" customHeight="1">
       <c r="A166" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C166" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D166" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="D166" s="15" t="s">
+      <c r="E166" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="E166" s="8" t="s">
-        <v>425</v>
-      </c>
       <c r="F166" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G166" s="4"/>
       <c r="H166" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I166" s="4"/>
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
       <c r="L166" s="4"/>
       <c r="M166" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="15" customHeight="1">
       <c r="A167" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B167" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="C167" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="C167" s="5" t="s">
+      <c r="D167" s="15" t="s">
         <v>427</v>
-      </c>
-      <c r="D167" s="15" t="s">
-        <v>428</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
       <c r="H167" s="4"/>
       <c r="I167" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J167" s="4"/>
       <c r="K167" s="4"/>
@@ -8057,16 +8075,16 @@
     </row>
     <row r="168" spans="1:13" ht="13.5" customHeight="1">
       <c r="A168" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C168" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D168" s="15" t="s">
         <v>430</v>
-      </c>
-      <c r="D168" s="15" t="s">
-        <v>431</v>
       </c>
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
@@ -8080,23 +8098,23 @@
     </row>
     <row r="169" spans="1:13" ht="13.5" customHeight="1">
       <c r="A169" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B169" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C169" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="C169" s="5" t="s">
+      <c r="D169" s="15" t="s">
         <v>433</v>
-      </c>
-      <c r="D169" s="15" t="s">
-        <v>434</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
       <c r="H169" s="4"/>
       <c r="I169" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
@@ -8105,26 +8123,26 @@
     </row>
     <row r="170" spans="1:13" ht="13.5" customHeight="1">
       <c r="A170" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C170" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D170" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="D170" s="15" t="s">
+      <c r="E170" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="E170" s="8" t="s">
-        <v>438</v>
-      </c>
       <c r="F170" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G170" s="4"/>
       <c r="H170" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I170" s="4"/>
       <c r="J170" s="4"/>
@@ -8134,23 +8152,23 @@
     </row>
     <row r="171" spans="1:13" ht="13.5" customHeight="1">
       <c r="A171" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C171" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="D171" s="15" t="s">
         <v>439</v>
-      </c>
-      <c r="D171" s="15" t="s">
-        <v>440</v>
       </c>
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
       <c r="G171" s="4"/>
       <c r="H171" s="4"/>
       <c r="I171" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
@@ -8159,23 +8177,23 @@
     </row>
     <row r="172" spans="1:13" ht="13.5" customHeight="1">
       <c r="A172" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C172" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="D172" s="15" t="s">
         <v>441</v>
-      </c>
-      <c r="D172" s="15" t="s">
-        <v>442</v>
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
       <c r="I172" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
@@ -8184,23 +8202,23 @@
     </row>
     <row r="173" spans="1:13" ht="13.5" customHeight="1">
       <c r="A173" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C173" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D173" s="15" t="s">
         <v>444</v>
-      </c>
-      <c r="D173" s="15" t="s">
-        <v>445</v>
       </c>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
       <c r="H173" s="4"/>
       <c r="I173" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
@@ -8209,23 +8227,23 @@
     </row>
     <row r="174" spans="1:13" ht="13.5" customHeight="1">
       <c r="A174" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C174" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D174" s="15" t="s">
         <v>446</v>
-      </c>
-      <c r="D174" s="15" t="s">
-        <v>447</v>
       </c>
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
       <c r="H174" s="4"/>
       <c r="I174" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
@@ -8234,26 +8252,26 @@
     </row>
     <row r="175" spans="1:13" ht="13.5" customHeight="1">
       <c r="A175" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C175" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D175" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="D175" s="15" t="s">
+      <c r="E175" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="E175" s="8" t="s">
-        <v>451</v>
-      </c>
       <c r="F175" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G175" s="4"/>
       <c r="H175" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
@@ -8263,24 +8281,24 @@
     </row>
     <row r="176" spans="1:13" ht="13.5" customHeight="1">
       <c r="A176" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B176" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C176" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="C176" s="8" t="s">
+      <c r="D176" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="D176" s="17" t="s">
+      <c r="E176" s="8" t="s">
         <v>454</v>
-      </c>
-      <c r="E176" s="8" t="s">
-        <v>455</v>
       </c>
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
       <c r="H176" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
@@ -8290,24 +8308,24 @@
     </row>
     <row r="177" spans="1:13" ht="13.5" customHeight="1">
       <c r="A177" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C177" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="D177" s="17" t="s">
         <v>456</v>
       </c>
-      <c r="D177" s="17" t="s">
+      <c r="E177" s="8" t="s">
         <v>457</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>458</v>
       </c>
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
       <c r="H177" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
@@ -8317,24 +8335,24 @@
     </row>
     <row r="178" spans="1:13" ht="13.5" customHeight="1">
       <c r="A178" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C178" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="D178" s="17" t="s">
         <v>459</v>
       </c>
-      <c r="D178" s="17" t="s">
+      <c r="E178" s="8" t="s">
         <v>460</v>
-      </c>
-      <c r="E178" s="8" t="s">
-        <v>461</v>
       </c>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
       <c r="H178" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
@@ -8344,24 +8362,24 @@
     </row>
     <row r="179" spans="1:13" ht="13.5" customHeight="1">
       <c r="A179" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C179" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="D179" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="D179" s="17" t="s">
+      <c r="E179" s="8" t="s">
         <v>463</v>
-      </c>
-      <c r="E179" s="8" t="s">
-        <v>464</v>
       </c>
       <c r="F179" s="4"/>
       <c r="G179" s="4"/>
       <c r="H179" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
@@ -8371,22 +8389,22 @@
     </row>
     <row r="180" spans="1:13" ht="13.5" customHeight="1">
       <c r="A180" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B180" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="C180" s="22" t="s">
         <v>465</v>
       </c>
-      <c r="C180" s="22" t="s">
+      <c r="D180" s="27" t="s">
         <v>466</v>
-      </c>
-      <c r="D180" s="27" t="s">
-        <v>467</v>
       </c>
       <c r="E180" s="5"/>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
       <c r="H180" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
@@ -8396,22 +8414,22 @@
     </row>
     <row r="181" spans="1:13" ht="13.5" customHeight="1">
       <c r="A181" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C181" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="D181" s="27" t="s">
         <v>469</v>
-      </c>
-      <c r="D181" s="27" t="s">
-        <v>470</v>
       </c>
       <c r="E181" s="5"/>
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
       <c r="H181" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
@@ -8421,22 +8439,22 @@
     </row>
     <row r="182" spans="1:13" ht="13.5" customHeight="1">
       <c r="A182" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B182" s="22" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C182" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="D182" s="28" t="s">
         <v>472</v>
-      </c>
-      <c r="D182" s="28" t="s">
-        <v>473</v>
       </c>
       <c r="E182" s="5"/>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
       <c r="H182" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
@@ -8446,22 +8464,22 @@
     </row>
     <row r="183" spans="1:13" ht="13.5" customHeight="1">
       <c r="A183" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B183" s="22" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C183" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="D183" s="27" t="s">
         <v>475</v>
-      </c>
-      <c r="D183" s="27" t="s">
-        <v>476</v>
       </c>
       <c r="E183" s="5"/>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
       <c r="H183" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
@@ -8471,22 +8489,22 @@
     </row>
     <row r="184" spans="1:13" ht="13.5" customHeight="1">
       <c r="A184" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B184" s="22" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C184" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="D184" s="27" t="s">
         <v>478</v>
-      </c>
-      <c r="D184" s="27" t="s">
-        <v>479</v>
       </c>
       <c r="E184" s="5"/>
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
       <c r="H184" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
@@ -8496,23 +8514,23 @@
     </row>
     <row r="185" spans="1:13" ht="13.5" customHeight="1">
       <c r="A185" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="D185" s="15" t="s">
         <v>482</v>
       </c>
-      <c r="D185" s="15" t="s">
-        <v>483</v>
-      </c>
       <c r="E185" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
       <c r="H185" s="5"/>
       <c r="I185" s="23" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
@@ -8521,22 +8539,22 @@
     </row>
     <row r="186" spans="1:13" ht="13.5" customHeight="1">
       <c r="A186" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="B186" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="B186" s="5" t="s">
+      <c r="C186" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="C186" s="5" t="s">
+      <c r="D186" s="15" t="s">
         <v>487</v>
       </c>
-      <c r="D186" s="15" t="s">
+      <c r="E186" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="E186" s="8" t="s">
-        <v>489</v>
-      </c>
       <c r="F186" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G186" s="4"/>
       <c r="H186" s="4"/>
@@ -8548,22 +8566,22 @@
     </row>
     <row r="187" spans="1:13" ht="13.5" customHeight="1">
       <c r="A187" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="B187" s="5" t="s">
-        <v>486</v>
-      </c>
       <c r="C187" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="D187" s="15" t="s">
         <v>490</v>
       </c>
-      <c r="D187" s="15" t="s">
+      <c r="E187" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="E187" s="8" t="s">
-        <v>492</v>
-      </c>
       <c r="F187" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G187" s="4"/>
       <c r="H187" s="4"/>
@@ -8575,24 +8593,24 @@
     </row>
     <row r="188" spans="1:13" ht="13.5" customHeight="1">
       <c r="A188" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B188" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="D188" s="15" t="s">
         <v>493</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="D188" s="15" t="s">
-        <v>494</v>
       </c>
       <c r="E188" s="4"/>
       <c r="F188" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G188" s="4"/>
       <c r="H188" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
@@ -8602,26 +8620,26 @@
     </row>
     <row r="189" spans="1:13" ht="13.5" customHeight="1">
       <c r="A189" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B189" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C189" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="C189" s="5" t="s">
+      <c r="D189" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="D189" s="15" t="s">
+      <c r="E189" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="E189" s="8" t="s">
-        <v>499</v>
-      </c>
       <c r="F189" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G189" s="4"/>
       <c r="H189" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
@@ -8631,16 +8649,16 @@
     </row>
     <row r="190" spans="1:13" ht="13.5" customHeight="1">
       <c r="A190" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C190" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="D190" s="15" t="s">
         <v>500</v>
-      </c>
-      <c r="D190" s="15" t="s">
-        <v>501</v>
       </c>
       <c r="E190" s="8" t="s">
         <v>23</v>
@@ -8660,21 +8678,21 @@
     </row>
     <row r="191" spans="1:13" ht="13.5" customHeight="1">
       <c r="A191" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B191" s="4"/>
       <c r="C191" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D191" s="15" t="s">
         <v>502</v>
-      </c>
-      <c r="D191" s="15" t="s">
-        <v>503</v>
       </c>
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
       <c r="H191" s="4"/>
       <c r="I191" s="8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
@@ -8683,23 +8701,23 @@
     </row>
     <row r="192" spans="1:13" ht="13.5" customHeight="1">
       <c r="A192" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="B192" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B192" s="7" t="s">
+      <c r="C192" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="C192" s="7" t="s">
+      <c r="D192" s="15" t="s">
         <v>507</v>
-      </c>
-      <c r="D192" s="15" t="s">
-        <v>508</v>
       </c>
       <c r="E192" s="4"/>
       <c r="F192" s="4"/>
       <c r="G192" s="4"/>
       <c r="H192" s="4"/>
       <c r="I192" s="10" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
@@ -8708,24 +8726,24 @@
     </row>
     <row r="193" spans="1:13" ht="13.5" customHeight="1">
       <c r="A193" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="B193" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B193" s="7" t="s">
-        <v>506</v>
-      </c>
       <c r="C193" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="D193" s="15" t="s">
         <v>510</v>
       </c>
-      <c r="D193" s="15" t="s">
-        <v>511</v>
-      </c>
       <c r="E193" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
       <c r="H193" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
@@ -8735,23 +8753,23 @@
     </row>
     <row r="194" spans="1:13" ht="13.5" customHeight="1">
       <c r="A194" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B194" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="C194" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="C194" s="7" t="s">
+      <c r="D194" s="29" t="s">
         <v>513</v>
-      </c>
-      <c r="D194" s="29" t="s">
-        <v>514</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194" s="30"/>
       <c r="G194" s="30"/>
       <c r="H194" s="31"/>
       <c r="I194" s="10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
@@ -8760,24 +8778,24 @@
     </row>
     <row r="195" spans="1:13" ht="13.5" customHeight="1">
       <c r="A195" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C195" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D195" s="15" t="s">
         <v>516</v>
       </c>
-      <c r="D195" s="15" t="s">
+      <c r="E195" s="8" t="s">
         <v>517</v>
-      </c>
-      <c r="E195" s="8" t="s">
-        <v>518</v>
       </c>
       <c r="F195" s="4"/>
       <c r="G195" s="4"/>
       <c r="H195" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I195" s="4"/>
       <c r="J195" s="4"/>
@@ -8787,20 +8805,20 @@
     </row>
     <row r="196" spans="1:13" ht="13.5" customHeight="1">
       <c r="A196" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B196" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="C196" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="C196" s="7" t="s">
+      <c r="D196" s="15" t="s">
         <v>520</v>
-      </c>
-      <c r="D196" s="15" t="s">
-        <v>521</v>
       </c>
       <c r="E196" s="4"/>
       <c r="F196" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G196" s="4"/>
       <c r="H196" s="4"/>
@@ -8812,20 +8830,20 @@
     </row>
     <row r="197" spans="1:13" ht="13.5" customHeight="1">
       <c r="A197" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C197" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="D197" s="15" t="s">
         <v>523</v>
-      </c>
-      <c r="D197" s="15" t="s">
-        <v>524</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G197" s="4"/>
       <c r="H197" s="4"/>
@@ -8837,20 +8855,20 @@
     </row>
     <row r="198" spans="1:13" ht="13.5" customHeight="1">
       <c r="A198" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C198" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D198" s="15" t="s">
         <v>526</v>
-      </c>
-      <c r="D198" s="15" t="s">
-        <v>527</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G198" s="4"/>
       <c r="H198" s="4"/>
@@ -8862,20 +8880,20 @@
     </row>
     <row r="199" spans="1:13" ht="13.5" customHeight="1">
       <c r="A199" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C199" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D199" s="15" t="s">
         <v>529</v>
-      </c>
-      <c r="D199" s="15" t="s">
-        <v>530</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G199" s="4"/>
       <c r="H199" s="4"/>
@@ -8887,20 +8905,20 @@
     </row>
     <row r="200" spans="1:13" ht="13.5" customHeight="1">
       <c r="A200" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C200" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D200" s="15" t="s">
         <v>532</v>
-      </c>
-      <c r="D200" s="15" t="s">
-        <v>533</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
@@ -8912,20 +8930,20 @@
     </row>
     <row r="201" spans="1:13" ht="13.5" customHeight="1">
       <c r="A201" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C201" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="D201" s="15" t="s">
         <v>535</v>
-      </c>
-      <c r="D201" s="15" t="s">
-        <v>536</v>
       </c>
       <c r="E201" s="4"/>
       <c r="F201" s="8" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
@@ -8937,20 +8955,20 @@
     </row>
     <row r="202" spans="1:13" ht="13.5" customHeight="1">
       <c r="A202" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C202" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="D202" s="15" t="s">
         <v>538</v>
-      </c>
-      <c r="D202" s="15" t="s">
-        <v>539</v>
       </c>
       <c r="E202" s="4"/>
       <c r="F202" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
@@ -8962,20 +8980,20 @@
     </row>
     <row r="203" spans="1:13" ht="13.5" customHeight="1">
       <c r="A203" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C203" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="D203" s="15" t="s">
         <v>541</v>
-      </c>
-      <c r="D203" s="15" t="s">
-        <v>542</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="8" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
@@ -8987,20 +9005,20 @@
     </row>
     <row r="204" spans="1:13" ht="13.5" customHeight="1">
       <c r="A204" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C204" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="D204" s="15" t="s">
         <v>544</v>
-      </c>
-      <c r="D204" s="15" t="s">
-        <v>545</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G204" s="4"/>
       <c r="H204" s="4"/>
@@ -9012,20 +9030,20 @@
     </row>
     <row r="205" spans="1:13" ht="13.5" customHeight="1">
       <c r="A205" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C205" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="D205" s="15" t="s">
         <v>547</v>
-      </c>
-      <c r="D205" s="15" t="s">
-        <v>548</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="8" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
@@ -9037,20 +9055,20 @@
     </row>
     <row r="206" spans="1:13" ht="13.5" customHeight="1">
       <c r="A206" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C206" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="D206" s="15" t="s">
         <v>550</v>
-      </c>
-      <c r="D206" s="15" t="s">
-        <v>551</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="8" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
@@ -9062,20 +9080,20 @@
     </row>
     <row r="207" spans="1:13" ht="13.5" customHeight="1">
       <c r="A207" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C207" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="D207" s="15" t="s">
         <v>553</v>
-      </c>
-      <c r="D207" s="15" t="s">
-        <v>554</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="8" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
@@ -9087,20 +9105,20 @@
     </row>
     <row r="208" spans="1:13" ht="13.5" customHeight="1">
       <c r="A208" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C208" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="D208" s="15" t="s">
         <v>556</v>
-      </c>
-      <c r="D208" s="15" t="s">
-        <v>557</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
@@ -9112,21 +9130,21 @@
     </row>
     <row r="209" spans="1:13" ht="13.5" customHeight="1">
       <c r="A209" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B209" s="7"/>
       <c r="C209" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="D209" s="45" t="s">
         <v>642</v>
-      </c>
-      <c r="D209" s="45" t="s">
-        <v>643</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="8"/>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
       <c r="I209" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="J209" s="4"/>
       <c r="K209" s="4"/>
@@ -9135,23 +9153,23 @@
     </row>
     <row r="210" spans="1:13" ht="13.5" customHeight="1">
       <c r="A210" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B210" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="C210" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="C210" s="7" t="s">
+      <c r="D210" s="15" t="s">
         <v>560</v>
-      </c>
-      <c r="D210" s="15" t="s">
-        <v>561</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="4"/>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
       <c r="I210" s="23" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J210" s="4"/>
       <c r="K210" s="4"/>
@@ -9160,23 +9178,23 @@
     </row>
     <row r="211" spans="1:13" ht="13.5" customHeight="1">
       <c r="A211" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B211" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="C211" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="C211" s="7" t="s">
+      <c r="D211" s="15" t="s">
         <v>564</v>
-      </c>
-      <c r="D211" s="15" t="s">
-        <v>565</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
       <c r="I211" s="23" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J211" s="4"/>
       <c r="K211" s="4"/>
@@ -9185,23 +9203,23 @@
     </row>
     <row r="212" spans="1:13" ht="13.5" customHeight="1">
       <c r="A212" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C212" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="D212" s="15" t="s">
         <v>567</v>
-      </c>
-      <c r="D212" s="15" t="s">
-        <v>568</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="4"/>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
       <c r="I212" s="23" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J212" s="4"/>
       <c r="K212" s="4"/>
@@ -9210,23 +9228,23 @@
     </row>
     <row r="213" spans="1:13" ht="13.5" customHeight="1">
       <c r="A213" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C213" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="D213" s="15" t="s">
         <v>570</v>
-      </c>
-      <c r="D213" s="15" t="s">
-        <v>571</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="4"/>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
       <c r="I213" s="8" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
@@ -9235,21 +9253,21 @@
     </row>
     <row r="214" spans="1:13" ht="13.5" customHeight="1">
       <c r="A214" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B214" s="4"/>
       <c r="C214" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="D214" s="15" t="s">
         <v>574</v>
-      </c>
-      <c r="D214" s="15" t="s">
-        <v>575</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
       <c r="I214" s="8" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J214" s="4"/>
       <c r="K214" s="4"/>
@@ -9258,20 +9276,20 @@
     </row>
     <row r="215" spans="1:13" ht="13.5" customHeight="1">
       <c r="A215" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B215" s="4"/>
       <c r="C215" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="D215" s="15" t="s">
         <v>577</v>
       </c>
-      <c r="D215" s="15" t="s">
+      <c r="E215" s="23" t="s">
         <v>578</v>
       </c>
-      <c r="E215" s="23" t="s">
-        <v>579</v>
-      </c>
       <c r="F215" s="23" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
@@ -9283,23 +9301,23 @@
     </row>
     <row r="216" spans="1:13" ht="13.5" customHeight="1">
       <c r="A216" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="B216" s="24" t="s">
         <v>580</v>
       </c>
-      <c r="B216" s="24" t="s">
+      <c r="C216" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="D216" s="33" t="s">
         <v>581</v>
-      </c>
-      <c r="C216" s="32" t="s">
-        <v>581</v>
-      </c>
-      <c r="D216" s="33" t="s">
-        <v>582</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
       <c r="I216" s="23" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
@@ -9308,22 +9326,22 @@
     </row>
     <row r="217" spans="1:13" ht="13.5" customHeight="1">
       <c r="A217" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="B217" s="24" t="s">
         <v>580</v>
       </c>
-      <c r="B217" s="24" t="s">
-        <v>581</v>
-      </c>
       <c r="C217" s="32" t="s">
+        <v>583</v>
+      </c>
+      <c r="D217" s="15" t="s">
         <v>584</v>
       </c>
-      <c r="D217" s="15" t="s">
-        <v>585</v>
-      </c>
       <c r="E217" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F217" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
@@ -9335,21 +9353,21 @@
     </row>
     <row r="218" spans="1:13" ht="13.5" customHeight="1">
       <c r="A218" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B218" s="4"/>
       <c r="C218" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="D218" s="15" t="s">
         <v>586</v>
-      </c>
-      <c r="D218" s="15" t="s">
-        <v>587</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
       <c r="I218" s="8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
@@ -9358,21 +9376,21 @@
     </row>
     <row r="219" spans="1:13" ht="13.5" customHeight="1">
       <c r="A219" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="D219" s="15" t="s">
         <v>589</v>
-      </c>
-      <c r="D219" s="15" t="s">
-        <v>590</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
       <c r="I219" s="10" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
@@ -9381,21 +9399,21 @@
     </row>
     <row r="220" spans="1:13" ht="13.5" customHeight="1">
       <c r="A220" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B220" s="4"/>
       <c r="C220" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="D220" s="15" t="s">
         <v>592</v>
-      </c>
-      <c r="D220" s="15" t="s">
-        <v>593</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
       <c r="I220" s="8" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
@@ -9404,21 +9422,21 @@
     </row>
     <row r="221" spans="1:13" ht="13.5" customHeight="1">
       <c r="A221" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B221" s="4"/>
       <c r="C221" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="D221" s="15" t="s">
         <v>595</v>
-      </c>
-      <c r="D221" s="15" t="s">
-        <v>596</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
       <c r="I221" s="8" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
@@ -9427,17 +9445,17 @@
     </row>
     <row r="222" spans="1:13" ht="13.5" customHeight="1">
       <c r="A222" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B222" s="4"/>
       <c r="C222" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="D222" s="15" t="s">
         <v>598</v>
       </c>
-      <c r="D222" s="15" t="s">
+      <c r="E222" s="8" t="s">
         <v>599</v>
-      </c>
-      <c r="E222" s="8" t="s">
-        <v>600</v>
       </c>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
@@ -9450,21 +9468,21 @@
     </row>
     <row r="223" spans="1:13" ht="13.5" customHeight="1">
       <c r="A223" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B223" s="4"/>
       <c r="C223" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="D223" s="33" t="s">
         <v>602</v>
-      </c>
-      <c r="D223" s="33" t="s">
-        <v>603</v>
       </c>
       <c r="E223" s="5"/>
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
       <c r="I223" s="23" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
@@ -9473,21 +9491,21 @@
     </row>
     <row r="224" spans="1:13" ht="13.5" customHeight="1">
       <c r="A224" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B224" s="3"/>
       <c r="C224" s="34" t="s">
+        <v>604</v>
+      </c>
+      <c r="D224" s="35" t="s">
         <v>605</v>
-      </c>
-      <c r="D224" s="35" t="s">
-        <v>606</v>
       </c>
       <c r="E224" s="3"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
       <c r="H224" s="3"/>
       <c r="I224" s="8" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
@@ -9496,21 +9514,21 @@
     </row>
     <row r="225" spans="1:13" ht="13.5" customHeight="1">
       <c r="A225" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B225" s="3"/>
       <c r="C225" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="D225" s="9" t="s">
         <v>608</v>
-      </c>
-      <c r="D225" s="9" t="s">
-        <v>609</v>
       </c>
       <c r="E225" s="3"/>
       <c r="F225" s="4"/>
       <c r="G225" s="4"/>
       <c r="H225" s="3"/>
       <c r="I225" s="8" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
@@ -9519,21 +9537,21 @@
     </row>
     <row r="226" spans="1:13" ht="13.5" customHeight="1">
       <c r="A226" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B226" s="3"/>
       <c r="C226" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="D226" s="9" t="s">
         <v>611</v>
-      </c>
-      <c r="D226" s="9" t="s">
-        <v>612</v>
       </c>
       <c r="E226" s="3"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
       <c r="H226" s="3"/>
       <c r="I226" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
@@ -9542,21 +9560,21 @@
     </row>
     <row r="227" spans="1:13" ht="13.5" customHeight="1">
       <c r="A227" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B227" s="4"/>
       <c r="C227" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="D227" s="15" t="s">
         <v>615</v>
-      </c>
-      <c r="D227" s="15" t="s">
-        <v>616</v>
       </c>
       <c r="E227" s="4"/>
       <c r="F227" s="4"/>
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
       <c r="I227" s="8" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J227" s="4"/>
       <c r="K227" s="4"/>
@@ -9565,21 +9583,21 @@
     </row>
     <row r="228" spans="1:13" ht="13.5" customHeight="1">
       <c r="A228" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B228" s="4"/>
       <c r="C228" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="D228" s="36" t="s">
         <v>618</v>
-      </c>
-      <c r="D228" s="36" t="s">
-        <v>619</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
       <c r="G228" s="4"/>
       <c r="H228" s="4"/>
       <c r="I228" s="8" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J228" s="4"/>
       <c r="K228" s="4"/>
@@ -9588,21 +9606,21 @@
     </row>
     <row r="229" spans="1:13" ht="13.5" customHeight="1">
       <c r="A229" s="37" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B229" s="38"/>
       <c r="C229" s="39" t="s">
+        <v>621</v>
+      </c>
+      <c r="D229" s="40" t="s">
         <v>622</v>
-      </c>
-      <c r="D229" s="40" t="s">
-        <v>623</v>
       </c>
       <c r="E229" s="41"/>
       <c r="F229" s="4"/>
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
       <c r="I229" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
@@ -9611,21 +9629,21 @@
     </row>
     <row r="230" spans="1:13" ht="13.5" customHeight="1">
       <c r="A230" s="37" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B230" s="24"/>
       <c r="C230" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="D230" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="D230" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="E230" s="3"/>
       <c r="F230" s="20"/>
       <c r="G230" s="20"/>
       <c r="H230" s="3"/>
       <c r="I230" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
@@ -9634,21 +9652,21 @@
     </row>
     <row r="231" spans="1:13" ht="13.5" customHeight="1">
       <c r="A231" s="37" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B231" s="24"/>
       <c r="C231" s="39" t="s">
+        <v>623</v>
+      </c>
+      <c r="D231" s="40" t="s">
         <v>624</v>
-      </c>
-      <c r="D231" s="40" t="s">
-        <v>625</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="4"/>
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
       <c r="I231" s="23" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
@@ -9657,21 +9675,21 @@
     </row>
     <row r="232" spans="1:13" ht="13.5" customHeight="1">
       <c r="A232" s="37" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B232" s="38"/>
       <c r="C232" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D232" s="44" t="s">
         <v>232</v>
-      </c>
-      <c r="D232" s="44" t="s">
-        <v>233</v>
       </c>
       <c r="E232" s="3"/>
       <c r="F232" s="20"/>
       <c r="G232" s="20"/>
       <c r="H232" s="3"/>
       <c r="I232" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
@@ -9680,21 +9698,21 @@
     </row>
     <row r="233" spans="1:13" ht="13.5" customHeight="1">
       <c r="A233" s="37" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B233" s="38"/>
       <c r="C233" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D233" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E233" s="3"/>
       <c r="F233" s="20"/>
       <c r="G233" s="20"/>
       <c r="H233" s="3"/>
       <c r="I233" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
@@ -9703,23 +9721,23 @@
     </row>
     <row r="234" spans="1:13" ht="13.5" customHeight="1">
       <c r="A234" s="37" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B234" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="C234" s="39" t="s">
         <v>626</v>
       </c>
-      <c r="C234" s="39" t="s">
+      <c r="D234" s="40" t="s">
         <v>627</v>
-      </c>
-      <c r="D234" s="40" t="s">
-        <v>628</v>
       </c>
       <c r="E234" s="4"/>
       <c r="F234" s="4"/>
       <c r="G234" s="4"/>
       <c r="H234" s="4"/>
       <c r="I234" s="23" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
@@ -9728,23 +9746,23 @@
     </row>
     <row r="235" spans="1:13" ht="13.5" customHeight="1">
       <c r="A235" s="37" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B235" s="38" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C235" s="39" t="s">
+        <v>629</v>
+      </c>
+      <c r="D235" s="40" t="s">
         <v>630</v>
-      </c>
-      <c r="D235" s="40" t="s">
-        <v>631</v>
       </c>
       <c r="E235" s="4"/>
       <c r="F235" s="4"/>
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
       <c r="I235" s="23" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="J235" s="4"/>
       <c r="K235" s="4"/>
@@ -9753,23 +9771,23 @@
     </row>
     <row r="236" spans="1:13" ht="13.5" customHeight="1">
       <c r="A236" s="37" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B236" s="38" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C236" s="39" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D236" s="40" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E236" s="4"/>
       <c r="F236" s="4"/>
       <c r="G236" s="4"/>
       <c r="H236" s="4"/>
       <c r="I236" s="23" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J236" s="4"/>
       <c r="K236" s="4"/>
@@ -13179,7 +13197,7 @@
     <row r="1019" ht="15.75" customHeight="1"/>
     <row r="1020" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="14"/>
+  <phoneticPr fontId="15"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\vm22flo01\DownloadFiles\スマートシティ課\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900785F1-3AFA-4EC2-A333-B03E27B74E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3054D43-2D05-4D30-B152-7E00339F7D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="655">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -3215,6 +3215,17 @@
       </rPr>
       <t/>
     </r>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%82%A2%E3%83%B3%E3%83%80%E3%83%BC%E3%83%91%E3%82%B9/tiles.json</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>アンダーパス</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>underpass</t>
   </si>
 </sst>
 </file>
@@ -3848,7 +3859,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M1020"/>
+  <dimension ref="A1:M1021"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -4276,24 +4287,24 @@
     </row>
     <row r="17" spans="1:13" ht="13.5" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>16</v>
+        <v>638</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>652</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="12" t="s">
+        <v>654</v>
+      </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -4307,14 +4318,14 @@
         <v>57</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -4332,14 +4343,14 @@
         <v>57</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -4354,21 +4365,21 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="F20" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
-      <c r="I20" s="8" t="s">
-        <v>70</v>
-      </c>
+      <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -4382,17 +4393,17 @@
         <v>67</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -4403,24 +4414,22 @@
       <c r="A22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="B22" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="C22" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>77</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -4430,19 +4439,23 @@
       <c r="A23" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>79</v>
+      <c r="B23" s="3"/>
+      <c r="C23" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="G23" s="4"/>
-      <c r="H23" s="3"/>
+      <c r="H23" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
@@ -4457,10 +4470,10 @@
         <v>78</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="4"/>
@@ -4476,19 +4489,19 @@
       <c r="A25" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="4"/>
+      <c r="B25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="3"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="H25" s="3"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -4500,22 +4513,18 @@
         <v>16</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>87</v>
+        <v>83</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>89</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="8" t="s">
-        <v>89</v>
-      </c>
+      <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
@@ -4530,18 +4539,18 @@
         <v>86</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -4557,18 +4566,18 @@
         <v>86</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -4584,18 +4593,18 @@
         <v>86</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
@@ -4611,18 +4620,18 @@
         <v>86</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -4635,18 +4644,22 @@
         <v>16</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>103</v>
+        <v>86</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>99</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>101</v>
+      </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="H31" s="8" t="s">
+        <v>101</v>
+      </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
@@ -4661,10 +4674,10 @@
         <v>102</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
@@ -4684,10 +4697,10 @@
         <v>102</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -4707,10 +4720,10 @@
         <v>102</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -4730,10 +4743,10 @@
         <v>102</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -4753,10 +4766,10 @@
         <v>102</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -4776,10 +4789,10 @@
         <v>102</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -4799,10 +4812,10 @@
         <v>102</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -4822,10 +4835,10 @@
         <v>102</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -4845,10 +4858,10 @@
         <v>102</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -4868,10 +4881,10 @@
         <v>102</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -4891,10 +4904,10 @@
         <v>102</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -4914,10 +4927,10 @@
         <v>102</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -4937,10 +4950,10 @@
         <v>102</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -4960,10 +4973,10 @@
         <v>102</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -4983,10 +4996,10 @@
         <v>102</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -5006,10 +5019,10 @@
         <v>102</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>136</v>
+        <v>133</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>134</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -5026,13 +5039,13 @@
         <v>16</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>138</v>
+        <v>135</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>136</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -5052,10 +5065,10 @@
         <v>137</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -5075,10 +5088,10 @@
         <v>137</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
@@ -5098,10 +5111,10 @@
         <v>137</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
@@ -5121,10 +5134,10 @@
         <v>137</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
@@ -5144,10 +5157,10 @@
         <v>137</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
@@ -5167,10 +5180,10 @@
         <v>137</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
@@ -5187,13 +5200,13 @@
         <v>16</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
@@ -5213,10 +5226,10 @@
         <v>145</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
@@ -5236,10 +5249,10 @@
         <v>145</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
@@ -5259,10 +5272,10 @@
         <v>145</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
@@ -5282,10 +5295,10 @@
         <v>145</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
@@ -5305,10 +5318,10 @@
         <v>145</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
@@ -5328,10 +5341,10 @@
         <v>145</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
@@ -5351,10 +5364,10 @@
         <v>145</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
@@ -5374,10 +5387,10 @@
         <v>145</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
@@ -5394,22 +5407,18 @@
         <v>16</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>157</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
-      <c r="H64" s="8" t="s">
-        <v>157</v>
-      </c>
+      <c r="H64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
@@ -5421,22 +5430,22 @@
         <v>16</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>161</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="F65" s="4"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
+      <c r="H65" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
@@ -5451,10 +5460,10 @@
         <v>158</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>160</v>
@@ -5478,10 +5487,10 @@
         <v>158</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>160</v>
@@ -5505,10 +5514,10 @@
         <v>158</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>160</v>
@@ -5532,10 +5541,10 @@
         <v>158</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>160</v>
@@ -5559,10 +5568,10 @@
         <v>158</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>160</v>
@@ -5586,10 +5595,10 @@
         <v>158</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>160</v>
@@ -5613,10 +5622,10 @@
         <v>158</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>160</v>
@@ -5632,20 +5641,24 @@
       <c r="L72" s="4"/>
       <c r="M72" s="5"/>
     </row>
-    <row r="73" spans="1:13" ht="14.25" customHeight="1">
+    <row r="73" spans="1:13" ht="13.5" customHeight="1">
       <c r="A73" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B73" s="4"/>
+      <c r="B73" s="5" t="s">
+        <v>158</v>
+      </c>
       <c r="C73" s="5" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="E73" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>160</v>
+      </c>
       <c r="F73" s="8" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
@@ -5655,27 +5668,23 @@
       <c r="L73" s="4"/>
       <c r="M73" s="5"/>
     </row>
-    <row r="74" spans="1:13" ht="13.5" customHeight="1">
+    <row r="74" spans="1:13" ht="14.25" customHeight="1">
       <c r="A74" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B74" s="5" t="s">
-        <v>650</v>
-      </c>
+      <c r="B74" s="4"/>
       <c r="C74" s="5" t="s">
-        <v>646</v>
+        <v>169</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" s="4"/>
+        <v>170</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="G74" s="4"/>
-      <c r="H74" s="10" t="s">
-        <v>15</v>
-      </c>
+      <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
@@ -5690,10 +5699,10 @@
         <v>650</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="D75" s="45" t="s">
-        <v>648</v>
+        <v>646</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>15</v>
@@ -5714,13 +5723,13 @@
         <v>16</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D76" s="45" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>15</v>
@@ -5744,10 +5753,10 @@
         <v>651</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="D77" s="17" t="s">
-        <v>172</v>
+        <v>645</v>
+      </c>
+      <c r="D77" s="45" t="s">
+        <v>647</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>15</v>
@@ -5771,10 +5780,10 @@
         <v>651</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>173</v>
+        <v>649</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>15</v>
@@ -5798,10 +5807,10 @@
         <v>651</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>15</v>
@@ -5825,10 +5834,10 @@
         <v>651</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>15</v>
@@ -5852,24 +5861,24 @@
         <v>651</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F81" s="20"/>
-      <c r="G81" s="20"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
       <c r="H81" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I81" s="20"/>
-      <c r="J81" s="20"/>
-      <c r="K81" s="20"/>
-      <c r="L81" s="20"/>
-      <c r="M81" s="21"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="5"/>
     </row>
     <row r="82" spans="1:13" ht="13.5" customHeight="1">
       <c r="A82" s="7" t="s">
@@ -5879,24 +5888,24 @@
         <v>651</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
       <c r="H82" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="5"/>
+      <c r="I82" s="20"/>
+      <c r="J82" s="20"/>
+      <c r="K82" s="20"/>
+      <c r="L82" s="20"/>
+      <c r="M82" s="21"/>
     </row>
     <row r="83" spans="1:13" ht="13.5" customHeight="1">
       <c r="A83" s="7" t="s">
@@ -5906,10 +5915,10 @@
         <v>651</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>15</v>
@@ -5933,10 +5942,10 @@
         <v>651</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>15</v>
@@ -5960,10 +5969,10 @@
         <v>651</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>15</v>
@@ -5987,10 +5996,10 @@
         <v>651</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>15</v>
@@ -6014,10 +6023,10 @@
         <v>651</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>15</v>
@@ -6041,10 +6050,10 @@
         <v>651</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>15</v>
@@ -6068,10 +6077,10 @@
         <v>651</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>15</v>
@@ -6095,10 +6104,10 @@
         <v>651</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>15</v>
@@ -6122,10 +6131,10 @@
         <v>651</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>15</v>
@@ -6149,10 +6158,10 @@
         <v>651</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>15</v>
@@ -6176,24 +6185,24 @@
         <v>651</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F93" s="20"/>
-      <c r="G93" s="20"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
       <c r="H93" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I93" s="20"/>
-      <c r="J93" s="20"/>
-      <c r="K93" s="20"/>
-      <c r="L93" s="20"/>
-      <c r="M93" s="21"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="5"/>
     </row>
     <row r="94" spans="1:13" ht="13.5" customHeight="1">
       <c r="A94" s="7" t="s">
@@ -6203,24 +6212,24 @@
         <v>651</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
+      <c r="F94" s="20"/>
+      <c r="G94" s="20"/>
       <c r="H94" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="5"/>
+      <c r="I94" s="20"/>
+      <c r="J94" s="20"/>
+      <c r="K94" s="20"/>
+      <c r="L94" s="20"/>
+      <c r="M94" s="21"/>
     </row>
     <row r="95" spans="1:13" ht="13.5" customHeight="1">
       <c r="A95" s="7" t="s">
@@ -6230,24 +6239,24 @@
         <v>651</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F95" s="20"/>
-      <c r="G95" s="20"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
       <c r="H95" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
-      <c r="K95" s="20"/>
-      <c r="L95" s="20"/>
-      <c r="M95" s="21"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="5"/>
     </row>
     <row r="96" spans="1:13" ht="13.5" customHeight="1">
       <c r="A96" s="7" t="s">
@@ -6257,40 +6266,46 @@
         <v>651</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
+      <c r="F96" s="20"/>
+      <c r="G96" s="20"/>
       <c r="H96" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="5"/>
+      <c r="K96" s="20"/>
+      <c r="L96" s="20"/>
+      <c r="M96" s="21"/>
     </row>
     <row r="97" spans="1:13" ht="13.5" customHeight="1">
       <c r="A97" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B97" s="5"/>
+      <c r="B97" s="5" t="s">
+        <v>651</v>
+      </c>
       <c r="C97" s="5" t="s">
-        <v>640</v>
+        <v>209</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="E97" s="7"/>
+        <v>210</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
-      <c r="H97" s="7"/>
+      <c r="H97" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
@@ -6303,10 +6318,10 @@
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5" t="s">
-        <v>212</v>
+        <v>640</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E98" s="7"/>
       <c r="F98" s="4"/>
@@ -6324,19 +6339,15 @@
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>216</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="E99" s="7"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
-      <c r="H99" s="10" t="s">
-        <v>216</v>
-      </c>
+      <c r="H99" s="7"/>
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
@@ -6349,18 +6360,18 @@
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
       <c r="H100" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
@@ -6370,24 +6381,24 @@
     </row>
     <row r="101" spans="1:13" ht="13.5" customHeight="1">
       <c r="A101" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B101" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="C101" s="22" t="s">
-        <v>222</v>
+        <v>16</v>
+      </c>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="E101" s="7"/>
+        <v>218</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>219</v>
+      </c>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="23" t="s">
-        <v>224</v>
-      </c>
+      <c r="H101" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I101" s="4"/>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
@@ -6401,17 +6412,17 @@
         <v>221</v>
       </c>
       <c r="C102" s="22" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
       <c r="H102" s="7"/>
       <c r="I102" s="23" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
@@ -6426,17 +6437,17 @@
         <v>221</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
       <c r="H103" s="7"/>
       <c r="I103" s="23" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
@@ -6447,19 +6458,21 @@
       <c r="A104" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B104" s="4"/>
-      <c r="C104" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="E104" s="3"/>
-      <c r="F104" s="20"/>
-      <c r="G104" s="20"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="8" t="s">
-        <v>224</v>
+      <c r="B104" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="C104" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D104" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="E104" s="7"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="23" t="s">
+        <v>230</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
@@ -6470,21 +6483,19 @@
       <c r="A105" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B105" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="C105" s="22" t="s">
-        <v>234</v>
+      <c r="B105" s="4"/>
+      <c r="C105" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="20"/>
       <c r="G105" s="20"/>
       <c r="H105" s="3"/>
       <c r="I105" s="8" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
@@ -6499,17 +6510,17 @@
         <v>233</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="20"/>
       <c r="G106" s="20"/>
       <c r="H106" s="3"/>
       <c r="I106" s="8" t="s">
-        <v>634</v>
+        <v>236</v>
       </c>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
@@ -6524,17 +6535,17 @@
         <v>233</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="20"/>
       <c r="G107" s="20"/>
       <c r="H107" s="3"/>
       <c r="I107" s="8" t="s">
-        <v>236</v>
+        <v>634</v>
       </c>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
@@ -6549,10 +6560,10 @@
         <v>233</v>
       </c>
       <c r="C108" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="D108" s="25" t="s">
-        <v>242</v>
+        <v>239</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>240</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="20"/>
@@ -6574,10 +6585,10 @@
         <v>233</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
+      </c>
+      <c r="D109" s="25" t="s">
+        <v>242</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="20"/>
@@ -6595,21 +6606,21 @@
       <c r="A110" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B110" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>246</v>
+      <c r="B110" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="C110" s="22" t="s">
+        <v>243</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="20"/>
       <c r="G110" s="20"/>
       <c r="H110" s="3"/>
       <c r="I110" s="8" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
@@ -6624,17 +6635,17 @@
         <v>245</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E111" s="3"/>
-      <c r="F111" s="4"/>
+      <c r="F111" s="20"/>
       <c r="G111" s="20"/>
       <c r="H111" s="3"/>
       <c r="I111" s="8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
@@ -6645,19 +6656,21 @@
       <c r="A112" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B112" s="3"/>
+      <c r="B112" s="5" t="s">
+        <v>245</v>
+      </c>
       <c r="C112" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E112" s="3"/>
-      <c r="F112" s="20"/>
+      <c r="F112" s="4"/>
       <c r="G112" s="20"/>
       <c r="H112" s="3"/>
       <c r="I112" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
@@ -6670,17 +6683,17 @@
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="20"/>
       <c r="G113" s="20"/>
       <c r="H113" s="3"/>
       <c r="I113" s="8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
@@ -6693,17 +6706,17 @@
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="20"/>
       <c r="G114" s="20"/>
       <c r="H114" s="3"/>
       <c r="I114" s="8" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
@@ -6714,28 +6727,26 @@
       <c r="A115" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B115" s="5" t="s">
-        <v>261</v>
-      </c>
+      <c r="B115" s="3"/>
       <c r="C115" s="7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="20"/>
       <c r="G115" s="20"/>
       <c r="H115" s="3"/>
-      <c r="I115" s="10" t="s">
-        <v>264</v>
+      <c r="I115" s="8" t="s">
+        <v>260</v>
       </c>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
       <c r="L115" s="4"/>
       <c r="M115" s="5"/>
     </row>
-    <row r="116" spans="1:13" ht="15" customHeight="1">
+    <row r="116" spans="1:13" ht="13.5" customHeight="1">
       <c r="A116" s="7" t="s">
         <v>220</v>
       </c>
@@ -6743,41 +6754,43 @@
         <v>261</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E116" s="3"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
-      <c r="H116" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="I116" s="4"/>
+      <c r="F116" s="20"/>
+      <c r="G116" s="20"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="10" t="s">
+        <v>264</v>
+      </c>
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
     </row>
-    <row r="117" spans="1:13" ht="13.5" customHeight="1">
+    <row r="117" spans="1:13" ht="15" customHeight="1">
       <c r="A117" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B117" s="4"/>
+      <c r="B117" s="5" t="s">
+        <v>261</v>
+      </c>
       <c r="C117" s="7" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E117" s="3"/>
-      <c r="F117" s="20"/>
-      <c r="G117" s="20"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="8" t="s">
-        <v>269</v>
-      </c>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="I117" s="4"/>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
@@ -6789,42 +6802,40 @@
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E118" s="3"/>
-      <c r="F118" s="4"/>
-      <c r="G118" s="4"/>
-      <c r="H118" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="I118" s="4"/>
+      <c r="F118" s="20"/>
+      <c r="G118" s="20"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="8" t="s">
+        <v>269</v>
+      </c>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
       <c r="L118" s="4"/>
       <c r="M118" s="5"/>
     </row>
-    <row r="119" spans="1:13" ht="12.75" customHeight="1">
+    <row r="119" spans="1:13" ht="13.5" customHeight="1">
       <c r="A119" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B119" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="B119" s="4"/>
       <c r="C119" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="D119" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="E119" s="4"/>
-      <c r="F119" s="8" t="s">
-        <v>276</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E119" s="3"/>
+      <c r="F119" s="4"/>
       <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
+      <c r="H119" s="14" t="s">
+        <v>272</v>
+      </c>
       <c r="I119" s="4"/>
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
@@ -6839,14 +6850,14 @@
         <v>273</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
@@ -6864,14 +6875,14 @@
         <v>273</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E121" s="4"/>
       <c r="F121" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
@@ -6889,14 +6900,14 @@
         <v>273</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
@@ -6914,14 +6925,14 @@
         <v>273</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="8" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
@@ -6939,14 +6950,14 @@
         <v>273</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E124" s="4"/>
       <c r="F124" s="8" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
@@ -6964,14 +6975,14 @@
         <v>273</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="8" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
@@ -6981,7 +6992,7 @@
       <c r="L125" s="4"/>
       <c r="M125" s="5"/>
     </row>
-    <row r="126" spans="1:13" ht="13.5" customHeight="1">
+    <row r="126" spans="1:13" ht="12.75" customHeight="1">
       <c r="A126" s="7" t="s">
         <v>220</v>
       </c>
@@ -6989,19 +7000,19 @@
         <v>273</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E126" s="4"/>
-      <c r="F126" s="4"/>
+      <c r="F126" s="8" t="s">
+        <v>294</v>
+      </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
-      <c r="I126" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="J126" s="20"/>
+      <c r="I126" s="4"/>
+      <c r="J126" s="4"/>
       <c r="K126" s="4"/>
       <c r="L126" s="4"/>
       <c r="M126" s="5"/>
@@ -7014,17 +7025,17 @@
         <v>273</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="D127" s="17" t="s">
-        <v>299</v>
+        <v>295</v>
+      </c>
+      <c r="D127" s="15" t="s">
+        <v>296</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
       <c r="I127" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J127" s="20"/>
       <c r="K127" s="4"/>
@@ -7038,41 +7049,45 @@
       <c r="B128" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C128" s="5" t="s">
-        <v>301</v>
+      <c r="C128" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E128" s="4"/>
-      <c r="F128" s="26" t="s">
-        <v>303</v>
-      </c>
+      <c r="F128" s="4"/>
       <c r="G128" s="4"/>
-      <c r="H128" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="I128" s="4"/>
-      <c r="J128" s="4"/>
+      <c r="H128" s="4"/>
+      <c r="I128" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="J128" s="20"/>
       <c r="K128" s="4"/>
       <c r="L128" s="4"/>
       <c r="M128" s="5"/>
     </row>
     <row r="129" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A129" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B129" s="4"/>
+      <c r="A129" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="C129" s="5" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E129" s="4"/>
-      <c r="F129" s="4"/>
+      <c r="F129" s="26" t="s">
+        <v>303</v>
+      </c>
       <c r="G129" s="4"/>
-      <c r="H129" s="4"/>
+      <c r="H129" s="26" t="s">
+        <v>304</v>
+      </c>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
@@ -7080,24 +7095,20 @@
       <c r="M129" s="5"/>
     </row>
     <row r="130" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A130" s="7" t="s">
+      <c r="A130" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B130" s="5" t="s">
-        <v>308</v>
-      </c>
+      <c r="B130" s="4"/>
       <c r="C130" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="E130" s="10" t="s">
-        <v>311</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="E130" s="4"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
-      <c r="H130" s="3"/>
+      <c r="H130" s="4"/>
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
@@ -7112,13 +7123,13 @@
         <v>308</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
@@ -7137,13 +7148,13 @@
         <v>308</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
@@ -7162,13 +7173,13 @@
         <v>308</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
@@ -7187,17 +7198,17 @@
         <v>308</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>322</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>323</v>
+        <v>319</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>320</v>
       </c>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
+      <c r="H134" s="3"/>
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
@@ -7212,17 +7223,17 @@
         <v>308</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>326</v>
+        <v>322</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>323</v>
       </c>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
-      <c r="H135" s="3"/>
+      <c r="H135" s="4"/>
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
@@ -7237,13 +7248,13 @@
         <v>308</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
@@ -7262,13 +7273,13 @@
         <v>308</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
@@ -7287,17 +7298,17 @@
         <v>308</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="E138" s="8" t="s">
-        <v>335</v>
+        <v>331</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>332</v>
       </c>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
+      <c r="H138" s="3"/>
       <c r="I138" s="4"/>
       <c r="J138" s="4"/>
       <c r="K138" s="4"/>
@@ -7312,10 +7323,10 @@
         <v>308</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E139" s="8" t="s">
         <v>335</v>
@@ -7337,13 +7348,13 @@
         <v>308</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
@@ -7362,13 +7373,13 @@
         <v>308</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F141" s="4"/>
       <c r="G141" s="4"/>
@@ -7384,20 +7395,18 @@
         <v>305</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="F142" s="8" t="s">
-        <v>347</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="F142" s="4"/>
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
@@ -7414,13 +7423,13 @@
         <v>343</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>347</v>
@@ -7441,13 +7450,13 @@
         <v>343</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>347</v>
@@ -7468,13 +7477,13 @@
         <v>343</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>347</v>
@@ -7495,13 +7504,13 @@
         <v>343</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>347</v>
@@ -7522,13 +7531,13 @@
         <v>343</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>347</v>
@@ -7549,16 +7558,16 @@
         <v>343</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4"/>
@@ -7576,19 +7585,19 @@
         <v>343</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="E149" s="10" t="s">
-        <v>369</v>
+        <v>364</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>365</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>366</v>
       </c>
       <c r="G149" s="4"/>
-      <c r="H149" s="3"/>
+      <c r="H149" s="4"/>
       <c r="I149" s="4"/>
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
@@ -7603,19 +7612,19 @@
         <v>343</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>372</v>
+        <v>368</v>
+      </c>
+      <c r="E150" s="10" t="s">
+        <v>369</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>366</v>
       </c>
       <c r="G150" s="4"/>
-      <c r="H150" s="4"/>
+      <c r="H150" s="3"/>
       <c r="I150" s="4"/>
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
@@ -7630,13 +7639,13 @@
         <v>343</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>366</v>
@@ -7657,13 +7666,13 @@
         <v>343</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>366</v>
@@ -7680,17 +7689,17 @@
       <c r="A153" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B153" s="7" t="s">
+      <c r="B153" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="C153" s="7" t="s">
-        <v>379</v>
+      <c r="C153" s="5" t="s">
+        <v>376</v>
       </c>
       <c r="D153" s="17" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>366</v>
@@ -7698,34 +7707,34 @@
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
-      <c r="J153" s="5"/>
+      <c r="J153" s="4"/>
       <c r="K153" s="4"/>
       <c r="L153" s="4"/>
       <c r="M153" s="5"/>
     </row>
     <row r="154" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A154" s="5" t="s">
+      <c r="A154" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B154" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>383</v>
+      <c r="B154" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>379</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="E154" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="F154" s="23" t="s">
-        <v>385</v>
+        <v>380</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>366</v>
       </c>
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
+      <c r="J154" s="5"/>
       <c r="K154" s="4"/>
       <c r="L154" s="4"/>
       <c r="M154" s="5"/>
@@ -7738,16 +7747,16 @@
         <v>382</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E155" s="23" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F155" s="23" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
@@ -7758,24 +7767,28 @@
       <c r="M155" s="5"/>
     </row>
     <row r="156" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A156" s="7" t="s">
+      <c r="A156" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B156" s="4"/>
+      <c r="B156" s="5" t="s">
+        <v>382</v>
+      </c>
       <c r="C156" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D156" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="E156" s="4"/>
-      <c r="F156" s="20"/>
-      <c r="G156" s="20"/>
+        <v>387</v>
+      </c>
+      <c r="E156" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="F156" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="G156" s="4"/>
       <c r="H156" s="4"/>
-      <c r="I156" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="J156" s="20"/>
+      <c r="I156" s="4"/>
+      <c r="J156" s="4"/>
       <c r="K156" s="4"/>
       <c r="L156" s="4"/>
       <c r="M156" s="5"/>
@@ -7786,17 +7799,17 @@
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E157" s="4"/>
       <c r="F157" s="20"/>
       <c r="G157" s="20"/>
       <c r="H157" s="4"/>
       <c r="I157" s="26" t="s">
-        <v>393</v>
+        <v>300</v>
       </c>
       <c r="J157" s="20"/>
       <c r="K157" s="4"/>
@@ -7809,43 +7822,41 @@
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D158" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="E158" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="F158" s="4"/>
-      <c r="G158" s="4"/>
-      <c r="H158" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="I158" s="4"/>
-      <c r="J158" s="4"/>
+        <v>391</v>
+      </c>
+      <c r="D158" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="E158" s="4"/>
+      <c r="F158" s="20"/>
+      <c r="G158" s="20"/>
+      <c r="H158" s="4"/>
+      <c r="I158" s="26" t="s">
+        <v>393</v>
+      </c>
+      <c r="J158" s="20"/>
       <c r="K158" s="4"/>
       <c r="L158" s="4"/>
       <c r="M158" s="5"/>
     </row>
     <row r="159" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A159" s="5" t="s">
-        <v>397</v>
+      <c r="A159" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="5" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F159" s="4"/>
       <c r="G159" s="4"/>
       <c r="H159" s="8" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
@@ -7859,18 +7870,18 @@
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="5" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F160" s="4"/>
       <c r="G160" s="4"/>
       <c r="H160" s="8" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
@@ -7884,19 +7895,19 @@
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F161" s="8" t="s">
-        <v>406</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="F161" s="4"/>
       <c r="G161" s="4"/>
-      <c r="H161" s="4"/>
+      <c r="H161" s="8" t="s">
+        <v>403</v>
+      </c>
       <c r="I161" s="4"/>
       <c r="J161" s="4"/>
       <c r="K161" s="4"/>
@@ -7905,19 +7916,21 @@
     </row>
     <row r="162" spans="1:13" ht="13.5" customHeight="1">
       <c r="A162" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="B162" s="5"/>
+        <v>397</v>
+      </c>
+      <c r="B162" s="4"/>
       <c r="C162" s="5" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="F162" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>406</v>
+      </c>
       <c r="G162" s="4"/>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
@@ -7930,30 +7943,24 @@
       <c r="A163" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B163" s="5" t="s">
-        <v>411</v>
-      </c>
+      <c r="B163" s="5"/>
       <c r="C163" s="5" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="F163" s="8" t="s">
-        <v>414</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="F163" s="4"/>
       <c r="G163" s="4"/>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
       <c r="K163" s="4"/>
       <c r="L163" s="4"/>
-      <c r="M163" s="8" t="s">
-        <v>415</v>
-      </c>
+      <c r="M163" s="5"/>
     </row>
     <row r="164" spans="1:13" ht="13.5" customHeight="1">
       <c r="A164" s="5" t="s">
@@ -7963,21 +7970,19 @@
         <v>411</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F164" s="8" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G164" s="4"/>
-      <c r="H164" s="8" t="s">
-        <v>418</v>
-      </c>
+      <c r="H164" s="4"/>
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
       <c r="K164" s="4"/>
@@ -7994,20 +7999,20 @@
         <v>411</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="G165" s="4"/>
       <c r="H165" s="8" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
@@ -8025,20 +8030,20 @@
         <v>411</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G166" s="4"/>
       <c r="H166" s="8" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="I166" s="4"/>
       <c r="J166" s="4"/>
@@ -8048,32 +8053,38 @@
         <v>415</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="15" customHeight="1">
+    <row r="167" spans="1:13" ht="13.5" customHeight="1">
       <c r="A167" s="5" t="s">
         <v>407</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="E167" s="4"/>
-      <c r="F167" s="4"/>
+        <v>423</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>424</v>
+      </c>
       <c r="G167" s="4"/>
-      <c r="H167" s="4"/>
-      <c r="I167" s="8" t="s">
-        <v>428</v>
-      </c>
+      <c r="H167" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I167" s="4"/>
       <c r="J167" s="4"/>
       <c r="K167" s="4"/>
       <c r="L167" s="4"/>
-      <c r="M167" s="5"/>
-    </row>
-    <row r="168" spans="1:13" ht="13.5" customHeight="1">
+      <c r="M167" s="8" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" ht="15" customHeight="1">
       <c r="A168" s="5" t="s">
         <v>407</v>
       </c>
@@ -8081,16 +8092,18 @@
         <v>425</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
       <c r="G168" s="4"/>
       <c r="H168" s="4"/>
-      <c r="I168" s="4"/>
+      <c r="I168" s="8" t="s">
+        <v>428</v>
+      </c>
       <c r="J168" s="4"/>
       <c r="K168" s="4"/>
       <c r="L168" s="4"/>
@@ -8100,22 +8113,20 @@
       <c r="A169" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B169" s="7" t="s">
-        <v>431</v>
+      <c r="B169" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
       <c r="H169" s="4"/>
-      <c r="I169" s="8" t="s">
-        <v>434</v>
-      </c>
+      <c r="I169" s="4"/>
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
       <c r="L169" s="4"/>
@@ -8129,22 +8140,18 @@
         <v>431</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="E170" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="F170" s="8" t="s">
-        <v>437</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="E170" s="4"/>
+      <c r="F170" s="4"/>
       <c r="G170" s="4"/>
-      <c r="H170" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="I170" s="4"/>
+      <c r="H170" s="4"/>
+      <c r="I170" s="8" t="s">
+        <v>434</v>
+      </c>
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
       <c r="L170" s="4"/>
@@ -8158,18 +8165,22 @@
         <v>431</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="E171" s="4"/>
-      <c r="F171" s="4"/>
+        <v>436</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>437</v>
+      </c>
       <c r="G171" s="4"/>
-      <c r="H171" s="4"/>
-      <c r="I171" s="8" t="s">
-        <v>434</v>
-      </c>
+      <c r="H171" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="I171" s="4"/>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
       <c r="L171" s="4"/>
@@ -8183,17 +8194,17 @@
         <v>431</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
-      <c r="I172" s="10" t="s">
-        <v>442</v>
+      <c r="I172" s="8" t="s">
+        <v>434</v>
       </c>
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
@@ -8208,10 +8219,10 @@
         <v>431</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
@@ -8233,17 +8244,17 @@
         <v>431</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
       <c r="H174" s="4"/>
       <c r="I174" s="10" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
@@ -8258,22 +8269,18 @@
         <v>431</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="F175" s="8" t="s">
-        <v>450</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4"/>
       <c r="G175" s="4"/>
-      <c r="H175" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="I175" s="4"/>
+      <c r="H175" s="4"/>
+      <c r="I175" s="10" t="s">
+        <v>447</v>
+      </c>
       <c r="J175" s="4"/>
       <c r="K175" s="4"/>
       <c r="L175" s="4"/>
@@ -8283,22 +8290,24 @@
       <c r="A176" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B176" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C176" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D176" s="17" t="s">
-        <v>453</v>
+      <c r="B176" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D176" s="15" t="s">
+        <v>449</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="F176" s="4"/>
+        <v>450</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="G176" s="4"/>
       <c r="H176" s="8" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
@@ -8314,18 +8323,18 @@
         <v>451</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D177" s="17" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
       <c r="H177" s="8" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
@@ -8341,18 +8350,18 @@
         <v>451</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D178" s="17" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
       <c r="H178" s="8" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
@@ -8368,18 +8377,18 @@
         <v>451</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F179" s="4"/>
       <c r="G179" s="4"/>
       <c r="H179" s="8" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
@@ -8391,20 +8400,22 @@
       <c r="A180" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B180" s="22" t="s">
-        <v>464</v>
-      </c>
-      <c r="C180" s="22" t="s">
-        <v>465</v>
-      </c>
-      <c r="D180" s="27" t="s">
-        <v>466</v>
-      </c>
-      <c r="E180" s="5"/>
+      <c r="B180" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="D180" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>463</v>
+      </c>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
       <c r="H180" s="8" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
@@ -8420,16 +8431,16 @@
         <v>464</v>
       </c>
       <c r="C181" s="22" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D181" s="27" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E181" s="5"/>
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
       <c r="H181" s="8" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
@@ -8445,16 +8456,16 @@
         <v>464</v>
       </c>
       <c r="C182" s="22" t="s">
-        <v>471</v>
-      </c>
-      <c r="D182" s="28" t="s">
-        <v>472</v>
+        <v>468</v>
+      </c>
+      <c r="D182" s="27" t="s">
+        <v>469</v>
       </c>
       <c r="E182" s="5"/>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
       <c r="H182" s="8" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
@@ -8470,16 +8481,16 @@
         <v>464</v>
       </c>
       <c r="C183" s="22" t="s">
-        <v>474</v>
-      </c>
-      <c r="D183" s="27" t="s">
-        <v>475</v>
+        <v>471</v>
+      </c>
+      <c r="D183" s="28" t="s">
+        <v>472</v>
       </c>
       <c r="E183" s="5"/>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
       <c r="H183" s="8" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
@@ -8495,16 +8506,16 @@
         <v>464</v>
       </c>
       <c r="C184" s="22" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D184" s="27" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E184" s="5"/>
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
       <c r="H184" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
@@ -8514,51 +8525,49 @@
     </row>
     <row r="185" spans="1:13" ht="13.5" customHeight="1">
       <c r="A185" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="B185" s="4"/>
-      <c r="C185" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="D185" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="E185" s="8" t="s">
-        <v>320</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="B185" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="C185" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="D185" s="27" t="s">
+        <v>478</v>
+      </c>
+      <c r="E185" s="5"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
-      <c r="H185" s="5"/>
-      <c r="I185" s="23" t="s">
-        <v>483</v>
-      </c>
+      <c r="H185" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="I185" s="4"/>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
       <c r="L185" s="4"/>
       <c r="M185" s="5"/>
     </row>
     <row r="186" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A186" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>485</v>
-      </c>
+      <c r="A186" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B186" s="4"/>
       <c r="C186" s="5" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D186" s="15" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="F186" s="8" t="s">
-        <v>323</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="F186" s="4"/>
       <c r="G186" s="4"/>
-      <c r="H186" s="4"/>
-      <c r="I186" s="4"/>
+      <c r="H186" s="5"/>
+      <c r="I186" s="23" t="s">
+        <v>483</v>
+      </c>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
       <c r="L186" s="4"/>
@@ -8572,13 +8581,13 @@
         <v>485</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D187" s="15" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F187" s="8" t="s">
         <v>323</v>
@@ -8596,22 +8605,22 @@
         <v>484</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D188" s="15" t="s">
-        <v>493</v>
-      </c>
-      <c r="E188" s="4"/>
+        <v>490</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>491</v>
+      </c>
       <c r="F188" s="8" t="s">
-        <v>494</v>
+        <v>323</v>
       </c>
       <c r="G188" s="4"/>
-      <c r="H188" s="8" t="s">
-        <v>494</v>
-      </c>
+      <c r="H188" s="4"/>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
@@ -8623,23 +8632,21 @@
         <v>484</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>497</v>
-      </c>
-      <c r="E189" s="8" t="s">
-        <v>498</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="E189" s="4"/>
       <c r="F189" s="8" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G189" s="4"/>
       <c r="H189" s="8" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
@@ -8655,20 +8662,20 @@
         <v>495</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>23</v>
+        <v>498</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>23</v>
+        <v>498</v>
       </c>
       <c r="G190" s="4"/>
       <c r="H190" s="8" t="s">
-        <v>23</v>
+        <v>498</v>
       </c>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
@@ -8680,20 +8687,26 @@
       <c r="A191" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="B191" s="4"/>
+      <c r="B191" s="5" t="s">
+        <v>495</v>
+      </c>
       <c r="C191" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="E191" s="4"/>
-      <c r="F191" s="4"/>
+        <v>500</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="G191" s="4"/>
-      <c r="H191" s="4"/>
-      <c r="I191" s="8" t="s">
-        <v>503</v>
-      </c>
+      <c r="H191" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I191" s="4"/>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
       <c r="L191" s="4"/>
@@ -8701,23 +8714,21 @@
     </row>
     <row r="192" spans="1:13" ht="13.5" customHeight="1">
       <c r="A192" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="C192" s="7" t="s">
-        <v>506</v>
+        <v>484</v>
+      </c>
+      <c r="B192" s="4"/>
+      <c r="C192" s="5" t="s">
+        <v>501</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="E192" s="4"/>
       <c r="F192" s="4"/>
       <c r="G192" s="4"/>
       <c r="H192" s="4"/>
-      <c r="I192" s="10" t="s">
-        <v>508</v>
+      <c r="I192" s="8" t="s">
+        <v>503</v>
       </c>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
@@ -8732,20 +8743,18 @@
         <v>505</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D193" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="E193" s="8" t="s">
-        <v>320</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="E193" s="4"/>
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
-      <c r="H193" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="I193" s="4"/>
+      <c r="H193" s="4"/>
+      <c r="I193" s="10" t="s">
+        <v>508</v>
+      </c>
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
       <c r="L193" s="4"/>
@@ -8756,21 +8765,23 @@
         <v>504</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="D194" s="29" t="s">
-        <v>513</v>
-      </c>
-      <c r="E194" s="30"/>
-      <c r="F194" s="30"/>
-      <c r="G194" s="30"/>
-      <c r="H194" s="31"/>
-      <c r="I194" s="10" t="s">
-        <v>514</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="D194" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="F194" s="4"/>
+      <c r="G194" s="4"/>
+      <c r="H194" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="I194" s="4"/>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
       <c r="L194" s="4"/>
@@ -8784,20 +8795,18 @@
         <v>511</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="D195" s="15" t="s">
-        <v>516</v>
-      </c>
-      <c r="E195" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="F195" s="4"/>
-      <c r="G195" s="4"/>
-      <c r="H195" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="I195" s="4"/>
+        <v>512</v>
+      </c>
+      <c r="D195" s="29" t="s">
+        <v>513</v>
+      </c>
+      <c r="E195" s="30"/>
+      <c r="F195" s="30"/>
+      <c r="G195" s="30"/>
+      <c r="H195" s="31"/>
+      <c r="I195" s="10" t="s">
+        <v>514</v>
+      </c>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
       <c r="L195" s="4"/>
@@ -8808,20 +8817,22 @@
         <v>504</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="E196" s="4"/>
-      <c r="F196" s="8" t="s">
-        <v>521</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F196" s="4"/>
       <c r="G196" s="4"/>
-      <c r="H196" s="4"/>
+      <c r="H196" s="8" t="s">
+        <v>517</v>
+      </c>
       <c r="I196" s="4"/>
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
@@ -8836,14 +8847,14 @@
         <v>518</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E197" s="4"/>
       <c r="F197" s="8" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G197" s="4"/>
       <c r="H197" s="4"/>
@@ -8861,14 +8872,14 @@
         <v>518</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E198" s="4"/>
       <c r="F198" s="8" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G198" s="4"/>
       <c r="H198" s="4"/>
@@ -8886,14 +8897,14 @@
         <v>518</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="8" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="G199" s="4"/>
       <c r="H199" s="4"/>
@@ -8911,14 +8922,14 @@
         <v>518</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="8" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
@@ -8936,14 +8947,14 @@
         <v>518</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D201" s="15" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E201" s="4"/>
       <c r="F201" s="8" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
@@ -8961,14 +8972,14 @@
         <v>518</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E202" s="4"/>
       <c r="F202" s="8" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
@@ -8986,14 +8997,14 @@
         <v>518</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="8" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
@@ -9011,14 +9022,14 @@
         <v>518</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="G204" s="4"/>
       <c r="H204" s="4"/>
@@ -9036,14 +9047,14 @@
         <v>518</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D205" s="15" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
@@ -9061,14 +9072,14 @@
         <v>518</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="8" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
@@ -9086,14 +9097,14 @@
         <v>518</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="8" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
@@ -9111,14 +9122,14 @@
         <v>518</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="8" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
@@ -9132,20 +9143,22 @@
       <c r="A209" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="B209" s="7"/>
+      <c r="B209" s="7" t="s">
+        <v>518</v>
+      </c>
       <c r="C209" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="D209" s="45" t="s">
-        <v>642</v>
+        <v>555</v>
+      </c>
+      <c r="D209" s="15" t="s">
+        <v>556</v>
       </c>
       <c r="E209" s="4"/>
-      <c r="F209" s="8"/>
+      <c r="F209" s="8" t="s">
+        <v>557</v>
+      </c>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
-      <c r="I209" s="4" t="s">
-        <v>643</v>
-      </c>
+      <c r="I209" s="4"/>
       <c r="J209" s="4"/>
       <c r="K209" s="4"/>
       <c r="L209" s="4"/>
@@ -9155,21 +9168,19 @@
       <c r="A210" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="B210" s="7" t="s">
-        <v>558</v>
-      </c>
+      <c r="B210" s="7"/>
       <c r="C210" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="D210" s="15" t="s">
-        <v>560</v>
+        <v>641</v>
+      </c>
+      <c r="D210" s="45" t="s">
+        <v>642</v>
       </c>
       <c r="E210" s="4"/>
-      <c r="F210" s="4"/>
+      <c r="F210" s="8"/>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
-      <c r="I210" s="23" t="s">
-        <v>561</v>
+      <c r="I210" s="4" t="s">
+        <v>643</v>
       </c>
       <c r="J210" s="4"/>
       <c r="K210" s="4"/>
@@ -9181,20 +9192,20 @@
         <v>504</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
       <c r="I211" s="23" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="J211" s="4"/>
       <c r="K211" s="4"/>
@@ -9209,17 +9220,17 @@
         <v>562</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="4"/>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
       <c r="I212" s="23" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="J212" s="4"/>
       <c r="K212" s="4"/>
@@ -9234,17 +9245,17 @@
         <v>562</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="4"/>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
-      <c r="I213" s="8" t="s">
-        <v>571</v>
+      <c r="I213" s="23" t="s">
+        <v>568</v>
       </c>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
@@ -9253,21 +9264,23 @@
     </row>
     <row r="214" spans="1:13" ht="13.5" customHeight="1">
       <c r="A214" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="B214" s="4"/>
+        <v>504</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>562</v>
+      </c>
       <c r="C214" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
       <c r="I214" s="8" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="J214" s="4"/>
       <c r="K214" s="4"/>
@@ -9280,45 +9293,43 @@
       </c>
       <c r="B215" s="4"/>
       <c r="C215" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>577</v>
-      </c>
-      <c r="E215" s="23" t="s">
-        <v>578</v>
-      </c>
-      <c r="F215" s="23" t="s">
-        <v>578</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="E215" s="4"/>
+      <c r="F215" s="4"/>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
-      <c r="I215" s="4"/>
+      <c r="I215" s="8" t="s">
+        <v>575</v>
+      </c>
       <c r="J215" s="4"/>
       <c r="K215" s="4"/>
       <c r="L215" s="4"/>
       <c r="M215" s="5"/>
     </row>
     <row r="216" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A216" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="B216" s="24" t="s">
-        <v>580</v>
-      </c>
-      <c r="C216" s="32" t="s">
-        <v>580</v>
-      </c>
-      <c r="D216" s="33" t="s">
-        <v>581</v>
-      </c>
-      <c r="E216" s="4"/>
-      <c r="F216" s="4"/>
+      <c r="A216" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="B216" s="4"/>
+      <c r="C216" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="D216" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="E216" s="23" t="s">
+        <v>578</v>
+      </c>
+      <c r="F216" s="23" t="s">
+        <v>578</v>
+      </c>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
-      <c r="I216" s="23" t="s">
-        <v>582</v>
-      </c>
+      <c r="I216" s="4"/>
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
       <c r="L216" s="4"/>
@@ -9332,20 +9343,18 @@
         <v>580</v>
       </c>
       <c r="C217" s="32" t="s">
-        <v>583</v>
-      </c>
-      <c r="D217" s="15" t="s">
-        <v>584</v>
-      </c>
-      <c r="E217" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="F217" s="23" t="s">
-        <v>266</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="D217" s="33" t="s">
+        <v>581</v>
+      </c>
+      <c r="E217" s="4"/>
+      <c r="F217" s="4"/>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
-      <c r="I217" s="4"/>
+      <c r="I217" s="23" t="s">
+        <v>582</v>
+      </c>
       <c r="J217" s="4"/>
       <c r="K217" s="4"/>
       <c r="L217" s="4"/>
@@ -9355,20 +9364,24 @@
       <c r="A218" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="B218" s="4"/>
-      <c r="C218" s="5" t="s">
-        <v>585</v>
+      <c r="B218" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="C218" s="32" t="s">
+        <v>583</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="E218" s="4"/>
-      <c r="F218" s="4"/>
+        <v>584</v>
+      </c>
+      <c r="E218" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F218" s="23" t="s">
+        <v>266</v>
+      </c>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
-      <c r="I218" s="8" t="s">
-        <v>587</v>
-      </c>
+      <c r="I218" s="4"/>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
       <c r="L218" s="4"/>
@@ -9379,18 +9392,18 @@
         <v>579</v>
       </c>
       <c r="B219" s="4"/>
-      <c r="C219" s="7" t="s">
-        <v>588</v>
+      <c r="C219" s="5" t="s">
+        <v>585</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
-      <c r="I219" s="10" t="s">
-        <v>590</v>
+      <c r="I219" s="8" t="s">
+        <v>587</v>
       </c>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
@@ -9403,17 +9416,17 @@
       </c>
       <c r="B220" s="4"/>
       <c r="C220" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D220" s="15" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
-      <c r="I220" s="8" t="s">
-        <v>593</v>
+      <c r="I220" s="10" t="s">
+        <v>590</v>
       </c>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
@@ -9425,18 +9438,18 @@
         <v>579</v>
       </c>
       <c r="B221" s="4"/>
-      <c r="C221" s="5" t="s">
-        <v>594</v>
+      <c r="C221" s="7" t="s">
+        <v>591</v>
       </c>
       <c r="D221" s="15" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
       <c r="I221" s="8" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
@@ -9449,41 +9462,41 @@
       </c>
       <c r="B222" s="4"/>
       <c r="C222" s="5" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D222" s="15" t="s">
-        <v>598</v>
-      </c>
-      <c r="E222" s="8" t="s">
-        <v>599</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="E222" s="4"/>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
       <c r="H222" s="4"/>
-      <c r="I222" s="4"/>
+      <c r="I222" s="8" t="s">
+        <v>596</v>
+      </c>
       <c r="J222" s="4"/>
       <c r="K222" s="4"/>
       <c r="L222" s="4"/>
       <c r="M222" s="5"/>
     </row>
     <row r="223" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A223" s="7" t="s">
-        <v>600</v>
+      <c r="A223" s="5" t="s">
+        <v>579</v>
       </c>
       <c r="B223" s="4"/>
-      <c r="C223" s="22" t="s">
-        <v>601</v>
-      </c>
-      <c r="D223" s="33" t="s">
-        <v>602</v>
-      </c>
-      <c r="E223" s="5"/>
+      <c r="C223" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="D223" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="E223" s="8" t="s">
+        <v>599</v>
+      </c>
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
-      <c r="I223" s="23" t="s">
-        <v>603</v>
-      </c>
+      <c r="I223" s="4"/>
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
       <c r="L223" s="4"/>
@@ -9493,19 +9506,19 @@
       <c r="A224" s="7" t="s">
         <v>600</v>
       </c>
-      <c r="B224" s="3"/>
-      <c r="C224" s="34" t="s">
-        <v>604</v>
-      </c>
-      <c r="D224" s="35" t="s">
-        <v>605</v>
-      </c>
-      <c r="E224" s="3"/>
+      <c r="B224" s="4"/>
+      <c r="C224" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="D224" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="E224" s="5"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
-      <c r="H224" s="3"/>
-      <c r="I224" s="8" t="s">
-        <v>606</v>
+      <c r="H224" s="4"/>
+      <c r="I224" s="23" t="s">
+        <v>603</v>
       </c>
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
@@ -9517,18 +9530,18 @@
         <v>600</v>
       </c>
       <c r="B225" s="3"/>
-      <c r="C225" s="7" t="s">
-        <v>607</v>
-      </c>
-      <c r="D225" s="9" t="s">
-        <v>608</v>
+      <c r="C225" s="34" t="s">
+        <v>604</v>
+      </c>
+      <c r="D225" s="35" t="s">
+        <v>605</v>
       </c>
       <c r="E225" s="3"/>
       <c r="F225" s="4"/>
       <c r="G225" s="4"/>
       <c r="H225" s="3"/>
       <c r="I225" s="8" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
@@ -9540,18 +9553,18 @@
         <v>600</v>
       </c>
       <c r="B226" s="3"/>
-      <c r="C226" s="10" t="s">
-        <v>610</v>
+      <c r="C226" s="7" t="s">
+        <v>607</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E226" s="3"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
       <c r="H226" s="3"/>
       <c r="I226" s="8" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
@@ -9560,21 +9573,21 @@
     </row>
     <row r="227" spans="1:13" ht="13.5" customHeight="1">
       <c r="A227" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="B227" s="4"/>
-      <c r="C227" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="D227" s="15" t="s">
-        <v>615</v>
-      </c>
-      <c r="E227" s="4"/>
+        <v>600</v>
+      </c>
+      <c r="B227" s="3"/>
+      <c r="C227" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="E227" s="3"/>
       <c r="F227" s="4"/>
       <c r="G227" s="4"/>
-      <c r="H227" s="4"/>
+      <c r="H227" s="3"/>
       <c r="I227" s="8" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="J227" s="4"/>
       <c r="K227" s="4"/>
@@ -9586,18 +9599,18 @@
         <v>613</v>
       </c>
       <c r="B228" s="4"/>
-      <c r="C228" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="D228" s="36" t="s">
-        <v>618</v>
+      <c r="C228" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="D228" s="15" t="s">
+        <v>615</v>
       </c>
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
       <c r="G228" s="4"/>
       <c r="H228" s="4"/>
       <c r="I228" s="8" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="J228" s="4"/>
       <c r="K228" s="4"/>
@@ -9605,22 +9618,22 @@
       <c r="M228" s="5"/>
     </row>
     <row r="229" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A229" s="37" t="s">
-        <v>620</v>
-      </c>
-      <c r="B229" s="38"/>
-      <c r="C229" s="39" t="s">
-        <v>621</v>
-      </c>
-      <c r="D229" s="40" t="s">
-        <v>622</v>
-      </c>
-      <c r="E229" s="41"/>
+      <c r="A229" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B229" s="4"/>
+      <c r="C229" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="D229" s="36" t="s">
+        <v>618</v>
+      </c>
+      <c r="E229" s="4"/>
       <c r="F229" s="4"/>
       <c r="G229" s="4"/>
       <c r="H229" s="4"/>
       <c r="I229" s="8" t="s">
-        <v>269</v>
+        <v>619</v>
       </c>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
@@ -9631,19 +9644,19 @@
       <c r="A230" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B230" s="24"/>
-      <c r="C230" s="42" t="s">
-        <v>255</v>
-      </c>
-      <c r="D230" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="E230" s="3"/>
-      <c r="F230" s="20"/>
-      <c r="G230" s="20"/>
-      <c r="H230" s="3"/>
+      <c r="B230" s="38"/>
+      <c r="C230" s="39" t="s">
+        <v>621</v>
+      </c>
+      <c r="D230" s="40" t="s">
+        <v>622</v>
+      </c>
+      <c r="E230" s="41"/>
+      <c r="F230" s="4"/>
+      <c r="G230" s="4"/>
+      <c r="H230" s="4"/>
       <c r="I230" s="8" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
@@ -9655,18 +9668,18 @@
         <v>620</v>
       </c>
       <c r="B231" s="24"/>
-      <c r="C231" s="39" t="s">
-        <v>623</v>
-      </c>
-      <c r="D231" s="40" t="s">
-        <v>624</v>
-      </c>
-      <c r="E231" s="4"/>
-      <c r="F231" s="4"/>
-      <c r="G231" s="4"/>
-      <c r="H231" s="4"/>
-      <c r="I231" s="23" t="s">
-        <v>582</v>
+      <c r="C231" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="D231" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E231" s="3"/>
+      <c r="F231" s="20"/>
+      <c r="G231" s="20"/>
+      <c r="H231" s="3"/>
+      <c r="I231" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
@@ -9677,19 +9690,19 @@
       <c r="A232" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B232" s="38"/>
-      <c r="C232" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="D232" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="E232" s="3"/>
-      <c r="F232" s="20"/>
-      <c r="G232" s="20"/>
-      <c r="H232" s="3"/>
-      <c r="I232" s="8" t="s">
-        <v>224</v>
+      <c r="B232" s="24"/>
+      <c r="C232" s="39" t="s">
+        <v>623</v>
+      </c>
+      <c r="D232" s="40" t="s">
+        <v>624</v>
+      </c>
+      <c r="E232" s="4"/>
+      <c r="F232" s="4"/>
+      <c r="G232" s="4"/>
+      <c r="H232" s="4"/>
+      <c r="I232" s="23" t="s">
+        <v>582</v>
       </c>
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
@@ -9701,18 +9714,18 @@
         <v>620</v>
       </c>
       <c r="B233" s="38"/>
-      <c r="C233" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D233" s="9" t="s">
-        <v>247</v>
+      <c r="C233" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D233" s="44" t="s">
+        <v>232</v>
       </c>
       <c r="E233" s="3"/>
       <c r="F233" s="20"/>
       <c r="G233" s="20"/>
       <c r="H233" s="3"/>
       <c r="I233" s="8" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
@@ -9723,21 +9736,19 @@
       <c r="A234" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B234" s="38" t="s">
-        <v>625</v>
-      </c>
-      <c r="C234" s="39" t="s">
-        <v>626</v>
-      </c>
-      <c r="D234" s="40" t="s">
-        <v>627</v>
-      </c>
-      <c r="E234" s="4"/>
-      <c r="F234" s="4"/>
-      <c r="G234" s="4"/>
-      <c r="H234" s="4"/>
-      <c r="I234" s="23" t="s">
-        <v>628</v>
+      <c r="B234" s="38"/>
+      <c r="C234" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E234" s="3"/>
+      <c r="F234" s="20"/>
+      <c r="G234" s="20"/>
+      <c r="H234" s="3"/>
+      <c r="I234" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
@@ -9752,17 +9763,17 @@
         <v>625</v>
       </c>
       <c r="C235" s="39" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D235" s="40" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E235" s="4"/>
       <c r="F235" s="4"/>
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
       <c r="I235" s="23" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="J235" s="4"/>
       <c r="K235" s="4"/>
@@ -9777,17 +9788,17 @@
         <v>625</v>
       </c>
       <c r="C236" s="39" t="s">
-        <v>228</v>
+        <v>629</v>
       </c>
       <c r="D236" s="40" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E236" s="4"/>
       <c r="F236" s="4"/>
       <c r="G236" s="4"/>
       <c r="H236" s="4"/>
       <c r="I236" s="23" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="J236" s="4"/>
       <c r="K236" s="4"/>
@@ -9795,15 +9806,25 @@
       <c r="M236" s="5"/>
     </row>
     <row r="237" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A237" s="4"/>
-      <c r="B237" s="4"/>
-      <c r="C237" s="4"/>
-      <c r="D237" s="4"/>
+      <c r="A237" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="B237" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="C237" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="D237" s="40" t="s">
+        <v>632</v>
+      </c>
       <c r="E237" s="4"/>
       <c r="F237" s="4"/>
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
-      <c r="I237" s="4"/>
+      <c r="I237" s="23" t="s">
+        <v>633</v>
+      </c>
       <c r="J237" s="4"/>
       <c r="K237" s="4"/>
       <c r="L237" s="4"/>
@@ -12599,7 +12620,21 @@
       <c r="L423" s="4"/>
       <c r="M423" s="5"/>
     </row>
-    <row r="424" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="424" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A424" s="4"/>
+      <c r="B424" s="4"/>
+      <c r="C424" s="4"/>
+      <c r="D424" s="4"/>
+      <c r="E424" s="4"/>
+      <c r="F424" s="4"/>
+      <c r="G424" s="4"/>
+      <c r="H424" s="4"/>
+      <c r="I424" s="4"/>
+      <c r="J424" s="4"/>
+      <c r="K424" s="4"/>
+      <c r="L424" s="4"/>
+      <c r="M424" s="5"/>
+    </row>
     <row r="425" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="426" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="427" spans="1:13" ht="15.75" customHeight="1"/>
@@ -13196,6 +13231,7 @@
     <row r="1018" ht="15.75" customHeight="1"/>
     <row r="1019" ht="15.75" customHeight="1"/>
     <row r="1020" ht="15.75" customHeight="1"/>
+    <row r="1021" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="15"/>
   <hyperlinks>
@@ -13212,203 +13248,204 @@
     <hyperlink ref="D13" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
     <hyperlink ref="D14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="D15" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D17" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="D18" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="D19" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="D20" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="D21" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D22" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="D23" r:id="rId20" display="https://tileserver.geolonia.com/yaizu-smartmap-shindobunpu/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpbmRvYnVucHV8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zaGluZG9idW5wdS0wMUpGWTlGRzE1VDdCSlhRUTJQU1k4TlYzTiP8BmltEvFgZ7AbtdKg7djJVPCvEaVsVGPshOWpe6gKgg&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D24" r:id="rId21" display="https://tileserver.geolonia.com/yaizu-smartmap-ekijyouka/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtZWtpanlvdWthfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtZWtpanlvdWthLTAxSkcwNTZOWFhRQk1UTkpGQUhUOFhNWkVaI3kGu2YpRPXXVDMk0_MykR8ek8rKaS9gxzJwC5M4jj0c&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="D25" r:id="rId22" display="https://tileserver.geolonia.com/yaizu-smartmap-4th-tsunami-shinsui/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtNHRoLXRzdW5hbWktc2hpbnN1aXxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLTR0aC10c3VuYW1pLXNoaW5zdWktMDFKRzFRRjFTQ1hLNUhaRzJZWkRGSk1XM1gjLfrbRh2tvRwxB46BnVq1eJAP4L5jhCAiR9miZwWJ3hk&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="D26" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="D27" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="D28" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="D29" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="D30" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D31" r:id="rId28" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWFsbF9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNNDZIR1hZR0swUUpNTjNZUDRLNlkjPCK5r3Br4iBJ6gs43vYJ3CP6pHMrS3prdRz8lVj3KiE&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="D32" r:id="rId29" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1vb2lnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU05U0dKUVZQNjBTTVE5MzBBNVBTUyN4ZFSCYWcG-VtbFmW8f7esVIHQGyyB-N_-8c-5sjW6lQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="D33" r:id="rId30" display="https://tileserver.geolonia.com/yaizu-smartmap-takakusagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdGFrYWt1c2FnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXRha2FrdXNhZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQUJIQTdUVjRYWEE5QTkzR0FHWkgjimM1TsDVEkqLCSi4wpFK8q5JcfTnTIY6i3i6r57CX0A&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D34" r:id="rId31" display="https://tileserver.geolonia.com/yaizu-smartmap-ishiwakigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaXNoaXdha2lnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWlzaGl3YWtpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOTkyRkZLRFoxV0ZZMDVXOUg1RTUjdD9kb3q6n-edazGHScn5Z_BB2dOtDwwBL0WYUslrNz0&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="D35" r:id="rId32" display="https://tileserver.geolonia.com/yaizu-smartmap-asahinagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTkyN0VEWVA2RzZHWlFENkZHWFdCI5apEATwxiJ5O-u8vrCa_Aq8i588yYu99pyHCD-6cnJD&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="D36" r:id="rId33" display="https://tileserver.geolonia.com/yaizu-smartmap-hanashigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTk1UFdES1ZZUUdFNjg1RkRFWDA5IzJO1Gu9VFWg7akAUXsx62QIvoMMD3bV0B99FamjVRWH&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="D37" r:id="rId34" display="https://tileserver.geolonia.com/yaizu-smartmap-umedagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdW1lZGFnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXVtZWRhZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQU4wNUFFQ0c1Q0dXNFE3VE5GVFkjVEgHYpNTdDz0-WFNj93-ZwFbTyu6Z0d2wk2iM9R5u7Q&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="D38" r:id="rId35" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TUE0RDdKMFZIS0o4Sk1WOTJOTTVBIxuMCm_quVhuckWPNF1obvQO2eCdJtGYUMEVHn3gRKKK&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="D39" r:id="rId36" display="https://tileserver.geolonia.com/yaizu-smartmap-uchisetotanigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdWNoaXNldG90YW5pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC11Y2hpc2V0b3RhbmlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BSjVRSDkwVEg4OUtHV1NDWUQ1WSMydwZLx6k83TZLytgIgc_DPtLeFNHJTqwf9gZAhWFbfA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="D40" r:id="rId37" display="https://tileserver.geolonia.com/yaizu-smartmap-koishigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta29pc2hpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1rb2lzaGlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU05RjdYWU1ZNkpQM0dKTjg5NkhXNiNYOsA7y7e0r_Iu0xpEQOEsj_X5p1-ruM4dQIoVYOSRVw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="D41" r:id="rId38" display="https://tileserver.geolonia.com/yaizu-smartmap-kuroishigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta3Vyb2lzaGlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWt1cm9pc2hpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOU5GNjA3OEs0WUFHQkhXNUhQRFYjLsEzoWos3xapWiBFua2VXJUD5vbReBaMpvfpr_TB3Ng&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="D42" r:id="rId39" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTlKNTROUjlCUVM4QlBWWVc3SzEwI3r7R2_FhpUp13cFLSg7diJ2jHwWVzgQWzKSk7nqnxoQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="D43" r:id="rId40" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC10b2NoaXlhbWFnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BRTlCVDNEWFAxQkdCSjBLNlI2UCOyAh242YqHr6vhWYEoYxNDPOkyFsQGJOX99vXLPs9jvQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="D44" r:id="rId41" display="https://tileserver.geolonia.com/yaizu-smartmap-seanjigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2VhbmppZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zZWFuamlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BMUM5TVJaS0hSVFpTTUJNRU5ITSOLbk41LqC3NJjdsDptQg3a5dUe1-jYrf9Ci_w7me138w&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="D45" r:id="rId42" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXNoaWRhdGFuYWthZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQTg5NjExWUs0M0pKWFhKMzNEQ0sjjXDhElx_Bq-DmgbAZv1rkLWFAJz_mYHzTJ1uT5fEXXE&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="D46" r:id="rId43" display="https://tileserver.geolonia.com/yaizu-smartmap-izumigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaXp1bWlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWl6dW1pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOUMyNEM3NDIzWlA4M0U5MTFaOTIjiZDvCV2809c0N38igMrrlYkjUOlioRRIzO2VhSPcBEU&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="D47" r:id="rId44" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLW90c3V0YW5pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOVhUMUJDMEU1OVMwRUhRQzRRRU4juXpVh3i0MnT59rsmSRi1Y-5Yv9Q2ka273F77i7qhk6M&amp;key=bb4125ebc1ba442da48d3556f1fe13f5_x000a_" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="D48" r:id="rId45" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1hbGxfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVRETjFRNVk2S1E3WTYwV0JSWkVXRiMvFbymz4lH_fdrJRy-jvgwTVw2D13DlzjxNICrb7qY1A&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="D49" r:id="rId46" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyLTAxSko1VERWUkdYNjBLNlFBQTFLM1I5UU5SI3K6_rl11h-EuwrNQ4AE7yQiOLb8PCKqFDOJ4FDRsG-g&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D50" r:id="rId47" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXNldG9nYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjItMDFKSjVURTFZNVRWRTBIVzFWOUFLMzBLRFcji6G-BXNCHGZShICjglWb3w_mWK_NKrvuXH_tI_9nlgQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="D51" r:id="rId48" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWtveWFnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjItMDFKSjVURFJXSldXSkVXUFdESEMzV0sxNTgjf-2T3_0XdWSFLtX6dSNEbLxxCj2IDXBYnWuWoALGMxI&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="D52" r:id="rId49" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyLTAxSko1VEU4NktENUZWU1RGVjE4RDNRVFBUI0UGkE67qVTbtRvaLl2OvOsiZu9Hnd-9AT1ia-ckrXPG&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="D53" r:id="rId50" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zaGlkYXRhbmFrYWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVRFNTUyV0dRWUVTWVdWVkFHNURDUiM6XrMaFpsN_nu69zOxecuTueNyhch7DBXrxCJmaCBV8w&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="D54" r:id="rId51" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1vdHN1dGFuaWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVREWkFYQVcyMktRNEdWVkhOTTQ4USPJeHao4Q6wyWn0IEPkPECr5W-lDwzRh1n7dcRP_rd19Q&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="D55" r:id="rId52" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-duration/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLWR1cmF0aW9ufGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLWR1cmF0aW9uLTAxSkZDMjM2TkNFOEE4WlY1RlpXUTFUNjdQI72n4lnDlqr_qS3dvbGif0AlepOAnvK3E1Vx_MjVLXsc&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="D56" r:id="rId53" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZHxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLW9vaWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWQtMDFKRkMyM0tRRTBOOE02RlJaWlBYWTdNVEsjb6TUQ42ra-hBJK2eSP06FX90ArT2yTi5_X9jzEWntEw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="D57" r:id="rId54" display="https://tileserver.geolonia.com/yaizu-smartmap-asahinagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1hc2FoaW5hZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzQUtEQkFQUkpXMkNKSE45Q0pWNCOv1qiFcrLRZll0zMjGPpeTcM-NM60iPJiH7OxfIPrruw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D58" r:id="rId55" display="https://tileserver.geolonia.com/yaizu-smartmap-hanashigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1oYW5hc2hpZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzRFJBTVYzWFRDUlY0WVJCUUVIUyOyqbE2vnFeS_9BZw94HXS20jBUsE7o_rmOXEyGSp0CYA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="D59" r:id="rId56" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zZXRvZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzVDFETjRKNDZSSENUNkc3VlBGMSM4etkawiLQc6u4jK6mqi1X2xklmi7fEC1D6aIWymyDbA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D60" r:id="rId57" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1rb3lhZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzR1ZZWEFDQzg4MUg3QjlLV1lFOCOfdwjLULNhmI_ow4g0dWNl2dx8qQUUG8aFUeQo_0hXDQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="D61" r:id="rId58" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZHxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXRvY2hpeWFtYWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWQtMDFKRkMyM1pWWVE3MEowUzdaNTZHWkNKRFojC5eX3JK7qasK2odfocPvh5KVdzgW8GfTWFIWWxO0-OY&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="D62" r:id="rId59" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkLTAxSkZDMjNYNFlBNDZLMlQxTVdGMVFWODJaI8I_8TmmNT2ZBas2uO_iuv708Hw-rSmd9df6Iy_TRMzO&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D63" r:id="rId60" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkLTAxSkZDMjNRNENHRURIR1FLNEtGU1lLMzZBI7KZF6uvKMllQBtCXF86Bop_8GzzniSe6NN1Rp0RaowV&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="D64" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D65" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="D66" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D67" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="D68" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D69" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="D70" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D71" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="D72" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D73" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="D74" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D77" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="D78" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D79" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D80" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D81" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D82" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D83" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D84" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D85" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D86" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D87" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D88" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D89" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D90" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D91" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D92" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D93" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D94" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D95" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D96" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D104" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D110" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D111" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D112" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D113" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D114" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D115" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="D116" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D117" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D118" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D119" r:id="rId102" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="D120" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="D121" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="D122" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="D123" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="D124" r:id="rId107" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="D125" r:id="rId108" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="D126" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="D127" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="D128" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D129" r:id="rId112" display="https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="D130" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="D131" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="D132" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D133" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="D134" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="D135" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="D136" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="D137" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="D138" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D139" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="D140" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="D141" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="D142" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="D143" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="D144" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="D145" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="D146" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="D147" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="D148" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="D149" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="D150" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="D151" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="D152" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="D153" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="D154" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="D155" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="D156" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="D157" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="D158" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="D159" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="D160" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="D161" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="D167" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="D168" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="D169" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="D170" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="D171" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="D172" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="D173" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="D174" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="D175" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="D176" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="D177" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="D178" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="D179" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="D180" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="D181" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="D183" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="D184" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D185" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="D186" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D187" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="D188" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D189" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D190" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D191" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="D192" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D193" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="D194" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D195" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="D196" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D197" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D198" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D199" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D200" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D201" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="D202" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D203" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="D204" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D205" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="D206" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D207" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="D208" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D210" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D211" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D212" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D213" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D214" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D215" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D216" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D218" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D219" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D220" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D221" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D222" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D223" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="D224" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D225" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="D226" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D227" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="D228" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D230" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="D232" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D233" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="D18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="D19" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="D20" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="D21" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="D22" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="D23" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="D24" r:id="rId20" display="https://tileserver.geolonia.com/yaizu-smartmap-shindobunpu/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpbmRvYnVucHV8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zaGluZG9idW5wdS0wMUpGWTlGRzE1VDdCSlhRUTJQU1k4TlYzTiP8BmltEvFgZ7AbtdKg7djJVPCvEaVsVGPshOWpe6gKgg&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D25" r:id="rId21" display="https://tileserver.geolonia.com/yaizu-smartmap-ekijyouka/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtZWtpanlvdWthfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtZWtpanlvdWthLTAxSkcwNTZOWFhRQk1UTkpGQUhUOFhNWkVaI3kGu2YpRPXXVDMk0_MykR8ek8rKaS9gxzJwC5M4jj0c&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="D26" r:id="rId22" display="https://tileserver.geolonia.com/yaizu-smartmap-4th-tsunami-shinsui/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtNHRoLXRzdW5hbWktc2hpbnN1aXxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLTR0aC10c3VuYW1pLXNoaW5zdWktMDFKRzFRRjFTQ1hLNUhaRzJZWkRGSk1XM1gjLfrbRh2tvRwxB46BnVq1eJAP4L5jhCAiR9miZwWJ3hk&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="D27" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="D28" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="D29" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="D30" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="D31" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D32" r:id="rId28" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWFsbF9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNNDZIR1hZR0swUUpNTjNZUDRLNlkjPCK5r3Br4iBJ6gs43vYJ3CP6pHMrS3prdRz8lVj3KiE&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="D33" r:id="rId29" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1vb2lnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU05U0dKUVZQNjBTTVE5MzBBNVBTUyN4ZFSCYWcG-VtbFmW8f7esVIHQGyyB-N_-8c-5sjW6lQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="D34" r:id="rId30" display="https://tileserver.geolonia.com/yaizu-smartmap-takakusagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdGFrYWt1c2FnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXRha2FrdXNhZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQUJIQTdUVjRYWEE5QTkzR0FHWkgjimM1TsDVEkqLCSi4wpFK8q5JcfTnTIY6i3i6r57CX0A&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D35" r:id="rId31" display="https://tileserver.geolonia.com/yaizu-smartmap-ishiwakigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaXNoaXdha2lnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWlzaGl3YWtpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOTkyRkZLRFoxV0ZZMDVXOUg1RTUjdD9kb3q6n-edazGHScn5Z_BB2dOtDwwBL0WYUslrNz0&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="D36" r:id="rId32" display="https://tileserver.geolonia.com/yaizu-smartmap-asahinagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTkyN0VEWVA2RzZHWlFENkZHWFdCI5apEATwxiJ5O-u8vrCa_Aq8i588yYu99pyHCD-6cnJD&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="D37" r:id="rId33" display="https://tileserver.geolonia.com/yaizu-smartmap-hanashigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTk1UFdES1ZZUUdFNjg1RkRFWDA5IzJO1Gu9VFWg7akAUXsx62QIvoMMD3bV0B99FamjVRWH&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="D38" r:id="rId34" display="https://tileserver.geolonia.com/yaizu-smartmap-umedagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdW1lZGFnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXVtZWRhZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQU4wNUFFQ0c1Q0dXNFE3VE5GVFkjVEgHYpNTdDz0-WFNj93-ZwFbTyu6Z0d2wk2iM9R5u7Q&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="D39" r:id="rId35" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TUE0RDdKMFZIS0o4Sk1WOTJOTTVBIxuMCm_quVhuckWPNF1obvQO2eCdJtGYUMEVHn3gRKKK&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="D40" r:id="rId36" display="https://tileserver.geolonia.com/yaizu-smartmap-uchisetotanigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdWNoaXNldG90YW5pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC11Y2hpc2V0b3RhbmlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BSjVRSDkwVEg4OUtHV1NDWUQ1WSMydwZLx6k83TZLytgIgc_DPtLeFNHJTqwf9gZAhWFbfA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="D41" r:id="rId37" display="https://tileserver.geolonia.com/yaizu-smartmap-koishigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta29pc2hpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1rb2lzaGlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU05RjdYWU1ZNkpQM0dKTjg5NkhXNiNYOsA7y7e0r_Iu0xpEQOEsj_X5p1-ruM4dQIoVYOSRVw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="D42" r:id="rId38" display="https://tileserver.geolonia.com/yaizu-smartmap-kuroishigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta3Vyb2lzaGlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWt1cm9pc2hpZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOU5GNjA3OEs0WUFHQkhXNUhQRFYjLsEzoWos3xapWiBFua2VXJUD5vbReBaMpvfpr_TB3Ng&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="D43" r:id="rId39" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtbWF4LTIwMjUwMTIyLTAxSko1TTlKNTROUjlCUVM4QlBWWVc3SzEwI3r7R2_FhpUp13cFLSg7diJ2jHwWVzgQWzKSk7nqnxoQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="D44" r:id="rId40" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC10b2NoaXlhbWFnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BRTlCVDNEWFAxQkdCSjBLNlI2UCOyAh242YqHr6vhWYEoYxNDPOkyFsQGJOX99vXLPs9jvQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="D45" r:id="rId41" display="https://tileserver.geolonia.com/yaizu-smartmap-seanjigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2VhbmppZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zZWFuamlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMi0wMUpKNU1BMUM5TVJaS0hSVFpTTUJNRU5ITSOLbk41LqC3NJjdsDptQg3a5dUe1-jYrf9Ci_w7me138w&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="D46" r:id="rId42" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXNoaWRhdGFuYWthZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNQTg5NjExWUs0M0pKWFhKMzNEQ0sjjXDhElx_Bq-DmgbAZv1rkLWFAJz_mYHzTJ1uT5fEXXE&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="D47" r:id="rId43" display="https://tileserver.geolonia.com/yaizu-smartmap-izumigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaXp1bWlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWl6dW1pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOUMyNEM3NDIzWlA4M0U5MTFaOTIjiZDvCV2809c0N38igMrrlYkjUOlioRRIzO2VhSPcBEU&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="D48" r:id="rId44" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-max-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLW1heC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLW90c3V0YW5pZ2F3YV9mbG9vZC1tYXgtMjAyNTAxMjItMDFKSjVNOVhUMUJDMEU1OVMwRUhRQzRRRU4juXpVh3i0MnT59rsmSRi1Y-5Yv9Q2ka273F77i7qhk6M&amp;key=bb4125ebc1ba442da48d3556f1fe13f5_x000a_" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="D49" r:id="rId45" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1hbGxfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVRETjFRNVk2S1E3WTYwV0JSWkVXRiMvFbymz4lH_fdrJRy-jvgwTVw2D13DlzjxNICrb7qY1A&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="D50" r:id="rId46" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyLTAxSko1VERWUkdYNjBLNlFBQTFLM1I5UU5SI3K6_rl11h-EuwrNQ4AE7yQiOLb8PCKqFDOJ4FDRsG-g&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="D51" r:id="rId47" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXNldG9nYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjItMDFKSjVURTFZNVRWRTBIVzFWOUFLMzBLRFcji6G-BXNCHGZShICjglWb3w_mWK_NKrvuXH_tI_9nlgQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="D52" r:id="rId48" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMnxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLWtveWFnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjItMDFKSjVURFJXSldXSkVXUFdESEMzV0sxNTgjf-2T3_0XdWSFLtX6dSNEbLxxCj2IDXBYnWuWoALGMxI&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="D53" r:id="rId49" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1wbGFubmVkLTIwMjUwMTIyLTAxSko1VEU4NktENUZWU1RGVjE4RDNRVFBUI0UGkE67qVTbtRvaLl2OvOsiZu9Hnd-9AT1ia-ckrXPG&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="D54" r:id="rId50" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zaGlkYXRhbmFrYWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVRFNTUyV0dRWUVTWVdWVkFHNURDUiM6XrMaFpsN_nu69zOxecuTueNyhch7DBXrxCJmaCBV8w&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="D55" r:id="rId51" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-planned-20250122/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLXBsYW5uZWQtMjAyNTAxMjJ8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1vdHN1dGFuaWdhd2FfZmxvb2QtcGxhbm5lZC0yMDI1MDEyMi0wMUpKNVREWkFYQVcyMktRNEdWVkhOTTQ4USPJeHao4Q6wyWn0IEPkPECr5W-lDwzRh1n7dcRP_rd19Q&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="D56" r:id="rId52" display="https://tileserver.geolonia.com/yaizu-smartmap-all_flood-duration/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLWR1cmF0aW9ufGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtYWxsX2Zsb29kLWR1cmF0aW9uLTAxSkZDMjM2TkNFOEE4WlY1RlpXUTFUNjdQI72n4lnDlqr_qS3dvbGif0AlepOAnvK3E1Vx_MjVLXsc&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="D57" r:id="rId53" display="https://tileserver.geolonia.com/yaizu-smartmap-ooigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb29pZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZHxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLW9vaWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWQtMDFKRkMyM0tRRTBOOE02RlJaWlBYWTdNVEsjb6TUQ42ra-hBJK2eSP06FX90ArT2yTi5_X9jzEWntEw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="D58" r:id="rId54" display="https://tileserver.geolonia.com/yaizu-smartmap-asahinagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYXNhaGluYWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1hc2FoaW5hZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzQUtEQkFQUkpXMkNKSE45Q0pWNCOv1qiFcrLRZll0zMjGPpeTcM-NM60iPJiH7OxfIPrruw&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D59" r:id="rId55" display="https://tileserver.geolonia.com/yaizu-smartmap-hanashigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtaGFuYXNoaWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1oYW5hc2hpZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzRFJBTVYzWFRDUlY0WVJCUUVIUyOyqbE2vnFeS_9BZw94HXS20jBUsE7o_rmOXEyGSp0CYA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="D60" r:id="rId56" display="https://tileserver.geolonia.com/yaizu-smartmap-setogawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2V0b2dhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1zZXRvZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzVDFETjRKNDZSSENUNkc3VlBGMSM4etkawiLQc6u4jK6mqi1X2xklmi7fEC1D6aIWymyDbA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D61" r:id="rId57" display="https://tileserver.geolonia.com/yaizu-smartmap-koyagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAta295YWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWR8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1rb3lhZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZC0wMUpGQzIzR1ZZWEFDQzg4MUg3QjlLV1lFOCOfdwjLULNhmI_ow4g0dWNl2dx8qQUUG8aFUeQo_0hXDQ&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="D62" r:id="rId58" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZHxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXRvY2hpeWFtYWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWQtMDFKRkMyM1pWWVE3MEowUzdaNTZHWkNKRFojC5eX3JK7qasK2odfocPvh5KVdzgW8GfTWFIWWxO0-OY&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="D63" r:id="rId59" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkLTAxSkZDMjNYNFlBNDZLMlQxTVdGMVFWODJaI8I_8TmmNT2ZBas2uO_iuv708Hw-rSmd9df6Iy_TRMzO&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D64" r:id="rId60" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkLTAxSkZDMjNRNENHRURIR1FLNEtGU1lLMzZBI7KZF6uvKMllQBtCXF86Bop_8GzzniSe6NN1Rp0RaowV&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="D65" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="D66" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="D67" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D68" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="D69" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="D70" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="D71" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="D72" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="D73" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="D74" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="D75" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="D78" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D79" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="D80" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D81" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D82" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D83" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D84" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D85" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D86" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D87" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D88" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D89" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D90" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D91" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D92" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D93" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D94" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D95" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D96" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D97" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D105" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D111" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D112" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D113" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D114" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D115" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="D116" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="D117" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="D118" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D119" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="D120" r:id="rId102" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="D121" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="D122" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="D123" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="D124" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="D125" r:id="rId107" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="D126" r:id="rId108" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="D127" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="D128" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="D129" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="D130" r:id="rId112" display="https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="D131" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="D132" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="D133" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="D134" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="D135" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="D136" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="D137" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="D138" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="D139" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="D140" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="D141" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="D142" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="D143" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="D144" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="D145" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="D146" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="D147" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="D148" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="D149" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="D150" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="D151" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="D152" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="D153" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="D154" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="D155" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="D156" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="D157" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="D158" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="D159" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="D160" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="D161" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="D162" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="D168" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="D169" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="D170" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="D171" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="D172" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="D173" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="D174" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="D175" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="D176" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="D177" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="D178" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="D179" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="D180" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="D181" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="D182" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="D184" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="D185" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="D186" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="D187" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="D188" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="D189" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="D190" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="D191" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="D192" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="D193" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="D194" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="D195" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="D196" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="D197" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="D198" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="D199" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="D200" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="D201" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="D202" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="D203" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="D204" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="D205" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="D206" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="D207" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="D208" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="D209" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="D211" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D212" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D213" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D214" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D215" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D216" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D217" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D219" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D220" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D221" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D222" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D223" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D224" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="D225" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="D226" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="D227" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="D228" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="D229" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="D231" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="D233" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="D234" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
     <hyperlink ref="D16" r:id="rId207" xr:uid="{101A33D7-B7BA-422E-B2FC-342D5148D1EA}"/>
-    <hyperlink ref="D209" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
-    <hyperlink ref="D76" r:id="rId209" xr:uid="{15E62A8C-2F55-4EC5-B29A-D16518F2E4D9}"/>
-    <hyperlink ref="D75" r:id="rId210" xr:uid="{FC2D964E-B283-4703-AAB9-28EC36520D76}"/>
+    <hyperlink ref="D210" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
+    <hyperlink ref="D77" r:id="rId209" xr:uid="{15E62A8C-2F55-4EC5-B29A-D16518F2E4D9}"/>
+    <hyperlink ref="D76" r:id="rId210" xr:uid="{FC2D964E-B283-4703-AAB9-28EC36520D76}"/>
+    <hyperlink ref="D17" r:id="rId211" xr:uid="{BAFD46EC-62AB-41E1-B82A-03A62E913A64}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\vm22flo01\DownloadFiles\スマートシティ課\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3054D43-2D05-4D30-B152-7E00339F7D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431F92A0-012B-4E43-8734-6B62ACE82309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="663">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -3226,6 +3226,60 @@
   </si>
   <si>
     <t>underpass</t>
+  </si>
+  <si>
+    <t>交通事故分析情報</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <r>
+      <t>2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <r>
+      <t>2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E4%BA%A4%E9%80%9A%E4%BA%8B%E6%95%85_2023/tiles.json</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E4%BA%A4%E9%80%9A%E4%BA%8B%E6%95%85_2024/tiles.json</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>#1E6577</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>#165e83</t>
+  </si>
+  <si>
+    <t>#33cccc</t>
   </si>
 </sst>
 </file>
@@ -3859,7 +3913,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M1021"/>
+  <dimension ref="A1:M1023"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -8323,18 +8377,18 @@
         <v>451</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D177" s="17" t="s">
-        <v>453</v>
+        <v>656</v>
+      </c>
+      <c r="D177" s="45" t="s">
+        <v>659</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="F177" s="4"/>
+        <v>662</v>
+      </c>
+      <c r="F177" s="8"/>
       <c r="G177" s="4"/>
       <c r="H177" s="8" t="s">
-        <v>454</v>
+        <v>662</v>
       </c>
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
@@ -8350,18 +8404,18 @@
         <v>451</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="D178" s="17" t="s">
-        <v>456</v>
+        <v>657</v>
+      </c>
+      <c r="D178" s="45" t="s">
+        <v>658</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="F178" s="4"/>
+        <v>661</v>
+      </c>
+      <c r="F178" s="8"/>
       <c r="G178" s="4"/>
       <c r="H178" s="8" t="s">
-        <v>457</v>
+        <v>661</v>
       </c>
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
@@ -8377,18 +8431,18 @@
         <v>451</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="F179" s="4"/>
       <c r="G179" s="4"/>
       <c r="H179" s="8" t="s">
-        <v>460</v>
+        <v>660</v>
       </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
@@ -8404,18 +8458,18 @@
         <v>451</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D180" s="17" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
       <c r="H180" s="8" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
@@ -8427,20 +8481,22 @@
       <c r="A181" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B181" s="22" t="s">
-        <v>464</v>
-      </c>
-      <c r="C181" s="22" t="s">
-        <v>465</v>
-      </c>
-      <c r="D181" s="27" t="s">
-        <v>466</v>
-      </c>
-      <c r="E181" s="5"/>
+      <c r="B181" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="D181" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>460</v>
+      </c>
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
       <c r="H181" s="8" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
@@ -8452,20 +8508,22 @@
       <c r="A182" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B182" s="22" t="s">
-        <v>464</v>
-      </c>
-      <c r="C182" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="D182" s="27" t="s">
-        <v>469</v>
-      </c>
-      <c r="E182" s="5"/>
+      <c r="B182" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="D182" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>463</v>
+      </c>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
       <c r="H182" s="8" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
@@ -8481,16 +8539,16 @@
         <v>464</v>
       </c>
       <c r="C183" s="22" t="s">
-        <v>471</v>
-      </c>
-      <c r="D183" s="28" t="s">
-        <v>472</v>
+        <v>465</v>
+      </c>
+      <c r="D183" s="27" t="s">
+        <v>466</v>
       </c>
       <c r="E183" s="5"/>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
       <c r="H183" s="8" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
@@ -8506,16 +8564,16 @@
         <v>464</v>
       </c>
       <c r="C184" s="22" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D184" s="27" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E184" s="5"/>
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
       <c r="H184" s="8" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
@@ -8531,16 +8589,16 @@
         <v>464</v>
       </c>
       <c r="C185" s="22" t="s">
-        <v>477</v>
-      </c>
-      <c r="D185" s="27" t="s">
-        <v>478</v>
+        <v>471</v>
+      </c>
+      <c r="D185" s="28" t="s">
+        <v>472</v>
       </c>
       <c r="E185" s="5"/>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
       <c r="H185" s="8" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="I185" s="4"/>
       <c r="J185" s="4"/>
@@ -8550,50 +8608,48 @@
     </row>
     <row r="186" spans="1:13" ht="13.5" customHeight="1">
       <c r="A186" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="B186" s="4"/>
-      <c r="C186" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="D186" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="E186" s="8" t="s">
-        <v>320</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="B186" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="C186" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="D186" s="27" t="s">
+        <v>475</v>
+      </c>
+      <c r="E186" s="5"/>
       <c r="F186" s="4"/>
       <c r="G186" s="4"/>
-      <c r="H186" s="5"/>
-      <c r="I186" s="23" t="s">
-        <v>483</v>
-      </c>
+      <c r="H186" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="I186" s="4"/>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
       <c r="L186" s="4"/>
       <c r="M186" s="5"/>
     </row>
     <row r="187" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A187" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="D187" s="15" t="s">
-        <v>487</v>
-      </c>
-      <c r="E187" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="F187" s="8" t="s">
-        <v>323</v>
-      </c>
+      <c r="A187" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B187" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="C187" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="D187" s="27" t="s">
+        <v>478</v>
+      </c>
+      <c r="E187" s="5"/>
+      <c r="F187" s="4"/>
       <c r="G187" s="4"/>
-      <c r="H187" s="4"/>
+      <c r="H187" s="8" t="s">
+        <v>479</v>
+      </c>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
@@ -8601,27 +8657,25 @@
       <c r="M187" s="5"/>
     </row>
     <row r="188" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A188" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>485</v>
-      </c>
+      <c r="A188" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B188" s="4"/>
       <c r="C188" s="5" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="D188" s="15" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="F188" s="8" t="s">
-        <v>323</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="F188" s="4"/>
       <c r="G188" s="4"/>
-      <c r="H188" s="4"/>
-      <c r="I188" s="4"/>
+      <c r="H188" s="5"/>
+      <c r="I188" s="23" t="s">
+        <v>483</v>
+      </c>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
       <c r="L188" s="4"/>
@@ -8632,22 +8686,22 @@
         <v>484</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>493</v>
-      </c>
-      <c r="E189" s="4"/>
+        <v>487</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>488</v>
+      </c>
       <c r="F189" s="8" t="s">
-        <v>494</v>
+        <v>323</v>
       </c>
       <c r="G189" s="4"/>
-      <c r="H189" s="8" t="s">
-        <v>494</v>
-      </c>
+      <c r="H189" s="4"/>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
@@ -8659,24 +8713,22 @@
         <v>484</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>498</v>
+        <v>323</v>
       </c>
       <c r="G190" s="4"/>
-      <c r="H190" s="8" t="s">
-        <v>498</v>
-      </c>
+      <c r="H190" s="4"/>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
@@ -8688,23 +8740,21 @@
         <v>484</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>500</v>
-      </c>
-      <c r="E191" s="8" t="s">
-        <v>23</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="E191" s="4"/>
       <c r="F191" s="8" t="s">
-        <v>23</v>
+        <v>494</v>
       </c>
       <c r="G191" s="4"/>
       <c r="H191" s="8" t="s">
-        <v>23</v>
+        <v>494</v>
       </c>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
@@ -8716,20 +8766,26 @@
       <c r="A192" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="B192" s="4"/>
+      <c r="B192" s="5" t="s">
+        <v>495</v>
+      </c>
       <c r="C192" s="5" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="E192" s="4"/>
-      <c r="F192" s="4"/>
+        <v>497</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>498</v>
+      </c>
       <c r="G192" s="4"/>
-      <c r="H192" s="4"/>
-      <c r="I192" s="8" t="s">
-        <v>503</v>
-      </c>
+      <c r="H192" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="I192" s="4"/>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
       <c r="L192" s="4"/>
@@ -8737,24 +8793,28 @@
     </row>
     <row r="193" spans="1:13" ht="13.5" customHeight="1">
       <c r="A193" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="B193" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="C193" s="7" t="s">
-        <v>506</v>
+        <v>484</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>499</v>
       </c>
       <c r="D193" s="15" t="s">
-        <v>507</v>
-      </c>
-      <c r="E193" s="4"/>
-      <c r="F193" s="4"/>
+        <v>500</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="G193" s="4"/>
-      <c r="H193" s="4"/>
-      <c r="I193" s="10" t="s">
-        <v>508</v>
-      </c>
+      <c r="H193" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I193" s="4"/>
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
       <c r="L193" s="4"/>
@@ -8762,26 +8822,22 @@
     </row>
     <row r="194" spans="1:13" ht="13.5" customHeight="1">
       <c r="A194" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="C194" s="7" t="s">
-        <v>509</v>
+        <v>484</v>
+      </c>
+      <c r="B194" s="4"/>
+      <c r="C194" s="5" t="s">
+        <v>501</v>
       </c>
       <c r="D194" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="E194" s="8" t="s">
-        <v>320</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="E194" s="4"/>
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
-      <c r="H194" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="I194" s="4"/>
+      <c r="H194" s="4"/>
+      <c r="I194" s="8" t="s">
+        <v>503</v>
+      </c>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
       <c r="L194" s="4"/>
@@ -8792,20 +8848,20 @@
         <v>504</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="D195" s="29" t="s">
-        <v>513</v>
-      </c>
-      <c r="E195" s="30"/>
-      <c r="F195" s="30"/>
-      <c r="G195" s="30"/>
-      <c r="H195" s="31"/>
+        <v>506</v>
+      </c>
+      <c r="D195" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4"/>
+      <c r="G195" s="4"/>
+      <c r="H195" s="4"/>
       <c r="I195" s="10" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
@@ -8817,21 +8873,21 @@
         <v>504</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>517</v>
+        <v>320</v>
       </c>
       <c r="F196" s="4"/>
       <c r="G196" s="4"/>
       <c r="H196" s="8" t="s">
-        <v>517</v>
+        <v>320</v>
       </c>
       <c r="I196" s="4"/>
       <c r="J196" s="4"/>
@@ -8844,21 +8900,21 @@
         <v>504</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="D197" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="E197" s="4"/>
-      <c r="F197" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="G197" s="4"/>
-      <c r="H197" s="4"/>
-      <c r="I197" s="4"/>
+        <v>512</v>
+      </c>
+      <c r="D197" s="29" t="s">
+        <v>513</v>
+      </c>
+      <c r="E197" s="30"/>
+      <c r="F197" s="30"/>
+      <c r="G197" s="30"/>
+      <c r="H197" s="31"/>
+      <c r="I197" s="10" t="s">
+        <v>514</v>
+      </c>
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
       <c r="L197" s="4"/>
@@ -8869,20 +8925,22 @@
         <v>504</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>523</v>
-      </c>
-      <c r="E198" s="4"/>
-      <c r="F198" s="8" t="s">
-        <v>524</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F198" s="4"/>
       <c r="G198" s="4"/>
-      <c r="H198" s="4"/>
+      <c r="H198" s="8" t="s">
+        <v>517</v>
+      </c>
       <c r="I198" s="4"/>
       <c r="J198" s="4"/>
       <c r="K198" s="4"/>
@@ -8897,14 +8955,14 @@
         <v>518</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="E199" s="4"/>
       <c r="F199" s="8" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="G199" s="4"/>
       <c r="H199" s="4"/>
@@ -8922,14 +8980,14 @@
         <v>518</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="8" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
@@ -8947,14 +9005,14 @@
         <v>518</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="D201" s="15" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E201" s="4"/>
       <c r="F201" s="8" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
@@ -8972,14 +9030,14 @@
         <v>518</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E202" s="4"/>
       <c r="F202" s="8" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
@@ -8997,14 +9055,14 @@
         <v>518</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="8" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
@@ -9022,14 +9080,14 @@
         <v>518</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="8" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G204" s="4"/>
       <c r="H204" s="4"/>
@@ -9047,14 +9105,14 @@
         <v>518</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="D205" s="15" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="8" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
@@ -9072,14 +9130,14 @@
         <v>518</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="8" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
@@ -9097,14 +9155,14 @@
         <v>518</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="8" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
@@ -9122,14 +9180,14 @@
         <v>518</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="8" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
@@ -9147,14 +9205,14 @@
         <v>518</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="8" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
@@ -9168,20 +9226,22 @@
       <c r="A210" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="B210" s="7"/>
+      <c r="B210" s="7" t="s">
+        <v>518</v>
+      </c>
       <c r="C210" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="D210" s="45" t="s">
-        <v>642</v>
+        <v>552</v>
+      </c>
+      <c r="D210" s="15" t="s">
+        <v>553</v>
       </c>
       <c r="E210" s="4"/>
-      <c r="F210" s="8"/>
+      <c r="F210" s="8" t="s">
+        <v>554</v>
+      </c>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
-      <c r="I210" s="4" t="s">
-        <v>643</v>
-      </c>
+      <c r="I210" s="4"/>
       <c r="J210" s="4"/>
       <c r="K210" s="4"/>
       <c r="L210" s="4"/>
@@ -9192,21 +9252,21 @@
         <v>504</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>558</v>
+        <v>518</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E211" s="4"/>
-      <c r="F211" s="4"/>
+      <c r="F211" s="8" t="s">
+        <v>557</v>
+      </c>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
-      <c r="I211" s="23" t="s">
-        <v>561</v>
-      </c>
+      <c r="I211" s="4"/>
       <c r="J211" s="4"/>
       <c r="K211" s="4"/>
       <c r="L211" s="4"/>
@@ -9216,21 +9276,19 @@
       <c r="A212" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="B212" s="7" t="s">
-        <v>562</v>
-      </c>
+      <c r="B212" s="7"/>
       <c r="C212" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="D212" s="15" t="s">
-        <v>564</v>
+        <v>641</v>
+      </c>
+      <c r="D212" s="45" t="s">
+        <v>642</v>
       </c>
       <c r="E212" s="4"/>
-      <c r="F212" s="4"/>
+      <c r="F212" s="8"/>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
-      <c r="I212" s="23" t="s">
-        <v>565</v>
+      <c r="I212" s="4" t="s">
+        <v>643</v>
       </c>
       <c r="J212" s="4"/>
       <c r="K212" s="4"/>
@@ -9242,20 +9300,20 @@
         <v>504</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="E213" s="4"/>
       <c r="F213" s="4"/>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
       <c r="I213" s="23" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
@@ -9270,17 +9328,17 @@
         <v>562</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
-      <c r="I214" s="8" t="s">
-        <v>571</v>
+      <c r="I214" s="23" t="s">
+        <v>565</v>
       </c>
       <c r="J214" s="4"/>
       <c r="K214" s="4"/>
@@ -9289,21 +9347,23 @@
     </row>
     <row r="215" spans="1:13" ht="13.5" customHeight="1">
       <c r="A215" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="B215" s="4"/>
+        <v>504</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>562</v>
+      </c>
       <c r="C215" s="7" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="4"/>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
-      <c r="I215" s="8" t="s">
-        <v>575</v>
+      <c r="I215" s="23" t="s">
+        <v>568</v>
       </c>
       <c r="J215" s="4"/>
       <c r="K215" s="4"/>
@@ -9312,48 +9372,46 @@
     </row>
     <row r="216" spans="1:13" ht="13.5" customHeight="1">
       <c r="A216" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="B216" s="4"/>
+        <v>504</v>
+      </c>
+      <c r="B216" s="7" t="s">
+        <v>562</v>
+      </c>
       <c r="C216" s="7" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="D216" s="15" t="s">
-        <v>577</v>
-      </c>
-      <c r="E216" s="23" t="s">
-        <v>578</v>
-      </c>
-      <c r="F216" s="23" t="s">
-        <v>578</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="E216" s="4"/>
+      <c r="F216" s="4"/>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
-      <c r="I216" s="4"/>
+      <c r="I216" s="8" t="s">
+        <v>571</v>
+      </c>
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
       <c r="L216" s="4"/>
       <c r="M216" s="5"/>
     </row>
     <row r="217" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A217" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="B217" s="24" t="s">
-        <v>580</v>
-      </c>
-      <c r="C217" s="32" t="s">
-        <v>580</v>
-      </c>
-      <c r="D217" s="33" t="s">
-        <v>581</v>
+      <c r="A217" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="B217" s="4"/>
+      <c r="C217" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="D217" s="15" t="s">
+        <v>574</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
-      <c r="I217" s="23" t="s">
-        <v>582</v>
+      <c r="I217" s="8" t="s">
+        <v>575</v>
       </c>
       <c r="J217" s="4"/>
       <c r="K217" s="4"/>
@@ -9361,23 +9419,21 @@
       <c r="M217" s="5"/>
     </row>
     <row r="218" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A218" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="B218" s="24" t="s">
-        <v>580</v>
-      </c>
-      <c r="C218" s="32" t="s">
-        <v>583</v>
+      <c r="A218" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="B218" s="4"/>
+      <c r="C218" s="7" t="s">
+        <v>576</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="E218" s="23" t="s">
-        <v>266</v>
+        <v>578</v>
       </c>
       <c r="F218" s="23" t="s">
-        <v>266</v>
+        <v>578</v>
       </c>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
@@ -9391,19 +9447,21 @@
       <c r="A219" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="B219" s="4"/>
-      <c r="C219" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="D219" s="15" t="s">
-        <v>586</v>
+      <c r="B219" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="C219" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="D219" s="33" t="s">
+        <v>581</v>
       </c>
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
-      <c r="I219" s="8" t="s">
-        <v>587</v>
+      <c r="I219" s="23" t="s">
+        <v>582</v>
       </c>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
@@ -9414,20 +9472,24 @@
       <c r="A220" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="B220" s="4"/>
-      <c r="C220" s="7" t="s">
-        <v>588</v>
+      <c r="B220" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="C220" s="32" t="s">
+        <v>583</v>
       </c>
       <c r="D220" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="E220" s="4"/>
-      <c r="F220" s="4"/>
+        <v>584</v>
+      </c>
+      <c r="E220" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F220" s="23" t="s">
+        <v>266</v>
+      </c>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
-      <c r="I220" s="10" t="s">
-        <v>590</v>
-      </c>
+      <c r="I220" s="4"/>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
       <c r="L220" s="4"/>
@@ -9438,18 +9500,18 @@
         <v>579</v>
       </c>
       <c r="B221" s="4"/>
-      <c r="C221" s="7" t="s">
-        <v>591</v>
+      <c r="C221" s="5" t="s">
+        <v>585</v>
       </c>
       <c r="D221" s="15" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
       <c r="I221" s="8" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
@@ -9461,18 +9523,18 @@
         <v>579</v>
       </c>
       <c r="B222" s="4"/>
-      <c r="C222" s="5" t="s">
-        <v>594</v>
+      <c r="C222" s="7" t="s">
+        <v>588</v>
       </c>
       <c r="D222" s="15" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
       <c r="H222" s="4"/>
-      <c r="I222" s="8" t="s">
-        <v>596</v>
+      <c r="I222" s="10" t="s">
+        <v>590</v>
       </c>
       <c r="J222" s="4"/>
       <c r="K222" s="4"/>
@@ -9484,41 +9546,41 @@
         <v>579</v>
       </c>
       <c r="B223" s="4"/>
-      <c r="C223" s="5" t="s">
-        <v>597</v>
+      <c r="C223" s="7" t="s">
+        <v>591</v>
       </c>
       <c r="D223" s="15" t="s">
-        <v>598</v>
-      </c>
-      <c r="E223" s="8" t="s">
-        <v>599</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="E223" s="4"/>
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
-      <c r="I223" s="4"/>
+      <c r="I223" s="8" t="s">
+        <v>593</v>
+      </c>
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
       <c r="L223" s="4"/>
       <c r="M223" s="5"/>
     </row>
     <row r="224" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A224" s="7" t="s">
-        <v>600</v>
+      <c r="A224" s="5" t="s">
+        <v>579</v>
       </c>
       <c r="B224" s="4"/>
-      <c r="C224" s="22" t="s">
-        <v>601</v>
-      </c>
-      <c r="D224" s="33" t="s">
-        <v>602</v>
-      </c>
-      <c r="E224" s="5"/>
+      <c r="C224" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="D224" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="E224" s="4"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
-      <c r="I224" s="23" t="s">
-        <v>603</v>
+      <c r="I224" s="8" t="s">
+        <v>596</v>
       </c>
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
@@ -9526,23 +9588,23 @@
       <c r="M224" s="5"/>
     </row>
     <row r="225" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A225" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="B225" s="3"/>
-      <c r="C225" s="34" t="s">
-        <v>604</v>
-      </c>
-      <c r="D225" s="35" t="s">
-        <v>605</v>
-      </c>
-      <c r="E225" s="3"/>
+      <c r="A225" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="B225" s="4"/>
+      <c r="C225" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="D225" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="E225" s="8" t="s">
+        <v>599</v>
+      </c>
       <c r="F225" s="4"/>
       <c r="G225" s="4"/>
-      <c r="H225" s="3"/>
-      <c r="I225" s="8" t="s">
-        <v>606</v>
-      </c>
+      <c r="H225" s="4"/>
+      <c r="I225" s="4"/>
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
       <c r="L225" s="4"/>
@@ -9552,19 +9614,19 @@
       <c r="A226" s="7" t="s">
         <v>600</v>
       </c>
-      <c r="B226" s="3"/>
-      <c r="C226" s="7" t="s">
-        <v>607</v>
-      </c>
-      <c r="D226" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="E226" s="3"/>
+      <c r="B226" s="4"/>
+      <c r="C226" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="D226" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="E226" s="5"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
-      <c r="H226" s="3"/>
-      <c r="I226" s="8" t="s">
-        <v>609</v>
+      <c r="H226" s="4"/>
+      <c r="I226" s="23" t="s">
+        <v>603</v>
       </c>
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
@@ -9576,18 +9638,18 @@
         <v>600</v>
       </c>
       <c r="B227" s="3"/>
-      <c r="C227" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="D227" s="9" t="s">
-        <v>611</v>
+      <c r="C227" s="34" t="s">
+        <v>604</v>
+      </c>
+      <c r="D227" s="35" t="s">
+        <v>605</v>
       </c>
       <c r="E227" s="3"/>
       <c r="F227" s="4"/>
       <c r="G227" s="4"/>
       <c r="H227" s="3"/>
       <c r="I227" s="8" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="J227" s="4"/>
       <c r="K227" s="4"/>
@@ -9596,21 +9658,21 @@
     </row>
     <row r="228" spans="1:13" ht="13.5" customHeight="1">
       <c r="A228" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="B228" s="4"/>
-      <c r="C228" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="D228" s="15" t="s">
-        <v>615</v>
-      </c>
-      <c r="E228" s="4"/>
+        <v>600</v>
+      </c>
+      <c r="B228" s="3"/>
+      <c r="C228" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="D228" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="E228" s="3"/>
       <c r="F228" s="4"/>
       <c r="G228" s="4"/>
-      <c r="H228" s="4"/>
+      <c r="H228" s="3"/>
       <c r="I228" s="8" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="J228" s="4"/>
       <c r="K228" s="4"/>
@@ -9619,21 +9681,21 @@
     </row>
     <row r="229" spans="1:13" ht="13.5" customHeight="1">
       <c r="A229" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="B229" s="4"/>
-      <c r="C229" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="D229" s="36" t="s">
-        <v>618</v>
-      </c>
-      <c r="E229" s="4"/>
+        <v>600</v>
+      </c>
+      <c r="B229" s="3"/>
+      <c r="C229" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="E229" s="3"/>
       <c r="F229" s="4"/>
       <c r="G229" s="4"/>
-      <c r="H229" s="4"/>
+      <c r="H229" s="3"/>
       <c r="I229" s="8" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
@@ -9641,22 +9703,22 @@
       <c r="M229" s="5"/>
     </row>
     <row r="230" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A230" s="37" t="s">
-        <v>620</v>
-      </c>
-      <c r="B230" s="38"/>
-      <c r="C230" s="39" t="s">
-        <v>621</v>
-      </c>
-      <c r="D230" s="40" t="s">
-        <v>622</v>
-      </c>
-      <c r="E230" s="41"/>
+      <c r="A230" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B230" s="4"/>
+      <c r="C230" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="D230" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="E230" s="4"/>
       <c r="F230" s="4"/>
       <c r="G230" s="4"/>
       <c r="H230" s="4"/>
       <c r="I230" s="8" t="s">
-        <v>269</v>
+        <v>616</v>
       </c>
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
@@ -9664,22 +9726,22 @@
       <c r="M230" s="5"/>
     </row>
     <row r="231" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A231" s="37" t="s">
-        <v>620</v>
-      </c>
-      <c r="B231" s="24"/>
-      <c r="C231" s="42" t="s">
-        <v>255</v>
-      </c>
-      <c r="D231" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="E231" s="3"/>
-      <c r="F231" s="20"/>
-      <c r="G231" s="20"/>
-      <c r="H231" s="3"/>
+      <c r="A231" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B231" s="4"/>
+      <c r="C231" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="D231" s="36" t="s">
+        <v>618</v>
+      </c>
+      <c r="E231" s="4"/>
+      <c r="F231" s="4"/>
+      <c r="G231" s="4"/>
+      <c r="H231" s="4"/>
       <c r="I231" s="8" t="s">
-        <v>257</v>
+        <v>619</v>
       </c>
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
@@ -9690,19 +9752,19 @@
       <c r="A232" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B232" s="24"/>
+      <c r="B232" s="38"/>
       <c r="C232" s="39" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D232" s="40" t="s">
-        <v>624</v>
-      </c>
-      <c r="E232" s="4"/>
+        <v>622</v>
+      </c>
+      <c r="E232" s="41"/>
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
       <c r="H232" s="4"/>
-      <c r="I232" s="23" t="s">
-        <v>582</v>
+      <c r="I232" s="8" t="s">
+        <v>269</v>
       </c>
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
@@ -9713,19 +9775,19 @@
       <c r="A233" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B233" s="38"/>
-      <c r="C233" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="D233" s="44" t="s">
-        <v>232</v>
+      <c r="B233" s="24"/>
+      <c r="C233" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>256</v>
       </c>
       <c r="E233" s="3"/>
       <c r="F233" s="20"/>
       <c r="G233" s="20"/>
       <c r="H233" s="3"/>
       <c r="I233" s="8" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
@@ -9736,19 +9798,19 @@
       <c r="A234" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B234" s="38"/>
-      <c r="C234" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D234" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="E234" s="3"/>
-      <c r="F234" s="20"/>
-      <c r="G234" s="20"/>
-      <c r="H234" s="3"/>
-      <c r="I234" s="8" t="s">
-        <v>248</v>
+      <c r="B234" s="24"/>
+      <c r="C234" s="39" t="s">
+        <v>623</v>
+      </c>
+      <c r="D234" s="40" t="s">
+        <v>624</v>
+      </c>
+      <c r="E234" s="4"/>
+      <c r="F234" s="4"/>
+      <c r="G234" s="4"/>
+      <c r="H234" s="4"/>
+      <c r="I234" s="23" t="s">
+        <v>582</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
@@ -9759,21 +9821,19 @@
       <c r="A235" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B235" s="38" t="s">
-        <v>625</v>
-      </c>
-      <c r="C235" s="39" t="s">
-        <v>626</v>
-      </c>
-      <c r="D235" s="40" t="s">
-        <v>627</v>
-      </c>
-      <c r="E235" s="4"/>
-      <c r="F235" s="4"/>
-      <c r="G235" s="4"/>
-      <c r="H235" s="4"/>
-      <c r="I235" s="23" t="s">
-        <v>628</v>
+      <c r="B235" s="38"/>
+      <c r="C235" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D235" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="E235" s="3"/>
+      <c r="F235" s="20"/>
+      <c r="G235" s="20"/>
+      <c r="H235" s="3"/>
+      <c r="I235" s="8" t="s">
+        <v>224</v>
       </c>
       <c r="J235" s="4"/>
       <c r="K235" s="4"/>
@@ -9784,21 +9844,19 @@
       <c r="A236" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B236" s="38" t="s">
-        <v>625</v>
-      </c>
-      <c r="C236" s="39" t="s">
-        <v>629</v>
-      </c>
-      <c r="D236" s="40" t="s">
-        <v>630</v>
-      </c>
-      <c r="E236" s="4"/>
-      <c r="F236" s="4"/>
-      <c r="G236" s="4"/>
-      <c r="H236" s="4"/>
-      <c r="I236" s="23" t="s">
-        <v>631</v>
+      <c r="B236" s="38"/>
+      <c r="C236" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D236" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E236" s="3"/>
+      <c r="F236" s="20"/>
+      <c r="G236" s="20"/>
+      <c r="H236" s="3"/>
+      <c r="I236" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="J236" s="4"/>
       <c r="K236" s="4"/>
@@ -9813,17 +9871,17 @@
         <v>625</v>
       </c>
       <c r="C237" s="39" t="s">
-        <v>228</v>
+        <v>626</v>
       </c>
       <c r="D237" s="40" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="E237" s="4"/>
       <c r="F237" s="4"/>
       <c r="G237" s="4"/>
       <c r="H237" s="4"/>
       <c r="I237" s="23" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="J237" s="4"/>
       <c r="K237" s="4"/>
@@ -9831,30 +9889,50 @@
       <c r="M237" s="5"/>
     </row>
     <row r="238" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A238" s="4"/>
-      <c r="B238" s="4"/>
-      <c r="C238" s="4"/>
-      <c r="D238" s="4"/>
+      <c r="A238" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="B238" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="C238" s="39" t="s">
+        <v>629</v>
+      </c>
+      <c r="D238" s="40" t="s">
+        <v>630</v>
+      </c>
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
-      <c r="I238" s="4"/>
+      <c r="I238" s="23" t="s">
+        <v>631</v>
+      </c>
       <c r="J238" s="4"/>
       <c r="K238" s="4"/>
       <c r="L238" s="4"/>
       <c r="M238" s="5"/>
     </row>
     <row r="239" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A239" s="4"/>
-      <c r="B239" s="4"/>
-      <c r="C239" s="4"/>
-      <c r="D239" s="4"/>
+      <c r="A239" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="B239" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="C239" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="D239" s="40" t="s">
+        <v>632</v>
+      </c>
       <c r="E239" s="4"/>
       <c r="F239" s="4"/>
       <c r="G239" s="4"/>
       <c r="H239" s="4"/>
-      <c r="I239" s="4"/>
+      <c r="I239" s="23" t="s">
+        <v>633</v>
+      </c>
       <c r="J239" s="4"/>
       <c r="K239" s="4"/>
       <c r="L239" s="4"/>
@@ -12635,8 +12713,36 @@
       <c r="L424" s="4"/>
       <c r="M424" s="5"/>
     </row>
-    <row r="425" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="426" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="425" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A425" s="4"/>
+      <c r="B425" s="4"/>
+      <c r="C425" s="4"/>
+      <c r="D425" s="4"/>
+      <c r="E425" s="4"/>
+      <c r="F425" s="4"/>
+      <c r="G425" s="4"/>
+      <c r="H425" s="4"/>
+      <c r="I425" s="4"/>
+      <c r="J425" s="4"/>
+      <c r="K425" s="4"/>
+      <c r="L425" s="4"/>
+      <c r="M425" s="5"/>
+    </row>
+    <row r="426" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A426" s="4"/>
+      <c r="B426" s="4"/>
+      <c r="C426" s="4"/>
+      <c r="D426" s="4"/>
+      <c r="E426" s="4"/>
+      <c r="F426" s="4"/>
+      <c r="G426" s="4"/>
+      <c r="H426" s="4"/>
+      <c r="I426" s="4"/>
+      <c r="J426" s="4"/>
+      <c r="K426" s="4"/>
+      <c r="L426" s="4"/>
+      <c r="M426" s="5"/>
+    </row>
     <row r="427" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="428" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="429" spans="1:13" ht="15.75" customHeight="1"/>
@@ -13232,6 +13338,8 @@
     <row r="1019" ht="15.75" customHeight="1"/>
     <row r="1020" ht="15.75" customHeight="1"/>
     <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
+    <row r="1023" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="15"/>
   <hyperlinks>
@@ -13388,64 +13496,66 @@
     <hyperlink ref="D174" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
     <hyperlink ref="D175" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
     <hyperlink ref="D176" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="D177" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="D178" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="D179" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="D180" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="D181" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="D182" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="D184" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="D185" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D186" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="D187" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D188" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="D189" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D190" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D191" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D192" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="D193" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D194" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="D195" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D196" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="D197" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D198" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D199" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D200" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D201" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D202" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="D203" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D204" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="D205" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D206" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="D207" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D208" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="D209" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D211" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D212" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D213" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D214" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D215" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D216" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D217" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D219" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D220" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D221" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D222" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D223" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D224" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="D225" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D226" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="D227" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D228" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="D229" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D231" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="D233" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D234" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="D179" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="D180" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="D181" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="D182" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="D183" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="D184" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="D186" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="D187" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="D188" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="D189" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="D190" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="D191" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="D192" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="D193" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="D194" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="D195" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="D196" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="D197" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="D198" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="D199" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="D200" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="D201" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="D202" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="D203" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="D204" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="D205" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="D206" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="D207" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="D208" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="D209" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="D210" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="D211" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="D213" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D214" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D215" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D216" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D217" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D218" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D219" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D221" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D222" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D223" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D224" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D225" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D226" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="D227" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="D228" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="D229" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="D230" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="D231" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="D233" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="D235" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="D236" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
     <hyperlink ref="D16" r:id="rId207" xr:uid="{101A33D7-B7BA-422E-B2FC-342D5148D1EA}"/>
-    <hyperlink ref="D210" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
+    <hyperlink ref="D212" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
     <hyperlink ref="D77" r:id="rId209" xr:uid="{15E62A8C-2F55-4EC5-B29A-D16518F2E4D9}"/>
     <hyperlink ref="D76" r:id="rId210" xr:uid="{FC2D964E-B283-4703-AAB9-28EC36520D76}"/>
     <hyperlink ref="D17" r:id="rId211" xr:uid="{BAFD46EC-62AB-41E1-B82A-03A62E913A64}"/>
+    <hyperlink ref="D178" r:id="rId212" xr:uid="{1B2883BA-7428-4C3B-8B0A-0E84AA25F727}"/>
+    <hyperlink ref="D177" r:id="rId213" xr:uid="{94880ED8-4B43-4BE4-B733-30DFCED08C71}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\vm22flo01\DownloadFiles\スマートシティ課\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431F92A0-012B-4E43-8734-6B62ACE82309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC863E1-1121-4536-82E1-66BA301D13B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="666">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -3280,6 +3280,27 @@
   </si>
   <si>
     <t>#33cccc</t>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%83%93%E3%83%BC%E3%83%81%E3%82%AF%E3%83%AA%E3%83%BC%E3%83%B3%E5%A4%A7%E4%BD%9C%E6%88%A6/tiles.json</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>ビーチクリーン大作戦（海岸清掃）</t>
+    <rPh sb="7" eb="10">
+      <t>ダイサクセン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カイガン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイソウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>litter-pickup</t>
+    <phoneticPr fontId="15"/>
   </si>
 </sst>
 </file>
@@ -3543,7 +3564,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3648,6 +3669,7 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -3913,12 +3935,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M1023"/>
+  <dimension ref="A1:M1024"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="25.21875" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="32.109375" customWidth="1"/>
     <col min="4" max="4" width="153.109375" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" customWidth="1"/>
     <col min="6" max="7" width="19.88671875" customWidth="1"/>
@@ -8660,21 +8682,19 @@
       <c r="A188" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="B188" s="4"/>
-      <c r="C188" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="D188" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="E188" s="8" t="s">
-        <v>320</v>
-      </c>
+      <c r="B188" s="22"/>
+      <c r="C188" s="22" t="s">
+        <v>664</v>
+      </c>
+      <c r="D188" s="46" t="s">
+        <v>663</v>
+      </c>
+      <c r="E188" s="5"/>
       <c r="F188" s="4"/>
       <c r="G188" s="4"/>
-      <c r="H188" s="5"/>
-      <c r="I188" s="23" t="s">
-        <v>483</v>
+      <c r="H188" s="8"/>
+      <c r="I188" s="4" t="s">
+        <v>665</v>
       </c>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
@@ -8682,27 +8702,25 @@
       <c r="M188" s="5"/>
     </row>
     <row r="189" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A189" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>485</v>
-      </c>
+      <c r="A189" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B189" s="4"/>
       <c r="C189" s="5" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="E189" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="F189" s="8" t="s">
-        <v>323</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="F189" s="4"/>
       <c r="G189" s="4"/>
-      <c r="H189" s="4"/>
-      <c r="I189" s="4"/>
+      <c r="H189" s="5"/>
+      <c r="I189" s="23" t="s">
+        <v>483</v>
+      </c>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
       <c r="L189" s="4"/>
@@ -8716,13 +8734,13 @@
         <v>485</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>323</v>
@@ -8740,22 +8758,22 @@
         <v>484</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>493</v>
-      </c>
-      <c r="E191" s="4"/>
+        <v>490</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>491</v>
+      </c>
       <c r="F191" s="8" t="s">
-        <v>494</v>
+        <v>323</v>
       </c>
       <c r="G191" s="4"/>
-      <c r="H191" s="8" t="s">
-        <v>494</v>
-      </c>
+      <c r="H191" s="4"/>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
@@ -8767,23 +8785,21 @@
         <v>484</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>497</v>
-      </c>
-      <c r="E192" s="8" t="s">
-        <v>498</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="E192" s="4"/>
       <c r="F192" s="8" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G192" s="4"/>
       <c r="H192" s="8" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="I192" s="4"/>
       <c r="J192" s="4"/>
@@ -8799,20 +8815,20 @@
         <v>495</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D193" s="15" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>23</v>
+        <v>498</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>23</v>
+        <v>498</v>
       </c>
       <c r="G193" s="4"/>
       <c r="H193" s="8" t="s">
-        <v>23</v>
+        <v>498</v>
       </c>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
@@ -8824,20 +8840,26 @@
       <c r="A194" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="B194" s="4"/>
+      <c r="B194" s="5" t="s">
+        <v>495</v>
+      </c>
       <c r="C194" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D194" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="E194" s="4"/>
-      <c r="F194" s="4"/>
+        <v>500</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="G194" s="4"/>
-      <c r="H194" s="4"/>
-      <c r="I194" s="8" t="s">
-        <v>503</v>
-      </c>
+      <c r="H194" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I194" s="4"/>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
       <c r="L194" s="4"/>
@@ -8845,23 +8867,21 @@
     </row>
     <row r="195" spans="1:13" ht="13.5" customHeight="1">
       <c r="A195" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="B195" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="C195" s="7" t="s">
-        <v>506</v>
+        <v>484</v>
+      </c>
+      <c r="B195" s="4"/>
+      <c r="C195" s="5" t="s">
+        <v>501</v>
       </c>
       <c r="D195" s="15" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="E195" s="4"/>
       <c r="F195" s="4"/>
       <c r="G195" s="4"/>
       <c r="H195" s="4"/>
-      <c r="I195" s="10" t="s">
-        <v>508</v>
+      <c r="I195" s="8" t="s">
+        <v>503</v>
       </c>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
@@ -8876,20 +8896,18 @@
         <v>505</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="E196" s="8" t="s">
-        <v>320</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="E196" s="4"/>
       <c r="F196" s="4"/>
       <c r="G196" s="4"/>
-      <c r="H196" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="I196" s="4"/>
+      <c r="H196" s="4"/>
+      <c r="I196" s="10" t="s">
+        <v>508</v>
+      </c>
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
       <c r="L196" s="4"/>
@@ -8900,21 +8918,23 @@
         <v>504</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="D197" s="29" t="s">
-        <v>513</v>
-      </c>
-      <c r="E197" s="30"/>
-      <c r="F197" s="30"/>
-      <c r="G197" s="30"/>
-      <c r="H197" s="31"/>
-      <c r="I197" s="10" t="s">
-        <v>514</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="D197" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="F197" s="4"/>
+      <c r="G197" s="4"/>
+      <c r="H197" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="I197" s="4"/>
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
       <c r="L197" s="4"/>
@@ -8928,20 +8948,18 @@
         <v>511</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="D198" s="15" t="s">
-        <v>516</v>
-      </c>
-      <c r="E198" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="F198" s="4"/>
-      <c r="G198" s="4"/>
-      <c r="H198" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="I198" s="4"/>
+        <v>512</v>
+      </c>
+      <c r="D198" s="29" t="s">
+        <v>513</v>
+      </c>
+      <c r="E198" s="30"/>
+      <c r="F198" s="30"/>
+      <c r="G198" s="30"/>
+      <c r="H198" s="31"/>
+      <c r="I198" s="10" t="s">
+        <v>514</v>
+      </c>
       <c r="J198" s="4"/>
       <c r="K198" s="4"/>
       <c r="L198" s="4"/>
@@ -8952,20 +8970,22 @@
         <v>504</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="E199" s="4"/>
-      <c r="F199" s="8" t="s">
-        <v>521</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F199" s="4"/>
       <c r="G199" s="4"/>
-      <c r="H199" s="4"/>
+      <c r="H199" s="8" t="s">
+        <v>517</v>
+      </c>
       <c r="I199" s="4"/>
       <c r="J199" s="4"/>
       <c r="K199" s="4"/>
@@ -8980,14 +9000,14 @@
         <v>518</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E200" s="4"/>
       <c r="F200" s="8" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="G200" s="4"/>
       <c r="H200" s="4"/>
@@ -9005,14 +9025,14 @@
         <v>518</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D201" s="15" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E201" s="4"/>
       <c r="F201" s="8" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G201" s="4"/>
       <c r="H201" s="4"/>
@@ -9030,14 +9050,14 @@
         <v>518</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E202" s="4"/>
       <c r="F202" s="8" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="G202" s="4"/>
       <c r="H202" s="4"/>
@@ -9055,14 +9075,14 @@
         <v>518</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="8" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
@@ -9080,14 +9100,14 @@
         <v>518</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="8" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="G204" s="4"/>
       <c r="H204" s="4"/>
@@ -9105,14 +9125,14 @@
         <v>518</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D205" s="15" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="8" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
@@ -9130,14 +9150,14 @@
         <v>518</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="8" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
@@ -9155,14 +9175,14 @@
         <v>518</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="8" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
@@ -9180,14 +9200,14 @@
         <v>518</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
@@ -9205,14 +9225,14 @@
         <v>518</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="8" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
@@ -9230,14 +9250,14 @@
         <v>518</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D210" s="15" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="8" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
@@ -9255,14 +9275,14 @@
         <v>518</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="8" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
@@ -9276,20 +9296,22 @@
       <c r="A212" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="B212" s="7"/>
+      <c r="B212" s="7" t="s">
+        <v>518</v>
+      </c>
       <c r="C212" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="D212" s="45" t="s">
-        <v>642</v>
+        <v>555</v>
+      </c>
+      <c r="D212" s="15" t="s">
+        <v>556</v>
       </c>
       <c r="E212" s="4"/>
-      <c r="F212" s="8"/>
+      <c r="F212" s="8" t="s">
+        <v>557</v>
+      </c>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
-      <c r="I212" s="4" t="s">
-        <v>643</v>
-      </c>
+      <c r="I212" s="4"/>
       <c r="J212" s="4"/>
       <c r="K212" s="4"/>
       <c r="L212" s="4"/>
@@ -9299,21 +9321,19 @@
       <c r="A213" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="B213" s="7" t="s">
-        <v>558</v>
-      </c>
+      <c r="B213" s="7"/>
       <c r="C213" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="D213" s="15" t="s">
-        <v>560</v>
+        <v>641</v>
+      </c>
+      <c r="D213" s="45" t="s">
+        <v>642</v>
       </c>
       <c r="E213" s="4"/>
-      <c r="F213" s="4"/>
+      <c r="F213" s="8"/>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
-      <c r="I213" s="23" t="s">
-        <v>561</v>
+      <c r="I213" s="4" t="s">
+        <v>643</v>
       </c>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
@@ -9325,20 +9345,20 @@
         <v>504</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
       <c r="I214" s="23" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="J214" s="4"/>
       <c r="K214" s="4"/>
@@ -9353,17 +9373,17 @@
         <v>562</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E215" s="4"/>
       <c r="F215" s="4"/>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
       <c r="I215" s="23" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="J215" s="4"/>
       <c r="K215" s="4"/>
@@ -9378,17 +9398,17 @@
         <v>562</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D216" s="15" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
-      <c r="I216" s="8" t="s">
-        <v>571</v>
+      <c r="I216" s="23" t="s">
+        <v>568</v>
       </c>
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
@@ -9397,21 +9417,23 @@
     </row>
     <row r="217" spans="1:13" ht="13.5" customHeight="1">
       <c r="A217" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="B217" s="4"/>
+        <v>504</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>562</v>
+      </c>
       <c r="C217" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
       <c r="I217" s="8" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="J217" s="4"/>
       <c r="K217" s="4"/>
@@ -9424,45 +9446,43 @@
       </c>
       <c r="B218" s="4"/>
       <c r="C218" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>577</v>
-      </c>
-      <c r="E218" s="23" t="s">
-        <v>578</v>
-      </c>
-      <c r="F218" s="23" t="s">
-        <v>578</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="E218" s="4"/>
+      <c r="F218" s="4"/>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
-      <c r="I218" s="4"/>
+      <c r="I218" s="8" t="s">
+        <v>575</v>
+      </c>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
       <c r="L218" s="4"/>
       <c r="M218" s="5"/>
     </row>
     <row r="219" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A219" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="B219" s="24" t="s">
-        <v>580</v>
-      </c>
-      <c r="C219" s="32" t="s">
-        <v>580</v>
-      </c>
-      <c r="D219" s="33" t="s">
-        <v>581</v>
-      </c>
-      <c r="E219" s="4"/>
-      <c r="F219" s="4"/>
+      <c r="A219" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="B219" s="4"/>
+      <c r="C219" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="D219" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="E219" s="23" t="s">
+        <v>578</v>
+      </c>
+      <c r="F219" s="23" t="s">
+        <v>578</v>
+      </c>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
-      <c r="I219" s="23" t="s">
-        <v>582</v>
-      </c>
+      <c r="I219" s="4"/>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
       <c r="L219" s="4"/>
@@ -9476,20 +9496,18 @@
         <v>580</v>
       </c>
       <c r="C220" s="32" t="s">
-        <v>583</v>
-      </c>
-      <c r="D220" s="15" t="s">
-        <v>584</v>
-      </c>
-      <c r="E220" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="F220" s="23" t="s">
-        <v>266</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="D220" s="33" t="s">
+        <v>581</v>
+      </c>
+      <c r="E220" s="4"/>
+      <c r="F220" s="4"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
-      <c r="I220" s="4"/>
+      <c r="I220" s="23" t="s">
+        <v>582</v>
+      </c>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
       <c r="L220" s="4"/>
@@ -9499,20 +9517,24 @@
       <c r="A221" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="B221" s="4"/>
-      <c r="C221" s="5" t="s">
-        <v>585</v>
+      <c r="B221" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="C221" s="32" t="s">
+        <v>583</v>
       </c>
       <c r="D221" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="E221" s="4"/>
-      <c r="F221" s="4"/>
+        <v>584</v>
+      </c>
+      <c r="E221" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F221" s="23" t="s">
+        <v>266</v>
+      </c>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
-      <c r="I221" s="8" t="s">
-        <v>587</v>
-      </c>
+      <c r="I221" s="4"/>
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
       <c r="L221" s="4"/>
@@ -9523,18 +9545,18 @@
         <v>579</v>
       </c>
       <c r="B222" s="4"/>
-      <c r="C222" s="7" t="s">
-        <v>588</v>
+      <c r="C222" s="5" t="s">
+        <v>585</v>
       </c>
       <c r="D222" s="15" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E222" s="4"/>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
       <c r="H222" s="4"/>
-      <c r="I222" s="10" t="s">
-        <v>590</v>
+      <c r="I222" s="8" t="s">
+        <v>587</v>
       </c>
       <c r="J222" s="4"/>
       <c r="K222" s="4"/>
@@ -9547,17 +9569,17 @@
       </c>
       <c r="B223" s="4"/>
       <c r="C223" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D223" s="15" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E223" s="4"/>
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
-      <c r="I223" s="8" t="s">
-        <v>593</v>
+      <c r="I223" s="10" t="s">
+        <v>590</v>
       </c>
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
@@ -9569,18 +9591,18 @@
         <v>579</v>
       </c>
       <c r="B224" s="4"/>
-      <c r="C224" s="5" t="s">
-        <v>594</v>
+      <c r="C224" s="7" t="s">
+        <v>591</v>
       </c>
       <c r="D224" s="15" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E224" s="4"/>
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
       <c r="I224" s="8" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
@@ -9593,41 +9615,41 @@
       </c>
       <c r="B225" s="4"/>
       <c r="C225" s="5" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D225" s="15" t="s">
-        <v>598</v>
-      </c>
-      <c r="E225" s="8" t="s">
-        <v>599</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="E225" s="4"/>
       <c r="F225" s="4"/>
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
-      <c r="I225" s="4"/>
+      <c r="I225" s="8" t="s">
+        <v>596</v>
+      </c>
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
       <c r="L225" s="4"/>
       <c r="M225" s="5"/>
     </row>
     <row r="226" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A226" s="7" t="s">
-        <v>600</v>
+      <c r="A226" s="5" t="s">
+        <v>579</v>
       </c>
       <c r="B226" s="4"/>
-      <c r="C226" s="22" t="s">
-        <v>601</v>
-      </c>
-      <c r="D226" s="33" t="s">
-        <v>602</v>
-      </c>
-      <c r="E226" s="5"/>
+      <c r="C226" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="D226" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="E226" s="8" t="s">
+        <v>599</v>
+      </c>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
       <c r="H226" s="4"/>
-      <c r="I226" s="23" t="s">
-        <v>603</v>
-      </c>
+      <c r="I226" s="4"/>
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
       <c r="L226" s="4"/>
@@ -9637,19 +9659,19 @@
       <c r="A227" s="7" t="s">
         <v>600</v>
       </c>
-      <c r="B227" s="3"/>
-      <c r="C227" s="34" t="s">
-        <v>604</v>
-      </c>
-      <c r="D227" s="35" t="s">
-        <v>605</v>
-      </c>
-      <c r="E227" s="3"/>
+      <c r="B227" s="4"/>
+      <c r="C227" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="D227" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="E227" s="5"/>
       <c r="F227" s="4"/>
       <c r="G227" s="4"/>
-      <c r="H227" s="3"/>
-      <c r="I227" s="8" t="s">
-        <v>606</v>
+      <c r="H227" s="4"/>
+      <c r="I227" s="23" t="s">
+        <v>603</v>
       </c>
       <c r="J227" s="4"/>
       <c r="K227" s="4"/>
@@ -9661,18 +9683,18 @@
         <v>600</v>
       </c>
       <c r="B228" s="3"/>
-      <c r="C228" s="7" t="s">
-        <v>607</v>
-      </c>
-      <c r="D228" s="9" t="s">
-        <v>608</v>
+      <c r="C228" s="34" t="s">
+        <v>604</v>
+      </c>
+      <c r="D228" s="35" t="s">
+        <v>605</v>
       </c>
       <c r="E228" s="3"/>
       <c r="F228" s="4"/>
       <c r="G228" s="4"/>
       <c r="H228" s="3"/>
       <c r="I228" s="8" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="J228" s="4"/>
       <c r="K228" s="4"/>
@@ -9684,18 +9706,18 @@
         <v>600</v>
       </c>
       <c r="B229" s="3"/>
-      <c r="C229" s="10" t="s">
-        <v>610</v>
+      <c r="C229" s="7" t="s">
+        <v>607</v>
       </c>
       <c r="D229" s="9" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E229" s="3"/>
       <c r="F229" s="4"/>
       <c r="G229" s="4"/>
       <c r="H229" s="3"/>
       <c r="I229" s="8" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
@@ -9704,21 +9726,21 @@
     </row>
     <row r="230" spans="1:13" ht="13.5" customHeight="1">
       <c r="A230" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="B230" s="4"/>
-      <c r="C230" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="D230" s="15" t="s">
-        <v>615</v>
-      </c>
-      <c r="E230" s="4"/>
+        <v>600</v>
+      </c>
+      <c r="B230" s="3"/>
+      <c r="C230" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="D230" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="E230" s="3"/>
       <c r="F230" s="4"/>
       <c r="G230" s="4"/>
-      <c r="H230" s="4"/>
+      <c r="H230" s="3"/>
       <c r="I230" s="8" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
@@ -9730,18 +9752,18 @@
         <v>613</v>
       </c>
       <c r="B231" s="4"/>
-      <c r="C231" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="D231" s="36" t="s">
-        <v>618</v>
+      <c r="C231" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="D231" s="15" t="s">
+        <v>615</v>
       </c>
       <c r="E231" s="4"/>
       <c r="F231" s="4"/>
       <c r="G231" s="4"/>
       <c r="H231" s="4"/>
       <c r="I231" s="8" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
@@ -9749,22 +9771,22 @@
       <c r="M231" s="5"/>
     </row>
     <row r="232" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A232" s="37" t="s">
-        <v>620</v>
-      </c>
-      <c r="B232" s="38"/>
-      <c r="C232" s="39" t="s">
-        <v>621</v>
-      </c>
-      <c r="D232" s="40" t="s">
-        <v>622</v>
-      </c>
-      <c r="E232" s="41"/>
+      <c r="A232" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B232" s="4"/>
+      <c r="C232" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="D232" s="36" t="s">
+        <v>618</v>
+      </c>
+      <c r="E232" s="4"/>
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
       <c r="H232" s="4"/>
       <c r="I232" s="8" t="s">
-        <v>269</v>
+        <v>619</v>
       </c>
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
@@ -9775,19 +9797,19 @@
       <c r="A233" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B233" s="24"/>
-      <c r="C233" s="42" t="s">
-        <v>255</v>
-      </c>
-      <c r="D233" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="E233" s="3"/>
-      <c r="F233" s="20"/>
-      <c r="G233" s="20"/>
-      <c r="H233" s="3"/>
+      <c r="B233" s="38"/>
+      <c r="C233" s="39" t="s">
+        <v>621</v>
+      </c>
+      <c r="D233" s="40" t="s">
+        <v>622</v>
+      </c>
+      <c r="E233" s="41"/>
+      <c r="F233" s="4"/>
+      <c r="G233" s="4"/>
+      <c r="H233" s="4"/>
       <c r="I233" s="8" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
@@ -9799,18 +9821,18 @@
         <v>620</v>
       </c>
       <c r="B234" s="24"/>
-      <c r="C234" s="39" t="s">
-        <v>623</v>
-      </c>
-      <c r="D234" s="40" t="s">
-        <v>624</v>
-      </c>
-      <c r="E234" s="4"/>
-      <c r="F234" s="4"/>
-      <c r="G234" s="4"/>
-      <c r="H234" s="4"/>
-      <c r="I234" s="23" t="s">
-        <v>582</v>
+      <c r="C234" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E234" s="3"/>
+      <c r="F234" s="20"/>
+      <c r="G234" s="20"/>
+      <c r="H234" s="3"/>
+      <c r="I234" s="8" t="s">
+        <v>257</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
@@ -9821,19 +9843,19 @@
       <c r="A235" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B235" s="38"/>
-      <c r="C235" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="D235" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="E235" s="3"/>
-      <c r="F235" s="20"/>
-      <c r="G235" s="20"/>
-      <c r="H235" s="3"/>
-      <c r="I235" s="8" t="s">
-        <v>224</v>
+      <c r="B235" s="24"/>
+      <c r="C235" s="39" t="s">
+        <v>623</v>
+      </c>
+      <c r="D235" s="40" t="s">
+        <v>624</v>
+      </c>
+      <c r="E235" s="4"/>
+      <c r="F235" s="4"/>
+      <c r="G235" s="4"/>
+      <c r="H235" s="4"/>
+      <c r="I235" s="23" t="s">
+        <v>582</v>
       </c>
       <c r="J235" s="4"/>
       <c r="K235" s="4"/>
@@ -9845,18 +9867,18 @@
         <v>620</v>
       </c>
       <c r="B236" s="38"/>
-      <c r="C236" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D236" s="9" t="s">
-        <v>247</v>
+      <c r="C236" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D236" s="44" t="s">
+        <v>232</v>
       </c>
       <c r="E236" s="3"/>
       <c r="F236" s="20"/>
       <c r="G236" s="20"/>
       <c r="H236" s="3"/>
       <c r="I236" s="8" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="J236" s="4"/>
       <c r="K236" s="4"/>
@@ -9867,21 +9889,19 @@
       <c r="A237" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B237" s="38" t="s">
-        <v>625</v>
-      </c>
-      <c r="C237" s="39" t="s">
-        <v>626</v>
-      </c>
-      <c r="D237" s="40" t="s">
-        <v>627</v>
-      </c>
-      <c r="E237" s="4"/>
-      <c r="F237" s="4"/>
-      <c r="G237" s="4"/>
-      <c r="H237" s="4"/>
-      <c r="I237" s="23" t="s">
-        <v>628</v>
+      <c r="B237" s="38"/>
+      <c r="C237" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D237" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E237" s="3"/>
+      <c r="F237" s="20"/>
+      <c r="G237" s="20"/>
+      <c r="H237" s="3"/>
+      <c r="I237" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="J237" s="4"/>
       <c r="K237" s="4"/>
@@ -9896,17 +9916,17 @@
         <v>625</v>
       </c>
       <c r="C238" s="39" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D238" s="40" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
       <c r="I238" s="23" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="J238" s="4"/>
       <c r="K238" s="4"/>
@@ -9921,17 +9941,17 @@
         <v>625</v>
       </c>
       <c r="C239" s="39" t="s">
-        <v>228</v>
+        <v>629</v>
       </c>
       <c r="D239" s="40" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E239" s="4"/>
       <c r="F239" s="4"/>
       <c r="G239" s="4"/>
       <c r="H239" s="4"/>
       <c r="I239" s="23" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="J239" s="4"/>
       <c r="K239" s="4"/>
@@ -9939,15 +9959,25 @@
       <c r="M239" s="5"/>
     </row>
     <row r="240" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A240" s="4"/>
-      <c r="B240" s="4"/>
-      <c r="C240" s="4"/>
-      <c r="D240" s="4"/>
+      <c r="A240" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="B240" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="C240" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="D240" s="40" t="s">
+        <v>632</v>
+      </c>
       <c r="E240" s="4"/>
       <c r="F240" s="4"/>
       <c r="G240" s="4"/>
       <c r="H240" s="4"/>
-      <c r="I240" s="4"/>
+      <c r="I240" s="23" t="s">
+        <v>633</v>
+      </c>
       <c r="J240" s="4"/>
       <c r="K240" s="4"/>
       <c r="L240" s="4"/>
@@ -12743,7 +12773,21 @@
       <c r="L426" s="4"/>
       <c r="M426" s="5"/>
     </row>
-    <row r="427" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="427" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A427" s="4"/>
+      <c r="B427" s="4"/>
+      <c r="C427" s="4"/>
+      <c r="D427" s="4"/>
+      <c r="E427" s="4"/>
+      <c r="F427" s="4"/>
+      <c r="G427" s="4"/>
+      <c r="H427" s="4"/>
+      <c r="I427" s="4"/>
+      <c r="J427" s="4"/>
+      <c r="K427" s="4"/>
+      <c r="L427" s="4"/>
+      <c r="M427" s="5"/>
+    </row>
     <row r="428" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="429" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="430" spans="1:13" ht="15.75" customHeight="1"/>
@@ -13340,6 +13384,7 @@
     <row r="1021" ht="15.75" customHeight="1"/>
     <row r="1022" ht="15.75" customHeight="1"/>
     <row r="1023" ht="15.75" customHeight="1"/>
+    <row r="1024" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="15"/>
   <hyperlinks>
@@ -13504,58 +13549,59 @@
     <hyperlink ref="D184" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
     <hyperlink ref="D186" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
     <hyperlink ref="D187" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D188" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="D189" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D190" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="D191" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D192" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D193" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D194" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="D195" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D196" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="D197" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D198" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="D199" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D200" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D201" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D202" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D203" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D204" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="D205" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D206" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="D207" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D208" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="D209" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D210" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="D211" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D213" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D214" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D215" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D216" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D217" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D218" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D219" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D221" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D222" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D223" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D224" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D225" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D226" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="D227" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D228" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="D229" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D230" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="D231" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D233" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="D235" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D236" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="D189" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="D190" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="D191" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="D192" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="D193" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="D194" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="D195" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="D196" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="D197" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="D198" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="D199" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="D200" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="D201" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="D202" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="D203" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="D204" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="D205" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="D206" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="D207" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="D208" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="D209" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="D210" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="D211" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="D212" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="D214" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D215" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D216" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D217" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D218" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D219" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D220" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D222" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D223" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D224" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D225" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D226" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D227" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="D228" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="D229" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="D230" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="D231" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="D232" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="D234" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="D236" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="D237" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
     <hyperlink ref="D16" r:id="rId207" xr:uid="{101A33D7-B7BA-422E-B2FC-342D5148D1EA}"/>
-    <hyperlink ref="D212" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
+    <hyperlink ref="D213" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
     <hyperlink ref="D77" r:id="rId209" xr:uid="{15E62A8C-2F55-4EC5-B29A-D16518F2E4D9}"/>
     <hyperlink ref="D76" r:id="rId210" xr:uid="{FC2D964E-B283-4703-AAB9-28EC36520D76}"/>
     <hyperlink ref="D17" r:id="rId211" xr:uid="{BAFD46EC-62AB-41E1-B82A-03A62E913A64}"/>
     <hyperlink ref="D178" r:id="rId212" xr:uid="{1B2883BA-7428-4C3B-8B0A-0E84AA25F727}"/>
     <hyperlink ref="D177" r:id="rId213" xr:uid="{94880ED8-4B43-4BE4-B733-30DFCED08C71}"/>
+    <hyperlink ref="D188" r:id="rId214" xr:uid="{7A4126AD-D394-4C29-AE05-60E7F949761F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/メニュー/メニュー.xlsx
+++ b/メニュー/メニュー.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\vm22flo01\DownloadFiles\スマートシティ課\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dx-user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC863E1-1121-4536-82E1-66BA301D13B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1C6658-3498-4E25-8E1B-ECF91AF0B18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="672">
   <si>
     <t>大カテゴリー</t>
   </si>
@@ -3300,6 +3300,33 @@
   </si>
   <si>
     <t>litter-pickup</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>全域</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E5%B8%82%E5%85%A8%E5%9F%9F_%E5%AE%B6%E5%B1%8B%E5%80%92%E5%A3%8A%E7%AD%89%E6%B0%BE%E6%BF%AB%E6%83%B3%E5%AE%9A%EF%BC%88%E6%B0%BE%E6%BF%AB%E6%B5%81%E3%83%BB%E6%B4%AA%E6%B0%B4%EF%BC%89/tiles.json</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E7%84%BC%E6%B4%A5%E5%B8%82%E5%85%A8%E5%9F%9F_%E5%AE%B6%E5%B1%8B%E5%80%92%E5%A3%8A%E7%AD%89%E6%B0%BE%E6%BF%AB%E6%83%B3%E5%AE%9A%EF%BC%88%E6%B2%B3%E5%B2%B8%E4%BE%B5%E9%A3%9F%EF%BC%89/tiles.json</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>イベント情報</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>https://yaizu-smartcity.jp/tiles/%E3%82%A4%E3%83%99%E3%83%B3%E3%83%88%E6%83%85%E5%A0%B1/tiles.json</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>balloon</t>
     <phoneticPr fontId="15"/>
   </si>
 </sst>
@@ -3935,7 +3962,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M1024"/>
+  <dimension ref="A1:M1027"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -5509,10 +5536,10 @@
         <v>155</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D65" s="17" t="s">
-        <v>156</v>
+        <v>666</v>
+      </c>
+      <c r="D65" s="45" t="s">
+        <v>667</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>157</v>
@@ -5533,22 +5560,22 @@
         <v>16</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>105</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>161</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="F66" s="4"/>
       <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
+      <c r="H66" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
@@ -5563,10 +5590,10 @@
         <v>158</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>162</v>
+        <v>666</v>
+      </c>
+      <c r="D67" s="45" t="s">
+        <v>668</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>160</v>
@@ -5575,7 +5602,7 @@
         <v>161</v>
       </c>
       <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
+      <c r="H67" s="8"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
@@ -5590,10 +5617,10 @@
         <v>158</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>160</v>
@@ -5617,10 +5644,10 @@
         <v>158</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>160</v>
@@ -5644,10 +5671,10 @@
         <v>158</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>160</v>
@@ -5671,10 +5698,10 @@
         <v>158</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>160</v>
@@ -5698,10 +5725,10 @@
         <v>158</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>160</v>
@@ -5725,10 +5752,10 @@
         <v>158</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>160</v>
@@ -5744,20 +5771,24 @@
       <c r="L73" s="4"/>
       <c r="M73" s="5"/>
     </row>
-    <row r="74" spans="1:13" ht="14.25" customHeight="1">
+    <row r="74" spans="1:13" ht="13.5" customHeight="1">
       <c r="A74" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B74" s="4"/>
+      <c r="B74" s="5" t="s">
+        <v>158</v>
+      </c>
       <c r="C74" s="5" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="E74" s="4"/>
+        <v>167</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>160</v>
+      </c>
       <c r="F74" s="8" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
@@ -5772,49 +5803,45 @@
         <v>16</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>650</v>
+        <v>158</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>646</v>
+        <v>135</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F75" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>161</v>
+      </c>
       <c r="G75" s="4"/>
-      <c r="H75" s="10" t="s">
-        <v>15</v>
-      </c>
+      <c r="H75" s="4"/>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
       <c r="M75" s="5"/>
     </row>
-    <row r="76" spans="1:13" ht="13.5" customHeight="1">
+    <row r="76" spans="1:13" ht="14.25" customHeight="1">
       <c r="A76" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>650</v>
-      </c>
+      <c r="B76" s="4"/>
       <c r="C76" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="D76" s="45" t="s">
-        <v>648</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" s="4"/>
+        <v>169</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="G76" s="4"/>
-      <c r="H76" s="10" t="s">
-        <v>15</v>
-      </c>
+      <c r="H76" s="4"/>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
@@ -5826,13 +5853,13 @@
         <v>16</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="D77" s="45" t="s">
-        <v>647</v>
+        <v>646</v>
+      </c>
+      <c r="D77" s="17" t="s">
+        <v>171</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>15</v>
@@ -5853,13 +5880,13 @@
         <v>16</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="D78" s="17" t="s">
-        <v>172</v>
+        <v>644</v>
+      </c>
+      <c r="D78" s="45" t="s">
+        <v>648</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>15</v>
@@ -5883,10 +5910,10 @@
         <v>651</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D79" s="17" t="s">
-        <v>174</v>
+        <v>645</v>
+      </c>
+      <c r="D79" s="45" t="s">
+        <v>647</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>15</v>
@@ -5910,10 +5937,10 @@
         <v>651</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>175</v>
+        <v>649</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>15</v>
@@ -5937,10 +5964,10 @@
         <v>651</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>15</v>
@@ -5964,24 +5991,24 @@
         <v>651</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F82" s="20"/>
-      <c r="G82" s="20"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
       <c r="H82" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I82" s="20"/>
-      <c r="J82" s="20"/>
-      <c r="K82" s="20"/>
-      <c r="L82" s="20"/>
-      <c r="M82" s="21"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="5"/>
     </row>
     <row r="83" spans="1:13" ht="13.5" customHeight="1">
       <c r="A83" s="7" t="s">
@@ -5991,10 +6018,10 @@
         <v>651</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>15</v>
@@ -6018,24 +6045,24 @@
         <v>651</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20"/>
       <c r="H84" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
-      <c r="M84" s="5"/>
+      <c r="I84" s="20"/>
+      <c r="J84" s="20"/>
+      <c r="K84" s="20"/>
+      <c r="L84" s="20"/>
+      <c r="M84" s="21"/>
     </row>
     <row r="85" spans="1:13" ht="13.5" customHeight="1">
       <c r="A85" s="7" t="s">
@@ -6045,10 +6072,10 @@
         <v>651</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>15</v>
@@ -6072,10 +6099,10 @@
         <v>651</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>15</v>
@@ -6099,10 +6126,10 @@
         <v>651</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>15</v>
@@ -6126,10 +6153,10 @@
         <v>651</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>15</v>
@@ -6153,10 +6180,10 @@
         <v>651</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>15</v>
@@ -6180,10 +6207,10 @@
         <v>651</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>15</v>
@@ -6207,10 +6234,10 @@
         <v>651</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>15</v>
@@ -6234,10 +6261,10 @@
         <v>651</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>15</v>
@@ -6261,10 +6288,10 @@
         <v>651</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>15</v>
@@ -6288,24 +6315,24 @@
         <v>651</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F94" s="20"/>
-      <c r="G94" s="20"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
       <c r="H94" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I94" s="20"/>
-      <c r="J94" s="20"/>
-      <c r="K94" s="20"/>
-      <c r="L94" s="20"/>
-      <c r="M94" s="21"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="5"/>
     </row>
     <row r="95" spans="1:13" ht="13.5" customHeight="1">
       <c r="A95" s="7" t="s">
@@ -6315,10 +6342,10 @@
         <v>651</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>15</v>
@@ -6342,10 +6369,10 @@
         <v>651</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>15</v>
@@ -6355,8 +6382,8 @@
       <c r="H96" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
+      <c r="I96" s="20"/>
+      <c r="J96" s="20"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
       <c r="M96" s="21"/>
@@ -6369,10 +6396,10 @@
         <v>651</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>15</v>
@@ -6392,38 +6419,50 @@
       <c r="A98" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B98" s="5"/>
+      <c r="B98" s="5" t="s">
+        <v>651</v>
+      </c>
       <c r="C98" s="5" t="s">
-        <v>640</v>
+        <v>207</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="E98" s="7"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="7"/>
+        <v>208</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98" s="20"/>
+      <c r="G98" s="20"/>
+      <c r="H98" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="I98" s="4"/>
       <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="4"/>
-      <c r="M98" s="5"/>
+      <c r="K98" s="20"/>
+      <c r="L98" s="20"/>
+      <c r="M98" s="21"/>
     </row>
     <row r="99" spans="1:13" ht="13.5" customHeight="1">
       <c r="A99" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B99" s="5"/>
+      <c r="B99" s="5" t="s">
+        <v>651</v>
+      </c>
       <c r="C99" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="E99" s="7"/>
+        <v>210</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
-      <c r="H99" s="7"/>
+      <c r="H99" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
@@ -6436,19 +6475,15 @@
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5" t="s">
-        <v>214</v>
+        <v>640</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>216</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="E100" s="7"/>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
-      <c r="H100" s="10" t="s">
-        <v>216</v>
-      </c>
+      <c r="H100" s="7"/>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
@@ -6461,19 +6496,15 @@
       </c>
       <c r="B101" s="5"/>
       <c r="C101" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>219</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="E101" s="7"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
-      <c r="H101" s="10" t="s">
-        <v>219</v>
-      </c>
+      <c r="H101" s="7"/>
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
@@ -6482,24 +6513,24 @@
     </row>
     <row r="102" spans="1:13" ht="13.5" customHeight="1">
       <c r="A102" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B102" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="C102" s="22" t="s">
-        <v>222</v>
+        <v>16</v>
+      </c>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="E102" s="7"/>
+        <v>215</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>216</v>
+      </c>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
-      <c r="H102" s="7"/>
-      <c r="I102" s="23" t="s">
-        <v>224</v>
-      </c>
+      <c r="H102" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="I102" s="4"/>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
@@ -6507,24 +6538,24 @@
     </row>
     <row r="103" spans="1:13" ht="13.5" customHeight="1">
       <c r="A103" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B103" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="C103" s="22" t="s">
-        <v>225</v>
+        <v>16</v>
+      </c>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="E103" s="7"/>
+        <v>218</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>219</v>
+      </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
-      <c r="H103" s="7"/>
-      <c r="I103" s="23" t="s">
-        <v>227</v>
-      </c>
+      <c r="H103" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I103" s="4"/>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
@@ -6534,21 +6565,19 @@
       <c r="A104" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B104" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="C104" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="D104" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="E104" s="7"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="D104" s="45" t="s">
+        <v>670</v>
+      </c>
+      <c r="E104" s="10"/>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
-      <c r="H104" s="7"/>
-      <c r="I104" s="23" t="s">
-        <v>230</v>
+      <c r="H104" s="10"/>
+      <c r="I104" s="4" t="s">
+        <v>671</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
@@ -6559,18 +6588,20 @@
       <c r="A105" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B105" s="4"/>
-      <c r="C105" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="E105" s="3"/>
-      <c r="F105" s="20"/>
-      <c r="G105" s="20"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="8" t="s">
+      <c r="B105" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="C105" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="D105" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="E105" s="7"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="23" t="s">
         <v>224</v>
       </c>
       <c r="J105" s="4"/>
@@ -6582,21 +6613,21 @@
       <c r="A106" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B106" s="24" t="s">
-        <v>233</v>
+      <c r="B106" s="22" t="s">
+        <v>221</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="E106" s="3"/>
-      <c r="F106" s="20"/>
-      <c r="G106" s="20"/>
-      <c r="H106" s="3"/>
-      <c r="I106" s="8" t="s">
-        <v>236</v>
+        <v>225</v>
+      </c>
+      <c r="D106" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="E106" s="7"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="23" t="s">
+        <v>227</v>
       </c>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
@@ -6607,21 +6638,21 @@
       <c r="A107" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B107" s="24" t="s">
-        <v>233</v>
+      <c r="B107" s="22" t="s">
+        <v>221</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="E107" s="3"/>
-      <c r="F107" s="20"/>
-      <c r="G107" s="20"/>
-      <c r="H107" s="3"/>
-      <c r="I107" s="8" t="s">
-        <v>634</v>
+        <v>228</v>
+      </c>
+      <c r="D107" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="E107" s="7"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="23" t="s">
+        <v>230</v>
       </c>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
@@ -6632,21 +6663,19 @@
       <c r="A108" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B108" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="C108" s="22" t="s">
-        <v>239</v>
+      <c r="B108" s="4"/>
+      <c r="C108" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="20"/>
       <c r="G108" s="20"/>
       <c r="H108" s="3"/>
       <c r="I108" s="8" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
@@ -6661,10 +6690,10 @@
         <v>233</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="D109" s="25" t="s">
-        <v>242</v>
+        <v>234</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="20"/>
@@ -6686,17 +6715,17 @@
         <v>233</v>
       </c>
       <c r="C110" s="22" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="20"/>
       <c r="G110" s="20"/>
       <c r="H110" s="3"/>
       <c r="I110" s="8" t="s">
-        <v>236</v>
+        <v>634</v>
       </c>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
@@ -6707,21 +6736,21 @@
       <c r="A111" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B111" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>246</v>
+      <c r="B111" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="C111" s="22" t="s">
+        <v>239</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="20"/>
       <c r="G111" s="20"/>
       <c r="H111" s="3"/>
       <c r="I111" s="8" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
@@ -6732,21 +6761,21 @@
       <c r="A112" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B112" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D112" s="9" t="s">
-        <v>250</v>
+      <c r="B112" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="C112" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="D112" s="25" t="s">
+        <v>242</v>
       </c>
       <c r="E112" s="3"/>
-      <c r="F112" s="4"/>
+      <c r="F112" s="20"/>
       <c r="G112" s="20"/>
       <c r="H112" s="3"/>
       <c r="I112" s="8" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
@@ -6757,19 +6786,21 @@
       <c r="A113" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B113" s="3"/>
-      <c r="C113" s="7" t="s">
-        <v>252</v>
+      <c r="B113" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="C113" s="22" t="s">
+        <v>243</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="20"/>
       <c r="G113" s="20"/>
       <c r="H113" s="3"/>
       <c r="I113" s="8" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
@@ -6780,19 +6811,21 @@
       <c r="A114" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B114" s="3"/>
+      <c r="B114" s="5" t="s">
+        <v>245</v>
+      </c>
       <c r="C114" s="7" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="20"/>
       <c r="G114" s="20"/>
       <c r="H114" s="3"/>
       <c r="I114" s="8" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
@@ -6803,19 +6836,21 @@
       <c r="A115" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B115" s="3"/>
+      <c r="B115" s="5" t="s">
+        <v>245</v>
+      </c>
       <c r="C115" s="7" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="E115" s="3"/>
-      <c r="F115" s="20"/>
+      <c r="F115" s="4"/>
       <c r="G115" s="20"/>
       <c r="H115" s="3"/>
       <c r="I115" s="8" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
@@ -6826,47 +6861,43 @@
       <c r="A116" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B116" s="5" t="s">
-        <v>261</v>
-      </c>
+      <c r="B116" s="3"/>
       <c r="C116" s="7" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="20"/>
       <c r="G116" s="20"/>
       <c r="H116" s="3"/>
-      <c r="I116" s="10" t="s">
-        <v>264</v>
+      <c r="I116" s="8" t="s">
+        <v>254</v>
       </c>
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
     </row>
-    <row r="117" spans="1:13" ht="15" customHeight="1">
+    <row r="117" spans="1:13" ht="13.5" customHeight="1">
       <c r="A117" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B117" s="5" t="s">
-        <v>261</v>
-      </c>
+      <c r="B117" s="3"/>
       <c r="C117" s="7" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E117" s="3"/>
-      <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
-      <c r="H117" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="I117" s="4"/>
+      <c r="F117" s="20"/>
+      <c r="G117" s="20"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="8" t="s">
+        <v>257</v>
+      </c>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
@@ -6876,19 +6907,19 @@
       <c r="A118" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B118" s="4"/>
+      <c r="B118" s="3"/>
       <c r="C118" s="7" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="20"/>
       <c r="G118" s="20"/>
       <c r="H118" s="3"/>
       <c r="I118" s="8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
@@ -6899,94 +6930,92 @@
       <c r="A119" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B119" s="4"/>
+      <c r="B119" s="5" t="s">
+        <v>261</v>
+      </c>
       <c r="C119" s="7" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E119" s="3"/>
-      <c r="F119" s="4"/>
-      <c r="G119" s="4"/>
-      <c r="H119" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="I119" s="4"/>
+      <c r="F119" s="20"/>
+      <c r="G119" s="20"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="10" t="s">
+        <v>264</v>
+      </c>
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
       <c r="L119" s="4"/>
       <c r="M119" s="5"/>
     </row>
-    <row r="120" spans="1:13" ht="12.75" customHeight="1">
+    <row r="120" spans="1:13" ht="15" customHeight="1">
       <c r="A120" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B120" s="7" t="s">
-        <v>273</v>
+      <c r="B120" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="D120" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="E120" s="4"/>
-      <c r="F120" s="8" t="s">
-        <v>276</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="E120" s="3"/>
+      <c r="F120" s="4"/>
       <c r="G120" s="4"/>
-      <c r="H120" s="4"/>
+      <c r="H120" s="10" t="s">
+        <v>266</v>
+      </c>
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
       <c r="L120" s="4"/>
       <c r="M120" s="5"/>
     </row>
-    <row r="121" spans="1:13" ht="12.75" customHeight="1">
+    <row r="121" spans="1:13" ht="13.5" customHeight="1">
       <c r="A121" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B121" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="B121" s="4"/>
       <c r="C121" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="D121" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="E121" s="4"/>
-      <c r="F121" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="4"/>
+        <v>267</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E121" s="3"/>
+      <c r="F121" s="20"/>
+      <c r="G121" s="20"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="8" t="s">
+        <v>269</v>
+      </c>
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
       <c r="L121" s="4"/>
       <c r="M121" s="5"/>
     </row>
-    <row r="122" spans="1:13" ht="12.75" customHeight="1">
+    <row r="122" spans="1:13" ht="13.5" customHeight="1">
       <c r="A122" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B122" s="7" t="s">
-        <v>273</v>
-      </c>
+      <c r="B122" s="4"/>
       <c r="C122" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="D122" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="E122" s="4"/>
-      <c r="F122" s="8" t="s">
-        <v>282</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E122" s="3"/>
+      <c r="F122" s="4"/>
       <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
+      <c r="H122" s="14" t="s">
+        <v>272</v>
+      </c>
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
       <c r="K122" s="4"/>
@@ -7001,14 +7030,14 @@
         <v>273</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="8" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
@@ -7026,14 +7055,14 @@
         <v>273</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E124" s="4"/>
       <c r="F124" s="8" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
@@ -7051,14 +7080,14 @@
         <v>273</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="8" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
@@ -7076,14 +7105,14 @@
         <v>273</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="8" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
@@ -7093,7 +7122,7 @@
       <c r="L126" s="4"/>
       <c r="M126" s="5"/>
     </row>
-    <row r="127" spans="1:13" ht="13.5" customHeight="1">
+    <row r="127" spans="1:13" ht="12.75" customHeight="1">
       <c r="A127" s="7" t="s">
         <v>220</v>
       </c>
@@ -7101,24 +7130,24 @@
         <v>273</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D127" s="15" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="E127" s="4"/>
-      <c r="F127" s="4"/>
+      <c r="F127" s="8" t="s">
+        <v>288</v>
+      </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
-      <c r="I127" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="J127" s="20"/>
+      <c r="I127" s="4"/>
+      <c r="J127" s="4"/>
       <c r="K127" s="4"/>
       <c r="L127" s="4"/>
       <c r="M127" s="5"/>
     </row>
-    <row r="128" spans="1:13" ht="13.5" customHeight="1">
+    <row r="128" spans="1:13" ht="12.75" customHeight="1">
       <c r="A128" s="7" t="s">
         <v>220</v>
       </c>
@@ -7126,44 +7155,42 @@
         <v>273</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="D128" s="17" t="s">
-        <v>299</v>
+        <v>289</v>
+      </c>
+      <c r="D128" s="15" t="s">
+        <v>290</v>
       </c>
       <c r="E128" s="4"/>
-      <c r="F128" s="4"/>
+      <c r="F128" s="8" t="s">
+        <v>291</v>
+      </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
-      <c r="I128" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="J128" s="20"/>
+      <c r="I128" s="4"/>
+      <c r="J128" s="4"/>
       <c r="K128" s="4"/>
       <c r="L128" s="4"/>
       <c r="M128" s="5"/>
     </row>
-    <row r="129" spans="1:13" ht="13.5" customHeight="1">
+    <row r="129" spans="1:13" ht="12.75" customHeight="1">
       <c r="A129" s="7" t="s">
         <v>220</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C129" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="D129" s="17" t="s">
-        <v>302</v>
+      <c r="C129" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D129" s="15" t="s">
+        <v>293</v>
       </c>
       <c r="E129" s="4"/>
-      <c r="F129" s="26" t="s">
-        <v>303</v>
+      <c r="F129" s="8" t="s">
+        <v>294</v>
       </c>
       <c r="G129" s="4"/>
-      <c r="H129" s="26" t="s">
-        <v>304</v>
-      </c>
+      <c r="H129" s="4"/>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
@@ -7171,70 +7198,76 @@
       <c r="M129" s="5"/>
     </row>
     <row r="130" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A130" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B130" s="4"/>
-      <c r="C130" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="D130" s="17" t="s">
-        <v>307</v>
+      <c r="A130" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D130" s="15" t="s">
+        <v>296</v>
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
-      <c r="I130" s="4"/>
-      <c r="J130" s="4"/>
+      <c r="I130" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="J130" s="20"/>
       <c r="K130" s="4"/>
       <c r="L130" s="4"/>
       <c r="M130" s="5"/>
     </row>
     <row r="131" spans="1:13" ht="13.5" customHeight="1">
       <c r="A131" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>309</v>
+        <v>220</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="E131" s="10" t="s">
-        <v>311</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="E131" s="4"/>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
-      <c r="H131" s="3"/>
-      <c r="I131" s="4"/>
-      <c r="J131" s="4"/>
+      <c r="H131" s="4"/>
+      <c r="I131" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="J131" s="20"/>
       <c r="K131" s="4"/>
       <c r="L131" s="4"/>
       <c r="M131" s="5"/>
     </row>
     <row r="132" spans="1:13" ht="13.5" customHeight="1">
       <c r="A132" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>308</v>
+        <v>220</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>273</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="E132" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F132" s="4"/>
+        <v>302</v>
+      </c>
+      <c r="E132" s="4"/>
+      <c r="F132" s="26" t="s">
+        <v>303</v>
+      </c>
       <c r="G132" s="4"/>
-      <c r="H132" s="3"/>
+      <c r="H132" s="26" t="s">
+        <v>304</v>
+      </c>
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
@@ -7242,24 +7275,20 @@
       <c r="M132" s="5"/>
     </row>
     <row r="133" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A133" s="7" t="s">
+      <c r="A133" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B133" s="5" t="s">
-        <v>308</v>
-      </c>
+      <c r="B133" s="4"/>
       <c r="C133" s="5" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>317</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="E133" s="4"/>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
-      <c r="H133" s="3"/>
+      <c r="H133" s="4"/>
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
@@ -7274,13 +7303,13 @@
         <v>308</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
@@ -7299,17 +7328,17 @@
         <v>308</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>322</v>
-      </c>
-      <c r="E135" s="8" t="s">
-        <v>323</v>
+        <v>313</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>314</v>
       </c>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
-      <c r="H135" s="4"/>
+      <c r="H135" s="3"/>
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
@@ -7324,13 +7353,13 @@
         <v>308</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
@@ -7349,13 +7378,13 @@
         <v>308</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
@@ -7374,17 +7403,17 @@
         <v>308</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="E138" s="10" t="s">
-        <v>332</v>
+        <v>322</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>323</v>
       </c>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
-      <c r="H138" s="3"/>
+      <c r="H138" s="4"/>
       <c r="I138" s="4"/>
       <c r="J138" s="4"/>
       <c r="K138" s="4"/>
@@ -7399,17 +7428,17 @@
         <v>308</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>334</v>
-      </c>
-      <c r="E139" s="8" t="s">
-        <v>335</v>
+        <v>325</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>326</v>
       </c>
       <c r="F139" s="4"/>
       <c r="G139" s="4"/>
-      <c r="H139" s="4"/>
+      <c r="H139" s="3"/>
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
@@ -7424,17 +7453,17 @@
         <v>308</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="E140" s="8" t="s">
-        <v>335</v>
+        <v>328</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>329</v>
       </c>
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
+      <c r="H140" s="3"/>
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
@@ -7449,17 +7478,17 @@
         <v>308</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>339</v>
-      </c>
-      <c r="E141" s="8" t="s">
-        <v>340</v>
+        <v>331</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>332</v>
       </c>
       <c r="F141" s="4"/>
       <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
+      <c r="H141" s="3"/>
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
@@ -7474,13 +7503,13 @@
         <v>308</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F142" s="4"/>
       <c r="G142" s="4"/>
@@ -7496,20 +7525,18 @@
         <v>305</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="F143" s="8" t="s">
-        <v>347</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="F143" s="4"/>
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
@@ -7523,20 +7550,18 @@
         <v>305</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="F144" s="8" t="s">
-        <v>347</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="F144" s="4"/>
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
@@ -7550,20 +7575,18 @@
         <v>305</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="F145" s="8" t="s">
-        <v>347</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="F145" s="4"/>
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
@@ -7580,13 +7603,13 @@
         <v>343</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>347</v>
@@ -7607,13 +7630,13 @@
         <v>343</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>347</v>
@@ -7634,13 +7657,13 @@
         <v>343</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F148" s="8" t="s">
         <v>347</v>
@@ -7661,16 +7684,16 @@
         <v>343</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="G149" s="4"/>
       <c r="H149" s="4"/>
@@ -7688,19 +7711,19 @@
         <v>343</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="E150" s="10" t="s">
-        <v>369</v>
+        <v>358</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>359</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="G150" s="4"/>
-      <c r="H150" s="3"/>
+      <c r="H150" s="4"/>
       <c r="I150" s="4"/>
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
@@ -7715,16 +7738,16 @@
         <v>343</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
@@ -7742,13 +7765,13 @@
         <v>343</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>366</v>
@@ -7769,19 +7792,19 @@
         <v>343</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="D153" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="E153" s="8" t="s">
-        <v>378</v>
+        <v>368</v>
+      </c>
+      <c r="E153" s="10" t="s">
+        <v>369</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>366</v>
       </c>
       <c r="G153" s="4"/>
-      <c r="H153" s="4"/>
+      <c r="H153" s="3"/>
       <c r="I153" s="4"/>
       <c r="J153" s="4"/>
       <c r="K153" s="4"/>
@@ -7792,17 +7815,17 @@
       <c r="A154" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B154" s="7" t="s">
+      <c r="B154" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="C154" s="7" t="s">
-        <v>379</v>
+      <c r="C154" s="5" t="s">
+        <v>370</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>366</v>
@@ -7810,29 +7833,29 @@
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
-      <c r="J154" s="5"/>
+      <c r="J154" s="4"/>
       <c r="K154" s="4"/>
       <c r="L154" s="4"/>
       <c r="M154" s="5"/>
     </row>
     <row r="155" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A155" s="5" t="s">
+      <c r="A155" s="7" t="s">
         <v>305</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="E155" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="F155" s="23" t="s">
-        <v>385</v>
+        <v>374</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>366</v>
       </c>
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
@@ -7843,23 +7866,23 @@
       <c r="M155" s="5"/>
     </row>
     <row r="156" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A156" s="5" t="s">
+      <c r="A156" s="7" t="s">
         <v>305</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D156" s="17" t="s">
-        <v>387</v>
-      </c>
-      <c r="E156" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="F156" s="23" t="s">
-        <v>388</v>
+        <v>377</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>366</v>
       </c>
       <c r="G156" s="4"/>
       <c r="H156" s="4"/>
@@ -7873,67 +7896,77 @@
       <c r="A157" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B157" s="4"/>
-      <c r="C157" s="5" t="s">
-        <v>389</v>
+      <c r="B157" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>379</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="E157" s="4"/>
-      <c r="F157" s="20"/>
-      <c r="G157" s="20"/>
+        <v>380</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="G157" s="4"/>
       <c r="H157" s="4"/>
-      <c r="I157" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="J157" s="20"/>
+      <c r="I157" s="4"/>
+      <c r="J157" s="5"/>
       <c r="K157" s="4"/>
       <c r="L157" s="4"/>
       <c r="M157" s="5"/>
     </row>
     <row r="158" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A158" s="7" t="s">
+      <c r="A158" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B158" s="4"/>
+      <c r="B158" s="5" t="s">
+        <v>382</v>
+      </c>
       <c r="C158" s="5" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="E158" s="4"/>
-      <c r="F158" s="20"/>
-      <c r="G158" s="20"/>
+        <v>384</v>
+      </c>
+      <c r="E158" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="F158" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="G158" s="4"/>
       <c r="H158" s="4"/>
-      <c r="I158" s="26" t="s">
-        <v>393</v>
-      </c>
-      <c r="J158" s="20"/>
+      <c r="I158" s="4"/>
+      <c r="J158" s="4"/>
       <c r="K158" s="4"/>
       <c r="L158" s="4"/>
       <c r="M158" s="5"/>
     </row>
     <row r="159" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A159" s="7" t="s">
+      <c r="A159" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B159" s="4"/>
+      <c r="B159" s="5" t="s">
+        <v>382</v>
+      </c>
       <c r="C159" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D159" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="F159" s="4"/>
+        <v>386</v>
+      </c>
+      <c r="D159" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="E159" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="F159" s="23" t="s">
+        <v>388</v>
+      </c>
       <c r="G159" s="4"/>
-      <c r="H159" s="8" t="s">
-        <v>396</v>
-      </c>
+      <c r="H159" s="4"/>
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
       <c r="K159" s="4"/>
@@ -7941,74 +7974,70 @@
       <c r="M159" s="5"/>
     </row>
     <row r="160" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A160" s="5" t="s">
-        <v>397</v>
+      <c r="A160" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="D160" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="E160" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="F160" s="4"/>
-      <c r="G160" s="4"/>
-      <c r="H160" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="I160" s="4"/>
-      <c r="J160" s="4"/>
+        <v>389</v>
+      </c>
+      <c r="D160" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="E160" s="4"/>
+      <c r="F160" s="20"/>
+      <c r="G160" s="20"/>
+      <c r="H160" s="4"/>
+      <c r="I160" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="J160" s="20"/>
       <c r="K160" s="4"/>
       <c r="L160" s="4"/>
       <c r="M160" s="5"/>
     </row>
     <row r="161" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A161" s="5" t="s">
-        <v>397</v>
+      <c r="A161" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="D161" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="E161" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="F161" s="4"/>
-      <c r="G161" s="4"/>
-      <c r="H161" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="I161" s="4"/>
-      <c r="J161" s="4"/>
+        <v>391</v>
+      </c>
+      <c r="D161" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="E161" s="4"/>
+      <c r="F161" s="20"/>
+      <c r="G161" s="20"/>
+      <c r="H161" s="4"/>
+      <c r="I161" s="26" t="s">
+        <v>393</v>
+      </c>
+      <c r="J161" s="20"/>
       <c r="K161" s="4"/>
       <c r="L161" s="4"/>
       <c r="M161" s="5"/>
     </row>
     <row r="162" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A162" s="5" t="s">
-        <v>397</v>
+      <c r="A162" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="5" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F162" s="8" t="s">
-        <v>406</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="F162" s="4"/>
       <c r="G162" s="4"/>
-      <c r="H162" s="4"/>
+      <c r="H162" s="8" t="s">
+        <v>396</v>
+      </c>
       <c r="I162" s="4"/>
       <c r="J162" s="4"/>
       <c r="K162" s="4"/>
@@ -8017,21 +8046,23 @@
     </row>
     <row r="163" spans="1:13" ht="13.5" customHeight="1">
       <c r="A163" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="B163" s="5"/>
+        <v>397</v>
+      </c>
+      <c r="B163" s="4"/>
       <c r="C163" s="5" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="F163" s="4"/>
       <c r="G163" s="4"/>
-      <c r="H163" s="4"/>
+      <c r="H163" s="8" t="s">
+        <v>400</v>
+      </c>
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
       <c r="K163" s="4"/>
@@ -8040,94 +8071,76 @@
     </row>
     <row r="164" spans="1:13" ht="13.5" customHeight="1">
       <c r="A164" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>411</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="B164" s="4"/>
       <c r="C164" s="5" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="E164" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="F164" s="8" t="s">
-        <v>414</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="F164" s="4"/>
       <c r="G164" s="4"/>
-      <c r="H164" s="4"/>
+      <c r="H164" s="8" t="s">
+        <v>403</v>
+      </c>
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
       <c r="K164" s="4"/>
       <c r="L164" s="4"/>
-      <c r="M164" s="8" t="s">
-        <v>415</v>
-      </c>
+      <c r="M164" s="5"/>
     </row>
     <row r="165" spans="1:13" ht="13.5" customHeight="1">
       <c r="A165" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="B165" s="5" t="s">
-        <v>411</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="B165" s="4"/>
       <c r="C165" s="5" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>418</v>
+        <v>76</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="G165" s="4"/>
-      <c r="H165" s="8" t="s">
-        <v>418</v>
-      </c>
+      <c r="H165" s="4"/>
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
       <c r="L165" s="4"/>
-      <c r="M165" s="8" t="s">
-        <v>415</v>
-      </c>
+      <c r="M165" s="5"/>
     </row>
     <row r="166" spans="1:13" ht="13.5" customHeight="1">
       <c r="A166" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B166" s="5" t="s">
-        <v>411</v>
-      </c>
+      <c r="B166" s="5"/>
       <c r="C166" s="5" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="F166" s="8" t="s">
-        <v>421</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="F166" s="4"/>
       <c r="G166" s="4"/>
-      <c r="H166" s="8" t="s">
-        <v>421</v>
-      </c>
+      <c r="H166" s="4"/>
       <c r="I166" s="4"/>
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
       <c r="L166" s="4"/>
-      <c r="M166" s="8" t="s">
-        <v>415</v>
-      </c>
+      <c r="M166" s="5"/>
     </row>
     <row r="167" spans="1:13" ht="13.5" customHeight="1">
       <c r="A167" s="5" t="s">
@@ -8137,21 +8150,19 @@
         <v>411</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="G167" s="4"/>
-      <c r="H167" s="8" t="s">
-        <v>424</v>
-      </c>
+      <c r="H167" s="4"/>
       <c r="I167" s="4"/>
       <c r="J167" s="4"/>
       <c r="K167" s="4"/>
@@ -8160,103 +8171,119 @@
         <v>415</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="15" customHeight="1">
+    <row r="168" spans="1:13" ht="13.5" customHeight="1">
       <c r="A168" s="5" t="s">
         <v>407</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="E168" s="4"/>
-      <c r="F168" s="4"/>
+        <v>417</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>418</v>
+      </c>
       <c r="G168" s="4"/>
-      <c r="H168" s="4"/>
-      <c r="I168" s="8" t="s">
-        <v>428</v>
-      </c>
+      <c r="H168" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="I168" s="4"/>
       <c r="J168" s="4"/>
       <c r="K168" s="4"/>
       <c r="L168" s="4"/>
-      <c r="M168" s="5"/>
+      <c r="M168" s="8" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="169" spans="1:13" ht="13.5" customHeight="1">
       <c r="A169" s="5" t="s">
         <v>407</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="E169" s="4"/>
-      <c r="F169" s="4"/>
+        <v>420</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>421</v>
+      </c>
       <c r="G169" s="4"/>
-      <c r="H169" s="4"/>
+      <c r="H169" s="8" t="s">
+        <v>421</v>
+      </c>
       <c r="I169" s="4"/>
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
       <c r="L169" s="4"/>
-      <c r="M169" s="5"/>
+      <c r="M169" s="8" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="170" spans="1:13" ht="13.5" customHeight="1">
       <c r="A170" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B170" s="7" t="s">
-        <v>431</v>
+      <c r="B170" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="E170" s="4"/>
-      <c r="F170" s="4"/>
+        <v>423</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>424</v>
+      </c>
       <c r="G170" s="4"/>
-      <c r="H170" s="4"/>
-      <c r="I170" s="8" t="s">
-        <v>434</v>
-      </c>
+      <c r="H170" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="I170" s="4"/>
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
       <c r="L170" s="4"/>
-      <c r="M170" s="5"/>
-    </row>
-    <row r="171" spans="1:13" ht="13.5" customHeight="1">
+      <c r="M170" s="8" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" ht="15" customHeight="1">
       <c r="A171" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B171" s="7" t="s">
-        <v>431</v>
+      <c r="B171" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="F171" s="8" t="s">
-        <v>437</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4"/>
       <c r="G171" s="4"/>
-      <c r="H171" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="I171" s="4"/>
+      <c r="H171" s="4"/>
+      <c r="I171" s="8" t="s">
+        <v>428</v>
+      </c>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
       <c r="L171" s="4"/>
@@ -8266,22 +8293,20 @@
       <c r="A172" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B172" s="7" t="s">
-        <v>431</v>
+      <c r="B172" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
       <c r="H172" s="4"/>
-      <c r="I172" s="8" t="s">
-        <v>434</v>
-      </c>
+      <c r="I172" s="4"/>
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
       <c r="L172" s="4"/>
@@ -8295,17 +8320,17 @@
         <v>431</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
       <c r="H173" s="4"/>
-      <c r="I173" s="10" t="s">
-        <v>442</v>
+      <c r="I173" s="8" t="s">
+        <v>434</v>
       </c>
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
@@ -8320,18 +8345,22 @@
         <v>431</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="E174" s="4"/>
-      <c r="F174" s="4"/>
+        <v>436</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>437</v>
+      </c>
       <c r="G174" s="4"/>
-      <c r="H174" s="4"/>
-      <c r="I174" s="10" t="s">
-        <v>442</v>
-      </c>
+      <c r="H174" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="I174" s="4"/>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
       <c r="L174" s="4"/>
@@ -8345,17 +8374,17 @@
         <v>431</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
       <c r="G175" s="4"/>
       <c r="H175" s="4"/>
-      <c r="I175" s="10" t="s">
-        <v>447</v>
+      <c r="I175" s="8" t="s">
+        <v>434</v>
       </c>
       <c r="J175" s="4"/>
       <c r="K175" s="4"/>
@@ -8370,22 +8399,18 @@
         <v>431</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="E176" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="F176" s="8" t="s">
-        <v>450</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4"/>
       <c r="G176" s="4"/>
-      <c r="H176" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="I176" s="4"/>
+      <c r="H176" s="4"/>
+      <c r="I176" s="10" t="s">
+        <v>442</v>
+      </c>
       <c r="J176" s="4"/>
       <c r="K176" s="4"/>
       <c r="L176" s="4"/>
@@ -8395,24 +8420,22 @@
       <c r="A177" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B177" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="D177" s="45" t="s">
-        <v>659</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="F177" s="8"/>
+      <c r="B177" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D177" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4"/>
       <c r="G177" s="4"/>
-      <c r="H177" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="I177" s="4"/>
+      <c r="H177" s="4"/>
+      <c r="I177" s="10" t="s">
+        <v>442</v>
+      </c>
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
       <c r="L177" s="4"/>
@@ -8422,24 +8445,22 @@
       <c r="A178" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B178" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="D178" s="45" t="s">
-        <v>658</v>
-      </c>
-      <c r="E178" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="F178" s="8"/>
+      <c r="B178" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D178" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="E178" s="4"/>
+      <c r="F178" s="4"/>
       <c r="G178" s="4"/>
-      <c r="H178" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="I178" s="4"/>
+      <c r="H178" s="4"/>
+      <c r="I178" s="10" t="s">
+        <v>447</v>
+      </c>
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
       <c r="L178" s="4"/>
@@ -8449,22 +8470,24 @@
       <c r="A179" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B179" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D179" s="17" t="s">
-        <v>453</v>
+      <c r="B179" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D179" s="15" t="s">
+        <v>449</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="F179" s="4"/>
+        <v>450</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="G179" s="4"/>
       <c r="H179" s="8" t="s">
-        <v>660</v>
+        <v>450</v>
       </c>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
@@ -8480,18 +8503,18 @@
         <v>451</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="D180" s="17" t="s">
-        <v>456</v>
+        <v>656</v>
+      </c>
+      <c r="D180" s="45" t="s">
+        <v>659</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="F180" s="4"/>
+        <v>662</v>
+      </c>
+      <c r="F180" s="8"/>
       <c r="G180" s="4"/>
       <c r="H180" s="8" t="s">
-        <v>457</v>
+        <v>662</v>
       </c>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
@@ -8507,18 +8530,18 @@
         <v>451</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="D181" s="17" t="s">
-        <v>459</v>
+        <v>657</v>
+      </c>
+      <c r="D181" s="45" t="s">
+        <v>658</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="F181" s="4"/>
+        <v>661</v>
+      </c>
+      <c r="F181" s="8"/>
       <c r="G181" s="4"/>
       <c r="H181" s="8" t="s">
-        <v>460</v>
+        <v>661</v>
       </c>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
@@ -8531,21 +8554,21 @@
         <v>407</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>655</v>
+        <v>451</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D182" s="17" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
       <c r="H182" s="8" t="s">
-        <v>463</v>
+        <v>660</v>
       </c>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
@@ -8557,20 +8580,22 @@
       <c r="A183" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B183" s="22" t="s">
-        <v>464</v>
-      </c>
-      <c r="C183" s="22" t="s">
-        <v>465</v>
-      </c>
-      <c r="D183" s="27" t="s">
-        <v>466</v>
-      </c>
-      <c r="E183" s="5"/>
+      <c r="B183" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="D183" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>457</v>
+      </c>
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
       <c r="H183" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
@@ -8582,20 +8607,22 @@
       <c r="A184" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B184" s="22" t="s">
-        <v>464</v>
-      </c>
-      <c r="C184" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="D184" s="27" t="s">
-        <v>469</v>
-      </c>
-      <c r="E184" s="5"/>
+      <c r="B184" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="D184" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>460</v>
+      </c>
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
       <c r="H184" s="8" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
@@ -8607,20 +8634,22 @@
       <c r="A185" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B185" s="22" t="s">
-        <v>464</v>
-      </c>
-      <c r="C185" s="22" t="s">
-        <v>471</v>
-      </c>
-      <c r="D185" s="28" t="s">
-        <v>472</v>
-      </c>
-      <c r="E185" s="5"/>
+      <c r="B185" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="D185" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>463</v>
+      </c>
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
       <c r="H185" s="8" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="I185" s="4"/>
       <c r="J185" s="4"/>
@@ -8636,16 +8665,16 @@
         <v>464</v>
       </c>
       <c r="C186" s="22" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="D186" s="27" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="E186" s="5"/>
       <c r="F186" s="4"/>
       <c r="G186" s="4"/>
       <c r="H186" s="8" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
@@ -8661,16 +8690,16 @@
         <v>464</v>
       </c>
       <c r="C187" s="22" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="D187" s="27" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="E187" s="5"/>
       <c r="F187" s="4"/>
       <c r="G187" s="4"/>
       <c r="H187" s="8" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
@@ -8680,22 +8709,24 @@
     </row>
     <row r="188" spans="1:13" ht="13.5" customHeight="1">
       <c r="A188" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="B188" s="22"/>
+        <v>407</v>
+      </c>
+      <c r="B188" s="22" t="s">
+        <v>464</v>
+      </c>
       <c r="C188" s="22" t="s">
-        <v>664</v>
-      </c>
-      <c r="D188" s="46" t="s">
-        <v>663</v>
+        <v>471</v>
+      </c>
+      <c r="D188" s="28" t="s">
+        <v>472</v>
       </c>
       <c r="E188" s="5"/>
       <c r="F188" s="4"/>
       <c r="G188" s="4"/>
-      <c r="H188" s="8"/>
-      <c r="I188" s="4" t="s">
-        <v>665</v>
-      </c>
+      <c r="H188" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="I188" s="4"/>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
       <c r="L188" s="4"/>
@@ -8703,50 +8734,48 @@
     </row>
     <row r="189" spans="1:13" ht="13.5" customHeight="1">
       <c r="A189" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="B189" s="4"/>
-      <c r="C189" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="D189" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="E189" s="8" t="s">
-        <v>320</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="B189" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="C189" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="D189" s="27" t="s">
+        <v>475</v>
+      </c>
+      <c r="E189" s="5"/>
       <c r="F189" s="4"/>
       <c r="G189" s="4"/>
-      <c r="H189" s="5"/>
-      <c r="I189" s="23" t="s">
-        <v>483</v>
-      </c>
+      <c r="H189" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="I189" s="4"/>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
       <c r="L189" s="4"/>
       <c r="M189" s="5"/>
     </row>
     <row r="190" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A190" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="D190" s="15" t="s">
-        <v>487</v>
-      </c>
-      <c r="E190" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="F190" s="8" t="s">
-        <v>323</v>
-      </c>
+      <c r="A190" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B190" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="C190" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="D190" s="27" t="s">
+        <v>478</v>
+      </c>
+      <c r="E190" s="5"/>
+      <c r="F190" s="4"/>
       <c r="G190" s="4"/>
-      <c r="H190" s="4"/>
+      <c r="H190" s="8" t="s">
+        <v>479</v>
+      </c>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
@@ -8754,54 +8783,48 @@
       <c r="M190" s="5"/>
     </row>
     <row r="191" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A191" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B191" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="D191" s="15" t="s">
-        <v>490</v>
-      </c>
-      <c r="E191" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="F191" s="8" t="s">
-        <v>323</v>
-      </c>
+      <c r="A191" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B191" s="22"/>
+      <c r="C191" s="22" t="s">
+        <v>664</v>
+      </c>
+      <c r="D191" s="46" t="s">
+        <v>663</v>
+      </c>
+      <c r="E191" s="5"/>
+      <c r="F191" s="4"/>
       <c r="G191" s="4"/>
-      <c r="H191" s="4"/>
-      <c r="I191" s="4"/>
+      <c r="H191" s="8"/>
+      <c r="I191" s="4" t="s">
+        <v>665</v>
+      </c>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
       <c r="L191" s="4"/>
       <c r="M191" s="5"/>
     </row>
     <row r="192" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A192" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B192" s="5" t="s">
-        <v>492</v>
-      </c>
+      <c r="A192" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B192" s="4"/>
       <c r="C192" s="5" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>493</v>
-      </c>
-      <c r="E192" s="4"/>
-      <c r="F192" s="8" t="s">
-        <v>494</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="F192" s="4"/>
       <c r="G192" s="4"/>
-      <c r="H192" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="I192" s="4"/>
+      <c r="H192" s="5"/>
+      <c r="I192" s="23" t="s">
+        <v>483</v>
+      </c>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
       <c r="L192" s="4"/>
@@ -8812,24 +8835,22 @@
         <v>484</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="D193" s="15" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>498</v>
+        <v>323</v>
       </c>
       <c r="G193" s="4"/>
-      <c r="H193" s="8" t="s">
-        <v>498</v>
-      </c>
+      <c r="H193" s="4"/>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
@@ -8841,24 +8862,22 @@
         <v>484</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="D194" s="15" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>23</v>
+        <v>491</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>23</v>
+        <v>323</v>
       </c>
       <c r="G194" s="4"/>
-      <c r="H194" s="8" t="s">
-        <v>23</v>
-      </c>
+      <c r="H194" s="4"/>
       <c r="I194" s="4"/>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
@@ -8869,20 +8888,24 @@
       <c r="A195" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="B195" s="4"/>
+      <c r="B195" s="5" t="s">
+        <v>492</v>
+      </c>
       <c r="C195" s="5" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="D195" s="15" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="E195" s="4"/>
-      <c r="F195" s="4"/>
+      <c r="F195" s="8" t="s">
+        <v>494</v>
+      </c>
       <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
-      <c r="I195" s="8" t="s">
-        <v>503</v>
-      </c>
+      <c r="H195" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="I195" s="4"/>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
       <c r="L195" s="4"/>
@@ -8890,24 +8913,28 @@
     </row>
     <row r="196" spans="1:13" ht="13.5" customHeight="1">
       <c r="A196" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="B196" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="C196" s="7" t="s">
-        <v>506</v>
+        <v>484</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>496</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>507</v>
-      </c>
-      <c r="E196" s="4"/>
-      <c r="F196" s="4"/>
+        <v>497</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>498</v>
+      </c>
       <c r="G196" s="4"/>
-      <c r="H196" s="4"/>
-      <c r="I196" s="10" t="s">
-        <v>508</v>
-      </c>
+      <c r="H196" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="I196" s="4"/>
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
       <c r="L196" s="4"/>
@@ -8915,24 +8942,26 @@
     </row>
     <row r="197" spans="1:13" ht="13.5" customHeight="1">
       <c r="A197" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="B197" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="C197" s="7" t="s">
-        <v>509</v>
+        <v>484</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>499</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="F197" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="G197" s="4"/>
       <c r="H197" s="8" t="s">
-        <v>320</v>
+        <v>23</v>
       </c>
       <c r="I197" s="4"/>
       <c r="J197" s="4"/>
@@ -8942,23 +8971,21 @@
     </row>
     <row r="198" spans="1:13" ht="13.5" customHeight="1">
       <c r="A198" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="B198" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="C198" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="D198" s="29" t="s">
-        <v>513</v>
-      </c>
-      <c r="E198" s="30"/>
-      <c r="F198" s="30"/>
-      <c r="G198" s="30"/>
-      <c r="H198" s="31"/>
-      <c r="I198" s="10" t="s">
-        <v>514</v>
+        <v>484</v>
+      </c>
+      <c r="B198" s="4"/>
+      <c r="C198" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D198" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
+      <c r="G198" s="4"/>
+      <c r="H198" s="4"/>
+      <c r="I198" s="8" t="s">
+        <v>503</v>
       </c>
       <c r="J198" s="4"/>
       <c r="K198" s="4"/>
@@ -8970,23 +8997,21 @@
         <v>504</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>516</v>
-      </c>
-      <c r="E199" s="8" t="s">
-        <v>517</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="E199" s="4"/>
       <c r="F199" s="4"/>
       <c r="G199" s="4"/>
-      <c r="H199" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="I199" s="4"/>
+      <c r="H199" s="4"/>
+      <c r="I199" s="10" t="s">
+        <v>508</v>
+      </c>
       <c r="J199" s="4"/>
       <c r="K199" s="4"/>
       <c r="L199" s="4"/>
@@ -8997,20 +9022,22 @@
         <v>504</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="E200" s="4"/>
-      <c r="F200" s="8" t="s">
-        <v>521</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="F200" s="4"/>
       <c r="G200" s="4"/>
-      <c r="H200" s="4"/>
+      <c r="H200" s="8" t="s">
+        <v>320</v>
+      </c>
       <c r="I200" s="4"/>
       <c r="J200" s="4"/>
       <c r="K200" s="4"/>
@@ -9022,21 +9049,21 @@
         <v>504</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="D201" s="15" t="s">
-        <v>523</v>
-      </c>
-      <c r="E201" s="4"/>
-      <c r="F201" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="G201" s="4"/>
-      <c r="H201" s="4"/>
-      <c r="I201" s="4"/>
+        <v>512</v>
+      </c>
+      <c r="D201" s="29" t="s">
+        <v>513</v>
+      </c>
+      <c r="E201" s="30"/>
+      <c r="F201" s="30"/>
+      <c r="G201" s="30"/>
+      <c r="H201" s="31"/>
+      <c r="I201" s="10" t="s">
+        <v>514</v>
+      </c>
       <c r="J201" s="4"/>
       <c r="K201" s="4"/>
       <c r="L201" s="4"/>
@@ -9047,20 +9074,22 @@
         <v>504</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>526</v>
-      </c>
-      <c r="E202" s="4"/>
-      <c r="F202" s="8" t="s">
-        <v>527</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F202" s="4"/>
       <c r="G202" s="4"/>
-      <c r="H202" s="4"/>
+      <c r="H202" s="8" t="s">
+        <v>517</v>
+      </c>
       <c r="I202" s="4"/>
       <c r="J202" s="4"/>
       <c r="K202" s="4"/>
@@ -9075,14 +9104,14 @@
         <v>518</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="E203" s="4"/>
       <c r="F203" s="8" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="G203" s="4"/>
       <c r="H203" s="4"/>
@@ -9100,14 +9129,14 @@
         <v>518</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="E204" s="4"/>
       <c r="F204" s="8" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="G204" s="4"/>
       <c r="H204" s="4"/>
@@ -9125,14 +9154,14 @@
         <v>518</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="D205" s="15" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="E205" s="4"/>
       <c r="F205" s="8" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="G205" s="4"/>
       <c r="H205" s="4"/>
@@ -9150,14 +9179,14 @@
         <v>518</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="E206" s="4"/>
       <c r="F206" s="8" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="G206" s="4"/>
       <c r="H206" s="4"/>
@@ -9175,14 +9204,14 @@
         <v>518</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E207" s="4"/>
       <c r="F207" s="8" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="G207" s="4"/>
       <c r="H207" s="4"/>
@@ -9200,14 +9229,14 @@
         <v>518</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="E208" s="4"/>
       <c r="F208" s="8" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="G208" s="4"/>
       <c r="H208" s="4"/>
@@ -9225,14 +9254,14 @@
         <v>518</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="E209" s="4"/>
       <c r="F209" s="8" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="G209" s="4"/>
       <c r="H209" s="4"/>
@@ -9250,14 +9279,14 @@
         <v>518</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="D210" s="15" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="E210" s="4"/>
       <c r="F210" s="8" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="G210" s="4"/>
       <c r="H210" s="4"/>
@@ -9275,14 +9304,14 @@
         <v>518</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E211" s="4"/>
       <c r="F211" s="8" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="G211" s="4"/>
       <c r="H211" s="4"/>
@@ -9300,14 +9329,14 @@
         <v>518</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E212" s="4"/>
       <c r="F212" s="8" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="G212" s="4"/>
       <c r="H212" s="4"/>
@@ -9321,20 +9350,22 @@
       <c r="A213" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="B213" s="7"/>
+      <c r="B213" s="7" t="s">
+        <v>518</v>
+      </c>
       <c r="C213" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="D213" s="45" t="s">
-        <v>642</v>
+        <v>549</v>
+      </c>
+      <c r="D213" s="15" t="s">
+        <v>550</v>
       </c>
       <c r="E213" s="4"/>
-      <c r="F213" s="8"/>
+      <c r="F213" s="8" t="s">
+        <v>551</v>
+      </c>
       <c r="G213" s="4"/>
       <c r="H213" s="4"/>
-      <c r="I213" s="4" t="s">
-        <v>643</v>
-      </c>
+      <c r="I213" s="4"/>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
       <c r="L213" s="4"/>
@@ -9345,21 +9376,21 @@
         <v>504</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>558</v>
+        <v>518</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E214" s="4"/>
-      <c r="F214" s="4"/>
+      <c r="F214" s="8" t="s">
+        <v>554</v>
+      </c>
       <c r="G214" s="4"/>
       <c r="H214" s="4"/>
-      <c r="I214" s="23" t="s">
-        <v>561</v>
-      </c>
+      <c r="I214" s="4"/>
       <c r="J214" s="4"/>
       <c r="K214" s="4"/>
       <c r="L214" s="4"/>
@@ -9370,21 +9401,21 @@
         <v>504</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>562</v>
+        <v>518</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="E215" s="4"/>
-      <c r="F215" s="4"/>
+      <c r="F215" s="8" t="s">
+        <v>557</v>
+      </c>
       <c r="G215" s="4"/>
       <c r="H215" s="4"/>
-      <c r="I215" s="23" t="s">
-        <v>565</v>
-      </c>
+      <c r="I215" s="4"/>
       <c r="J215" s="4"/>
       <c r="K215" s="4"/>
       <c r="L215" s="4"/>
@@ -9394,21 +9425,19 @@
       <c r="A216" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="B216" s="7" t="s">
-        <v>562</v>
-      </c>
+      <c r="B216" s="7"/>
       <c r="C216" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="D216" s="15" t="s">
-        <v>567</v>
+        <v>641</v>
+      </c>
+      <c r="D216" s="45" t="s">
+        <v>642</v>
       </c>
       <c r="E216" s="4"/>
-      <c r="F216" s="4"/>
+      <c r="F216" s="8"/>
       <c r="G216" s="4"/>
       <c r="H216" s="4"/>
-      <c r="I216" s="23" t="s">
-        <v>568</v>
+      <c r="I216" s="4" t="s">
+        <v>643</v>
       </c>
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
@@ -9420,20 +9449,20 @@
         <v>504</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
       <c r="G217" s="4"/>
       <c r="H217" s="4"/>
-      <c r="I217" s="8" t="s">
-        <v>571</v>
+      <c r="I217" s="23" t="s">
+        <v>561</v>
       </c>
       <c r="J217" s="4"/>
       <c r="K217" s="4"/>
@@ -9442,21 +9471,23 @@
     </row>
     <row r="218" spans="1:13" ht="13.5" customHeight="1">
       <c r="A218" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="B218" s="4"/>
+        <v>504</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>562</v>
+      </c>
       <c r="C218" s="7" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
       <c r="G218" s="4"/>
       <c r="H218" s="4"/>
-      <c r="I218" s="8" t="s">
-        <v>575</v>
+      <c r="I218" s="23" t="s">
+        <v>565</v>
       </c>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
@@ -9465,48 +9496,48 @@
     </row>
     <row r="219" spans="1:13" ht="13.5" customHeight="1">
       <c r="A219" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="B219" s="4"/>
+        <v>504</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>562</v>
+      </c>
       <c r="C219" s="7" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>577</v>
-      </c>
-      <c r="E219" s="23" t="s">
-        <v>578</v>
-      </c>
-      <c r="F219" s="23" t="s">
-        <v>578</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="E219" s="4"/>
+      <c r="F219" s="4"/>
       <c r="G219" s="4"/>
       <c r="H219" s="4"/>
-      <c r="I219" s="4"/>
+      <c r="I219" s="23" t="s">
+        <v>568</v>
+      </c>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
       <c r="L219" s="4"/>
       <c r="M219" s="5"/>
     </row>
     <row r="220" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A220" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="B220" s="24" t="s">
-        <v>580</v>
-      </c>
-      <c r="C220" s="32" t="s">
-        <v>580</v>
-      </c>
-      <c r="D220" s="33" t="s">
-        <v>581</v>
+      <c r="A220" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="D220" s="15" t="s">
+        <v>570</v>
       </c>
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
       <c r="G220" s="4"/>
       <c r="H220" s="4"/>
-      <c r="I220" s="23" t="s">
-        <v>582</v>
+      <c r="I220" s="8" t="s">
+        <v>571</v>
       </c>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
@@ -9514,50 +9545,48 @@
       <c r="M220" s="5"/>
     </row>
     <row r="221" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A221" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="B221" s="24" t="s">
-        <v>580</v>
-      </c>
-      <c r="C221" s="32" t="s">
-        <v>583</v>
+      <c r="A221" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="B221" s="4"/>
+      <c r="C221" s="7" t="s">
+        <v>573</v>
       </c>
       <c r="D221" s="15" t="s">
-        <v>584</v>
-      </c>
-      <c r="E221" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="F221" s="23" t="s">
-        <v>266</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="E221" s="4"/>
+      <c r="F221" s="4"/>
       <c r="G221" s="4"/>
       <c r="H221" s="4"/>
-      <c r="I221" s="4"/>
+      <c r="I221" s="8" t="s">
+        <v>575</v>
+      </c>
       <c r="J221" s="4"/>
       <c r="K221" s="4"/>
       <c r="L221" s="4"/>
       <c r="M221" s="5"/>
     </row>
     <row r="222" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A222" s="5" t="s">
-        <v>579</v>
+      <c r="A222" s="7" t="s">
+        <v>572</v>
       </c>
       <c r="B222" s="4"/>
-      <c r="C222" s="5" t="s">
-        <v>585</v>
+      <c r="C222" s="7" t="s">
+        <v>576</v>
       </c>
       <c r="D222" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="E222" s="4"/>
-      <c r="F222" s="4"/>
+        <v>577</v>
+      </c>
+      <c r="E222" s="23" t="s">
+        <v>578</v>
+      </c>
+      <c r="F222" s="23" t="s">
+        <v>578</v>
+      </c>
       <c r="G222" s="4"/>
       <c r="H222" s="4"/>
-      <c r="I222" s="8" t="s">
-        <v>587</v>
-      </c>
+      <c r="I222" s="4"/>
       <c r="J222" s="4"/>
       <c r="K222" s="4"/>
       <c r="L222" s="4"/>
@@ -9567,19 +9596,21 @@
       <c r="A223" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="B223" s="4"/>
-      <c r="C223" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="D223" s="15" t="s">
-        <v>589</v>
+      <c r="B223" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="C223" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="D223" s="33" t="s">
+        <v>581</v>
       </c>
       <c r="E223" s="4"/>
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
       <c r="H223" s="4"/>
-      <c r="I223" s="10" t="s">
-        <v>590</v>
+      <c r="I223" s="23" t="s">
+        <v>582</v>
       </c>
       <c r="J223" s="4"/>
       <c r="K223" s="4"/>
@@ -9590,20 +9621,24 @@
       <c r="A224" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="B224" s="4"/>
-      <c r="C224" s="7" t="s">
-        <v>591</v>
+      <c r="B224" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="C224" s="32" t="s">
+        <v>583</v>
       </c>
       <c r="D224" s="15" t="s">
-        <v>592</v>
-      </c>
-      <c r="E224" s="4"/>
-      <c r="F224" s="4"/>
+        <v>584</v>
+      </c>
+      <c r="E224" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F224" s="23" t="s">
+        <v>266</v>
+      </c>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
-      <c r="I224" s="8" t="s">
-        <v>593</v>
-      </c>
+      <c r="I224" s="4"/>
       <c r="J224" s="4"/>
       <c r="K224" s="4"/>
       <c r="L224" s="4"/>
@@ -9615,17 +9650,17 @@
       </c>
       <c r="B225" s="4"/>
       <c r="C225" s="5" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="D225" s="15" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="E225" s="4"/>
       <c r="F225" s="4"/>
       <c r="G225" s="4"/>
       <c r="H225" s="4"/>
       <c r="I225" s="8" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
@@ -9637,41 +9672,41 @@
         <v>579</v>
       </c>
       <c r="B226" s="4"/>
-      <c r="C226" s="5" t="s">
-        <v>597</v>
+      <c r="C226" s="7" t="s">
+        <v>588</v>
       </c>
       <c r="D226" s="15" t="s">
-        <v>598</v>
-      </c>
-      <c r="E226" s="8" t="s">
-        <v>599</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="E226" s="4"/>
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
       <c r="H226" s="4"/>
-      <c r="I226" s="4"/>
+      <c r="I226" s="10" t="s">
+        <v>590</v>
+      </c>
       <c r="J226" s="4"/>
       <c r="K226" s="4"/>
       <c r="L226" s="4"/>
       <c r="M226" s="5"/>
     </row>
     <row r="227" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A227" s="7" t="s">
-        <v>600</v>
+      <c r="A227" s="5" t="s">
+        <v>579</v>
       </c>
       <c r="B227" s="4"/>
-      <c r="C227" s="22" t="s">
-        <v>601</v>
-      </c>
-      <c r="D227" s="33" t="s">
-        <v>602</v>
-      </c>
-      <c r="E227" s="5"/>
+      <c r="C227" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="D227" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="E227" s="4"/>
       <c r="F227" s="4"/>
       <c r="G227" s="4"/>
       <c r="H227" s="4"/>
-      <c r="I227" s="23" t="s">
-        <v>603</v>
+      <c r="I227" s="8" t="s">
+        <v>593</v>
       </c>
       <c r="J227" s="4"/>
       <c r="K227" s="4"/>
@@ -9679,22 +9714,22 @@
       <c r="M227" s="5"/>
     </row>
     <row r="228" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A228" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="B228" s="3"/>
-      <c r="C228" s="34" t="s">
-        <v>604</v>
-      </c>
-      <c r="D228" s="35" t="s">
-        <v>605</v>
-      </c>
-      <c r="E228" s="3"/>
+      <c r="A228" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="B228" s="4"/>
+      <c r="C228" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="D228" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="E228" s="4"/>
       <c r="F228" s="4"/>
       <c r="G228" s="4"/>
-      <c r="H228" s="3"/>
+      <c r="H228" s="4"/>
       <c r="I228" s="8" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="J228" s="4"/>
       <c r="K228" s="4"/>
@@ -9702,23 +9737,23 @@
       <c r="M228" s="5"/>
     </row>
     <row r="229" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A229" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="B229" s="3"/>
-      <c r="C229" s="7" t="s">
-        <v>607</v>
-      </c>
-      <c r="D229" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="E229" s="3"/>
+      <c r="A229" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="B229" s="4"/>
+      <c r="C229" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="D229" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="E229" s="8" t="s">
+        <v>599</v>
+      </c>
       <c r="F229" s="4"/>
       <c r="G229" s="4"/>
-      <c r="H229" s="3"/>
-      <c r="I229" s="8" t="s">
-        <v>609</v>
-      </c>
+      <c r="H229" s="4"/>
+      <c r="I229" s="4"/>
       <c r="J229" s="4"/>
       <c r="K229" s="4"/>
       <c r="L229" s="4"/>
@@ -9728,19 +9763,19 @@
       <c r="A230" s="7" t="s">
         <v>600</v>
       </c>
-      <c r="B230" s="3"/>
-      <c r="C230" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="D230" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="E230" s="3"/>
+      <c r="B230" s="4"/>
+      <c r="C230" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="D230" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="E230" s="5"/>
       <c r="F230" s="4"/>
       <c r="G230" s="4"/>
-      <c r="H230" s="3"/>
-      <c r="I230" s="8" t="s">
-        <v>612</v>
+      <c r="H230" s="4"/>
+      <c r="I230" s="23" t="s">
+        <v>603</v>
       </c>
       <c r="J230" s="4"/>
       <c r="K230" s="4"/>
@@ -9749,21 +9784,21 @@
     </row>
     <row r="231" spans="1:13" ht="13.5" customHeight="1">
       <c r="A231" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="B231" s="4"/>
-      <c r="C231" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="D231" s="15" t="s">
-        <v>615</v>
-      </c>
-      <c r="E231" s="4"/>
+        <v>600</v>
+      </c>
+      <c r="B231" s="3"/>
+      <c r="C231" s="34" t="s">
+        <v>604</v>
+      </c>
+      <c r="D231" s="35" t="s">
+        <v>605</v>
+      </c>
+      <c r="E231" s="3"/>
       <c r="F231" s="4"/>
       <c r="G231" s="4"/>
-      <c r="H231" s="4"/>
+      <c r="H231" s="3"/>
       <c r="I231" s="8" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
@@ -9772,21 +9807,21 @@
     </row>
     <row r="232" spans="1:13" ht="13.5" customHeight="1">
       <c r="A232" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="B232" s="4"/>
-      <c r="C232" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="D232" s="36" t="s">
-        <v>618</v>
-      </c>
-      <c r="E232" s="4"/>
+        <v>600</v>
+      </c>
+      <c r="B232" s="3"/>
+      <c r="C232" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="D232" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="E232" s="3"/>
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
-      <c r="H232" s="4"/>
+      <c r="H232" s="3"/>
       <c r="I232" s="8" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="J232" s="4"/>
       <c r="K232" s="4"/>
@@ -9794,22 +9829,22 @@
       <c r="M232" s="5"/>
     </row>
     <row r="233" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A233" s="37" t="s">
-        <v>620</v>
-      </c>
-      <c r="B233" s="38"/>
-      <c r="C233" s="39" t="s">
-        <v>621</v>
-      </c>
-      <c r="D233" s="40" t="s">
-        <v>622</v>
-      </c>
-      <c r="E233" s="41"/>
+      <c r="A233" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="B233" s="3"/>
+      <c r="C233" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="E233" s="3"/>
       <c r="F233" s="4"/>
       <c r="G233" s="4"/>
-      <c r="H233" s="4"/>
+      <c r="H233" s="3"/>
       <c r="I233" s="8" t="s">
-        <v>269</v>
+        <v>612</v>
       </c>
       <c r="J233" s="4"/>
       <c r="K233" s="4"/>
@@ -9817,22 +9852,22 @@
       <c r="M233" s="5"/>
     </row>
     <row r="234" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A234" s="37" t="s">
-        <v>620</v>
-      </c>
-      <c r="B234" s="24"/>
-      <c r="C234" s="42" t="s">
-        <v>255</v>
-      </c>
-      <c r="D234" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="E234" s="3"/>
-      <c r="F234" s="20"/>
-      <c r="G234" s="20"/>
-      <c r="H234" s="3"/>
+      <c r="A234" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B234" s="4"/>
+      <c r="C234" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="D234" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="E234" s="4"/>
+      <c r="F234" s="4"/>
+      <c r="G234" s="4"/>
+      <c r="H234" s="4"/>
       <c r="I234" s="8" t="s">
-        <v>257</v>
+        <v>616</v>
       </c>
       <c r="J234" s="4"/>
       <c r="K234" s="4"/>
@@ -9840,22 +9875,22 @@
       <c r="M234" s="5"/>
     </row>
     <row r="235" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A235" s="37" t="s">
-        <v>620</v>
-      </c>
-      <c r="B235" s="24"/>
-      <c r="C235" s="39" t="s">
-        <v>623</v>
-      </c>
-      <c r="D235" s="40" t="s">
-        <v>624</v>
+      <c r="A235" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B235" s="4"/>
+      <c r="C235" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="D235" s="36" t="s">
+        <v>618</v>
       </c>
       <c r="E235" s="4"/>
       <c r="F235" s="4"/>
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
-      <c r="I235" s="23" t="s">
-        <v>582</v>
+      <c r="I235" s="8" t="s">
+        <v>619</v>
       </c>
       <c r="J235" s="4"/>
       <c r="K235" s="4"/>
@@ -9867,18 +9902,18 @@
         <v>620</v>
       </c>
       <c r="B236" s="38"/>
-      <c r="C236" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="D236" s="44" t="s">
-        <v>232</v>
-      </c>
-      <c r="E236" s="3"/>
-      <c r="F236" s="20"/>
-      <c r="G236" s="20"/>
-      <c r="H236" s="3"/>
+      <c r="C236" s="39" t="s">
+        <v>621</v>
+      </c>
+      <c r="D236" s="40" t="s">
+        <v>622</v>
+      </c>
+      <c r="E236" s="41"/>
+      <c r="F236" s="4"/>
+      <c r="G236" s="4"/>
+      <c r="H236" s="4"/>
       <c r="I236" s="8" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="J236" s="4"/>
       <c r="K236" s="4"/>
@@ -9889,19 +9924,19 @@
       <c r="A237" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B237" s="38"/>
-      <c r="C237" s="5" t="s">
-        <v>245</v>
+      <c r="B237" s="24"/>
+      <c r="C237" s="42" t="s">
+        <v>255</v>
       </c>
       <c r="D237" s="9" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="E237" s="3"/>
       <c r="F237" s="20"/>
       <c r="G237" s="20"/>
       <c r="H237" s="3"/>
       <c r="I237" s="8" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="J237" s="4"/>
       <c r="K237" s="4"/>
@@ -9912,21 +9947,19 @@
       <c r="A238" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B238" s="38" t="s">
-        <v>625</v>
-      </c>
+      <c r="B238" s="24"/>
       <c r="C238" s="39" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D238" s="40" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
       <c r="I238" s="23" t="s">
-        <v>628</v>
+        <v>582</v>
       </c>
       <c r="J238" s="4"/>
       <c r="K238" s="4"/>
@@ -9937,21 +9970,19 @@
       <c r="A239" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B239" s="38" t="s">
-        <v>625</v>
-      </c>
-      <c r="C239" s="39" t="s">
-        <v>629</v>
-      </c>
-      <c r="D239" s="40" t="s">
-        <v>630</v>
-      </c>
-      <c r="E239" s="4"/>
-      <c r="F239" s="4"/>
-      <c r="G239" s="4"/>
-      <c r="H239" s="4"/>
-      <c r="I239" s="23" t="s">
-        <v>631</v>
+      <c r="B239" s="38"/>
+      <c r="C239" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="D239" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="E239" s="3"/>
+      <c r="F239" s="20"/>
+      <c r="G239" s="20"/>
+      <c r="H239" s="3"/>
+      <c r="I239" s="8" t="s">
+        <v>224</v>
       </c>
       <c r="J239" s="4"/>
       <c r="K239" s="4"/>
@@ -9962,21 +9993,19 @@
       <c r="A240" s="37" t="s">
         <v>620</v>
       </c>
-      <c r="B240" s="38" t="s">
-        <v>625</v>
-      </c>
-      <c r="C240" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="D240" s="40" t="s">
-        <v>632</v>
-      </c>
-      <c r="E240" s="4"/>
-      <c r="F240" s="4"/>
-      <c r="G240" s="4"/>
-      <c r="H240" s="4"/>
-      <c r="I240" s="23" t="s">
-        <v>633</v>
+      <c r="B240" s="38"/>
+      <c r="C240" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D240" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E240" s="3"/>
+      <c r="F240" s="20"/>
+      <c r="G240" s="20"/>
+      <c r="H240" s="3"/>
+      <c r="I240" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="J240" s="4"/>
       <c r="K240" s="4"/>
@@ -9984,45 +10013,75 @@
       <c r="M240" s="5"/>
     </row>
     <row r="241" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A241" s="4"/>
-      <c r="B241" s="4"/>
-      <c r="C241" s="4"/>
-      <c r="D241" s="4"/>
+      <c r="A241" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="B241" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="C241" s="39" t="s">
+        <v>626</v>
+      </c>
+      <c r="D241" s="40" t="s">
+        <v>627</v>
+      </c>
       <c r="E241" s="4"/>
       <c r="F241" s="4"/>
       <c r="G241" s="4"/>
       <c r="H241" s="4"/>
-      <c r="I241" s="4"/>
+      <c r="I241" s="23" t="s">
+        <v>628</v>
+      </c>
       <c r="J241" s="4"/>
       <c r="K241" s="4"/>
       <c r="L241" s="4"/>
       <c r="M241" s="5"/>
     </row>
     <row r="242" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A242" s="4"/>
-      <c r="B242" s="4"/>
-      <c r="C242" s="4"/>
-      <c r="D242" s="4"/>
+      <c r="A242" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="B242" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="C242" s="39" t="s">
+        <v>629</v>
+      </c>
+      <c r="D242" s="40" t="s">
+        <v>630</v>
+      </c>
       <c r="E242" s="4"/>
       <c r="F242" s="4"/>
       <c r="G242" s="4"/>
       <c r="H242" s="4"/>
-      <c r="I242" s="4"/>
+      <c r="I242" s="23" t="s">
+        <v>631</v>
+      </c>
       <c r="J242" s="4"/>
       <c r="K242" s="4"/>
       <c r="L242" s="4"/>
       <c r="M242" s="5"/>
     </row>
     <row r="243" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A243" s="4"/>
-      <c r="B243" s="4"/>
-      <c r="C243" s="4"/>
-      <c r="D243" s="4"/>
+      <c r="A243" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="B243" s="38" t="s">
+        <v>625</v>
+      </c>
+      <c r="C243" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="D243" s="40" t="s">
+        <v>632</v>
+      </c>
       <c r="E243" s="4"/>
       <c r="F243" s="4"/>
       <c r="G243" s="4"/>
       <c r="H243" s="4"/>
-      <c r="I243" s="4"/>
+      <c r="I243" s="23" t="s">
+        <v>633</v>
+      </c>
       <c r="J243" s="4"/>
       <c r="K243" s="4"/>
       <c r="L243" s="4"/>
@@ -12788,9 +12847,51 @@
       <c r="L427" s="4"/>
       <c r="M427" s="5"/>
     </row>
-    <row r="428" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="429" spans="1:13" ht="15.75" customHeight="1"/>
-    <row r="430" spans="1:13" ht="15.75" customHeight="1"/>
+    <row r="428" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A428" s="4"/>
+      <c r="B428" s="4"/>
+      <c r="C428" s="4"/>
+      <c r="D428" s="4"/>
+      <c r="E428" s="4"/>
+      <c r="F428" s="4"/>
+      <c r="G428" s="4"/>
+      <c r="H428" s="4"/>
+      <c r="I428" s="4"/>
+      <c r="J428" s="4"/>
+      <c r="K428" s="4"/>
+      <c r="L428" s="4"/>
+      <c r="M428" s="5"/>
+    </row>
+    <row r="429" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A429" s="4"/>
+      <c r="B429" s="4"/>
+      <c r="C429" s="4"/>
+      <c r="D429" s="4"/>
+      <c r="E429" s="4"/>
+      <c r="F429" s="4"/>
+      <c r="G429" s="4"/>
+      <c r="H429" s="4"/>
+      <c r="I429" s="4"/>
+      <c r="J429" s="4"/>
+      <c r="K429" s="4"/>
+      <c r="L429" s="4"/>
+      <c r="M429" s="5"/>
+    </row>
+    <row r="430" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A430" s="4"/>
+      <c r="B430" s="4"/>
+      <c r="C430" s="4"/>
+      <c r="D430" s="4"/>
+      <c r="E430" s="4"/>
+      <c r="F430" s="4"/>
+      <c r="G430" s="4"/>
+      <c r="H430" s="4"/>
+      <c r="I430" s="4"/>
+      <c r="J430" s="4"/>
+      <c r="K430" s="4"/>
+      <c r="L430" s="4"/>
+      <c r="M430" s="5"/>
+    </row>
     <row r="431" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="432" spans="1:13" ht="15.75" customHeight="1"/>
     <row r="433" ht="15.75" customHeight="1"/>
@@ -13385,6 +13486,9 @@
     <row r="1022" ht="15.75" customHeight="1"/>
     <row r="1023" ht="15.75" customHeight="1"/>
     <row r="1024" ht="15.75" customHeight="1"/>
+    <row r="1025" ht="15.75" customHeight="1"/>
+    <row r="1026" ht="15.75" customHeight="1"/>
+    <row r="1027" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="15"/>
   <hyperlinks>
@@ -13448,160 +13552,163 @@
     <hyperlink ref="D62" r:id="rId58" display="https://tileserver.geolonia.com/yaizu-smartmap-tochiyamagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtdG9jaGl5YW1hZ2F3YV9mbG9vZC1kdXJhdGlvbl9tb2RpZmllZHxhZG1pbi11cGxvYWRzL3lhaXp1LXNtYXJ0bWFwLXRvY2hpeWFtYWdhd2FfZmxvb2QtZHVyYXRpb25fbW9kaWZpZWQtMDFKRkMyM1pWWVE3MEowUzdaNTZHWkNKRFojC5eX3JK7qasK2odfocPvh5KVdzgW8GfTWFIWWxO0-OY&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
     <hyperlink ref="D63" r:id="rId59" display="https://tileserver.geolonia.com/yaizu-smartmap-shidatanakagawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtc2hpZGF0YW5ha2FnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkLTAxSkZDMjNYNFlBNDZLMlQxTVdGMVFWODJaI8I_8TmmNT2ZBas2uO_iuv708Hw-rSmd9df6Iy_TRMzO&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
     <hyperlink ref="D64" r:id="rId60" display="https://tileserver.geolonia.com/yaizu-smartmap-otsutanigawa_flood-duration_modified/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkfGFkbWluLXVwbG9hZHMveWFpenUtc21hcnRtYXAtb3RzdXRhbmlnYXdhX2Zsb29kLWR1cmF0aW9uX21vZGlmaWVkLTAxSkZDMjNRNENHRURIR1FLNEtGU1lLMzZBI7KZF6uvKMllQBtCXF86Bop_8GzzniSe6NN1Rp0RaowV&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="D65" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D66" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="D67" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D68" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="D69" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D70" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="D71" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D72" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="D73" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D74" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="D75" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D78" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="D79" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D80" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D81" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D82" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D83" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D84" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D85" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D86" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D87" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D88" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D89" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D90" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D91" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D92" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D93" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D94" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D95" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D96" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D97" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D105" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D111" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D112" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D113" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D114" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D115" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D116" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="D117" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D118" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="D119" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="D120" r:id="rId102" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="D121" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="D122" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="D123" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="D124" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="D125" r:id="rId107" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="D126" r:id="rId108" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="D127" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="D128" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="D129" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="D130" r:id="rId112" display="https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="D131" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="D132" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="D133" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="D134" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="D135" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="D136" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="D137" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="D138" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="D139" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="D140" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="D141" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="D142" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="D143" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="D144" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="D145" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="D146" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="D147" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="D148" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="D149" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="D150" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="D151" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="D152" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="D153" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="D154" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="D155" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="D156" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="D157" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="D158" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="D159" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="D160" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="D161" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="D162" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="D168" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="D169" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="D170" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="D171" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="D172" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="D173" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="D174" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="D175" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="D176" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="D179" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="D180" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="D181" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="D182" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="D183" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="D184" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="D186" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="D187" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="D189" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="D190" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="D191" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="D192" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="D193" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="D194" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="D195" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="D196" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="D197" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="D198" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="D199" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="D200" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="D201" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="D202" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="D203" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="D204" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="D205" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="D206" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="D207" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="D208" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="D209" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="D210" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="D211" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="D212" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="D214" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="D215" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="D216" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="D217" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="D218" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="D219" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="D220" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="D222" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="D223" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="D224" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="D225" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="D226" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="D227" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="D228" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="D229" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="D230" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="D231" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="D232" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="D234" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="D236" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="D237" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="D66" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="D68" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="D69" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D70" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="D71" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="D72" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="D73" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="D74" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="D75" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="D76" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="D77" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="D80" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D81" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="D82" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D83" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D84" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D85" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D86" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D87" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D88" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D89" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D90" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D91" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D92" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D93" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D94" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D95" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D96" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D97" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D98" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D99" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D108" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D114" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D115" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D116" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D117" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D118" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="D119" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="D120" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="D121" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D122" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="D123" r:id="rId102" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_1-1%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C_%E9%9E%8D%E6%8E%9B%E5%B3%A0_%E9%AB%98%E8%8D%89%E5%B1%B1_%E7%9F%B3%E8%84%87%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="D124" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="D125" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="D126" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="D127" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="D128" r:id="rId107" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-1%E5%85%A5%E5%8F%A3_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E3%81%AE%E9%87%8C%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="D129" r:id="rId108" display="https://yaizu-smartcity.jp/tiles/%E3%83%8F%E3%82%A4%E3%82%AD%E3%83%B3%E3%82%B0%E3%82%B3%E3%83%BC%E3%82%B9_3-2%E9%9D%99%E5%B2%A1%E5%B8%82_%E5%B0%8F%E5%9D%82_%E6%97%A5%E6%9C%AC%E5%9D%82%E5%B3%A0_%E8%8A%B1%E6%B2%A2%E5%B1%B1_%E7%9F%B3%E9%83%A8%E3%82%B3%E3%83%BC%E3%82%B9/tiles.json" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="D130" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="D131" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="D132" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="D133" r:id="rId112" display="https://tileserver.geolonia.com/yaizu-smartmap-airplane-photo-20250107/tiles/{z}/{x}/{y}.png?v=eWFpenUtc21hcnRtYXAtYWlycGxhbmUtcGhvdG8tMjAyNTAxMDd8YWRtaW4tdXBsb2Fkcy95YWl6dS1zbWFydG1hcC1haXJwbGFuZS1waG90by0yMDI1MDEwNy0wMUpHWjZYNFREVkRGWENaUTZLMFI0OTI3SCNrke6hy68odQSAeYKKqMfyyh60LcOUvZIyg0WHjX-LWA&amp;key=bb4125ebc1ba442da48d3556f1fe13f5" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="D134" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="D135" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="D136" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="D137" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="D138" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="D139" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="D140" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="D141" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="D142" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="D143" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="D144" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="D145" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="D146" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="D147" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="D148" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="D149" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="D150" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="D151" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="D152" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="D153" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="D154" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="D155" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="D156" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="D157" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="D158" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="D159" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="D160" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="D161" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="D162" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="D163" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="D164" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="D165" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="D171" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="D172" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="D173" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="D174" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="D175" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="D176" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="D177" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="D178" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="D179" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="D182" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="D183" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="D184" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="D185" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="D186" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="D187" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="D189" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="D190" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="D192" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="D193" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="D194" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="D195" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="D196" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="D197" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="D198" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="D199" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="D200" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="D201" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="D202" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="D203" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="D204" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="D205" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="D206" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="D207" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="D208" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="D209" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="D210" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="D211" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="D212" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="D213" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="D214" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="D215" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="D217" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="D218" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="D219" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="D220" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="D221" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="D222" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="D223" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="D225" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="D226" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="D227" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="D228" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="D229" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="D230" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="D231" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="D232" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="D233" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="D234" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="D235" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="D237" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="D239" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="D240" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
     <hyperlink ref="D16" r:id="rId207" xr:uid="{101A33D7-B7BA-422E-B2FC-342D5148D1EA}"/>
-    <hyperlink ref="D213" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
-    <hyperlink ref="D77" r:id="rId209" xr:uid="{15E62A8C-2F55-4EC5-B29A-D16518F2E4D9}"/>
-    <hyperlink ref="D76" r:id="rId210" xr:uid="{FC2D964E-B283-4703-AAB9-28EC36520D76}"/>
+    <hyperlink ref="D216" r:id="rId208" xr:uid="{5275DA95-4BC8-4D91-A893-12062A102F77}"/>
+    <hyperlink ref="D79" r:id="rId209" xr:uid="{15E62A8C-2F55-4EC5-B29A-D16518F2E4D9}"/>
+    <hyperlink ref="D78" r:id="rId210" xr:uid="{FC2D964E-B283-4703-AAB9-28EC36520D76}"/>
     <hyperlink ref="D17" r:id="rId211" xr:uid="{BAFD46EC-62AB-41E1-B82A-03A62E913A64}"/>
-    <hyperlink ref="D178" r:id="rId212" xr:uid="{1B2883BA-7428-4C3B-8B0A-0E84AA25F727}"/>
-    <hyperlink ref="D177" r:id="rId213" xr:uid="{94880ED8-4B43-4BE4-B733-30DFCED08C71}"/>
-    <hyperlink ref="D188" r:id="rId214" xr:uid="{7A4126AD-D394-4C29-AE05-60E7F949761F}"/>
+    <hyperlink ref="D181" r:id="rId212" xr:uid="{1B2883BA-7428-4C3B-8B0A-0E84AA25F727}"/>
+    <hyperlink ref="D180" r:id="rId213" xr:uid="{94880ED8-4B43-4BE4-B733-30DFCED08C71}"/>
+    <hyperlink ref="D191" r:id="rId214" xr:uid="{7A4126AD-D394-4C29-AE05-60E7F949761F}"/>
+    <hyperlink ref="D65" r:id="rId215" xr:uid="{349D2697-0B58-452C-89DF-D93FE46DA3AE}"/>
+    <hyperlink ref="D67" r:id="rId216" xr:uid="{EE2B1F06-D337-4BD7-A0B2-6A0065E96182}"/>
+    <hyperlink ref="D104" r:id="rId217" xr:uid="{EF3D1E05-BE62-412D-99DD-0C89EB50EF52}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
